--- a/testdata.xlsx
+++ b/testdata.xlsx
@@ -8,12 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sshiwani\workspace\find-information-products-services-tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3F78E4F-24B3-4DAC-AED2-E19EF79D17E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55804917-92F1-4B7D-BF36-02503B3D2E86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="products" sheetId="1" r:id="rId1"/>
+    <sheet name="category_phase" sheetId="1" r:id="rId1"/>
+    <sheet name="category_channel" sheetId="2" r:id="rId2"/>
+    <sheet name="category_group" sheetId="3" r:id="rId3"/>
+    <sheet name="category_type" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="131">
   <si>
     <t>products?phase=request</t>
   </si>
@@ -169,6 +172,255 @@
   </si>
   <si>
     <t>Checkbox_Locator</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text('Chat')</t>
+  </si>
+  <si>
+    <t>Remove this filter Chat</t>
+  </si>
+  <si>
+    <t>products?channel=chat</t>
+  </si>
+  <si>
+    <t>//h3[normalize-space()='Channel']</t>
+  </si>
+  <si>
+    <t>#channel-chat</t>
+  </si>
+  <si>
+    <t>products?channel=email</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text('Email')</t>
+  </si>
+  <si>
+    <t>Remove this filter Email</t>
+  </si>
+  <si>
+    <t>#channel-email</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text('Face-to-face')</t>
+  </si>
+  <si>
+    <t>products?channel=face-to-face</t>
+  </si>
+  <si>
+    <t>Remove this filter Face-to-face</t>
+  </si>
+  <si>
+    <t>#channel-face-to-face</t>
+  </si>
+  <si>
+    <t>products?channel=native-app</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text('Native-app')</t>
+  </si>
+  <si>
+    <t>Remove this filter Native-app</t>
+  </si>
+  <si>
+    <t>#channel-native-app</t>
+  </si>
+  <si>
+    <t>products?channel=other-digital-media</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text('Other digital media')</t>
+  </si>
+  <si>
+    <t>Remove this filter Other digital media</t>
+  </si>
+  <si>
+    <t>#channel-other-digital-media</t>
+  </si>
+  <si>
+    <t>products?channel=phone</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text('Phone')</t>
+  </si>
+  <si>
+    <t>Remove this filter Phone</t>
+  </si>
+  <si>
+    <t>#channel-phone</t>
+  </si>
+  <si>
+    <t>products?channel=print-media</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text('Print media')</t>
+  </si>
+  <si>
+    <t>Remove this filter Print media</t>
+  </si>
+  <si>
+    <t>#channel-print-media</t>
+  </si>
+  <si>
+    <t>products?channel=sms</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text('SMS')</t>
+  </si>
+  <si>
+    <t>Remove this filter SMS</t>
+  </si>
+  <si>
+    <t>#channel-sms</t>
+  </si>
+  <si>
+    <t>products?channel=web</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text('Web')</t>
+  </si>
+  <si>
+    <t>Remove this filter Web</t>
+  </si>
+  <si>
+    <t>#channel-web</t>
+  </si>
+  <si>
+    <t>products?group=families</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text('families')</t>
+  </si>
+  <si>
+    <t>Remove this filter families</t>
+  </si>
+  <si>
+    <t>//h3[normalize-space()='Group']</t>
+  </si>
+  <si>
+    <t>#group-families</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text('regions')</t>
+  </si>
+  <si>
+    <t>Remove this filter regions</t>
+  </si>
+  <si>
+    <t>#group-regions</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text('schools')</t>
+  </si>
+  <si>
+    <t>Remove this filter schools</t>
+  </si>
+  <si>
+    <t>#group-schools</t>
+  </si>
+  <si>
+    <t>products?group=schools</t>
+  </si>
+  <si>
+    <t>products?group=regions</t>
+  </si>
+  <si>
+    <t>products?group=skills</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text('skills')</t>
+  </si>
+  <si>
+    <t>Remove this filter skills</t>
+  </si>
+  <si>
+    <t>#group-skills</t>
+  </si>
+  <si>
+    <t>products?group=operations-and-infrastructure</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text('operations-and-infrastructure')</t>
+  </si>
+  <si>
+    <t>Remove this filter operations-and-infrastructure</t>
+  </si>
+  <si>
+    <t>#group-operations-and-infrastructure</t>
+  </si>
+  <si>
+    <t>products?group=cxd</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text('cxd')</t>
+  </si>
+  <si>
+    <t>Remove this filter cxd</t>
+  </si>
+  <si>
+    <t>#group-cxd</t>
+  </si>
+  <si>
+    <t>products?group=funding</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text('funding')</t>
+  </si>
+  <si>
+    <t>Remove this filter funding</t>
+  </si>
+  <si>
+    <t>#group-funding</t>
+  </si>
+  <si>
+    <t>products?type=api</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text('API')</t>
+  </si>
+  <si>
+    <t>Remove this filter API</t>
+  </si>
+  <si>
+    <t>//h3[normalize-space()='Type']</t>
+  </si>
+  <si>
+    <t>#type-api</t>
+  </si>
+  <si>
+    <t>products?type=campaign</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text('Campaign')</t>
+  </si>
+  <si>
+    <t>Remove this filter Campaign</t>
+  </si>
+  <si>
+    <t>#type-campaign</t>
+  </si>
+  <si>
+    <t>products?type=information</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Information')</t>
+  </si>
+  <si>
+    <t>Remove this filter Information</t>
+  </si>
+  <si>
+    <t>#type-information</t>
+  </si>
+  <si>
+    <t>products?type=transactional</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Transactional')</t>
+  </si>
+  <si>
+    <t>Remove this filter Transactional</t>
+  </si>
+  <si>
+    <t>#type-transactional</t>
   </si>
 </sst>
 </file>
@@ -184,7 +436,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -200,6 +452,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -242,12 +500,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -559,204 +820,3210 @@
         <v>47</v>
       </c>
     </row>
+    <row r="2" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2DC696B-E1A8-430C-BC9E-87DD1A6FBE9F}">
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="33.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="33.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.90625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
     <row r="2" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>2</v>
+        <v>49</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>4</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>6</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>9</v>
+        <v>54</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>4</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>7</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>11</v>
+        <v>57</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>12</v>
+        <v>59</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>4</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>13</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>14</v>
+        <v>61</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>15</v>
+        <v>62</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>16</v>
+        <v>63</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>4</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>19</v>
+        <v>66</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>4</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>21</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>22</v>
+        <v>69</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>4</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>25</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>26</v>
+        <v>73</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>27</v>
+        <v>74</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>28</v>
+        <v>75</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>4</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>29</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>31</v>
+        <v>78</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>32</v>
+        <v>79</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>4</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>33</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>35</v>
+        <v>82</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>36</v>
+        <v>83</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>4</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>37</v>
+        <v>84</v>
       </c>
     </row>
-    <row r="11" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="D11" s="3" t="s">
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9169CA5-09CB-4ADC-8EEE-AB383FD3DBB7}">
+  <dimension ref="A1:AMO8"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="40.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="52.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="33.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.26953125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="32.7265625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1029" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1029" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E11" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>41</v>
+      <c r="E2" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2"/>
+      <c r="H2"/>
+      <c r="I2"/>
+      <c r="J2"/>
+      <c r="K2"/>
+      <c r="L2"/>
+      <c r="M2"/>
+      <c r="N2"/>
+      <c r="O2"/>
+      <c r="P2"/>
+      <c r="Q2"/>
+      <c r="R2"/>
+      <c r="S2"/>
+      <c r="T2"/>
+      <c r="U2"/>
+      <c r="V2"/>
+      <c r="W2"/>
+      <c r="X2"/>
+      <c r="Y2"/>
+      <c r="Z2"/>
+      <c r="AA2"/>
+      <c r="AB2"/>
+      <c r="AC2"/>
+      <c r="AD2"/>
+      <c r="AE2"/>
+      <c r="AF2"/>
+      <c r="AG2"/>
+      <c r="AH2"/>
+      <c r="AI2"/>
+      <c r="AJ2"/>
+      <c r="AK2"/>
+      <c r="AL2"/>
+      <c r="AM2"/>
+      <c r="AN2"/>
+      <c r="AO2"/>
+      <c r="AP2"/>
+      <c r="AQ2"/>
+      <c r="AR2"/>
+      <c r="AS2"/>
+      <c r="AT2"/>
+      <c r="AU2"/>
+      <c r="AV2"/>
+      <c r="AW2"/>
+      <c r="AX2"/>
+      <c r="AY2"/>
+      <c r="AZ2"/>
+      <c r="BA2"/>
+      <c r="BB2"/>
+      <c r="BC2"/>
+      <c r="BD2"/>
+      <c r="BE2"/>
+      <c r="BF2"/>
+      <c r="BG2"/>
+      <c r="BH2"/>
+      <c r="BI2"/>
+      <c r="BJ2"/>
+      <c r="BK2"/>
+      <c r="BL2"/>
+      <c r="BM2"/>
+      <c r="BN2"/>
+      <c r="BO2"/>
+      <c r="BP2"/>
+      <c r="BQ2"/>
+      <c r="BR2"/>
+      <c r="BS2"/>
+      <c r="BT2"/>
+      <c r="BU2"/>
+      <c r="BV2"/>
+      <c r="BW2"/>
+      <c r="BX2"/>
+      <c r="BY2"/>
+      <c r="BZ2"/>
+      <c r="CA2"/>
+      <c r="CB2"/>
+      <c r="CC2"/>
+      <c r="CD2"/>
+      <c r="CE2"/>
+      <c r="CF2"/>
+      <c r="CG2"/>
+      <c r="CH2"/>
+      <c r="CI2"/>
+      <c r="CJ2"/>
+      <c r="CK2"/>
+      <c r="CL2"/>
+      <c r="CM2"/>
+      <c r="CN2"/>
+      <c r="CO2"/>
+      <c r="CP2"/>
+      <c r="CQ2"/>
+      <c r="CR2"/>
+      <c r="CS2"/>
+      <c r="CT2"/>
+      <c r="CU2"/>
+      <c r="CV2"/>
+      <c r="CW2"/>
+      <c r="CX2"/>
+      <c r="CY2"/>
+      <c r="CZ2"/>
+      <c r="DA2"/>
+      <c r="DB2"/>
+      <c r="DC2"/>
+      <c r="DD2"/>
+      <c r="DE2"/>
+      <c r="DF2"/>
+      <c r="DG2"/>
+      <c r="DH2"/>
+      <c r="DI2"/>
+      <c r="DJ2"/>
+      <c r="DK2"/>
+      <c r="DL2"/>
+      <c r="DM2"/>
+      <c r="DN2"/>
+      <c r="DO2"/>
+      <c r="DP2"/>
+      <c r="DQ2"/>
+      <c r="DR2"/>
+      <c r="DS2"/>
+      <c r="DT2"/>
+      <c r="DU2"/>
+      <c r="DV2"/>
+      <c r="DW2"/>
+      <c r="DX2"/>
+      <c r="DY2"/>
+      <c r="DZ2"/>
+      <c r="EA2"/>
+      <c r="EB2"/>
+      <c r="EC2"/>
+      <c r="ED2"/>
+      <c r="EE2"/>
+      <c r="EF2"/>
+      <c r="EG2"/>
+      <c r="EH2"/>
+      <c r="EI2"/>
+      <c r="EJ2"/>
+      <c r="EK2"/>
+      <c r="EL2"/>
+      <c r="EM2"/>
+      <c r="EN2"/>
+      <c r="EO2"/>
+      <c r="EP2"/>
+      <c r="EQ2"/>
+      <c r="ER2"/>
+      <c r="ES2"/>
+      <c r="ET2"/>
+      <c r="EU2"/>
+      <c r="EV2"/>
+      <c r="EW2"/>
+      <c r="EX2"/>
+      <c r="EY2"/>
+      <c r="EZ2"/>
+      <c r="FA2"/>
+      <c r="FB2"/>
+      <c r="FC2"/>
+      <c r="FD2"/>
+      <c r="FE2"/>
+      <c r="FF2"/>
+      <c r="FG2"/>
+      <c r="FH2"/>
+      <c r="FI2"/>
+      <c r="FJ2"/>
+      <c r="FK2"/>
+      <c r="FL2"/>
+      <c r="FM2"/>
+      <c r="FN2"/>
+      <c r="FO2"/>
+      <c r="FP2"/>
+      <c r="FQ2"/>
+      <c r="FR2"/>
+      <c r="FS2"/>
+      <c r="FT2"/>
+      <c r="FU2"/>
+      <c r="FV2"/>
+      <c r="FW2"/>
+      <c r="FX2"/>
+      <c r="FY2"/>
+      <c r="FZ2"/>
+      <c r="GA2"/>
+      <c r="GB2"/>
+      <c r="GC2"/>
+      <c r="GD2"/>
+      <c r="GE2"/>
+      <c r="GF2"/>
+      <c r="GG2"/>
+      <c r="GH2"/>
+      <c r="GI2"/>
+      <c r="GJ2"/>
+      <c r="GK2"/>
+      <c r="GL2"/>
+      <c r="GM2"/>
+      <c r="GN2"/>
+      <c r="GO2"/>
+      <c r="GP2"/>
+      <c r="GQ2"/>
+      <c r="GR2"/>
+      <c r="GS2"/>
+      <c r="GT2"/>
+      <c r="GU2"/>
+      <c r="GV2"/>
+      <c r="GW2"/>
+      <c r="GX2"/>
+      <c r="GY2"/>
+      <c r="GZ2"/>
+      <c r="HA2"/>
+      <c r="HB2"/>
+      <c r="HC2"/>
+      <c r="HD2"/>
+      <c r="HE2"/>
+      <c r="HF2"/>
+      <c r="HG2"/>
+      <c r="HH2"/>
+      <c r="HI2"/>
+      <c r="HJ2"/>
+      <c r="HK2"/>
+      <c r="HL2"/>
+      <c r="HM2"/>
+      <c r="HN2"/>
+      <c r="HO2"/>
+      <c r="HP2"/>
+      <c r="HQ2"/>
+      <c r="HR2"/>
+      <c r="HS2"/>
+      <c r="HT2"/>
+      <c r="HU2"/>
+      <c r="HV2"/>
+      <c r="HW2"/>
+      <c r="HX2"/>
+      <c r="HY2"/>
+      <c r="HZ2"/>
+      <c r="IA2"/>
+      <c r="IB2"/>
+      <c r="IC2"/>
+      <c r="ID2"/>
+      <c r="IE2"/>
+      <c r="IF2"/>
+      <c r="IG2"/>
+      <c r="IH2"/>
+      <c r="II2"/>
+      <c r="IJ2"/>
+      <c r="IK2"/>
+      <c r="IL2"/>
+      <c r="IM2"/>
+      <c r="IN2"/>
+      <c r="IO2"/>
+      <c r="IP2"/>
+      <c r="IQ2"/>
+      <c r="IR2"/>
+      <c r="IS2"/>
+      <c r="IT2"/>
+      <c r="IU2"/>
+      <c r="IV2"/>
+      <c r="IW2"/>
+      <c r="IX2"/>
+      <c r="IY2"/>
+      <c r="IZ2"/>
+      <c r="JA2"/>
+      <c r="JB2"/>
+      <c r="JC2"/>
+      <c r="JD2"/>
+      <c r="JE2"/>
+      <c r="JF2"/>
+      <c r="JG2"/>
+      <c r="JH2"/>
+      <c r="JI2"/>
+      <c r="JJ2"/>
+      <c r="JK2"/>
+      <c r="JL2"/>
+      <c r="JM2"/>
+      <c r="JN2"/>
+      <c r="JO2"/>
+      <c r="JP2"/>
+      <c r="JQ2"/>
+      <c r="JR2"/>
+      <c r="JS2"/>
+      <c r="JT2"/>
+      <c r="JU2"/>
+      <c r="JV2"/>
+      <c r="JW2"/>
+      <c r="JX2"/>
+      <c r="JY2"/>
+      <c r="JZ2"/>
+      <c r="KA2"/>
+      <c r="KB2"/>
+      <c r="KC2"/>
+      <c r="KD2"/>
+      <c r="KE2"/>
+      <c r="KF2"/>
+      <c r="KG2"/>
+      <c r="KH2"/>
+      <c r="KI2"/>
+      <c r="KJ2"/>
+      <c r="KK2"/>
+      <c r="KL2"/>
+      <c r="KM2"/>
+      <c r="KN2"/>
+      <c r="KO2"/>
+      <c r="KP2"/>
+      <c r="KQ2"/>
+      <c r="KR2"/>
+      <c r="KS2"/>
+      <c r="KT2"/>
+      <c r="KU2"/>
+      <c r="KV2"/>
+      <c r="KW2"/>
+      <c r="KX2"/>
+      <c r="KY2"/>
+      <c r="KZ2"/>
+      <c r="LA2"/>
+      <c r="LB2"/>
+      <c r="LC2"/>
+      <c r="LD2"/>
+      <c r="LE2"/>
+      <c r="LF2"/>
+      <c r="LG2"/>
+      <c r="LH2"/>
+      <c r="LI2"/>
+      <c r="LJ2"/>
+      <c r="LK2"/>
+      <c r="LL2"/>
+      <c r="LM2"/>
+      <c r="LN2"/>
+      <c r="LO2"/>
+      <c r="LP2"/>
+      <c r="LQ2"/>
+      <c r="LR2"/>
+      <c r="LS2"/>
+      <c r="LT2"/>
+      <c r="LU2"/>
+      <c r="LV2"/>
+      <c r="LW2"/>
+      <c r="LX2"/>
+      <c r="LY2"/>
+      <c r="LZ2"/>
+      <c r="MA2"/>
+      <c r="MB2"/>
+      <c r="MC2"/>
+      <c r="MD2"/>
+      <c r="ME2"/>
+      <c r="MF2"/>
+      <c r="MG2"/>
+      <c r="MH2"/>
+      <c r="MI2"/>
+      <c r="MJ2"/>
+      <c r="MK2"/>
+      <c r="ML2"/>
+      <c r="MM2"/>
+      <c r="MN2"/>
+      <c r="MO2"/>
+      <c r="MP2"/>
+      <c r="MQ2"/>
+      <c r="MR2"/>
+      <c r="MS2"/>
+      <c r="MT2"/>
+      <c r="MU2"/>
+      <c r="MV2"/>
+      <c r="MW2"/>
+      <c r="MX2"/>
+      <c r="MY2"/>
+      <c r="MZ2"/>
+      <c r="NA2"/>
+      <c r="NB2"/>
+      <c r="NC2"/>
+      <c r="ND2"/>
+      <c r="NE2"/>
+      <c r="NF2"/>
+      <c r="NG2"/>
+      <c r="NH2"/>
+      <c r="NI2"/>
+      <c r="NJ2"/>
+      <c r="NK2"/>
+      <c r="NL2"/>
+      <c r="NM2"/>
+      <c r="NN2"/>
+      <c r="NO2"/>
+      <c r="NP2"/>
+      <c r="NQ2"/>
+      <c r="NR2"/>
+      <c r="NS2"/>
+      <c r="NT2"/>
+      <c r="NU2"/>
+      <c r="NV2"/>
+      <c r="NW2"/>
+      <c r="NX2"/>
+      <c r="NY2"/>
+      <c r="NZ2"/>
+      <c r="OA2"/>
+      <c r="OB2"/>
+      <c r="OC2"/>
+      <c r="OD2"/>
+      <c r="OE2"/>
+      <c r="OF2"/>
+      <c r="OG2"/>
+      <c r="OH2"/>
+      <c r="OI2"/>
+      <c r="OJ2"/>
+      <c r="OK2"/>
+      <c r="OL2"/>
+      <c r="OM2"/>
+      <c r="ON2"/>
+      <c r="OO2"/>
+      <c r="OP2"/>
+      <c r="OQ2"/>
+      <c r="OR2"/>
+      <c r="OS2"/>
+      <c r="OT2"/>
+      <c r="OU2"/>
+      <c r="OV2"/>
+      <c r="OW2"/>
+      <c r="OX2"/>
+      <c r="OY2"/>
+      <c r="OZ2"/>
+      <c r="PA2"/>
+      <c r="PB2"/>
+      <c r="PC2"/>
+      <c r="PD2"/>
+      <c r="PE2"/>
+      <c r="PF2"/>
+      <c r="PG2"/>
+      <c r="PH2"/>
+      <c r="PI2"/>
+      <c r="PJ2"/>
+      <c r="PK2"/>
+      <c r="PL2"/>
+      <c r="PM2"/>
+      <c r="PN2"/>
+      <c r="PO2"/>
+      <c r="PP2"/>
+      <c r="PQ2"/>
+      <c r="PR2"/>
+      <c r="PS2"/>
+      <c r="PT2"/>
+      <c r="PU2"/>
+      <c r="PV2"/>
+      <c r="PW2"/>
+      <c r="PX2"/>
+      <c r="PY2"/>
+      <c r="PZ2"/>
+      <c r="QA2"/>
+      <c r="QB2"/>
+      <c r="QC2"/>
+      <c r="QD2"/>
+      <c r="QE2"/>
+      <c r="QF2"/>
+      <c r="QG2"/>
+      <c r="QH2"/>
+      <c r="QI2"/>
+      <c r="QJ2"/>
+      <c r="QK2"/>
+      <c r="QL2"/>
+      <c r="QM2"/>
+      <c r="QN2"/>
+      <c r="QO2"/>
+      <c r="QP2"/>
+      <c r="QQ2"/>
+      <c r="QR2"/>
+      <c r="QS2"/>
+      <c r="QT2"/>
+      <c r="QU2"/>
+      <c r="QV2"/>
+      <c r="QW2"/>
+      <c r="QX2"/>
+      <c r="QY2"/>
+      <c r="QZ2"/>
+      <c r="RA2"/>
+      <c r="RB2"/>
+      <c r="RC2"/>
+      <c r="RD2"/>
+      <c r="RE2"/>
+      <c r="RF2"/>
+      <c r="RG2"/>
+      <c r="RH2"/>
+      <c r="RI2"/>
+      <c r="RJ2"/>
+      <c r="RK2"/>
+      <c r="RL2"/>
+      <c r="RM2"/>
+      <c r="RN2"/>
+      <c r="RO2"/>
+      <c r="RP2"/>
+      <c r="RQ2"/>
+      <c r="RR2"/>
+      <c r="RS2"/>
+      <c r="RT2"/>
+      <c r="RU2"/>
+      <c r="RV2"/>
+      <c r="RW2"/>
+      <c r="RX2"/>
+      <c r="RY2"/>
+      <c r="RZ2"/>
+      <c r="SA2"/>
+      <c r="SB2"/>
+      <c r="SC2"/>
+      <c r="SD2"/>
+      <c r="SE2"/>
+      <c r="SF2"/>
+      <c r="SG2"/>
+      <c r="SH2"/>
+      <c r="SI2"/>
+      <c r="SJ2"/>
+      <c r="SK2"/>
+      <c r="SL2"/>
+      <c r="SM2"/>
+      <c r="SN2"/>
+      <c r="SO2"/>
+      <c r="SP2"/>
+      <c r="SQ2"/>
+      <c r="SR2"/>
+      <c r="SS2"/>
+      <c r="ST2"/>
+      <c r="SU2"/>
+      <c r="SV2"/>
+      <c r="SW2"/>
+      <c r="SX2"/>
+      <c r="SY2"/>
+      <c r="SZ2"/>
+      <c r="TA2"/>
+      <c r="TB2"/>
+      <c r="TC2"/>
+      <c r="TD2"/>
+      <c r="TE2"/>
+      <c r="TF2"/>
+      <c r="TG2"/>
+      <c r="TH2"/>
+      <c r="TI2"/>
+      <c r="TJ2"/>
+      <c r="TK2"/>
+      <c r="TL2"/>
+      <c r="TM2"/>
+      <c r="TN2"/>
+      <c r="TO2"/>
+      <c r="TP2"/>
+      <c r="TQ2"/>
+      <c r="TR2"/>
+      <c r="TS2"/>
+      <c r="TT2"/>
+      <c r="TU2"/>
+      <c r="TV2"/>
+      <c r="TW2"/>
+      <c r="TX2"/>
+      <c r="TY2"/>
+      <c r="TZ2"/>
+      <c r="UA2"/>
+      <c r="UB2"/>
+      <c r="UC2"/>
+      <c r="UD2"/>
+      <c r="UE2"/>
+      <c r="UF2"/>
+      <c r="UG2"/>
+      <c r="UH2"/>
+      <c r="UI2"/>
+      <c r="UJ2"/>
+      <c r="UK2"/>
+      <c r="UL2"/>
+      <c r="UM2"/>
+      <c r="UN2"/>
+      <c r="UO2"/>
+      <c r="UP2"/>
+      <c r="UQ2"/>
+      <c r="UR2"/>
+      <c r="US2"/>
+      <c r="UT2"/>
+      <c r="UU2"/>
+      <c r="UV2"/>
+      <c r="UW2"/>
+      <c r="UX2"/>
+      <c r="UY2"/>
+      <c r="UZ2"/>
+      <c r="VA2"/>
+      <c r="VB2"/>
+      <c r="VC2"/>
+      <c r="VD2"/>
+      <c r="VE2"/>
+      <c r="VF2"/>
+      <c r="VG2"/>
+      <c r="VH2"/>
+      <c r="VI2"/>
+      <c r="VJ2"/>
+      <c r="VK2"/>
+      <c r="VL2"/>
+      <c r="VM2"/>
+      <c r="VN2"/>
+      <c r="VO2"/>
+      <c r="VP2"/>
+      <c r="VQ2"/>
+      <c r="VR2"/>
+      <c r="VS2"/>
+      <c r="VT2"/>
+      <c r="VU2"/>
+      <c r="VV2"/>
+      <c r="VW2"/>
+      <c r="VX2"/>
+      <c r="VY2"/>
+      <c r="VZ2"/>
+      <c r="WA2"/>
+      <c r="WB2"/>
+      <c r="WC2"/>
+      <c r="WD2"/>
+      <c r="WE2"/>
+      <c r="WF2"/>
+      <c r="WG2"/>
+      <c r="WH2"/>
+      <c r="WI2"/>
+      <c r="WJ2"/>
+      <c r="WK2"/>
+      <c r="WL2"/>
+      <c r="WM2"/>
+      <c r="WN2"/>
+      <c r="WO2"/>
+      <c r="WP2"/>
+      <c r="WQ2"/>
+      <c r="WR2"/>
+      <c r="WS2"/>
+      <c r="WT2"/>
+      <c r="WU2"/>
+      <c r="WV2"/>
+      <c r="WW2"/>
+      <c r="WX2"/>
+      <c r="WY2"/>
+      <c r="WZ2"/>
+      <c r="XA2"/>
+      <c r="XB2"/>
+      <c r="XC2"/>
+      <c r="XD2"/>
+      <c r="XE2"/>
+      <c r="XF2"/>
+      <c r="XG2"/>
+      <c r="XH2"/>
+      <c r="XI2"/>
+      <c r="XJ2"/>
+      <c r="XK2"/>
+      <c r="XL2"/>
+      <c r="XM2"/>
+      <c r="XN2"/>
+      <c r="XO2"/>
+      <c r="XP2"/>
+      <c r="XQ2"/>
+      <c r="XR2"/>
+      <c r="XS2"/>
+      <c r="XT2"/>
+      <c r="XU2"/>
+      <c r="XV2"/>
+      <c r="XW2"/>
+      <c r="XX2"/>
+      <c r="XY2"/>
+      <c r="XZ2"/>
+      <c r="YA2"/>
+      <c r="YB2"/>
+      <c r="YC2"/>
+      <c r="YD2"/>
+      <c r="YE2"/>
+      <c r="YF2"/>
+      <c r="YG2"/>
+      <c r="YH2"/>
+      <c r="YI2"/>
+      <c r="YJ2"/>
+      <c r="YK2"/>
+      <c r="YL2"/>
+      <c r="YM2"/>
+      <c r="YN2"/>
+      <c r="YO2"/>
+      <c r="YP2"/>
+      <c r="YQ2"/>
+      <c r="YR2"/>
+      <c r="YS2"/>
+      <c r="YT2"/>
+      <c r="YU2"/>
+      <c r="YV2"/>
+      <c r="YW2"/>
+      <c r="YX2"/>
+      <c r="YY2"/>
+      <c r="YZ2"/>
+      <c r="ZA2"/>
+      <c r="ZB2"/>
+      <c r="ZC2"/>
+      <c r="ZD2"/>
+      <c r="ZE2"/>
+      <c r="ZF2"/>
+      <c r="ZG2"/>
+      <c r="ZH2"/>
+      <c r="ZI2"/>
+      <c r="ZJ2"/>
+      <c r="ZK2"/>
+      <c r="ZL2"/>
+      <c r="ZM2"/>
+      <c r="ZN2"/>
+      <c r="ZO2"/>
+      <c r="ZP2"/>
+      <c r="ZQ2"/>
+      <c r="ZR2"/>
+      <c r="ZS2"/>
+      <c r="ZT2"/>
+      <c r="ZU2"/>
+      <c r="ZV2"/>
+      <c r="ZW2"/>
+      <c r="ZX2"/>
+      <c r="ZY2"/>
+      <c r="ZZ2"/>
+      <c r="AAA2"/>
+      <c r="AAB2"/>
+      <c r="AAC2"/>
+      <c r="AAD2"/>
+      <c r="AAE2"/>
+      <c r="AAF2"/>
+      <c r="AAG2"/>
+      <c r="AAH2"/>
+      <c r="AAI2"/>
+      <c r="AAJ2"/>
+      <c r="AAK2"/>
+      <c r="AAL2"/>
+      <c r="AAM2"/>
+      <c r="AAN2"/>
+      <c r="AAO2"/>
+      <c r="AAP2"/>
+      <c r="AAQ2"/>
+      <c r="AAR2"/>
+      <c r="AAS2"/>
+      <c r="AAT2"/>
+      <c r="AAU2"/>
+      <c r="AAV2"/>
+      <c r="AAW2"/>
+      <c r="AAX2"/>
+      <c r="AAY2"/>
+      <c r="AAZ2"/>
+      <c r="ABA2"/>
+      <c r="ABB2"/>
+      <c r="ABC2"/>
+      <c r="ABD2"/>
+      <c r="ABE2"/>
+      <c r="ABF2"/>
+      <c r="ABG2"/>
+      <c r="ABH2"/>
+      <c r="ABI2"/>
+      <c r="ABJ2"/>
+      <c r="ABK2"/>
+      <c r="ABL2"/>
+      <c r="ABM2"/>
+      <c r="ABN2"/>
+      <c r="ABO2"/>
+      <c r="ABP2"/>
+      <c r="ABQ2"/>
+      <c r="ABR2"/>
+      <c r="ABS2"/>
+      <c r="ABT2"/>
+      <c r="ABU2"/>
+      <c r="ABV2"/>
+      <c r="ABW2"/>
+      <c r="ABX2"/>
+      <c r="ABY2"/>
+      <c r="ABZ2"/>
+      <c r="ACA2"/>
+      <c r="ACB2"/>
+      <c r="ACC2"/>
+      <c r="ACD2"/>
+      <c r="ACE2"/>
+      <c r="ACF2"/>
+      <c r="ACG2"/>
+      <c r="ACH2"/>
+      <c r="ACI2"/>
+      <c r="ACJ2"/>
+      <c r="ACK2"/>
+      <c r="ACL2"/>
+      <c r="ACM2"/>
+      <c r="ACN2"/>
+      <c r="ACO2"/>
+      <c r="ACP2"/>
+      <c r="ACQ2"/>
+      <c r="ACR2"/>
+      <c r="ACS2"/>
+      <c r="ACT2"/>
+      <c r="ACU2"/>
+      <c r="ACV2"/>
+      <c r="ACW2"/>
+      <c r="ACX2"/>
+      <c r="ACY2"/>
+      <c r="ACZ2"/>
+      <c r="ADA2"/>
+      <c r="ADB2"/>
+      <c r="ADC2"/>
+      <c r="ADD2"/>
+      <c r="ADE2"/>
+      <c r="ADF2"/>
+      <c r="ADG2"/>
+      <c r="ADH2"/>
+      <c r="ADI2"/>
+      <c r="ADJ2"/>
+      <c r="ADK2"/>
+      <c r="ADL2"/>
+      <c r="ADM2"/>
+      <c r="ADN2"/>
+      <c r="ADO2"/>
+      <c r="ADP2"/>
+      <c r="ADQ2"/>
+      <c r="ADR2"/>
+      <c r="ADS2"/>
+      <c r="ADT2"/>
+      <c r="ADU2"/>
+      <c r="ADV2"/>
+      <c r="ADW2"/>
+      <c r="ADX2"/>
+      <c r="ADY2"/>
+      <c r="ADZ2"/>
+      <c r="AEA2"/>
+      <c r="AEB2"/>
+      <c r="AEC2"/>
+      <c r="AED2"/>
+      <c r="AEE2"/>
+      <c r="AEF2"/>
+      <c r="AEG2"/>
+      <c r="AEH2"/>
+      <c r="AEI2"/>
+      <c r="AEJ2"/>
+      <c r="AEK2"/>
+      <c r="AEL2"/>
+      <c r="AEM2"/>
+      <c r="AEN2"/>
+      <c r="AEO2"/>
+      <c r="AEP2"/>
+      <c r="AEQ2"/>
+      <c r="AER2"/>
+      <c r="AES2"/>
+      <c r="AET2"/>
+      <c r="AEU2"/>
+      <c r="AEV2"/>
+      <c r="AEW2"/>
+      <c r="AEX2"/>
+      <c r="AEY2"/>
+      <c r="AEZ2"/>
+      <c r="AFA2"/>
+      <c r="AFB2"/>
+      <c r="AFC2"/>
+      <c r="AFD2"/>
+      <c r="AFE2"/>
+      <c r="AFF2"/>
+      <c r="AFG2"/>
+      <c r="AFH2"/>
+      <c r="AFI2"/>
+      <c r="AFJ2"/>
+      <c r="AFK2"/>
+      <c r="AFL2"/>
+      <c r="AFM2"/>
+      <c r="AFN2"/>
+      <c r="AFO2"/>
+      <c r="AFP2"/>
+      <c r="AFQ2"/>
+      <c r="AFR2"/>
+      <c r="AFS2"/>
+      <c r="AFT2"/>
+      <c r="AFU2"/>
+      <c r="AFV2"/>
+      <c r="AFW2"/>
+      <c r="AFX2"/>
+      <c r="AFY2"/>
+      <c r="AFZ2"/>
+      <c r="AGA2"/>
+      <c r="AGB2"/>
+      <c r="AGC2"/>
+      <c r="AGD2"/>
+      <c r="AGE2"/>
+      <c r="AGF2"/>
+      <c r="AGG2"/>
+      <c r="AGH2"/>
+      <c r="AGI2"/>
+      <c r="AGJ2"/>
+      <c r="AGK2"/>
+      <c r="AGL2"/>
+      <c r="AGM2"/>
+      <c r="AGN2"/>
+      <c r="AGO2"/>
+      <c r="AGP2"/>
+      <c r="AGQ2"/>
+      <c r="AGR2"/>
+      <c r="AGS2"/>
+      <c r="AGT2"/>
+      <c r="AGU2"/>
+      <c r="AGV2"/>
+      <c r="AGW2"/>
+      <c r="AGX2"/>
+      <c r="AGY2"/>
+      <c r="AGZ2"/>
+      <c r="AHA2"/>
+      <c r="AHB2"/>
+      <c r="AHC2"/>
+      <c r="AHD2"/>
+      <c r="AHE2"/>
+      <c r="AHF2"/>
+      <c r="AHG2"/>
+      <c r="AHH2"/>
+      <c r="AHI2"/>
+      <c r="AHJ2"/>
+      <c r="AHK2"/>
+      <c r="AHL2"/>
+      <c r="AHM2"/>
+      <c r="AHN2"/>
+      <c r="AHO2"/>
+      <c r="AHP2"/>
+      <c r="AHQ2"/>
+      <c r="AHR2"/>
+      <c r="AHS2"/>
+      <c r="AHT2"/>
+      <c r="AHU2"/>
+      <c r="AHV2"/>
+      <c r="AHW2"/>
+      <c r="AHX2"/>
+      <c r="AHY2"/>
+      <c r="AHZ2"/>
+      <c r="AIA2"/>
+      <c r="AIB2"/>
+      <c r="AIC2"/>
+      <c r="AID2"/>
+      <c r="AIE2"/>
+      <c r="AIF2"/>
+      <c r="AIG2"/>
+      <c r="AIH2"/>
+      <c r="AII2"/>
+      <c r="AIJ2"/>
+      <c r="AIK2"/>
+      <c r="AIL2"/>
+      <c r="AIM2"/>
+      <c r="AIN2"/>
+      <c r="AIO2"/>
+      <c r="AIP2"/>
+      <c r="AIQ2"/>
+      <c r="AIR2"/>
+      <c r="AIS2"/>
+      <c r="AIT2"/>
+      <c r="AIU2"/>
+      <c r="AIV2"/>
+      <c r="AIW2"/>
+      <c r="AIX2"/>
+      <c r="AIY2"/>
+      <c r="AIZ2"/>
+      <c r="AJA2"/>
+      <c r="AJB2"/>
+      <c r="AJC2"/>
+      <c r="AJD2"/>
+      <c r="AJE2"/>
+      <c r="AJF2"/>
+      <c r="AJG2"/>
+      <c r="AJH2"/>
+      <c r="AJI2"/>
+      <c r="AJJ2"/>
+      <c r="AJK2"/>
+      <c r="AJL2"/>
+      <c r="AJM2"/>
+      <c r="AJN2"/>
+      <c r="AJO2"/>
+      <c r="AJP2"/>
+      <c r="AJQ2"/>
+      <c r="AJR2"/>
+      <c r="AJS2"/>
+      <c r="AJT2"/>
+      <c r="AJU2"/>
+      <c r="AJV2"/>
+      <c r="AJW2"/>
+      <c r="AJX2"/>
+      <c r="AJY2"/>
+      <c r="AJZ2"/>
+      <c r="AKA2"/>
+      <c r="AKB2"/>
+      <c r="AKC2"/>
+      <c r="AKD2"/>
+      <c r="AKE2"/>
+      <c r="AKF2"/>
+      <c r="AKG2"/>
+      <c r="AKH2"/>
+      <c r="AKI2"/>
+      <c r="AKJ2"/>
+      <c r="AKK2"/>
+      <c r="AKL2"/>
+      <c r="AKM2"/>
+      <c r="AKN2"/>
+      <c r="AKO2"/>
+      <c r="AKP2"/>
+      <c r="AKQ2"/>
+      <c r="AKR2"/>
+      <c r="AKS2"/>
+      <c r="AKT2"/>
+      <c r="AKU2"/>
+      <c r="AKV2"/>
+      <c r="AKW2"/>
+      <c r="AKX2"/>
+      <c r="AKY2"/>
+      <c r="AKZ2"/>
+      <c r="ALA2"/>
+      <c r="ALB2"/>
+      <c r="ALC2"/>
+      <c r="ALD2"/>
+      <c r="ALE2"/>
+      <c r="ALF2"/>
+      <c r="ALG2"/>
+      <c r="ALH2"/>
+      <c r="ALI2"/>
+      <c r="ALJ2"/>
+      <c r="ALK2"/>
+      <c r="ALL2"/>
+      <c r="ALM2"/>
+      <c r="ALN2"/>
+      <c r="ALO2"/>
+      <c r="ALP2"/>
+      <c r="ALQ2"/>
+      <c r="ALR2"/>
+      <c r="ALS2"/>
+      <c r="ALT2"/>
+      <c r="ALU2"/>
+      <c r="ALV2"/>
+      <c r="ALW2"/>
+      <c r="ALX2"/>
+      <c r="ALY2"/>
+      <c r="ALZ2"/>
+      <c r="AMA2"/>
+      <c r="AMB2"/>
+      <c r="AMC2"/>
+      <c r="AMD2"/>
+      <c r="AME2"/>
+      <c r="AMF2"/>
+      <c r="AMG2"/>
+      <c r="AMH2"/>
+      <c r="AMI2"/>
+      <c r="AMJ2"/>
+      <c r="AMK2"/>
+      <c r="AML2"/>
+      <c r="AMM2"/>
+      <c r="AMN2"/>
+      <c r="AMO2"/>
+    </row>
+    <row r="3" spans="1:1029" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G3"/>
+      <c r="H3"/>
+      <c r="I3"/>
+      <c r="J3"/>
+      <c r="K3"/>
+      <c r="L3"/>
+      <c r="M3"/>
+      <c r="N3"/>
+      <c r="O3"/>
+      <c r="P3"/>
+      <c r="Q3"/>
+      <c r="R3"/>
+      <c r="S3"/>
+      <c r="T3"/>
+      <c r="U3"/>
+      <c r="V3"/>
+      <c r="W3"/>
+      <c r="X3"/>
+      <c r="Y3"/>
+      <c r="Z3"/>
+      <c r="AA3"/>
+      <c r="AB3"/>
+      <c r="AC3"/>
+      <c r="AD3"/>
+      <c r="AE3"/>
+      <c r="AF3"/>
+      <c r="AG3"/>
+      <c r="AH3"/>
+      <c r="AI3"/>
+      <c r="AJ3"/>
+      <c r="AK3"/>
+      <c r="AL3"/>
+      <c r="AM3"/>
+      <c r="AN3"/>
+      <c r="AO3"/>
+      <c r="AP3"/>
+      <c r="AQ3"/>
+      <c r="AR3"/>
+      <c r="AS3"/>
+      <c r="AT3"/>
+      <c r="AU3"/>
+      <c r="AV3"/>
+      <c r="AW3"/>
+      <c r="AX3"/>
+      <c r="AY3"/>
+      <c r="AZ3"/>
+      <c r="BA3"/>
+      <c r="BB3"/>
+      <c r="BC3"/>
+      <c r="BD3"/>
+      <c r="BE3"/>
+      <c r="BF3"/>
+      <c r="BG3"/>
+      <c r="BH3"/>
+      <c r="BI3"/>
+      <c r="BJ3"/>
+      <c r="BK3"/>
+      <c r="BL3"/>
+      <c r="BM3"/>
+      <c r="BN3"/>
+      <c r="BO3"/>
+      <c r="BP3"/>
+      <c r="BQ3"/>
+      <c r="BR3"/>
+      <c r="BS3"/>
+      <c r="BT3"/>
+      <c r="BU3"/>
+      <c r="BV3"/>
+      <c r="BW3"/>
+      <c r="BX3"/>
+      <c r="BY3"/>
+      <c r="BZ3"/>
+      <c r="CA3"/>
+      <c r="CB3"/>
+      <c r="CC3"/>
+      <c r="CD3"/>
+      <c r="CE3"/>
+      <c r="CF3"/>
+      <c r="CG3"/>
+      <c r="CH3"/>
+      <c r="CI3"/>
+      <c r="CJ3"/>
+      <c r="CK3"/>
+      <c r="CL3"/>
+      <c r="CM3"/>
+      <c r="CN3"/>
+      <c r="CO3"/>
+      <c r="CP3"/>
+      <c r="CQ3"/>
+      <c r="CR3"/>
+      <c r="CS3"/>
+      <c r="CT3"/>
+      <c r="CU3"/>
+      <c r="CV3"/>
+      <c r="CW3"/>
+      <c r="CX3"/>
+      <c r="CY3"/>
+      <c r="CZ3"/>
+      <c r="DA3"/>
+      <c r="DB3"/>
+      <c r="DC3"/>
+      <c r="DD3"/>
+      <c r="DE3"/>
+      <c r="DF3"/>
+      <c r="DG3"/>
+      <c r="DH3"/>
+      <c r="DI3"/>
+      <c r="DJ3"/>
+      <c r="DK3"/>
+      <c r="DL3"/>
+      <c r="DM3"/>
+      <c r="DN3"/>
+      <c r="DO3"/>
+      <c r="DP3"/>
+      <c r="DQ3"/>
+      <c r="DR3"/>
+      <c r="DS3"/>
+      <c r="DT3"/>
+      <c r="DU3"/>
+      <c r="DV3"/>
+      <c r="DW3"/>
+      <c r="DX3"/>
+      <c r="DY3"/>
+      <c r="DZ3"/>
+      <c r="EA3"/>
+      <c r="EB3"/>
+      <c r="EC3"/>
+      <c r="ED3"/>
+      <c r="EE3"/>
+      <c r="EF3"/>
+      <c r="EG3"/>
+      <c r="EH3"/>
+      <c r="EI3"/>
+      <c r="EJ3"/>
+      <c r="EK3"/>
+      <c r="EL3"/>
+      <c r="EM3"/>
+      <c r="EN3"/>
+      <c r="EO3"/>
+      <c r="EP3"/>
+      <c r="EQ3"/>
+      <c r="ER3"/>
+      <c r="ES3"/>
+      <c r="ET3"/>
+      <c r="EU3"/>
+      <c r="EV3"/>
+      <c r="EW3"/>
+      <c r="EX3"/>
+      <c r="EY3"/>
+      <c r="EZ3"/>
+      <c r="FA3"/>
+      <c r="FB3"/>
+      <c r="FC3"/>
+      <c r="FD3"/>
+      <c r="FE3"/>
+      <c r="FF3"/>
+      <c r="FG3"/>
+      <c r="FH3"/>
+      <c r="FI3"/>
+      <c r="FJ3"/>
+      <c r="FK3"/>
+      <c r="FL3"/>
+      <c r="FM3"/>
+      <c r="FN3"/>
+      <c r="FO3"/>
+      <c r="FP3"/>
+      <c r="FQ3"/>
+      <c r="FR3"/>
+      <c r="FS3"/>
+      <c r="FT3"/>
+      <c r="FU3"/>
+      <c r="FV3"/>
+      <c r="FW3"/>
+      <c r="FX3"/>
+      <c r="FY3"/>
+      <c r="FZ3"/>
+      <c r="GA3"/>
+      <c r="GB3"/>
+      <c r="GC3"/>
+      <c r="GD3"/>
+      <c r="GE3"/>
+      <c r="GF3"/>
+      <c r="GG3"/>
+      <c r="GH3"/>
+      <c r="GI3"/>
+      <c r="GJ3"/>
+      <c r="GK3"/>
+      <c r="GL3"/>
+      <c r="GM3"/>
+      <c r="GN3"/>
+      <c r="GO3"/>
+      <c r="GP3"/>
+      <c r="GQ3"/>
+      <c r="GR3"/>
+      <c r="GS3"/>
+      <c r="GT3"/>
+      <c r="GU3"/>
+      <c r="GV3"/>
+      <c r="GW3"/>
+      <c r="GX3"/>
+      <c r="GY3"/>
+      <c r="GZ3"/>
+      <c r="HA3"/>
+      <c r="HB3"/>
+      <c r="HC3"/>
+      <c r="HD3"/>
+      <c r="HE3"/>
+      <c r="HF3"/>
+      <c r="HG3"/>
+      <c r="HH3"/>
+      <c r="HI3"/>
+      <c r="HJ3"/>
+      <c r="HK3"/>
+      <c r="HL3"/>
+      <c r="HM3"/>
+      <c r="HN3"/>
+      <c r="HO3"/>
+      <c r="HP3"/>
+      <c r="HQ3"/>
+      <c r="HR3"/>
+      <c r="HS3"/>
+      <c r="HT3"/>
+      <c r="HU3"/>
+      <c r="HV3"/>
+      <c r="HW3"/>
+      <c r="HX3"/>
+      <c r="HY3"/>
+      <c r="HZ3"/>
+      <c r="IA3"/>
+      <c r="IB3"/>
+      <c r="IC3"/>
+      <c r="ID3"/>
+      <c r="IE3"/>
+      <c r="IF3"/>
+      <c r="IG3"/>
+      <c r="IH3"/>
+      <c r="II3"/>
+      <c r="IJ3"/>
+      <c r="IK3"/>
+      <c r="IL3"/>
+      <c r="IM3"/>
+      <c r="IN3"/>
+      <c r="IO3"/>
+      <c r="IP3"/>
+      <c r="IQ3"/>
+      <c r="IR3"/>
+      <c r="IS3"/>
+      <c r="IT3"/>
+      <c r="IU3"/>
+      <c r="IV3"/>
+      <c r="IW3"/>
+      <c r="IX3"/>
+      <c r="IY3"/>
+      <c r="IZ3"/>
+      <c r="JA3"/>
+      <c r="JB3"/>
+      <c r="JC3"/>
+      <c r="JD3"/>
+      <c r="JE3"/>
+      <c r="JF3"/>
+      <c r="JG3"/>
+      <c r="JH3"/>
+      <c r="JI3"/>
+      <c r="JJ3"/>
+      <c r="JK3"/>
+      <c r="JL3"/>
+      <c r="JM3"/>
+      <c r="JN3"/>
+      <c r="JO3"/>
+      <c r="JP3"/>
+      <c r="JQ3"/>
+      <c r="JR3"/>
+      <c r="JS3"/>
+      <c r="JT3"/>
+      <c r="JU3"/>
+      <c r="JV3"/>
+      <c r="JW3"/>
+      <c r="JX3"/>
+      <c r="JY3"/>
+      <c r="JZ3"/>
+      <c r="KA3"/>
+      <c r="KB3"/>
+      <c r="KC3"/>
+      <c r="KD3"/>
+      <c r="KE3"/>
+      <c r="KF3"/>
+      <c r="KG3"/>
+      <c r="KH3"/>
+      <c r="KI3"/>
+      <c r="KJ3"/>
+      <c r="KK3"/>
+      <c r="KL3"/>
+      <c r="KM3"/>
+      <c r="KN3"/>
+      <c r="KO3"/>
+      <c r="KP3"/>
+      <c r="KQ3"/>
+      <c r="KR3"/>
+      <c r="KS3"/>
+      <c r="KT3"/>
+      <c r="KU3"/>
+      <c r="KV3"/>
+      <c r="KW3"/>
+      <c r="KX3"/>
+      <c r="KY3"/>
+      <c r="KZ3"/>
+      <c r="LA3"/>
+      <c r="LB3"/>
+      <c r="LC3"/>
+      <c r="LD3"/>
+      <c r="LE3"/>
+      <c r="LF3"/>
+      <c r="LG3"/>
+      <c r="LH3"/>
+      <c r="LI3"/>
+      <c r="LJ3"/>
+      <c r="LK3"/>
+      <c r="LL3"/>
+      <c r="LM3"/>
+      <c r="LN3"/>
+      <c r="LO3"/>
+      <c r="LP3"/>
+      <c r="LQ3"/>
+      <c r="LR3"/>
+      <c r="LS3"/>
+      <c r="LT3"/>
+      <c r="LU3"/>
+      <c r="LV3"/>
+      <c r="LW3"/>
+      <c r="LX3"/>
+      <c r="LY3"/>
+      <c r="LZ3"/>
+      <c r="MA3"/>
+      <c r="MB3"/>
+      <c r="MC3"/>
+      <c r="MD3"/>
+      <c r="ME3"/>
+      <c r="MF3"/>
+      <c r="MG3"/>
+      <c r="MH3"/>
+      <c r="MI3"/>
+      <c r="MJ3"/>
+      <c r="MK3"/>
+      <c r="ML3"/>
+      <c r="MM3"/>
+      <c r="MN3"/>
+      <c r="MO3"/>
+      <c r="MP3"/>
+      <c r="MQ3"/>
+      <c r="MR3"/>
+      <c r="MS3"/>
+      <c r="MT3"/>
+      <c r="MU3"/>
+      <c r="MV3"/>
+      <c r="MW3"/>
+      <c r="MX3"/>
+      <c r="MY3"/>
+      <c r="MZ3"/>
+      <c r="NA3"/>
+      <c r="NB3"/>
+      <c r="NC3"/>
+      <c r="ND3"/>
+      <c r="NE3"/>
+      <c r="NF3"/>
+      <c r="NG3"/>
+      <c r="NH3"/>
+      <c r="NI3"/>
+      <c r="NJ3"/>
+      <c r="NK3"/>
+      <c r="NL3"/>
+      <c r="NM3"/>
+      <c r="NN3"/>
+      <c r="NO3"/>
+      <c r="NP3"/>
+      <c r="NQ3"/>
+      <c r="NR3"/>
+      <c r="NS3"/>
+      <c r="NT3"/>
+      <c r="NU3"/>
+      <c r="NV3"/>
+      <c r="NW3"/>
+      <c r="NX3"/>
+      <c r="NY3"/>
+      <c r="NZ3"/>
+      <c r="OA3"/>
+      <c r="OB3"/>
+      <c r="OC3"/>
+      <c r="OD3"/>
+      <c r="OE3"/>
+      <c r="OF3"/>
+      <c r="OG3"/>
+      <c r="OH3"/>
+      <c r="OI3"/>
+      <c r="OJ3"/>
+      <c r="OK3"/>
+      <c r="OL3"/>
+      <c r="OM3"/>
+      <c r="ON3"/>
+      <c r="OO3"/>
+      <c r="OP3"/>
+      <c r="OQ3"/>
+      <c r="OR3"/>
+      <c r="OS3"/>
+      <c r="OT3"/>
+      <c r="OU3"/>
+      <c r="OV3"/>
+      <c r="OW3"/>
+      <c r="OX3"/>
+      <c r="OY3"/>
+      <c r="OZ3"/>
+      <c r="PA3"/>
+      <c r="PB3"/>
+      <c r="PC3"/>
+      <c r="PD3"/>
+      <c r="PE3"/>
+      <c r="PF3"/>
+      <c r="PG3"/>
+      <c r="PH3"/>
+      <c r="PI3"/>
+      <c r="PJ3"/>
+      <c r="PK3"/>
+      <c r="PL3"/>
+      <c r="PM3"/>
+      <c r="PN3"/>
+      <c r="PO3"/>
+      <c r="PP3"/>
+      <c r="PQ3"/>
+      <c r="PR3"/>
+      <c r="PS3"/>
+      <c r="PT3"/>
+      <c r="PU3"/>
+      <c r="PV3"/>
+      <c r="PW3"/>
+      <c r="PX3"/>
+      <c r="PY3"/>
+      <c r="PZ3"/>
+      <c r="QA3"/>
+      <c r="QB3"/>
+      <c r="QC3"/>
+      <c r="QD3"/>
+      <c r="QE3"/>
+      <c r="QF3"/>
+      <c r="QG3"/>
+      <c r="QH3"/>
+      <c r="QI3"/>
+      <c r="QJ3"/>
+      <c r="QK3"/>
+      <c r="QL3"/>
+      <c r="QM3"/>
+      <c r="QN3"/>
+      <c r="QO3"/>
+      <c r="QP3"/>
+      <c r="QQ3"/>
+      <c r="QR3"/>
+      <c r="QS3"/>
+      <c r="QT3"/>
+      <c r="QU3"/>
+      <c r="QV3"/>
+      <c r="QW3"/>
+      <c r="QX3"/>
+      <c r="QY3"/>
+      <c r="QZ3"/>
+      <c r="RA3"/>
+      <c r="RB3"/>
+      <c r="RC3"/>
+      <c r="RD3"/>
+      <c r="RE3"/>
+      <c r="RF3"/>
+      <c r="RG3"/>
+      <c r="RH3"/>
+      <c r="RI3"/>
+      <c r="RJ3"/>
+      <c r="RK3"/>
+      <c r="RL3"/>
+      <c r="RM3"/>
+      <c r="RN3"/>
+      <c r="RO3"/>
+      <c r="RP3"/>
+      <c r="RQ3"/>
+      <c r="RR3"/>
+      <c r="RS3"/>
+      <c r="RT3"/>
+      <c r="RU3"/>
+      <c r="RV3"/>
+      <c r="RW3"/>
+      <c r="RX3"/>
+      <c r="RY3"/>
+      <c r="RZ3"/>
+      <c r="SA3"/>
+      <c r="SB3"/>
+      <c r="SC3"/>
+      <c r="SD3"/>
+      <c r="SE3"/>
+      <c r="SF3"/>
+      <c r="SG3"/>
+      <c r="SH3"/>
+      <c r="SI3"/>
+      <c r="SJ3"/>
+      <c r="SK3"/>
+      <c r="SL3"/>
+      <c r="SM3"/>
+      <c r="SN3"/>
+      <c r="SO3"/>
+      <c r="SP3"/>
+      <c r="SQ3"/>
+      <c r="SR3"/>
+      <c r="SS3"/>
+      <c r="ST3"/>
+      <c r="SU3"/>
+      <c r="SV3"/>
+      <c r="SW3"/>
+      <c r="SX3"/>
+      <c r="SY3"/>
+      <c r="SZ3"/>
+      <c r="TA3"/>
+      <c r="TB3"/>
+      <c r="TC3"/>
+      <c r="TD3"/>
+      <c r="TE3"/>
+      <c r="TF3"/>
+      <c r="TG3"/>
+      <c r="TH3"/>
+      <c r="TI3"/>
+      <c r="TJ3"/>
+      <c r="TK3"/>
+      <c r="TL3"/>
+      <c r="TM3"/>
+      <c r="TN3"/>
+      <c r="TO3"/>
+      <c r="TP3"/>
+      <c r="TQ3"/>
+      <c r="TR3"/>
+      <c r="TS3"/>
+      <c r="TT3"/>
+      <c r="TU3"/>
+      <c r="TV3"/>
+      <c r="TW3"/>
+      <c r="TX3"/>
+      <c r="TY3"/>
+      <c r="TZ3"/>
+      <c r="UA3"/>
+      <c r="UB3"/>
+      <c r="UC3"/>
+      <c r="UD3"/>
+      <c r="UE3"/>
+      <c r="UF3"/>
+      <c r="UG3"/>
+      <c r="UH3"/>
+      <c r="UI3"/>
+      <c r="UJ3"/>
+      <c r="UK3"/>
+      <c r="UL3"/>
+      <c r="UM3"/>
+      <c r="UN3"/>
+      <c r="UO3"/>
+      <c r="UP3"/>
+      <c r="UQ3"/>
+      <c r="UR3"/>
+      <c r="US3"/>
+      <c r="UT3"/>
+      <c r="UU3"/>
+      <c r="UV3"/>
+      <c r="UW3"/>
+      <c r="UX3"/>
+      <c r="UY3"/>
+      <c r="UZ3"/>
+      <c r="VA3"/>
+      <c r="VB3"/>
+      <c r="VC3"/>
+      <c r="VD3"/>
+      <c r="VE3"/>
+      <c r="VF3"/>
+      <c r="VG3"/>
+      <c r="VH3"/>
+      <c r="VI3"/>
+      <c r="VJ3"/>
+      <c r="VK3"/>
+      <c r="VL3"/>
+      <c r="VM3"/>
+      <c r="VN3"/>
+      <c r="VO3"/>
+      <c r="VP3"/>
+      <c r="VQ3"/>
+      <c r="VR3"/>
+      <c r="VS3"/>
+      <c r="VT3"/>
+      <c r="VU3"/>
+      <c r="VV3"/>
+      <c r="VW3"/>
+      <c r="VX3"/>
+      <c r="VY3"/>
+      <c r="VZ3"/>
+      <c r="WA3"/>
+      <c r="WB3"/>
+      <c r="WC3"/>
+      <c r="WD3"/>
+      <c r="WE3"/>
+      <c r="WF3"/>
+      <c r="WG3"/>
+      <c r="WH3"/>
+      <c r="WI3"/>
+      <c r="WJ3"/>
+      <c r="WK3"/>
+      <c r="WL3"/>
+      <c r="WM3"/>
+      <c r="WN3"/>
+      <c r="WO3"/>
+      <c r="WP3"/>
+      <c r="WQ3"/>
+      <c r="WR3"/>
+      <c r="WS3"/>
+      <c r="WT3"/>
+      <c r="WU3"/>
+      <c r="WV3"/>
+      <c r="WW3"/>
+      <c r="WX3"/>
+      <c r="WY3"/>
+      <c r="WZ3"/>
+      <c r="XA3"/>
+      <c r="XB3"/>
+      <c r="XC3"/>
+      <c r="XD3"/>
+      <c r="XE3"/>
+      <c r="XF3"/>
+      <c r="XG3"/>
+      <c r="XH3"/>
+      <c r="XI3"/>
+      <c r="XJ3"/>
+      <c r="XK3"/>
+      <c r="XL3"/>
+      <c r="XM3"/>
+      <c r="XN3"/>
+      <c r="XO3"/>
+      <c r="XP3"/>
+      <c r="XQ3"/>
+      <c r="XR3"/>
+      <c r="XS3"/>
+      <c r="XT3"/>
+      <c r="XU3"/>
+      <c r="XV3"/>
+      <c r="XW3"/>
+      <c r="XX3"/>
+      <c r="XY3"/>
+      <c r="XZ3"/>
+      <c r="YA3"/>
+      <c r="YB3"/>
+      <c r="YC3"/>
+      <c r="YD3"/>
+      <c r="YE3"/>
+      <c r="YF3"/>
+      <c r="YG3"/>
+      <c r="YH3"/>
+      <c r="YI3"/>
+      <c r="YJ3"/>
+      <c r="YK3"/>
+      <c r="YL3"/>
+      <c r="YM3"/>
+      <c r="YN3"/>
+      <c r="YO3"/>
+      <c r="YP3"/>
+      <c r="YQ3"/>
+      <c r="YR3"/>
+      <c r="YS3"/>
+      <c r="YT3"/>
+      <c r="YU3"/>
+      <c r="YV3"/>
+      <c r="YW3"/>
+      <c r="YX3"/>
+      <c r="YY3"/>
+      <c r="YZ3"/>
+      <c r="ZA3"/>
+      <c r="ZB3"/>
+      <c r="ZC3"/>
+      <c r="ZD3"/>
+      <c r="ZE3"/>
+      <c r="ZF3"/>
+      <c r="ZG3"/>
+      <c r="ZH3"/>
+      <c r="ZI3"/>
+      <c r="ZJ3"/>
+      <c r="ZK3"/>
+      <c r="ZL3"/>
+      <c r="ZM3"/>
+      <c r="ZN3"/>
+      <c r="ZO3"/>
+      <c r="ZP3"/>
+      <c r="ZQ3"/>
+      <c r="ZR3"/>
+      <c r="ZS3"/>
+      <c r="ZT3"/>
+      <c r="ZU3"/>
+      <c r="ZV3"/>
+      <c r="ZW3"/>
+      <c r="ZX3"/>
+      <c r="ZY3"/>
+      <c r="ZZ3"/>
+      <c r="AAA3"/>
+      <c r="AAB3"/>
+      <c r="AAC3"/>
+      <c r="AAD3"/>
+      <c r="AAE3"/>
+      <c r="AAF3"/>
+      <c r="AAG3"/>
+      <c r="AAH3"/>
+      <c r="AAI3"/>
+      <c r="AAJ3"/>
+      <c r="AAK3"/>
+      <c r="AAL3"/>
+      <c r="AAM3"/>
+      <c r="AAN3"/>
+      <c r="AAO3"/>
+      <c r="AAP3"/>
+      <c r="AAQ3"/>
+      <c r="AAR3"/>
+      <c r="AAS3"/>
+      <c r="AAT3"/>
+      <c r="AAU3"/>
+      <c r="AAV3"/>
+      <c r="AAW3"/>
+      <c r="AAX3"/>
+      <c r="AAY3"/>
+      <c r="AAZ3"/>
+      <c r="ABA3"/>
+      <c r="ABB3"/>
+      <c r="ABC3"/>
+      <c r="ABD3"/>
+      <c r="ABE3"/>
+      <c r="ABF3"/>
+      <c r="ABG3"/>
+      <c r="ABH3"/>
+      <c r="ABI3"/>
+      <c r="ABJ3"/>
+      <c r="ABK3"/>
+      <c r="ABL3"/>
+      <c r="ABM3"/>
+      <c r="ABN3"/>
+      <c r="ABO3"/>
+      <c r="ABP3"/>
+      <c r="ABQ3"/>
+      <c r="ABR3"/>
+      <c r="ABS3"/>
+      <c r="ABT3"/>
+      <c r="ABU3"/>
+      <c r="ABV3"/>
+      <c r="ABW3"/>
+      <c r="ABX3"/>
+      <c r="ABY3"/>
+      <c r="ABZ3"/>
+      <c r="ACA3"/>
+      <c r="ACB3"/>
+      <c r="ACC3"/>
+      <c r="ACD3"/>
+      <c r="ACE3"/>
+      <c r="ACF3"/>
+      <c r="ACG3"/>
+      <c r="ACH3"/>
+      <c r="ACI3"/>
+      <c r="ACJ3"/>
+      <c r="ACK3"/>
+      <c r="ACL3"/>
+      <c r="ACM3"/>
+      <c r="ACN3"/>
+      <c r="ACO3"/>
+      <c r="ACP3"/>
+      <c r="ACQ3"/>
+      <c r="ACR3"/>
+      <c r="ACS3"/>
+      <c r="ACT3"/>
+      <c r="ACU3"/>
+      <c r="ACV3"/>
+      <c r="ACW3"/>
+      <c r="ACX3"/>
+      <c r="ACY3"/>
+      <c r="ACZ3"/>
+      <c r="ADA3"/>
+      <c r="ADB3"/>
+      <c r="ADC3"/>
+      <c r="ADD3"/>
+      <c r="ADE3"/>
+      <c r="ADF3"/>
+      <c r="ADG3"/>
+      <c r="ADH3"/>
+      <c r="ADI3"/>
+      <c r="ADJ3"/>
+      <c r="ADK3"/>
+      <c r="ADL3"/>
+      <c r="ADM3"/>
+      <c r="ADN3"/>
+      <c r="ADO3"/>
+      <c r="ADP3"/>
+      <c r="ADQ3"/>
+      <c r="ADR3"/>
+      <c r="ADS3"/>
+      <c r="ADT3"/>
+      <c r="ADU3"/>
+      <c r="ADV3"/>
+      <c r="ADW3"/>
+      <c r="ADX3"/>
+      <c r="ADY3"/>
+      <c r="ADZ3"/>
+      <c r="AEA3"/>
+      <c r="AEB3"/>
+      <c r="AEC3"/>
+      <c r="AED3"/>
+      <c r="AEE3"/>
+      <c r="AEF3"/>
+      <c r="AEG3"/>
+      <c r="AEH3"/>
+      <c r="AEI3"/>
+      <c r="AEJ3"/>
+      <c r="AEK3"/>
+      <c r="AEL3"/>
+      <c r="AEM3"/>
+      <c r="AEN3"/>
+      <c r="AEO3"/>
+      <c r="AEP3"/>
+      <c r="AEQ3"/>
+      <c r="AER3"/>
+      <c r="AES3"/>
+      <c r="AET3"/>
+      <c r="AEU3"/>
+      <c r="AEV3"/>
+      <c r="AEW3"/>
+      <c r="AEX3"/>
+      <c r="AEY3"/>
+      <c r="AEZ3"/>
+      <c r="AFA3"/>
+      <c r="AFB3"/>
+      <c r="AFC3"/>
+      <c r="AFD3"/>
+      <c r="AFE3"/>
+      <c r="AFF3"/>
+      <c r="AFG3"/>
+      <c r="AFH3"/>
+      <c r="AFI3"/>
+      <c r="AFJ3"/>
+      <c r="AFK3"/>
+      <c r="AFL3"/>
+      <c r="AFM3"/>
+      <c r="AFN3"/>
+      <c r="AFO3"/>
+      <c r="AFP3"/>
+      <c r="AFQ3"/>
+      <c r="AFR3"/>
+      <c r="AFS3"/>
+      <c r="AFT3"/>
+      <c r="AFU3"/>
+      <c r="AFV3"/>
+      <c r="AFW3"/>
+      <c r="AFX3"/>
+      <c r="AFY3"/>
+      <c r="AFZ3"/>
+      <c r="AGA3"/>
+      <c r="AGB3"/>
+      <c r="AGC3"/>
+      <c r="AGD3"/>
+      <c r="AGE3"/>
+      <c r="AGF3"/>
+      <c r="AGG3"/>
+      <c r="AGH3"/>
+      <c r="AGI3"/>
+      <c r="AGJ3"/>
+      <c r="AGK3"/>
+      <c r="AGL3"/>
+      <c r="AGM3"/>
+      <c r="AGN3"/>
+      <c r="AGO3"/>
+      <c r="AGP3"/>
+      <c r="AGQ3"/>
+      <c r="AGR3"/>
+      <c r="AGS3"/>
+      <c r="AGT3"/>
+      <c r="AGU3"/>
+      <c r="AGV3"/>
+      <c r="AGW3"/>
+      <c r="AGX3"/>
+      <c r="AGY3"/>
+      <c r="AGZ3"/>
+      <c r="AHA3"/>
+      <c r="AHB3"/>
+      <c r="AHC3"/>
+      <c r="AHD3"/>
+      <c r="AHE3"/>
+      <c r="AHF3"/>
+      <c r="AHG3"/>
+      <c r="AHH3"/>
+      <c r="AHI3"/>
+      <c r="AHJ3"/>
+      <c r="AHK3"/>
+      <c r="AHL3"/>
+      <c r="AHM3"/>
+      <c r="AHN3"/>
+      <c r="AHO3"/>
+      <c r="AHP3"/>
+      <c r="AHQ3"/>
+      <c r="AHR3"/>
+      <c r="AHS3"/>
+      <c r="AHT3"/>
+      <c r="AHU3"/>
+      <c r="AHV3"/>
+      <c r="AHW3"/>
+      <c r="AHX3"/>
+      <c r="AHY3"/>
+      <c r="AHZ3"/>
+      <c r="AIA3"/>
+      <c r="AIB3"/>
+      <c r="AIC3"/>
+      <c r="AID3"/>
+      <c r="AIE3"/>
+      <c r="AIF3"/>
+      <c r="AIG3"/>
+      <c r="AIH3"/>
+      <c r="AII3"/>
+      <c r="AIJ3"/>
+      <c r="AIK3"/>
+      <c r="AIL3"/>
+      <c r="AIM3"/>
+      <c r="AIN3"/>
+      <c r="AIO3"/>
+      <c r="AIP3"/>
+      <c r="AIQ3"/>
+      <c r="AIR3"/>
+      <c r="AIS3"/>
+      <c r="AIT3"/>
+      <c r="AIU3"/>
+      <c r="AIV3"/>
+      <c r="AIW3"/>
+      <c r="AIX3"/>
+      <c r="AIY3"/>
+      <c r="AIZ3"/>
+      <c r="AJA3"/>
+      <c r="AJB3"/>
+      <c r="AJC3"/>
+      <c r="AJD3"/>
+      <c r="AJE3"/>
+      <c r="AJF3"/>
+      <c r="AJG3"/>
+      <c r="AJH3"/>
+      <c r="AJI3"/>
+      <c r="AJJ3"/>
+      <c r="AJK3"/>
+      <c r="AJL3"/>
+      <c r="AJM3"/>
+      <c r="AJN3"/>
+      <c r="AJO3"/>
+      <c r="AJP3"/>
+      <c r="AJQ3"/>
+      <c r="AJR3"/>
+      <c r="AJS3"/>
+      <c r="AJT3"/>
+      <c r="AJU3"/>
+      <c r="AJV3"/>
+      <c r="AJW3"/>
+      <c r="AJX3"/>
+      <c r="AJY3"/>
+      <c r="AJZ3"/>
+      <c r="AKA3"/>
+      <c r="AKB3"/>
+      <c r="AKC3"/>
+      <c r="AKD3"/>
+      <c r="AKE3"/>
+      <c r="AKF3"/>
+      <c r="AKG3"/>
+      <c r="AKH3"/>
+      <c r="AKI3"/>
+      <c r="AKJ3"/>
+      <c r="AKK3"/>
+      <c r="AKL3"/>
+      <c r="AKM3"/>
+      <c r="AKN3"/>
+      <c r="AKO3"/>
+      <c r="AKP3"/>
+      <c r="AKQ3"/>
+      <c r="AKR3"/>
+      <c r="AKS3"/>
+      <c r="AKT3"/>
+      <c r="AKU3"/>
+      <c r="AKV3"/>
+      <c r="AKW3"/>
+      <c r="AKX3"/>
+      <c r="AKY3"/>
+      <c r="AKZ3"/>
+      <c r="ALA3"/>
+      <c r="ALB3"/>
+      <c r="ALC3"/>
+      <c r="ALD3"/>
+      <c r="ALE3"/>
+      <c r="ALF3"/>
+      <c r="ALG3"/>
+      <c r="ALH3"/>
+      <c r="ALI3"/>
+      <c r="ALJ3"/>
+      <c r="ALK3"/>
+      <c r="ALL3"/>
+      <c r="ALM3"/>
+      <c r="ALN3"/>
+      <c r="ALO3"/>
+      <c r="ALP3"/>
+      <c r="ALQ3"/>
+      <c r="ALR3"/>
+      <c r="ALS3"/>
+      <c r="ALT3"/>
+      <c r="ALU3"/>
+      <c r="ALV3"/>
+      <c r="ALW3"/>
+      <c r="ALX3"/>
+      <c r="ALY3"/>
+      <c r="ALZ3"/>
+      <c r="AMA3"/>
+      <c r="AMB3"/>
+      <c r="AMC3"/>
+      <c r="AMD3"/>
+      <c r="AME3"/>
+      <c r="AMF3"/>
+      <c r="AMG3"/>
+      <c r="AMH3"/>
+      <c r="AMI3"/>
+      <c r="AMJ3"/>
+      <c r="AMK3"/>
+      <c r="AML3"/>
+      <c r="AMM3"/>
+      <c r="AMN3"/>
+      <c r="AMO3"/>
+    </row>
+    <row r="4" spans="1:1029" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1029" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1029" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1029" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1029" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{005D001A-3768-4392-8BD8-510250183310}">
+  <dimension ref="A1:HU5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="24.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="39.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="33.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.90625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.08984375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="G2"/>
+      <c r="H2"/>
+      <c r="I2"/>
+      <c r="J2"/>
+      <c r="K2"/>
+      <c r="L2"/>
+      <c r="M2"/>
+      <c r="N2"/>
+      <c r="O2"/>
+      <c r="P2"/>
+      <c r="Q2"/>
+      <c r="R2"/>
+      <c r="S2"/>
+      <c r="T2"/>
+      <c r="U2"/>
+      <c r="V2"/>
+      <c r="W2"/>
+      <c r="X2"/>
+      <c r="Y2"/>
+      <c r="Z2"/>
+      <c r="AA2"/>
+      <c r="AB2"/>
+      <c r="AC2"/>
+      <c r="AD2"/>
+      <c r="AE2"/>
+      <c r="AF2"/>
+      <c r="AG2"/>
+      <c r="AH2"/>
+      <c r="AI2"/>
+      <c r="AJ2"/>
+      <c r="AK2"/>
+      <c r="AL2"/>
+      <c r="AM2"/>
+      <c r="AN2"/>
+      <c r="AO2"/>
+      <c r="AP2"/>
+      <c r="AQ2"/>
+      <c r="AR2"/>
+      <c r="AS2"/>
+      <c r="AT2"/>
+      <c r="AU2"/>
+      <c r="AV2"/>
+      <c r="AW2"/>
+      <c r="AX2"/>
+      <c r="AY2"/>
+      <c r="AZ2"/>
+      <c r="BA2"/>
+      <c r="BB2"/>
+      <c r="BC2"/>
+      <c r="BD2"/>
+      <c r="BE2"/>
+      <c r="BF2"/>
+      <c r="BG2"/>
+      <c r="BH2"/>
+      <c r="BI2"/>
+      <c r="BJ2"/>
+      <c r="BK2"/>
+      <c r="BL2"/>
+      <c r="BM2"/>
+      <c r="BN2"/>
+      <c r="BO2"/>
+      <c r="BP2"/>
+      <c r="BQ2"/>
+      <c r="BR2"/>
+      <c r="BS2"/>
+      <c r="BT2"/>
+      <c r="BU2"/>
+      <c r="BV2"/>
+      <c r="BW2"/>
+      <c r="BX2"/>
+      <c r="BY2"/>
+      <c r="BZ2"/>
+      <c r="CA2"/>
+      <c r="CB2"/>
+      <c r="CC2"/>
+      <c r="CD2"/>
+      <c r="CE2"/>
+      <c r="CF2"/>
+      <c r="CG2"/>
+      <c r="CH2"/>
+      <c r="CI2"/>
+      <c r="CJ2"/>
+      <c r="CK2"/>
+      <c r="CL2"/>
+      <c r="CM2"/>
+      <c r="CN2"/>
+      <c r="CO2"/>
+      <c r="CP2"/>
+      <c r="CQ2"/>
+      <c r="CR2"/>
+      <c r="CS2"/>
+      <c r="CT2"/>
+      <c r="CU2"/>
+      <c r="CV2"/>
+      <c r="CW2"/>
+      <c r="CX2"/>
+      <c r="CY2"/>
+      <c r="CZ2"/>
+      <c r="DA2"/>
+      <c r="DB2"/>
+      <c r="DC2"/>
+      <c r="DD2"/>
+      <c r="DE2"/>
+      <c r="DF2"/>
+      <c r="DG2"/>
+      <c r="DH2"/>
+      <c r="DI2"/>
+      <c r="DJ2"/>
+      <c r="DK2"/>
+      <c r="DL2"/>
+      <c r="DM2"/>
+      <c r="DN2"/>
+      <c r="DO2"/>
+      <c r="DP2"/>
+      <c r="DQ2"/>
+      <c r="DR2"/>
+      <c r="DS2"/>
+      <c r="DT2"/>
+      <c r="DU2"/>
+      <c r="DV2"/>
+      <c r="DW2"/>
+      <c r="DX2"/>
+      <c r="DY2"/>
+      <c r="DZ2"/>
+      <c r="EA2"/>
+      <c r="EB2"/>
+      <c r="EC2"/>
+      <c r="ED2"/>
+      <c r="EE2"/>
+      <c r="EF2"/>
+      <c r="EG2"/>
+      <c r="EH2"/>
+      <c r="EI2"/>
+      <c r="EJ2"/>
+      <c r="EK2"/>
+      <c r="EL2"/>
+      <c r="EM2"/>
+      <c r="EN2"/>
+      <c r="EO2"/>
+      <c r="EP2"/>
+      <c r="EQ2"/>
+      <c r="ER2"/>
+      <c r="ES2"/>
+      <c r="ET2"/>
+      <c r="EU2"/>
+      <c r="EV2"/>
+      <c r="EW2"/>
+      <c r="EX2"/>
+      <c r="EY2"/>
+      <c r="EZ2"/>
+      <c r="FA2"/>
+      <c r="FB2"/>
+      <c r="FC2"/>
+      <c r="FD2"/>
+      <c r="FE2"/>
+      <c r="FF2"/>
+      <c r="FG2"/>
+      <c r="FH2"/>
+      <c r="FI2"/>
+      <c r="FJ2"/>
+      <c r="FK2"/>
+      <c r="FL2"/>
+      <c r="FM2"/>
+      <c r="FN2"/>
+      <c r="FO2"/>
+      <c r="FP2"/>
+      <c r="FQ2"/>
+      <c r="FR2"/>
+      <c r="FS2"/>
+      <c r="FT2"/>
+      <c r="FU2"/>
+      <c r="FV2"/>
+      <c r="FW2"/>
+      <c r="FX2"/>
+      <c r="FY2"/>
+      <c r="FZ2"/>
+      <c r="GA2"/>
+      <c r="GB2"/>
+      <c r="GC2"/>
+      <c r="GD2"/>
+      <c r="GE2"/>
+      <c r="GF2"/>
+      <c r="GG2"/>
+      <c r="GH2"/>
+      <c r="GI2"/>
+      <c r="GJ2"/>
+      <c r="GK2"/>
+      <c r="GL2"/>
+      <c r="GM2"/>
+      <c r="GN2"/>
+      <c r="GO2"/>
+      <c r="GP2"/>
+      <c r="GQ2"/>
+      <c r="GR2"/>
+      <c r="GS2"/>
+      <c r="GT2"/>
+      <c r="GU2"/>
+      <c r="GV2"/>
+      <c r="GW2"/>
+      <c r="GX2"/>
+      <c r="GY2"/>
+      <c r="GZ2"/>
+      <c r="HA2"/>
+      <c r="HB2"/>
+      <c r="HC2"/>
+      <c r="HD2"/>
+      <c r="HE2"/>
+      <c r="HF2"/>
+      <c r="HG2"/>
+      <c r="HH2"/>
+      <c r="HI2"/>
+      <c r="HJ2"/>
+      <c r="HK2"/>
+      <c r="HL2"/>
+      <c r="HM2"/>
+      <c r="HN2"/>
+      <c r="HO2"/>
+      <c r="HP2"/>
+      <c r="HQ2"/>
+      <c r="HR2"/>
+      <c r="HS2"/>
+      <c r="HT2"/>
+      <c r="HU2"/>
+    </row>
+    <row r="3" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="G3"/>
+      <c r="H3"/>
+      <c r="I3"/>
+      <c r="J3"/>
+      <c r="K3"/>
+      <c r="L3"/>
+      <c r="M3"/>
+      <c r="N3"/>
+      <c r="O3"/>
+      <c r="P3"/>
+      <c r="Q3"/>
+      <c r="R3"/>
+      <c r="S3"/>
+      <c r="T3"/>
+      <c r="U3"/>
+      <c r="V3"/>
+      <c r="W3"/>
+      <c r="X3"/>
+      <c r="Y3"/>
+      <c r="Z3"/>
+      <c r="AA3"/>
+      <c r="AB3"/>
+      <c r="AC3"/>
+      <c r="AD3"/>
+      <c r="AE3"/>
+      <c r="AF3"/>
+      <c r="AG3"/>
+      <c r="AH3"/>
+      <c r="AI3"/>
+      <c r="AJ3"/>
+      <c r="AK3"/>
+      <c r="AL3"/>
+      <c r="AM3"/>
+      <c r="AN3"/>
+      <c r="AO3"/>
+      <c r="AP3"/>
+      <c r="AQ3"/>
+      <c r="AR3"/>
+      <c r="AS3"/>
+      <c r="AT3"/>
+      <c r="AU3"/>
+      <c r="AV3"/>
+      <c r="AW3"/>
+      <c r="AX3"/>
+      <c r="AY3"/>
+      <c r="AZ3"/>
+      <c r="BA3"/>
+      <c r="BB3"/>
+      <c r="BC3"/>
+      <c r="BD3"/>
+      <c r="BE3"/>
+      <c r="BF3"/>
+      <c r="BG3"/>
+      <c r="BH3"/>
+      <c r="BI3"/>
+      <c r="BJ3"/>
+      <c r="BK3"/>
+      <c r="BL3"/>
+      <c r="BM3"/>
+      <c r="BN3"/>
+      <c r="BO3"/>
+      <c r="BP3"/>
+      <c r="BQ3"/>
+      <c r="BR3"/>
+      <c r="BS3"/>
+      <c r="BT3"/>
+      <c r="BU3"/>
+      <c r="BV3"/>
+      <c r="BW3"/>
+      <c r="BX3"/>
+      <c r="BY3"/>
+      <c r="BZ3"/>
+      <c r="CA3"/>
+      <c r="CB3"/>
+      <c r="CC3"/>
+      <c r="CD3"/>
+      <c r="CE3"/>
+      <c r="CF3"/>
+      <c r="CG3"/>
+      <c r="CH3"/>
+      <c r="CI3"/>
+      <c r="CJ3"/>
+      <c r="CK3"/>
+      <c r="CL3"/>
+      <c r="CM3"/>
+      <c r="CN3"/>
+      <c r="CO3"/>
+      <c r="CP3"/>
+      <c r="CQ3"/>
+      <c r="CR3"/>
+      <c r="CS3"/>
+      <c r="CT3"/>
+      <c r="CU3"/>
+      <c r="CV3"/>
+      <c r="CW3"/>
+      <c r="CX3"/>
+      <c r="CY3"/>
+      <c r="CZ3"/>
+      <c r="DA3"/>
+      <c r="DB3"/>
+      <c r="DC3"/>
+      <c r="DD3"/>
+      <c r="DE3"/>
+      <c r="DF3"/>
+      <c r="DG3"/>
+      <c r="DH3"/>
+      <c r="DI3"/>
+      <c r="DJ3"/>
+      <c r="DK3"/>
+      <c r="DL3"/>
+      <c r="DM3"/>
+      <c r="DN3"/>
+      <c r="DO3"/>
+      <c r="DP3"/>
+      <c r="DQ3"/>
+      <c r="DR3"/>
+      <c r="DS3"/>
+      <c r="DT3"/>
+      <c r="DU3"/>
+      <c r="DV3"/>
+      <c r="DW3"/>
+      <c r="DX3"/>
+      <c r="DY3"/>
+      <c r="DZ3"/>
+      <c r="EA3"/>
+      <c r="EB3"/>
+      <c r="EC3"/>
+      <c r="ED3"/>
+      <c r="EE3"/>
+      <c r="EF3"/>
+      <c r="EG3"/>
+      <c r="EH3"/>
+      <c r="EI3"/>
+      <c r="EJ3"/>
+      <c r="EK3"/>
+      <c r="EL3"/>
+      <c r="EM3"/>
+      <c r="EN3"/>
+      <c r="EO3"/>
+      <c r="EP3"/>
+      <c r="EQ3"/>
+      <c r="ER3"/>
+      <c r="ES3"/>
+      <c r="ET3"/>
+      <c r="EU3"/>
+      <c r="EV3"/>
+      <c r="EW3"/>
+      <c r="EX3"/>
+      <c r="EY3"/>
+      <c r="EZ3"/>
+      <c r="FA3"/>
+      <c r="FB3"/>
+      <c r="FC3"/>
+      <c r="FD3"/>
+      <c r="FE3"/>
+      <c r="FF3"/>
+      <c r="FG3"/>
+      <c r="FH3"/>
+      <c r="FI3"/>
+      <c r="FJ3"/>
+      <c r="FK3"/>
+      <c r="FL3"/>
+      <c r="FM3"/>
+      <c r="FN3"/>
+      <c r="FO3"/>
+      <c r="FP3"/>
+      <c r="FQ3"/>
+      <c r="FR3"/>
+      <c r="FS3"/>
+      <c r="FT3"/>
+      <c r="FU3"/>
+      <c r="FV3"/>
+      <c r="FW3"/>
+      <c r="FX3"/>
+      <c r="FY3"/>
+      <c r="FZ3"/>
+      <c r="GA3"/>
+      <c r="GB3"/>
+      <c r="GC3"/>
+      <c r="GD3"/>
+      <c r="GE3"/>
+      <c r="GF3"/>
+      <c r="GG3"/>
+      <c r="GH3"/>
+      <c r="GI3"/>
+      <c r="GJ3"/>
+      <c r="GK3"/>
+      <c r="GL3"/>
+      <c r="GM3"/>
+      <c r="GN3"/>
+      <c r="GO3"/>
+      <c r="GP3"/>
+      <c r="GQ3"/>
+      <c r="GR3"/>
+      <c r="GS3"/>
+      <c r="GT3"/>
+      <c r="GU3"/>
+      <c r="GV3"/>
+      <c r="GW3"/>
+      <c r="GX3"/>
+      <c r="GY3"/>
+      <c r="GZ3"/>
+      <c r="HA3"/>
+      <c r="HB3"/>
+      <c r="HC3"/>
+      <c r="HD3"/>
+      <c r="HE3"/>
+      <c r="HF3"/>
+      <c r="HG3"/>
+      <c r="HH3"/>
+      <c r="HI3"/>
+      <c r="HJ3"/>
+      <c r="HK3"/>
+      <c r="HL3"/>
+      <c r="HM3"/>
+      <c r="HN3"/>
+      <c r="HO3"/>
+      <c r="HP3"/>
+      <c r="HQ3"/>
+      <c r="HR3"/>
+      <c r="HS3"/>
+      <c r="HT3"/>
+      <c r="HU3"/>
+    </row>
+    <row r="4" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A4" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="5" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A5" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>130</v>
       </c>
     </row>
   </sheetData>

--- a/testdata.xlsx
+++ b/testdata.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sshiwani\workspace\find-information-products-services-tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55804917-92F1-4B7D-BF36-02503B3D2E86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65523A05-6494-4F6F-9A24-032AF18B86CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -500,7 +500,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
@@ -508,7 +508,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3987,10 +3986,10 @@
       <c r="HU3"/>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="3" t="s">
         <v>124</v>
       </c>
       <c r="C4" s="3" t="s">
@@ -4007,10 +4006,10 @@
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="3" t="s">
         <v>128</v>
       </c>
       <c r="C5" s="3" t="s">

--- a/testdata.xlsx
+++ b/testdata.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sshiwani\workspace\find-information-products-services-tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA56CDD4-9DE4-410E-8DC1-36548A45032A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{759335DB-C01C-4D37-91AF-2CDF617A42C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" firstSheet="12" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="category_phase" sheetId="1" r:id="rId1"/>
     <sheet name="category_channel" sheetId="2" r:id="rId2"/>
-    <sheet name="category_group" sheetId="3" r:id="rId3"/>
+    <sheet name="category_businessarea" sheetId="3" r:id="rId3"/>
     <sheet name="category_type" sheetId="4" r:id="rId4"/>
     <sheet name="usergroup_AdultLearner18_list" sheetId="5" r:id="rId5"/>
     <sheet name="usergroup_CareersAdviser_list" sheetId="6" r:id="rId6"/>
@@ -28,6 +28,13 @@
     <sheet name="usergroup_ParentorCarer_list" sheetId="13" r:id="rId13"/>
     <sheet name="usergroup_ProfExtUserofDfE_list" sheetId="14" r:id="rId14"/>
     <sheet name="usergroup_SocialCWorkforce_list" sheetId="15" r:id="rId15"/>
+    <sheet name="UGSubcategory_AdultLearner" sheetId="16" r:id="rId16"/>
+    <sheet name="UGSubcategory_CareersAdviser" sheetId="17" r:id="rId17"/>
+    <sheet name="UGSubcategory_ChildOrYoungPers" sheetId="18" r:id="rId18"/>
+    <sheet name="UGSubcategory_DfEWorkforce" sheetId="19" r:id="rId19"/>
+    <sheet name="UGSubcategory_Employer" sheetId="20" r:id="rId20"/>
+    <sheet name="UGSubcategory_LAWorkforce" sheetId="21" r:id="rId21"/>
+    <sheet name="UGSubcategory_NEETOrCareerSeek" sheetId="22" r:id="rId22"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -39,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="889" uniqueCount="407">
   <si>
     <t>products?phase=request</t>
   </si>
@@ -296,9 +303,6 @@
     <t>Remove this filter families</t>
   </si>
   <si>
-    <t>//h3[normalize-space()='Group']</t>
-  </si>
-  <si>
     <t>#group-families</t>
   </si>
   <si>
@@ -798,16 +802,487 @@
   </si>
   <si>
     <t>Social worker</t>
+  </si>
+  <si>
+    <t>Remove this filter Adult learner</t>
+  </si>
+  <si>
+    <t>//h3[normalize-space()='User groups']</t>
+  </si>
+  <si>
+    <t>#user-0</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text('Adult learner')</t>
+  </si>
+  <si>
+    <t>products?userGroup=adult-learner-18</t>
+  </si>
+  <si>
+    <t>products?userGroup=category-value</t>
+  </si>
+  <si>
+    <t>products?userGroup=adult-learner-in-non-work-based-learning-or-training</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Adult in work based learning or training  (Adult learner (18+))')</t>
+  </si>
+  <si>
+    <t>Remove this filter Adult in work based learning or training  (Adult learner (18+))</t>
+  </si>
+  <si>
+    <t>Selected_UserTypes_Locator</t>
+  </si>
+  <si>
+    <t>Selected_UserTypes</t>
+  </si>
+  <si>
+    <t>//*[@id="selected-users-list"]/div/label</t>
+  </si>
+  <si>
+    <t>//label[contains(text(),'Adult in work based learning')]</t>
+  </si>
+  <si>
+    <t>Adult in work based learning or training  (Adult learner (18+))</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Adult learner in non-work based learning or training  (Adult learner')</t>
+  </si>
+  <si>
+    <t>Remove this filter Adult learner in non-work based learning or training  (Adult learner</t>
+  </si>
+  <si>
+    <t>//label[contains(text(),'Adult learner in non-work based learning or traini')]</t>
+  </si>
+  <si>
+    <t>Adult learner in non-work based learning or training (Adult learner (18+))</t>
+  </si>
+  <si>
+    <t>products?userGroup=student-further-education</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Student (further education)  (Adult learner (18+))')</t>
+  </si>
+  <si>
+    <t>Remove this filter Student (further education)  (Adult learner (18+))</t>
+  </si>
+  <si>
+    <t>//label[contains(text(),'Student (further education)')]</t>
+  </si>
+  <si>
+    <t>Student (further education)  (Adult learner (18+))</t>
+  </si>
+  <si>
+    <t>products?userGroup=student-higher-education</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Student (higher education)  (Adult learner (18+))')</t>
+  </si>
+  <si>
+    <t>Remove this filter Student (higher education)  (Adult learner (18+))</t>
+  </si>
+  <si>
+    <t>//label[contains(text(),'Student (higher education)')]</t>
+  </si>
+  <si>
+    <t>Student (higher education)  (Adult learner (18+))</t>
+  </si>
+  <si>
+    <t>products?userGroup=careers-adviser-or-work-coach</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Careers adviser or work coach')</t>
+  </si>
+  <si>
+    <t>Remove this filter Careers adviser or work coach</t>
+  </si>
+  <si>
+    <t>products?userGroup=independent-careers-adviser</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Independent careers adviser  (Careers adviser or work coach)')</t>
+  </si>
+  <si>
+    <t>Remove this filter Independent careers adviser  (Careers adviser or work coach)</t>
+  </si>
+  <si>
+    <t>Independent careers adviser  (Careers adviser or work coach)</t>
+  </si>
+  <si>
+    <t>products?userGroup=national-careers-service-careers-adviser</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' National careers service careers adviser  (Careers adviser or work coach)')</t>
+  </si>
+  <si>
+    <t>Remove this filter National careers service careers adviser  (Careers adviser or work coach)</t>
+  </si>
+  <si>
+    <t>National careers service careers adviser  (Careers adviser or work coach)</t>
+  </si>
+  <si>
+    <t>products?userGroup=work-coach</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Work coach  (Careers adviser or work coach)')</t>
+  </si>
+  <si>
+    <t>Remove this filter Work coach  (Careers adviser or work coach)</t>
+  </si>
+  <si>
+    <t>Work coach  (Careers adviser or work coach)</t>
+  </si>
+  <si>
+    <t>products?userGroup=child-or-young-person</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Child or young person')</t>
+  </si>
+  <si>
+    <t>Remove this filter Child or young person</t>
+  </si>
+  <si>
+    <t>products?userGroup=child-early-years-age</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Child (early years age) ')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remove this filter Child (early years age) </t>
+  </si>
+  <si>
+    <t>Child (early years age)  (Child or young person)</t>
+  </si>
+  <si>
+    <t>products?userGroup=child-primary-age</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remove this filter Child (primary age) </t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Child (primary age) ')</t>
+  </si>
+  <si>
+    <t>Child (primary age)  (Child or young person)</t>
+  </si>
+  <si>
+    <t>products?userGroup=child-secondary-age-up-to-16</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Child (secondary age up to 16)  (Child or young person)')</t>
+  </si>
+  <si>
+    <t>Remove this filter Child (secondary age up to 16)  (Child or young person)</t>
+  </si>
+  <si>
+    <t>Child (secondary age up to 16)  (Child or young person)</t>
+  </si>
+  <si>
+    <t>products?userGroup=young-person-16-18</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Young person (16-18)  (Child or young person)')</t>
+  </si>
+  <si>
+    <t>Remove this filter Young person (16-18)  (Child or young person)</t>
+  </si>
+  <si>
+    <t>Young person (16-18)  (Child or young person)</t>
+  </si>
+  <si>
+    <t>products?userGroup=young-person-with-send-16-25</t>
+  </si>
+  <si>
+    <t>Remove this filter Young person with SEND (16-25)  (Child or young person)</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Young person with SEND (16-25)  (Child or young person)')</t>
+  </si>
+  <si>
+    <t>Young person with SEND (16-25)  (Child or young person)</t>
+  </si>
+  <si>
+    <t>products?userGroup=department-for-education-workforce</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Department for Education workforce')</t>
+  </si>
+  <si>
+    <t>Remove this filter Department for Education workforce</t>
+  </si>
+  <si>
+    <t>products?userGroup=colleague-supporting-dfe-users</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Colleague supporting DfE users  (Department for Education workforce)')</t>
+  </si>
+  <si>
+    <t>Remove this filter Colleague supporting DfE users  (Department for Education workforce)</t>
+  </si>
+  <si>
+    <t>Colleague supporting DfE users  (Department for Education workforce)</t>
+  </si>
+  <si>
+    <t>products?userGroup=colleague-supporting-external-stakeholders</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Colleague supporting external stakeholders  (Department for Education workforce)')</t>
+  </si>
+  <si>
+    <t>Remove this filter Colleague supporting external stakeholders  (Department for Education workforce)</t>
+  </si>
+  <si>
+    <t>Colleague supporting external stakeholders  (Department for Education workforce)</t>
+  </si>
+  <si>
+    <t>products?userGroup=colleague-using-data</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Colleague using data  (Department for Education workforce)')</t>
+  </si>
+  <si>
+    <t>Remove this filter Colleague using data  (Department for Education workforce)</t>
+  </si>
+  <si>
+    <t>Colleague using data  (Department for Education workforce)</t>
+  </si>
+  <si>
+    <t>products?userGroup=colleague-using-digital-to-deliver-services</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Colleague using digital to deliver services  (Department for Education workforce)')</t>
+  </si>
+  <si>
+    <t>Remove this filter Colleague using digital to deliver services  (Department for Education workforce)</t>
+  </si>
+  <si>
+    <t>Colleague using digital to deliver services  (Department for Education workforce)</t>
+  </si>
+  <si>
+    <t>products?userGroup=employer</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Employer')</t>
+  </si>
+  <si>
+    <t>Remove this filter Employer</t>
+  </si>
+  <si>
+    <t>products?userGroup=employer-1-249-employees</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Employer (1-249 employees)  (Employer)')</t>
+  </si>
+  <si>
+    <t>Remove this filter Employer (1-249 employees)  (Employer)</t>
+  </si>
+  <si>
+    <t>Employer (1-249 employees)  (Employer)</t>
+  </si>
+  <si>
+    <t>products?userGroup=employer-250-or-more-employees</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Employer (250 or more employees)  (Employer)')</t>
+  </si>
+  <si>
+    <t>Remove this filter Employer (250 or more employees)  (Employer)</t>
+  </si>
+  <si>
+    <t>Employer (250 or more employees)  (Employer)</t>
+  </si>
+  <si>
+    <t>products?userGroup=self-employed-person</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Self-employed person  (Employer)')</t>
+  </si>
+  <si>
+    <t>Remove this filter Self-employed person  (Employer)</t>
+  </si>
+  <si>
+    <t>Self-employed person  (Employer)</t>
+  </si>
+  <si>
+    <t>products?userGroup=local-authority-workforce</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Local authority workforce')</t>
+  </si>
+  <si>
+    <t>Remove this filter Local authority workforce</t>
+  </si>
+  <si>
+    <t>products?userGroup=business-support-officer-local-authority</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Business support officer (local authority) ')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remove this filter Business support officer (local authority) </t>
+  </si>
+  <si>
+    <t>Business support officer (local authority)  (Local authority workforce)</t>
+  </si>
+  <si>
+    <t>products?userGroup=category-value-1</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Digital professional (local authority)  (Local authority workforce)')</t>
+  </si>
+  <si>
+    <t>Remove this filter Digital professional (local authority)  (Local authority workforce)</t>
+  </si>
+  <si>
+    <t>Digital professional (local authority)  (Local authority workforce)</t>
+  </si>
+  <si>
+    <t>products?userGroup=finance-support-officer-local-authority</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Finance support officer (local authority) ')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remove this filter Finance support officer (local authority) </t>
+  </si>
+  <si>
+    <t>Finance support officer (local authority)  (Local authority workforce)</t>
+  </si>
+  <si>
+    <t>products?userGroup=senior-leader-local-authority</t>
+  </si>
+  <si>
+    <t>Remove this filter Senior leader (local authority)  (Local authority workforce)</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Senior leader (local authority)  (Local authority workforce)')</t>
+  </si>
+  <si>
+    <t>Senior leader (local authority)  (Local authority workforce)</t>
+  </si>
+  <si>
+    <t>products?userGroup=technology-professional-local-authority</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Technology professional (local authority)  (Local authority workforce)')</t>
+  </si>
+  <si>
+    <t>Remove this filter Technology professional (local authority)  (Local authority workforce)</t>
+  </si>
+  <si>
+    <t>Technology professional (local authority)  (Local authority workforce)</t>
+  </si>
+  <si>
+    <t>products?userGroup=neet-or-career-seeker</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' NEET or career seeker')</t>
+  </si>
+  <si>
+    <t>Remove this filter NEET or career seeker</t>
+  </si>
+  <si>
+    <t>products?userGroup=adult-19-25-neet</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Adult (19-25) (NEET)  (NEET or career seeker)')</t>
+  </si>
+  <si>
+    <t>Remove this filter Adult (19-25) (NEET)  (NEET or career seeker)</t>
+  </si>
+  <si>
+    <t>Adult (19-25) (NEET)  (NEET or career seeker)</t>
+  </si>
+  <si>
+    <t>products?userGroup=adult-career-seeker-starter-or-changer</t>
+  </si>
+  <si>
+    <t>Remove this filter Adult career seeker (starter or changer)  (NEET or career seeker)</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Adult career seeker (starter or changer)  (NEET or career seeker)')</t>
+  </si>
+  <si>
+    <t>Adult career seeker (starter or changer)  (NEET or career seeker)</t>
+  </si>
+  <si>
+    <t>products?userGroup=young-person-16-18-career-seeker</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Young person (16-18) (career seeker)  (NEET or career seeker)')</t>
+  </si>
+  <si>
+    <t>Remove this filter Young person (16-18) (career seeker)  (NEET or career seeker)</t>
+  </si>
+  <si>
+    <t>Young person (16-18) (career seeker)  (NEET or career seeker)</t>
+  </si>
+  <si>
+    <t>products?userGroup=young-person-16-18-neet</t>
+  </si>
+  <si>
+    <t>Remove this filter Young person (16-18) (NEET)  (NEET or career seeker)</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Young person (16-18) (NEET)  (NEET or career seeker)')</t>
+  </si>
+  <si>
+    <t>Young person (16-18) (NEET)  (NEET or career seeker)</t>
+  </si>
+  <si>
+    <t>products?userGroup=young-person-with-send-16-25-career-seeker</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Young person with SEND (16-25) (career seeker)  (NEET or career seeker)')</t>
+  </si>
+  <si>
+    <t>Remove this filter Young person with SEND (16-25) (career seeker)  (NEET or career seeker)</t>
+  </si>
+  <si>
+    <t>Young person with SEND (16-25) (career seeker)  (NEET or career seeker)</t>
+  </si>
+  <si>
+    <t>//h3[normalize-space()='Business area']</t>
+  </si>
+  <si>
+    <t>products?group=commercial</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' commercial')</t>
+  </si>
+  <si>
+    <t>Remove this filter commercial</t>
+  </si>
+  <si>
+    <t>#group-commercial</t>
+  </si>
+  <si>
+    <t>products?type=data-collection-and-reporting</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Data collection and reporting')</t>
+  </si>
+  <si>
+    <t>Remove this filter Data collection and reporting</t>
+  </si>
+  <si>
+    <t>#type-data-collection-and-reporting</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -845,7 +1320,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -879,11 +1354,37 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
@@ -891,6 +1392,8 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -12849,86 +13352,86 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="C1" s="6" t="s">
         <v>140</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>199</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3"/>
       <c r="B7" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>158</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3"/>
       <c r="B8" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>156</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>157</v>
       </c>
     </row>
   </sheetData>
@@ -12948,108 +13451,108 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="C1" s="6" t="s">
         <v>140</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>205</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3"/>
       <c r="B9" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>158</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="3"/>
       <c r="B10" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>156</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>157</v>
       </c>
     </row>
   </sheetData>
@@ -13070,108 +13573,108 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="C1" s="6" t="s">
         <v>140</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>213</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3"/>
       <c r="B9" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>158</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="3"/>
       <c r="B10" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>156</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>157</v>
       </c>
     </row>
   </sheetData>
@@ -13191,141 +13694,141 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="C1" s="6" t="s">
         <v>140</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>221</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>232</v>
-      </c>
       <c r="C11" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="3"/>
       <c r="B12" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>158</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="3"/>
       <c r="B13" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>156</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>157</v>
       </c>
     </row>
   </sheetData>
@@ -13345,119 +13848,119 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="C1" s="6" t="s">
         <v>140</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>233</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="3"/>
       <c r="B10" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>158</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="3"/>
       <c r="B11" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>156</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>157</v>
       </c>
     </row>
   </sheetData>
@@ -13477,141 +13980,141 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="C1" s="6" t="s">
         <v>140</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>242</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="3"/>
       <c r="B12" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>158</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="3"/>
       <c r="B13" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>156</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>157</v>
       </c>
     </row>
   </sheetData>
@@ -13619,20 +14122,22 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2DC696B-E1A8-430C-BC9E-87DD1A6FBE9F}">
-  <dimension ref="A1:F10"/>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB5527F7-85DB-4F8E-B4B3-EC8453E599E1}">
+  <dimension ref="A1:HU6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="33.08984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="43.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="34.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="52.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.453125" customWidth="1"/>
     <col min="4" max="4" width="33.36328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.90625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="25.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="33.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.08984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="46.36328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="62.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>42</v>
       </c>
@@ -13651,246 +14156,38 @@
       <c r="F1" s="2" t="s">
         <v>47</v>
       </c>
+      <c r="G1" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>262</v>
+      </c>
     </row>
-    <row r="2" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>50</v>
+        <v>256</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>48</v>
+        <v>255</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>49</v>
+        <v>252</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>4</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>51</v>
+        <v>253</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>81</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9169CA5-09CB-4ADC-8EEE-AB383FD3DBB7}">
-  <dimension ref="A1:AMO10"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="40.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="52.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.36328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="33.36328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.26953125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="32.7265625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1029" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1029" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="G2"/>
-      <c r="H2"/>
+        <v>254</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>145</v>
+      </c>
       <c r="I2"/>
       <c r="J2"/>
       <c r="K2"/>
@@ -14112,1988 +14409,5021 @@
       <c r="HS2"/>
       <c r="HT2"/>
       <c r="HU2"/>
-      <c r="HV2"/>
-      <c r="HW2"/>
-      <c r="HX2"/>
-      <c r="HY2"/>
-      <c r="HZ2"/>
-      <c r="IA2"/>
-      <c r="IB2"/>
-      <c r="IC2"/>
-      <c r="ID2"/>
-      <c r="IE2"/>
-      <c r="IF2"/>
-      <c r="IG2"/>
-      <c r="IH2"/>
-      <c r="II2"/>
-      <c r="IJ2"/>
-      <c r="IK2"/>
-      <c r="IL2"/>
-      <c r="IM2"/>
-      <c r="IN2"/>
-      <c r="IO2"/>
-      <c r="IP2"/>
-      <c r="IQ2"/>
-      <c r="IR2"/>
-      <c r="IS2"/>
-      <c r="IT2"/>
-      <c r="IU2"/>
-      <c r="IV2"/>
-      <c r="IW2"/>
-      <c r="IX2"/>
-      <c r="IY2"/>
-      <c r="IZ2"/>
-      <c r="JA2"/>
-      <c r="JB2"/>
-      <c r="JC2"/>
-      <c r="JD2"/>
-      <c r="JE2"/>
-      <c r="JF2"/>
-      <c r="JG2"/>
-      <c r="JH2"/>
-      <c r="JI2"/>
-      <c r="JJ2"/>
-      <c r="JK2"/>
-      <c r="JL2"/>
-      <c r="JM2"/>
-      <c r="JN2"/>
-      <c r="JO2"/>
-      <c r="JP2"/>
-      <c r="JQ2"/>
-      <c r="JR2"/>
-      <c r="JS2"/>
-      <c r="JT2"/>
-      <c r="JU2"/>
-      <c r="JV2"/>
-      <c r="JW2"/>
-      <c r="JX2"/>
-      <c r="JY2"/>
-      <c r="JZ2"/>
-      <c r="KA2"/>
-      <c r="KB2"/>
-      <c r="KC2"/>
-      <c r="KD2"/>
-      <c r="KE2"/>
-      <c r="KF2"/>
-      <c r="KG2"/>
-      <c r="KH2"/>
-      <c r="KI2"/>
-      <c r="KJ2"/>
-      <c r="KK2"/>
-      <c r="KL2"/>
-      <c r="KM2"/>
-      <c r="KN2"/>
-      <c r="KO2"/>
-      <c r="KP2"/>
-      <c r="KQ2"/>
-      <c r="KR2"/>
-      <c r="KS2"/>
-      <c r="KT2"/>
-      <c r="KU2"/>
-      <c r="KV2"/>
-      <c r="KW2"/>
-      <c r="KX2"/>
-      <c r="KY2"/>
-      <c r="KZ2"/>
-      <c r="LA2"/>
-      <c r="LB2"/>
-      <c r="LC2"/>
-      <c r="LD2"/>
-      <c r="LE2"/>
-      <c r="LF2"/>
-      <c r="LG2"/>
-      <c r="LH2"/>
-      <c r="LI2"/>
-      <c r="LJ2"/>
-      <c r="LK2"/>
-      <c r="LL2"/>
-      <c r="LM2"/>
-      <c r="LN2"/>
-      <c r="LO2"/>
-      <c r="LP2"/>
-      <c r="LQ2"/>
-      <c r="LR2"/>
-      <c r="LS2"/>
-      <c r="LT2"/>
-      <c r="LU2"/>
-      <c r="LV2"/>
-      <c r="LW2"/>
-      <c r="LX2"/>
-      <c r="LY2"/>
-      <c r="LZ2"/>
-      <c r="MA2"/>
-      <c r="MB2"/>
-      <c r="MC2"/>
-      <c r="MD2"/>
-      <c r="ME2"/>
-      <c r="MF2"/>
-      <c r="MG2"/>
-      <c r="MH2"/>
-      <c r="MI2"/>
-      <c r="MJ2"/>
-      <c r="MK2"/>
-      <c r="ML2"/>
-      <c r="MM2"/>
-      <c r="MN2"/>
-      <c r="MO2"/>
-      <c r="MP2"/>
-      <c r="MQ2"/>
-      <c r="MR2"/>
-      <c r="MS2"/>
-      <c r="MT2"/>
-      <c r="MU2"/>
-      <c r="MV2"/>
-      <c r="MW2"/>
-      <c r="MX2"/>
-      <c r="MY2"/>
-      <c r="MZ2"/>
-      <c r="NA2"/>
-      <c r="NB2"/>
-      <c r="NC2"/>
-      <c r="ND2"/>
-      <c r="NE2"/>
-      <c r="NF2"/>
-      <c r="NG2"/>
-      <c r="NH2"/>
-      <c r="NI2"/>
-      <c r="NJ2"/>
-      <c r="NK2"/>
-      <c r="NL2"/>
-      <c r="NM2"/>
-      <c r="NN2"/>
-      <c r="NO2"/>
-      <c r="NP2"/>
-      <c r="NQ2"/>
-      <c r="NR2"/>
-      <c r="NS2"/>
-      <c r="NT2"/>
-      <c r="NU2"/>
-      <c r="NV2"/>
-      <c r="NW2"/>
-      <c r="NX2"/>
-      <c r="NY2"/>
-      <c r="NZ2"/>
-      <c r="OA2"/>
-      <c r="OB2"/>
-      <c r="OC2"/>
-      <c r="OD2"/>
-      <c r="OE2"/>
-      <c r="OF2"/>
-      <c r="OG2"/>
-      <c r="OH2"/>
-      <c r="OI2"/>
-      <c r="OJ2"/>
-      <c r="OK2"/>
-      <c r="OL2"/>
-      <c r="OM2"/>
-      <c r="ON2"/>
-      <c r="OO2"/>
-      <c r="OP2"/>
-      <c r="OQ2"/>
-      <c r="OR2"/>
-      <c r="OS2"/>
-      <c r="OT2"/>
-      <c r="OU2"/>
-      <c r="OV2"/>
-      <c r="OW2"/>
-      <c r="OX2"/>
-      <c r="OY2"/>
-      <c r="OZ2"/>
-      <c r="PA2"/>
-      <c r="PB2"/>
-      <c r="PC2"/>
-      <c r="PD2"/>
-      <c r="PE2"/>
-      <c r="PF2"/>
-      <c r="PG2"/>
-      <c r="PH2"/>
-      <c r="PI2"/>
-      <c r="PJ2"/>
-      <c r="PK2"/>
-      <c r="PL2"/>
-      <c r="PM2"/>
-      <c r="PN2"/>
-      <c r="PO2"/>
-      <c r="PP2"/>
-      <c r="PQ2"/>
-      <c r="PR2"/>
-      <c r="PS2"/>
-      <c r="PT2"/>
-      <c r="PU2"/>
-      <c r="PV2"/>
-      <c r="PW2"/>
-      <c r="PX2"/>
-      <c r="PY2"/>
-      <c r="PZ2"/>
-      <c r="QA2"/>
-      <c r="QB2"/>
-      <c r="QC2"/>
-      <c r="QD2"/>
-      <c r="QE2"/>
-      <c r="QF2"/>
-      <c r="QG2"/>
-      <c r="QH2"/>
-      <c r="QI2"/>
-      <c r="QJ2"/>
-      <c r="QK2"/>
-      <c r="QL2"/>
-      <c r="QM2"/>
-      <c r="QN2"/>
-      <c r="QO2"/>
-      <c r="QP2"/>
-      <c r="QQ2"/>
-      <c r="QR2"/>
-      <c r="QS2"/>
-      <c r="QT2"/>
-      <c r="QU2"/>
-      <c r="QV2"/>
-      <c r="QW2"/>
-      <c r="QX2"/>
-      <c r="QY2"/>
-      <c r="QZ2"/>
-      <c r="RA2"/>
-      <c r="RB2"/>
-      <c r="RC2"/>
-      <c r="RD2"/>
-      <c r="RE2"/>
-      <c r="RF2"/>
-      <c r="RG2"/>
-      <c r="RH2"/>
-      <c r="RI2"/>
-      <c r="RJ2"/>
-      <c r="RK2"/>
-      <c r="RL2"/>
-      <c r="RM2"/>
-      <c r="RN2"/>
-      <c r="RO2"/>
-      <c r="RP2"/>
-      <c r="RQ2"/>
-      <c r="RR2"/>
-      <c r="RS2"/>
-      <c r="RT2"/>
-      <c r="RU2"/>
-      <c r="RV2"/>
-      <c r="RW2"/>
-      <c r="RX2"/>
-      <c r="RY2"/>
-      <c r="RZ2"/>
-      <c r="SA2"/>
-      <c r="SB2"/>
-      <c r="SC2"/>
-      <c r="SD2"/>
-      <c r="SE2"/>
-      <c r="SF2"/>
-      <c r="SG2"/>
-      <c r="SH2"/>
-      <c r="SI2"/>
-      <c r="SJ2"/>
-      <c r="SK2"/>
-      <c r="SL2"/>
-      <c r="SM2"/>
-      <c r="SN2"/>
-      <c r="SO2"/>
-      <c r="SP2"/>
-      <c r="SQ2"/>
-      <c r="SR2"/>
-      <c r="SS2"/>
-      <c r="ST2"/>
-      <c r="SU2"/>
-      <c r="SV2"/>
-      <c r="SW2"/>
-      <c r="SX2"/>
-      <c r="SY2"/>
-      <c r="SZ2"/>
-      <c r="TA2"/>
-      <c r="TB2"/>
-      <c r="TC2"/>
-      <c r="TD2"/>
-      <c r="TE2"/>
-      <c r="TF2"/>
-      <c r="TG2"/>
-      <c r="TH2"/>
-      <c r="TI2"/>
-      <c r="TJ2"/>
-      <c r="TK2"/>
-      <c r="TL2"/>
-      <c r="TM2"/>
-      <c r="TN2"/>
-      <c r="TO2"/>
-      <c r="TP2"/>
-      <c r="TQ2"/>
-      <c r="TR2"/>
-      <c r="TS2"/>
-      <c r="TT2"/>
-      <c r="TU2"/>
-      <c r="TV2"/>
-      <c r="TW2"/>
-      <c r="TX2"/>
-      <c r="TY2"/>
-      <c r="TZ2"/>
-      <c r="UA2"/>
-      <c r="UB2"/>
-      <c r="UC2"/>
-      <c r="UD2"/>
-      <c r="UE2"/>
-      <c r="UF2"/>
-      <c r="UG2"/>
-      <c r="UH2"/>
-      <c r="UI2"/>
-      <c r="UJ2"/>
-      <c r="UK2"/>
-      <c r="UL2"/>
-      <c r="UM2"/>
-      <c r="UN2"/>
-      <c r="UO2"/>
-      <c r="UP2"/>
-      <c r="UQ2"/>
-      <c r="UR2"/>
-      <c r="US2"/>
-      <c r="UT2"/>
-      <c r="UU2"/>
-      <c r="UV2"/>
-      <c r="UW2"/>
-      <c r="UX2"/>
-      <c r="UY2"/>
-      <c r="UZ2"/>
-      <c r="VA2"/>
-      <c r="VB2"/>
-      <c r="VC2"/>
-      <c r="VD2"/>
-      <c r="VE2"/>
-      <c r="VF2"/>
-      <c r="VG2"/>
-      <c r="VH2"/>
-      <c r="VI2"/>
-      <c r="VJ2"/>
-      <c r="VK2"/>
-      <c r="VL2"/>
-      <c r="VM2"/>
-      <c r="VN2"/>
-      <c r="VO2"/>
-      <c r="VP2"/>
-      <c r="VQ2"/>
-      <c r="VR2"/>
-      <c r="VS2"/>
-      <c r="VT2"/>
-      <c r="VU2"/>
-      <c r="VV2"/>
-      <c r="VW2"/>
-      <c r="VX2"/>
-      <c r="VY2"/>
-      <c r="VZ2"/>
-      <c r="WA2"/>
-      <c r="WB2"/>
-      <c r="WC2"/>
-      <c r="WD2"/>
-      <c r="WE2"/>
-      <c r="WF2"/>
-      <c r="WG2"/>
-      <c r="WH2"/>
-      <c r="WI2"/>
-      <c r="WJ2"/>
-      <c r="WK2"/>
-      <c r="WL2"/>
-      <c r="WM2"/>
-      <c r="WN2"/>
-      <c r="WO2"/>
-      <c r="WP2"/>
-      <c r="WQ2"/>
-      <c r="WR2"/>
-      <c r="WS2"/>
-      <c r="WT2"/>
-      <c r="WU2"/>
-      <c r="WV2"/>
-      <c r="WW2"/>
-      <c r="WX2"/>
-      <c r="WY2"/>
-      <c r="WZ2"/>
-      <c r="XA2"/>
-      <c r="XB2"/>
-      <c r="XC2"/>
-      <c r="XD2"/>
-      <c r="XE2"/>
-      <c r="XF2"/>
-      <c r="XG2"/>
-      <c r="XH2"/>
-      <c r="XI2"/>
-      <c r="XJ2"/>
-      <c r="XK2"/>
-      <c r="XL2"/>
-      <c r="XM2"/>
-      <c r="XN2"/>
-      <c r="XO2"/>
-      <c r="XP2"/>
-      <c r="XQ2"/>
-      <c r="XR2"/>
-      <c r="XS2"/>
-      <c r="XT2"/>
-      <c r="XU2"/>
-      <c r="XV2"/>
-      <c r="XW2"/>
-      <c r="XX2"/>
-      <c r="XY2"/>
-      <c r="XZ2"/>
-      <c r="YA2"/>
-      <c r="YB2"/>
-      <c r="YC2"/>
-      <c r="YD2"/>
-      <c r="YE2"/>
-      <c r="YF2"/>
-      <c r="YG2"/>
-      <c r="YH2"/>
-      <c r="YI2"/>
-      <c r="YJ2"/>
-      <c r="YK2"/>
-      <c r="YL2"/>
-      <c r="YM2"/>
-      <c r="YN2"/>
-      <c r="YO2"/>
-      <c r="YP2"/>
-      <c r="YQ2"/>
-      <c r="YR2"/>
-      <c r="YS2"/>
-      <c r="YT2"/>
-      <c r="YU2"/>
-      <c r="YV2"/>
-      <c r="YW2"/>
-      <c r="YX2"/>
-      <c r="YY2"/>
-      <c r="YZ2"/>
-      <c r="ZA2"/>
-      <c r="ZB2"/>
-      <c r="ZC2"/>
-      <c r="ZD2"/>
-      <c r="ZE2"/>
-      <c r="ZF2"/>
-      <c r="ZG2"/>
-      <c r="ZH2"/>
-      <c r="ZI2"/>
-      <c r="ZJ2"/>
-      <c r="ZK2"/>
-      <c r="ZL2"/>
-      <c r="ZM2"/>
-      <c r="ZN2"/>
-      <c r="ZO2"/>
-      <c r="ZP2"/>
-      <c r="ZQ2"/>
-      <c r="ZR2"/>
-      <c r="ZS2"/>
-      <c r="ZT2"/>
-      <c r="ZU2"/>
-      <c r="ZV2"/>
-      <c r="ZW2"/>
-      <c r="ZX2"/>
-      <c r="ZY2"/>
-      <c r="ZZ2"/>
-      <c r="AAA2"/>
-      <c r="AAB2"/>
-      <c r="AAC2"/>
-      <c r="AAD2"/>
-      <c r="AAE2"/>
-      <c r="AAF2"/>
-      <c r="AAG2"/>
-      <c r="AAH2"/>
-      <c r="AAI2"/>
-      <c r="AAJ2"/>
-      <c r="AAK2"/>
-      <c r="AAL2"/>
-      <c r="AAM2"/>
-      <c r="AAN2"/>
-      <c r="AAO2"/>
-      <c r="AAP2"/>
-      <c r="AAQ2"/>
-      <c r="AAR2"/>
-      <c r="AAS2"/>
-      <c r="AAT2"/>
-      <c r="AAU2"/>
-      <c r="AAV2"/>
-      <c r="AAW2"/>
-      <c r="AAX2"/>
-      <c r="AAY2"/>
-      <c r="AAZ2"/>
-      <c r="ABA2"/>
-      <c r="ABB2"/>
-      <c r="ABC2"/>
-      <c r="ABD2"/>
-      <c r="ABE2"/>
-      <c r="ABF2"/>
-      <c r="ABG2"/>
-      <c r="ABH2"/>
-      <c r="ABI2"/>
-      <c r="ABJ2"/>
-      <c r="ABK2"/>
-      <c r="ABL2"/>
-      <c r="ABM2"/>
-      <c r="ABN2"/>
-      <c r="ABO2"/>
-      <c r="ABP2"/>
-      <c r="ABQ2"/>
-      <c r="ABR2"/>
-      <c r="ABS2"/>
-      <c r="ABT2"/>
-      <c r="ABU2"/>
-      <c r="ABV2"/>
-      <c r="ABW2"/>
-      <c r="ABX2"/>
-      <c r="ABY2"/>
-      <c r="ABZ2"/>
-      <c r="ACA2"/>
-      <c r="ACB2"/>
-      <c r="ACC2"/>
-      <c r="ACD2"/>
-      <c r="ACE2"/>
-      <c r="ACF2"/>
-      <c r="ACG2"/>
-      <c r="ACH2"/>
-      <c r="ACI2"/>
-      <c r="ACJ2"/>
-      <c r="ACK2"/>
-      <c r="ACL2"/>
-      <c r="ACM2"/>
-      <c r="ACN2"/>
-      <c r="ACO2"/>
-      <c r="ACP2"/>
-      <c r="ACQ2"/>
-      <c r="ACR2"/>
-      <c r="ACS2"/>
-      <c r="ACT2"/>
-      <c r="ACU2"/>
-      <c r="ACV2"/>
-      <c r="ACW2"/>
-      <c r="ACX2"/>
-      <c r="ACY2"/>
-      <c r="ACZ2"/>
-      <c r="ADA2"/>
-      <c r="ADB2"/>
-      <c r="ADC2"/>
-      <c r="ADD2"/>
-      <c r="ADE2"/>
-      <c r="ADF2"/>
-      <c r="ADG2"/>
-      <c r="ADH2"/>
-      <c r="ADI2"/>
-      <c r="ADJ2"/>
-      <c r="ADK2"/>
-      <c r="ADL2"/>
-      <c r="ADM2"/>
-      <c r="ADN2"/>
-      <c r="ADO2"/>
-      <c r="ADP2"/>
-      <c r="ADQ2"/>
-      <c r="ADR2"/>
-      <c r="ADS2"/>
-      <c r="ADT2"/>
-      <c r="ADU2"/>
-      <c r="ADV2"/>
-      <c r="ADW2"/>
-      <c r="ADX2"/>
-      <c r="ADY2"/>
-      <c r="ADZ2"/>
-      <c r="AEA2"/>
-      <c r="AEB2"/>
-      <c r="AEC2"/>
-      <c r="AED2"/>
-      <c r="AEE2"/>
-      <c r="AEF2"/>
-      <c r="AEG2"/>
-      <c r="AEH2"/>
-      <c r="AEI2"/>
-      <c r="AEJ2"/>
-      <c r="AEK2"/>
-      <c r="AEL2"/>
-      <c r="AEM2"/>
-      <c r="AEN2"/>
-      <c r="AEO2"/>
-      <c r="AEP2"/>
-      <c r="AEQ2"/>
-      <c r="AER2"/>
-      <c r="AES2"/>
-      <c r="AET2"/>
-      <c r="AEU2"/>
-      <c r="AEV2"/>
-      <c r="AEW2"/>
-      <c r="AEX2"/>
-      <c r="AEY2"/>
-      <c r="AEZ2"/>
-      <c r="AFA2"/>
-      <c r="AFB2"/>
-      <c r="AFC2"/>
-      <c r="AFD2"/>
-      <c r="AFE2"/>
-      <c r="AFF2"/>
-      <c r="AFG2"/>
-      <c r="AFH2"/>
-      <c r="AFI2"/>
-      <c r="AFJ2"/>
-      <c r="AFK2"/>
-      <c r="AFL2"/>
-      <c r="AFM2"/>
-      <c r="AFN2"/>
-      <c r="AFO2"/>
-      <c r="AFP2"/>
-      <c r="AFQ2"/>
-      <c r="AFR2"/>
-      <c r="AFS2"/>
-      <c r="AFT2"/>
-      <c r="AFU2"/>
-      <c r="AFV2"/>
-      <c r="AFW2"/>
-      <c r="AFX2"/>
-      <c r="AFY2"/>
-      <c r="AFZ2"/>
-      <c r="AGA2"/>
-      <c r="AGB2"/>
-      <c r="AGC2"/>
-      <c r="AGD2"/>
-      <c r="AGE2"/>
-      <c r="AGF2"/>
-      <c r="AGG2"/>
-      <c r="AGH2"/>
-      <c r="AGI2"/>
-      <c r="AGJ2"/>
-      <c r="AGK2"/>
-      <c r="AGL2"/>
-      <c r="AGM2"/>
-      <c r="AGN2"/>
-      <c r="AGO2"/>
-      <c r="AGP2"/>
-      <c r="AGQ2"/>
-      <c r="AGR2"/>
-      <c r="AGS2"/>
-      <c r="AGT2"/>
-      <c r="AGU2"/>
-      <c r="AGV2"/>
-      <c r="AGW2"/>
-      <c r="AGX2"/>
-      <c r="AGY2"/>
-      <c r="AGZ2"/>
-      <c r="AHA2"/>
-      <c r="AHB2"/>
-      <c r="AHC2"/>
-      <c r="AHD2"/>
-      <c r="AHE2"/>
-      <c r="AHF2"/>
-      <c r="AHG2"/>
-      <c r="AHH2"/>
-      <c r="AHI2"/>
-      <c r="AHJ2"/>
-      <c r="AHK2"/>
-      <c r="AHL2"/>
-      <c r="AHM2"/>
-      <c r="AHN2"/>
-      <c r="AHO2"/>
-      <c r="AHP2"/>
-      <c r="AHQ2"/>
-      <c r="AHR2"/>
-      <c r="AHS2"/>
-      <c r="AHT2"/>
-      <c r="AHU2"/>
-      <c r="AHV2"/>
-      <c r="AHW2"/>
-      <c r="AHX2"/>
-      <c r="AHY2"/>
-      <c r="AHZ2"/>
-      <c r="AIA2"/>
-      <c r="AIB2"/>
-      <c r="AIC2"/>
-      <c r="AID2"/>
-      <c r="AIE2"/>
-      <c r="AIF2"/>
-      <c r="AIG2"/>
-      <c r="AIH2"/>
-      <c r="AII2"/>
-      <c r="AIJ2"/>
-      <c r="AIK2"/>
-      <c r="AIL2"/>
-      <c r="AIM2"/>
-      <c r="AIN2"/>
-      <c r="AIO2"/>
-      <c r="AIP2"/>
-      <c r="AIQ2"/>
-      <c r="AIR2"/>
-      <c r="AIS2"/>
-      <c r="AIT2"/>
-      <c r="AIU2"/>
-      <c r="AIV2"/>
-      <c r="AIW2"/>
-      <c r="AIX2"/>
-      <c r="AIY2"/>
-      <c r="AIZ2"/>
-      <c r="AJA2"/>
-      <c r="AJB2"/>
-      <c r="AJC2"/>
-      <c r="AJD2"/>
-      <c r="AJE2"/>
-      <c r="AJF2"/>
-      <c r="AJG2"/>
-      <c r="AJH2"/>
-      <c r="AJI2"/>
-      <c r="AJJ2"/>
-      <c r="AJK2"/>
-      <c r="AJL2"/>
-      <c r="AJM2"/>
-      <c r="AJN2"/>
-      <c r="AJO2"/>
-      <c r="AJP2"/>
-      <c r="AJQ2"/>
-      <c r="AJR2"/>
-      <c r="AJS2"/>
-      <c r="AJT2"/>
-      <c r="AJU2"/>
-      <c r="AJV2"/>
-      <c r="AJW2"/>
-      <c r="AJX2"/>
-      <c r="AJY2"/>
-      <c r="AJZ2"/>
-      <c r="AKA2"/>
-      <c r="AKB2"/>
-      <c r="AKC2"/>
-      <c r="AKD2"/>
-      <c r="AKE2"/>
-      <c r="AKF2"/>
-      <c r="AKG2"/>
-      <c r="AKH2"/>
-      <c r="AKI2"/>
-      <c r="AKJ2"/>
-      <c r="AKK2"/>
-      <c r="AKL2"/>
-      <c r="AKM2"/>
-      <c r="AKN2"/>
-      <c r="AKO2"/>
-      <c r="AKP2"/>
-      <c r="AKQ2"/>
-      <c r="AKR2"/>
-      <c r="AKS2"/>
-      <c r="AKT2"/>
-      <c r="AKU2"/>
-      <c r="AKV2"/>
-      <c r="AKW2"/>
-      <c r="AKX2"/>
-      <c r="AKY2"/>
-      <c r="AKZ2"/>
-      <c r="ALA2"/>
-      <c r="ALB2"/>
-      <c r="ALC2"/>
-      <c r="ALD2"/>
-      <c r="ALE2"/>
-      <c r="ALF2"/>
-      <c r="ALG2"/>
-      <c r="ALH2"/>
-      <c r="ALI2"/>
-      <c r="ALJ2"/>
-      <c r="ALK2"/>
-      <c r="ALL2"/>
-      <c r="ALM2"/>
-      <c r="ALN2"/>
-      <c r="ALO2"/>
-      <c r="ALP2"/>
-      <c r="ALQ2"/>
-      <c r="ALR2"/>
-      <c r="ALS2"/>
-      <c r="ALT2"/>
-      <c r="ALU2"/>
-      <c r="ALV2"/>
-      <c r="ALW2"/>
-      <c r="ALX2"/>
-      <c r="ALY2"/>
-      <c r="ALZ2"/>
-      <c r="AMA2"/>
-      <c r="AMB2"/>
-      <c r="AMC2"/>
-      <c r="AMD2"/>
-      <c r="AME2"/>
-      <c r="AMF2"/>
-      <c r="AMG2"/>
-      <c r="AMH2"/>
-      <c r="AMI2"/>
-      <c r="AMJ2"/>
-      <c r="AMK2"/>
-      <c r="AML2"/>
-      <c r="AMM2"/>
-      <c r="AMN2"/>
-      <c r="AMO2"/>
     </row>
-    <row r="3" spans="1:1029" s="4" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>94</v>
+        <v>257</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>87</v>
+        <v>259</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>88</v>
+        <v>260</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>4</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>85</v>
+        <v>253</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="G3"/>
-      <c r="H3"/>
-      <c r="I3"/>
-      <c r="J3"/>
-      <c r="K3"/>
-      <c r="L3"/>
-      <c r="M3"/>
-      <c r="N3"/>
-      <c r="O3"/>
-      <c r="P3"/>
-      <c r="Q3"/>
-      <c r="R3"/>
-      <c r="S3"/>
-      <c r="T3"/>
-      <c r="U3"/>
-      <c r="V3"/>
-      <c r="W3"/>
-      <c r="X3"/>
-      <c r="Y3"/>
-      <c r="Z3"/>
-      <c r="AA3"/>
-      <c r="AB3"/>
-      <c r="AC3"/>
-      <c r="AD3"/>
-      <c r="AE3"/>
-      <c r="AF3"/>
-      <c r="AG3"/>
-      <c r="AH3"/>
-      <c r="AI3"/>
-      <c r="AJ3"/>
-      <c r="AK3"/>
-      <c r="AL3"/>
-      <c r="AM3"/>
-      <c r="AN3"/>
-      <c r="AO3"/>
-      <c r="AP3"/>
-      <c r="AQ3"/>
-      <c r="AR3"/>
-      <c r="AS3"/>
-      <c r="AT3"/>
-      <c r="AU3"/>
-      <c r="AV3"/>
-      <c r="AW3"/>
-      <c r="AX3"/>
-      <c r="AY3"/>
-      <c r="AZ3"/>
-      <c r="BA3"/>
-      <c r="BB3"/>
-      <c r="BC3"/>
-      <c r="BD3"/>
-      <c r="BE3"/>
-      <c r="BF3"/>
-      <c r="BG3"/>
-      <c r="BH3"/>
-      <c r="BI3"/>
-      <c r="BJ3"/>
-      <c r="BK3"/>
-      <c r="BL3"/>
-      <c r="BM3"/>
-      <c r="BN3"/>
-      <c r="BO3"/>
-      <c r="BP3"/>
-      <c r="BQ3"/>
-      <c r="BR3"/>
-      <c r="BS3"/>
-      <c r="BT3"/>
-      <c r="BU3"/>
-      <c r="BV3"/>
-      <c r="BW3"/>
-      <c r="BX3"/>
-      <c r="BY3"/>
-      <c r="BZ3"/>
-      <c r="CA3"/>
-      <c r="CB3"/>
-      <c r="CC3"/>
-      <c r="CD3"/>
-      <c r="CE3"/>
-      <c r="CF3"/>
-      <c r="CG3"/>
-      <c r="CH3"/>
-      <c r="CI3"/>
-      <c r="CJ3"/>
-      <c r="CK3"/>
-      <c r="CL3"/>
-      <c r="CM3"/>
-      <c r="CN3"/>
-      <c r="CO3"/>
-      <c r="CP3"/>
-      <c r="CQ3"/>
-      <c r="CR3"/>
-      <c r="CS3"/>
-      <c r="CT3"/>
-      <c r="CU3"/>
-      <c r="CV3"/>
-      <c r="CW3"/>
-      <c r="CX3"/>
-      <c r="CY3"/>
-      <c r="CZ3"/>
-      <c r="DA3"/>
-      <c r="DB3"/>
-      <c r="DC3"/>
-      <c r="DD3"/>
-      <c r="DE3"/>
-      <c r="DF3"/>
-      <c r="DG3"/>
-      <c r="DH3"/>
-      <c r="DI3"/>
-      <c r="DJ3"/>
-      <c r="DK3"/>
-      <c r="DL3"/>
-      <c r="DM3"/>
-      <c r="DN3"/>
-      <c r="DO3"/>
-      <c r="DP3"/>
-      <c r="DQ3"/>
-      <c r="DR3"/>
-      <c r="DS3"/>
-      <c r="DT3"/>
-      <c r="DU3"/>
-      <c r="DV3"/>
-      <c r="DW3"/>
-      <c r="DX3"/>
-      <c r="DY3"/>
-      <c r="DZ3"/>
-      <c r="EA3"/>
-      <c r="EB3"/>
-      <c r="EC3"/>
-      <c r="ED3"/>
-      <c r="EE3"/>
-      <c r="EF3"/>
-      <c r="EG3"/>
-      <c r="EH3"/>
-      <c r="EI3"/>
-      <c r="EJ3"/>
-      <c r="EK3"/>
-      <c r="EL3"/>
-      <c r="EM3"/>
-      <c r="EN3"/>
-      <c r="EO3"/>
-      <c r="EP3"/>
-      <c r="EQ3"/>
-      <c r="ER3"/>
-      <c r="ES3"/>
-      <c r="ET3"/>
-      <c r="EU3"/>
-      <c r="EV3"/>
-      <c r="EW3"/>
-      <c r="EX3"/>
-      <c r="EY3"/>
-      <c r="EZ3"/>
-      <c r="FA3"/>
-      <c r="FB3"/>
-      <c r="FC3"/>
-      <c r="FD3"/>
-      <c r="FE3"/>
-      <c r="FF3"/>
-      <c r="FG3"/>
-      <c r="FH3"/>
-      <c r="FI3"/>
-      <c r="FJ3"/>
-      <c r="FK3"/>
-      <c r="FL3"/>
-      <c r="FM3"/>
-      <c r="FN3"/>
-      <c r="FO3"/>
-      <c r="FP3"/>
-      <c r="FQ3"/>
-      <c r="FR3"/>
-      <c r="FS3"/>
-      <c r="FT3"/>
-      <c r="FU3"/>
-      <c r="FV3"/>
-      <c r="FW3"/>
-      <c r="FX3"/>
-      <c r="FY3"/>
-      <c r="FZ3"/>
-      <c r="GA3"/>
-      <c r="GB3"/>
-      <c r="GC3"/>
-      <c r="GD3"/>
-      <c r="GE3"/>
-      <c r="GF3"/>
-      <c r="GG3"/>
-      <c r="GH3"/>
-      <c r="GI3"/>
-      <c r="GJ3"/>
-      <c r="GK3"/>
-      <c r="GL3"/>
-      <c r="GM3"/>
-      <c r="GN3"/>
-      <c r="GO3"/>
-      <c r="GP3"/>
-      <c r="GQ3"/>
-      <c r="GR3"/>
-      <c r="GS3"/>
-      <c r="GT3"/>
-      <c r="GU3"/>
-      <c r="GV3"/>
-      <c r="GW3"/>
-      <c r="GX3"/>
-      <c r="GY3"/>
-      <c r="GZ3"/>
-      <c r="HA3"/>
-      <c r="HB3"/>
-      <c r="HC3"/>
-      <c r="HD3"/>
-      <c r="HE3"/>
-      <c r="HF3"/>
-      <c r="HG3"/>
-      <c r="HH3"/>
-      <c r="HI3"/>
-      <c r="HJ3"/>
-      <c r="HK3"/>
-      <c r="HL3"/>
-      <c r="HM3"/>
-      <c r="HN3"/>
-      <c r="HO3"/>
-      <c r="HP3"/>
-      <c r="HQ3"/>
-      <c r="HR3"/>
-      <c r="HS3"/>
-      <c r="HT3"/>
-      <c r="HU3"/>
-      <c r="HV3"/>
-      <c r="HW3"/>
-      <c r="HX3"/>
-      <c r="HY3"/>
-      <c r="HZ3"/>
-      <c r="IA3"/>
-      <c r="IB3"/>
-      <c r="IC3"/>
-      <c r="ID3"/>
-      <c r="IE3"/>
-      <c r="IF3"/>
-      <c r="IG3"/>
-      <c r="IH3"/>
-      <c r="II3"/>
-      <c r="IJ3"/>
-      <c r="IK3"/>
-      <c r="IL3"/>
-      <c r="IM3"/>
-      <c r="IN3"/>
-      <c r="IO3"/>
-      <c r="IP3"/>
-      <c r="IQ3"/>
-      <c r="IR3"/>
-      <c r="IS3"/>
-      <c r="IT3"/>
-      <c r="IU3"/>
-      <c r="IV3"/>
-      <c r="IW3"/>
-      <c r="IX3"/>
-      <c r="IY3"/>
-      <c r="IZ3"/>
-      <c r="JA3"/>
-      <c r="JB3"/>
-      <c r="JC3"/>
-      <c r="JD3"/>
-      <c r="JE3"/>
-      <c r="JF3"/>
-      <c r="JG3"/>
-      <c r="JH3"/>
-      <c r="JI3"/>
-      <c r="JJ3"/>
-      <c r="JK3"/>
-      <c r="JL3"/>
-      <c r="JM3"/>
-      <c r="JN3"/>
-      <c r="JO3"/>
-      <c r="JP3"/>
-      <c r="JQ3"/>
-      <c r="JR3"/>
-      <c r="JS3"/>
-      <c r="JT3"/>
-      <c r="JU3"/>
-      <c r="JV3"/>
-      <c r="JW3"/>
-      <c r="JX3"/>
-      <c r="JY3"/>
-      <c r="JZ3"/>
-      <c r="KA3"/>
-      <c r="KB3"/>
-      <c r="KC3"/>
-      <c r="KD3"/>
-      <c r="KE3"/>
-      <c r="KF3"/>
-      <c r="KG3"/>
-      <c r="KH3"/>
-      <c r="KI3"/>
-      <c r="KJ3"/>
-      <c r="KK3"/>
-      <c r="KL3"/>
-      <c r="KM3"/>
-      <c r="KN3"/>
-      <c r="KO3"/>
-      <c r="KP3"/>
-      <c r="KQ3"/>
-      <c r="KR3"/>
-      <c r="KS3"/>
-      <c r="KT3"/>
-      <c r="KU3"/>
-      <c r="KV3"/>
-      <c r="KW3"/>
-      <c r="KX3"/>
-      <c r="KY3"/>
-      <c r="KZ3"/>
-      <c r="LA3"/>
-      <c r="LB3"/>
-      <c r="LC3"/>
-      <c r="LD3"/>
-      <c r="LE3"/>
-      <c r="LF3"/>
-      <c r="LG3"/>
-      <c r="LH3"/>
-      <c r="LI3"/>
-      <c r="LJ3"/>
-      <c r="LK3"/>
-      <c r="LL3"/>
-      <c r="LM3"/>
-      <c r="LN3"/>
-      <c r="LO3"/>
-      <c r="LP3"/>
-      <c r="LQ3"/>
-      <c r="LR3"/>
-      <c r="LS3"/>
-      <c r="LT3"/>
-      <c r="LU3"/>
-      <c r="LV3"/>
-      <c r="LW3"/>
-      <c r="LX3"/>
-      <c r="LY3"/>
-      <c r="LZ3"/>
-      <c r="MA3"/>
-      <c r="MB3"/>
-      <c r="MC3"/>
-      <c r="MD3"/>
-      <c r="ME3"/>
-      <c r="MF3"/>
-      <c r="MG3"/>
-      <c r="MH3"/>
-      <c r="MI3"/>
-      <c r="MJ3"/>
-      <c r="MK3"/>
-      <c r="ML3"/>
-      <c r="MM3"/>
-      <c r="MN3"/>
-      <c r="MO3"/>
-      <c r="MP3"/>
-      <c r="MQ3"/>
-      <c r="MR3"/>
-      <c r="MS3"/>
-      <c r="MT3"/>
-      <c r="MU3"/>
-      <c r="MV3"/>
-      <c r="MW3"/>
-      <c r="MX3"/>
-      <c r="MY3"/>
-      <c r="MZ3"/>
-      <c r="NA3"/>
-      <c r="NB3"/>
-      <c r="NC3"/>
-      <c r="ND3"/>
-      <c r="NE3"/>
-      <c r="NF3"/>
-      <c r="NG3"/>
-      <c r="NH3"/>
-      <c r="NI3"/>
-      <c r="NJ3"/>
-      <c r="NK3"/>
-      <c r="NL3"/>
-      <c r="NM3"/>
-      <c r="NN3"/>
-      <c r="NO3"/>
-      <c r="NP3"/>
-      <c r="NQ3"/>
-      <c r="NR3"/>
-      <c r="NS3"/>
-      <c r="NT3"/>
-      <c r="NU3"/>
-      <c r="NV3"/>
-      <c r="NW3"/>
-      <c r="NX3"/>
-      <c r="NY3"/>
-      <c r="NZ3"/>
-      <c r="OA3"/>
-      <c r="OB3"/>
-      <c r="OC3"/>
-      <c r="OD3"/>
-      <c r="OE3"/>
-      <c r="OF3"/>
-      <c r="OG3"/>
-      <c r="OH3"/>
-      <c r="OI3"/>
-      <c r="OJ3"/>
-      <c r="OK3"/>
-      <c r="OL3"/>
-      <c r="OM3"/>
-      <c r="ON3"/>
-      <c r="OO3"/>
-      <c r="OP3"/>
-      <c r="OQ3"/>
-      <c r="OR3"/>
-      <c r="OS3"/>
-      <c r="OT3"/>
-      <c r="OU3"/>
-      <c r="OV3"/>
-      <c r="OW3"/>
-      <c r="OX3"/>
-      <c r="OY3"/>
-      <c r="OZ3"/>
-      <c r="PA3"/>
-      <c r="PB3"/>
-      <c r="PC3"/>
-      <c r="PD3"/>
-      <c r="PE3"/>
-      <c r="PF3"/>
-      <c r="PG3"/>
-      <c r="PH3"/>
-      <c r="PI3"/>
-      <c r="PJ3"/>
-      <c r="PK3"/>
-      <c r="PL3"/>
-      <c r="PM3"/>
-      <c r="PN3"/>
-      <c r="PO3"/>
-      <c r="PP3"/>
-      <c r="PQ3"/>
-      <c r="PR3"/>
-      <c r="PS3"/>
-      <c r="PT3"/>
-      <c r="PU3"/>
-      <c r="PV3"/>
-      <c r="PW3"/>
-      <c r="PX3"/>
-      <c r="PY3"/>
-      <c r="PZ3"/>
-      <c r="QA3"/>
-      <c r="QB3"/>
-      <c r="QC3"/>
-      <c r="QD3"/>
-      <c r="QE3"/>
-      <c r="QF3"/>
-      <c r="QG3"/>
-      <c r="QH3"/>
-      <c r="QI3"/>
-      <c r="QJ3"/>
-      <c r="QK3"/>
-      <c r="QL3"/>
-      <c r="QM3"/>
-      <c r="QN3"/>
-      <c r="QO3"/>
-      <c r="QP3"/>
-      <c r="QQ3"/>
-      <c r="QR3"/>
-      <c r="QS3"/>
-      <c r="QT3"/>
-      <c r="QU3"/>
-      <c r="QV3"/>
-      <c r="QW3"/>
-      <c r="QX3"/>
-      <c r="QY3"/>
-      <c r="QZ3"/>
-      <c r="RA3"/>
-      <c r="RB3"/>
-      <c r="RC3"/>
-      <c r="RD3"/>
-      <c r="RE3"/>
-      <c r="RF3"/>
-      <c r="RG3"/>
-      <c r="RH3"/>
-      <c r="RI3"/>
-      <c r="RJ3"/>
-      <c r="RK3"/>
-      <c r="RL3"/>
-      <c r="RM3"/>
-      <c r="RN3"/>
-      <c r="RO3"/>
-      <c r="RP3"/>
-      <c r="RQ3"/>
-      <c r="RR3"/>
-      <c r="RS3"/>
-      <c r="RT3"/>
-      <c r="RU3"/>
-      <c r="RV3"/>
-      <c r="RW3"/>
-      <c r="RX3"/>
-      <c r="RY3"/>
-      <c r="RZ3"/>
-      <c r="SA3"/>
-      <c r="SB3"/>
-      <c r="SC3"/>
-      <c r="SD3"/>
-      <c r="SE3"/>
-      <c r="SF3"/>
-      <c r="SG3"/>
-      <c r="SH3"/>
-      <c r="SI3"/>
-      <c r="SJ3"/>
-      <c r="SK3"/>
-      <c r="SL3"/>
-      <c r="SM3"/>
-      <c r="SN3"/>
-      <c r="SO3"/>
-      <c r="SP3"/>
-      <c r="SQ3"/>
-      <c r="SR3"/>
-      <c r="SS3"/>
-      <c r="ST3"/>
-      <c r="SU3"/>
-      <c r="SV3"/>
-      <c r="SW3"/>
-      <c r="SX3"/>
-      <c r="SY3"/>
-      <c r="SZ3"/>
-      <c r="TA3"/>
-      <c r="TB3"/>
-      <c r="TC3"/>
-      <c r="TD3"/>
-      <c r="TE3"/>
-      <c r="TF3"/>
-      <c r="TG3"/>
-      <c r="TH3"/>
-      <c r="TI3"/>
-      <c r="TJ3"/>
-      <c r="TK3"/>
-      <c r="TL3"/>
-      <c r="TM3"/>
-      <c r="TN3"/>
-      <c r="TO3"/>
-      <c r="TP3"/>
-      <c r="TQ3"/>
-      <c r="TR3"/>
-      <c r="TS3"/>
-      <c r="TT3"/>
-      <c r="TU3"/>
-      <c r="TV3"/>
-      <c r="TW3"/>
-      <c r="TX3"/>
-      <c r="TY3"/>
-      <c r="TZ3"/>
-      <c r="UA3"/>
-      <c r="UB3"/>
-      <c r="UC3"/>
-      <c r="UD3"/>
-      <c r="UE3"/>
-      <c r="UF3"/>
-      <c r="UG3"/>
-      <c r="UH3"/>
-      <c r="UI3"/>
-      <c r="UJ3"/>
-      <c r="UK3"/>
-      <c r="UL3"/>
-      <c r="UM3"/>
-      <c r="UN3"/>
-      <c r="UO3"/>
-      <c r="UP3"/>
-      <c r="UQ3"/>
-      <c r="UR3"/>
-      <c r="US3"/>
-      <c r="UT3"/>
-      <c r="UU3"/>
-      <c r="UV3"/>
-      <c r="UW3"/>
-      <c r="UX3"/>
-      <c r="UY3"/>
-      <c r="UZ3"/>
-      <c r="VA3"/>
-      <c r="VB3"/>
-      <c r="VC3"/>
-      <c r="VD3"/>
-      <c r="VE3"/>
-      <c r="VF3"/>
-      <c r="VG3"/>
-      <c r="VH3"/>
-      <c r="VI3"/>
-      <c r="VJ3"/>
-      <c r="VK3"/>
-      <c r="VL3"/>
-      <c r="VM3"/>
-      <c r="VN3"/>
-      <c r="VO3"/>
-      <c r="VP3"/>
-      <c r="VQ3"/>
-      <c r="VR3"/>
-      <c r="VS3"/>
-      <c r="VT3"/>
-      <c r="VU3"/>
-      <c r="VV3"/>
-      <c r="VW3"/>
-      <c r="VX3"/>
-      <c r="VY3"/>
-      <c r="VZ3"/>
-      <c r="WA3"/>
-      <c r="WB3"/>
-      <c r="WC3"/>
-      <c r="WD3"/>
-      <c r="WE3"/>
-      <c r="WF3"/>
-      <c r="WG3"/>
-      <c r="WH3"/>
-      <c r="WI3"/>
-      <c r="WJ3"/>
-      <c r="WK3"/>
-      <c r="WL3"/>
-      <c r="WM3"/>
-      <c r="WN3"/>
-      <c r="WO3"/>
-      <c r="WP3"/>
-      <c r="WQ3"/>
-      <c r="WR3"/>
-      <c r="WS3"/>
-      <c r="WT3"/>
-      <c r="WU3"/>
-      <c r="WV3"/>
-      <c r="WW3"/>
-      <c r="WX3"/>
-      <c r="WY3"/>
-      <c r="WZ3"/>
-      <c r="XA3"/>
-      <c r="XB3"/>
-      <c r="XC3"/>
-      <c r="XD3"/>
-      <c r="XE3"/>
-      <c r="XF3"/>
-      <c r="XG3"/>
-      <c r="XH3"/>
-      <c r="XI3"/>
-      <c r="XJ3"/>
-      <c r="XK3"/>
-      <c r="XL3"/>
-      <c r="XM3"/>
-      <c r="XN3"/>
-      <c r="XO3"/>
-      <c r="XP3"/>
-      <c r="XQ3"/>
-      <c r="XR3"/>
-      <c r="XS3"/>
-      <c r="XT3"/>
-      <c r="XU3"/>
-      <c r="XV3"/>
-      <c r="XW3"/>
-      <c r="XX3"/>
-      <c r="XY3"/>
-      <c r="XZ3"/>
-      <c r="YA3"/>
-      <c r="YB3"/>
-      <c r="YC3"/>
-      <c r="YD3"/>
-      <c r="YE3"/>
-      <c r="YF3"/>
-      <c r="YG3"/>
-      <c r="YH3"/>
-      <c r="YI3"/>
-      <c r="YJ3"/>
-      <c r="YK3"/>
-      <c r="YL3"/>
-      <c r="YM3"/>
-      <c r="YN3"/>
-      <c r="YO3"/>
-      <c r="YP3"/>
-      <c r="YQ3"/>
-      <c r="YR3"/>
-      <c r="YS3"/>
-      <c r="YT3"/>
-      <c r="YU3"/>
-      <c r="YV3"/>
-      <c r="YW3"/>
-      <c r="YX3"/>
-      <c r="YY3"/>
-      <c r="YZ3"/>
-      <c r="ZA3"/>
-      <c r="ZB3"/>
-      <c r="ZC3"/>
-      <c r="ZD3"/>
-      <c r="ZE3"/>
-      <c r="ZF3"/>
-      <c r="ZG3"/>
-      <c r="ZH3"/>
-      <c r="ZI3"/>
-      <c r="ZJ3"/>
-      <c r="ZK3"/>
-      <c r="ZL3"/>
-      <c r="ZM3"/>
-      <c r="ZN3"/>
-      <c r="ZO3"/>
-      <c r="ZP3"/>
-      <c r="ZQ3"/>
-      <c r="ZR3"/>
-      <c r="ZS3"/>
-      <c r="ZT3"/>
-      <c r="ZU3"/>
-      <c r="ZV3"/>
-      <c r="ZW3"/>
-      <c r="ZX3"/>
-      <c r="ZY3"/>
-      <c r="ZZ3"/>
-      <c r="AAA3"/>
-      <c r="AAB3"/>
-      <c r="AAC3"/>
-      <c r="AAD3"/>
-      <c r="AAE3"/>
-      <c r="AAF3"/>
-      <c r="AAG3"/>
-      <c r="AAH3"/>
-      <c r="AAI3"/>
-      <c r="AAJ3"/>
-      <c r="AAK3"/>
-      <c r="AAL3"/>
-      <c r="AAM3"/>
-      <c r="AAN3"/>
-      <c r="AAO3"/>
-      <c r="AAP3"/>
-      <c r="AAQ3"/>
-      <c r="AAR3"/>
-      <c r="AAS3"/>
-      <c r="AAT3"/>
-      <c r="AAU3"/>
-      <c r="AAV3"/>
-      <c r="AAW3"/>
-      <c r="AAX3"/>
-      <c r="AAY3"/>
-      <c r="AAZ3"/>
-      <c r="ABA3"/>
-      <c r="ABB3"/>
-      <c r="ABC3"/>
-      <c r="ABD3"/>
-      <c r="ABE3"/>
-      <c r="ABF3"/>
-      <c r="ABG3"/>
-      <c r="ABH3"/>
-      <c r="ABI3"/>
-      <c r="ABJ3"/>
-      <c r="ABK3"/>
-      <c r="ABL3"/>
-      <c r="ABM3"/>
-      <c r="ABN3"/>
-      <c r="ABO3"/>
-      <c r="ABP3"/>
-      <c r="ABQ3"/>
-      <c r="ABR3"/>
-      <c r="ABS3"/>
-      <c r="ABT3"/>
-      <c r="ABU3"/>
-      <c r="ABV3"/>
-      <c r="ABW3"/>
-      <c r="ABX3"/>
-      <c r="ABY3"/>
-      <c r="ABZ3"/>
-      <c r="ACA3"/>
-      <c r="ACB3"/>
-      <c r="ACC3"/>
-      <c r="ACD3"/>
-      <c r="ACE3"/>
-      <c r="ACF3"/>
-      <c r="ACG3"/>
-      <c r="ACH3"/>
-      <c r="ACI3"/>
-      <c r="ACJ3"/>
-      <c r="ACK3"/>
-      <c r="ACL3"/>
-      <c r="ACM3"/>
-      <c r="ACN3"/>
-      <c r="ACO3"/>
-      <c r="ACP3"/>
-      <c r="ACQ3"/>
-      <c r="ACR3"/>
-      <c r="ACS3"/>
-      <c r="ACT3"/>
-      <c r="ACU3"/>
-      <c r="ACV3"/>
-      <c r="ACW3"/>
-      <c r="ACX3"/>
-      <c r="ACY3"/>
-      <c r="ACZ3"/>
-      <c r="ADA3"/>
-      <c r="ADB3"/>
-      <c r="ADC3"/>
-      <c r="ADD3"/>
-      <c r="ADE3"/>
-      <c r="ADF3"/>
-      <c r="ADG3"/>
-      <c r="ADH3"/>
-      <c r="ADI3"/>
-      <c r="ADJ3"/>
-      <c r="ADK3"/>
-      <c r="ADL3"/>
-      <c r="ADM3"/>
-      <c r="ADN3"/>
-      <c r="ADO3"/>
-      <c r="ADP3"/>
-      <c r="ADQ3"/>
-      <c r="ADR3"/>
-      <c r="ADS3"/>
-      <c r="ADT3"/>
-      <c r="ADU3"/>
-      <c r="ADV3"/>
-      <c r="ADW3"/>
-      <c r="ADX3"/>
-      <c r="ADY3"/>
-      <c r="ADZ3"/>
-      <c r="AEA3"/>
-      <c r="AEB3"/>
-      <c r="AEC3"/>
-      <c r="AED3"/>
-      <c r="AEE3"/>
-      <c r="AEF3"/>
-      <c r="AEG3"/>
-      <c r="AEH3"/>
-      <c r="AEI3"/>
-      <c r="AEJ3"/>
-      <c r="AEK3"/>
-      <c r="AEL3"/>
-      <c r="AEM3"/>
-      <c r="AEN3"/>
-      <c r="AEO3"/>
-      <c r="AEP3"/>
-      <c r="AEQ3"/>
-      <c r="AER3"/>
-      <c r="AES3"/>
-      <c r="AET3"/>
-      <c r="AEU3"/>
-      <c r="AEV3"/>
-      <c r="AEW3"/>
-      <c r="AEX3"/>
-      <c r="AEY3"/>
-      <c r="AEZ3"/>
-      <c r="AFA3"/>
-      <c r="AFB3"/>
-      <c r="AFC3"/>
-      <c r="AFD3"/>
-      <c r="AFE3"/>
-      <c r="AFF3"/>
-      <c r="AFG3"/>
-      <c r="AFH3"/>
-      <c r="AFI3"/>
-      <c r="AFJ3"/>
-      <c r="AFK3"/>
-      <c r="AFL3"/>
-      <c r="AFM3"/>
-      <c r="AFN3"/>
-      <c r="AFO3"/>
-      <c r="AFP3"/>
-      <c r="AFQ3"/>
-      <c r="AFR3"/>
-      <c r="AFS3"/>
-      <c r="AFT3"/>
-      <c r="AFU3"/>
-      <c r="AFV3"/>
-      <c r="AFW3"/>
-      <c r="AFX3"/>
-      <c r="AFY3"/>
-      <c r="AFZ3"/>
-      <c r="AGA3"/>
-      <c r="AGB3"/>
-      <c r="AGC3"/>
-      <c r="AGD3"/>
-      <c r="AGE3"/>
-      <c r="AGF3"/>
-      <c r="AGG3"/>
-      <c r="AGH3"/>
-      <c r="AGI3"/>
-      <c r="AGJ3"/>
-      <c r="AGK3"/>
-      <c r="AGL3"/>
-      <c r="AGM3"/>
-      <c r="AGN3"/>
-      <c r="AGO3"/>
-      <c r="AGP3"/>
-      <c r="AGQ3"/>
-      <c r="AGR3"/>
-      <c r="AGS3"/>
-      <c r="AGT3"/>
-      <c r="AGU3"/>
-      <c r="AGV3"/>
-      <c r="AGW3"/>
-      <c r="AGX3"/>
-      <c r="AGY3"/>
-      <c r="AGZ3"/>
-      <c r="AHA3"/>
-      <c r="AHB3"/>
-      <c r="AHC3"/>
-      <c r="AHD3"/>
-      <c r="AHE3"/>
-      <c r="AHF3"/>
-      <c r="AHG3"/>
-      <c r="AHH3"/>
-      <c r="AHI3"/>
-      <c r="AHJ3"/>
-      <c r="AHK3"/>
-      <c r="AHL3"/>
-      <c r="AHM3"/>
-      <c r="AHN3"/>
-      <c r="AHO3"/>
-      <c r="AHP3"/>
-      <c r="AHQ3"/>
-      <c r="AHR3"/>
-      <c r="AHS3"/>
-      <c r="AHT3"/>
-      <c r="AHU3"/>
-      <c r="AHV3"/>
-      <c r="AHW3"/>
-      <c r="AHX3"/>
-      <c r="AHY3"/>
-      <c r="AHZ3"/>
-      <c r="AIA3"/>
-      <c r="AIB3"/>
-      <c r="AIC3"/>
-      <c r="AID3"/>
-      <c r="AIE3"/>
-      <c r="AIF3"/>
-      <c r="AIG3"/>
-      <c r="AIH3"/>
-      <c r="AII3"/>
-      <c r="AIJ3"/>
-      <c r="AIK3"/>
-      <c r="AIL3"/>
-      <c r="AIM3"/>
-      <c r="AIN3"/>
-      <c r="AIO3"/>
-      <c r="AIP3"/>
-      <c r="AIQ3"/>
-      <c r="AIR3"/>
-      <c r="AIS3"/>
-      <c r="AIT3"/>
-      <c r="AIU3"/>
-      <c r="AIV3"/>
-      <c r="AIW3"/>
-      <c r="AIX3"/>
-      <c r="AIY3"/>
-      <c r="AIZ3"/>
-      <c r="AJA3"/>
-      <c r="AJB3"/>
-      <c r="AJC3"/>
-      <c r="AJD3"/>
-      <c r="AJE3"/>
-      <c r="AJF3"/>
-      <c r="AJG3"/>
-      <c r="AJH3"/>
-      <c r="AJI3"/>
-      <c r="AJJ3"/>
-      <c r="AJK3"/>
-      <c r="AJL3"/>
-      <c r="AJM3"/>
-      <c r="AJN3"/>
-      <c r="AJO3"/>
-      <c r="AJP3"/>
-      <c r="AJQ3"/>
-      <c r="AJR3"/>
-      <c r="AJS3"/>
-      <c r="AJT3"/>
-      <c r="AJU3"/>
-      <c r="AJV3"/>
-      <c r="AJW3"/>
-      <c r="AJX3"/>
-      <c r="AJY3"/>
-      <c r="AJZ3"/>
-      <c r="AKA3"/>
-      <c r="AKB3"/>
-      <c r="AKC3"/>
-      <c r="AKD3"/>
-      <c r="AKE3"/>
-      <c r="AKF3"/>
-      <c r="AKG3"/>
-      <c r="AKH3"/>
-      <c r="AKI3"/>
-      <c r="AKJ3"/>
-      <c r="AKK3"/>
-      <c r="AKL3"/>
-      <c r="AKM3"/>
-      <c r="AKN3"/>
-      <c r="AKO3"/>
-      <c r="AKP3"/>
-      <c r="AKQ3"/>
-      <c r="AKR3"/>
-      <c r="AKS3"/>
-      <c r="AKT3"/>
-      <c r="AKU3"/>
-      <c r="AKV3"/>
-      <c r="AKW3"/>
-      <c r="AKX3"/>
-      <c r="AKY3"/>
-      <c r="AKZ3"/>
-      <c r="ALA3"/>
-      <c r="ALB3"/>
-      <c r="ALC3"/>
-      <c r="ALD3"/>
-      <c r="ALE3"/>
-      <c r="ALF3"/>
-      <c r="ALG3"/>
-      <c r="ALH3"/>
-      <c r="ALI3"/>
-      <c r="ALJ3"/>
-      <c r="ALK3"/>
-      <c r="ALL3"/>
-      <c r="ALM3"/>
-      <c r="ALN3"/>
-      <c r="ALO3"/>
-      <c r="ALP3"/>
-      <c r="ALQ3"/>
-      <c r="ALR3"/>
-      <c r="ALS3"/>
-      <c r="ALT3"/>
-      <c r="ALU3"/>
-      <c r="ALV3"/>
-      <c r="ALW3"/>
-      <c r="ALX3"/>
-      <c r="ALY3"/>
-      <c r="ALZ3"/>
-      <c r="AMA3"/>
-      <c r="AMB3"/>
-      <c r="AMC3"/>
-      <c r="AMD3"/>
-      <c r="AME3"/>
-      <c r="AMF3"/>
-      <c r="AMG3"/>
-      <c r="AMH3"/>
-      <c r="AMI3"/>
-      <c r="AMJ3"/>
-      <c r="AMK3"/>
-      <c r="AML3"/>
-      <c r="AMM3"/>
-      <c r="AMN3"/>
-      <c r="AMO3"/>
+        <v>254</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="4" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="5" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="6" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>279</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A99CF6C3-F305-48A2-AB80-2C2D7CE6460C}">
+  <dimension ref="A1:HU5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="45.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="52.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.453125" customWidth="1"/>
+    <col min="4" max="4" width="33.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="33.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.08984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="40.81640625" customWidth="1"/>
+    <col min="8" max="8" width="62.54296875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="I2"/>
+      <c r="J2"/>
+      <c r="K2"/>
+      <c r="L2"/>
+      <c r="M2"/>
+      <c r="N2"/>
+      <c r="O2"/>
+      <c r="P2"/>
+      <c r="Q2"/>
+      <c r="R2"/>
+      <c r="S2"/>
+      <c r="T2"/>
+      <c r="U2"/>
+      <c r="V2"/>
+      <c r="W2"/>
+      <c r="X2"/>
+      <c r="Y2"/>
+      <c r="Z2"/>
+      <c r="AA2"/>
+      <c r="AB2"/>
+      <c r="AC2"/>
+      <c r="AD2"/>
+      <c r="AE2"/>
+      <c r="AF2"/>
+      <c r="AG2"/>
+      <c r="AH2"/>
+      <c r="AI2"/>
+      <c r="AJ2"/>
+      <c r="AK2"/>
+      <c r="AL2"/>
+      <c r="AM2"/>
+      <c r="AN2"/>
+      <c r="AO2"/>
+      <c r="AP2"/>
+      <c r="AQ2"/>
+      <c r="AR2"/>
+      <c r="AS2"/>
+      <c r="AT2"/>
+      <c r="AU2"/>
+      <c r="AV2"/>
+      <c r="AW2"/>
+      <c r="AX2"/>
+      <c r="AY2"/>
+      <c r="AZ2"/>
+      <c r="BA2"/>
+      <c r="BB2"/>
+      <c r="BC2"/>
+      <c r="BD2"/>
+      <c r="BE2"/>
+      <c r="BF2"/>
+      <c r="BG2"/>
+      <c r="BH2"/>
+      <c r="BI2"/>
+      <c r="BJ2"/>
+      <c r="BK2"/>
+      <c r="BL2"/>
+      <c r="BM2"/>
+      <c r="BN2"/>
+      <c r="BO2"/>
+      <c r="BP2"/>
+      <c r="BQ2"/>
+      <c r="BR2"/>
+      <c r="BS2"/>
+      <c r="BT2"/>
+      <c r="BU2"/>
+      <c r="BV2"/>
+      <c r="BW2"/>
+      <c r="BX2"/>
+      <c r="BY2"/>
+      <c r="BZ2"/>
+      <c r="CA2"/>
+      <c r="CB2"/>
+      <c r="CC2"/>
+      <c r="CD2"/>
+      <c r="CE2"/>
+      <c r="CF2"/>
+      <c r="CG2"/>
+      <c r="CH2"/>
+      <c r="CI2"/>
+      <c r="CJ2"/>
+      <c r="CK2"/>
+      <c r="CL2"/>
+      <c r="CM2"/>
+      <c r="CN2"/>
+      <c r="CO2"/>
+      <c r="CP2"/>
+      <c r="CQ2"/>
+      <c r="CR2"/>
+      <c r="CS2"/>
+      <c r="CT2"/>
+      <c r="CU2"/>
+      <c r="CV2"/>
+      <c r="CW2"/>
+      <c r="CX2"/>
+      <c r="CY2"/>
+      <c r="CZ2"/>
+      <c r="DA2"/>
+      <c r="DB2"/>
+      <c r="DC2"/>
+      <c r="DD2"/>
+      <c r="DE2"/>
+      <c r="DF2"/>
+      <c r="DG2"/>
+      <c r="DH2"/>
+      <c r="DI2"/>
+      <c r="DJ2"/>
+      <c r="DK2"/>
+      <c r="DL2"/>
+      <c r="DM2"/>
+      <c r="DN2"/>
+      <c r="DO2"/>
+      <c r="DP2"/>
+      <c r="DQ2"/>
+      <c r="DR2"/>
+      <c r="DS2"/>
+      <c r="DT2"/>
+      <c r="DU2"/>
+      <c r="DV2"/>
+      <c r="DW2"/>
+      <c r="DX2"/>
+      <c r="DY2"/>
+      <c r="DZ2"/>
+      <c r="EA2"/>
+      <c r="EB2"/>
+      <c r="EC2"/>
+      <c r="ED2"/>
+      <c r="EE2"/>
+      <c r="EF2"/>
+      <c r="EG2"/>
+      <c r="EH2"/>
+      <c r="EI2"/>
+      <c r="EJ2"/>
+      <c r="EK2"/>
+      <c r="EL2"/>
+      <c r="EM2"/>
+      <c r="EN2"/>
+      <c r="EO2"/>
+      <c r="EP2"/>
+      <c r="EQ2"/>
+      <c r="ER2"/>
+      <c r="ES2"/>
+      <c r="ET2"/>
+      <c r="EU2"/>
+      <c r="EV2"/>
+      <c r="EW2"/>
+      <c r="EX2"/>
+      <c r="EY2"/>
+      <c r="EZ2"/>
+      <c r="FA2"/>
+      <c r="FB2"/>
+      <c r="FC2"/>
+      <c r="FD2"/>
+      <c r="FE2"/>
+      <c r="FF2"/>
+      <c r="FG2"/>
+      <c r="FH2"/>
+      <c r="FI2"/>
+      <c r="FJ2"/>
+      <c r="FK2"/>
+      <c r="FL2"/>
+      <c r="FM2"/>
+      <c r="FN2"/>
+      <c r="FO2"/>
+      <c r="FP2"/>
+      <c r="FQ2"/>
+      <c r="FR2"/>
+      <c r="FS2"/>
+      <c r="FT2"/>
+      <c r="FU2"/>
+      <c r="FV2"/>
+      <c r="FW2"/>
+      <c r="FX2"/>
+      <c r="FY2"/>
+      <c r="FZ2"/>
+      <c r="GA2"/>
+      <c r="GB2"/>
+      <c r="GC2"/>
+      <c r="GD2"/>
+      <c r="GE2"/>
+      <c r="GF2"/>
+      <c r="GG2"/>
+      <c r="GH2"/>
+      <c r="GI2"/>
+      <c r="GJ2"/>
+      <c r="GK2"/>
+      <c r="GL2"/>
+      <c r="GM2"/>
+      <c r="GN2"/>
+      <c r="GO2"/>
+      <c r="GP2"/>
+      <c r="GQ2"/>
+      <c r="GR2"/>
+      <c r="GS2"/>
+      <c r="GT2"/>
+      <c r="GU2"/>
+      <c r="GV2"/>
+      <c r="GW2"/>
+      <c r="GX2"/>
+      <c r="GY2"/>
+      <c r="GZ2"/>
+      <c r="HA2"/>
+      <c r="HB2"/>
+      <c r="HC2"/>
+      <c r="HD2"/>
+      <c r="HE2"/>
+      <c r="HF2"/>
+      <c r="HG2"/>
+      <c r="HH2"/>
+      <c r="HI2"/>
+      <c r="HJ2"/>
+      <c r="HK2"/>
+      <c r="HL2"/>
+      <c r="HM2"/>
+      <c r="HN2"/>
+      <c r="HO2"/>
+      <c r="HP2"/>
+      <c r="HQ2"/>
+      <c r="HR2"/>
+      <c r="HS2"/>
+      <c r="HT2"/>
+      <c r="HU2"/>
+    </row>
+    <row r="3" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="4" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="5" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>294</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EFF0597-7FD1-4E6A-AA71-DB9F9FAB97A9}">
+  <dimension ref="A1:HU7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="45.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="52.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.453125" customWidth="1"/>
+    <col min="4" max="4" width="33.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="33.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.08984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="40.81640625" customWidth="1"/>
+    <col min="8" max="8" width="62.54296875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="I2"/>
+      <c r="J2"/>
+      <c r="K2"/>
+      <c r="L2"/>
+      <c r="M2"/>
+      <c r="N2"/>
+      <c r="O2"/>
+      <c r="P2"/>
+      <c r="Q2"/>
+      <c r="R2"/>
+      <c r="S2"/>
+      <c r="T2"/>
+      <c r="U2"/>
+      <c r="V2"/>
+      <c r="W2"/>
+      <c r="X2"/>
+      <c r="Y2"/>
+      <c r="Z2"/>
+      <c r="AA2"/>
+      <c r="AB2"/>
+      <c r="AC2"/>
+      <c r="AD2"/>
+      <c r="AE2"/>
+      <c r="AF2"/>
+      <c r="AG2"/>
+      <c r="AH2"/>
+      <c r="AI2"/>
+      <c r="AJ2"/>
+      <c r="AK2"/>
+      <c r="AL2"/>
+      <c r="AM2"/>
+      <c r="AN2"/>
+      <c r="AO2"/>
+      <c r="AP2"/>
+      <c r="AQ2"/>
+      <c r="AR2"/>
+      <c r="AS2"/>
+      <c r="AT2"/>
+      <c r="AU2"/>
+      <c r="AV2"/>
+      <c r="AW2"/>
+      <c r="AX2"/>
+      <c r="AY2"/>
+      <c r="AZ2"/>
+      <c r="BA2"/>
+      <c r="BB2"/>
+      <c r="BC2"/>
+      <c r="BD2"/>
+      <c r="BE2"/>
+      <c r="BF2"/>
+      <c r="BG2"/>
+      <c r="BH2"/>
+      <c r="BI2"/>
+      <c r="BJ2"/>
+      <c r="BK2"/>
+      <c r="BL2"/>
+      <c r="BM2"/>
+      <c r="BN2"/>
+      <c r="BO2"/>
+      <c r="BP2"/>
+      <c r="BQ2"/>
+      <c r="BR2"/>
+      <c r="BS2"/>
+      <c r="BT2"/>
+      <c r="BU2"/>
+      <c r="BV2"/>
+      <c r="BW2"/>
+      <c r="BX2"/>
+      <c r="BY2"/>
+      <c r="BZ2"/>
+      <c r="CA2"/>
+      <c r="CB2"/>
+      <c r="CC2"/>
+      <c r="CD2"/>
+      <c r="CE2"/>
+      <c r="CF2"/>
+      <c r="CG2"/>
+      <c r="CH2"/>
+      <c r="CI2"/>
+      <c r="CJ2"/>
+      <c r="CK2"/>
+      <c r="CL2"/>
+      <c r="CM2"/>
+      <c r="CN2"/>
+      <c r="CO2"/>
+      <c r="CP2"/>
+      <c r="CQ2"/>
+      <c r="CR2"/>
+      <c r="CS2"/>
+      <c r="CT2"/>
+      <c r="CU2"/>
+      <c r="CV2"/>
+      <c r="CW2"/>
+      <c r="CX2"/>
+      <c r="CY2"/>
+      <c r="CZ2"/>
+      <c r="DA2"/>
+      <c r="DB2"/>
+      <c r="DC2"/>
+      <c r="DD2"/>
+      <c r="DE2"/>
+      <c r="DF2"/>
+      <c r="DG2"/>
+      <c r="DH2"/>
+      <c r="DI2"/>
+      <c r="DJ2"/>
+      <c r="DK2"/>
+      <c r="DL2"/>
+      <c r="DM2"/>
+      <c r="DN2"/>
+      <c r="DO2"/>
+      <c r="DP2"/>
+      <c r="DQ2"/>
+      <c r="DR2"/>
+      <c r="DS2"/>
+      <c r="DT2"/>
+      <c r="DU2"/>
+      <c r="DV2"/>
+      <c r="DW2"/>
+      <c r="DX2"/>
+      <c r="DY2"/>
+      <c r="DZ2"/>
+      <c r="EA2"/>
+      <c r="EB2"/>
+      <c r="EC2"/>
+      <c r="ED2"/>
+      <c r="EE2"/>
+      <c r="EF2"/>
+      <c r="EG2"/>
+      <c r="EH2"/>
+      <c r="EI2"/>
+      <c r="EJ2"/>
+      <c r="EK2"/>
+      <c r="EL2"/>
+      <c r="EM2"/>
+      <c r="EN2"/>
+      <c r="EO2"/>
+      <c r="EP2"/>
+      <c r="EQ2"/>
+      <c r="ER2"/>
+      <c r="ES2"/>
+      <c r="ET2"/>
+      <c r="EU2"/>
+      <c r="EV2"/>
+      <c r="EW2"/>
+      <c r="EX2"/>
+      <c r="EY2"/>
+      <c r="EZ2"/>
+      <c r="FA2"/>
+      <c r="FB2"/>
+      <c r="FC2"/>
+      <c r="FD2"/>
+      <c r="FE2"/>
+      <c r="FF2"/>
+      <c r="FG2"/>
+      <c r="FH2"/>
+      <c r="FI2"/>
+      <c r="FJ2"/>
+      <c r="FK2"/>
+      <c r="FL2"/>
+      <c r="FM2"/>
+      <c r="FN2"/>
+      <c r="FO2"/>
+      <c r="FP2"/>
+      <c r="FQ2"/>
+      <c r="FR2"/>
+      <c r="FS2"/>
+      <c r="FT2"/>
+      <c r="FU2"/>
+      <c r="FV2"/>
+      <c r="FW2"/>
+      <c r="FX2"/>
+      <c r="FY2"/>
+      <c r="FZ2"/>
+      <c r="GA2"/>
+      <c r="GB2"/>
+      <c r="GC2"/>
+      <c r="GD2"/>
+      <c r="GE2"/>
+      <c r="GF2"/>
+      <c r="GG2"/>
+      <c r="GH2"/>
+      <c r="GI2"/>
+      <c r="GJ2"/>
+      <c r="GK2"/>
+      <c r="GL2"/>
+      <c r="GM2"/>
+      <c r="GN2"/>
+      <c r="GO2"/>
+      <c r="GP2"/>
+      <c r="GQ2"/>
+      <c r="GR2"/>
+      <c r="GS2"/>
+      <c r="GT2"/>
+      <c r="GU2"/>
+      <c r="GV2"/>
+      <c r="GW2"/>
+      <c r="GX2"/>
+      <c r="GY2"/>
+      <c r="GZ2"/>
+      <c r="HA2"/>
+      <c r="HB2"/>
+      <c r="HC2"/>
+      <c r="HD2"/>
+      <c r="HE2"/>
+      <c r="HF2"/>
+      <c r="HG2"/>
+      <c r="HH2"/>
+      <c r="HI2"/>
+      <c r="HJ2"/>
+      <c r="HK2"/>
+      <c r="HL2"/>
+      <c r="HM2"/>
+      <c r="HN2"/>
+      <c r="HO2"/>
+      <c r="HP2"/>
+      <c r="HQ2"/>
+      <c r="HR2"/>
+      <c r="HS2"/>
+      <c r="HT2"/>
+      <c r="HU2"/>
+    </row>
+    <row r="3" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="4" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="5" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A5" s="8" t="s">
+        <v>306</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>308</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="6" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="7" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>317</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F4A57AC-4620-4875-88AE-9F5C739A9042}">
+  <dimension ref="A1:HU6"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="50.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="52.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.453125" customWidth="1"/>
+    <col min="4" max="4" width="33.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="33.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.08984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="40.81640625" customWidth="1"/>
+    <col min="8" max="8" width="62.54296875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="I2"/>
+      <c r="J2"/>
+      <c r="K2"/>
+      <c r="L2"/>
+      <c r="M2"/>
+      <c r="N2"/>
+      <c r="O2"/>
+      <c r="P2"/>
+      <c r="Q2"/>
+      <c r="R2"/>
+      <c r="S2"/>
+      <c r="T2"/>
+      <c r="U2"/>
+      <c r="V2"/>
+      <c r="W2"/>
+      <c r="X2"/>
+      <c r="Y2"/>
+      <c r="Z2"/>
+      <c r="AA2"/>
+      <c r="AB2"/>
+      <c r="AC2"/>
+      <c r="AD2"/>
+      <c r="AE2"/>
+      <c r="AF2"/>
+      <c r="AG2"/>
+      <c r="AH2"/>
+      <c r="AI2"/>
+      <c r="AJ2"/>
+      <c r="AK2"/>
+      <c r="AL2"/>
+      <c r="AM2"/>
+      <c r="AN2"/>
+      <c r="AO2"/>
+      <c r="AP2"/>
+      <c r="AQ2"/>
+      <c r="AR2"/>
+      <c r="AS2"/>
+      <c r="AT2"/>
+      <c r="AU2"/>
+      <c r="AV2"/>
+      <c r="AW2"/>
+      <c r="AX2"/>
+      <c r="AY2"/>
+      <c r="AZ2"/>
+      <c r="BA2"/>
+      <c r="BB2"/>
+      <c r="BC2"/>
+      <c r="BD2"/>
+      <c r="BE2"/>
+      <c r="BF2"/>
+      <c r="BG2"/>
+      <c r="BH2"/>
+      <c r="BI2"/>
+      <c r="BJ2"/>
+      <c r="BK2"/>
+      <c r="BL2"/>
+      <c r="BM2"/>
+      <c r="BN2"/>
+      <c r="BO2"/>
+      <c r="BP2"/>
+      <c r="BQ2"/>
+      <c r="BR2"/>
+      <c r="BS2"/>
+      <c r="BT2"/>
+      <c r="BU2"/>
+      <c r="BV2"/>
+      <c r="BW2"/>
+      <c r="BX2"/>
+      <c r="BY2"/>
+      <c r="BZ2"/>
+      <c r="CA2"/>
+      <c r="CB2"/>
+      <c r="CC2"/>
+      <c r="CD2"/>
+      <c r="CE2"/>
+      <c r="CF2"/>
+      <c r="CG2"/>
+      <c r="CH2"/>
+      <c r="CI2"/>
+      <c r="CJ2"/>
+      <c r="CK2"/>
+      <c r="CL2"/>
+      <c r="CM2"/>
+      <c r="CN2"/>
+      <c r="CO2"/>
+      <c r="CP2"/>
+      <c r="CQ2"/>
+      <c r="CR2"/>
+      <c r="CS2"/>
+      <c r="CT2"/>
+      <c r="CU2"/>
+      <c r="CV2"/>
+      <c r="CW2"/>
+      <c r="CX2"/>
+      <c r="CY2"/>
+      <c r="CZ2"/>
+      <c r="DA2"/>
+      <c r="DB2"/>
+      <c r="DC2"/>
+      <c r="DD2"/>
+      <c r="DE2"/>
+      <c r="DF2"/>
+      <c r="DG2"/>
+      <c r="DH2"/>
+      <c r="DI2"/>
+      <c r="DJ2"/>
+      <c r="DK2"/>
+      <c r="DL2"/>
+      <c r="DM2"/>
+      <c r="DN2"/>
+      <c r="DO2"/>
+      <c r="DP2"/>
+      <c r="DQ2"/>
+      <c r="DR2"/>
+      <c r="DS2"/>
+      <c r="DT2"/>
+      <c r="DU2"/>
+      <c r="DV2"/>
+      <c r="DW2"/>
+      <c r="DX2"/>
+      <c r="DY2"/>
+      <c r="DZ2"/>
+      <c r="EA2"/>
+      <c r="EB2"/>
+      <c r="EC2"/>
+      <c r="ED2"/>
+      <c r="EE2"/>
+      <c r="EF2"/>
+      <c r="EG2"/>
+      <c r="EH2"/>
+      <c r="EI2"/>
+      <c r="EJ2"/>
+      <c r="EK2"/>
+      <c r="EL2"/>
+      <c r="EM2"/>
+      <c r="EN2"/>
+      <c r="EO2"/>
+      <c r="EP2"/>
+      <c r="EQ2"/>
+      <c r="ER2"/>
+      <c r="ES2"/>
+      <c r="ET2"/>
+      <c r="EU2"/>
+      <c r="EV2"/>
+      <c r="EW2"/>
+      <c r="EX2"/>
+      <c r="EY2"/>
+      <c r="EZ2"/>
+      <c r="FA2"/>
+      <c r="FB2"/>
+      <c r="FC2"/>
+      <c r="FD2"/>
+      <c r="FE2"/>
+      <c r="FF2"/>
+      <c r="FG2"/>
+      <c r="FH2"/>
+      <c r="FI2"/>
+      <c r="FJ2"/>
+      <c r="FK2"/>
+      <c r="FL2"/>
+      <c r="FM2"/>
+      <c r="FN2"/>
+      <c r="FO2"/>
+      <c r="FP2"/>
+      <c r="FQ2"/>
+      <c r="FR2"/>
+      <c r="FS2"/>
+      <c r="FT2"/>
+      <c r="FU2"/>
+      <c r="FV2"/>
+      <c r="FW2"/>
+      <c r="FX2"/>
+      <c r="FY2"/>
+      <c r="FZ2"/>
+      <c r="GA2"/>
+      <c r="GB2"/>
+      <c r="GC2"/>
+      <c r="GD2"/>
+      <c r="GE2"/>
+      <c r="GF2"/>
+      <c r="GG2"/>
+      <c r="GH2"/>
+      <c r="GI2"/>
+      <c r="GJ2"/>
+      <c r="GK2"/>
+      <c r="GL2"/>
+      <c r="GM2"/>
+      <c r="GN2"/>
+      <c r="GO2"/>
+      <c r="GP2"/>
+      <c r="GQ2"/>
+      <c r="GR2"/>
+      <c r="GS2"/>
+      <c r="GT2"/>
+      <c r="GU2"/>
+      <c r="GV2"/>
+      <c r="GW2"/>
+      <c r="GX2"/>
+      <c r="GY2"/>
+      <c r="GZ2"/>
+      <c r="HA2"/>
+      <c r="HB2"/>
+      <c r="HC2"/>
+      <c r="HD2"/>
+      <c r="HE2"/>
+      <c r="HF2"/>
+      <c r="HG2"/>
+      <c r="HH2"/>
+      <c r="HI2"/>
+      <c r="HJ2"/>
+      <c r="HK2"/>
+      <c r="HL2"/>
+      <c r="HM2"/>
+      <c r="HN2"/>
+      <c r="HO2"/>
+      <c r="HP2"/>
+      <c r="HQ2"/>
+      <c r="HR2"/>
+      <c r="HS2"/>
+      <c r="HT2"/>
+      <c r="HU2"/>
+    </row>
+    <row r="3" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="4" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="5" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A5" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="6" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>336</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2DC696B-E1A8-430C-BC9E-87DD1A6FBE9F}">
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="33.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="33.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.90625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C1C130F-0899-4810-82F6-950C9CB07234}">
+  <dimension ref="A1:HU5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="45.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="52.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.453125" customWidth="1"/>
+    <col min="4" max="4" width="33.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="33.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.08984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="40.81640625" customWidth="1"/>
+    <col min="8" max="8" width="62.54296875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="I2"/>
+      <c r="J2"/>
+      <c r="K2"/>
+      <c r="L2"/>
+      <c r="M2"/>
+      <c r="N2"/>
+      <c r="O2"/>
+      <c r="P2"/>
+      <c r="Q2"/>
+      <c r="R2"/>
+      <c r="S2"/>
+      <c r="T2"/>
+      <c r="U2"/>
+      <c r="V2"/>
+      <c r="W2"/>
+      <c r="X2"/>
+      <c r="Y2"/>
+      <c r="Z2"/>
+      <c r="AA2"/>
+      <c r="AB2"/>
+      <c r="AC2"/>
+      <c r="AD2"/>
+      <c r="AE2"/>
+      <c r="AF2"/>
+      <c r="AG2"/>
+      <c r="AH2"/>
+      <c r="AI2"/>
+      <c r="AJ2"/>
+      <c r="AK2"/>
+      <c r="AL2"/>
+      <c r="AM2"/>
+      <c r="AN2"/>
+      <c r="AO2"/>
+      <c r="AP2"/>
+      <c r="AQ2"/>
+      <c r="AR2"/>
+      <c r="AS2"/>
+      <c r="AT2"/>
+      <c r="AU2"/>
+      <c r="AV2"/>
+      <c r="AW2"/>
+      <c r="AX2"/>
+      <c r="AY2"/>
+      <c r="AZ2"/>
+      <c r="BA2"/>
+      <c r="BB2"/>
+      <c r="BC2"/>
+      <c r="BD2"/>
+      <c r="BE2"/>
+      <c r="BF2"/>
+      <c r="BG2"/>
+      <c r="BH2"/>
+      <c r="BI2"/>
+      <c r="BJ2"/>
+      <c r="BK2"/>
+      <c r="BL2"/>
+      <c r="BM2"/>
+      <c r="BN2"/>
+      <c r="BO2"/>
+      <c r="BP2"/>
+      <c r="BQ2"/>
+      <c r="BR2"/>
+      <c r="BS2"/>
+      <c r="BT2"/>
+      <c r="BU2"/>
+      <c r="BV2"/>
+      <c r="BW2"/>
+      <c r="BX2"/>
+      <c r="BY2"/>
+      <c r="BZ2"/>
+      <c r="CA2"/>
+      <c r="CB2"/>
+      <c r="CC2"/>
+      <c r="CD2"/>
+      <c r="CE2"/>
+      <c r="CF2"/>
+      <c r="CG2"/>
+      <c r="CH2"/>
+      <c r="CI2"/>
+      <c r="CJ2"/>
+      <c r="CK2"/>
+      <c r="CL2"/>
+      <c r="CM2"/>
+      <c r="CN2"/>
+      <c r="CO2"/>
+      <c r="CP2"/>
+      <c r="CQ2"/>
+      <c r="CR2"/>
+      <c r="CS2"/>
+      <c r="CT2"/>
+      <c r="CU2"/>
+      <c r="CV2"/>
+      <c r="CW2"/>
+      <c r="CX2"/>
+      <c r="CY2"/>
+      <c r="CZ2"/>
+      <c r="DA2"/>
+      <c r="DB2"/>
+      <c r="DC2"/>
+      <c r="DD2"/>
+      <c r="DE2"/>
+      <c r="DF2"/>
+      <c r="DG2"/>
+      <c r="DH2"/>
+      <c r="DI2"/>
+      <c r="DJ2"/>
+      <c r="DK2"/>
+      <c r="DL2"/>
+      <c r="DM2"/>
+      <c r="DN2"/>
+      <c r="DO2"/>
+      <c r="DP2"/>
+      <c r="DQ2"/>
+      <c r="DR2"/>
+      <c r="DS2"/>
+      <c r="DT2"/>
+      <c r="DU2"/>
+      <c r="DV2"/>
+      <c r="DW2"/>
+      <c r="DX2"/>
+      <c r="DY2"/>
+      <c r="DZ2"/>
+      <c r="EA2"/>
+      <c r="EB2"/>
+      <c r="EC2"/>
+      <c r="ED2"/>
+      <c r="EE2"/>
+      <c r="EF2"/>
+      <c r="EG2"/>
+      <c r="EH2"/>
+      <c r="EI2"/>
+      <c r="EJ2"/>
+      <c r="EK2"/>
+      <c r="EL2"/>
+      <c r="EM2"/>
+      <c r="EN2"/>
+      <c r="EO2"/>
+      <c r="EP2"/>
+      <c r="EQ2"/>
+      <c r="ER2"/>
+      <c r="ES2"/>
+      <c r="ET2"/>
+      <c r="EU2"/>
+      <c r="EV2"/>
+      <c r="EW2"/>
+      <c r="EX2"/>
+      <c r="EY2"/>
+      <c r="EZ2"/>
+      <c r="FA2"/>
+      <c r="FB2"/>
+      <c r="FC2"/>
+      <c r="FD2"/>
+      <c r="FE2"/>
+      <c r="FF2"/>
+      <c r="FG2"/>
+      <c r="FH2"/>
+      <c r="FI2"/>
+      <c r="FJ2"/>
+      <c r="FK2"/>
+      <c r="FL2"/>
+      <c r="FM2"/>
+      <c r="FN2"/>
+      <c r="FO2"/>
+      <c r="FP2"/>
+      <c r="FQ2"/>
+      <c r="FR2"/>
+      <c r="FS2"/>
+      <c r="FT2"/>
+      <c r="FU2"/>
+      <c r="FV2"/>
+      <c r="FW2"/>
+      <c r="FX2"/>
+      <c r="FY2"/>
+      <c r="FZ2"/>
+      <c r="GA2"/>
+      <c r="GB2"/>
+      <c r="GC2"/>
+      <c r="GD2"/>
+      <c r="GE2"/>
+      <c r="GF2"/>
+      <c r="GG2"/>
+      <c r="GH2"/>
+      <c r="GI2"/>
+      <c r="GJ2"/>
+      <c r="GK2"/>
+      <c r="GL2"/>
+      <c r="GM2"/>
+      <c r="GN2"/>
+      <c r="GO2"/>
+      <c r="GP2"/>
+      <c r="GQ2"/>
+      <c r="GR2"/>
+      <c r="GS2"/>
+      <c r="GT2"/>
+      <c r="GU2"/>
+      <c r="GV2"/>
+      <c r="GW2"/>
+      <c r="GX2"/>
+      <c r="GY2"/>
+      <c r="GZ2"/>
+      <c r="HA2"/>
+      <c r="HB2"/>
+      <c r="HC2"/>
+      <c r="HD2"/>
+      <c r="HE2"/>
+      <c r="HF2"/>
+      <c r="HG2"/>
+      <c r="HH2"/>
+      <c r="HI2"/>
+      <c r="HJ2"/>
+      <c r="HK2"/>
+      <c r="HL2"/>
+      <c r="HM2"/>
+      <c r="HN2"/>
+      <c r="HO2"/>
+      <c r="HP2"/>
+      <c r="HQ2"/>
+      <c r="HR2"/>
+      <c r="HS2"/>
+      <c r="HT2"/>
+      <c r="HU2"/>
+    </row>
+    <row r="3" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="4" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="5" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>351</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AB9395B-D522-49AD-B790-5334356249F6}">
+  <dimension ref="A1:HU7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="50.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="52.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.453125" customWidth="1"/>
+    <col min="4" max="4" width="33.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="33.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.08984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="40.81640625" customWidth="1"/>
+    <col min="8" max="8" width="62.54296875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="I2"/>
+      <c r="J2"/>
+      <c r="K2"/>
+      <c r="L2"/>
+      <c r="M2"/>
+      <c r="N2"/>
+      <c r="O2"/>
+      <c r="P2"/>
+      <c r="Q2"/>
+      <c r="R2"/>
+      <c r="S2"/>
+      <c r="T2"/>
+      <c r="U2"/>
+      <c r="V2"/>
+      <c r="W2"/>
+      <c r="X2"/>
+      <c r="Y2"/>
+      <c r="Z2"/>
+      <c r="AA2"/>
+      <c r="AB2"/>
+      <c r="AC2"/>
+      <c r="AD2"/>
+      <c r="AE2"/>
+      <c r="AF2"/>
+      <c r="AG2"/>
+      <c r="AH2"/>
+      <c r="AI2"/>
+      <c r="AJ2"/>
+      <c r="AK2"/>
+      <c r="AL2"/>
+      <c r="AM2"/>
+      <c r="AN2"/>
+      <c r="AO2"/>
+      <c r="AP2"/>
+      <c r="AQ2"/>
+      <c r="AR2"/>
+      <c r="AS2"/>
+      <c r="AT2"/>
+      <c r="AU2"/>
+      <c r="AV2"/>
+      <c r="AW2"/>
+      <c r="AX2"/>
+      <c r="AY2"/>
+      <c r="AZ2"/>
+      <c r="BA2"/>
+      <c r="BB2"/>
+      <c r="BC2"/>
+      <c r="BD2"/>
+      <c r="BE2"/>
+      <c r="BF2"/>
+      <c r="BG2"/>
+      <c r="BH2"/>
+      <c r="BI2"/>
+      <c r="BJ2"/>
+      <c r="BK2"/>
+      <c r="BL2"/>
+      <c r="BM2"/>
+      <c r="BN2"/>
+      <c r="BO2"/>
+      <c r="BP2"/>
+      <c r="BQ2"/>
+      <c r="BR2"/>
+      <c r="BS2"/>
+      <c r="BT2"/>
+      <c r="BU2"/>
+      <c r="BV2"/>
+      <c r="BW2"/>
+      <c r="BX2"/>
+      <c r="BY2"/>
+      <c r="BZ2"/>
+      <c r="CA2"/>
+      <c r="CB2"/>
+      <c r="CC2"/>
+      <c r="CD2"/>
+      <c r="CE2"/>
+      <c r="CF2"/>
+      <c r="CG2"/>
+      <c r="CH2"/>
+      <c r="CI2"/>
+      <c r="CJ2"/>
+      <c r="CK2"/>
+      <c r="CL2"/>
+      <c r="CM2"/>
+      <c r="CN2"/>
+      <c r="CO2"/>
+      <c r="CP2"/>
+      <c r="CQ2"/>
+      <c r="CR2"/>
+      <c r="CS2"/>
+      <c r="CT2"/>
+      <c r="CU2"/>
+      <c r="CV2"/>
+      <c r="CW2"/>
+      <c r="CX2"/>
+      <c r="CY2"/>
+      <c r="CZ2"/>
+      <c r="DA2"/>
+      <c r="DB2"/>
+      <c r="DC2"/>
+      <c r="DD2"/>
+      <c r="DE2"/>
+      <c r="DF2"/>
+      <c r="DG2"/>
+      <c r="DH2"/>
+      <c r="DI2"/>
+      <c r="DJ2"/>
+      <c r="DK2"/>
+      <c r="DL2"/>
+      <c r="DM2"/>
+      <c r="DN2"/>
+      <c r="DO2"/>
+      <c r="DP2"/>
+      <c r="DQ2"/>
+      <c r="DR2"/>
+      <c r="DS2"/>
+      <c r="DT2"/>
+      <c r="DU2"/>
+      <c r="DV2"/>
+      <c r="DW2"/>
+      <c r="DX2"/>
+      <c r="DY2"/>
+      <c r="DZ2"/>
+      <c r="EA2"/>
+      <c r="EB2"/>
+      <c r="EC2"/>
+      <c r="ED2"/>
+      <c r="EE2"/>
+      <c r="EF2"/>
+      <c r="EG2"/>
+      <c r="EH2"/>
+      <c r="EI2"/>
+      <c r="EJ2"/>
+      <c r="EK2"/>
+      <c r="EL2"/>
+      <c r="EM2"/>
+      <c r="EN2"/>
+      <c r="EO2"/>
+      <c r="EP2"/>
+      <c r="EQ2"/>
+      <c r="ER2"/>
+      <c r="ES2"/>
+      <c r="ET2"/>
+      <c r="EU2"/>
+      <c r="EV2"/>
+      <c r="EW2"/>
+      <c r="EX2"/>
+      <c r="EY2"/>
+      <c r="EZ2"/>
+      <c r="FA2"/>
+      <c r="FB2"/>
+      <c r="FC2"/>
+      <c r="FD2"/>
+      <c r="FE2"/>
+      <c r="FF2"/>
+      <c r="FG2"/>
+      <c r="FH2"/>
+      <c r="FI2"/>
+      <c r="FJ2"/>
+      <c r="FK2"/>
+      <c r="FL2"/>
+      <c r="FM2"/>
+      <c r="FN2"/>
+      <c r="FO2"/>
+      <c r="FP2"/>
+      <c r="FQ2"/>
+      <c r="FR2"/>
+      <c r="FS2"/>
+      <c r="FT2"/>
+      <c r="FU2"/>
+      <c r="FV2"/>
+      <c r="FW2"/>
+      <c r="FX2"/>
+      <c r="FY2"/>
+      <c r="FZ2"/>
+      <c r="GA2"/>
+      <c r="GB2"/>
+      <c r="GC2"/>
+      <c r="GD2"/>
+      <c r="GE2"/>
+      <c r="GF2"/>
+      <c r="GG2"/>
+      <c r="GH2"/>
+      <c r="GI2"/>
+      <c r="GJ2"/>
+      <c r="GK2"/>
+      <c r="GL2"/>
+      <c r="GM2"/>
+      <c r="GN2"/>
+      <c r="GO2"/>
+      <c r="GP2"/>
+      <c r="GQ2"/>
+      <c r="GR2"/>
+      <c r="GS2"/>
+      <c r="GT2"/>
+      <c r="GU2"/>
+      <c r="GV2"/>
+      <c r="GW2"/>
+      <c r="GX2"/>
+      <c r="GY2"/>
+      <c r="GZ2"/>
+      <c r="HA2"/>
+      <c r="HB2"/>
+      <c r="HC2"/>
+      <c r="HD2"/>
+      <c r="HE2"/>
+      <c r="HF2"/>
+      <c r="HG2"/>
+      <c r="HH2"/>
+      <c r="HI2"/>
+      <c r="HJ2"/>
+      <c r="HK2"/>
+      <c r="HL2"/>
+      <c r="HM2"/>
+      <c r="HN2"/>
+      <c r="HO2"/>
+      <c r="HP2"/>
+      <c r="HQ2"/>
+      <c r="HR2"/>
+      <c r="HS2"/>
+      <c r="HT2"/>
+      <c r="HU2"/>
+    </row>
+    <row r="3" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="4" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="5" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A5" s="8" t="s">
+        <v>363</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>364</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="6" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="7" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>374</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEE91763-AD0C-4544-A433-3B50C88AEB79}">
+  <dimension ref="A1:HU7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="50.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="52.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.453125" customWidth="1"/>
+    <col min="4" max="4" width="33.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="33.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.08984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="40.81640625" customWidth="1"/>
+    <col min="8" max="8" width="62.54296875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="I2"/>
+      <c r="J2"/>
+      <c r="K2"/>
+      <c r="L2"/>
+      <c r="M2"/>
+      <c r="N2"/>
+      <c r="O2"/>
+      <c r="P2"/>
+      <c r="Q2"/>
+      <c r="R2"/>
+      <c r="S2"/>
+      <c r="T2"/>
+      <c r="U2"/>
+      <c r="V2"/>
+      <c r="W2"/>
+      <c r="X2"/>
+      <c r="Y2"/>
+      <c r="Z2"/>
+      <c r="AA2"/>
+      <c r="AB2"/>
+      <c r="AC2"/>
+      <c r="AD2"/>
+      <c r="AE2"/>
+      <c r="AF2"/>
+      <c r="AG2"/>
+      <c r="AH2"/>
+      <c r="AI2"/>
+      <c r="AJ2"/>
+      <c r="AK2"/>
+      <c r="AL2"/>
+      <c r="AM2"/>
+      <c r="AN2"/>
+      <c r="AO2"/>
+      <c r="AP2"/>
+      <c r="AQ2"/>
+      <c r="AR2"/>
+      <c r="AS2"/>
+      <c r="AT2"/>
+      <c r="AU2"/>
+      <c r="AV2"/>
+      <c r="AW2"/>
+      <c r="AX2"/>
+      <c r="AY2"/>
+      <c r="AZ2"/>
+      <c r="BA2"/>
+      <c r="BB2"/>
+      <c r="BC2"/>
+      <c r="BD2"/>
+      <c r="BE2"/>
+      <c r="BF2"/>
+      <c r="BG2"/>
+      <c r="BH2"/>
+      <c r="BI2"/>
+      <c r="BJ2"/>
+      <c r="BK2"/>
+      <c r="BL2"/>
+      <c r="BM2"/>
+      <c r="BN2"/>
+      <c r="BO2"/>
+      <c r="BP2"/>
+      <c r="BQ2"/>
+      <c r="BR2"/>
+      <c r="BS2"/>
+      <c r="BT2"/>
+      <c r="BU2"/>
+      <c r="BV2"/>
+      <c r="BW2"/>
+      <c r="BX2"/>
+      <c r="BY2"/>
+      <c r="BZ2"/>
+      <c r="CA2"/>
+      <c r="CB2"/>
+      <c r="CC2"/>
+      <c r="CD2"/>
+      <c r="CE2"/>
+      <c r="CF2"/>
+      <c r="CG2"/>
+      <c r="CH2"/>
+      <c r="CI2"/>
+      <c r="CJ2"/>
+      <c r="CK2"/>
+      <c r="CL2"/>
+      <c r="CM2"/>
+      <c r="CN2"/>
+      <c r="CO2"/>
+      <c r="CP2"/>
+      <c r="CQ2"/>
+      <c r="CR2"/>
+      <c r="CS2"/>
+      <c r="CT2"/>
+      <c r="CU2"/>
+      <c r="CV2"/>
+      <c r="CW2"/>
+      <c r="CX2"/>
+      <c r="CY2"/>
+      <c r="CZ2"/>
+      <c r="DA2"/>
+      <c r="DB2"/>
+      <c r="DC2"/>
+      <c r="DD2"/>
+      <c r="DE2"/>
+      <c r="DF2"/>
+      <c r="DG2"/>
+      <c r="DH2"/>
+      <c r="DI2"/>
+      <c r="DJ2"/>
+      <c r="DK2"/>
+      <c r="DL2"/>
+      <c r="DM2"/>
+      <c r="DN2"/>
+      <c r="DO2"/>
+      <c r="DP2"/>
+      <c r="DQ2"/>
+      <c r="DR2"/>
+      <c r="DS2"/>
+      <c r="DT2"/>
+      <c r="DU2"/>
+      <c r="DV2"/>
+      <c r="DW2"/>
+      <c r="DX2"/>
+      <c r="DY2"/>
+      <c r="DZ2"/>
+      <c r="EA2"/>
+      <c r="EB2"/>
+      <c r="EC2"/>
+      <c r="ED2"/>
+      <c r="EE2"/>
+      <c r="EF2"/>
+      <c r="EG2"/>
+      <c r="EH2"/>
+      <c r="EI2"/>
+      <c r="EJ2"/>
+      <c r="EK2"/>
+      <c r="EL2"/>
+      <c r="EM2"/>
+      <c r="EN2"/>
+      <c r="EO2"/>
+      <c r="EP2"/>
+      <c r="EQ2"/>
+      <c r="ER2"/>
+      <c r="ES2"/>
+      <c r="ET2"/>
+      <c r="EU2"/>
+      <c r="EV2"/>
+      <c r="EW2"/>
+      <c r="EX2"/>
+      <c r="EY2"/>
+      <c r="EZ2"/>
+      <c r="FA2"/>
+      <c r="FB2"/>
+      <c r="FC2"/>
+      <c r="FD2"/>
+      <c r="FE2"/>
+      <c r="FF2"/>
+      <c r="FG2"/>
+      <c r="FH2"/>
+      <c r="FI2"/>
+      <c r="FJ2"/>
+      <c r="FK2"/>
+      <c r="FL2"/>
+      <c r="FM2"/>
+      <c r="FN2"/>
+      <c r="FO2"/>
+      <c r="FP2"/>
+      <c r="FQ2"/>
+      <c r="FR2"/>
+      <c r="FS2"/>
+      <c r="FT2"/>
+      <c r="FU2"/>
+      <c r="FV2"/>
+      <c r="FW2"/>
+      <c r="FX2"/>
+      <c r="FY2"/>
+      <c r="FZ2"/>
+      <c r="GA2"/>
+      <c r="GB2"/>
+      <c r="GC2"/>
+      <c r="GD2"/>
+      <c r="GE2"/>
+      <c r="GF2"/>
+      <c r="GG2"/>
+      <c r="GH2"/>
+      <c r="GI2"/>
+      <c r="GJ2"/>
+      <c r="GK2"/>
+      <c r="GL2"/>
+      <c r="GM2"/>
+      <c r="GN2"/>
+      <c r="GO2"/>
+      <c r="GP2"/>
+      <c r="GQ2"/>
+      <c r="GR2"/>
+      <c r="GS2"/>
+      <c r="GT2"/>
+      <c r="GU2"/>
+      <c r="GV2"/>
+      <c r="GW2"/>
+      <c r="GX2"/>
+      <c r="GY2"/>
+      <c r="GZ2"/>
+      <c r="HA2"/>
+      <c r="HB2"/>
+      <c r="HC2"/>
+      <c r="HD2"/>
+      <c r="HE2"/>
+      <c r="HF2"/>
+      <c r="HG2"/>
+      <c r="HH2"/>
+      <c r="HI2"/>
+      <c r="HJ2"/>
+      <c r="HK2"/>
+      <c r="HL2"/>
+      <c r="HM2"/>
+      <c r="HN2"/>
+      <c r="HO2"/>
+      <c r="HP2"/>
+      <c r="HQ2"/>
+      <c r="HR2"/>
+      <c r="HS2"/>
+      <c r="HT2"/>
+      <c r="HU2"/>
+    </row>
+    <row r="3" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="4" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="5" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A5" s="8" t="s">
+        <v>386</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>387</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>388</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="6" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="7" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>397</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9169CA5-09CB-4ADC-8EEE-AB383FD3DBB7}">
+  <dimension ref="A1:AMO11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="40.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="52.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="33.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="34.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="32.7265625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1029" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1029" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1029" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="4" spans="1:1029" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>93</v>
+        <v>133</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>90</v>
+        <v>134</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>91</v>
+        <v>135</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>4</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>85</v>
+        <v>398</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>92</v>
+        <v>136</v>
       </c>
     </row>
-    <row r="5" spans="1:1029" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:1029" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>4</v>
       </c>
       <c r="E5" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>98</v>
-      </c>
+      <c r="G5"/>
+      <c r="H5"/>
+      <c r="I5"/>
+      <c r="J5"/>
+      <c r="K5"/>
+      <c r="L5"/>
+      <c r="M5"/>
+      <c r="N5"/>
+      <c r="O5"/>
+      <c r="P5"/>
+      <c r="Q5"/>
+      <c r="R5"/>
+      <c r="S5"/>
+      <c r="T5"/>
+      <c r="U5"/>
+      <c r="V5"/>
+      <c r="W5"/>
+      <c r="X5"/>
+      <c r="Y5"/>
+      <c r="Z5"/>
+      <c r="AA5"/>
+      <c r="AB5"/>
+      <c r="AC5"/>
+      <c r="AD5"/>
+      <c r="AE5"/>
+      <c r="AF5"/>
+      <c r="AG5"/>
+      <c r="AH5"/>
+      <c r="AI5"/>
+      <c r="AJ5"/>
+      <c r="AK5"/>
+      <c r="AL5"/>
+      <c r="AM5"/>
+      <c r="AN5"/>
+      <c r="AO5"/>
+      <c r="AP5"/>
+      <c r="AQ5"/>
+      <c r="AR5"/>
+      <c r="AS5"/>
+      <c r="AT5"/>
+      <c r="AU5"/>
+      <c r="AV5"/>
+      <c r="AW5"/>
+      <c r="AX5"/>
+      <c r="AY5"/>
+      <c r="AZ5"/>
+      <c r="BA5"/>
+      <c r="BB5"/>
+      <c r="BC5"/>
+      <c r="BD5"/>
+      <c r="BE5"/>
+      <c r="BF5"/>
+      <c r="BG5"/>
+      <c r="BH5"/>
+      <c r="BI5"/>
+      <c r="BJ5"/>
+      <c r="BK5"/>
+      <c r="BL5"/>
+      <c r="BM5"/>
+      <c r="BN5"/>
+      <c r="BO5"/>
+      <c r="BP5"/>
+      <c r="BQ5"/>
+      <c r="BR5"/>
+      <c r="BS5"/>
+      <c r="BT5"/>
+      <c r="BU5"/>
+      <c r="BV5"/>
+      <c r="BW5"/>
+      <c r="BX5"/>
+      <c r="BY5"/>
+      <c r="BZ5"/>
+      <c r="CA5"/>
+      <c r="CB5"/>
+      <c r="CC5"/>
+      <c r="CD5"/>
+      <c r="CE5"/>
+      <c r="CF5"/>
+      <c r="CG5"/>
+      <c r="CH5"/>
+      <c r="CI5"/>
+      <c r="CJ5"/>
+      <c r="CK5"/>
+      <c r="CL5"/>
+      <c r="CM5"/>
+      <c r="CN5"/>
+      <c r="CO5"/>
+      <c r="CP5"/>
+      <c r="CQ5"/>
+      <c r="CR5"/>
+      <c r="CS5"/>
+      <c r="CT5"/>
+      <c r="CU5"/>
+      <c r="CV5"/>
+      <c r="CW5"/>
+      <c r="CX5"/>
+      <c r="CY5"/>
+      <c r="CZ5"/>
+      <c r="DA5"/>
+      <c r="DB5"/>
+      <c r="DC5"/>
+      <c r="DD5"/>
+      <c r="DE5"/>
+      <c r="DF5"/>
+      <c r="DG5"/>
+      <c r="DH5"/>
+      <c r="DI5"/>
+      <c r="DJ5"/>
+      <c r="DK5"/>
+      <c r="DL5"/>
+      <c r="DM5"/>
+      <c r="DN5"/>
+      <c r="DO5"/>
+      <c r="DP5"/>
+      <c r="DQ5"/>
+      <c r="DR5"/>
+      <c r="DS5"/>
+      <c r="DT5"/>
+      <c r="DU5"/>
+      <c r="DV5"/>
+      <c r="DW5"/>
+      <c r="DX5"/>
+      <c r="DY5"/>
+      <c r="DZ5"/>
+      <c r="EA5"/>
+      <c r="EB5"/>
+      <c r="EC5"/>
+      <c r="ED5"/>
+      <c r="EE5"/>
+      <c r="EF5"/>
+      <c r="EG5"/>
+      <c r="EH5"/>
+      <c r="EI5"/>
+      <c r="EJ5"/>
+      <c r="EK5"/>
+      <c r="EL5"/>
+      <c r="EM5"/>
+      <c r="EN5"/>
+      <c r="EO5"/>
+      <c r="EP5"/>
+      <c r="EQ5"/>
+      <c r="ER5"/>
+      <c r="ES5"/>
+      <c r="ET5"/>
+      <c r="EU5"/>
+      <c r="EV5"/>
+      <c r="EW5"/>
+      <c r="EX5"/>
+      <c r="EY5"/>
+      <c r="EZ5"/>
+      <c r="FA5"/>
+      <c r="FB5"/>
+      <c r="FC5"/>
+      <c r="FD5"/>
+      <c r="FE5"/>
+      <c r="FF5"/>
+      <c r="FG5"/>
+      <c r="FH5"/>
+      <c r="FI5"/>
+      <c r="FJ5"/>
+      <c r="FK5"/>
+      <c r="FL5"/>
+      <c r="FM5"/>
+      <c r="FN5"/>
+      <c r="FO5"/>
+      <c r="FP5"/>
+      <c r="FQ5"/>
+      <c r="FR5"/>
+      <c r="FS5"/>
+      <c r="FT5"/>
+      <c r="FU5"/>
+      <c r="FV5"/>
+      <c r="FW5"/>
+      <c r="FX5"/>
+      <c r="FY5"/>
+      <c r="FZ5"/>
+      <c r="GA5"/>
+      <c r="GB5"/>
+      <c r="GC5"/>
+      <c r="GD5"/>
+      <c r="GE5"/>
+      <c r="GF5"/>
+      <c r="GG5"/>
+      <c r="GH5"/>
+      <c r="GI5"/>
+      <c r="GJ5"/>
+      <c r="GK5"/>
+      <c r="GL5"/>
+      <c r="GM5"/>
+      <c r="GN5"/>
+      <c r="GO5"/>
+      <c r="GP5"/>
+      <c r="GQ5"/>
+      <c r="GR5"/>
+      <c r="GS5"/>
+      <c r="GT5"/>
+      <c r="GU5"/>
+      <c r="GV5"/>
+      <c r="GW5"/>
+      <c r="GX5"/>
+      <c r="GY5"/>
+      <c r="GZ5"/>
+      <c r="HA5"/>
+      <c r="HB5"/>
+      <c r="HC5"/>
+      <c r="HD5"/>
+      <c r="HE5"/>
+      <c r="HF5"/>
+      <c r="HG5"/>
+      <c r="HH5"/>
+      <c r="HI5"/>
+      <c r="HJ5"/>
+      <c r="HK5"/>
+      <c r="HL5"/>
+      <c r="HM5"/>
+      <c r="HN5"/>
+      <c r="HO5"/>
+      <c r="HP5"/>
+      <c r="HQ5"/>
+      <c r="HR5"/>
+      <c r="HS5"/>
+      <c r="HT5"/>
+      <c r="HU5"/>
+      <c r="HV5"/>
+      <c r="HW5"/>
+      <c r="HX5"/>
+      <c r="HY5"/>
+      <c r="HZ5"/>
+      <c r="IA5"/>
+      <c r="IB5"/>
+      <c r="IC5"/>
+      <c r="ID5"/>
+      <c r="IE5"/>
+      <c r="IF5"/>
+      <c r="IG5"/>
+      <c r="IH5"/>
+      <c r="II5"/>
+      <c r="IJ5"/>
+      <c r="IK5"/>
+      <c r="IL5"/>
+      <c r="IM5"/>
+      <c r="IN5"/>
+      <c r="IO5"/>
+      <c r="IP5"/>
+      <c r="IQ5"/>
+      <c r="IR5"/>
+      <c r="IS5"/>
+      <c r="IT5"/>
+      <c r="IU5"/>
+      <c r="IV5"/>
+      <c r="IW5"/>
+      <c r="IX5"/>
+      <c r="IY5"/>
+      <c r="IZ5"/>
+      <c r="JA5"/>
+      <c r="JB5"/>
+      <c r="JC5"/>
+      <c r="JD5"/>
+      <c r="JE5"/>
+      <c r="JF5"/>
+      <c r="JG5"/>
+      <c r="JH5"/>
+      <c r="JI5"/>
+      <c r="JJ5"/>
+      <c r="JK5"/>
+      <c r="JL5"/>
+      <c r="JM5"/>
+      <c r="JN5"/>
+      <c r="JO5"/>
+      <c r="JP5"/>
+      <c r="JQ5"/>
+      <c r="JR5"/>
+      <c r="JS5"/>
+      <c r="JT5"/>
+      <c r="JU5"/>
+      <c r="JV5"/>
+      <c r="JW5"/>
+      <c r="JX5"/>
+      <c r="JY5"/>
+      <c r="JZ5"/>
+      <c r="KA5"/>
+      <c r="KB5"/>
+      <c r="KC5"/>
+      <c r="KD5"/>
+      <c r="KE5"/>
+      <c r="KF5"/>
+      <c r="KG5"/>
+      <c r="KH5"/>
+      <c r="KI5"/>
+      <c r="KJ5"/>
+      <c r="KK5"/>
+      <c r="KL5"/>
+      <c r="KM5"/>
+      <c r="KN5"/>
+      <c r="KO5"/>
+      <c r="KP5"/>
+      <c r="KQ5"/>
+      <c r="KR5"/>
+      <c r="KS5"/>
+      <c r="KT5"/>
+      <c r="KU5"/>
+      <c r="KV5"/>
+      <c r="KW5"/>
+      <c r="KX5"/>
+      <c r="KY5"/>
+      <c r="KZ5"/>
+      <c r="LA5"/>
+      <c r="LB5"/>
+      <c r="LC5"/>
+      <c r="LD5"/>
+      <c r="LE5"/>
+      <c r="LF5"/>
+      <c r="LG5"/>
+      <c r="LH5"/>
+      <c r="LI5"/>
+      <c r="LJ5"/>
+      <c r="LK5"/>
+      <c r="LL5"/>
+      <c r="LM5"/>
+      <c r="LN5"/>
+      <c r="LO5"/>
+      <c r="LP5"/>
+      <c r="LQ5"/>
+      <c r="LR5"/>
+      <c r="LS5"/>
+      <c r="LT5"/>
+      <c r="LU5"/>
+      <c r="LV5"/>
+      <c r="LW5"/>
+      <c r="LX5"/>
+      <c r="LY5"/>
+      <c r="LZ5"/>
+      <c r="MA5"/>
+      <c r="MB5"/>
+      <c r="MC5"/>
+      <c r="MD5"/>
+      <c r="ME5"/>
+      <c r="MF5"/>
+      <c r="MG5"/>
+      <c r="MH5"/>
+      <c r="MI5"/>
+      <c r="MJ5"/>
+      <c r="MK5"/>
+      <c r="ML5"/>
+      <c r="MM5"/>
+      <c r="MN5"/>
+      <c r="MO5"/>
+      <c r="MP5"/>
+      <c r="MQ5"/>
+      <c r="MR5"/>
+      <c r="MS5"/>
+      <c r="MT5"/>
+      <c r="MU5"/>
+      <c r="MV5"/>
+      <c r="MW5"/>
+      <c r="MX5"/>
+      <c r="MY5"/>
+      <c r="MZ5"/>
+      <c r="NA5"/>
+      <c r="NB5"/>
+      <c r="NC5"/>
+      <c r="ND5"/>
+      <c r="NE5"/>
+      <c r="NF5"/>
+      <c r="NG5"/>
+      <c r="NH5"/>
+      <c r="NI5"/>
+      <c r="NJ5"/>
+      <c r="NK5"/>
+      <c r="NL5"/>
+      <c r="NM5"/>
+      <c r="NN5"/>
+      <c r="NO5"/>
+      <c r="NP5"/>
+      <c r="NQ5"/>
+      <c r="NR5"/>
+      <c r="NS5"/>
+      <c r="NT5"/>
+      <c r="NU5"/>
+      <c r="NV5"/>
+      <c r="NW5"/>
+      <c r="NX5"/>
+      <c r="NY5"/>
+      <c r="NZ5"/>
+      <c r="OA5"/>
+      <c r="OB5"/>
+      <c r="OC5"/>
+      <c r="OD5"/>
+      <c r="OE5"/>
+      <c r="OF5"/>
+      <c r="OG5"/>
+      <c r="OH5"/>
+      <c r="OI5"/>
+      <c r="OJ5"/>
+      <c r="OK5"/>
+      <c r="OL5"/>
+      <c r="OM5"/>
+      <c r="ON5"/>
+      <c r="OO5"/>
+      <c r="OP5"/>
+      <c r="OQ5"/>
+      <c r="OR5"/>
+      <c r="OS5"/>
+      <c r="OT5"/>
+      <c r="OU5"/>
+      <c r="OV5"/>
+      <c r="OW5"/>
+      <c r="OX5"/>
+      <c r="OY5"/>
+      <c r="OZ5"/>
+      <c r="PA5"/>
+      <c r="PB5"/>
+      <c r="PC5"/>
+      <c r="PD5"/>
+      <c r="PE5"/>
+      <c r="PF5"/>
+      <c r="PG5"/>
+      <c r="PH5"/>
+      <c r="PI5"/>
+      <c r="PJ5"/>
+      <c r="PK5"/>
+      <c r="PL5"/>
+      <c r="PM5"/>
+      <c r="PN5"/>
+      <c r="PO5"/>
+      <c r="PP5"/>
+      <c r="PQ5"/>
+      <c r="PR5"/>
+      <c r="PS5"/>
+      <c r="PT5"/>
+      <c r="PU5"/>
+      <c r="PV5"/>
+      <c r="PW5"/>
+      <c r="PX5"/>
+      <c r="PY5"/>
+      <c r="PZ5"/>
+      <c r="QA5"/>
+      <c r="QB5"/>
+      <c r="QC5"/>
+      <c r="QD5"/>
+      <c r="QE5"/>
+      <c r="QF5"/>
+      <c r="QG5"/>
+      <c r="QH5"/>
+      <c r="QI5"/>
+      <c r="QJ5"/>
+      <c r="QK5"/>
+      <c r="QL5"/>
+      <c r="QM5"/>
+      <c r="QN5"/>
+      <c r="QO5"/>
+      <c r="QP5"/>
+      <c r="QQ5"/>
+      <c r="QR5"/>
+      <c r="QS5"/>
+      <c r="QT5"/>
+      <c r="QU5"/>
+      <c r="QV5"/>
+      <c r="QW5"/>
+      <c r="QX5"/>
+      <c r="QY5"/>
+      <c r="QZ5"/>
+      <c r="RA5"/>
+      <c r="RB5"/>
+      <c r="RC5"/>
+      <c r="RD5"/>
+      <c r="RE5"/>
+      <c r="RF5"/>
+      <c r="RG5"/>
+      <c r="RH5"/>
+      <c r="RI5"/>
+      <c r="RJ5"/>
+      <c r="RK5"/>
+      <c r="RL5"/>
+      <c r="RM5"/>
+      <c r="RN5"/>
+      <c r="RO5"/>
+      <c r="RP5"/>
+      <c r="RQ5"/>
+      <c r="RR5"/>
+      <c r="RS5"/>
+      <c r="RT5"/>
+      <c r="RU5"/>
+      <c r="RV5"/>
+      <c r="RW5"/>
+      <c r="RX5"/>
+      <c r="RY5"/>
+      <c r="RZ5"/>
+      <c r="SA5"/>
+      <c r="SB5"/>
+      <c r="SC5"/>
+      <c r="SD5"/>
+      <c r="SE5"/>
+      <c r="SF5"/>
+      <c r="SG5"/>
+      <c r="SH5"/>
+      <c r="SI5"/>
+      <c r="SJ5"/>
+      <c r="SK5"/>
+      <c r="SL5"/>
+      <c r="SM5"/>
+      <c r="SN5"/>
+      <c r="SO5"/>
+      <c r="SP5"/>
+      <c r="SQ5"/>
+      <c r="SR5"/>
+      <c r="SS5"/>
+      <c r="ST5"/>
+      <c r="SU5"/>
+      <c r="SV5"/>
+      <c r="SW5"/>
+      <c r="SX5"/>
+      <c r="SY5"/>
+      <c r="SZ5"/>
+      <c r="TA5"/>
+      <c r="TB5"/>
+      <c r="TC5"/>
+      <c r="TD5"/>
+      <c r="TE5"/>
+      <c r="TF5"/>
+      <c r="TG5"/>
+      <c r="TH5"/>
+      <c r="TI5"/>
+      <c r="TJ5"/>
+      <c r="TK5"/>
+      <c r="TL5"/>
+      <c r="TM5"/>
+      <c r="TN5"/>
+      <c r="TO5"/>
+      <c r="TP5"/>
+      <c r="TQ5"/>
+      <c r="TR5"/>
+      <c r="TS5"/>
+      <c r="TT5"/>
+      <c r="TU5"/>
+      <c r="TV5"/>
+      <c r="TW5"/>
+      <c r="TX5"/>
+      <c r="TY5"/>
+      <c r="TZ5"/>
+      <c r="UA5"/>
+      <c r="UB5"/>
+      <c r="UC5"/>
+      <c r="UD5"/>
+      <c r="UE5"/>
+      <c r="UF5"/>
+      <c r="UG5"/>
+      <c r="UH5"/>
+      <c r="UI5"/>
+      <c r="UJ5"/>
+      <c r="UK5"/>
+      <c r="UL5"/>
+      <c r="UM5"/>
+      <c r="UN5"/>
+      <c r="UO5"/>
+      <c r="UP5"/>
+      <c r="UQ5"/>
+      <c r="UR5"/>
+      <c r="US5"/>
+      <c r="UT5"/>
+      <c r="UU5"/>
+      <c r="UV5"/>
+      <c r="UW5"/>
+      <c r="UX5"/>
+      <c r="UY5"/>
+      <c r="UZ5"/>
+      <c r="VA5"/>
+      <c r="VB5"/>
+      <c r="VC5"/>
+      <c r="VD5"/>
+      <c r="VE5"/>
+      <c r="VF5"/>
+      <c r="VG5"/>
+      <c r="VH5"/>
+      <c r="VI5"/>
+      <c r="VJ5"/>
+      <c r="VK5"/>
+      <c r="VL5"/>
+      <c r="VM5"/>
+      <c r="VN5"/>
+      <c r="VO5"/>
+      <c r="VP5"/>
+      <c r="VQ5"/>
+      <c r="VR5"/>
+      <c r="VS5"/>
+      <c r="VT5"/>
+      <c r="VU5"/>
+      <c r="VV5"/>
+      <c r="VW5"/>
+      <c r="VX5"/>
+      <c r="VY5"/>
+      <c r="VZ5"/>
+      <c r="WA5"/>
+      <c r="WB5"/>
+      <c r="WC5"/>
+      <c r="WD5"/>
+      <c r="WE5"/>
+      <c r="WF5"/>
+      <c r="WG5"/>
+      <c r="WH5"/>
+      <c r="WI5"/>
+      <c r="WJ5"/>
+      <c r="WK5"/>
+      <c r="WL5"/>
+      <c r="WM5"/>
+      <c r="WN5"/>
+      <c r="WO5"/>
+      <c r="WP5"/>
+      <c r="WQ5"/>
+      <c r="WR5"/>
+      <c r="WS5"/>
+      <c r="WT5"/>
+      <c r="WU5"/>
+      <c r="WV5"/>
+      <c r="WW5"/>
+      <c r="WX5"/>
+      <c r="WY5"/>
+      <c r="WZ5"/>
+      <c r="XA5"/>
+      <c r="XB5"/>
+      <c r="XC5"/>
+      <c r="XD5"/>
+      <c r="XE5"/>
+      <c r="XF5"/>
+      <c r="XG5"/>
+      <c r="XH5"/>
+      <c r="XI5"/>
+      <c r="XJ5"/>
+      <c r="XK5"/>
+      <c r="XL5"/>
+      <c r="XM5"/>
+      <c r="XN5"/>
+      <c r="XO5"/>
+      <c r="XP5"/>
+      <c r="XQ5"/>
+      <c r="XR5"/>
+      <c r="XS5"/>
+      <c r="XT5"/>
+      <c r="XU5"/>
+      <c r="XV5"/>
+      <c r="XW5"/>
+      <c r="XX5"/>
+      <c r="XY5"/>
+      <c r="XZ5"/>
+      <c r="YA5"/>
+      <c r="YB5"/>
+      <c r="YC5"/>
+      <c r="YD5"/>
+      <c r="YE5"/>
+      <c r="YF5"/>
+      <c r="YG5"/>
+      <c r="YH5"/>
+      <c r="YI5"/>
+      <c r="YJ5"/>
+      <c r="YK5"/>
+      <c r="YL5"/>
+      <c r="YM5"/>
+      <c r="YN5"/>
+      <c r="YO5"/>
+      <c r="YP5"/>
+      <c r="YQ5"/>
+      <c r="YR5"/>
+      <c r="YS5"/>
+      <c r="YT5"/>
+      <c r="YU5"/>
+      <c r="YV5"/>
+      <c r="YW5"/>
+      <c r="YX5"/>
+      <c r="YY5"/>
+      <c r="YZ5"/>
+      <c r="ZA5"/>
+      <c r="ZB5"/>
+      <c r="ZC5"/>
+      <c r="ZD5"/>
+      <c r="ZE5"/>
+      <c r="ZF5"/>
+      <c r="ZG5"/>
+      <c r="ZH5"/>
+      <c r="ZI5"/>
+      <c r="ZJ5"/>
+      <c r="ZK5"/>
+      <c r="ZL5"/>
+      <c r="ZM5"/>
+      <c r="ZN5"/>
+      <c r="ZO5"/>
+      <c r="ZP5"/>
+      <c r="ZQ5"/>
+      <c r="ZR5"/>
+      <c r="ZS5"/>
+      <c r="ZT5"/>
+      <c r="ZU5"/>
+      <c r="ZV5"/>
+      <c r="ZW5"/>
+      <c r="ZX5"/>
+      <c r="ZY5"/>
+      <c r="ZZ5"/>
+      <c r="AAA5"/>
+      <c r="AAB5"/>
+      <c r="AAC5"/>
+      <c r="AAD5"/>
+      <c r="AAE5"/>
+      <c r="AAF5"/>
+      <c r="AAG5"/>
+      <c r="AAH5"/>
+      <c r="AAI5"/>
+      <c r="AAJ5"/>
+      <c r="AAK5"/>
+      <c r="AAL5"/>
+      <c r="AAM5"/>
+      <c r="AAN5"/>
+      <c r="AAO5"/>
+      <c r="AAP5"/>
+      <c r="AAQ5"/>
+      <c r="AAR5"/>
+      <c r="AAS5"/>
+      <c r="AAT5"/>
+      <c r="AAU5"/>
+      <c r="AAV5"/>
+      <c r="AAW5"/>
+      <c r="AAX5"/>
+      <c r="AAY5"/>
+      <c r="AAZ5"/>
+      <c r="ABA5"/>
+      <c r="ABB5"/>
+      <c r="ABC5"/>
+      <c r="ABD5"/>
+      <c r="ABE5"/>
+      <c r="ABF5"/>
+      <c r="ABG5"/>
+      <c r="ABH5"/>
+      <c r="ABI5"/>
+      <c r="ABJ5"/>
+      <c r="ABK5"/>
+      <c r="ABL5"/>
+      <c r="ABM5"/>
+      <c r="ABN5"/>
+      <c r="ABO5"/>
+      <c r="ABP5"/>
+      <c r="ABQ5"/>
+      <c r="ABR5"/>
+      <c r="ABS5"/>
+      <c r="ABT5"/>
+      <c r="ABU5"/>
+      <c r="ABV5"/>
+      <c r="ABW5"/>
+      <c r="ABX5"/>
+      <c r="ABY5"/>
+      <c r="ABZ5"/>
+      <c r="ACA5"/>
+      <c r="ACB5"/>
+      <c r="ACC5"/>
+      <c r="ACD5"/>
+      <c r="ACE5"/>
+      <c r="ACF5"/>
+      <c r="ACG5"/>
+      <c r="ACH5"/>
+      <c r="ACI5"/>
+      <c r="ACJ5"/>
+      <c r="ACK5"/>
+      <c r="ACL5"/>
+      <c r="ACM5"/>
+      <c r="ACN5"/>
+      <c r="ACO5"/>
+      <c r="ACP5"/>
+      <c r="ACQ5"/>
+      <c r="ACR5"/>
+      <c r="ACS5"/>
+      <c r="ACT5"/>
+      <c r="ACU5"/>
+      <c r="ACV5"/>
+      <c r="ACW5"/>
+      <c r="ACX5"/>
+      <c r="ACY5"/>
+      <c r="ACZ5"/>
+      <c r="ADA5"/>
+      <c r="ADB5"/>
+      <c r="ADC5"/>
+      <c r="ADD5"/>
+      <c r="ADE5"/>
+      <c r="ADF5"/>
+      <c r="ADG5"/>
+      <c r="ADH5"/>
+      <c r="ADI5"/>
+      <c r="ADJ5"/>
+      <c r="ADK5"/>
+      <c r="ADL5"/>
+      <c r="ADM5"/>
+      <c r="ADN5"/>
+      <c r="ADO5"/>
+      <c r="ADP5"/>
+      <c r="ADQ5"/>
+      <c r="ADR5"/>
+      <c r="ADS5"/>
+      <c r="ADT5"/>
+      <c r="ADU5"/>
+      <c r="ADV5"/>
+      <c r="ADW5"/>
+      <c r="ADX5"/>
+      <c r="ADY5"/>
+      <c r="ADZ5"/>
+      <c r="AEA5"/>
+      <c r="AEB5"/>
+      <c r="AEC5"/>
+      <c r="AED5"/>
+      <c r="AEE5"/>
+      <c r="AEF5"/>
+      <c r="AEG5"/>
+      <c r="AEH5"/>
+      <c r="AEI5"/>
+      <c r="AEJ5"/>
+      <c r="AEK5"/>
+      <c r="AEL5"/>
+      <c r="AEM5"/>
+      <c r="AEN5"/>
+      <c r="AEO5"/>
+      <c r="AEP5"/>
+      <c r="AEQ5"/>
+      <c r="AER5"/>
+      <c r="AES5"/>
+      <c r="AET5"/>
+      <c r="AEU5"/>
+      <c r="AEV5"/>
+      <c r="AEW5"/>
+      <c r="AEX5"/>
+      <c r="AEY5"/>
+      <c r="AEZ5"/>
+      <c r="AFA5"/>
+      <c r="AFB5"/>
+      <c r="AFC5"/>
+      <c r="AFD5"/>
+      <c r="AFE5"/>
+      <c r="AFF5"/>
+      <c r="AFG5"/>
+      <c r="AFH5"/>
+      <c r="AFI5"/>
+      <c r="AFJ5"/>
+      <c r="AFK5"/>
+      <c r="AFL5"/>
+      <c r="AFM5"/>
+      <c r="AFN5"/>
+      <c r="AFO5"/>
+      <c r="AFP5"/>
+      <c r="AFQ5"/>
+      <c r="AFR5"/>
+      <c r="AFS5"/>
+      <c r="AFT5"/>
+      <c r="AFU5"/>
+      <c r="AFV5"/>
+      <c r="AFW5"/>
+      <c r="AFX5"/>
+      <c r="AFY5"/>
+      <c r="AFZ5"/>
+      <c r="AGA5"/>
+      <c r="AGB5"/>
+      <c r="AGC5"/>
+      <c r="AGD5"/>
+      <c r="AGE5"/>
+      <c r="AGF5"/>
+      <c r="AGG5"/>
+      <c r="AGH5"/>
+      <c r="AGI5"/>
+      <c r="AGJ5"/>
+      <c r="AGK5"/>
+      <c r="AGL5"/>
+      <c r="AGM5"/>
+      <c r="AGN5"/>
+      <c r="AGO5"/>
+      <c r="AGP5"/>
+      <c r="AGQ5"/>
+      <c r="AGR5"/>
+      <c r="AGS5"/>
+      <c r="AGT5"/>
+      <c r="AGU5"/>
+      <c r="AGV5"/>
+      <c r="AGW5"/>
+      <c r="AGX5"/>
+      <c r="AGY5"/>
+      <c r="AGZ5"/>
+      <c r="AHA5"/>
+      <c r="AHB5"/>
+      <c r="AHC5"/>
+      <c r="AHD5"/>
+      <c r="AHE5"/>
+      <c r="AHF5"/>
+      <c r="AHG5"/>
+      <c r="AHH5"/>
+      <c r="AHI5"/>
+      <c r="AHJ5"/>
+      <c r="AHK5"/>
+      <c r="AHL5"/>
+      <c r="AHM5"/>
+      <c r="AHN5"/>
+      <c r="AHO5"/>
+      <c r="AHP5"/>
+      <c r="AHQ5"/>
+      <c r="AHR5"/>
+      <c r="AHS5"/>
+      <c r="AHT5"/>
+      <c r="AHU5"/>
+      <c r="AHV5"/>
+      <c r="AHW5"/>
+      <c r="AHX5"/>
+      <c r="AHY5"/>
+      <c r="AHZ5"/>
+      <c r="AIA5"/>
+      <c r="AIB5"/>
+      <c r="AIC5"/>
+      <c r="AID5"/>
+      <c r="AIE5"/>
+      <c r="AIF5"/>
+      <c r="AIG5"/>
+      <c r="AIH5"/>
+      <c r="AII5"/>
+      <c r="AIJ5"/>
+      <c r="AIK5"/>
+      <c r="AIL5"/>
+      <c r="AIM5"/>
+      <c r="AIN5"/>
+      <c r="AIO5"/>
+      <c r="AIP5"/>
+      <c r="AIQ5"/>
+      <c r="AIR5"/>
+      <c r="AIS5"/>
+      <c r="AIT5"/>
+      <c r="AIU5"/>
+      <c r="AIV5"/>
+      <c r="AIW5"/>
+      <c r="AIX5"/>
+      <c r="AIY5"/>
+      <c r="AIZ5"/>
+      <c r="AJA5"/>
+      <c r="AJB5"/>
+      <c r="AJC5"/>
+      <c r="AJD5"/>
+      <c r="AJE5"/>
+      <c r="AJF5"/>
+      <c r="AJG5"/>
+      <c r="AJH5"/>
+      <c r="AJI5"/>
+      <c r="AJJ5"/>
+      <c r="AJK5"/>
+      <c r="AJL5"/>
+      <c r="AJM5"/>
+      <c r="AJN5"/>
+      <c r="AJO5"/>
+      <c r="AJP5"/>
+      <c r="AJQ5"/>
+      <c r="AJR5"/>
+      <c r="AJS5"/>
+      <c r="AJT5"/>
+      <c r="AJU5"/>
+      <c r="AJV5"/>
+      <c r="AJW5"/>
+      <c r="AJX5"/>
+      <c r="AJY5"/>
+      <c r="AJZ5"/>
+      <c r="AKA5"/>
+      <c r="AKB5"/>
+      <c r="AKC5"/>
+      <c r="AKD5"/>
+      <c r="AKE5"/>
+      <c r="AKF5"/>
+      <c r="AKG5"/>
+      <c r="AKH5"/>
+      <c r="AKI5"/>
+      <c r="AKJ5"/>
+      <c r="AKK5"/>
+      <c r="AKL5"/>
+      <c r="AKM5"/>
+      <c r="AKN5"/>
+      <c r="AKO5"/>
+      <c r="AKP5"/>
+      <c r="AKQ5"/>
+      <c r="AKR5"/>
+      <c r="AKS5"/>
+      <c r="AKT5"/>
+      <c r="AKU5"/>
+      <c r="AKV5"/>
+      <c r="AKW5"/>
+      <c r="AKX5"/>
+      <c r="AKY5"/>
+      <c r="AKZ5"/>
+      <c r="ALA5"/>
+      <c r="ALB5"/>
+      <c r="ALC5"/>
+      <c r="ALD5"/>
+      <c r="ALE5"/>
+      <c r="ALF5"/>
+      <c r="ALG5"/>
+      <c r="ALH5"/>
+      <c r="ALI5"/>
+      <c r="ALJ5"/>
+      <c r="ALK5"/>
+      <c r="ALL5"/>
+      <c r="ALM5"/>
+      <c r="ALN5"/>
+      <c r="ALO5"/>
+      <c r="ALP5"/>
+      <c r="ALQ5"/>
+      <c r="ALR5"/>
+      <c r="ALS5"/>
+      <c r="ALT5"/>
+      <c r="ALU5"/>
+      <c r="ALV5"/>
+      <c r="ALW5"/>
+      <c r="ALX5"/>
+      <c r="ALY5"/>
+      <c r="ALZ5"/>
+      <c r="AMA5"/>
+      <c r="AMB5"/>
+      <c r="AMC5"/>
+      <c r="AMD5"/>
+      <c r="AME5"/>
+      <c r="AMF5"/>
+      <c r="AMG5"/>
+      <c r="AMH5"/>
+      <c r="AMI5"/>
+      <c r="AMJ5"/>
+      <c r="AMK5"/>
+      <c r="AML5"/>
+      <c r="AMM5"/>
+      <c r="AMN5"/>
+      <c r="AMO5"/>
     </row>
     <row r="6" spans="1:1029" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>130</v>
+        <v>106</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>131</v>
+        <v>107</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>132</v>
+        <v>108</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>4</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>85</v>
+        <v>398</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>133</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7" spans="1:1029" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="C7" s="3" t="s">
         <v>100</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>101</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>4</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>85</v>
+        <v>398</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
-    <row r="8" spans="1:1029" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:1029" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>4</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>85</v>
+        <v>398</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>106</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="G8"/>
+      <c r="H8"/>
+      <c r="I8"/>
+      <c r="J8"/>
+      <c r="K8"/>
+      <c r="L8"/>
+      <c r="M8"/>
+      <c r="N8"/>
+      <c r="O8"/>
+      <c r="P8"/>
+      <c r="Q8"/>
+      <c r="R8"/>
+      <c r="S8"/>
+      <c r="T8"/>
+      <c r="U8"/>
+      <c r="V8"/>
+      <c r="W8"/>
+      <c r="X8"/>
+      <c r="Y8"/>
+      <c r="Z8"/>
+      <c r="AA8"/>
+      <c r="AB8"/>
+      <c r="AC8"/>
+      <c r="AD8"/>
+      <c r="AE8"/>
+      <c r="AF8"/>
+      <c r="AG8"/>
+      <c r="AH8"/>
+      <c r="AI8"/>
+      <c r="AJ8"/>
+      <c r="AK8"/>
+      <c r="AL8"/>
+      <c r="AM8"/>
+      <c r="AN8"/>
+      <c r="AO8"/>
+      <c r="AP8"/>
+      <c r="AQ8"/>
+      <c r="AR8"/>
+      <c r="AS8"/>
+      <c r="AT8"/>
+      <c r="AU8"/>
+      <c r="AV8"/>
+      <c r="AW8"/>
+      <c r="AX8"/>
+      <c r="AY8"/>
+      <c r="AZ8"/>
+      <c r="BA8"/>
+      <c r="BB8"/>
+      <c r="BC8"/>
+      <c r="BD8"/>
+      <c r="BE8"/>
+      <c r="BF8"/>
+      <c r="BG8"/>
+      <c r="BH8"/>
+      <c r="BI8"/>
+      <c r="BJ8"/>
+      <c r="BK8"/>
+      <c r="BL8"/>
+      <c r="BM8"/>
+      <c r="BN8"/>
+      <c r="BO8"/>
+      <c r="BP8"/>
+      <c r="BQ8"/>
+      <c r="BR8"/>
+      <c r="BS8"/>
+      <c r="BT8"/>
+      <c r="BU8"/>
+      <c r="BV8"/>
+      <c r="BW8"/>
+      <c r="BX8"/>
+      <c r="BY8"/>
+      <c r="BZ8"/>
+      <c r="CA8"/>
+      <c r="CB8"/>
+      <c r="CC8"/>
+      <c r="CD8"/>
+      <c r="CE8"/>
+      <c r="CF8"/>
+      <c r="CG8"/>
+      <c r="CH8"/>
+      <c r="CI8"/>
+      <c r="CJ8"/>
+      <c r="CK8"/>
+      <c r="CL8"/>
+      <c r="CM8"/>
+      <c r="CN8"/>
+      <c r="CO8"/>
+      <c r="CP8"/>
+      <c r="CQ8"/>
+      <c r="CR8"/>
+      <c r="CS8"/>
+      <c r="CT8"/>
+      <c r="CU8"/>
+      <c r="CV8"/>
+      <c r="CW8"/>
+      <c r="CX8"/>
+      <c r="CY8"/>
+      <c r="CZ8"/>
+      <c r="DA8"/>
+      <c r="DB8"/>
+      <c r="DC8"/>
+      <c r="DD8"/>
+      <c r="DE8"/>
+      <c r="DF8"/>
+      <c r="DG8"/>
+      <c r="DH8"/>
+      <c r="DI8"/>
+      <c r="DJ8"/>
+      <c r="DK8"/>
+      <c r="DL8"/>
+      <c r="DM8"/>
+      <c r="DN8"/>
+      <c r="DO8"/>
+      <c r="DP8"/>
+      <c r="DQ8"/>
+      <c r="DR8"/>
+      <c r="DS8"/>
+      <c r="DT8"/>
+      <c r="DU8"/>
+      <c r="DV8"/>
+      <c r="DW8"/>
+      <c r="DX8"/>
+      <c r="DY8"/>
+      <c r="DZ8"/>
+      <c r="EA8"/>
+      <c r="EB8"/>
+      <c r="EC8"/>
+      <c r="ED8"/>
+      <c r="EE8"/>
+      <c r="EF8"/>
+      <c r="EG8"/>
+      <c r="EH8"/>
+      <c r="EI8"/>
+      <c r="EJ8"/>
+      <c r="EK8"/>
+      <c r="EL8"/>
+      <c r="EM8"/>
+      <c r="EN8"/>
+      <c r="EO8"/>
+      <c r="EP8"/>
+      <c r="EQ8"/>
+      <c r="ER8"/>
+      <c r="ES8"/>
+      <c r="ET8"/>
+      <c r="EU8"/>
+      <c r="EV8"/>
+      <c r="EW8"/>
+      <c r="EX8"/>
+      <c r="EY8"/>
+      <c r="EZ8"/>
+      <c r="FA8"/>
+      <c r="FB8"/>
+      <c r="FC8"/>
+      <c r="FD8"/>
+      <c r="FE8"/>
+      <c r="FF8"/>
+      <c r="FG8"/>
+      <c r="FH8"/>
+      <c r="FI8"/>
+      <c r="FJ8"/>
+      <c r="FK8"/>
+      <c r="FL8"/>
+      <c r="FM8"/>
+      <c r="FN8"/>
+      <c r="FO8"/>
+      <c r="FP8"/>
+      <c r="FQ8"/>
+      <c r="FR8"/>
+      <c r="FS8"/>
+      <c r="FT8"/>
+      <c r="FU8"/>
+      <c r="FV8"/>
+      <c r="FW8"/>
+      <c r="FX8"/>
+      <c r="FY8"/>
+      <c r="FZ8"/>
+      <c r="GA8"/>
+      <c r="GB8"/>
+      <c r="GC8"/>
+      <c r="GD8"/>
+      <c r="GE8"/>
+      <c r="GF8"/>
+      <c r="GG8"/>
+      <c r="GH8"/>
+      <c r="GI8"/>
+      <c r="GJ8"/>
+      <c r="GK8"/>
+      <c r="GL8"/>
+      <c r="GM8"/>
+      <c r="GN8"/>
+      <c r="GO8"/>
+      <c r="GP8"/>
+      <c r="GQ8"/>
+      <c r="GR8"/>
+      <c r="GS8"/>
+      <c r="GT8"/>
+      <c r="GU8"/>
+      <c r="GV8"/>
+      <c r="GW8"/>
+      <c r="GX8"/>
+      <c r="GY8"/>
+      <c r="GZ8"/>
+      <c r="HA8"/>
+      <c r="HB8"/>
+      <c r="HC8"/>
+      <c r="HD8"/>
+      <c r="HE8"/>
+      <c r="HF8"/>
+      <c r="HG8"/>
+      <c r="HH8"/>
+      <c r="HI8"/>
+      <c r="HJ8"/>
+      <c r="HK8"/>
+      <c r="HL8"/>
+      <c r="HM8"/>
+      <c r="HN8"/>
+      <c r="HO8"/>
+      <c r="HP8"/>
+      <c r="HQ8"/>
+      <c r="HR8"/>
+      <c r="HS8"/>
+      <c r="HT8"/>
+      <c r="HU8"/>
+      <c r="HV8"/>
+      <c r="HW8"/>
+      <c r="HX8"/>
+      <c r="HY8"/>
+      <c r="HZ8"/>
+      <c r="IA8"/>
+      <c r="IB8"/>
+      <c r="IC8"/>
+      <c r="ID8"/>
+      <c r="IE8"/>
+      <c r="IF8"/>
+      <c r="IG8"/>
+      <c r="IH8"/>
+      <c r="II8"/>
+      <c r="IJ8"/>
+      <c r="IK8"/>
+      <c r="IL8"/>
+      <c r="IM8"/>
+      <c r="IN8"/>
+      <c r="IO8"/>
+      <c r="IP8"/>
+      <c r="IQ8"/>
+      <c r="IR8"/>
+      <c r="IS8"/>
+      <c r="IT8"/>
+      <c r="IU8"/>
+      <c r="IV8"/>
+      <c r="IW8"/>
+      <c r="IX8"/>
+      <c r="IY8"/>
+      <c r="IZ8"/>
+      <c r="JA8"/>
+      <c r="JB8"/>
+      <c r="JC8"/>
+      <c r="JD8"/>
+      <c r="JE8"/>
+      <c r="JF8"/>
+      <c r="JG8"/>
+      <c r="JH8"/>
+      <c r="JI8"/>
+      <c r="JJ8"/>
+      <c r="JK8"/>
+      <c r="JL8"/>
+      <c r="JM8"/>
+      <c r="JN8"/>
+      <c r="JO8"/>
+      <c r="JP8"/>
+      <c r="JQ8"/>
+      <c r="JR8"/>
+      <c r="JS8"/>
+      <c r="JT8"/>
+      <c r="JU8"/>
+      <c r="JV8"/>
+      <c r="JW8"/>
+      <c r="JX8"/>
+      <c r="JY8"/>
+      <c r="JZ8"/>
+      <c r="KA8"/>
+      <c r="KB8"/>
+      <c r="KC8"/>
+      <c r="KD8"/>
+      <c r="KE8"/>
+      <c r="KF8"/>
+      <c r="KG8"/>
+      <c r="KH8"/>
+      <c r="KI8"/>
+      <c r="KJ8"/>
+      <c r="KK8"/>
+      <c r="KL8"/>
+      <c r="KM8"/>
+      <c r="KN8"/>
+      <c r="KO8"/>
+      <c r="KP8"/>
+      <c r="KQ8"/>
+      <c r="KR8"/>
+      <c r="KS8"/>
+      <c r="KT8"/>
+      <c r="KU8"/>
+      <c r="KV8"/>
+      <c r="KW8"/>
+      <c r="KX8"/>
+      <c r="KY8"/>
+      <c r="KZ8"/>
+      <c r="LA8"/>
+      <c r="LB8"/>
+      <c r="LC8"/>
+      <c r="LD8"/>
+      <c r="LE8"/>
+      <c r="LF8"/>
+      <c r="LG8"/>
+      <c r="LH8"/>
+      <c r="LI8"/>
+      <c r="LJ8"/>
+      <c r="LK8"/>
+      <c r="LL8"/>
+      <c r="LM8"/>
+      <c r="LN8"/>
+      <c r="LO8"/>
+      <c r="LP8"/>
+      <c r="LQ8"/>
+      <c r="LR8"/>
+      <c r="LS8"/>
+      <c r="LT8"/>
+      <c r="LU8"/>
+      <c r="LV8"/>
+      <c r="LW8"/>
+      <c r="LX8"/>
+      <c r="LY8"/>
+      <c r="LZ8"/>
+      <c r="MA8"/>
+      <c r="MB8"/>
+      <c r="MC8"/>
+      <c r="MD8"/>
+      <c r="ME8"/>
+      <c r="MF8"/>
+      <c r="MG8"/>
+      <c r="MH8"/>
+      <c r="MI8"/>
+      <c r="MJ8"/>
+      <c r="MK8"/>
+      <c r="ML8"/>
+      <c r="MM8"/>
+      <c r="MN8"/>
+      <c r="MO8"/>
+      <c r="MP8"/>
+      <c r="MQ8"/>
+      <c r="MR8"/>
+      <c r="MS8"/>
+      <c r="MT8"/>
+      <c r="MU8"/>
+      <c r="MV8"/>
+      <c r="MW8"/>
+      <c r="MX8"/>
+      <c r="MY8"/>
+      <c r="MZ8"/>
+      <c r="NA8"/>
+      <c r="NB8"/>
+      <c r="NC8"/>
+      <c r="ND8"/>
+      <c r="NE8"/>
+      <c r="NF8"/>
+      <c r="NG8"/>
+      <c r="NH8"/>
+      <c r="NI8"/>
+      <c r="NJ8"/>
+      <c r="NK8"/>
+      <c r="NL8"/>
+      <c r="NM8"/>
+      <c r="NN8"/>
+      <c r="NO8"/>
+      <c r="NP8"/>
+      <c r="NQ8"/>
+      <c r="NR8"/>
+      <c r="NS8"/>
+      <c r="NT8"/>
+      <c r="NU8"/>
+      <c r="NV8"/>
+      <c r="NW8"/>
+      <c r="NX8"/>
+      <c r="NY8"/>
+      <c r="NZ8"/>
+      <c r="OA8"/>
+      <c r="OB8"/>
+      <c r="OC8"/>
+      <c r="OD8"/>
+      <c r="OE8"/>
+      <c r="OF8"/>
+      <c r="OG8"/>
+      <c r="OH8"/>
+      <c r="OI8"/>
+      <c r="OJ8"/>
+      <c r="OK8"/>
+      <c r="OL8"/>
+      <c r="OM8"/>
+      <c r="ON8"/>
+      <c r="OO8"/>
+      <c r="OP8"/>
+      <c r="OQ8"/>
+      <c r="OR8"/>
+      <c r="OS8"/>
+      <c r="OT8"/>
+      <c r="OU8"/>
+      <c r="OV8"/>
+      <c r="OW8"/>
+      <c r="OX8"/>
+      <c r="OY8"/>
+      <c r="OZ8"/>
+      <c r="PA8"/>
+      <c r="PB8"/>
+      <c r="PC8"/>
+      <c r="PD8"/>
+      <c r="PE8"/>
+      <c r="PF8"/>
+      <c r="PG8"/>
+      <c r="PH8"/>
+      <c r="PI8"/>
+      <c r="PJ8"/>
+      <c r="PK8"/>
+      <c r="PL8"/>
+      <c r="PM8"/>
+      <c r="PN8"/>
+      <c r="PO8"/>
+      <c r="PP8"/>
+      <c r="PQ8"/>
+      <c r="PR8"/>
+      <c r="PS8"/>
+      <c r="PT8"/>
+      <c r="PU8"/>
+      <c r="PV8"/>
+      <c r="PW8"/>
+      <c r="PX8"/>
+      <c r="PY8"/>
+      <c r="PZ8"/>
+      <c r="QA8"/>
+      <c r="QB8"/>
+      <c r="QC8"/>
+      <c r="QD8"/>
+      <c r="QE8"/>
+      <c r="QF8"/>
+      <c r="QG8"/>
+      <c r="QH8"/>
+      <c r="QI8"/>
+      <c r="QJ8"/>
+      <c r="QK8"/>
+      <c r="QL8"/>
+      <c r="QM8"/>
+      <c r="QN8"/>
+      <c r="QO8"/>
+      <c r="QP8"/>
+      <c r="QQ8"/>
+      <c r="QR8"/>
+      <c r="QS8"/>
+      <c r="QT8"/>
+      <c r="QU8"/>
+      <c r="QV8"/>
+      <c r="QW8"/>
+      <c r="QX8"/>
+      <c r="QY8"/>
+      <c r="QZ8"/>
+      <c r="RA8"/>
+      <c r="RB8"/>
+      <c r="RC8"/>
+      <c r="RD8"/>
+      <c r="RE8"/>
+      <c r="RF8"/>
+      <c r="RG8"/>
+      <c r="RH8"/>
+      <c r="RI8"/>
+      <c r="RJ8"/>
+      <c r="RK8"/>
+      <c r="RL8"/>
+      <c r="RM8"/>
+      <c r="RN8"/>
+      <c r="RO8"/>
+      <c r="RP8"/>
+      <c r="RQ8"/>
+      <c r="RR8"/>
+      <c r="RS8"/>
+      <c r="RT8"/>
+      <c r="RU8"/>
+      <c r="RV8"/>
+      <c r="RW8"/>
+      <c r="RX8"/>
+      <c r="RY8"/>
+      <c r="RZ8"/>
+      <c r="SA8"/>
+      <c r="SB8"/>
+      <c r="SC8"/>
+      <c r="SD8"/>
+      <c r="SE8"/>
+      <c r="SF8"/>
+      <c r="SG8"/>
+      <c r="SH8"/>
+      <c r="SI8"/>
+      <c r="SJ8"/>
+      <c r="SK8"/>
+      <c r="SL8"/>
+      <c r="SM8"/>
+      <c r="SN8"/>
+      <c r="SO8"/>
+      <c r="SP8"/>
+      <c r="SQ8"/>
+      <c r="SR8"/>
+      <c r="SS8"/>
+      <c r="ST8"/>
+      <c r="SU8"/>
+      <c r="SV8"/>
+      <c r="SW8"/>
+      <c r="SX8"/>
+      <c r="SY8"/>
+      <c r="SZ8"/>
+      <c r="TA8"/>
+      <c r="TB8"/>
+      <c r="TC8"/>
+      <c r="TD8"/>
+      <c r="TE8"/>
+      <c r="TF8"/>
+      <c r="TG8"/>
+      <c r="TH8"/>
+      <c r="TI8"/>
+      <c r="TJ8"/>
+      <c r="TK8"/>
+      <c r="TL8"/>
+      <c r="TM8"/>
+      <c r="TN8"/>
+      <c r="TO8"/>
+      <c r="TP8"/>
+      <c r="TQ8"/>
+      <c r="TR8"/>
+      <c r="TS8"/>
+      <c r="TT8"/>
+      <c r="TU8"/>
+      <c r="TV8"/>
+      <c r="TW8"/>
+      <c r="TX8"/>
+      <c r="TY8"/>
+      <c r="TZ8"/>
+      <c r="UA8"/>
+      <c r="UB8"/>
+      <c r="UC8"/>
+      <c r="UD8"/>
+      <c r="UE8"/>
+      <c r="UF8"/>
+      <c r="UG8"/>
+      <c r="UH8"/>
+      <c r="UI8"/>
+      <c r="UJ8"/>
+      <c r="UK8"/>
+      <c r="UL8"/>
+      <c r="UM8"/>
+      <c r="UN8"/>
+      <c r="UO8"/>
+      <c r="UP8"/>
+      <c r="UQ8"/>
+      <c r="UR8"/>
+      <c r="US8"/>
+      <c r="UT8"/>
+      <c r="UU8"/>
+      <c r="UV8"/>
+      <c r="UW8"/>
+      <c r="UX8"/>
+      <c r="UY8"/>
+      <c r="UZ8"/>
+      <c r="VA8"/>
+      <c r="VB8"/>
+      <c r="VC8"/>
+      <c r="VD8"/>
+      <c r="VE8"/>
+      <c r="VF8"/>
+      <c r="VG8"/>
+      <c r="VH8"/>
+      <c r="VI8"/>
+      <c r="VJ8"/>
+      <c r="VK8"/>
+      <c r="VL8"/>
+      <c r="VM8"/>
+      <c r="VN8"/>
+      <c r="VO8"/>
+      <c r="VP8"/>
+      <c r="VQ8"/>
+      <c r="VR8"/>
+      <c r="VS8"/>
+      <c r="VT8"/>
+      <c r="VU8"/>
+      <c r="VV8"/>
+      <c r="VW8"/>
+      <c r="VX8"/>
+      <c r="VY8"/>
+      <c r="VZ8"/>
+      <c r="WA8"/>
+      <c r="WB8"/>
+      <c r="WC8"/>
+      <c r="WD8"/>
+      <c r="WE8"/>
+      <c r="WF8"/>
+      <c r="WG8"/>
+      <c r="WH8"/>
+      <c r="WI8"/>
+      <c r="WJ8"/>
+      <c r="WK8"/>
+      <c r="WL8"/>
+      <c r="WM8"/>
+      <c r="WN8"/>
+      <c r="WO8"/>
+      <c r="WP8"/>
+      <c r="WQ8"/>
+      <c r="WR8"/>
+      <c r="WS8"/>
+      <c r="WT8"/>
+      <c r="WU8"/>
+      <c r="WV8"/>
+      <c r="WW8"/>
+      <c r="WX8"/>
+      <c r="WY8"/>
+      <c r="WZ8"/>
+      <c r="XA8"/>
+      <c r="XB8"/>
+      <c r="XC8"/>
+      <c r="XD8"/>
+      <c r="XE8"/>
+      <c r="XF8"/>
+      <c r="XG8"/>
+      <c r="XH8"/>
+      <c r="XI8"/>
+      <c r="XJ8"/>
+      <c r="XK8"/>
+      <c r="XL8"/>
+      <c r="XM8"/>
+      <c r="XN8"/>
+      <c r="XO8"/>
+      <c r="XP8"/>
+      <c r="XQ8"/>
+      <c r="XR8"/>
+      <c r="XS8"/>
+      <c r="XT8"/>
+      <c r="XU8"/>
+      <c r="XV8"/>
+      <c r="XW8"/>
+      <c r="XX8"/>
+      <c r="XY8"/>
+      <c r="XZ8"/>
+      <c r="YA8"/>
+      <c r="YB8"/>
+      <c r="YC8"/>
+      <c r="YD8"/>
+      <c r="YE8"/>
+      <c r="YF8"/>
+      <c r="YG8"/>
+      <c r="YH8"/>
+      <c r="YI8"/>
+      <c r="YJ8"/>
+      <c r="YK8"/>
+      <c r="YL8"/>
+      <c r="YM8"/>
+      <c r="YN8"/>
+      <c r="YO8"/>
+      <c r="YP8"/>
+      <c r="YQ8"/>
+      <c r="YR8"/>
+      <c r="YS8"/>
+      <c r="YT8"/>
+      <c r="YU8"/>
+      <c r="YV8"/>
+      <c r="YW8"/>
+      <c r="YX8"/>
+      <c r="YY8"/>
+      <c r="YZ8"/>
+      <c r="ZA8"/>
+      <c r="ZB8"/>
+      <c r="ZC8"/>
+      <c r="ZD8"/>
+      <c r="ZE8"/>
+      <c r="ZF8"/>
+      <c r="ZG8"/>
+      <c r="ZH8"/>
+      <c r="ZI8"/>
+      <c r="ZJ8"/>
+      <c r="ZK8"/>
+      <c r="ZL8"/>
+      <c r="ZM8"/>
+      <c r="ZN8"/>
+      <c r="ZO8"/>
+      <c r="ZP8"/>
+      <c r="ZQ8"/>
+      <c r="ZR8"/>
+      <c r="ZS8"/>
+      <c r="ZT8"/>
+      <c r="ZU8"/>
+      <c r="ZV8"/>
+      <c r="ZW8"/>
+      <c r="ZX8"/>
+      <c r="ZY8"/>
+      <c r="ZZ8"/>
+      <c r="AAA8"/>
+      <c r="AAB8"/>
+      <c r="AAC8"/>
+      <c r="AAD8"/>
+      <c r="AAE8"/>
+      <c r="AAF8"/>
+      <c r="AAG8"/>
+      <c r="AAH8"/>
+      <c r="AAI8"/>
+      <c r="AAJ8"/>
+      <c r="AAK8"/>
+      <c r="AAL8"/>
+      <c r="AAM8"/>
+      <c r="AAN8"/>
+      <c r="AAO8"/>
+      <c r="AAP8"/>
+      <c r="AAQ8"/>
+      <c r="AAR8"/>
+      <c r="AAS8"/>
+      <c r="AAT8"/>
+      <c r="AAU8"/>
+      <c r="AAV8"/>
+      <c r="AAW8"/>
+      <c r="AAX8"/>
+      <c r="AAY8"/>
+      <c r="AAZ8"/>
+      <c r="ABA8"/>
+      <c r="ABB8"/>
+      <c r="ABC8"/>
+      <c r="ABD8"/>
+      <c r="ABE8"/>
+      <c r="ABF8"/>
+      <c r="ABG8"/>
+      <c r="ABH8"/>
+      <c r="ABI8"/>
+      <c r="ABJ8"/>
+      <c r="ABK8"/>
+      <c r="ABL8"/>
+      <c r="ABM8"/>
+      <c r="ABN8"/>
+      <c r="ABO8"/>
+      <c r="ABP8"/>
+      <c r="ABQ8"/>
+      <c r="ABR8"/>
+      <c r="ABS8"/>
+      <c r="ABT8"/>
+      <c r="ABU8"/>
+      <c r="ABV8"/>
+      <c r="ABW8"/>
+      <c r="ABX8"/>
+      <c r="ABY8"/>
+      <c r="ABZ8"/>
+      <c r="ACA8"/>
+      <c r="ACB8"/>
+      <c r="ACC8"/>
+      <c r="ACD8"/>
+      <c r="ACE8"/>
+      <c r="ACF8"/>
+      <c r="ACG8"/>
+      <c r="ACH8"/>
+      <c r="ACI8"/>
+      <c r="ACJ8"/>
+      <c r="ACK8"/>
+      <c r="ACL8"/>
+      <c r="ACM8"/>
+      <c r="ACN8"/>
+      <c r="ACO8"/>
+      <c r="ACP8"/>
+      <c r="ACQ8"/>
+      <c r="ACR8"/>
+      <c r="ACS8"/>
+      <c r="ACT8"/>
+      <c r="ACU8"/>
+      <c r="ACV8"/>
+      <c r="ACW8"/>
+      <c r="ACX8"/>
+      <c r="ACY8"/>
+      <c r="ACZ8"/>
+      <c r="ADA8"/>
+      <c r="ADB8"/>
+      <c r="ADC8"/>
+      <c r="ADD8"/>
+      <c r="ADE8"/>
+      <c r="ADF8"/>
+      <c r="ADG8"/>
+      <c r="ADH8"/>
+      <c r="ADI8"/>
+      <c r="ADJ8"/>
+      <c r="ADK8"/>
+      <c r="ADL8"/>
+      <c r="ADM8"/>
+      <c r="ADN8"/>
+      <c r="ADO8"/>
+      <c r="ADP8"/>
+      <c r="ADQ8"/>
+      <c r="ADR8"/>
+      <c r="ADS8"/>
+      <c r="ADT8"/>
+      <c r="ADU8"/>
+      <c r="ADV8"/>
+      <c r="ADW8"/>
+      <c r="ADX8"/>
+      <c r="ADY8"/>
+      <c r="ADZ8"/>
+      <c r="AEA8"/>
+      <c r="AEB8"/>
+      <c r="AEC8"/>
+      <c r="AED8"/>
+      <c r="AEE8"/>
+      <c r="AEF8"/>
+      <c r="AEG8"/>
+      <c r="AEH8"/>
+      <c r="AEI8"/>
+      <c r="AEJ8"/>
+      <c r="AEK8"/>
+      <c r="AEL8"/>
+      <c r="AEM8"/>
+      <c r="AEN8"/>
+      <c r="AEO8"/>
+      <c r="AEP8"/>
+      <c r="AEQ8"/>
+      <c r="AER8"/>
+      <c r="AES8"/>
+      <c r="AET8"/>
+      <c r="AEU8"/>
+      <c r="AEV8"/>
+      <c r="AEW8"/>
+      <c r="AEX8"/>
+      <c r="AEY8"/>
+      <c r="AEZ8"/>
+      <c r="AFA8"/>
+      <c r="AFB8"/>
+      <c r="AFC8"/>
+      <c r="AFD8"/>
+      <c r="AFE8"/>
+      <c r="AFF8"/>
+      <c r="AFG8"/>
+      <c r="AFH8"/>
+      <c r="AFI8"/>
+      <c r="AFJ8"/>
+      <c r="AFK8"/>
+      <c r="AFL8"/>
+      <c r="AFM8"/>
+      <c r="AFN8"/>
+      <c r="AFO8"/>
+      <c r="AFP8"/>
+      <c r="AFQ8"/>
+      <c r="AFR8"/>
+      <c r="AFS8"/>
+      <c r="AFT8"/>
+      <c r="AFU8"/>
+      <c r="AFV8"/>
+      <c r="AFW8"/>
+      <c r="AFX8"/>
+      <c r="AFY8"/>
+      <c r="AFZ8"/>
+      <c r="AGA8"/>
+      <c r="AGB8"/>
+      <c r="AGC8"/>
+      <c r="AGD8"/>
+      <c r="AGE8"/>
+      <c r="AGF8"/>
+      <c r="AGG8"/>
+      <c r="AGH8"/>
+      <c r="AGI8"/>
+      <c r="AGJ8"/>
+      <c r="AGK8"/>
+      <c r="AGL8"/>
+      <c r="AGM8"/>
+      <c r="AGN8"/>
+      <c r="AGO8"/>
+      <c r="AGP8"/>
+      <c r="AGQ8"/>
+      <c r="AGR8"/>
+      <c r="AGS8"/>
+      <c r="AGT8"/>
+      <c r="AGU8"/>
+      <c r="AGV8"/>
+      <c r="AGW8"/>
+      <c r="AGX8"/>
+      <c r="AGY8"/>
+      <c r="AGZ8"/>
+      <c r="AHA8"/>
+      <c r="AHB8"/>
+      <c r="AHC8"/>
+      <c r="AHD8"/>
+      <c r="AHE8"/>
+      <c r="AHF8"/>
+      <c r="AHG8"/>
+      <c r="AHH8"/>
+      <c r="AHI8"/>
+      <c r="AHJ8"/>
+      <c r="AHK8"/>
+      <c r="AHL8"/>
+      <c r="AHM8"/>
+      <c r="AHN8"/>
+      <c r="AHO8"/>
+      <c r="AHP8"/>
+      <c r="AHQ8"/>
+      <c r="AHR8"/>
+      <c r="AHS8"/>
+      <c r="AHT8"/>
+      <c r="AHU8"/>
+      <c r="AHV8"/>
+      <c r="AHW8"/>
+      <c r="AHX8"/>
+      <c r="AHY8"/>
+      <c r="AHZ8"/>
+      <c r="AIA8"/>
+      <c r="AIB8"/>
+      <c r="AIC8"/>
+      <c r="AID8"/>
+      <c r="AIE8"/>
+      <c r="AIF8"/>
+      <c r="AIG8"/>
+      <c r="AIH8"/>
+      <c r="AII8"/>
+      <c r="AIJ8"/>
+      <c r="AIK8"/>
+      <c r="AIL8"/>
+      <c r="AIM8"/>
+      <c r="AIN8"/>
+      <c r="AIO8"/>
+      <c r="AIP8"/>
+      <c r="AIQ8"/>
+      <c r="AIR8"/>
+      <c r="AIS8"/>
+      <c r="AIT8"/>
+      <c r="AIU8"/>
+      <c r="AIV8"/>
+      <c r="AIW8"/>
+      <c r="AIX8"/>
+      <c r="AIY8"/>
+      <c r="AIZ8"/>
+      <c r="AJA8"/>
+      <c r="AJB8"/>
+      <c r="AJC8"/>
+      <c r="AJD8"/>
+      <c r="AJE8"/>
+      <c r="AJF8"/>
+      <c r="AJG8"/>
+      <c r="AJH8"/>
+      <c r="AJI8"/>
+      <c r="AJJ8"/>
+      <c r="AJK8"/>
+      <c r="AJL8"/>
+      <c r="AJM8"/>
+      <c r="AJN8"/>
+      <c r="AJO8"/>
+      <c r="AJP8"/>
+      <c r="AJQ8"/>
+      <c r="AJR8"/>
+      <c r="AJS8"/>
+      <c r="AJT8"/>
+      <c r="AJU8"/>
+      <c r="AJV8"/>
+      <c r="AJW8"/>
+      <c r="AJX8"/>
+      <c r="AJY8"/>
+      <c r="AJZ8"/>
+      <c r="AKA8"/>
+      <c r="AKB8"/>
+      <c r="AKC8"/>
+      <c r="AKD8"/>
+      <c r="AKE8"/>
+      <c r="AKF8"/>
+      <c r="AKG8"/>
+      <c r="AKH8"/>
+      <c r="AKI8"/>
+      <c r="AKJ8"/>
+      <c r="AKK8"/>
+      <c r="AKL8"/>
+      <c r="AKM8"/>
+      <c r="AKN8"/>
+      <c r="AKO8"/>
+      <c r="AKP8"/>
+      <c r="AKQ8"/>
+      <c r="AKR8"/>
+      <c r="AKS8"/>
+      <c r="AKT8"/>
+      <c r="AKU8"/>
+      <c r="AKV8"/>
+      <c r="AKW8"/>
+      <c r="AKX8"/>
+      <c r="AKY8"/>
+      <c r="AKZ8"/>
+      <c r="ALA8"/>
+      <c r="ALB8"/>
+      <c r="ALC8"/>
+      <c r="ALD8"/>
+      <c r="ALE8"/>
+      <c r="ALF8"/>
+      <c r="ALG8"/>
+      <c r="ALH8"/>
+      <c r="ALI8"/>
+      <c r="ALJ8"/>
+      <c r="ALK8"/>
+      <c r="ALL8"/>
+      <c r="ALM8"/>
+      <c r="ALN8"/>
+      <c r="ALO8"/>
+      <c r="ALP8"/>
+      <c r="ALQ8"/>
+      <c r="ALR8"/>
+      <c r="ALS8"/>
+      <c r="ALT8"/>
+      <c r="ALU8"/>
+      <c r="ALV8"/>
+      <c r="ALW8"/>
+      <c r="ALX8"/>
+      <c r="ALY8"/>
+      <c r="ALZ8"/>
+      <c r="AMA8"/>
+      <c r="AMB8"/>
+      <c r="AMC8"/>
+      <c r="AMD8"/>
+      <c r="AME8"/>
+      <c r="AMF8"/>
+      <c r="AMG8"/>
+      <c r="AMH8"/>
+      <c r="AMI8"/>
+      <c r="AMJ8"/>
+      <c r="AMK8"/>
+      <c r="AML8"/>
+      <c r="AMM8"/>
+      <c r="AMN8"/>
+      <c r="AMO8"/>
     </row>
     <row r="9" spans="1:1029" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>134</v>
+        <v>92</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>135</v>
+        <v>89</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>136</v>
+        <v>90</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>4</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>85</v>
+        <v>398</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>137</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:1029" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>4</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>85</v>
+        <v>398</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>110</v>
+        <v>97</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1029" x14ac:dyDescent="0.35">
+      <c r="A11" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>132</v>
       </c>
     </row>
   </sheetData>
@@ -16103,15 +19433,15 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{005D001A-3768-4392-8BD8-510250183310}">
-  <dimension ref="A1:HU5"/>
+  <dimension ref="A1:HU6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="39.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.36328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="38.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="52.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40.54296875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="33.36328125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="27.90625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="31" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:229" x14ac:dyDescent="0.35">
@@ -16136,22 +19466,22 @@
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="3" t="s">
         <v>112</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>113</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>4</v>
       </c>
       <c r="E2" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>114</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>115</v>
       </c>
       <c r="G2"/>
       <c r="H2"/>
@@ -16379,22 +19709,22 @@
     </row>
     <row r="3" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>117</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>118</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>4</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G3"/>
       <c r="H3"/>
@@ -16620,44 +19950,287 @@
       <c r="HT3"/>
       <c r="HU3"/>
     </row>
-    <row r="4" spans="1:229" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>120</v>
+        <v>403</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>121</v>
+        <v>404</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>122</v>
+        <v>405</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>4</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>123</v>
-      </c>
+        <v>406</v>
+      </c>
+      <c r="G4"/>
+      <c r="H4"/>
+      <c r="I4"/>
+      <c r="J4"/>
+      <c r="K4"/>
+      <c r="L4"/>
+      <c r="M4"/>
+      <c r="N4"/>
+      <c r="O4"/>
+      <c r="P4"/>
+      <c r="Q4"/>
+      <c r="R4"/>
+      <c r="S4"/>
+      <c r="T4"/>
+      <c r="U4"/>
+      <c r="V4"/>
+      <c r="W4"/>
+      <c r="X4"/>
+      <c r="Y4"/>
+      <c r="Z4"/>
+      <c r="AA4"/>
+      <c r="AB4"/>
+      <c r="AC4"/>
+      <c r="AD4"/>
+      <c r="AE4"/>
+      <c r="AF4"/>
+      <c r="AG4"/>
+      <c r="AH4"/>
+      <c r="AI4"/>
+      <c r="AJ4"/>
+      <c r="AK4"/>
+      <c r="AL4"/>
+      <c r="AM4"/>
+      <c r="AN4"/>
+      <c r="AO4"/>
+      <c r="AP4"/>
+      <c r="AQ4"/>
+      <c r="AR4"/>
+      <c r="AS4"/>
+      <c r="AT4"/>
+      <c r="AU4"/>
+      <c r="AV4"/>
+      <c r="AW4"/>
+      <c r="AX4"/>
+      <c r="AY4"/>
+      <c r="AZ4"/>
+      <c r="BA4"/>
+      <c r="BB4"/>
+      <c r="BC4"/>
+      <c r="BD4"/>
+      <c r="BE4"/>
+      <c r="BF4"/>
+      <c r="BG4"/>
+      <c r="BH4"/>
+      <c r="BI4"/>
+      <c r="BJ4"/>
+      <c r="BK4"/>
+      <c r="BL4"/>
+      <c r="BM4"/>
+      <c r="BN4"/>
+      <c r="BO4"/>
+      <c r="BP4"/>
+      <c r="BQ4"/>
+      <c r="BR4"/>
+      <c r="BS4"/>
+      <c r="BT4"/>
+      <c r="BU4"/>
+      <c r="BV4"/>
+      <c r="BW4"/>
+      <c r="BX4"/>
+      <c r="BY4"/>
+      <c r="BZ4"/>
+      <c r="CA4"/>
+      <c r="CB4"/>
+      <c r="CC4"/>
+      <c r="CD4"/>
+      <c r="CE4"/>
+      <c r="CF4"/>
+      <c r="CG4"/>
+      <c r="CH4"/>
+      <c r="CI4"/>
+      <c r="CJ4"/>
+      <c r="CK4"/>
+      <c r="CL4"/>
+      <c r="CM4"/>
+      <c r="CN4"/>
+      <c r="CO4"/>
+      <c r="CP4"/>
+      <c r="CQ4"/>
+      <c r="CR4"/>
+      <c r="CS4"/>
+      <c r="CT4"/>
+      <c r="CU4"/>
+      <c r="CV4"/>
+      <c r="CW4"/>
+      <c r="CX4"/>
+      <c r="CY4"/>
+      <c r="CZ4"/>
+      <c r="DA4"/>
+      <c r="DB4"/>
+      <c r="DC4"/>
+      <c r="DD4"/>
+      <c r="DE4"/>
+      <c r="DF4"/>
+      <c r="DG4"/>
+      <c r="DH4"/>
+      <c r="DI4"/>
+      <c r="DJ4"/>
+      <c r="DK4"/>
+      <c r="DL4"/>
+      <c r="DM4"/>
+      <c r="DN4"/>
+      <c r="DO4"/>
+      <c r="DP4"/>
+      <c r="DQ4"/>
+      <c r="DR4"/>
+      <c r="DS4"/>
+      <c r="DT4"/>
+      <c r="DU4"/>
+      <c r="DV4"/>
+      <c r="DW4"/>
+      <c r="DX4"/>
+      <c r="DY4"/>
+      <c r="DZ4"/>
+      <c r="EA4"/>
+      <c r="EB4"/>
+      <c r="EC4"/>
+      <c r="ED4"/>
+      <c r="EE4"/>
+      <c r="EF4"/>
+      <c r="EG4"/>
+      <c r="EH4"/>
+      <c r="EI4"/>
+      <c r="EJ4"/>
+      <c r="EK4"/>
+      <c r="EL4"/>
+      <c r="EM4"/>
+      <c r="EN4"/>
+      <c r="EO4"/>
+      <c r="EP4"/>
+      <c r="EQ4"/>
+      <c r="ER4"/>
+      <c r="ES4"/>
+      <c r="ET4"/>
+      <c r="EU4"/>
+      <c r="EV4"/>
+      <c r="EW4"/>
+      <c r="EX4"/>
+      <c r="EY4"/>
+      <c r="EZ4"/>
+      <c r="FA4"/>
+      <c r="FB4"/>
+      <c r="FC4"/>
+      <c r="FD4"/>
+      <c r="FE4"/>
+      <c r="FF4"/>
+      <c r="FG4"/>
+      <c r="FH4"/>
+      <c r="FI4"/>
+      <c r="FJ4"/>
+      <c r="FK4"/>
+      <c r="FL4"/>
+      <c r="FM4"/>
+      <c r="FN4"/>
+      <c r="FO4"/>
+      <c r="FP4"/>
+      <c r="FQ4"/>
+      <c r="FR4"/>
+      <c r="FS4"/>
+      <c r="FT4"/>
+      <c r="FU4"/>
+      <c r="FV4"/>
+      <c r="FW4"/>
+      <c r="FX4"/>
+      <c r="FY4"/>
+      <c r="FZ4"/>
+      <c r="GA4"/>
+      <c r="GB4"/>
+      <c r="GC4"/>
+      <c r="GD4"/>
+      <c r="GE4"/>
+      <c r="GF4"/>
+      <c r="GG4"/>
+      <c r="GH4"/>
+      <c r="GI4"/>
+      <c r="GJ4"/>
+      <c r="GK4"/>
+      <c r="GL4"/>
+      <c r="GM4"/>
+      <c r="GN4"/>
+      <c r="GO4"/>
+      <c r="GP4"/>
+      <c r="GQ4"/>
+      <c r="GR4"/>
+      <c r="GS4"/>
+      <c r="GT4"/>
+      <c r="GU4"/>
+      <c r="GV4"/>
+      <c r="GW4"/>
+      <c r="GX4"/>
+      <c r="GY4"/>
+      <c r="GZ4"/>
+      <c r="HA4"/>
+      <c r="HB4"/>
+      <c r="HC4"/>
+      <c r="HD4"/>
+      <c r="HE4"/>
+      <c r="HF4"/>
+      <c r="HG4"/>
+      <c r="HH4"/>
+      <c r="HI4"/>
+      <c r="HJ4"/>
+      <c r="HK4"/>
+      <c r="HL4"/>
+      <c r="HM4"/>
+      <c r="HN4"/>
+      <c r="HO4"/>
+      <c r="HP4"/>
+      <c r="HQ4"/>
+      <c r="HR4"/>
+      <c r="HS4"/>
+      <c r="HT4"/>
+      <c r="HU4"/>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>4</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>127</v>
+        <v>122</v>
+      </c>
+    </row>
+    <row r="6" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -16677,97 +20250,97 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="C1" s="6" t="s">
         <v>140</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>143</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>147</v>
-      </c>
       <c r="C3" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3"/>
       <c r="B8" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>158</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3"/>
       <c r="B9" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>156</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>157</v>
       </c>
     </row>
   </sheetData>
@@ -16786,86 +20359,86 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="C1" s="6" t="s">
         <v>140</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>160</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3"/>
       <c r="B7" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>158</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3"/>
       <c r="B8" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>156</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>157</v>
       </c>
     </row>
   </sheetData>
@@ -16884,108 +20457,108 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="C1" s="6" t="s">
         <v>140</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>166</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3"/>
       <c r="B9" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>158</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="3"/>
       <c r="B10" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>156</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>157</v>
       </c>
     </row>
   </sheetData>
@@ -17005,97 +20578,97 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="C1" s="6" t="s">
         <v>140</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>175</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3"/>
       <c r="B8" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>158</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3"/>
       <c r="B9" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>156</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>157</v>
       </c>
     </row>
   </sheetData>
@@ -17115,130 +20688,130 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="C1" s="6" t="s">
         <v>140</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>182</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>191</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="3"/>
       <c r="B11" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>158</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="3"/>
       <c r="B12" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>156</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>157</v>
       </c>
     </row>
   </sheetData>

--- a/testdata.xlsx
+++ b/testdata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sshiwani\workspace\find-information-products-services-tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{759335DB-C01C-4D37-91AF-2CDF617A42C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84601013-AC13-48B6-BBD5-5C3C5F01E49F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,48 +46,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="889" uniqueCount="407">
-  <si>
-    <t>products?phase=request</t>
-  </si>
-  <si>
-    <t>products?phase=explore</t>
-  </si>
-  <si>
-    <t>Remove this filter Request</t>
-  </si>
-  <si>
-    <t>Remove this filter Explore</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="861" uniqueCount="395">
   <si>
     <t>Search and filter products and services</t>
   </si>
   <si>
     <t>//h3[normalize-space()='Phase']</t>
-  </si>
-  <si>
-    <t>#phase-request</t>
-  </si>
-  <si>
-    <t>#phase-explore</t>
-  </si>
-  <si>
-    <t>ul.moj-filter-tags li a:has-text('Request')</t>
-  </si>
-  <si>
-    <t>ul.moj-filter-tags li a:has-text('Explore')</t>
-  </si>
-  <si>
-    <t>products?phase=triage</t>
-  </si>
-  <si>
-    <t>ul.moj-filter-tags li a:has-text('Triage')</t>
-  </si>
-  <si>
-    <t>Remove this filter Triage</t>
-  </si>
-  <si>
-    <t>#phase-triage</t>
   </si>
   <si>
     <t>products?phase=discovery</t>
@@ -1674,7 +1638,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:ARE11"/>
+  <dimension ref="A1:ARE8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="30" bestFit="1" customWidth="1"/>
@@ -1687,42 +1651,42 @@
   <sheetData>
     <row r="1" spans="1:1149" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:1149" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="E2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>5</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>6</v>
       </c>
       <c r="G2"/>
       <c r="H2"/>
@@ -2870,22 +2834,22 @@
     </row>
     <row r="3" spans="1:1149" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>9</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>7</v>
       </c>
       <c r="G3"/>
       <c r="H3"/>
@@ -4042,10 +4006,10 @@
         <v>12</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>13</v>
@@ -5205,10 +5169,10 @@
         <v>16</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>17</v>
@@ -6368,10 +6332,10 @@
         <v>20</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>21</v>
@@ -7531,10 +7495,10 @@
         <v>24</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>25</v>
@@ -8694,10 +8658,10 @@
         <v>28</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>29</v>
@@ -9846,3495 +9810,6 @@
       <c r="ARD8"/>
       <c r="ARE8"/>
     </row>
-    <row r="9" spans="1:1149" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G9"/>
-      <c r="H9"/>
-      <c r="I9"/>
-      <c r="J9"/>
-      <c r="K9"/>
-      <c r="L9"/>
-      <c r="M9"/>
-      <c r="N9"/>
-      <c r="O9"/>
-      <c r="P9"/>
-      <c r="Q9"/>
-      <c r="R9"/>
-      <c r="S9"/>
-      <c r="T9"/>
-      <c r="U9"/>
-      <c r="V9"/>
-      <c r="W9"/>
-      <c r="X9"/>
-      <c r="Y9"/>
-      <c r="Z9"/>
-      <c r="AA9"/>
-      <c r="AB9"/>
-      <c r="AC9"/>
-      <c r="AD9"/>
-      <c r="AE9"/>
-      <c r="AF9"/>
-      <c r="AG9"/>
-      <c r="AH9"/>
-      <c r="AI9"/>
-      <c r="AJ9"/>
-      <c r="AK9"/>
-      <c r="AL9"/>
-      <c r="AM9"/>
-      <c r="AN9"/>
-      <c r="AO9"/>
-      <c r="AP9"/>
-      <c r="AQ9"/>
-      <c r="AR9"/>
-      <c r="AS9"/>
-      <c r="AT9"/>
-      <c r="AU9"/>
-      <c r="AV9"/>
-      <c r="AW9"/>
-      <c r="AX9"/>
-      <c r="AY9"/>
-      <c r="AZ9"/>
-      <c r="BA9"/>
-      <c r="BB9"/>
-      <c r="BC9"/>
-      <c r="BD9"/>
-      <c r="BE9"/>
-      <c r="BF9"/>
-      <c r="BG9"/>
-      <c r="BH9"/>
-      <c r="BI9"/>
-      <c r="BJ9"/>
-      <c r="BK9"/>
-      <c r="BL9"/>
-      <c r="BM9"/>
-      <c r="BN9"/>
-      <c r="BO9"/>
-      <c r="BP9"/>
-      <c r="BQ9"/>
-      <c r="BR9"/>
-      <c r="BS9"/>
-      <c r="BT9"/>
-      <c r="BU9"/>
-      <c r="BV9"/>
-      <c r="BW9"/>
-      <c r="BX9"/>
-      <c r="BY9"/>
-      <c r="BZ9"/>
-      <c r="CA9"/>
-      <c r="CB9"/>
-      <c r="CC9"/>
-      <c r="CD9"/>
-      <c r="CE9"/>
-      <c r="CF9"/>
-      <c r="CG9"/>
-      <c r="CH9"/>
-      <c r="CI9"/>
-      <c r="CJ9"/>
-      <c r="CK9"/>
-      <c r="CL9"/>
-      <c r="CM9"/>
-      <c r="CN9"/>
-      <c r="CO9"/>
-      <c r="CP9"/>
-      <c r="CQ9"/>
-      <c r="CR9"/>
-      <c r="CS9"/>
-      <c r="CT9"/>
-      <c r="CU9"/>
-      <c r="CV9"/>
-      <c r="CW9"/>
-      <c r="CX9"/>
-      <c r="CY9"/>
-      <c r="CZ9"/>
-      <c r="DA9"/>
-      <c r="DB9"/>
-      <c r="DC9"/>
-      <c r="DD9"/>
-      <c r="DE9"/>
-      <c r="DF9"/>
-      <c r="DG9"/>
-      <c r="DH9"/>
-      <c r="DI9"/>
-      <c r="DJ9"/>
-      <c r="DK9"/>
-      <c r="DL9"/>
-      <c r="DM9"/>
-      <c r="DN9"/>
-      <c r="DO9"/>
-      <c r="DP9"/>
-      <c r="DQ9"/>
-      <c r="DR9"/>
-      <c r="DS9"/>
-      <c r="DT9"/>
-      <c r="DU9"/>
-      <c r="DV9"/>
-      <c r="DW9"/>
-      <c r="DX9"/>
-      <c r="DY9"/>
-      <c r="DZ9"/>
-      <c r="EA9"/>
-      <c r="EB9"/>
-      <c r="EC9"/>
-      <c r="ED9"/>
-      <c r="EE9"/>
-      <c r="EF9"/>
-      <c r="EG9"/>
-      <c r="EH9"/>
-      <c r="EI9"/>
-      <c r="EJ9"/>
-      <c r="EK9"/>
-      <c r="EL9"/>
-      <c r="EM9"/>
-      <c r="EN9"/>
-      <c r="EO9"/>
-      <c r="EP9"/>
-      <c r="EQ9"/>
-      <c r="ER9"/>
-      <c r="ES9"/>
-      <c r="ET9"/>
-      <c r="EU9"/>
-      <c r="EV9"/>
-      <c r="EW9"/>
-      <c r="EX9"/>
-      <c r="EY9"/>
-      <c r="EZ9"/>
-      <c r="FA9"/>
-      <c r="FB9"/>
-      <c r="FC9"/>
-      <c r="FD9"/>
-      <c r="FE9"/>
-      <c r="FF9"/>
-      <c r="FG9"/>
-      <c r="FH9"/>
-      <c r="FI9"/>
-      <c r="FJ9"/>
-      <c r="FK9"/>
-      <c r="FL9"/>
-      <c r="FM9"/>
-      <c r="FN9"/>
-      <c r="FO9"/>
-      <c r="FP9"/>
-      <c r="FQ9"/>
-      <c r="FR9"/>
-      <c r="FS9"/>
-      <c r="FT9"/>
-      <c r="FU9"/>
-      <c r="FV9"/>
-      <c r="FW9"/>
-      <c r="FX9"/>
-      <c r="FY9"/>
-      <c r="FZ9"/>
-      <c r="GA9"/>
-      <c r="GB9"/>
-      <c r="GC9"/>
-      <c r="GD9"/>
-      <c r="GE9"/>
-      <c r="GF9"/>
-      <c r="GG9"/>
-      <c r="GH9"/>
-      <c r="GI9"/>
-      <c r="GJ9"/>
-      <c r="GK9"/>
-      <c r="GL9"/>
-      <c r="GM9"/>
-      <c r="GN9"/>
-      <c r="GO9"/>
-      <c r="GP9"/>
-      <c r="GQ9"/>
-      <c r="GR9"/>
-      <c r="GS9"/>
-      <c r="GT9"/>
-      <c r="GU9"/>
-      <c r="GV9"/>
-      <c r="GW9"/>
-      <c r="GX9"/>
-      <c r="GY9"/>
-      <c r="GZ9"/>
-      <c r="HA9"/>
-      <c r="HB9"/>
-      <c r="HC9"/>
-      <c r="HD9"/>
-      <c r="HE9"/>
-      <c r="HF9"/>
-      <c r="HG9"/>
-      <c r="HH9"/>
-      <c r="HI9"/>
-      <c r="HJ9"/>
-      <c r="HK9"/>
-      <c r="HL9"/>
-      <c r="HM9"/>
-      <c r="HN9"/>
-      <c r="HO9"/>
-      <c r="HP9"/>
-      <c r="HQ9"/>
-      <c r="HR9"/>
-      <c r="HS9"/>
-      <c r="HT9"/>
-      <c r="HU9"/>
-      <c r="HV9"/>
-      <c r="HW9"/>
-      <c r="HX9"/>
-      <c r="HY9"/>
-      <c r="HZ9"/>
-      <c r="IA9"/>
-      <c r="IB9"/>
-      <c r="IC9"/>
-      <c r="ID9"/>
-      <c r="IE9"/>
-      <c r="IF9"/>
-      <c r="IG9"/>
-      <c r="IH9"/>
-      <c r="II9"/>
-      <c r="IJ9"/>
-      <c r="IK9"/>
-      <c r="IL9"/>
-      <c r="IM9"/>
-      <c r="IN9"/>
-      <c r="IO9"/>
-      <c r="IP9"/>
-      <c r="IQ9"/>
-      <c r="IR9"/>
-      <c r="IS9"/>
-      <c r="IT9"/>
-      <c r="IU9"/>
-      <c r="IV9"/>
-      <c r="IW9"/>
-      <c r="IX9"/>
-      <c r="IY9"/>
-      <c r="IZ9"/>
-      <c r="JA9"/>
-      <c r="JB9"/>
-      <c r="JC9"/>
-      <c r="JD9"/>
-      <c r="JE9"/>
-      <c r="JF9"/>
-      <c r="JG9"/>
-      <c r="JH9"/>
-      <c r="JI9"/>
-      <c r="JJ9"/>
-      <c r="JK9"/>
-      <c r="JL9"/>
-      <c r="JM9"/>
-      <c r="JN9"/>
-      <c r="JO9"/>
-      <c r="JP9"/>
-      <c r="JQ9"/>
-      <c r="JR9"/>
-      <c r="JS9"/>
-      <c r="JT9"/>
-      <c r="JU9"/>
-      <c r="JV9"/>
-      <c r="JW9"/>
-      <c r="JX9"/>
-      <c r="JY9"/>
-      <c r="JZ9"/>
-      <c r="KA9"/>
-      <c r="KB9"/>
-      <c r="KC9"/>
-      <c r="KD9"/>
-      <c r="KE9"/>
-      <c r="KF9"/>
-      <c r="KG9"/>
-      <c r="KH9"/>
-      <c r="KI9"/>
-      <c r="KJ9"/>
-      <c r="KK9"/>
-      <c r="KL9"/>
-      <c r="KM9"/>
-      <c r="KN9"/>
-      <c r="KO9"/>
-      <c r="KP9"/>
-      <c r="KQ9"/>
-      <c r="KR9"/>
-      <c r="KS9"/>
-      <c r="KT9"/>
-      <c r="KU9"/>
-      <c r="KV9"/>
-      <c r="KW9"/>
-      <c r="KX9"/>
-      <c r="KY9"/>
-      <c r="KZ9"/>
-      <c r="LA9"/>
-      <c r="LB9"/>
-      <c r="LC9"/>
-      <c r="LD9"/>
-      <c r="LE9"/>
-      <c r="LF9"/>
-      <c r="LG9"/>
-      <c r="LH9"/>
-      <c r="LI9"/>
-      <c r="LJ9"/>
-      <c r="LK9"/>
-      <c r="LL9"/>
-      <c r="LM9"/>
-      <c r="LN9"/>
-      <c r="LO9"/>
-      <c r="LP9"/>
-      <c r="LQ9"/>
-      <c r="LR9"/>
-      <c r="LS9"/>
-      <c r="LT9"/>
-      <c r="LU9"/>
-      <c r="LV9"/>
-      <c r="LW9"/>
-      <c r="LX9"/>
-      <c r="LY9"/>
-      <c r="LZ9"/>
-      <c r="MA9"/>
-      <c r="MB9"/>
-      <c r="MC9"/>
-      <c r="MD9"/>
-      <c r="ME9"/>
-      <c r="MF9"/>
-      <c r="MG9"/>
-      <c r="MH9"/>
-      <c r="MI9"/>
-      <c r="MJ9"/>
-      <c r="MK9"/>
-      <c r="ML9"/>
-      <c r="MM9"/>
-      <c r="MN9"/>
-      <c r="MO9"/>
-      <c r="MP9"/>
-      <c r="MQ9"/>
-      <c r="MR9"/>
-      <c r="MS9"/>
-      <c r="MT9"/>
-      <c r="MU9"/>
-      <c r="MV9"/>
-      <c r="MW9"/>
-      <c r="MX9"/>
-      <c r="MY9"/>
-      <c r="MZ9"/>
-      <c r="NA9"/>
-      <c r="NB9"/>
-      <c r="NC9"/>
-      <c r="ND9"/>
-      <c r="NE9"/>
-      <c r="NF9"/>
-      <c r="NG9"/>
-      <c r="NH9"/>
-      <c r="NI9"/>
-      <c r="NJ9"/>
-      <c r="NK9"/>
-      <c r="NL9"/>
-      <c r="NM9"/>
-      <c r="NN9"/>
-      <c r="NO9"/>
-      <c r="NP9"/>
-      <c r="NQ9"/>
-      <c r="NR9"/>
-      <c r="NS9"/>
-      <c r="NT9"/>
-      <c r="NU9"/>
-      <c r="NV9"/>
-      <c r="NW9"/>
-      <c r="NX9"/>
-      <c r="NY9"/>
-      <c r="NZ9"/>
-      <c r="OA9"/>
-      <c r="OB9"/>
-      <c r="OC9"/>
-      <c r="OD9"/>
-      <c r="OE9"/>
-      <c r="OF9"/>
-      <c r="OG9"/>
-      <c r="OH9"/>
-      <c r="OI9"/>
-      <c r="OJ9"/>
-      <c r="OK9"/>
-      <c r="OL9"/>
-      <c r="OM9"/>
-      <c r="ON9"/>
-      <c r="OO9"/>
-      <c r="OP9"/>
-      <c r="OQ9"/>
-      <c r="OR9"/>
-      <c r="OS9"/>
-      <c r="OT9"/>
-      <c r="OU9"/>
-      <c r="OV9"/>
-      <c r="OW9"/>
-      <c r="OX9"/>
-      <c r="OY9"/>
-      <c r="OZ9"/>
-      <c r="PA9"/>
-      <c r="PB9"/>
-      <c r="PC9"/>
-      <c r="PD9"/>
-      <c r="PE9"/>
-      <c r="PF9"/>
-      <c r="PG9"/>
-      <c r="PH9"/>
-      <c r="PI9"/>
-      <c r="PJ9"/>
-      <c r="PK9"/>
-      <c r="PL9"/>
-      <c r="PM9"/>
-      <c r="PN9"/>
-      <c r="PO9"/>
-      <c r="PP9"/>
-      <c r="PQ9"/>
-      <c r="PR9"/>
-      <c r="PS9"/>
-      <c r="PT9"/>
-      <c r="PU9"/>
-      <c r="PV9"/>
-      <c r="PW9"/>
-      <c r="PX9"/>
-      <c r="PY9"/>
-      <c r="PZ9"/>
-      <c r="QA9"/>
-      <c r="QB9"/>
-      <c r="QC9"/>
-      <c r="QD9"/>
-      <c r="QE9"/>
-      <c r="QF9"/>
-      <c r="QG9"/>
-      <c r="QH9"/>
-      <c r="QI9"/>
-      <c r="QJ9"/>
-      <c r="QK9"/>
-      <c r="QL9"/>
-      <c r="QM9"/>
-      <c r="QN9"/>
-      <c r="QO9"/>
-      <c r="QP9"/>
-      <c r="QQ9"/>
-      <c r="QR9"/>
-      <c r="QS9"/>
-      <c r="QT9"/>
-      <c r="QU9"/>
-      <c r="QV9"/>
-      <c r="QW9"/>
-      <c r="QX9"/>
-      <c r="QY9"/>
-      <c r="QZ9"/>
-      <c r="RA9"/>
-      <c r="RB9"/>
-      <c r="RC9"/>
-      <c r="RD9"/>
-      <c r="RE9"/>
-      <c r="RF9"/>
-      <c r="RG9"/>
-      <c r="RH9"/>
-      <c r="RI9"/>
-      <c r="RJ9"/>
-      <c r="RK9"/>
-      <c r="RL9"/>
-      <c r="RM9"/>
-      <c r="RN9"/>
-      <c r="RO9"/>
-      <c r="RP9"/>
-      <c r="RQ9"/>
-      <c r="RR9"/>
-      <c r="RS9"/>
-      <c r="RT9"/>
-      <c r="RU9"/>
-      <c r="RV9"/>
-      <c r="RW9"/>
-      <c r="RX9"/>
-      <c r="RY9"/>
-      <c r="RZ9"/>
-      <c r="SA9"/>
-      <c r="SB9"/>
-      <c r="SC9"/>
-      <c r="SD9"/>
-      <c r="SE9"/>
-      <c r="SF9"/>
-      <c r="SG9"/>
-      <c r="SH9"/>
-      <c r="SI9"/>
-      <c r="SJ9"/>
-      <c r="SK9"/>
-      <c r="SL9"/>
-      <c r="SM9"/>
-      <c r="SN9"/>
-      <c r="SO9"/>
-      <c r="SP9"/>
-      <c r="SQ9"/>
-      <c r="SR9"/>
-      <c r="SS9"/>
-      <c r="ST9"/>
-      <c r="SU9"/>
-      <c r="SV9"/>
-      <c r="SW9"/>
-      <c r="SX9"/>
-      <c r="SY9"/>
-      <c r="SZ9"/>
-      <c r="TA9"/>
-      <c r="TB9"/>
-      <c r="TC9"/>
-      <c r="TD9"/>
-      <c r="TE9"/>
-      <c r="TF9"/>
-      <c r="TG9"/>
-      <c r="TH9"/>
-      <c r="TI9"/>
-      <c r="TJ9"/>
-      <c r="TK9"/>
-      <c r="TL9"/>
-      <c r="TM9"/>
-      <c r="TN9"/>
-      <c r="TO9"/>
-      <c r="TP9"/>
-      <c r="TQ9"/>
-      <c r="TR9"/>
-      <c r="TS9"/>
-      <c r="TT9"/>
-      <c r="TU9"/>
-      <c r="TV9"/>
-      <c r="TW9"/>
-      <c r="TX9"/>
-      <c r="TY9"/>
-      <c r="TZ9"/>
-      <c r="UA9"/>
-      <c r="UB9"/>
-      <c r="UC9"/>
-      <c r="UD9"/>
-      <c r="UE9"/>
-      <c r="UF9"/>
-      <c r="UG9"/>
-      <c r="UH9"/>
-      <c r="UI9"/>
-      <c r="UJ9"/>
-      <c r="UK9"/>
-      <c r="UL9"/>
-      <c r="UM9"/>
-      <c r="UN9"/>
-      <c r="UO9"/>
-      <c r="UP9"/>
-      <c r="UQ9"/>
-      <c r="UR9"/>
-      <c r="US9"/>
-      <c r="UT9"/>
-      <c r="UU9"/>
-      <c r="UV9"/>
-      <c r="UW9"/>
-      <c r="UX9"/>
-      <c r="UY9"/>
-      <c r="UZ9"/>
-      <c r="VA9"/>
-      <c r="VB9"/>
-      <c r="VC9"/>
-      <c r="VD9"/>
-      <c r="VE9"/>
-      <c r="VF9"/>
-      <c r="VG9"/>
-      <c r="VH9"/>
-      <c r="VI9"/>
-      <c r="VJ9"/>
-      <c r="VK9"/>
-      <c r="VL9"/>
-      <c r="VM9"/>
-      <c r="VN9"/>
-      <c r="VO9"/>
-      <c r="VP9"/>
-      <c r="VQ9"/>
-      <c r="VR9"/>
-      <c r="VS9"/>
-      <c r="VT9"/>
-      <c r="VU9"/>
-      <c r="VV9"/>
-      <c r="VW9"/>
-      <c r="VX9"/>
-      <c r="VY9"/>
-      <c r="VZ9"/>
-      <c r="WA9"/>
-      <c r="WB9"/>
-      <c r="WC9"/>
-      <c r="WD9"/>
-      <c r="WE9"/>
-      <c r="WF9"/>
-      <c r="WG9"/>
-      <c r="WH9"/>
-      <c r="WI9"/>
-      <c r="WJ9"/>
-      <c r="WK9"/>
-      <c r="WL9"/>
-      <c r="WM9"/>
-      <c r="WN9"/>
-      <c r="WO9"/>
-      <c r="WP9"/>
-      <c r="WQ9"/>
-      <c r="WR9"/>
-      <c r="WS9"/>
-      <c r="WT9"/>
-      <c r="WU9"/>
-      <c r="WV9"/>
-      <c r="WW9"/>
-      <c r="WX9"/>
-      <c r="WY9"/>
-      <c r="WZ9"/>
-      <c r="XA9"/>
-      <c r="XB9"/>
-      <c r="XC9"/>
-      <c r="XD9"/>
-      <c r="XE9"/>
-      <c r="XF9"/>
-      <c r="XG9"/>
-      <c r="XH9"/>
-      <c r="XI9"/>
-      <c r="XJ9"/>
-      <c r="XK9"/>
-      <c r="XL9"/>
-      <c r="XM9"/>
-      <c r="XN9"/>
-      <c r="XO9"/>
-      <c r="XP9"/>
-      <c r="XQ9"/>
-      <c r="XR9"/>
-      <c r="XS9"/>
-      <c r="XT9"/>
-      <c r="XU9"/>
-      <c r="XV9"/>
-      <c r="XW9"/>
-      <c r="XX9"/>
-      <c r="XY9"/>
-      <c r="XZ9"/>
-      <c r="YA9"/>
-      <c r="YB9"/>
-      <c r="YC9"/>
-      <c r="YD9"/>
-      <c r="YE9"/>
-      <c r="YF9"/>
-      <c r="YG9"/>
-      <c r="YH9"/>
-      <c r="YI9"/>
-      <c r="YJ9"/>
-      <c r="YK9"/>
-      <c r="YL9"/>
-      <c r="YM9"/>
-      <c r="YN9"/>
-      <c r="YO9"/>
-      <c r="YP9"/>
-      <c r="YQ9"/>
-      <c r="YR9"/>
-      <c r="YS9"/>
-      <c r="YT9"/>
-      <c r="YU9"/>
-      <c r="YV9"/>
-      <c r="YW9"/>
-      <c r="YX9"/>
-      <c r="YY9"/>
-      <c r="YZ9"/>
-      <c r="ZA9"/>
-      <c r="ZB9"/>
-      <c r="ZC9"/>
-      <c r="ZD9"/>
-      <c r="ZE9"/>
-      <c r="ZF9"/>
-      <c r="ZG9"/>
-      <c r="ZH9"/>
-      <c r="ZI9"/>
-      <c r="ZJ9"/>
-      <c r="ZK9"/>
-      <c r="ZL9"/>
-      <c r="ZM9"/>
-      <c r="ZN9"/>
-      <c r="ZO9"/>
-      <c r="ZP9"/>
-      <c r="ZQ9"/>
-      <c r="ZR9"/>
-      <c r="ZS9"/>
-      <c r="ZT9"/>
-      <c r="ZU9"/>
-      <c r="ZV9"/>
-      <c r="ZW9"/>
-      <c r="ZX9"/>
-      <c r="ZY9"/>
-      <c r="ZZ9"/>
-      <c r="AAA9"/>
-      <c r="AAB9"/>
-      <c r="AAC9"/>
-      <c r="AAD9"/>
-      <c r="AAE9"/>
-      <c r="AAF9"/>
-      <c r="AAG9"/>
-      <c r="AAH9"/>
-      <c r="AAI9"/>
-      <c r="AAJ9"/>
-      <c r="AAK9"/>
-      <c r="AAL9"/>
-      <c r="AAM9"/>
-      <c r="AAN9"/>
-      <c r="AAO9"/>
-      <c r="AAP9"/>
-      <c r="AAQ9"/>
-      <c r="AAR9"/>
-      <c r="AAS9"/>
-      <c r="AAT9"/>
-      <c r="AAU9"/>
-      <c r="AAV9"/>
-      <c r="AAW9"/>
-      <c r="AAX9"/>
-      <c r="AAY9"/>
-      <c r="AAZ9"/>
-      <c r="ABA9"/>
-      <c r="ABB9"/>
-      <c r="ABC9"/>
-      <c r="ABD9"/>
-      <c r="ABE9"/>
-      <c r="ABF9"/>
-      <c r="ABG9"/>
-      <c r="ABH9"/>
-      <c r="ABI9"/>
-      <c r="ABJ9"/>
-      <c r="ABK9"/>
-      <c r="ABL9"/>
-      <c r="ABM9"/>
-      <c r="ABN9"/>
-      <c r="ABO9"/>
-      <c r="ABP9"/>
-      <c r="ABQ9"/>
-      <c r="ABR9"/>
-      <c r="ABS9"/>
-      <c r="ABT9"/>
-      <c r="ABU9"/>
-      <c r="ABV9"/>
-      <c r="ABW9"/>
-      <c r="ABX9"/>
-      <c r="ABY9"/>
-      <c r="ABZ9"/>
-      <c r="ACA9"/>
-      <c r="ACB9"/>
-      <c r="ACC9"/>
-      <c r="ACD9"/>
-      <c r="ACE9"/>
-      <c r="ACF9"/>
-      <c r="ACG9"/>
-      <c r="ACH9"/>
-      <c r="ACI9"/>
-      <c r="ACJ9"/>
-      <c r="ACK9"/>
-      <c r="ACL9"/>
-      <c r="ACM9"/>
-      <c r="ACN9"/>
-      <c r="ACO9"/>
-      <c r="ACP9"/>
-      <c r="ACQ9"/>
-      <c r="ACR9"/>
-      <c r="ACS9"/>
-      <c r="ACT9"/>
-      <c r="ACU9"/>
-      <c r="ACV9"/>
-      <c r="ACW9"/>
-      <c r="ACX9"/>
-      <c r="ACY9"/>
-      <c r="ACZ9"/>
-      <c r="ADA9"/>
-      <c r="ADB9"/>
-      <c r="ADC9"/>
-      <c r="ADD9"/>
-      <c r="ADE9"/>
-      <c r="ADF9"/>
-      <c r="ADG9"/>
-      <c r="ADH9"/>
-      <c r="ADI9"/>
-      <c r="ADJ9"/>
-      <c r="ADK9"/>
-      <c r="ADL9"/>
-      <c r="ADM9"/>
-      <c r="ADN9"/>
-      <c r="ADO9"/>
-      <c r="ADP9"/>
-      <c r="ADQ9"/>
-      <c r="ADR9"/>
-      <c r="ADS9"/>
-      <c r="ADT9"/>
-      <c r="ADU9"/>
-      <c r="ADV9"/>
-      <c r="ADW9"/>
-      <c r="ADX9"/>
-      <c r="ADY9"/>
-      <c r="ADZ9"/>
-      <c r="AEA9"/>
-      <c r="AEB9"/>
-      <c r="AEC9"/>
-      <c r="AED9"/>
-      <c r="AEE9"/>
-      <c r="AEF9"/>
-      <c r="AEG9"/>
-      <c r="AEH9"/>
-      <c r="AEI9"/>
-      <c r="AEJ9"/>
-      <c r="AEK9"/>
-      <c r="AEL9"/>
-      <c r="AEM9"/>
-      <c r="AEN9"/>
-      <c r="AEO9"/>
-      <c r="AEP9"/>
-      <c r="AEQ9"/>
-      <c r="AER9"/>
-      <c r="AES9"/>
-      <c r="AET9"/>
-      <c r="AEU9"/>
-      <c r="AEV9"/>
-      <c r="AEW9"/>
-      <c r="AEX9"/>
-      <c r="AEY9"/>
-      <c r="AEZ9"/>
-      <c r="AFA9"/>
-      <c r="AFB9"/>
-      <c r="AFC9"/>
-      <c r="AFD9"/>
-      <c r="AFE9"/>
-      <c r="AFF9"/>
-      <c r="AFG9"/>
-      <c r="AFH9"/>
-      <c r="AFI9"/>
-      <c r="AFJ9"/>
-      <c r="AFK9"/>
-      <c r="AFL9"/>
-      <c r="AFM9"/>
-      <c r="AFN9"/>
-      <c r="AFO9"/>
-      <c r="AFP9"/>
-      <c r="AFQ9"/>
-      <c r="AFR9"/>
-      <c r="AFS9"/>
-      <c r="AFT9"/>
-      <c r="AFU9"/>
-      <c r="AFV9"/>
-      <c r="AFW9"/>
-      <c r="AFX9"/>
-      <c r="AFY9"/>
-      <c r="AFZ9"/>
-      <c r="AGA9"/>
-      <c r="AGB9"/>
-      <c r="AGC9"/>
-      <c r="AGD9"/>
-      <c r="AGE9"/>
-      <c r="AGF9"/>
-      <c r="AGG9"/>
-      <c r="AGH9"/>
-      <c r="AGI9"/>
-      <c r="AGJ9"/>
-      <c r="AGK9"/>
-      <c r="AGL9"/>
-      <c r="AGM9"/>
-      <c r="AGN9"/>
-      <c r="AGO9"/>
-      <c r="AGP9"/>
-      <c r="AGQ9"/>
-      <c r="AGR9"/>
-      <c r="AGS9"/>
-      <c r="AGT9"/>
-      <c r="AGU9"/>
-      <c r="AGV9"/>
-      <c r="AGW9"/>
-      <c r="AGX9"/>
-      <c r="AGY9"/>
-      <c r="AGZ9"/>
-      <c r="AHA9"/>
-      <c r="AHB9"/>
-      <c r="AHC9"/>
-      <c r="AHD9"/>
-      <c r="AHE9"/>
-      <c r="AHF9"/>
-      <c r="AHG9"/>
-      <c r="AHH9"/>
-      <c r="AHI9"/>
-      <c r="AHJ9"/>
-      <c r="AHK9"/>
-      <c r="AHL9"/>
-      <c r="AHM9"/>
-      <c r="AHN9"/>
-      <c r="AHO9"/>
-      <c r="AHP9"/>
-      <c r="AHQ9"/>
-      <c r="AHR9"/>
-      <c r="AHS9"/>
-      <c r="AHT9"/>
-      <c r="AHU9"/>
-      <c r="AHV9"/>
-      <c r="AHW9"/>
-      <c r="AHX9"/>
-      <c r="AHY9"/>
-      <c r="AHZ9"/>
-      <c r="AIA9"/>
-      <c r="AIB9"/>
-      <c r="AIC9"/>
-      <c r="AID9"/>
-      <c r="AIE9"/>
-      <c r="AIF9"/>
-      <c r="AIG9"/>
-      <c r="AIH9"/>
-      <c r="AII9"/>
-      <c r="AIJ9"/>
-      <c r="AIK9"/>
-      <c r="AIL9"/>
-      <c r="AIM9"/>
-      <c r="AIN9"/>
-      <c r="AIO9"/>
-      <c r="AIP9"/>
-      <c r="AIQ9"/>
-      <c r="AIR9"/>
-      <c r="AIS9"/>
-      <c r="AIT9"/>
-      <c r="AIU9"/>
-      <c r="AIV9"/>
-      <c r="AIW9"/>
-      <c r="AIX9"/>
-      <c r="AIY9"/>
-      <c r="AIZ9"/>
-      <c r="AJA9"/>
-      <c r="AJB9"/>
-      <c r="AJC9"/>
-      <c r="AJD9"/>
-      <c r="AJE9"/>
-      <c r="AJF9"/>
-      <c r="AJG9"/>
-      <c r="AJH9"/>
-      <c r="AJI9"/>
-      <c r="AJJ9"/>
-      <c r="AJK9"/>
-      <c r="AJL9"/>
-      <c r="AJM9"/>
-      <c r="AJN9"/>
-      <c r="AJO9"/>
-      <c r="AJP9"/>
-      <c r="AJQ9"/>
-      <c r="AJR9"/>
-      <c r="AJS9"/>
-      <c r="AJT9"/>
-      <c r="AJU9"/>
-      <c r="AJV9"/>
-      <c r="AJW9"/>
-      <c r="AJX9"/>
-      <c r="AJY9"/>
-      <c r="AJZ9"/>
-      <c r="AKA9"/>
-      <c r="AKB9"/>
-      <c r="AKC9"/>
-      <c r="AKD9"/>
-      <c r="AKE9"/>
-      <c r="AKF9"/>
-      <c r="AKG9"/>
-      <c r="AKH9"/>
-      <c r="AKI9"/>
-      <c r="AKJ9"/>
-      <c r="AKK9"/>
-      <c r="AKL9"/>
-      <c r="AKM9"/>
-      <c r="AKN9"/>
-      <c r="AKO9"/>
-      <c r="AKP9"/>
-      <c r="AKQ9"/>
-      <c r="AKR9"/>
-      <c r="AKS9"/>
-      <c r="AKT9"/>
-      <c r="AKU9"/>
-      <c r="AKV9"/>
-      <c r="AKW9"/>
-      <c r="AKX9"/>
-      <c r="AKY9"/>
-      <c r="AKZ9"/>
-      <c r="ALA9"/>
-      <c r="ALB9"/>
-      <c r="ALC9"/>
-      <c r="ALD9"/>
-      <c r="ALE9"/>
-      <c r="ALF9"/>
-      <c r="ALG9"/>
-      <c r="ALH9"/>
-      <c r="ALI9"/>
-      <c r="ALJ9"/>
-      <c r="ALK9"/>
-      <c r="ALL9"/>
-      <c r="ALM9"/>
-      <c r="ALN9"/>
-      <c r="ALO9"/>
-      <c r="ALP9"/>
-      <c r="ALQ9"/>
-      <c r="ALR9"/>
-      <c r="ALS9"/>
-      <c r="ALT9"/>
-      <c r="ALU9"/>
-      <c r="ALV9"/>
-      <c r="ALW9"/>
-      <c r="ALX9"/>
-      <c r="ALY9"/>
-      <c r="ALZ9"/>
-      <c r="AMA9"/>
-      <c r="AMB9"/>
-      <c r="AMC9"/>
-      <c r="AMD9"/>
-      <c r="AME9"/>
-      <c r="AMF9"/>
-      <c r="AMG9"/>
-      <c r="AMH9"/>
-      <c r="AMI9"/>
-      <c r="AMJ9"/>
-      <c r="AMK9"/>
-      <c r="AML9"/>
-      <c r="AMM9"/>
-      <c r="AMN9"/>
-      <c r="AMO9"/>
-      <c r="AMP9"/>
-      <c r="AMQ9"/>
-      <c r="AMR9"/>
-      <c r="AMS9"/>
-      <c r="AMT9"/>
-      <c r="AMU9"/>
-      <c r="AMV9"/>
-      <c r="AMW9"/>
-      <c r="AMX9"/>
-      <c r="AMY9"/>
-      <c r="AMZ9"/>
-      <c r="ANA9"/>
-      <c r="ANB9"/>
-      <c r="ANC9"/>
-      <c r="AND9"/>
-      <c r="ANE9"/>
-      <c r="ANF9"/>
-      <c r="ANG9"/>
-      <c r="ANH9"/>
-      <c r="ANI9"/>
-      <c r="ANJ9"/>
-      <c r="ANK9"/>
-      <c r="ANL9"/>
-      <c r="ANM9"/>
-      <c r="ANN9"/>
-      <c r="ANO9"/>
-      <c r="ANP9"/>
-      <c r="ANQ9"/>
-      <c r="ANR9"/>
-      <c r="ANS9"/>
-      <c r="ANT9"/>
-      <c r="ANU9"/>
-      <c r="ANV9"/>
-      <c r="ANW9"/>
-      <c r="ANX9"/>
-      <c r="ANY9"/>
-      <c r="ANZ9"/>
-      <c r="AOA9"/>
-      <c r="AOB9"/>
-      <c r="AOC9"/>
-      <c r="AOD9"/>
-      <c r="AOE9"/>
-      <c r="AOF9"/>
-      <c r="AOG9"/>
-      <c r="AOH9"/>
-      <c r="AOI9"/>
-      <c r="AOJ9"/>
-      <c r="AOK9"/>
-      <c r="AOL9"/>
-      <c r="AOM9"/>
-      <c r="AON9"/>
-      <c r="AOO9"/>
-      <c r="AOP9"/>
-      <c r="AOQ9"/>
-      <c r="AOR9"/>
-      <c r="AOS9"/>
-      <c r="AOT9"/>
-      <c r="AOU9"/>
-      <c r="AOV9"/>
-      <c r="AOW9"/>
-      <c r="AOX9"/>
-      <c r="AOY9"/>
-      <c r="AOZ9"/>
-      <c r="APA9"/>
-      <c r="APB9"/>
-      <c r="APC9"/>
-      <c r="APD9"/>
-      <c r="APE9"/>
-      <c r="APF9"/>
-      <c r="APG9"/>
-      <c r="APH9"/>
-      <c r="API9"/>
-      <c r="APJ9"/>
-      <c r="APK9"/>
-      <c r="APL9"/>
-      <c r="APM9"/>
-      <c r="APN9"/>
-      <c r="APO9"/>
-      <c r="APP9"/>
-      <c r="APQ9"/>
-      <c r="APR9"/>
-      <c r="APS9"/>
-      <c r="APT9"/>
-      <c r="APU9"/>
-      <c r="APV9"/>
-      <c r="APW9"/>
-      <c r="APX9"/>
-      <c r="APY9"/>
-      <c r="APZ9"/>
-      <c r="AQA9"/>
-      <c r="AQB9"/>
-      <c r="AQC9"/>
-      <c r="AQD9"/>
-      <c r="AQE9"/>
-      <c r="AQF9"/>
-      <c r="AQG9"/>
-      <c r="AQH9"/>
-      <c r="AQI9"/>
-      <c r="AQJ9"/>
-      <c r="AQK9"/>
-      <c r="AQL9"/>
-      <c r="AQM9"/>
-      <c r="AQN9"/>
-      <c r="AQO9"/>
-      <c r="AQP9"/>
-      <c r="AQQ9"/>
-      <c r="AQR9"/>
-      <c r="AQS9"/>
-      <c r="AQT9"/>
-      <c r="AQU9"/>
-      <c r="AQV9"/>
-      <c r="AQW9"/>
-      <c r="AQX9"/>
-      <c r="AQY9"/>
-      <c r="AQZ9"/>
-      <c r="ARA9"/>
-      <c r="ARB9"/>
-      <c r="ARC9"/>
-      <c r="ARD9"/>
-      <c r="ARE9"/>
-    </row>
-    <row r="10" spans="1:1149" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G10"/>
-      <c r="H10"/>
-      <c r="I10"/>
-      <c r="J10"/>
-      <c r="K10"/>
-      <c r="L10"/>
-      <c r="M10"/>
-      <c r="N10"/>
-      <c r="O10"/>
-      <c r="P10"/>
-      <c r="Q10"/>
-      <c r="R10"/>
-      <c r="S10"/>
-      <c r="T10"/>
-      <c r="U10"/>
-      <c r="V10"/>
-      <c r="W10"/>
-      <c r="X10"/>
-      <c r="Y10"/>
-      <c r="Z10"/>
-      <c r="AA10"/>
-      <c r="AB10"/>
-      <c r="AC10"/>
-      <c r="AD10"/>
-      <c r="AE10"/>
-      <c r="AF10"/>
-      <c r="AG10"/>
-      <c r="AH10"/>
-      <c r="AI10"/>
-      <c r="AJ10"/>
-      <c r="AK10"/>
-      <c r="AL10"/>
-      <c r="AM10"/>
-      <c r="AN10"/>
-      <c r="AO10"/>
-      <c r="AP10"/>
-      <c r="AQ10"/>
-      <c r="AR10"/>
-      <c r="AS10"/>
-      <c r="AT10"/>
-      <c r="AU10"/>
-      <c r="AV10"/>
-      <c r="AW10"/>
-      <c r="AX10"/>
-      <c r="AY10"/>
-      <c r="AZ10"/>
-      <c r="BA10"/>
-      <c r="BB10"/>
-      <c r="BC10"/>
-      <c r="BD10"/>
-      <c r="BE10"/>
-      <c r="BF10"/>
-      <c r="BG10"/>
-      <c r="BH10"/>
-      <c r="BI10"/>
-      <c r="BJ10"/>
-      <c r="BK10"/>
-      <c r="BL10"/>
-      <c r="BM10"/>
-      <c r="BN10"/>
-      <c r="BO10"/>
-      <c r="BP10"/>
-      <c r="BQ10"/>
-      <c r="BR10"/>
-      <c r="BS10"/>
-      <c r="BT10"/>
-      <c r="BU10"/>
-      <c r="BV10"/>
-      <c r="BW10"/>
-      <c r="BX10"/>
-      <c r="BY10"/>
-      <c r="BZ10"/>
-      <c r="CA10"/>
-      <c r="CB10"/>
-      <c r="CC10"/>
-      <c r="CD10"/>
-      <c r="CE10"/>
-      <c r="CF10"/>
-      <c r="CG10"/>
-      <c r="CH10"/>
-      <c r="CI10"/>
-      <c r="CJ10"/>
-      <c r="CK10"/>
-      <c r="CL10"/>
-      <c r="CM10"/>
-      <c r="CN10"/>
-      <c r="CO10"/>
-      <c r="CP10"/>
-      <c r="CQ10"/>
-      <c r="CR10"/>
-      <c r="CS10"/>
-      <c r="CT10"/>
-      <c r="CU10"/>
-      <c r="CV10"/>
-      <c r="CW10"/>
-      <c r="CX10"/>
-      <c r="CY10"/>
-      <c r="CZ10"/>
-      <c r="DA10"/>
-      <c r="DB10"/>
-      <c r="DC10"/>
-      <c r="DD10"/>
-      <c r="DE10"/>
-      <c r="DF10"/>
-      <c r="DG10"/>
-      <c r="DH10"/>
-      <c r="DI10"/>
-      <c r="DJ10"/>
-      <c r="DK10"/>
-      <c r="DL10"/>
-      <c r="DM10"/>
-      <c r="DN10"/>
-      <c r="DO10"/>
-      <c r="DP10"/>
-      <c r="DQ10"/>
-      <c r="DR10"/>
-      <c r="DS10"/>
-      <c r="DT10"/>
-      <c r="DU10"/>
-      <c r="DV10"/>
-      <c r="DW10"/>
-      <c r="DX10"/>
-      <c r="DY10"/>
-      <c r="DZ10"/>
-      <c r="EA10"/>
-      <c r="EB10"/>
-      <c r="EC10"/>
-      <c r="ED10"/>
-      <c r="EE10"/>
-      <c r="EF10"/>
-      <c r="EG10"/>
-      <c r="EH10"/>
-      <c r="EI10"/>
-      <c r="EJ10"/>
-      <c r="EK10"/>
-      <c r="EL10"/>
-      <c r="EM10"/>
-      <c r="EN10"/>
-      <c r="EO10"/>
-      <c r="EP10"/>
-      <c r="EQ10"/>
-      <c r="ER10"/>
-      <c r="ES10"/>
-      <c r="ET10"/>
-      <c r="EU10"/>
-      <c r="EV10"/>
-      <c r="EW10"/>
-      <c r="EX10"/>
-      <c r="EY10"/>
-      <c r="EZ10"/>
-      <c r="FA10"/>
-      <c r="FB10"/>
-      <c r="FC10"/>
-      <c r="FD10"/>
-      <c r="FE10"/>
-      <c r="FF10"/>
-      <c r="FG10"/>
-      <c r="FH10"/>
-      <c r="FI10"/>
-      <c r="FJ10"/>
-      <c r="FK10"/>
-      <c r="FL10"/>
-      <c r="FM10"/>
-      <c r="FN10"/>
-      <c r="FO10"/>
-      <c r="FP10"/>
-      <c r="FQ10"/>
-      <c r="FR10"/>
-      <c r="FS10"/>
-      <c r="FT10"/>
-      <c r="FU10"/>
-      <c r="FV10"/>
-      <c r="FW10"/>
-      <c r="FX10"/>
-      <c r="FY10"/>
-      <c r="FZ10"/>
-      <c r="GA10"/>
-      <c r="GB10"/>
-      <c r="GC10"/>
-      <c r="GD10"/>
-      <c r="GE10"/>
-      <c r="GF10"/>
-      <c r="GG10"/>
-      <c r="GH10"/>
-      <c r="GI10"/>
-      <c r="GJ10"/>
-      <c r="GK10"/>
-      <c r="GL10"/>
-      <c r="GM10"/>
-      <c r="GN10"/>
-      <c r="GO10"/>
-      <c r="GP10"/>
-      <c r="GQ10"/>
-      <c r="GR10"/>
-      <c r="GS10"/>
-      <c r="GT10"/>
-      <c r="GU10"/>
-      <c r="GV10"/>
-      <c r="GW10"/>
-      <c r="GX10"/>
-      <c r="GY10"/>
-      <c r="GZ10"/>
-      <c r="HA10"/>
-      <c r="HB10"/>
-      <c r="HC10"/>
-      <c r="HD10"/>
-      <c r="HE10"/>
-      <c r="HF10"/>
-      <c r="HG10"/>
-      <c r="HH10"/>
-      <c r="HI10"/>
-      <c r="HJ10"/>
-      <c r="HK10"/>
-      <c r="HL10"/>
-      <c r="HM10"/>
-      <c r="HN10"/>
-      <c r="HO10"/>
-      <c r="HP10"/>
-      <c r="HQ10"/>
-      <c r="HR10"/>
-      <c r="HS10"/>
-      <c r="HT10"/>
-      <c r="HU10"/>
-      <c r="HV10"/>
-      <c r="HW10"/>
-      <c r="HX10"/>
-      <c r="HY10"/>
-      <c r="HZ10"/>
-      <c r="IA10"/>
-      <c r="IB10"/>
-      <c r="IC10"/>
-      <c r="ID10"/>
-      <c r="IE10"/>
-      <c r="IF10"/>
-      <c r="IG10"/>
-      <c r="IH10"/>
-      <c r="II10"/>
-      <c r="IJ10"/>
-      <c r="IK10"/>
-      <c r="IL10"/>
-      <c r="IM10"/>
-      <c r="IN10"/>
-      <c r="IO10"/>
-      <c r="IP10"/>
-      <c r="IQ10"/>
-      <c r="IR10"/>
-      <c r="IS10"/>
-      <c r="IT10"/>
-      <c r="IU10"/>
-      <c r="IV10"/>
-      <c r="IW10"/>
-      <c r="IX10"/>
-      <c r="IY10"/>
-      <c r="IZ10"/>
-      <c r="JA10"/>
-      <c r="JB10"/>
-      <c r="JC10"/>
-      <c r="JD10"/>
-      <c r="JE10"/>
-      <c r="JF10"/>
-      <c r="JG10"/>
-      <c r="JH10"/>
-      <c r="JI10"/>
-      <c r="JJ10"/>
-      <c r="JK10"/>
-      <c r="JL10"/>
-      <c r="JM10"/>
-      <c r="JN10"/>
-      <c r="JO10"/>
-      <c r="JP10"/>
-      <c r="JQ10"/>
-      <c r="JR10"/>
-      <c r="JS10"/>
-      <c r="JT10"/>
-      <c r="JU10"/>
-      <c r="JV10"/>
-      <c r="JW10"/>
-      <c r="JX10"/>
-      <c r="JY10"/>
-      <c r="JZ10"/>
-      <c r="KA10"/>
-      <c r="KB10"/>
-      <c r="KC10"/>
-      <c r="KD10"/>
-      <c r="KE10"/>
-      <c r="KF10"/>
-      <c r="KG10"/>
-      <c r="KH10"/>
-      <c r="KI10"/>
-      <c r="KJ10"/>
-      <c r="KK10"/>
-      <c r="KL10"/>
-      <c r="KM10"/>
-      <c r="KN10"/>
-      <c r="KO10"/>
-      <c r="KP10"/>
-      <c r="KQ10"/>
-      <c r="KR10"/>
-      <c r="KS10"/>
-      <c r="KT10"/>
-      <c r="KU10"/>
-      <c r="KV10"/>
-      <c r="KW10"/>
-      <c r="KX10"/>
-      <c r="KY10"/>
-      <c r="KZ10"/>
-      <c r="LA10"/>
-      <c r="LB10"/>
-      <c r="LC10"/>
-      <c r="LD10"/>
-      <c r="LE10"/>
-      <c r="LF10"/>
-      <c r="LG10"/>
-      <c r="LH10"/>
-      <c r="LI10"/>
-      <c r="LJ10"/>
-      <c r="LK10"/>
-      <c r="LL10"/>
-      <c r="LM10"/>
-      <c r="LN10"/>
-      <c r="LO10"/>
-      <c r="LP10"/>
-      <c r="LQ10"/>
-      <c r="LR10"/>
-      <c r="LS10"/>
-      <c r="LT10"/>
-      <c r="LU10"/>
-      <c r="LV10"/>
-      <c r="LW10"/>
-      <c r="LX10"/>
-      <c r="LY10"/>
-      <c r="LZ10"/>
-      <c r="MA10"/>
-      <c r="MB10"/>
-      <c r="MC10"/>
-      <c r="MD10"/>
-      <c r="ME10"/>
-      <c r="MF10"/>
-      <c r="MG10"/>
-      <c r="MH10"/>
-      <c r="MI10"/>
-      <c r="MJ10"/>
-      <c r="MK10"/>
-      <c r="ML10"/>
-      <c r="MM10"/>
-      <c r="MN10"/>
-      <c r="MO10"/>
-      <c r="MP10"/>
-      <c r="MQ10"/>
-      <c r="MR10"/>
-      <c r="MS10"/>
-      <c r="MT10"/>
-      <c r="MU10"/>
-      <c r="MV10"/>
-      <c r="MW10"/>
-      <c r="MX10"/>
-      <c r="MY10"/>
-      <c r="MZ10"/>
-      <c r="NA10"/>
-      <c r="NB10"/>
-      <c r="NC10"/>
-      <c r="ND10"/>
-      <c r="NE10"/>
-      <c r="NF10"/>
-      <c r="NG10"/>
-      <c r="NH10"/>
-      <c r="NI10"/>
-      <c r="NJ10"/>
-      <c r="NK10"/>
-      <c r="NL10"/>
-      <c r="NM10"/>
-      <c r="NN10"/>
-      <c r="NO10"/>
-      <c r="NP10"/>
-      <c r="NQ10"/>
-      <c r="NR10"/>
-      <c r="NS10"/>
-      <c r="NT10"/>
-      <c r="NU10"/>
-      <c r="NV10"/>
-      <c r="NW10"/>
-      <c r="NX10"/>
-      <c r="NY10"/>
-      <c r="NZ10"/>
-      <c r="OA10"/>
-      <c r="OB10"/>
-      <c r="OC10"/>
-      <c r="OD10"/>
-      <c r="OE10"/>
-      <c r="OF10"/>
-      <c r="OG10"/>
-      <c r="OH10"/>
-      <c r="OI10"/>
-      <c r="OJ10"/>
-      <c r="OK10"/>
-      <c r="OL10"/>
-      <c r="OM10"/>
-      <c r="ON10"/>
-      <c r="OO10"/>
-      <c r="OP10"/>
-      <c r="OQ10"/>
-      <c r="OR10"/>
-      <c r="OS10"/>
-      <c r="OT10"/>
-      <c r="OU10"/>
-      <c r="OV10"/>
-      <c r="OW10"/>
-      <c r="OX10"/>
-      <c r="OY10"/>
-      <c r="OZ10"/>
-      <c r="PA10"/>
-      <c r="PB10"/>
-      <c r="PC10"/>
-      <c r="PD10"/>
-      <c r="PE10"/>
-      <c r="PF10"/>
-      <c r="PG10"/>
-      <c r="PH10"/>
-      <c r="PI10"/>
-      <c r="PJ10"/>
-      <c r="PK10"/>
-      <c r="PL10"/>
-      <c r="PM10"/>
-      <c r="PN10"/>
-      <c r="PO10"/>
-      <c r="PP10"/>
-      <c r="PQ10"/>
-      <c r="PR10"/>
-      <c r="PS10"/>
-      <c r="PT10"/>
-      <c r="PU10"/>
-      <c r="PV10"/>
-      <c r="PW10"/>
-      <c r="PX10"/>
-      <c r="PY10"/>
-      <c r="PZ10"/>
-      <c r="QA10"/>
-      <c r="QB10"/>
-      <c r="QC10"/>
-      <c r="QD10"/>
-      <c r="QE10"/>
-      <c r="QF10"/>
-      <c r="QG10"/>
-      <c r="QH10"/>
-      <c r="QI10"/>
-      <c r="QJ10"/>
-      <c r="QK10"/>
-      <c r="QL10"/>
-      <c r="QM10"/>
-      <c r="QN10"/>
-      <c r="QO10"/>
-      <c r="QP10"/>
-      <c r="QQ10"/>
-      <c r="QR10"/>
-      <c r="QS10"/>
-      <c r="QT10"/>
-      <c r="QU10"/>
-      <c r="QV10"/>
-      <c r="QW10"/>
-      <c r="QX10"/>
-      <c r="QY10"/>
-      <c r="QZ10"/>
-      <c r="RA10"/>
-      <c r="RB10"/>
-      <c r="RC10"/>
-      <c r="RD10"/>
-      <c r="RE10"/>
-      <c r="RF10"/>
-      <c r="RG10"/>
-      <c r="RH10"/>
-      <c r="RI10"/>
-      <c r="RJ10"/>
-      <c r="RK10"/>
-      <c r="RL10"/>
-      <c r="RM10"/>
-      <c r="RN10"/>
-      <c r="RO10"/>
-      <c r="RP10"/>
-      <c r="RQ10"/>
-      <c r="RR10"/>
-      <c r="RS10"/>
-      <c r="RT10"/>
-      <c r="RU10"/>
-      <c r="RV10"/>
-      <c r="RW10"/>
-      <c r="RX10"/>
-      <c r="RY10"/>
-      <c r="RZ10"/>
-      <c r="SA10"/>
-      <c r="SB10"/>
-      <c r="SC10"/>
-      <c r="SD10"/>
-      <c r="SE10"/>
-      <c r="SF10"/>
-      <c r="SG10"/>
-      <c r="SH10"/>
-      <c r="SI10"/>
-      <c r="SJ10"/>
-      <c r="SK10"/>
-      <c r="SL10"/>
-      <c r="SM10"/>
-      <c r="SN10"/>
-      <c r="SO10"/>
-      <c r="SP10"/>
-      <c r="SQ10"/>
-      <c r="SR10"/>
-      <c r="SS10"/>
-      <c r="ST10"/>
-      <c r="SU10"/>
-      <c r="SV10"/>
-      <c r="SW10"/>
-      <c r="SX10"/>
-      <c r="SY10"/>
-      <c r="SZ10"/>
-      <c r="TA10"/>
-      <c r="TB10"/>
-      <c r="TC10"/>
-      <c r="TD10"/>
-      <c r="TE10"/>
-      <c r="TF10"/>
-      <c r="TG10"/>
-      <c r="TH10"/>
-      <c r="TI10"/>
-      <c r="TJ10"/>
-      <c r="TK10"/>
-      <c r="TL10"/>
-      <c r="TM10"/>
-      <c r="TN10"/>
-      <c r="TO10"/>
-      <c r="TP10"/>
-      <c r="TQ10"/>
-      <c r="TR10"/>
-      <c r="TS10"/>
-      <c r="TT10"/>
-      <c r="TU10"/>
-      <c r="TV10"/>
-      <c r="TW10"/>
-      <c r="TX10"/>
-      <c r="TY10"/>
-      <c r="TZ10"/>
-      <c r="UA10"/>
-      <c r="UB10"/>
-      <c r="UC10"/>
-      <c r="UD10"/>
-      <c r="UE10"/>
-      <c r="UF10"/>
-      <c r="UG10"/>
-      <c r="UH10"/>
-      <c r="UI10"/>
-      <c r="UJ10"/>
-      <c r="UK10"/>
-      <c r="UL10"/>
-      <c r="UM10"/>
-      <c r="UN10"/>
-      <c r="UO10"/>
-      <c r="UP10"/>
-      <c r="UQ10"/>
-      <c r="UR10"/>
-      <c r="US10"/>
-      <c r="UT10"/>
-      <c r="UU10"/>
-      <c r="UV10"/>
-      <c r="UW10"/>
-      <c r="UX10"/>
-      <c r="UY10"/>
-      <c r="UZ10"/>
-      <c r="VA10"/>
-      <c r="VB10"/>
-      <c r="VC10"/>
-      <c r="VD10"/>
-      <c r="VE10"/>
-      <c r="VF10"/>
-      <c r="VG10"/>
-      <c r="VH10"/>
-      <c r="VI10"/>
-      <c r="VJ10"/>
-      <c r="VK10"/>
-      <c r="VL10"/>
-      <c r="VM10"/>
-      <c r="VN10"/>
-      <c r="VO10"/>
-      <c r="VP10"/>
-      <c r="VQ10"/>
-      <c r="VR10"/>
-      <c r="VS10"/>
-      <c r="VT10"/>
-      <c r="VU10"/>
-      <c r="VV10"/>
-      <c r="VW10"/>
-      <c r="VX10"/>
-      <c r="VY10"/>
-      <c r="VZ10"/>
-      <c r="WA10"/>
-      <c r="WB10"/>
-      <c r="WC10"/>
-      <c r="WD10"/>
-      <c r="WE10"/>
-      <c r="WF10"/>
-      <c r="WG10"/>
-      <c r="WH10"/>
-      <c r="WI10"/>
-      <c r="WJ10"/>
-      <c r="WK10"/>
-      <c r="WL10"/>
-      <c r="WM10"/>
-      <c r="WN10"/>
-      <c r="WO10"/>
-      <c r="WP10"/>
-      <c r="WQ10"/>
-      <c r="WR10"/>
-      <c r="WS10"/>
-      <c r="WT10"/>
-      <c r="WU10"/>
-      <c r="WV10"/>
-      <c r="WW10"/>
-      <c r="WX10"/>
-      <c r="WY10"/>
-      <c r="WZ10"/>
-      <c r="XA10"/>
-      <c r="XB10"/>
-      <c r="XC10"/>
-      <c r="XD10"/>
-      <c r="XE10"/>
-      <c r="XF10"/>
-      <c r="XG10"/>
-      <c r="XH10"/>
-      <c r="XI10"/>
-      <c r="XJ10"/>
-      <c r="XK10"/>
-      <c r="XL10"/>
-      <c r="XM10"/>
-      <c r="XN10"/>
-      <c r="XO10"/>
-      <c r="XP10"/>
-      <c r="XQ10"/>
-      <c r="XR10"/>
-      <c r="XS10"/>
-      <c r="XT10"/>
-      <c r="XU10"/>
-      <c r="XV10"/>
-      <c r="XW10"/>
-      <c r="XX10"/>
-      <c r="XY10"/>
-      <c r="XZ10"/>
-      <c r="YA10"/>
-      <c r="YB10"/>
-      <c r="YC10"/>
-      <c r="YD10"/>
-      <c r="YE10"/>
-      <c r="YF10"/>
-      <c r="YG10"/>
-      <c r="YH10"/>
-      <c r="YI10"/>
-      <c r="YJ10"/>
-      <c r="YK10"/>
-      <c r="YL10"/>
-      <c r="YM10"/>
-      <c r="YN10"/>
-      <c r="YO10"/>
-      <c r="YP10"/>
-      <c r="YQ10"/>
-      <c r="YR10"/>
-      <c r="YS10"/>
-      <c r="YT10"/>
-      <c r="YU10"/>
-      <c r="YV10"/>
-      <c r="YW10"/>
-      <c r="YX10"/>
-      <c r="YY10"/>
-      <c r="YZ10"/>
-      <c r="ZA10"/>
-      <c r="ZB10"/>
-      <c r="ZC10"/>
-      <c r="ZD10"/>
-      <c r="ZE10"/>
-      <c r="ZF10"/>
-      <c r="ZG10"/>
-      <c r="ZH10"/>
-      <c r="ZI10"/>
-      <c r="ZJ10"/>
-      <c r="ZK10"/>
-      <c r="ZL10"/>
-      <c r="ZM10"/>
-      <c r="ZN10"/>
-      <c r="ZO10"/>
-      <c r="ZP10"/>
-      <c r="ZQ10"/>
-      <c r="ZR10"/>
-      <c r="ZS10"/>
-      <c r="ZT10"/>
-      <c r="ZU10"/>
-      <c r="ZV10"/>
-      <c r="ZW10"/>
-      <c r="ZX10"/>
-      <c r="ZY10"/>
-      <c r="ZZ10"/>
-      <c r="AAA10"/>
-      <c r="AAB10"/>
-      <c r="AAC10"/>
-      <c r="AAD10"/>
-      <c r="AAE10"/>
-      <c r="AAF10"/>
-      <c r="AAG10"/>
-      <c r="AAH10"/>
-      <c r="AAI10"/>
-      <c r="AAJ10"/>
-      <c r="AAK10"/>
-      <c r="AAL10"/>
-      <c r="AAM10"/>
-      <c r="AAN10"/>
-      <c r="AAO10"/>
-      <c r="AAP10"/>
-      <c r="AAQ10"/>
-      <c r="AAR10"/>
-      <c r="AAS10"/>
-      <c r="AAT10"/>
-      <c r="AAU10"/>
-      <c r="AAV10"/>
-      <c r="AAW10"/>
-      <c r="AAX10"/>
-      <c r="AAY10"/>
-      <c r="AAZ10"/>
-      <c r="ABA10"/>
-      <c r="ABB10"/>
-      <c r="ABC10"/>
-      <c r="ABD10"/>
-      <c r="ABE10"/>
-      <c r="ABF10"/>
-      <c r="ABG10"/>
-      <c r="ABH10"/>
-      <c r="ABI10"/>
-      <c r="ABJ10"/>
-      <c r="ABK10"/>
-      <c r="ABL10"/>
-      <c r="ABM10"/>
-      <c r="ABN10"/>
-      <c r="ABO10"/>
-      <c r="ABP10"/>
-      <c r="ABQ10"/>
-      <c r="ABR10"/>
-      <c r="ABS10"/>
-      <c r="ABT10"/>
-      <c r="ABU10"/>
-      <c r="ABV10"/>
-      <c r="ABW10"/>
-      <c r="ABX10"/>
-      <c r="ABY10"/>
-      <c r="ABZ10"/>
-      <c r="ACA10"/>
-      <c r="ACB10"/>
-      <c r="ACC10"/>
-      <c r="ACD10"/>
-      <c r="ACE10"/>
-      <c r="ACF10"/>
-      <c r="ACG10"/>
-      <c r="ACH10"/>
-      <c r="ACI10"/>
-      <c r="ACJ10"/>
-      <c r="ACK10"/>
-      <c r="ACL10"/>
-      <c r="ACM10"/>
-      <c r="ACN10"/>
-      <c r="ACO10"/>
-      <c r="ACP10"/>
-      <c r="ACQ10"/>
-      <c r="ACR10"/>
-      <c r="ACS10"/>
-      <c r="ACT10"/>
-      <c r="ACU10"/>
-      <c r="ACV10"/>
-      <c r="ACW10"/>
-      <c r="ACX10"/>
-      <c r="ACY10"/>
-      <c r="ACZ10"/>
-      <c r="ADA10"/>
-      <c r="ADB10"/>
-      <c r="ADC10"/>
-      <c r="ADD10"/>
-      <c r="ADE10"/>
-      <c r="ADF10"/>
-      <c r="ADG10"/>
-      <c r="ADH10"/>
-      <c r="ADI10"/>
-      <c r="ADJ10"/>
-      <c r="ADK10"/>
-      <c r="ADL10"/>
-      <c r="ADM10"/>
-      <c r="ADN10"/>
-      <c r="ADO10"/>
-      <c r="ADP10"/>
-      <c r="ADQ10"/>
-      <c r="ADR10"/>
-      <c r="ADS10"/>
-      <c r="ADT10"/>
-      <c r="ADU10"/>
-      <c r="ADV10"/>
-      <c r="ADW10"/>
-      <c r="ADX10"/>
-      <c r="ADY10"/>
-      <c r="ADZ10"/>
-      <c r="AEA10"/>
-      <c r="AEB10"/>
-      <c r="AEC10"/>
-      <c r="AED10"/>
-      <c r="AEE10"/>
-      <c r="AEF10"/>
-      <c r="AEG10"/>
-      <c r="AEH10"/>
-      <c r="AEI10"/>
-      <c r="AEJ10"/>
-      <c r="AEK10"/>
-      <c r="AEL10"/>
-      <c r="AEM10"/>
-      <c r="AEN10"/>
-      <c r="AEO10"/>
-      <c r="AEP10"/>
-      <c r="AEQ10"/>
-      <c r="AER10"/>
-      <c r="AES10"/>
-      <c r="AET10"/>
-      <c r="AEU10"/>
-      <c r="AEV10"/>
-      <c r="AEW10"/>
-      <c r="AEX10"/>
-      <c r="AEY10"/>
-      <c r="AEZ10"/>
-      <c r="AFA10"/>
-      <c r="AFB10"/>
-      <c r="AFC10"/>
-      <c r="AFD10"/>
-      <c r="AFE10"/>
-      <c r="AFF10"/>
-      <c r="AFG10"/>
-      <c r="AFH10"/>
-      <c r="AFI10"/>
-      <c r="AFJ10"/>
-      <c r="AFK10"/>
-      <c r="AFL10"/>
-      <c r="AFM10"/>
-      <c r="AFN10"/>
-      <c r="AFO10"/>
-      <c r="AFP10"/>
-      <c r="AFQ10"/>
-      <c r="AFR10"/>
-      <c r="AFS10"/>
-      <c r="AFT10"/>
-      <c r="AFU10"/>
-      <c r="AFV10"/>
-      <c r="AFW10"/>
-      <c r="AFX10"/>
-      <c r="AFY10"/>
-      <c r="AFZ10"/>
-      <c r="AGA10"/>
-      <c r="AGB10"/>
-      <c r="AGC10"/>
-      <c r="AGD10"/>
-      <c r="AGE10"/>
-      <c r="AGF10"/>
-      <c r="AGG10"/>
-      <c r="AGH10"/>
-      <c r="AGI10"/>
-      <c r="AGJ10"/>
-      <c r="AGK10"/>
-      <c r="AGL10"/>
-      <c r="AGM10"/>
-      <c r="AGN10"/>
-      <c r="AGO10"/>
-      <c r="AGP10"/>
-      <c r="AGQ10"/>
-      <c r="AGR10"/>
-      <c r="AGS10"/>
-      <c r="AGT10"/>
-      <c r="AGU10"/>
-      <c r="AGV10"/>
-      <c r="AGW10"/>
-      <c r="AGX10"/>
-      <c r="AGY10"/>
-      <c r="AGZ10"/>
-      <c r="AHA10"/>
-      <c r="AHB10"/>
-      <c r="AHC10"/>
-      <c r="AHD10"/>
-      <c r="AHE10"/>
-      <c r="AHF10"/>
-      <c r="AHG10"/>
-      <c r="AHH10"/>
-      <c r="AHI10"/>
-      <c r="AHJ10"/>
-      <c r="AHK10"/>
-      <c r="AHL10"/>
-      <c r="AHM10"/>
-      <c r="AHN10"/>
-      <c r="AHO10"/>
-      <c r="AHP10"/>
-      <c r="AHQ10"/>
-      <c r="AHR10"/>
-      <c r="AHS10"/>
-      <c r="AHT10"/>
-      <c r="AHU10"/>
-      <c r="AHV10"/>
-      <c r="AHW10"/>
-      <c r="AHX10"/>
-      <c r="AHY10"/>
-      <c r="AHZ10"/>
-      <c r="AIA10"/>
-      <c r="AIB10"/>
-      <c r="AIC10"/>
-      <c r="AID10"/>
-      <c r="AIE10"/>
-      <c r="AIF10"/>
-      <c r="AIG10"/>
-      <c r="AIH10"/>
-      <c r="AII10"/>
-      <c r="AIJ10"/>
-      <c r="AIK10"/>
-      <c r="AIL10"/>
-      <c r="AIM10"/>
-      <c r="AIN10"/>
-      <c r="AIO10"/>
-      <c r="AIP10"/>
-      <c r="AIQ10"/>
-      <c r="AIR10"/>
-      <c r="AIS10"/>
-      <c r="AIT10"/>
-      <c r="AIU10"/>
-      <c r="AIV10"/>
-      <c r="AIW10"/>
-      <c r="AIX10"/>
-      <c r="AIY10"/>
-      <c r="AIZ10"/>
-      <c r="AJA10"/>
-      <c r="AJB10"/>
-      <c r="AJC10"/>
-      <c r="AJD10"/>
-      <c r="AJE10"/>
-      <c r="AJF10"/>
-      <c r="AJG10"/>
-      <c r="AJH10"/>
-      <c r="AJI10"/>
-      <c r="AJJ10"/>
-      <c r="AJK10"/>
-      <c r="AJL10"/>
-      <c r="AJM10"/>
-      <c r="AJN10"/>
-      <c r="AJO10"/>
-      <c r="AJP10"/>
-      <c r="AJQ10"/>
-      <c r="AJR10"/>
-      <c r="AJS10"/>
-      <c r="AJT10"/>
-      <c r="AJU10"/>
-      <c r="AJV10"/>
-      <c r="AJW10"/>
-      <c r="AJX10"/>
-      <c r="AJY10"/>
-      <c r="AJZ10"/>
-      <c r="AKA10"/>
-      <c r="AKB10"/>
-      <c r="AKC10"/>
-      <c r="AKD10"/>
-      <c r="AKE10"/>
-      <c r="AKF10"/>
-      <c r="AKG10"/>
-      <c r="AKH10"/>
-      <c r="AKI10"/>
-      <c r="AKJ10"/>
-      <c r="AKK10"/>
-      <c r="AKL10"/>
-      <c r="AKM10"/>
-      <c r="AKN10"/>
-      <c r="AKO10"/>
-      <c r="AKP10"/>
-      <c r="AKQ10"/>
-      <c r="AKR10"/>
-      <c r="AKS10"/>
-      <c r="AKT10"/>
-      <c r="AKU10"/>
-      <c r="AKV10"/>
-      <c r="AKW10"/>
-      <c r="AKX10"/>
-      <c r="AKY10"/>
-      <c r="AKZ10"/>
-      <c r="ALA10"/>
-      <c r="ALB10"/>
-      <c r="ALC10"/>
-      <c r="ALD10"/>
-      <c r="ALE10"/>
-      <c r="ALF10"/>
-      <c r="ALG10"/>
-      <c r="ALH10"/>
-      <c r="ALI10"/>
-      <c r="ALJ10"/>
-      <c r="ALK10"/>
-      <c r="ALL10"/>
-      <c r="ALM10"/>
-      <c r="ALN10"/>
-      <c r="ALO10"/>
-      <c r="ALP10"/>
-      <c r="ALQ10"/>
-      <c r="ALR10"/>
-      <c r="ALS10"/>
-      <c r="ALT10"/>
-      <c r="ALU10"/>
-      <c r="ALV10"/>
-      <c r="ALW10"/>
-      <c r="ALX10"/>
-      <c r="ALY10"/>
-      <c r="ALZ10"/>
-      <c r="AMA10"/>
-      <c r="AMB10"/>
-      <c r="AMC10"/>
-      <c r="AMD10"/>
-      <c r="AME10"/>
-      <c r="AMF10"/>
-      <c r="AMG10"/>
-      <c r="AMH10"/>
-      <c r="AMI10"/>
-      <c r="AMJ10"/>
-      <c r="AMK10"/>
-      <c r="AML10"/>
-      <c r="AMM10"/>
-      <c r="AMN10"/>
-      <c r="AMO10"/>
-      <c r="AMP10"/>
-      <c r="AMQ10"/>
-      <c r="AMR10"/>
-      <c r="AMS10"/>
-      <c r="AMT10"/>
-      <c r="AMU10"/>
-      <c r="AMV10"/>
-      <c r="AMW10"/>
-      <c r="AMX10"/>
-      <c r="AMY10"/>
-      <c r="AMZ10"/>
-      <c r="ANA10"/>
-      <c r="ANB10"/>
-      <c r="ANC10"/>
-      <c r="AND10"/>
-      <c r="ANE10"/>
-      <c r="ANF10"/>
-      <c r="ANG10"/>
-      <c r="ANH10"/>
-      <c r="ANI10"/>
-      <c r="ANJ10"/>
-      <c r="ANK10"/>
-      <c r="ANL10"/>
-      <c r="ANM10"/>
-      <c r="ANN10"/>
-      <c r="ANO10"/>
-      <c r="ANP10"/>
-      <c r="ANQ10"/>
-      <c r="ANR10"/>
-      <c r="ANS10"/>
-      <c r="ANT10"/>
-      <c r="ANU10"/>
-      <c r="ANV10"/>
-      <c r="ANW10"/>
-      <c r="ANX10"/>
-      <c r="ANY10"/>
-      <c r="ANZ10"/>
-      <c r="AOA10"/>
-      <c r="AOB10"/>
-      <c r="AOC10"/>
-      <c r="AOD10"/>
-      <c r="AOE10"/>
-      <c r="AOF10"/>
-      <c r="AOG10"/>
-      <c r="AOH10"/>
-      <c r="AOI10"/>
-      <c r="AOJ10"/>
-      <c r="AOK10"/>
-      <c r="AOL10"/>
-      <c r="AOM10"/>
-      <c r="AON10"/>
-      <c r="AOO10"/>
-      <c r="AOP10"/>
-      <c r="AOQ10"/>
-      <c r="AOR10"/>
-      <c r="AOS10"/>
-      <c r="AOT10"/>
-      <c r="AOU10"/>
-      <c r="AOV10"/>
-      <c r="AOW10"/>
-      <c r="AOX10"/>
-      <c r="AOY10"/>
-      <c r="AOZ10"/>
-      <c r="APA10"/>
-      <c r="APB10"/>
-      <c r="APC10"/>
-      <c r="APD10"/>
-      <c r="APE10"/>
-      <c r="APF10"/>
-      <c r="APG10"/>
-      <c r="APH10"/>
-      <c r="API10"/>
-      <c r="APJ10"/>
-      <c r="APK10"/>
-      <c r="APL10"/>
-      <c r="APM10"/>
-      <c r="APN10"/>
-      <c r="APO10"/>
-      <c r="APP10"/>
-      <c r="APQ10"/>
-      <c r="APR10"/>
-      <c r="APS10"/>
-      <c r="APT10"/>
-      <c r="APU10"/>
-      <c r="APV10"/>
-      <c r="APW10"/>
-      <c r="APX10"/>
-      <c r="APY10"/>
-      <c r="APZ10"/>
-      <c r="AQA10"/>
-      <c r="AQB10"/>
-      <c r="AQC10"/>
-      <c r="AQD10"/>
-      <c r="AQE10"/>
-      <c r="AQF10"/>
-      <c r="AQG10"/>
-      <c r="AQH10"/>
-      <c r="AQI10"/>
-      <c r="AQJ10"/>
-      <c r="AQK10"/>
-      <c r="AQL10"/>
-      <c r="AQM10"/>
-      <c r="AQN10"/>
-      <c r="AQO10"/>
-      <c r="AQP10"/>
-      <c r="AQQ10"/>
-      <c r="AQR10"/>
-      <c r="AQS10"/>
-      <c r="AQT10"/>
-      <c r="AQU10"/>
-      <c r="AQV10"/>
-      <c r="AQW10"/>
-      <c r="AQX10"/>
-      <c r="AQY10"/>
-      <c r="AQZ10"/>
-      <c r="ARA10"/>
-      <c r="ARB10"/>
-      <c r="ARC10"/>
-      <c r="ARD10"/>
-      <c r="ARE10"/>
-    </row>
-    <row r="11" spans="1:1149" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="G11"/>
-      <c r="H11"/>
-      <c r="I11"/>
-      <c r="J11"/>
-      <c r="K11"/>
-      <c r="L11"/>
-      <c r="M11"/>
-      <c r="N11"/>
-      <c r="O11"/>
-      <c r="P11"/>
-      <c r="Q11"/>
-      <c r="R11"/>
-      <c r="S11"/>
-      <c r="T11"/>
-      <c r="U11"/>
-      <c r="V11"/>
-      <c r="W11"/>
-      <c r="X11"/>
-      <c r="Y11"/>
-      <c r="Z11"/>
-      <c r="AA11"/>
-      <c r="AB11"/>
-      <c r="AC11"/>
-      <c r="AD11"/>
-      <c r="AE11"/>
-      <c r="AF11"/>
-      <c r="AG11"/>
-      <c r="AH11"/>
-      <c r="AI11"/>
-      <c r="AJ11"/>
-      <c r="AK11"/>
-      <c r="AL11"/>
-      <c r="AM11"/>
-      <c r="AN11"/>
-      <c r="AO11"/>
-      <c r="AP11"/>
-      <c r="AQ11"/>
-      <c r="AR11"/>
-      <c r="AS11"/>
-      <c r="AT11"/>
-      <c r="AU11"/>
-      <c r="AV11"/>
-      <c r="AW11"/>
-      <c r="AX11"/>
-      <c r="AY11"/>
-      <c r="AZ11"/>
-      <c r="BA11"/>
-      <c r="BB11"/>
-      <c r="BC11"/>
-      <c r="BD11"/>
-      <c r="BE11"/>
-      <c r="BF11"/>
-      <c r="BG11"/>
-      <c r="BH11"/>
-      <c r="BI11"/>
-      <c r="BJ11"/>
-      <c r="BK11"/>
-      <c r="BL11"/>
-      <c r="BM11"/>
-      <c r="BN11"/>
-      <c r="BO11"/>
-      <c r="BP11"/>
-      <c r="BQ11"/>
-      <c r="BR11"/>
-      <c r="BS11"/>
-      <c r="BT11"/>
-      <c r="BU11"/>
-      <c r="BV11"/>
-      <c r="BW11"/>
-      <c r="BX11"/>
-      <c r="BY11"/>
-      <c r="BZ11"/>
-      <c r="CA11"/>
-      <c r="CB11"/>
-      <c r="CC11"/>
-      <c r="CD11"/>
-      <c r="CE11"/>
-      <c r="CF11"/>
-      <c r="CG11"/>
-      <c r="CH11"/>
-      <c r="CI11"/>
-      <c r="CJ11"/>
-      <c r="CK11"/>
-      <c r="CL11"/>
-      <c r="CM11"/>
-      <c r="CN11"/>
-      <c r="CO11"/>
-      <c r="CP11"/>
-      <c r="CQ11"/>
-      <c r="CR11"/>
-      <c r="CS11"/>
-      <c r="CT11"/>
-      <c r="CU11"/>
-      <c r="CV11"/>
-      <c r="CW11"/>
-      <c r="CX11"/>
-      <c r="CY11"/>
-      <c r="CZ11"/>
-      <c r="DA11"/>
-      <c r="DB11"/>
-      <c r="DC11"/>
-      <c r="DD11"/>
-      <c r="DE11"/>
-      <c r="DF11"/>
-      <c r="DG11"/>
-      <c r="DH11"/>
-      <c r="DI11"/>
-      <c r="DJ11"/>
-      <c r="DK11"/>
-      <c r="DL11"/>
-      <c r="DM11"/>
-      <c r="DN11"/>
-      <c r="DO11"/>
-      <c r="DP11"/>
-      <c r="DQ11"/>
-      <c r="DR11"/>
-      <c r="DS11"/>
-      <c r="DT11"/>
-      <c r="DU11"/>
-      <c r="DV11"/>
-      <c r="DW11"/>
-      <c r="DX11"/>
-      <c r="DY11"/>
-      <c r="DZ11"/>
-      <c r="EA11"/>
-      <c r="EB11"/>
-      <c r="EC11"/>
-      <c r="ED11"/>
-      <c r="EE11"/>
-      <c r="EF11"/>
-      <c r="EG11"/>
-      <c r="EH11"/>
-      <c r="EI11"/>
-      <c r="EJ11"/>
-      <c r="EK11"/>
-      <c r="EL11"/>
-      <c r="EM11"/>
-      <c r="EN11"/>
-      <c r="EO11"/>
-      <c r="EP11"/>
-      <c r="EQ11"/>
-      <c r="ER11"/>
-      <c r="ES11"/>
-      <c r="ET11"/>
-      <c r="EU11"/>
-      <c r="EV11"/>
-      <c r="EW11"/>
-      <c r="EX11"/>
-      <c r="EY11"/>
-      <c r="EZ11"/>
-      <c r="FA11"/>
-      <c r="FB11"/>
-      <c r="FC11"/>
-      <c r="FD11"/>
-      <c r="FE11"/>
-      <c r="FF11"/>
-      <c r="FG11"/>
-      <c r="FH11"/>
-      <c r="FI11"/>
-      <c r="FJ11"/>
-      <c r="FK11"/>
-      <c r="FL11"/>
-      <c r="FM11"/>
-      <c r="FN11"/>
-      <c r="FO11"/>
-      <c r="FP11"/>
-      <c r="FQ11"/>
-      <c r="FR11"/>
-      <c r="FS11"/>
-      <c r="FT11"/>
-      <c r="FU11"/>
-      <c r="FV11"/>
-      <c r="FW11"/>
-      <c r="FX11"/>
-      <c r="FY11"/>
-      <c r="FZ11"/>
-      <c r="GA11"/>
-      <c r="GB11"/>
-      <c r="GC11"/>
-      <c r="GD11"/>
-      <c r="GE11"/>
-      <c r="GF11"/>
-      <c r="GG11"/>
-      <c r="GH11"/>
-      <c r="GI11"/>
-      <c r="GJ11"/>
-      <c r="GK11"/>
-      <c r="GL11"/>
-      <c r="GM11"/>
-      <c r="GN11"/>
-      <c r="GO11"/>
-      <c r="GP11"/>
-      <c r="GQ11"/>
-      <c r="GR11"/>
-      <c r="GS11"/>
-      <c r="GT11"/>
-      <c r="GU11"/>
-      <c r="GV11"/>
-      <c r="GW11"/>
-      <c r="GX11"/>
-      <c r="GY11"/>
-      <c r="GZ11"/>
-      <c r="HA11"/>
-      <c r="HB11"/>
-      <c r="HC11"/>
-      <c r="HD11"/>
-      <c r="HE11"/>
-      <c r="HF11"/>
-      <c r="HG11"/>
-      <c r="HH11"/>
-      <c r="HI11"/>
-      <c r="HJ11"/>
-      <c r="HK11"/>
-      <c r="HL11"/>
-      <c r="HM11"/>
-      <c r="HN11"/>
-      <c r="HO11"/>
-      <c r="HP11"/>
-      <c r="HQ11"/>
-      <c r="HR11"/>
-      <c r="HS11"/>
-      <c r="HT11"/>
-      <c r="HU11"/>
-      <c r="HV11"/>
-      <c r="HW11"/>
-      <c r="HX11"/>
-      <c r="HY11"/>
-      <c r="HZ11"/>
-      <c r="IA11"/>
-      <c r="IB11"/>
-      <c r="IC11"/>
-      <c r="ID11"/>
-      <c r="IE11"/>
-      <c r="IF11"/>
-      <c r="IG11"/>
-      <c r="IH11"/>
-      <c r="II11"/>
-      <c r="IJ11"/>
-      <c r="IK11"/>
-      <c r="IL11"/>
-      <c r="IM11"/>
-      <c r="IN11"/>
-      <c r="IO11"/>
-      <c r="IP11"/>
-      <c r="IQ11"/>
-      <c r="IR11"/>
-      <c r="IS11"/>
-      <c r="IT11"/>
-      <c r="IU11"/>
-      <c r="IV11"/>
-      <c r="IW11"/>
-      <c r="IX11"/>
-      <c r="IY11"/>
-      <c r="IZ11"/>
-      <c r="JA11"/>
-      <c r="JB11"/>
-      <c r="JC11"/>
-      <c r="JD11"/>
-      <c r="JE11"/>
-      <c r="JF11"/>
-      <c r="JG11"/>
-      <c r="JH11"/>
-      <c r="JI11"/>
-      <c r="JJ11"/>
-      <c r="JK11"/>
-      <c r="JL11"/>
-      <c r="JM11"/>
-      <c r="JN11"/>
-      <c r="JO11"/>
-      <c r="JP11"/>
-      <c r="JQ11"/>
-      <c r="JR11"/>
-      <c r="JS11"/>
-      <c r="JT11"/>
-      <c r="JU11"/>
-      <c r="JV11"/>
-      <c r="JW11"/>
-      <c r="JX11"/>
-      <c r="JY11"/>
-      <c r="JZ11"/>
-      <c r="KA11"/>
-      <c r="KB11"/>
-      <c r="KC11"/>
-      <c r="KD11"/>
-      <c r="KE11"/>
-      <c r="KF11"/>
-      <c r="KG11"/>
-      <c r="KH11"/>
-      <c r="KI11"/>
-      <c r="KJ11"/>
-      <c r="KK11"/>
-      <c r="KL11"/>
-      <c r="KM11"/>
-      <c r="KN11"/>
-      <c r="KO11"/>
-      <c r="KP11"/>
-      <c r="KQ11"/>
-      <c r="KR11"/>
-      <c r="KS11"/>
-      <c r="KT11"/>
-      <c r="KU11"/>
-      <c r="KV11"/>
-      <c r="KW11"/>
-      <c r="KX11"/>
-      <c r="KY11"/>
-      <c r="KZ11"/>
-      <c r="LA11"/>
-      <c r="LB11"/>
-      <c r="LC11"/>
-      <c r="LD11"/>
-      <c r="LE11"/>
-      <c r="LF11"/>
-      <c r="LG11"/>
-      <c r="LH11"/>
-      <c r="LI11"/>
-      <c r="LJ11"/>
-      <c r="LK11"/>
-      <c r="LL11"/>
-      <c r="LM11"/>
-      <c r="LN11"/>
-      <c r="LO11"/>
-      <c r="LP11"/>
-      <c r="LQ11"/>
-      <c r="LR11"/>
-      <c r="LS11"/>
-      <c r="LT11"/>
-      <c r="LU11"/>
-      <c r="LV11"/>
-      <c r="LW11"/>
-      <c r="LX11"/>
-      <c r="LY11"/>
-      <c r="LZ11"/>
-      <c r="MA11"/>
-      <c r="MB11"/>
-      <c r="MC11"/>
-      <c r="MD11"/>
-      <c r="ME11"/>
-      <c r="MF11"/>
-      <c r="MG11"/>
-      <c r="MH11"/>
-      <c r="MI11"/>
-      <c r="MJ11"/>
-      <c r="MK11"/>
-      <c r="ML11"/>
-      <c r="MM11"/>
-      <c r="MN11"/>
-      <c r="MO11"/>
-      <c r="MP11"/>
-      <c r="MQ11"/>
-      <c r="MR11"/>
-      <c r="MS11"/>
-      <c r="MT11"/>
-      <c r="MU11"/>
-      <c r="MV11"/>
-      <c r="MW11"/>
-      <c r="MX11"/>
-      <c r="MY11"/>
-      <c r="MZ11"/>
-      <c r="NA11"/>
-      <c r="NB11"/>
-      <c r="NC11"/>
-      <c r="ND11"/>
-      <c r="NE11"/>
-      <c r="NF11"/>
-      <c r="NG11"/>
-      <c r="NH11"/>
-      <c r="NI11"/>
-      <c r="NJ11"/>
-      <c r="NK11"/>
-      <c r="NL11"/>
-      <c r="NM11"/>
-      <c r="NN11"/>
-      <c r="NO11"/>
-      <c r="NP11"/>
-      <c r="NQ11"/>
-      <c r="NR11"/>
-      <c r="NS11"/>
-      <c r="NT11"/>
-      <c r="NU11"/>
-      <c r="NV11"/>
-      <c r="NW11"/>
-      <c r="NX11"/>
-      <c r="NY11"/>
-      <c r="NZ11"/>
-      <c r="OA11"/>
-      <c r="OB11"/>
-      <c r="OC11"/>
-      <c r="OD11"/>
-      <c r="OE11"/>
-      <c r="OF11"/>
-      <c r="OG11"/>
-      <c r="OH11"/>
-      <c r="OI11"/>
-      <c r="OJ11"/>
-      <c r="OK11"/>
-      <c r="OL11"/>
-      <c r="OM11"/>
-      <c r="ON11"/>
-      <c r="OO11"/>
-      <c r="OP11"/>
-      <c r="OQ11"/>
-      <c r="OR11"/>
-      <c r="OS11"/>
-      <c r="OT11"/>
-      <c r="OU11"/>
-      <c r="OV11"/>
-      <c r="OW11"/>
-      <c r="OX11"/>
-      <c r="OY11"/>
-      <c r="OZ11"/>
-      <c r="PA11"/>
-      <c r="PB11"/>
-      <c r="PC11"/>
-      <c r="PD11"/>
-      <c r="PE11"/>
-      <c r="PF11"/>
-      <c r="PG11"/>
-      <c r="PH11"/>
-      <c r="PI11"/>
-      <c r="PJ11"/>
-      <c r="PK11"/>
-      <c r="PL11"/>
-      <c r="PM11"/>
-      <c r="PN11"/>
-      <c r="PO11"/>
-      <c r="PP11"/>
-      <c r="PQ11"/>
-      <c r="PR11"/>
-      <c r="PS11"/>
-      <c r="PT11"/>
-      <c r="PU11"/>
-      <c r="PV11"/>
-      <c r="PW11"/>
-      <c r="PX11"/>
-      <c r="PY11"/>
-      <c r="PZ11"/>
-      <c r="QA11"/>
-      <c r="QB11"/>
-      <c r="QC11"/>
-      <c r="QD11"/>
-      <c r="QE11"/>
-      <c r="QF11"/>
-      <c r="QG11"/>
-      <c r="QH11"/>
-      <c r="QI11"/>
-      <c r="QJ11"/>
-      <c r="QK11"/>
-      <c r="QL11"/>
-      <c r="QM11"/>
-      <c r="QN11"/>
-      <c r="QO11"/>
-      <c r="QP11"/>
-      <c r="QQ11"/>
-      <c r="QR11"/>
-      <c r="QS11"/>
-      <c r="QT11"/>
-      <c r="QU11"/>
-      <c r="QV11"/>
-      <c r="QW11"/>
-      <c r="QX11"/>
-      <c r="QY11"/>
-      <c r="QZ11"/>
-      <c r="RA11"/>
-      <c r="RB11"/>
-      <c r="RC11"/>
-      <c r="RD11"/>
-      <c r="RE11"/>
-      <c r="RF11"/>
-      <c r="RG11"/>
-      <c r="RH11"/>
-      <c r="RI11"/>
-      <c r="RJ11"/>
-      <c r="RK11"/>
-      <c r="RL11"/>
-      <c r="RM11"/>
-      <c r="RN11"/>
-      <c r="RO11"/>
-      <c r="RP11"/>
-      <c r="RQ11"/>
-      <c r="RR11"/>
-      <c r="RS11"/>
-      <c r="RT11"/>
-      <c r="RU11"/>
-      <c r="RV11"/>
-      <c r="RW11"/>
-      <c r="RX11"/>
-      <c r="RY11"/>
-      <c r="RZ11"/>
-      <c r="SA11"/>
-      <c r="SB11"/>
-      <c r="SC11"/>
-      <c r="SD11"/>
-      <c r="SE11"/>
-      <c r="SF11"/>
-      <c r="SG11"/>
-      <c r="SH11"/>
-      <c r="SI11"/>
-      <c r="SJ11"/>
-      <c r="SK11"/>
-      <c r="SL11"/>
-      <c r="SM11"/>
-      <c r="SN11"/>
-      <c r="SO11"/>
-      <c r="SP11"/>
-      <c r="SQ11"/>
-      <c r="SR11"/>
-      <c r="SS11"/>
-      <c r="ST11"/>
-      <c r="SU11"/>
-      <c r="SV11"/>
-      <c r="SW11"/>
-      <c r="SX11"/>
-      <c r="SY11"/>
-      <c r="SZ11"/>
-      <c r="TA11"/>
-      <c r="TB11"/>
-      <c r="TC11"/>
-      <c r="TD11"/>
-      <c r="TE11"/>
-      <c r="TF11"/>
-      <c r="TG11"/>
-      <c r="TH11"/>
-      <c r="TI11"/>
-      <c r="TJ11"/>
-      <c r="TK11"/>
-      <c r="TL11"/>
-      <c r="TM11"/>
-      <c r="TN11"/>
-      <c r="TO11"/>
-      <c r="TP11"/>
-      <c r="TQ11"/>
-      <c r="TR11"/>
-      <c r="TS11"/>
-      <c r="TT11"/>
-      <c r="TU11"/>
-      <c r="TV11"/>
-      <c r="TW11"/>
-      <c r="TX11"/>
-      <c r="TY11"/>
-      <c r="TZ11"/>
-      <c r="UA11"/>
-      <c r="UB11"/>
-      <c r="UC11"/>
-      <c r="UD11"/>
-      <c r="UE11"/>
-      <c r="UF11"/>
-      <c r="UG11"/>
-      <c r="UH11"/>
-      <c r="UI11"/>
-      <c r="UJ11"/>
-      <c r="UK11"/>
-      <c r="UL11"/>
-      <c r="UM11"/>
-      <c r="UN11"/>
-      <c r="UO11"/>
-      <c r="UP11"/>
-      <c r="UQ11"/>
-      <c r="UR11"/>
-      <c r="US11"/>
-      <c r="UT11"/>
-      <c r="UU11"/>
-      <c r="UV11"/>
-      <c r="UW11"/>
-      <c r="UX11"/>
-      <c r="UY11"/>
-      <c r="UZ11"/>
-      <c r="VA11"/>
-      <c r="VB11"/>
-      <c r="VC11"/>
-      <c r="VD11"/>
-      <c r="VE11"/>
-      <c r="VF11"/>
-      <c r="VG11"/>
-      <c r="VH11"/>
-      <c r="VI11"/>
-      <c r="VJ11"/>
-      <c r="VK11"/>
-      <c r="VL11"/>
-      <c r="VM11"/>
-      <c r="VN11"/>
-      <c r="VO11"/>
-      <c r="VP11"/>
-      <c r="VQ11"/>
-      <c r="VR11"/>
-      <c r="VS11"/>
-      <c r="VT11"/>
-      <c r="VU11"/>
-      <c r="VV11"/>
-      <c r="VW11"/>
-      <c r="VX11"/>
-      <c r="VY11"/>
-      <c r="VZ11"/>
-      <c r="WA11"/>
-      <c r="WB11"/>
-      <c r="WC11"/>
-      <c r="WD11"/>
-      <c r="WE11"/>
-      <c r="WF11"/>
-      <c r="WG11"/>
-      <c r="WH11"/>
-      <c r="WI11"/>
-      <c r="WJ11"/>
-      <c r="WK11"/>
-      <c r="WL11"/>
-      <c r="WM11"/>
-      <c r="WN11"/>
-      <c r="WO11"/>
-      <c r="WP11"/>
-      <c r="WQ11"/>
-      <c r="WR11"/>
-      <c r="WS11"/>
-      <c r="WT11"/>
-      <c r="WU11"/>
-      <c r="WV11"/>
-      <c r="WW11"/>
-      <c r="WX11"/>
-      <c r="WY11"/>
-      <c r="WZ11"/>
-      <c r="XA11"/>
-      <c r="XB11"/>
-      <c r="XC11"/>
-      <c r="XD11"/>
-      <c r="XE11"/>
-      <c r="XF11"/>
-      <c r="XG11"/>
-      <c r="XH11"/>
-      <c r="XI11"/>
-      <c r="XJ11"/>
-      <c r="XK11"/>
-      <c r="XL11"/>
-      <c r="XM11"/>
-      <c r="XN11"/>
-      <c r="XO11"/>
-      <c r="XP11"/>
-      <c r="XQ11"/>
-      <c r="XR11"/>
-      <c r="XS11"/>
-      <c r="XT11"/>
-      <c r="XU11"/>
-      <c r="XV11"/>
-      <c r="XW11"/>
-      <c r="XX11"/>
-      <c r="XY11"/>
-      <c r="XZ11"/>
-      <c r="YA11"/>
-      <c r="YB11"/>
-      <c r="YC11"/>
-      <c r="YD11"/>
-      <c r="YE11"/>
-      <c r="YF11"/>
-      <c r="YG11"/>
-      <c r="YH11"/>
-      <c r="YI11"/>
-      <c r="YJ11"/>
-      <c r="YK11"/>
-      <c r="YL11"/>
-      <c r="YM11"/>
-      <c r="YN11"/>
-      <c r="YO11"/>
-      <c r="YP11"/>
-      <c r="YQ11"/>
-      <c r="YR11"/>
-      <c r="YS11"/>
-      <c r="YT11"/>
-      <c r="YU11"/>
-      <c r="YV11"/>
-      <c r="YW11"/>
-      <c r="YX11"/>
-      <c r="YY11"/>
-      <c r="YZ11"/>
-      <c r="ZA11"/>
-      <c r="ZB11"/>
-      <c r="ZC11"/>
-      <c r="ZD11"/>
-      <c r="ZE11"/>
-      <c r="ZF11"/>
-      <c r="ZG11"/>
-      <c r="ZH11"/>
-      <c r="ZI11"/>
-      <c r="ZJ11"/>
-      <c r="ZK11"/>
-      <c r="ZL11"/>
-      <c r="ZM11"/>
-      <c r="ZN11"/>
-      <c r="ZO11"/>
-      <c r="ZP11"/>
-      <c r="ZQ11"/>
-      <c r="ZR11"/>
-      <c r="ZS11"/>
-      <c r="ZT11"/>
-      <c r="ZU11"/>
-      <c r="ZV11"/>
-      <c r="ZW11"/>
-      <c r="ZX11"/>
-      <c r="ZY11"/>
-      <c r="ZZ11"/>
-      <c r="AAA11"/>
-      <c r="AAB11"/>
-      <c r="AAC11"/>
-      <c r="AAD11"/>
-      <c r="AAE11"/>
-      <c r="AAF11"/>
-      <c r="AAG11"/>
-      <c r="AAH11"/>
-      <c r="AAI11"/>
-      <c r="AAJ11"/>
-      <c r="AAK11"/>
-      <c r="AAL11"/>
-      <c r="AAM11"/>
-      <c r="AAN11"/>
-      <c r="AAO11"/>
-      <c r="AAP11"/>
-      <c r="AAQ11"/>
-      <c r="AAR11"/>
-      <c r="AAS11"/>
-      <c r="AAT11"/>
-      <c r="AAU11"/>
-      <c r="AAV11"/>
-      <c r="AAW11"/>
-      <c r="AAX11"/>
-      <c r="AAY11"/>
-      <c r="AAZ11"/>
-      <c r="ABA11"/>
-      <c r="ABB11"/>
-      <c r="ABC11"/>
-      <c r="ABD11"/>
-      <c r="ABE11"/>
-      <c r="ABF11"/>
-      <c r="ABG11"/>
-      <c r="ABH11"/>
-      <c r="ABI11"/>
-      <c r="ABJ11"/>
-      <c r="ABK11"/>
-      <c r="ABL11"/>
-      <c r="ABM11"/>
-      <c r="ABN11"/>
-      <c r="ABO11"/>
-      <c r="ABP11"/>
-      <c r="ABQ11"/>
-      <c r="ABR11"/>
-      <c r="ABS11"/>
-      <c r="ABT11"/>
-      <c r="ABU11"/>
-      <c r="ABV11"/>
-      <c r="ABW11"/>
-      <c r="ABX11"/>
-      <c r="ABY11"/>
-      <c r="ABZ11"/>
-      <c r="ACA11"/>
-      <c r="ACB11"/>
-      <c r="ACC11"/>
-      <c r="ACD11"/>
-      <c r="ACE11"/>
-      <c r="ACF11"/>
-      <c r="ACG11"/>
-      <c r="ACH11"/>
-      <c r="ACI11"/>
-      <c r="ACJ11"/>
-      <c r="ACK11"/>
-      <c r="ACL11"/>
-      <c r="ACM11"/>
-      <c r="ACN11"/>
-      <c r="ACO11"/>
-      <c r="ACP11"/>
-      <c r="ACQ11"/>
-      <c r="ACR11"/>
-      <c r="ACS11"/>
-      <c r="ACT11"/>
-      <c r="ACU11"/>
-      <c r="ACV11"/>
-      <c r="ACW11"/>
-      <c r="ACX11"/>
-      <c r="ACY11"/>
-      <c r="ACZ11"/>
-      <c r="ADA11"/>
-      <c r="ADB11"/>
-      <c r="ADC11"/>
-      <c r="ADD11"/>
-      <c r="ADE11"/>
-      <c r="ADF11"/>
-      <c r="ADG11"/>
-      <c r="ADH11"/>
-      <c r="ADI11"/>
-      <c r="ADJ11"/>
-      <c r="ADK11"/>
-      <c r="ADL11"/>
-      <c r="ADM11"/>
-      <c r="ADN11"/>
-      <c r="ADO11"/>
-      <c r="ADP11"/>
-      <c r="ADQ11"/>
-      <c r="ADR11"/>
-      <c r="ADS11"/>
-      <c r="ADT11"/>
-      <c r="ADU11"/>
-      <c r="ADV11"/>
-      <c r="ADW11"/>
-      <c r="ADX11"/>
-      <c r="ADY11"/>
-      <c r="ADZ11"/>
-      <c r="AEA11"/>
-      <c r="AEB11"/>
-      <c r="AEC11"/>
-      <c r="AED11"/>
-      <c r="AEE11"/>
-      <c r="AEF11"/>
-      <c r="AEG11"/>
-      <c r="AEH11"/>
-      <c r="AEI11"/>
-      <c r="AEJ11"/>
-      <c r="AEK11"/>
-      <c r="AEL11"/>
-      <c r="AEM11"/>
-      <c r="AEN11"/>
-      <c r="AEO11"/>
-      <c r="AEP11"/>
-      <c r="AEQ11"/>
-      <c r="AER11"/>
-      <c r="AES11"/>
-      <c r="AET11"/>
-      <c r="AEU11"/>
-      <c r="AEV11"/>
-      <c r="AEW11"/>
-      <c r="AEX11"/>
-      <c r="AEY11"/>
-      <c r="AEZ11"/>
-      <c r="AFA11"/>
-      <c r="AFB11"/>
-      <c r="AFC11"/>
-      <c r="AFD11"/>
-      <c r="AFE11"/>
-      <c r="AFF11"/>
-      <c r="AFG11"/>
-      <c r="AFH11"/>
-      <c r="AFI11"/>
-      <c r="AFJ11"/>
-      <c r="AFK11"/>
-      <c r="AFL11"/>
-      <c r="AFM11"/>
-      <c r="AFN11"/>
-      <c r="AFO11"/>
-      <c r="AFP11"/>
-      <c r="AFQ11"/>
-      <c r="AFR11"/>
-      <c r="AFS11"/>
-      <c r="AFT11"/>
-      <c r="AFU11"/>
-      <c r="AFV11"/>
-      <c r="AFW11"/>
-      <c r="AFX11"/>
-      <c r="AFY11"/>
-      <c r="AFZ11"/>
-      <c r="AGA11"/>
-      <c r="AGB11"/>
-      <c r="AGC11"/>
-      <c r="AGD11"/>
-      <c r="AGE11"/>
-      <c r="AGF11"/>
-      <c r="AGG11"/>
-      <c r="AGH11"/>
-      <c r="AGI11"/>
-      <c r="AGJ11"/>
-      <c r="AGK11"/>
-      <c r="AGL11"/>
-      <c r="AGM11"/>
-      <c r="AGN11"/>
-      <c r="AGO11"/>
-      <c r="AGP11"/>
-      <c r="AGQ11"/>
-      <c r="AGR11"/>
-      <c r="AGS11"/>
-      <c r="AGT11"/>
-      <c r="AGU11"/>
-      <c r="AGV11"/>
-      <c r="AGW11"/>
-      <c r="AGX11"/>
-      <c r="AGY11"/>
-      <c r="AGZ11"/>
-      <c r="AHA11"/>
-      <c r="AHB11"/>
-      <c r="AHC11"/>
-      <c r="AHD11"/>
-      <c r="AHE11"/>
-      <c r="AHF11"/>
-      <c r="AHG11"/>
-      <c r="AHH11"/>
-      <c r="AHI11"/>
-      <c r="AHJ11"/>
-      <c r="AHK11"/>
-      <c r="AHL11"/>
-      <c r="AHM11"/>
-      <c r="AHN11"/>
-      <c r="AHO11"/>
-      <c r="AHP11"/>
-      <c r="AHQ11"/>
-      <c r="AHR11"/>
-      <c r="AHS11"/>
-      <c r="AHT11"/>
-      <c r="AHU11"/>
-      <c r="AHV11"/>
-      <c r="AHW11"/>
-      <c r="AHX11"/>
-      <c r="AHY11"/>
-      <c r="AHZ11"/>
-      <c r="AIA11"/>
-      <c r="AIB11"/>
-      <c r="AIC11"/>
-      <c r="AID11"/>
-      <c r="AIE11"/>
-      <c r="AIF11"/>
-      <c r="AIG11"/>
-      <c r="AIH11"/>
-      <c r="AII11"/>
-      <c r="AIJ11"/>
-      <c r="AIK11"/>
-      <c r="AIL11"/>
-      <c r="AIM11"/>
-      <c r="AIN11"/>
-      <c r="AIO11"/>
-      <c r="AIP11"/>
-      <c r="AIQ11"/>
-      <c r="AIR11"/>
-      <c r="AIS11"/>
-      <c r="AIT11"/>
-      <c r="AIU11"/>
-      <c r="AIV11"/>
-      <c r="AIW11"/>
-      <c r="AIX11"/>
-      <c r="AIY11"/>
-      <c r="AIZ11"/>
-      <c r="AJA11"/>
-      <c r="AJB11"/>
-      <c r="AJC11"/>
-      <c r="AJD11"/>
-      <c r="AJE11"/>
-      <c r="AJF11"/>
-      <c r="AJG11"/>
-      <c r="AJH11"/>
-      <c r="AJI11"/>
-      <c r="AJJ11"/>
-      <c r="AJK11"/>
-      <c r="AJL11"/>
-      <c r="AJM11"/>
-      <c r="AJN11"/>
-      <c r="AJO11"/>
-      <c r="AJP11"/>
-      <c r="AJQ11"/>
-      <c r="AJR11"/>
-      <c r="AJS11"/>
-      <c r="AJT11"/>
-      <c r="AJU11"/>
-      <c r="AJV11"/>
-      <c r="AJW11"/>
-      <c r="AJX11"/>
-      <c r="AJY11"/>
-      <c r="AJZ11"/>
-      <c r="AKA11"/>
-      <c r="AKB11"/>
-      <c r="AKC11"/>
-      <c r="AKD11"/>
-      <c r="AKE11"/>
-      <c r="AKF11"/>
-      <c r="AKG11"/>
-      <c r="AKH11"/>
-      <c r="AKI11"/>
-      <c r="AKJ11"/>
-      <c r="AKK11"/>
-      <c r="AKL11"/>
-      <c r="AKM11"/>
-      <c r="AKN11"/>
-      <c r="AKO11"/>
-      <c r="AKP11"/>
-      <c r="AKQ11"/>
-      <c r="AKR11"/>
-      <c r="AKS11"/>
-      <c r="AKT11"/>
-      <c r="AKU11"/>
-      <c r="AKV11"/>
-      <c r="AKW11"/>
-      <c r="AKX11"/>
-      <c r="AKY11"/>
-      <c r="AKZ11"/>
-      <c r="ALA11"/>
-      <c r="ALB11"/>
-      <c r="ALC11"/>
-      <c r="ALD11"/>
-      <c r="ALE11"/>
-      <c r="ALF11"/>
-      <c r="ALG11"/>
-      <c r="ALH11"/>
-      <c r="ALI11"/>
-      <c r="ALJ11"/>
-      <c r="ALK11"/>
-      <c r="ALL11"/>
-      <c r="ALM11"/>
-      <c r="ALN11"/>
-      <c r="ALO11"/>
-      <c r="ALP11"/>
-      <c r="ALQ11"/>
-      <c r="ALR11"/>
-      <c r="ALS11"/>
-      <c r="ALT11"/>
-      <c r="ALU11"/>
-      <c r="ALV11"/>
-      <c r="ALW11"/>
-      <c r="ALX11"/>
-      <c r="ALY11"/>
-      <c r="ALZ11"/>
-      <c r="AMA11"/>
-      <c r="AMB11"/>
-      <c r="AMC11"/>
-      <c r="AMD11"/>
-      <c r="AME11"/>
-      <c r="AMF11"/>
-      <c r="AMG11"/>
-      <c r="AMH11"/>
-      <c r="AMI11"/>
-      <c r="AMJ11"/>
-      <c r="AMK11"/>
-      <c r="AML11"/>
-      <c r="AMM11"/>
-      <c r="AMN11"/>
-      <c r="AMO11"/>
-      <c r="AMP11"/>
-      <c r="AMQ11"/>
-      <c r="AMR11"/>
-      <c r="AMS11"/>
-      <c r="AMT11"/>
-      <c r="AMU11"/>
-      <c r="AMV11"/>
-      <c r="AMW11"/>
-      <c r="AMX11"/>
-      <c r="AMY11"/>
-      <c r="AMZ11"/>
-      <c r="ANA11"/>
-      <c r="ANB11"/>
-      <c r="ANC11"/>
-      <c r="AND11"/>
-      <c r="ANE11"/>
-      <c r="ANF11"/>
-      <c r="ANG11"/>
-      <c r="ANH11"/>
-      <c r="ANI11"/>
-      <c r="ANJ11"/>
-      <c r="ANK11"/>
-      <c r="ANL11"/>
-      <c r="ANM11"/>
-      <c r="ANN11"/>
-      <c r="ANO11"/>
-      <c r="ANP11"/>
-      <c r="ANQ11"/>
-      <c r="ANR11"/>
-      <c r="ANS11"/>
-      <c r="ANT11"/>
-      <c r="ANU11"/>
-      <c r="ANV11"/>
-      <c r="ANW11"/>
-      <c r="ANX11"/>
-      <c r="ANY11"/>
-      <c r="ANZ11"/>
-      <c r="AOA11"/>
-      <c r="AOB11"/>
-      <c r="AOC11"/>
-      <c r="AOD11"/>
-      <c r="AOE11"/>
-      <c r="AOF11"/>
-      <c r="AOG11"/>
-      <c r="AOH11"/>
-      <c r="AOI11"/>
-      <c r="AOJ11"/>
-      <c r="AOK11"/>
-      <c r="AOL11"/>
-      <c r="AOM11"/>
-      <c r="AON11"/>
-      <c r="AOO11"/>
-      <c r="AOP11"/>
-      <c r="AOQ11"/>
-      <c r="AOR11"/>
-      <c r="AOS11"/>
-      <c r="AOT11"/>
-      <c r="AOU11"/>
-      <c r="AOV11"/>
-      <c r="AOW11"/>
-      <c r="AOX11"/>
-      <c r="AOY11"/>
-      <c r="AOZ11"/>
-      <c r="APA11"/>
-      <c r="APB11"/>
-      <c r="APC11"/>
-      <c r="APD11"/>
-      <c r="APE11"/>
-      <c r="APF11"/>
-      <c r="APG11"/>
-      <c r="APH11"/>
-      <c r="API11"/>
-      <c r="APJ11"/>
-      <c r="APK11"/>
-      <c r="APL11"/>
-      <c r="APM11"/>
-      <c r="APN11"/>
-      <c r="APO11"/>
-      <c r="APP11"/>
-      <c r="APQ11"/>
-      <c r="APR11"/>
-      <c r="APS11"/>
-      <c r="APT11"/>
-      <c r="APU11"/>
-      <c r="APV11"/>
-      <c r="APW11"/>
-      <c r="APX11"/>
-      <c r="APY11"/>
-      <c r="APZ11"/>
-      <c r="AQA11"/>
-      <c r="AQB11"/>
-      <c r="AQC11"/>
-      <c r="AQD11"/>
-      <c r="AQE11"/>
-      <c r="AQF11"/>
-      <c r="AQG11"/>
-      <c r="AQH11"/>
-      <c r="AQI11"/>
-      <c r="AQJ11"/>
-      <c r="AQK11"/>
-      <c r="AQL11"/>
-      <c r="AQM11"/>
-      <c r="AQN11"/>
-      <c r="AQO11"/>
-      <c r="AQP11"/>
-      <c r="AQQ11"/>
-      <c r="AQR11"/>
-      <c r="AQS11"/>
-      <c r="AQT11"/>
-      <c r="AQU11"/>
-      <c r="AQV11"/>
-      <c r="AQW11"/>
-      <c r="AQX11"/>
-      <c r="AQY11"/>
-      <c r="AQZ11"/>
-      <c r="ARA11"/>
-      <c r="ARB11"/>
-      <c r="ARC11"/>
-      <c r="ARD11"/>
-      <c r="ARE11"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -13352,86 +9827,86 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3"/>
       <c r="B7" s="3" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3"/>
       <c r="B8" s="3" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -13451,108 +9926,108 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3"/>
       <c r="B9" s="3" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="3"/>
       <c r="B10" s="3" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -13573,108 +10048,108 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3"/>
       <c r="B9" s="3" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="3"/>
       <c r="B10" s="3" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -13694,141 +10169,141 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="3"/>
       <c r="B12" s="3" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="3"/>
       <c r="B13" s="3" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -13848,119 +10323,119 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>238</v>
+        <v>226</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="3"/>
       <c r="B10" s="3" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="3"/>
       <c r="B11" s="3" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -13980,141 +10455,141 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="3"/>
       <c r="B12" s="3" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="3"/>
       <c r="B13" s="3" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -14139,54 +10614,54 @@
   <sheetData>
     <row r="1" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -14412,106 +10887,106 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>253</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>269</v>
+        <v>257</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>270</v>
+        <v>258</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>273</v>
+        <v>261</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
     </row>
   </sheetData>
@@ -14537,54 +11012,54 @@
   <sheetData>
     <row r="1" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -14810,80 +11285,80 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>285</v>
+        <v>273</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>293</v>
+        <v>281</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>294</v>
+        <v>282</v>
       </c>
     </row>
   </sheetData>
@@ -14908,54 +11383,54 @@
   <sheetData>
     <row r="1" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -15181,132 +11656,132 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>299</v>
+        <v>287</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>300</v>
+        <v>288</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>301</v>
+        <v>289</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>304</v>
+        <v>292</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>305</v>
+        <v>293</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>307</v>
+        <v>295</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>308</v>
+        <v>296</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>309</v>
+        <v>297</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>310</v>
+        <v>298</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>311</v>
+        <v>299</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>312</v>
+        <v>300</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>313</v>
+        <v>301</v>
       </c>
     </row>
     <row r="7" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>314</v>
+        <v>302</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>316</v>
+        <v>304</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>315</v>
+        <v>303</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>317</v>
+        <v>305</v>
       </c>
     </row>
   </sheetData>
@@ -15332,54 +11807,54 @@
   <sheetData>
     <row r="1" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>318</v>
+        <v>306</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>319</v>
+        <v>307</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>320</v>
+        <v>308</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -15605,106 +12080,106 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>321</v>
+        <v>309</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>322</v>
+        <v>310</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>323</v>
+        <v>311</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>324</v>
+        <v>312</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>325</v>
+        <v>313</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>326</v>
+        <v>314</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>327</v>
+        <v>315</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
-        <v>329</v>
+        <v>317</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>331</v>
+        <v>319</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>332</v>
+        <v>320</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>334</v>
+        <v>322</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>335</v>
+        <v>323</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>336</v>
+        <v>324</v>
       </c>
     </row>
   </sheetData>
@@ -15727,202 +12202,202 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -15947,54 +12422,54 @@
   <sheetData>
     <row r="1" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>338</v>
+        <v>326</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -16220,80 +12695,80 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>340</v>
+        <v>328</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>341</v>
+        <v>329</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>342</v>
+        <v>330</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>343</v>
+        <v>331</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>344</v>
+        <v>332</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>346</v>
+        <v>334</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>347</v>
+        <v>335</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>348</v>
+        <v>336</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>349</v>
+        <v>337</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>350</v>
+        <v>338</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>351</v>
+        <v>339</v>
       </c>
     </row>
   </sheetData>
@@ -16318,54 +12793,54 @@
   <sheetData>
     <row r="1" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>352</v>
+        <v>340</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>353</v>
+        <v>341</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>354</v>
+        <v>342</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -16591,132 +13066,132 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>355</v>
+        <v>343</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>356</v>
+        <v>344</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>358</v>
+        <v>346</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>359</v>
+        <v>347</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>360</v>
+        <v>348</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>361</v>
+        <v>349</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>362</v>
+        <v>350</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
-        <v>363</v>
+        <v>351</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>364</v>
+        <v>352</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>365</v>
+        <v>353</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>366</v>
+        <v>354</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>367</v>
+        <v>355</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>369</v>
+        <v>357</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>368</v>
+        <v>356</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>370</v>
+        <v>358</v>
       </c>
     </row>
     <row r="7" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>371</v>
+        <v>359</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>372</v>
+        <v>360</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>373</v>
+        <v>361</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>374</v>
+        <v>362</v>
       </c>
     </row>
   </sheetData>
@@ -16741,54 +13216,54 @@
   <sheetData>
     <row r="1" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>375</v>
+        <v>363</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>377</v>
+        <v>365</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -17014,132 +13489,132 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>378</v>
+        <v>366</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>379</v>
+        <v>367</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>380</v>
+        <v>368</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>381</v>
+        <v>369</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>384</v>
+        <v>372</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>383</v>
+        <v>371</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>385</v>
+        <v>373</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
-        <v>386</v>
+        <v>374</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>387</v>
+        <v>375</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>388</v>
+        <v>376</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>389</v>
+        <v>377</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>390</v>
+        <v>378</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>392</v>
+        <v>380</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>391</v>
+        <v>379</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>393</v>
+        <v>381</v>
       </c>
     </row>
     <row r="7" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>394</v>
+        <v>382</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>395</v>
+        <v>383</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>396</v>
+        <v>384</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>397</v>
+        <v>385</v>
       </c>
     </row>
   </sheetData>
@@ -17162,102 +13637,102 @@
   <sheetData>
     <row r="1" spans="1:1029" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:1029" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>399</v>
+        <v>387</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>400</v>
+        <v>388</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>401</v>
+        <v>389</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>398</v>
+        <v>386</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>402</v>
+        <v>390</v>
       </c>
     </row>
     <row r="3" spans="1:1029" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>398</v>
+        <v>386</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" spans="1:1029" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>398</v>
+        <v>386</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
     </row>
     <row r="5" spans="1:1029" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>398</v>
+        <v>386</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="G5"/>
       <c r="H5"/>
@@ -18285,62 +14760,62 @@
     </row>
     <row r="6" spans="1:1029" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>398</v>
+        <v>386</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:1029" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>398</v>
+        <v>386</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8" spans="1:1029" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>398</v>
+        <v>386</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G8"/>
       <c r="H8"/>
@@ -19368,62 +15843,62 @@
     </row>
     <row r="9" spans="1:1029" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>398</v>
+        <v>386</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:1029" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>398</v>
+        <v>386</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11" spans="1:1029" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>398</v>
+        <v>386</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -19446,42 +15921,42 @@
   <sheetData>
     <row r="1" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="G2"/>
       <c r="H2"/>
@@ -19709,22 +16184,22 @@
     </row>
     <row r="3" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="G3"/>
       <c r="H3"/>
@@ -19952,22 +16427,22 @@
     </row>
     <row r="4" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>403</v>
+        <v>391</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>404</v>
+        <v>392</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>405</v>
+        <v>393</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>406</v>
+        <v>394</v>
       </c>
       <c r="G4"/>
       <c r="H4"/>
@@ -20195,42 +16670,42 @@
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -20250,97 +16725,71 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B4" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>144</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>141</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>141</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>141</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>158</v>
+      <c r="A8" s="3" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>156</v>
+      <c r="A9" s="3" t="s">
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -20359,86 +16808,86 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3"/>
       <c r="B7" s="3" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3"/>
       <c r="B8" s="3" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -20457,108 +16906,108 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3"/>
       <c r="B9" s="3" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="3"/>
       <c r="B10" s="3" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -20578,97 +17027,97 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3"/>
       <c r="B8" s="3" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3"/>
       <c r="B9" s="3" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -20688,130 +17137,130 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>192</v>
+        <v>180</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>192</v>
+        <v>180</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>192</v>
+        <v>180</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="3"/>
       <c r="B11" s="3" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="3"/>
       <c r="B12" s="3" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>

--- a/testdata.xlsx
+++ b/testdata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sshiwani\workspace\find-information-products-services-tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84601013-AC13-48B6-BBD5-5C3C5F01E49F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F43993A-715F-4D1C-B894-7EEE8875F979}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" firstSheet="21" activeTab="23" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="category_phase" sheetId="1" r:id="rId1"/>
@@ -35,6 +35,8 @@
     <sheet name="UGSubcategory_Employer" sheetId="20" r:id="rId20"/>
     <sheet name="UGSubcategory_LAWorkforce" sheetId="21" r:id="rId21"/>
     <sheet name="UGSubcategory_NEETOrCareerSeek" sheetId="22" r:id="rId22"/>
+    <sheet name="UGSubcategory_ParentOrCarer" sheetId="23" r:id="rId23"/>
+    <sheet name="UGSubcateg_ProfExtUserofDfEData" sheetId="24" r:id="rId24"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -46,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="861" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="877" uniqueCount="442">
   <si>
     <t>Search and filter products and services</t>
   </si>
@@ -435,9 +437,6 @@
     <t>Col3</t>
   </si>
   <si>
-    <t>View products in this category</t>
-  </si>
-  <si>
     <t>categories/user-group/adult-learner-18</t>
   </si>
   <si>
@@ -450,9 +449,6 @@
     <t>Adult learner (18+)</t>
   </si>
   <si>
-    <t>//*[@id="main-content"]/div/div/div/ul[1]/li/div/p</t>
-  </si>
-  <si>
     <t>Adult in work based learning or training</t>
   </si>
   <si>
@@ -465,18 +461,6 @@
     <t>Student (higher education)</t>
   </si>
   <si>
-    <t>//*[@id="main-content"]/div/div/div/ul[2]/li[1]/div/p</t>
-  </si>
-  <si>
-    <t>//*[@id="main-content"]/div/div/div/ul[2]/li[2]/div/p</t>
-  </si>
-  <si>
-    <t>//*[@id="main-content"]/div/div/div/ul[2]/li[3]/div/p</t>
-  </si>
-  <si>
-    <t>//*[@id="main-content"]/div/div/div/ul[2]/li[4]/div/p</t>
-  </si>
-  <si>
     <t>//*[@id="main-content"]/div/div/div/p[2]</t>
   </si>
   <si>
@@ -528,9 +512,6 @@
     <t>Young person (16-18)</t>
   </si>
   <si>
-    <t>//*[@id="main-content"]/div/div/div/ul[2]/li[5]/div/p</t>
-  </si>
-  <si>
     <t>Young person with SEND (16-25)</t>
   </si>
   <si>
@@ -579,30 +560,9 @@
     <t>Higher education workforce</t>
   </si>
   <si>
-    <t>//*[@id="main-content"]/div/div/div/ul[2]/li[6]/div/p</t>
-  </si>
-  <si>
     <t>School workforce</t>
   </si>
   <si>
-    <t>9 sub-categories</t>
-  </si>
-  <si>
-    <t>3 sub-categories</t>
-  </si>
-  <si>
-    <t>1 sub-categories</t>
-  </si>
-  <si>
-    <t>10 sub-categories</t>
-  </si>
-  <si>
-    <t>5 sub-categories</t>
-  </si>
-  <si>
-    <t>//*[@id="main-content"]/div/div/div/ul[2]/li[7]/div/p</t>
-  </si>
-  <si>
     <t>SEND professional</t>
   </si>
   <si>
@@ -705,9 +665,6 @@
     <t>Parent or carer of young person (16-18)</t>
   </si>
   <si>
-    <t>//*[@id="main-content"]/div/div/div/ul[2]/li[8]/div/p</t>
-  </si>
-  <si>
     <t>categories/user-group/professional-external-user-of-dfe-data</t>
   </si>
   <si>
@@ -1231,6 +1188,192 @@
   </si>
   <si>
     <t>#type-data-collection-and-reporting</t>
+  </si>
+  <si>
+    <t>products?userGroup=parent-or-carer</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Parent or carer')</t>
+  </si>
+  <si>
+    <t>Remove this filter Parent or carer</t>
+  </si>
+  <si>
+    <t>products?userGroup=expectant-parent</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Expectant parent ')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remove this filter Expectant parent </t>
+  </si>
+  <si>
+    <t>Expectant parent  (Parent or carer)</t>
+  </si>
+  <si>
+    <t>products?userGroup=parent-or-carer-of-adult-learner</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Parent or carer of adult learner  (Parent or carer)')</t>
+  </si>
+  <si>
+    <t>Remove this filter Parent or carer of adult learner  (Parent or carer)</t>
+  </si>
+  <si>
+    <t>Parent or carer of adult learner  (Parent or carer)</t>
+  </si>
+  <si>
+    <t>products?userGroup=parent-or-carer-of-career-seeker</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Parent or carer of career seeker  (Parent or carer)')</t>
+  </si>
+  <si>
+    <t>Remove this filter Parent or carer of career seeker  (Parent or carer)</t>
+  </si>
+  <si>
+    <t>Parent or carer of career seeker  (Parent or carer)</t>
+  </si>
+  <si>
+    <t>products?userGroup=parent-or-carer-of-child-early-years-age</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Parent or carer of child (early years age) ')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remove this filter Parent or carer of child (early years age) </t>
+  </si>
+  <si>
+    <t>Parent or carer of child (early years age)  (Parent or carer)</t>
+  </si>
+  <si>
+    <t>products?userGroup=parent-or-carer-of-child-primary-age</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Parent or carer of child (primary age) ')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remove this filter Parent or carer of child (primary age) </t>
+  </si>
+  <si>
+    <t>Parent or carer of child (primary age)  (Parent or carer)</t>
+  </si>
+  <si>
+    <t>products?userGroup=parent-or-carer-of-child-secondary-age</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Parent or carer of child (secondary age) ')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remove this filter Parent or carer of child (secondary age) </t>
+  </si>
+  <si>
+    <t>Parent or carer of child (secondary age)  (Parent or carer)</t>
+  </si>
+  <si>
+    <t>products?userGroup=parent-or-carer-of-child-send</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Parent or carer of child (SEND) ')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remove this filter Parent or carer of child (SEND) </t>
+  </si>
+  <si>
+    <t>Parent or carer of child (SEND)  (Parent or carer)</t>
+  </si>
+  <si>
+    <t>products?userGroup=parent-or-carer-of-young-person-16-18</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Parent or carer of young person (16-18)  (Parent or carer)')</t>
+  </si>
+  <si>
+    <t>Remove this filter Parent or carer of young person (16-18)  (Parent or carer)</t>
+  </si>
+  <si>
+    <t>Parent or carer of young person (16-18)  (Parent or carer)</t>
+  </si>
+  <si>
+    <t>products?userGroup=professional-external-user-of-dfe-data</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Professional external user of DfE data')</t>
+  </si>
+  <si>
+    <t>Remove this filter Professional external user of DfE data</t>
+  </si>
+  <si>
+    <t>products?userGroup=colleague-in-another-part-of-government-data-user</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Colleague in another part of government (data user)  (Professional external user of DfE data)')</t>
+  </si>
+  <si>
+    <t>Remove this filter Colleague in another part of government (data user)  (Professional external user of DfE data)</t>
+  </si>
+  <si>
+    <t>Colleague in another part of government (data user)  (Professional external user of DfE data)</t>
+  </si>
+  <si>
+    <t>products?userGroup=journalist-data-user</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Journalist (data user)  (Professional external user of DfE data)')</t>
+  </si>
+  <si>
+    <t>Remove this filter Journalist (data user)  (Professional external user of DfE data)</t>
+  </si>
+  <si>
+    <t>Journalist (data user)  (Professional external user of DfE data)</t>
+  </si>
+  <si>
+    <t>products?userGroup=member-of-a-professional-network-data-user</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Member of a professional network (data user)  (Professional external user of DfE data)')</t>
+  </si>
+  <si>
+    <t>Remove this filter Member of a professional network (data user)  (Professional external user of DfE data)</t>
+  </si>
+  <si>
+    <t>Member of a professional network (data user)  (Professional external user of DfE data)</t>
+  </si>
+  <si>
+    <t>products?userGroup=professional-representative-bodies-workforce-data-user</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Professional representative bodies workforce (data user)  (Professional external user of DfE data)')</t>
+  </si>
+  <si>
+    <t>Remove this filter Professional representative bodies workforce (data user)  (Professional external user of DfE data)</t>
+  </si>
+  <si>
+    <t>Professional representative bodies workforce (data user)  (Professional external user of DfE data)</t>
+  </si>
+  <si>
+    <t>products?userGroup=researcher-data-user</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Researcher (data user)  (Professional external user of DfE data)')</t>
+  </si>
+  <si>
+    <t>Remove this filter Researcher (data user)  (Professional external user of DfE data)</t>
+  </si>
+  <si>
+    <t>Researcher (data user)  (Professional external user of DfE data)</t>
+  </si>
+  <si>
+    <t>products?userGroup=trade-union-bodies-workforce-data-user</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Trade union bodies workforce (data user)  (Professional external user of DfE data)')</t>
+  </si>
+  <si>
+    <t>Remove this filter Trade union bodies workforce (data user)  (Professional external user of DfE data)</t>
+  </si>
+  <si>
+    <t>Trade union bodies workforce (data user)  (Professional external user of DfE data)</t>
   </si>
 </sst>
 </file>
@@ -1284,7 +1427,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -1344,11 +1487,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1358,6 +1512,7 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -9838,75 +9993,53 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
-        <v>188</v>
-      </c>
       <c r="B3" s="3" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
-        <v>189</v>
-      </c>
       <c r="B4" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>129</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>129</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>146</v>
+      <c r="A7" s="3" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>144</v>
+      <c r="A8" s="3" t="s">
+        <v>177</v>
       </c>
     </row>
   </sheetData>
@@ -9937,97 +10070,67 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
-        <v>194</v>
-      </c>
       <c r="B3" s="3" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
-        <v>195</v>
-      </c>
       <c r="B4" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>129</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>129</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>129</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>129</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>146</v>
+      <c r="A9" s="3" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>144</v>
+      <c r="A10" s="3" t="s">
+        <v>185</v>
       </c>
     </row>
   </sheetData>
@@ -10059,97 +10162,67 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>200</v>
+        <v>186</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>201</v>
+        <v>187</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
-        <v>202</v>
-      </c>
       <c r="B3" s="3" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
-        <v>203</v>
-      </c>
       <c r="B4" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>129</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>129</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>129</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>129</v>
-      </c>
+        <v>191</v>
+      </c>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>146</v>
+      <c r="A9" s="3" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>144</v>
+      <c r="A10" s="3" t="s">
+        <v>193</v>
       </c>
     </row>
   </sheetData>
@@ -10180,130 +10253,88 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>208</v>
+        <v>194</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>209</v>
+        <v>195</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
-        <v>210</v>
-      </c>
       <c r="B3" s="3" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
-        <v>211</v>
-      </c>
       <c r="B4" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>129</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>129</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>129</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>129</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>129</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>129</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>129</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>146</v>
+      <c r="A12" s="3" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>144</v>
+      <c r="A13" s="3" t="s">
+        <v>204</v>
       </c>
     </row>
   </sheetData>
@@ -10334,108 +10365,74 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>220</v>
+        <v>205</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>221</v>
+        <v>206</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
-        <v>222</v>
-      </c>
       <c r="B3" s="3" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
-        <v>223</v>
-      </c>
       <c r="B4" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>129</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>129</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>129</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>129</v>
-      </c>
+        <v>210</v>
+      </c>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>129</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>146</v>
+      <c r="A10" s="3" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>144</v>
+      <c r="A11" s="3" t="s">
+        <v>213</v>
       </c>
     </row>
   </sheetData>
@@ -10466,130 +10463,88 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
-        <v>231</v>
-      </c>
       <c r="B3" s="3" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
-        <v>232</v>
-      </c>
       <c r="B4" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>129</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>129</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>129</v>
-      </c>
+        <v>218</v>
+      </c>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>129</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>129</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>129</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>183</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>146</v>
+      <c r="A12" s="3" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>144</v>
+      <c r="A13" s="3" t="s">
+        <v>224</v>
       </c>
     </row>
   </sheetData>
@@ -10632,36 +10587,36 @@
         <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>249</v>
+        <v>234</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -10887,106 +10842,106 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>245</v>
+        <v>230</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>247</v>
+        <v>232</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>248</v>
+        <v>233</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>252</v>
+        <v>237</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>253</v>
+        <v>238</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>246</v>
+        <v>231</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>254</v>
+        <v>239</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>255</v>
+        <v>240</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="H4" s="3" t="s">
         <v>242</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>258</v>
+        <v>243</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>259</v>
+        <v>244</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>260</v>
+        <v>245</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>261</v>
+        <v>246</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>262</v>
+        <v>247</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>263</v>
+        <v>248</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>264</v>
+        <v>249</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>267</v>
+        <v>252</v>
       </c>
     </row>
   </sheetData>
@@ -11030,36 +10985,36 @@
         <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>249</v>
+        <v>234</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>268</v>
+        <v>253</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>269</v>
+        <v>254</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>270</v>
+        <v>255</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -11285,80 +11240,80 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>271</v>
+        <v>256</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>272</v>
+        <v>257</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>273</v>
+        <v>258</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>274</v>
+        <v>259</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>275</v>
+        <v>260</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>276</v>
+        <v>261</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>277</v>
+        <v>262</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>278</v>
+        <v>263</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>279</v>
+        <v>264</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>280</v>
+        <v>265</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>281</v>
+        <v>266</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>282</v>
+        <v>267</v>
       </c>
     </row>
   </sheetData>
@@ -11401,36 +11356,36 @@
         <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>249</v>
+        <v>234</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>283</v>
+        <v>268</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>284</v>
+        <v>269</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>285</v>
+        <v>270</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -11656,132 +11611,132 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>286</v>
+        <v>271</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>287</v>
+        <v>272</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>288</v>
+        <v>273</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>289</v>
+        <v>274</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>290</v>
+        <v>275</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>292</v>
+        <v>277</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>291</v>
+        <v>276</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>293</v>
+        <v>278</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
-        <v>294</v>
+        <v>279</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>295</v>
+        <v>280</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>296</v>
+        <v>281</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>297</v>
+        <v>282</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>298</v>
+        <v>283</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>299</v>
+        <v>284</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>300</v>
+        <v>285</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>301</v>
+        <v>286</v>
       </c>
     </row>
     <row r="7" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>302</v>
+        <v>287</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>303</v>
+        <v>288</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>305</v>
+        <v>290</v>
       </c>
     </row>
   </sheetData>
@@ -11825,36 +11780,36 @@
         <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>249</v>
+        <v>234</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>306</v>
+        <v>291</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>307</v>
+        <v>292</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>308</v>
+        <v>293</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -12080,106 +12035,106 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>309</v>
+        <v>294</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>310</v>
+        <v>295</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>311</v>
+        <v>296</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>312</v>
+        <v>297</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>313</v>
+        <v>298</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>314</v>
+        <v>299</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>315</v>
+        <v>300</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>316</v>
+        <v>301</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
-        <v>317</v>
+        <v>302</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>318</v>
+        <v>303</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>319</v>
+        <v>304</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>320</v>
+        <v>305</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>321</v>
+        <v>306</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>322</v>
+        <v>307</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>323</v>
+        <v>308</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>324</v>
+        <v>309</v>
       </c>
     </row>
   </sheetData>
@@ -12440,36 +12395,36 @@
         <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>249</v>
+        <v>234</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>325</v>
+        <v>310</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>326</v>
+        <v>311</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>327</v>
+        <v>312</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -12695,80 +12650,80 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>328</v>
+        <v>313</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>329</v>
+        <v>314</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>330</v>
+        <v>315</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>331</v>
+        <v>316</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>332</v>
+        <v>317</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>333</v>
+        <v>318</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>334</v>
+        <v>319</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>335</v>
+        <v>320</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>336</v>
+        <v>321</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>337</v>
+        <v>322</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>338</v>
+        <v>323</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>339</v>
+        <v>324</v>
       </c>
     </row>
   </sheetData>
@@ -12811,36 +12766,36 @@
         <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>249</v>
+        <v>234</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>340</v>
+        <v>325</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>341</v>
+        <v>326</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>342</v>
+        <v>327</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>194</v>
+        <v>180</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -13066,132 +13021,132 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>343</v>
+        <v>328</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>344</v>
+        <v>329</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>345</v>
+        <v>330</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>346</v>
+        <v>331</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>347</v>
+        <v>332</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>348</v>
+        <v>333</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>349</v>
+        <v>334</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>350</v>
+        <v>335</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
-        <v>351</v>
+        <v>336</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>352</v>
+        <v>337</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>353</v>
+        <v>338</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>354</v>
+        <v>339</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>355</v>
+        <v>340</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>357</v>
+        <v>342</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>356</v>
+        <v>341</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>358</v>
+        <v>343</v>
       </c>
     </row>
     <row r="7" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>359</v>
+        <v>344</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>360</v>
+        <v>345</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>361</v>
+        <v>346</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>362</v>
+        <v>347</v>
       </c>
     </row>
   </sheetData>
@@ -13234,36 +13189,36 @@
         <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>249</v>
+        <v>234</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>363</v>
+        <v>348</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>364</v>
+        <v>349</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>365</v>
+        <v>350</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>202</v>
+        <v>188</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -13489,135 +13444,1087 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>366</v>
+        <v>351</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>367</v>
+        <v>352</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>368</v>
+        <v>353</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>369</v>
+        <v>354</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>370</v>
+        <v>355</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>372</v>
+        <v>357</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>371</v>
+        <v>356</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>373</v>
+        <v>358</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
-        <v>374</v>
+        <v>359</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>375</v>
+        <v>360</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>376</v>
+        <v>361</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>377</v>
+        <v>362</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>378</v>
+        <v>363</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>380</v>
+        <v>365</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>379</v>
+        <v>364</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>381</v>
+        <v>366</v>
       </c>
     </row>
     <row r="7" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>382</v>
+        <v>367</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>383</v>
+        <v>368</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>384</v>
+        <v>369</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="H7" s="3" t="s">
+        <v>370</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20DD36AA-F163-4AAB-BD30-4AE6290CCAE7}">
+  <dimension ref="A1:HU10"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="50.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="52.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.453125" customWidth="1"/>
+    <col min="4" max="4" width="33.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="33.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.08984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="40.81640625" customWidth="1"/>
+    <col min="8" max="8" width="62.54296875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="I2"/>
+      <c r="J2"/>
+      <c r="K2"/>
+      <c r="L2"/>
+      <c r="M2"/>
+      <c r="N2"/>
+      <c r="O2"/>
+      <c r="P2"/>
+      <c r="Q2"/>
+      <c r="R2"/>
+      <c r="S2"/>
+      <c r="T2"/>
+      <c r="U2"/>
+      <c r="V2"/>
+      <c r="W2"/>
+      <c r="X2"/>
+      <c r="Y2"/>
+      <c r="Z2"/>
+      <c r="AA2"/>
+      <c r="AB2"/>
+      <c r="AC2"/>
+      <c r="AD2"/>
+      <c r="AE2"/>
+      <c r="AF2"/>
+      <c r="AG2"/>
+      <c r="AH2"/>
+      <c r="AI2"/>
+      <c r="AJ2"/>
+      <c r="AK2"/>
+      <c r="AL2"/>
+      <c r="AM2"/>
+      <c r="AN2"/>
+      <c r="AO2"/>
+      <c r="AP2"/>
+      <c r="AQ2"/>
+      <c r="AR2"/>
+      <c r="AS2"/>
+      <c r="AT2"/>
+      <c r="AU2"/>
+      <c r="AV2"/>
+      <c r="AW2"/>
+      <c r="AX2"/>
+      <c r="AY2"/>
+      <c r="AZ2"/>
+      <c r="BA2"/>
+      <c r="BB2"/>
+      <c r="BC2"/>
+      <c r="BD2"/>
+      <c r="BE2"/>
+      <c r="BF2"/>
+      <c r="BG2"/>
+      <c r="BH2"/>
+      <c r="BI2"/>
+      <c r="BJ2"/>
+      <c r="BK2"/>
+      <c r="BL2"/>
+      <c r="BM2"/>
+      <c r="BN2"/>
+      <c r="BO2"/>
+      <c r="BP2"/>
+      <c r="BQ2"/>
+      <c r="BR2"/>
+      <c r="BS2"/>
+      <c r="BT2"/>
+      <c r="BU2"/>
+      <c r="BV2"/>
+      <c r="BW2"/>
+      <c r="BX2"/>
+      <c r="BY2"/>
+      <c r="BZ2"/>
+      <c r="CA2"/>
+      <c r="CB2"/>
+      <c r="CC2"/>
+      <c r="CD2"/>
+      <c r="CE2"/>
+      <c r="CF2"/>
+      <c r="CG2"/>
+      <c r="CH2"/>
+      <c r="CI2"/>
+      <c r="CJ2"/>
+      <c r="CK2"/>
+      <c r="CL2"/>
+      <c r="CM2"/>
+      <c r="CN2"/>
+      <c r="CO2"/>
+      <c r="CP2"/>
+      <c r="CQ2"/>
+      <c r="CR2"/>
+      <c r="CS2"/>
+      <c r="CT2"/>
+      <c r="CU2"/>
+      <c r="CV2"/>
+      <c r="CW2"/>
+      <c r="CX2"/>
+      <c r="CY2"/>
+      <c r="CZ2"/>
+      <c r="DA2"/>
+      <c r="DB2"/>
+      <c r="DC2"/>
+      <c r="DD2"/>
+      <c r="DE2"/>
+      <c r="DF2"/>
+      <c r="DG2"/>
+      <c r="DH2"/>
+      <c r="DI2"/>
+      <c r="DJ2"/>
+      <c r="DK2"/>
+      <c r="DL2"/>
+      <c r="DM2"/>
+      <c r="DN2"/>
+      <c r="DO2"/>
+      <c r="DP2"/>
+      <c r="DQ2"/>
+      <c r="DR2"/>
+      <c r="DS2"/>
+      <c r="DT2"/>
+      <c r="DU2"/>
+      <c r="DV2"/>
+      <c r="DW2"/>
+      <c r="DX2"/>
+      <c r="DY2"/>
+      <c r="DZ2"/>
+      <c r="EA2"/>
+      <c r="EB2"/>
+      <c r="EC2"/>
+      <c r="ED2"/>
+      <c r="EE2"/>
+      <c r="EF2"/>
+      <c r="EG2"/>
+      <c r="EH2"/>
+      <c r="EI2"/>
+      <c r="EJ2"/>
+      <c r="EK2"/>
+      <c r="EL2"/>
+      <c r="EM2"/>
+      <c r="EN2"/>
+      <c r="EO2"/>
+      <c r="EP2"/>
+      <c r="EQ2"/>
+      <c r="ER2"/>
+      <c r="ES2"/>
+      <c r="ET2"/>
+      <c r="EU2"/>
+      <c r="EV2"/>
+      <c r="EW2"/>
+      <c r="EX2"/>
+      <c r="EY2"/>
+      <c r="EZ2"/>
+      <c r="FA2"/>
+      <c r="FB2"/>
+      <c r="FC2"/>
+      <c r="FD2"/>
+      <c r="FE2"/>
+      <c r="FF2"/>
+      <c r="FG2"/>
+      <c r="FH2"/>
+      <c r="FI2"/>
+      <c r="FJ2"/>
+      <c r="FK2"/>
+      <c r="FL2"/>
+      <c r="FM2"/>
+      <c r="FN2"/>
+      <c r="FO2"/>
+      <c r="FP2"/>
+      <c r="FQ2"/>
+      <c r="FR2"/>
+      <c r="FS2"/>
+      <c r="FT2"/>
+      <c r="FU2"/>
+      <c r="FV2"/>
+      <c r="FW2"/>
+      <c r="FX2"/>
+      <c r="FY2"/>
+      <c r="FZ2"/>
+      <c r="GA2"/>
+      <c r="GB2"/>
+      <c r="GC2"/>
+      <c r="GD2"/>
+      <c r="GE2"/>
+      <c r="GF2"/>
+      <c r="GG2"/>
+      <c r="GH2"/>
+      <c r="GI2"/>
+      <c r="GJ2"/>
+      <c r="GK2"/>
+      <c r="GL2"/>
+      <c r="GM2"/>
+      <c r="GN2"/>
+      <c r="GO2"/>
+      <c r="GP2"/>
+      <c r="GQ2"/>
+      <c r="GR2"/>
+      <c r="GS2"/>
+      <c r="GT2"/>
+      <c r="GU2"/>
+      <c r="GV2"/>
+      <c r="GW2"/>
+      <c r="GX2"/>
+      <c r="GY2"/>
+      <c r="GZ2"/>
+      <c r="HA2"/>
+      <c r="HB2"/>
+      <c r="HC2"/>
+      <c r="HD2"/>
+      <c r="HE2"/>
+      <c r="HF2"/>
+      <c r="HG2"/>
+      <c r="HH2"/>
+      <c r="HI2"/>
+      <c r="HJ2"/>
+      <c r="HK2"/>
+      <c r="HL2"/>
+      <c r="HM2"/>
+      <c r="HN2"/>
+      <c r="HO2"/>
+      <c r="HP2"/>
+      <c r="HQ2"/>
+      <c r="HR2"/>
+      <c r="HS2"/>
+      <c r="HT2"/>
+      <c r="HU2"/>
+    </row>
+    <row r="3" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>385</v>
       </c>
+      <c r="D3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="4" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="5" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A5" s="8" t="s">
+        <v>391</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>392</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>393</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="6" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="7" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="8" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="9" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="10" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>414</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6EE6111-FDB3-4B43-8820-BBF68AAFCD6D}">
+  <dimension ref="A1:HU8"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="50.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="52.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.453125" customWidth="1"/>
+    <col min="4" max="4" width="33.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="33.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.08984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="40.81640625" customWidth="1"/>
+    <col min="8" max="8" width="62.54296875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="I2"/>
+      <c r="J2"/>
+      <c r="K2"/>
+      <c r="L2"/>
+      <c r="M2"/>
+      <c r="N2"/>
+      <c r="O2"/>
+      <c r="P2"/>
+      <c r="Q2"/>
+      <c r="R2"/>
+      <c r="S2"/>
+      <c r="T2"/>
+      <c r="U2"/>
+      <c r="V2"/>
+      <c r="W2"/>
+      <c r="X2"/>
+      <c r="Y2"/>
+      <c r="Z2"/>
+      <c r="AA2"/>
+      <c r="AB2"/>
+      <c r="AC2"/>
+      <c r="AD2"/>
+      <c r="AE2"/>
+      <c r="AF2"/>
+      <c r="AG2"/>
+      <c r="AH2"/>
+      <c r="AI2"/>
+      <c r="AJ2"/>
+      <c r="AK2"/>
+      <c r="AL2"/>
+      <c r="AM2"/>
+      <c r="AN2"/>
+      <c r="AO2"/>
+      <c r="AP2"/>
+      <c r="AQ2"/>
+      <c r="AR2"/>
+      <c r="AS2"/>
+      <c r="AT2"/>
+      <c r="AU2"/>
+      <c r="AV2"/>
+      <c r="AW2"/>
+      <c r="AX2"/>
+      <c r="AY2"/>
+      <c r="AZ2"/>
+      <c r="BA2"/>
+      <c r="BB2"/>
+      <c r="BC2"/>
+      <c r="BD2"/>
+      <c r="BE2"/>
+      <c r="BF2"/>
+      <c r="BG2"/>
+      <c r="BH2"/>
+      <c r="BI2"/>
+      <c r="BJ2"/>
+      <c r="BK2"/>
+      <c r="BL2"/>
+      <c r="BM2"/>
+      <c r="BN2"/>
+      <c r="BO2"/>
+      <c r="BP2"/>
+      <c r="BQ2"/>
+      <c r="BR2"/>
+      <c r="BS2"/>
+      <c r="BT2"/>
+      <c r="BU2"/>
+      <c r="BV2"/>
+      <c r="BW2"/>
+      <c r="BX2"/>
+      <c r="BY2"/>
+      <c r="BZ2"/>
+      <c r="CA2"/>
+      <c r="CB2"/>
+      <c r="CC2"/>
+      <c r="CD2"/>
+      <c r="CE2"/>
+      <c r="CF2"/>
+      <c r="CG2"/>
+      <c r="CH2"/>
+      <c r="CI2"/>
+      <c r="CJ2"/>
+      <c r="CK2"/>
+      <c r="CL2"/>
+      <c r="CM2"/>
+      <c r="CN2"/>
+      <c r="CO2"/>
+      <c r="CP2"/>
+      <c r="CQ2"/>
+      <c r="CR2"/>
+      <c r="CS2"/>
+      <c r="CT2"/>
+      <c r="CU2"/>
+      <c r="CV2"/>
+      <c r="CW2"/>
+      <c r="CX2"/>
+      <c r="CY2"/>
+      <c r="CZ2"/>
+      <c r="DA2"/>
+      <c r="DB2"/>
+      <c r="DC2"/>
+      <c r="DD2"/>
+      <c r="DE2"/>
+      <c r="DF2"/>
+      <c r="DG2"/>
+      <c r="DH2"/>
+      <c r="DI2"/>
+      <c r="DJ2"/>
+      <c r="DK2"/>
+      <c r="DL2"/>
+      <c r="DM2"/>
+      <c r="DN2"/>
+      <c r="DO2"/>
+      <c r="DP2"/>
+      <c r="DQ2"/>
+      <c r="DR2"/>
+      <c r="DS2"/>
+      <c r="DT2"/>
+      <c r="DU2"/>
+      <c r="DV2"/>
+      <c r="DW2"/>
+      <c r="DX2"/>
+      <c r="DY2"/>
+      <c r="DZ2"/>
+      <c r="EA2"/>
+      <c r="EB2"/>
+      <c r="EC2"/>
+      <c r="ED2"/>
+      <c r="EE2"/>
+      <c r="EF2"/>
+      <c r="EG2"/>
+      <c r="EH2"/>
+      <c r="EI2"/>
+      <c r="EJ2"/>
+      <c r="EK2"/>
+      <c r="EL2"/>
+      <c r="EM2"/>
+      <c r="EN2"/>
+      <c r="EO2"/>
+      <c r="EP2"/>
+      <c r="EQ2"/>
+      <c r="ER2"/>
+      <c r="ES2"/>
+      <c r="ET2"/>
+      <c r="EU2"/>
+      <c r="EV2"/>
+      <c r="EW2"/>
+      <c r="EX2"/>
+      <c r="EY2"/>
+      <c r="EZ2"/>
+      <c r="FA2"/>
+      <c r="FB2"/>
+      <c r="FC2"/>
+      <c r="FD2"/>
+      <c r="FE2"/>
+      <c r="FF2"/>
+      <c r="FG2"/>
+      <c r="FH2"/>
+      <c r="FI2"/>
+      <c r="FJ2"/>
+      <c r="FK2"/>
+      <c r="FL2"/>
+      <c r="FM2"/>
+      <c r="FN2"/>
+      <c r="FO2"/>
+      <c r="FP2"/>
+      <c r="FQ2"/>
+      <c r="FR2"/>
+      <c r="FS2"/>
+      <c r="FT2"/>
+      <c r="FU2"/>
+      <c r="FV2"/>
+      <c r="FW2"/>
+      <c r="FX2"/>
+      <c r="FY2"/>
+      <c r="FZ2"/>
+      <c r="GA2"/>
+      <c r="GB2"/>
+      <c r="GC2"/>
+      <c r="GD2"/>
+      <c r="GE2"/>
+      <c r="GF2"/>
+      <c r="GG2"/>
+      <c r="GH2"/>
+      <c r="GI2"/>
+      <c r="GJ2"/>
+      <c r="GK2"/>
+      <c r="GL2"/>
+      <c r="GM2"/>
+      <c r="GN2"/>
+      <c r="GO2"/>
+      <c r="GP2"/>
+      <c r="GQ2"/>
+      <c r="GR2"/>
+      <c r="GS2"/>
+      <c r="GT2"/>
+      <c r="GU2"/>
+      <c r="GV2"/>
+      <c r="GW2"/>
+      <c r="GX2"/>
+      <c r="GY2"/>
+      <c r="GZ2"/>
+      <c r="HA2"/>
+      <c r="HB2"/>
+      <c r="HC2"/>
+      <c r="HD2"/>
+      <c r="HE2"/>
+      <c r="HF2"/>
+      <c r="HG2"/>
+      <c r="HH2"/>
+      <c r="HI2"/>
+      <c r="HJ2"/>
+      <c r="HK2"/>
+      <c r="HL2"/>
+      <c r="HM2"/>
+      <c r="HN2"/>
+      <c r="HO2"/>
+      <c r="HP2"/>
+      <c r="HQ2"/>
+      <c r="HR2"/>
+      <c r="HS2"/>
+      <c r="HT2"/>
+      <c r="HU2"/>
+    </row>
+    <row r="3" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="4" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="5" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A5" s="8" t="s">
+        <v>426</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>427</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>428</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="6" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="7" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="8" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A8" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>439</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>440</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>441</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -13657,22 +14564,22 @@
     </row>
     <row r="2" spans="1:1029" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>387</v>
+        <v>372</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>388</v>
+        <v>373</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>389</v>
+        <v>374</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>386</v>
+        <v>371</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>390</v>
+        <v>375</v>
       </c>
     </row>
     <row r="3" spans="1:1029" x14ac:dyDescent="0.35">
@@ -13689,7 +14596,7 @@
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>386</v>
+        <v>371</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>93</v>
@@ -13709,7 +14616,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>386</v>
+        <v>371</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>124</v>
@@ -13729,7 +14636,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>386</v>
+        <v>371</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>73</v>
@@ -14772,7 +15679,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>386</v>
+        <v>371</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>97</v>
@@ -14792,7 +15699,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>386</v>
+        <v>371</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>89</v>
@@ -14812,7 +15719,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>386</v>
+        <v>371</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>76</v>
@@ -15855,7 +16762,7 @@
         <v>0</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>386</v>
+        <v>371</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>79</v>
@@ -15875,7 +16782,7 @@
         <v>0</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>386</v>
+        <v>371</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>85</v>
@@ -15895,7 +16802,7 @@
         <v>0</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>386</v>
+        <v>371</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>120</v>
@@ -16427,13 +17334,13 @@
     </row>
     <row r="4" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>391</v>
+        <v>376</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>392</v>
+        <v>377</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>393</v>
+        <v>378</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
@@ -16442,7 +17349,7 @@
         <v>101</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>394</v>
+        <v>379</v>
       </c>
       <c r="G4"/>
       <c r="H4"/>
@@ -16736,60 +17643,60 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>130</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>
@@ -16819,75 +17726,53 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
-        <v>149</v>
-      </c>
       <c r="B3" s="3" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
-        <v>150</v>
-      </c>
       <c r="B4" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>129</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>129</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3" t="s">
+      <c r="A7" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="C7" s="3" t="s">
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
         <v>146</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -16917,97 +17802,67 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
-        <v>158</v>
-      </c>
       <c r="B3" s="3" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
-        <v>157</v>
-      </c>
       <c r="B4" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>129</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>129</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>129</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>129</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>146</v>
+      <c r="A9" s="3" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>144</v>
+      <c r="A10" s="3" t="s">
+        <v>154</v>
       </c>
     </row>
   </sheetData>
@@ -17038,86 +17893,60 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
-        <v>164</v>
-      </c>
       <c r="B3" s="3" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
-        <v>165</v>
-      </c>
       <c r="B4" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>129</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>129</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>129</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>146</v>
+      <c r="A8" s="3" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>144</v>
+      <c r="A9" s="3" t="s">
+        <v>161</v>
       </c>
     </row>
   </sheetData>
@@ -17148,119 +17977,81 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
-        <v>171</v>
-      </c>
       <c r="B3" s="3" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
-        <v>172</v>
-      </c>
       <c r="B4" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>182</v>
+        <v>138</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>180</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>181</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>180</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>180</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>179</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>183</v>
-      </c>
+        <v>169</v>
+      </c>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>146</v>
+      <c r="A11" s="3" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>144</v>
+      <c r="A12" s="3" t="s">
+        <v>171</v>
       </c>
     </row>
   </sheetData>

--- a/testdata.xlsx
+++ b/testdata.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sshiwani\workspace\find-information-products-services-tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F43993A-715F-4D1C-B894-7EEE8875F979}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9D47F77-FF77-46CE-ACAE-C8E70E8090EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" firstSheet="21" activeTab="23" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="category_phase" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="877" uniqueCount="442">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="883" uniqueCount="446">
   <si>
     <t>Search and filter products and services</t>
   </si>
@@ -1374,6 +1374,18 @@
   </si>
   <si>
     <t>Trade union bodies workforce (data user)  (Professional external user of DfE data)</t>
+  </si>
+  <si>
+    <t>products?phase=did-not-progress</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Did not progress')</t>
+  </si>
+  <si>
+    <t>Remove this filter Did not progress</t>
+  </si>
+  <si>
+    <t>#phase-did-not-progress</t>
   </si>
 </sst>
 </file>
@@ -1793,7 +1805,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:ARE8"/>
+  <dimension ref="A1:ARE9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="30" bestFit="1" customWidth="1"/>
@@ -4152,13 +4164,13 @@
     </row>
     <row r="4" spans="1:1149" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>10</v>
+        <v>442</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>11</v>
+        <v>443</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>12</v>
+        <v>444</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
@@ -4167,7 +4179,7 @@
         <v>1</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>13</v>
+        <v>445</v>
       </c>
       <c r="G4"/>
       <c r="H4"/>
@@ -5315,13 +5327,13 @@
     </row>
     <row r="5" spans="1:1149" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
@@ -5330,7 +5342,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G5"/>
       <c r="H5"/>
@@ -6478,13 +6490,13 @@
     </row>
     <row r="6" spans="1:1149" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>0</v>
@@ -6493,7 +6505,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="G6"/>
       <c r="H6"/>
@@ -7641,13 +7653,13 @@
     </row>
     <row r="7" spans="1:1149" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>0</v>
@@ -7656,7 +7668,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G7"/>
       <c r="H7"/>
@@ -8804,13 +8816,13 @@
     </row>
     <row r="8" spans="1:1149" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>0</v>
@@ -8819,7 +8831,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G8"/>
       <c r="H8"/>
@@ -9965,6 +9977,1169 @@
       <c r="ARD8"/>
       <c r="ARE8"/>
     </row>
+    <row r="9" spans="1:1149" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G9"/>
+      <c r="H9"/>
+      <c r="I9"/>
+      <c r="J9"/>
+      <c r="K9"/>
+      <c r="L9"/>
+      <c r="M9"/>
+      <c r="N9"/>
+      <c r="O9"/>
+      <c r="P9"/>
+      <c r="Q9"/>
+      <c r="R9"/>
+      <c r="S9"/>
+      <c r="T9"/>
+      <c r="U9"/>
+      <c r="V9"/>
+      <c r="W9"/>
+      <c r="X9"/>
+      <c r="Y9"/>
+      <c r="Z9"/>
+      <c r="AA9"/>
+      <c r="AB9"/>
+      <c r="AC9"/>
+      <c r="AD9"/>
+      <c r="AE9"/>
+      <c r="AF9"/>
+      <c r="AG9"/>
+      <c r="AH9"/>
+      <c r="AI9"/>
+      <c r="AJ9"/>
+      <c r="AK9"/>
+      <c r="AL9"/>
+      <c r="AM9"/>
+      <c r="AN9"/>
+      <c r="AO9"/>
+      <c r="AP9"/>
+      <c r="AQ9"/>
+      <c r="AR9"/>
+      <c r="AS9"/>
+      <c r="AT9"/>
+      <c r="AU9"/>
+      <c r="AV9"/>
+      <c r="AW9"/>
+      <c r="AX9"/>
+      <c r="AY9"/>
+      <c r="AZ9"/>
+      <c r="BA9"/>
+      <c r="BB9"/>
+      <c r="BC9"/>
+      <c r="BD9"/>
+      <c r="BE9"/>
+      <c r="BF9"/>
+      <c r="BG9"/>
+      <c r="BH9"/>
+      <c r="BI9"/>
+      <c r="BJ9"/>
+      <c r="BK9"/>
+      <c r="BL9"/>
+      <c r="BM9"/>
+      <c r="BN9"/>
+      <c r="BO9"/>
+      <c r="BP9"/>
+      <c r="BQ9"/>
+      <c r="BR9"/>
+      <c r="BS9"/>
+      <c r="BT9"/>
+      <c r="BU9"/>
+      <c r="BV9"/>
+      <c r="BW9"/>
+      <c r="BX9"/>
+      <c r="BY9"/>
+      <c r="BZ9"/>
+      <c r="CA9"/>
+      <c r="CB9"/>
+      <c r="CC9"/>
+      <c r="CD9"/>
+      <c r="CE9"/>
+      <c r="CF9"/>
+      <c r="CG9"/>
+      <c r="CH9"/>
+      <c r="CI9"/>
+      <c r="CJ9"/>
+      <c r="CK9"/>
+      <c r="CL9"/>
+      <c r="CM9"/>
+      <c r="CN9"/>
+      <c r="CO9"/>
+      <c r="CP9"/>
+      <c r="CQ9"/>
+      <c r="CR9"/>
+      <c r="CS9"/>
+      <c r="CT9"/>
+      <c r="CU9"/>
+      <c r="CV9"/>
+      <c r="CW9"/>
+      <c r="CX9"/>
+      <c r="CY9"/>
+      <c r="CZ9"/>
+      <c r="DA9"/>
+      <c r="DB9"/>
+      <c r="DC9"/>
+      <c r="DD9"/>
+      <c r="DE9"/>
+      <c r="DF9"/>
+      <c r="DG9"/>
+      <c r="DH9"/>
+      <c r="DI9"/>
+      <c r="DJ9"/>
+      <c r="DK9"/>
+      <c r="DL9"/>
+      <c r="DM9"/>
+      <c r="DN9"/>
+      <c r="DO9"/>
+      <c r="DP9"/>
+      <c r="DQ9"/>
+      <c r="DR9"/>
+      <c r="DS9"/>
+      <c r="DT9"/>
+      <c r="DU9"/>
+      <c r="DV9"/>
+      <c r="DW9"/>
+      <c r="DX9"/>
+      <c r="DY9"/>
+      <c r="DZ9"/>
+      <c r="EA9"/>
+      <c r="EB9"/>
+      <c r="EC9"/>
+      <c r="ED9"/>
+      <c r="EE9"/>
+      <c r="EF9"/>
+      <c r="EG9"/>
+      <c r="EH9"/>
+      <c r="EI9"/>
+      <c r="EJ9"/>
+      <c r="EK9"/>
+      <c r="EL9"/>
+      <c r="EM9"/>
+      <c r="EN9"/>
+      <c r="EO9"/>
+      <c r="EP9"/>
+      <c r="EQ9"/>
+      <c r="ER9"/>
+      <c r="ES9"/>
+      <c r="ET9"/>
+      <c r="EU9"/>
+      <c r="EV9"/>
+      <c r="EW9"/>
+      <c r="EX9"/>
+      <c r="EY9"/>
+      <c r="EZ9"/>
+      <c r="FA9"/>
+      <c r="FB9"/>
+      <c r="FC9"/>
+      <c r="FD9"/>
+      <c r="FE9"/>
+      <c r="FF9"/>
+      <c r="FG9"/>
+      <c r="FH9"/>
+      <c r="FI9"/>
+      <c r="FJ9"/>
+      <c r="FK9"/>
+      <c r="FL9"/>
+      <c r="FM9"/>
+      <c r="FN9"/>
+      <c r="FO9"/>
+      <c r="FP9"/>
+      <c r="FQ9"/>
+      <c r="FR9"/>
+      <c r="FS9"/>
+      <c r="FT9"/>
+      <c r="FU9"/>
+      <c r="FV9"/>
+      <c r="FW9"/>
+      <c r="FX9"/>
+      <c r="FY9"/>
+      <c r="FZ9"/>
+      <c r="GA9"/>
+      <c r="GB9"/>
+      <c r="GC9"/>
+      <c r="GD9"/>
+      <c r="GE9"/>
+      <c r="GF9"/>
+      <c r="GG9"/>
+      <c r="GH9"/>
+      <c r="GI9"/>
+      <c r="GJ9"/>
+      <c r="GK9"/>
+      <c r="GL9"/>
+      <c r="GM9"/>
+      <c r="GN9"/>
+      <c r="GO9"/>
+      <c r="GP9"/>
+      <c r="GQ9"/>
+      <c r="GR9"/>
+      <c r="GS9"/>
+      <c r="GT9"/>
+      <c r="GU9"/>
+      <c r="GV9"/>
+      <c r="GW9"/>
+      <c r="GX9"/>
+      <c r="GY9"/>
+      <c r="GZ9"/>
+      <c r="HA9"/>
+      <c r="HB9"/>
+      <c r="HC9"/>
+      <c r="HD9"/>
+      <c r="HE9"/>
+      <c r="HF9"/>
+      <c r="HG9"/>
+      <c r="HH9"/>
+      <c r="HI9"/>
+      <c r="HJ9"/>
+      <c r="HK9"/>
+      <c r="HL9"/>
+      <c r="HM9"/>
+      <c r="HN9"/>
+      <c r="HO9"/>
+      <c r="HP9"/>
+      <c r="HQ9"/>
+      <c r="HR9"/>
+      <c r="HS9"/>
+      <c r="HT9"/>
+      <c r="HU9"/>
+      <c r="HV9"/>
+      <c r="HW9"/>
+      <c r="HX9"/>
+      <c r="HY9"/>
+      <c r="HZ9"/>
+      <c r="IA9"/>
+      <c r="IB9"/>
+      <c r="IC9"/>
+      <c r="ID9"/>
+      <c r="IE9"/>
+      <c r="IF9"/>
+      <c r="IG9"/>
+      <c r="IH9"/>
+      <c r="II9"/>
+      <c r="IJ9"/>
+      <c r="IK9"/>
+      <c r="IL9"/>
+      <c r="IM9"/>
+      <c r="IN9"/>
+      <c r="IO9"/>
+      <c r="IP9"/>
+      <c r="IQ9"/>
+      <c r="IR9"/>
+      <c r="IS9"/>
+      <c r="IT9"/>
+      <c r="IU9"/>
+      <c r="IV9"/>
+      <c r="IW9"/>
+      <c r="IX9"/>
+      <c r="IY9"/>
+      <c r="IZ9"/>
+      <c r="JA9"/>
+      <c r="JB9"/>
+      <c r="JC9"/>
+      <c r="JD9"/>
+      <c r="JE9"/>
+      <c r="JF9"/>
+      <c r="JG9"/>
+      <c r="JH9"/>
+      <c r="JI9"/>
+      <c r="JJ9"/>
+      <c r="JK9"/>
+      <c r="JL9"/>
+      <c r="JM9"/>
+      <c r="JN9"/>
+      <c r="JO9"/>
+      <c r="JP9"/>
+      <c r="JQ9"/>
+      <c r="JR9"/>
+      <c r="JS9"/>
+      <c r="JT9"/>
+      <c r="JU9"/>
+      <c r="JV9"/>
+      <c r="JW9"/>
+      <c r="JX9"/>
+      <c r="JY9"/>
+      <c r="JZ9"/>
+      <c r="KA9"/>
+      <c r="KB9"/>
+      <c r="KC9"/>
+      <c r="KD9"/>
+      <c r="KE9"/>
+      <c r="KF9"/>
+      <c r="KG9"/>
+      <c r="KH9"/>
+      <c r="KI9"/>
+      <c r="KJ9"/>
+      <c r="KK9"/>
+      <c r="KL9"/>
+      <c r="KM9"/>
+      <c r="KN9"/>
+      <c r="KO9"/>
+      <c r="KP9"/>
+      <c r="KQ9"/>
+      <c r="KR9"/>
+      <c r="KS9"/>
+      <c r="KT9"/>
+      <c r="KU9"/>
+      <c r="KV9"/>
+      <c r="KW9"/>
+      <c r="KX9"/>
+      <c r="KY9"/>
+      <c r="KZ9"/>
+      <c r="LA9"/>
+      <c r="LB9"/>
+      <c r="LC9"/>
+      <c r="LD9"/>
+      <c r="LE9"/>
+      <c r="LF9"/>
+      <c r="LG9"/>
+      <c r="LH9"/>
+      <c r="LI9"/>
+      <c r="LJ9"/>
+      <c r="LK9"/>
+      <c r="LL9"/>
+      <c r="LM9"/>
+      <c r="LN9"/>
+      <c r="LO9"/>
+      <c r="LP9"/>
+      <c r="LQ9"/>
+      <c r="LR9"/>
+      <c r="LS9"/>
+      <c r="LT9"/>
+      <c r="LU9"/>
+      <c r="LV9"/>
+      <c r="LW9"/>
+      <c r="LX9"/>
+      <c r="LY9"/>
+      <c r="LZ9"/>
+      <c r="MA9"/>
+      <c r="MB9"/>
+      <c r="MC9"/>
+      <c r="MD9"/>
+      <c r="ME9"/>
+      <c r="MF9"/>
+      <c r="MG9"/>
+      <c r="MH9"/>
+      <c r="MI9"/>
+      <c r="MJ9"/>
+      <c r="MK9"/>
+      <c r="ML9"/>
+      <c r="MM9"/>
+      <c r="MN9"/>
+      <c r="MO9"/>
+      <c r="MP9"/>
+      <c r="MQ9"/>
+      <c r="MR9"/>
+      <c r="MS9"/>
+      <c r="MT9"/>
+      <c r="MU9"/>
+      <c r="MV9"/>
+      <c r="MW9"/>
+      <c r="MX9"/>
+      <c r="MY9"/>
+      <c r="MZ9"/>
+      <c r="NA9"/>
+      <c r="NB9"/>
+      <c r="NC9"/>
+      <c r="ND9"/>
+      <c r="NE9"/>
+      <c r="NF9"/>
+      <c r="NG9"/>
+      <c r="NH9"/>
+      <c r="NI9"/>
+      <c r="NJ9"/>
+      <c r="NK9"/>
+      <c r="NL9"/>
+      <c r="NM9"/>
+      <c r="NN9"/>
+      <c r="NO9"/>
+      <c r="NP9"/>
+      <c r="NQ9"/>
+      <c r="NR9"/>
+      <c r="NS9"/>
+      <c r="NT9"/>
+      <c r="NU9"/>
+      <c r="NV9"/>
+      <c r="NW9"/>
+      <c r="NX9"/>
+      <c r="NY9"/>
+      <c r="NZ9"/>
+      <c r="OA9"/>
+      <c r="OB9"/>
+      <c r="OC9"/>
+      <c r="OD9"/>
+      <c r="OE9"/>
+      <c r="OF9"/>
+      <c r="OG9"/>
+      <c r="OH9"/>
+      <c r="OI9"/>
+      <c r="OJ9"/>
+      <c r="OK9"/>
+      <c r="OL9"/>
+      <c r="OM9"/>
+      <c r="ON9"/>
+      <c r="OO9"/>
+      <c r="OP9"/>
+      <c r="OQ9"/>
+      <c r="OR9"/>
+      <c r="OS9"/>
+      <c r="OT9"/>
+      <c r="OU9"/>
+      <c r="OV9"/>
+      <c r="OW9"/>
+      <c r="OX9"/>
+      <c r="OY9"/>
+      <c r="OZ9"/>
+      <c r="PA9"/>
+      <c r="PB9"/>
+      <c r="PC9"/>
+      <c r="PD9"/>
+      <c r="PE9"/>
+      <c r="PF9"/>
+      <c r="PG9"/>
+      <c r="PH9"/>
+      <c r="PI9"/>
+      <c r="PJ9"/>
+      <c r="PK9"/>
+      <c r="PL9"/>
+      <c r="PM9"/>
+      <c r="PN9"/>
+      <c r="PO9"/>
+      <c r="PP9"/>
+      <c r="PQ9"/>
+      <c r="PR9"/>
+      <c r="PS9"/>
+      <c r="PT9"/>
+      <c r="PU9"/>
+      <c r="PV9"/>
+      <c r="PW9"/>
+      <c r="PX9"/>
+      <c r="PY9"/>
+      <c r="PZ9"/>
+      <c r="QA9"/>
+      <c r="QB9"/>
+      <c r="QC9"/>
+      <c r="QD9"/>
+      <c r="QE9"/>
+      <c r="QF9"/>
+      <c r="QG9"/>
+      <c r="QH9"/>
+      <c r="QI9"/>
+      <c r="QJ9"/>
+      <c r="QK9"/>
+      <c r="QL9"/>
+      <c r="QM9"/>
+      <c r="QN9"/>
+      <c r="QO9"/>
+      <c r="QP9"/>
+      <c r="QQ9"/>
+      <c r="QR9"/>
+      <c r="QS9"/>
+      <c r="QT9"/>
+      <c r="QU9"/>
+      <c r="QV9"/>
+      <c r="QW9"/>
+      <c r="QX9"/>
+      <c r="QY9"/>
+      <c r="QZ9"/>
+      <c r="RA9"/>
+      <c r="RB9"/>
+      <c r="RC9"/>
+      <c r="RD9"/>
+      <c r="RE9"/>
+      <c r="RF9"/>
+      <c r="RG9"/>
+      <c r="RH9"/>
+      <c r="RI9"/>
+      <c r="RJ9"/>
+      <c r="RK9"/>
+      <c r="RL9"/>
+      <c r="RM9"/>
+      <c r="RN9"/>
+      <c r="RO9"/>
+      <c r="RP9"/>
+      <c r="RQ9"/>
+      <c r="RR9"/>
+      <c r="RS9"/>
+      <c r="RT9"/>
+      <c r="RU9"/>
+      <c r="RV9"/>
+      <c r="RW9"/>
+      <c r="RX9"/>
+      <c r="RY9"/>
+      <c r="RZ9"/>
+      <c r="SA9"/>
+      <c r="SB9"/>
+      <c r="SC9"/>
+      <c r="SD9"/>
+      <c r="SE9"/>
+      <c r="SF9"/>
+      <c r="SG9"/>
+      <c r="SH9"/>
+      <c r="SI9"/>
+      <c r="SJ9"/>
+      <c r="SK9"/>
+      <c r="SL9"/>
+      <c r="SM9"/>
+      <c r="SN9"/>
+      <c r="SO9"/>
+      <c r="SP9"/>
+      <c r="SQ9"/>
+      <c r="SR9"/>
+      <c r="SS9"/>
+      <c r="ST9"/>
+      <c r="SU9"/>
+      <c r="SV9"/>
+      <c r="SW9"/>
+      <c r="SX9"/>
+      <c r="SY9"/>
+      <c r="SZ9"/>
+      <c r="TA9"/>
+      <c r="TB9"/>
+      <c r="TC9"/>
+      <c r="TD9"/>
+      <c r="TE9"/>
+      <c r="TF9"/>
+      <c r="TG9"/>
+      <c r="TH9"/>
+      <c r="TI9"/>
+      <c r="TJ9"/>
+      <c r="TK9"/>
+      <c r="TL9"/>
+      <c r="TM9"/>
+      <c r="TN9"/>
+      <c r="TO9"/>
+      <c r="TP9"/>
+      <c r="TQ9"/>
+      <c r="TR9"/>
+      <c r="TS9"/>
+      <c r="TT9"/>
+      <c r="TU9"/>
+      <c r="TV9"/>
+      <c r="TW9"/>
+      <c r="TX9"/>
+      <c r="TY9"/>
+      <c r="TZ9"/>
+      <c r="UA9"/>
+      <c r="UB9"/>
+      <c r="UC9"/>
+      <c r="UD9"/>
+      <c r="UE9"/>
+      <c r="UF9"/>
+      <c r="UG9"/>
+      <c r="UH9"/>
+      <c r="UI9"/>
+      <c r="UJ9"/>
+      <c r="UK9"/>
+      <c r="UL9"/>
+      <c r="UM9"/>
+      <c r="UN9"/>
+      <c r="UO9"/>
+      <c r="UP9"/>
+      <c r="UQ9"/>
+      <c r="UR9"/>
+      <c r="US9"/>
+      <c r="UT9"/>
+      <c r="UU9"/>
+      <c r="UV9"/>
+      <c r="UW9"/>
+      <c r="UX9"/>
+      <c r="UY9"/>
+      <c r="UZ9"/>
+      <c r="VA9"/>
+      <c r="VB9"/>
+      <c r="VC9"/>
+      <c r="VD9"/>
+      <c r="VE9"/>
+      <c r="VF9"/>
+      <c r="VG9"/>
+      <c r="VH9"/>
+      <c r="VI9"/>
+      <c r="VJ9"/>
+      <c r="VK9"/>
+      <c r="VL9"/>
+      <c r="VM9"/>
+      <c r="VN9"/>
+      <c r="VO9"/>
+      <c r="VP9"/>
+      <c r="VQ9"/>
+      <c r="VR9"/>
+      <c r="VS9"/>
+      <c r="VT9"/>
+      <c r="VU9"/>
+      <c r="VV9"/>
+      <c r="VW9"/>
+      <c r="VX9"/>
+      <c r="VY9"/>
+      <c r="VZ9"/>
+      <c r="WA9"/>
+      <c r="WB9"/>
+      <c r="WC9"/>
+      <c r="WD9"/>
+      <c r="WE9"/>
+      <c r="WF9"/>
+      <c r="WG9"/>
+      <c r="WH9"/>
+      <c r="WI9"/>
+      <c r="WJ9"/>
+      <c r="WK9"/>
+      <c r="WL9"/>
+      <c r="WM9"/>
+      <c r="WN9"/>
+      <c r="WO9"/>
+      <c r="WP9"/>
+      <c r="WQ9"/>
+      <c r="WR9"/>
+      <c r="WS9"/>
+      <c r="WT9"/>
+      <c r="WU9"/>
+      <c r="WV9"/>
+      <c r="WW9"/>
+      <c r="WX9"/>
+      <c r="WY9"/>
+      <c r="WZ9"/>
+      <c r="XA9"/>
+      <c r="XB9"/>
+      <c r="XC9"/>
+      <c r="XD9"/>
+      <c r="XE9"/>
+      <c r="XF9"/>
+      <c r="XG9"/>
+      <c r="XH9"/>
+      <c r="XI9"/>
+      <c r="XJ9"/>
+      <c r="XK9"/>
+      <c r="XL9"/>
+      <c r="XM9"/>
+      <c r="XN9"/>
+      <c r="XO9"/>
+      <c r="XP9"/>
+      <c r="XQ9"/>
+      <c r="XR9"/>
+      <c r="XS9"/>
+      <c r="XT9"/>
+      <c r="XU9"/>
+      <c r="XV9"/>
+      <c r="XW9"/>
+      <c r="XX9"/>
+      <c r="XY9"/>
+      <c r="XZ9"/>
+      <c r="YA9"/>
+      <c r="YB9"/>
+      <c r="YC9"/>
+      <c r="YD9"/>
+      <c r="YE9"/>
+      <c r="YF9"/>
+      <c r="YG9"/>
+      <c r="YH9"/>
+      <c r="YI9"/>
+      <c r="YJ9"/>
+      <c r="YK9"/>
+      <c r="YL9"/>
+      <c r="YM9"/>
+      <c r="YN9"/>
+      <c r="YO9"/>
+      <c r="YP9"/>
+      <c r="YQ9"/>
+      <c r="YR9"/>
+      <c r="YS9"/>
+      <c r="YT9"/>
+      <c r="YU9"/>
+      <c r="YV9"/>
+      <c r="YW9"/>
+      <c r="YX9"/>
+      <c r="YY9"/>
+      <c r="YZ9"/>
+      <c r="ZA9"/>
+      <c r="ZB9"/>
+      <c r="ZC9"/>
+      <c r="ZD9"/>
+      <c r="ZE9"/>
+      <c r="ZF9"/>
+      <c r="ZG9"/>
+      <c r="ZH9"/>
+      <c r="ZI9"/>
+      <c r="ZJ9"/>
+      <c r="ZK9"/>
+      <c r="ZL9"/>
+      <c r="ZM9"/>
+      <c r="ZN9"/>
+      <c r="ZO9"/>
+      <c r="ZP9"/>
+      <c r="ZQ9"/>
+      <c r="ZR9"/>
+      <c r="ZS9"/>
+      <c r="ZT9"/>
+      <c r="ZU9"/>
+      <c r="ZV9"/>
+      <c r="ZW9"/>
+      <c r="ZX9"/>
+      <c r="ZY9"/>
+      <c r="ZZ9"/>
+      <c r="AAA9"/>
+      <c r="AAB9"/>
+      <c r="AAC9"/>
+      <c r="AAD9"/>
+      <c r="AAE9"/>
+      <c r="AAF9"/>
+      <c r="AAG9"/>
+      <c r="AAH9"/>
+      <c r="AAI9"/>
+      <c r="AAJ9"/>
+      <c r="AAK9"/>
+      <c r="AAL9"/>
+      <c r="AAM9"/>
+      <c r="AAN9"/>
+      <c r="AAO9"/>
+      <c r="AAP9"/>
+      <c r="AAQ9"/>
+      <c r="AAR9"/>
+      <c r="AAS9"/>
+      <c r="AAT9"/>
+      <c r="AAU9"/>
+      <c r="AAV9"/>
+      <c r="AAW9"/>
+      <c r="AAX9"/>
+      <c r="AAY9"/>
+      <c r="AAZ9"/>
+      <c r="ABA9"/>
+      <c r="ABB9"/>
+      <c r="ABC9"/>
+      <c r="ABD9"/>
+      <c r="ABE9"/>
+      <c r="ABF9"/>
+      <c r="ABG9"/>
+      <c r="ABH9"/>
+      <c r="ABI9"/>
+      <c r="ABJ9"/>
+      <c r="ABK9"/>
+      <c r="ABL9"/>
+      <c r="ABM9"/>
+      <c r="ABN9"/>
+      <c r="ABO9"/>
+      <c r="ABP9"/>
+      <c r="ABQ9"/>
+      <c r="ABR9"/>
+      <c r="ABS9"/>
+      <c r="ABT9"/>
+      <c r="ABU9"/>
+      <c r="ABV9"/>
+      <c r="ABW9"/>
+      <c r="ABX9"/>
+      <c r="ABY9"/>
+      <c r="ABZ9"/>
+      <c r="ACA9"/>
+      <c r="ACB9"/>
+      <c r="ACC9"/>
+      <c r="ACD9"/>
+      <c r="ACE9"/>
+      <c r="ACF9"/>
+      <c r="ACG9"/>
+      <c r="ACH9"/>
+      <c r="ACI9"/>
+      <c r="ACJ9"/>
+      <c r="ACK9"/>
+      <c r="ACL9"/>
+      <c r="ACM9"/>
+      <c r="ACN9"/>
+      <c r="ACO9"/>
+      <c r="ACP9"/>
+      <c r="ACQ9"/>
+      <c r="ACR9"/>
+      <c r="ACS9"/>
+      <c r="ACT9"/>
+      <c r="ACU9"/>
+      <c r="ACV9"/>
+      <c r="ACW9"/>
+      <c r="ACX9"/>
+      <c r="ACY9"/>
+      <c r="ACZ9"/>
+      <c r="ADA9"/>
+      <c r="ADB9"/>
+      <c r="ADC9"/>
+      <c r="ADD9"/>
+      <c r="ADE9"/>
+      <c r="ADF9"/>
+      <c r="ADG9"/>
+      <c r="ADH9"/>
+      <c r="ADI9"/>
+      <c r="ADJ9"/>
+      <c r="ADK9"/>
+      <c r="ADL9"/>
+      <c r="ADM9"/>
+      <c r="ADN9"/>
+      <c r="ADO9"/>
+      <c r="ADP9"/>
+      <c r="ADQ9"/>
+      <c r="ADR9"/>
+      <c r="ADS9"/>
+      <c r="ADT9"/>
+      <c r="ADU9"/>
+      <c r="ADV9"/>
+      <c r="ADW9"/>
+      <c r="ADX9"/>
+      <c r="ADY9"/>
+      <c r="ADZ9"/>
+      <c r="AEA9"/>
+      <c r="AEB9"/>
+      <c r="AEC9"/>
+      <c r="AED9"/>
+      <c r="AEE9"/>
+      <c r="AEF9"/>
+      <c r="AEG9"/>
+      <c r="AEH9"/>
+      <c r="AEI9"/>
+      <c r="AEJ9"/>
+      <c r="AEK9"/>
+      <c r="AEL9"/>
+      <c r="AEM9"/>
+      <c r="AEN9"/>
+      <c r="AEO9"/>
+      <c r="AEP9"/>
+      <c r="AEQ9"/>
+      <c r="AER9"/>
+      <c r="AES9"/>
+      <c r="AET9"/>
+      <c r="AEU9"/>
+      <c r="AEV9"/>
+      <c r="AEW9"/>
+      <c r="AEX9"/>
+      <c r="AEY9"/>
+      <c r="AEZ9"/>
+      <c r="AFA9"/>
+      <c r="AFB9"/>
+      <c r="AFC9"/>
+      <c r="AFD9"/>
+      <c r="AFE9"/>
+      <c r="AFF9"/>
+      <c r="AFG9"/>
+      <c r="AFH9"/>
+      <c r="AFI9"/>
+      <c r="AFJ9"/>
+      <c r="AFK9"/>
+      <c r="AFL9"/>
+      <c r="AFM9"/>
+      <c r="AFN9"/>
+      <c r="AFO9"/>
+      <c r="AFP9"/>
+      <c r="AFQ9"/>
+      <c r="AFR9"/>
+      <c r="AFS9"/>
+      <c r="AFT9"/>
+      <c r="AFU9"/>
+      <c r="AFV9"/>
+      <c r="AFW9"/>
+      <c r="AFX9"/>
+      <c r="AFY9"/>
+      <c r="AFZ9"/>
+      <c r="AGA9"/>
+      <c r="AGB9"/>
+      <c r="AGC9"/>
+      <c r="AGD9"/>
+      <c r="AGE9"/>
+      <c r="AGF9"/>
+      <c r="AGG9"/>
+      <c r="AGH9"/>
+      <c r="AGI9"/>
+      <c r="AGJ9"/>
+      <c r="AGK9"/>
+      <c r="AGL9"/>
+      <c r="AGM9"/>
+      <c r="AGN9"/>
+      <c r="AGO9"/>
+      <c r="AGP9"/>
+      <c r="AGQ9"/>
+      <c r="AGR9"/>
+      <c r="AGS9"/>
+      <c r="AGT9"/>
+      <c r="AGU9"/>
+      <c r="AGV9"/>
+      <c r="AGW9"/>
+      <c r="AGX9"/>
+      <c r="AGY9"/>
+      <c r="AGZ9"/>
+      <c r="AHA9"/>
+      <c r="AHB9"/>
+      <c r="AHC9"/>
+      <c r="AHD9"/>
+      <c r="AHE9"/>
+      <c r="AHF9"/>
+      <c r="AHG9"/>
+      <c r="AHH9"/>
+      <c r="AHI9"/>
+      <c r="AHJ9"/>
+      <c r="AHK9"/>
+      <c r="AHL9"/>
+      <c r="AHM9"/>
+      <c r="AHN9"/>
+      <c r="AHO9"/>
+      <c r="AHP9"/>
+      <c r="AHQ9"/>
+      <c r="AHR9"/>
+      <c r="AHS9"/>
+      <c r="AHT9"/>
+      <c r="AHU9"/>
+      <c r="AHV9"/>
+      <c r="AHW9"/>
+      <c r="AHX9"/>
+      <c r="AHY9"/>
+      <c r="AHZ9"/>
+      <c r="AIA9"/>
+      <c r="AIB9"/>
+      <c r="AIC9"/>
+      <c r="AID9"/>
+      <c r="AIE9"/>
+      <c r="AIF9"/>
+      <c r="AIG9"/>
+      <c r="AIH9"/>
+      <c r="AII9"/>
+      <c r="AIJ9"/>
+      <c r="AIK9"/>
+      <c r="AIL9"/>
+      <c r="AIM9"/>
+      <c r="AIN9"/>
+      <c r="AIO9"/>
+      <c r="AIP9"/>
+      <c r="AIQ9"/>
+      <c r="AIR9"/>
+      <c r="AIS9"/>
+      <c r="AIT9"/>
+      <c r="AIU9"/>
+      <c r="AIV9"/>
+      <c r="AIW9"/>
+      <c r="AIX9"/>
+      <c r="AIY9"/>
+      <c r="AIZ9"/>
+      <c r="AJA9"/>
+      <c r="AJB9"/>
+      <c r="AJC9"/>
+      <c r="AJD9"/>
+      <c r="AJE9"/>
+      <c r="AJF9"/>
+      <c r="AJG9"/>
+      <c r="AJH9"/>
+      <c r="AJI9"/>
+      <c r="AJJ9"/>
+      <c r="AJK9"/>
+      <c r="AJL9"/>
+      <c r="AJM9"/>
+      <c r="AJN9"/>
+      <c r="AJO9"/>
+      <c r="AJP9"/>
+      <c r="AJQ9"/>
+      <c r="AJR9"/>
+      <c r="AJS9"/>
+      <c r="AJT9"/>
+      <c r="AJU9"/>
+      <c r="AJV9"/>
+      <c r="AJW9"/>
+      <c r="AJX9"/>
+      <c r="AJY9"/>
+      <c r="AJZ9"/>
+      <c r="AKA9"/>
+      <c r="AKB9"/>
+      <c r="AKC9"/>
+      <c r="AKD9"/>
+      <c r="AKE9"/>
+      <c r="AKF9"/>
+      <c r="AKG9"/>
+      <c r="AKH9"/>
+      <c r="AKI9"/>
+      <c r="AKJ9"/>
+      <c r="AKK9"/>
+      <c r="AKL9"/>
+      <c r="AKM9"/>
+      <c r="AKN9"/>
+      <c r="AKO9"/>
+      <c r="AKP9"/>
+      <c r="AKQ9"/>
+      <c r="AKR9"/>
+      <c r="AKS9"/>
+      <c r="AKT9"/>
+      <c r="AKU9"/>
+      <c r="AKV9"/>
+      <c r="AKW9"/>
+      <c r="AKX9"/>
+      <c r="AKY9"/>
+      <c r="AKZ9"/>
+      <c r="ALA9"/>
+      <c r="ALB9"/>
+      <c r="ALC9"/>
+      <c r="ALD9"/>
+      <c r="ALE9"/>
+      <c r="ALF9"/>
+      <c r="ALG9"/>
+      <c r="ALH9"/>
+      <c r="ALI9"/>
+      <c r="ALJ9"/>
+      <c r="ALK9"/>
+      <c r="ALL9"/>
+      <c r="ALM9"/>
+      <c r="ALN9"/>
+      <c r="ALO9"/>
+      <c r="ALP9"/>
+      <c r="ALQ9"/>
+      <c r="ALR9"/>
+      <c r="ALS9"/>
+      <c r="ALT9"/>
+      <c r="ALU9"/>
+      <c r="ALV9"/>
+      <c r="ALW9"/>
+      <c r="ALX9"/>
+      <c r="ALY9"/>
+      <c r="ALZ9"/>
+      <c r="AMA9"/>
+      <c r="AMB9"/>
+      <c r="AMC9"/>
+      <c r="AMD9"/>
+      <c r="AME9"/>
+      <c r="AMF9"/>
+      <c r="AMG9"/>
+      <c r="AMH9"/>
+      <c r="AMI9"/>
+      <c r="AMJ9"/>
+      <c r="AMK9"/>
+      <c r="AML9"/>
+      <c r="AMM9"/>
+      <c r="AMN9"/>
+      <c r="AMO9"/>
+      <c r="AMP9"/>
+      <c r="AMQ9"/>
+      <c r="AMR9"/>
+      <c r="AMS9"/>
+      <c r="AMT9"/>
+      <c r="AMU9"/>
+      <c r="AMV9"/>
+      <c r="AMW9"/>
+      <c r="AMX9"/>
+      <c r="AMY9"/>
+      <c r="AMZ9"/>
+      <c r="ANA9"/>
+      <c r="ANB9"/>
+      <c r="ANC9"/>
+      <c r="AND9"/>
+      <c r="ANE9"/>
+      <c r="ANF9"/>
+      <c r="ANG9"/>
+      <c r="ANH9"/>
+      <c r="ANI9"/>
+      <c r="ANJ9"/>
+      <c r="ANK9"/>
+      <c r="ANL9"/>
+      <c r="ANM9"/>
+      <c r="ANN9"/>
+      <c r="ANO9"/>
+      <c r="ANP9"/>
+      <c r="ANQ9"/>
+      <c r="ANR9"/>
+      <c r="ANS9"/>
+      <c r="ANT9"/>
+      <c r="ANU9"/>
+      <c r="ANV9"/>
+      <c r="ANW9"/>
+      <c r="ANX9"/>
+      <c r="ANY9"/>
+      <c r="ANZ9"/>
+      <c r="AOA9"/>
+      <c r="AOB9"/>
+      <c r="AOC9"/>
+      <c r="AOD9"/>
+      <c r="AOE9"/>
+      <c r="AOF9"/>
+      <c r="AOG9"/>
+      <c r="AOH9"/>
+      <c r="AOI9"/>
+      <c r="AOJ9"/>
+      <c r="AOK9"/>
+      <c r="AOL9"/>
+      <c r="AOM9"/>
+      <c r="AON9"/>
+      <c r="AOO9"/>
+      <c r="AOP9"/>
+      <c r="AOQ9"/>
+      <c r="AOR9"/>
+      <c r="AOS9"/>
+      <c r="AOT9"/>
+      <c r="AOU9"/>
+      <c r="AOV9"/>
+      <c r="AOW9"/>
+      <c r="AOX9"/>
+      <c r="AOY9"/>
+      <c r="AOZ9"/>
+      <c r="APA9"/>
+      <c r="APB9"/>
+      <c r="APC9"/>
+      <c r="APD9"/>
+      <c r="APE9"/>
+      <c r="APF9"/>
+      <c r="APG9"/>
+      <c r="APH9"/>
+      <c r="API9"/>
+      <c r="APJ9"/>
+      <c r="APK9"/>
+      <c r="APL9"/>
+      <c r="APM9"/>
+      <c r="APN9"/>
+      <c r="APO9"/>
+      <c r="APP9"/>
+      <c r="APQ9"/>
+      <c r="APR9"/>
+      <c r="APS9"/>
+      <c r="APT9"/>
+      <c r="APU9"/>
+      <c r="APV9"/>
+      <c r="APW9"/>
+      <c r="APX9"/>
+      <c r="APY9"/>
+      <c r="APZ9"/>
+      <c r="AQA9"/>
+      <c r="AQB9"/>
+      <c r="AQC9"/>
+      <c r="AQD9"/>
+      <c r="AQE9"/>
+      <c r="AQF9"/>
+      <c r="AQG9"/>
+      <c r="AQH9"/>
+      <c r="AQI9"/>
+      <c r="AQJ9"/>
+      <c r="AQK9"/>
+      <c r="AQL9"/>
+      <c r="AQM9"/>
+      <c r="AQN9"/>
+      <c r="AQO9"/>
+      <c r="AQP9"/>
+      <c r="AQQ9"/>
+      <c r="AQR9"/>
+      <c r="AQS9"/>
+      <c r="AQT9"/>
+      <c r="AQU9"/>
+      <c r="AQV9"/>
+      <c r="AQW9"/>
+      <c r="AQX9"/>
+      <c r="AQY9"/>
+      <c r="AQZ9"/>
+      <c r="ARA9"/>
+      <c r="ARB9"/>
+      <c r="ARC9"/>
+      <c r="ARD9"/>
+      <c r="ARE9"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/testdata.xlsx
+++ b/testdata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sshiwani\workspace\find-information-products-services-tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9D47F77-FF77-46CE-ACAE-C8E70E8090EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF52F74F-C8C7-4680-9CCB-7A8939371F03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="category_phase" sheetId="1" r:id="rId1"/>

--- a/testdata.xlsx
+++ b/testdata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sshiwani\workspace\find-information-products-services-tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF52F74F-C8C7-4680-9CCB-7A8939371F03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7442755-0F79-49B6-9FA8-E67CA91AD833}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="category_phase" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="883" uniqueCount="446">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="889" uniqueCount="450">
   <si>
     <t>Search and filter products and services</t>
   </si>
@@ -260,42 +260,6 @@
     <t>#channel-web</t>
   </si>
   <si>
-    <t>products?group=families</t>
-  </si>
-  <si>
-    <t>ul.moj-filter-tags li a:has-text('families')</t>
-  </si>
-  <si>
-    <t>Remove this filter families</t>
-  </si>
-  <si>
-    <t>#group-families</t>
-  </si>
-  <si>
-    <t>ul.moj-filter-tags li a:has-text('regions')</t>
-  </si>
-  <si>
-    <t>Remove this filter regions</t>
-  </si>
-  <si>
-    <t>#group-regions</t>
-  </si>
-  <si>
-    <t>ul.moj-filter-tags li a:has-text('schools')</t>
-  </si>
-  <si>
-    <t>Remove this filter schools</t>
-  </si>
-  <si>
-    <t>#group-schools</t>
-  </si>
-  <si>
-    <t>products?group=schools</t>
-  </si>
-  <si>
-    <t>products?group=regions</t>
-  </si>
-  <si>
     <t>products?group=skills</t>
   </si>
   <si>
@@ -1386,6 +1350,54 @@
   </si>
   <si>
     <t>#phase-did-not-progress</t>
+  </si>
+  <si>
+    <t>products?group=children-and-families</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' children-and-families')</t>
+  </si>
+  <si>
+    <t>Remove this filter children-and-families</t>
+  </si>
+  <si>
+    <t>#group-children-and-families</t>
+  </si>
+  <si>
+    <t>products?group=regional-digital-services</t>
+  </si>
+  <si>
+    <t>Remove this filter regional-digital-services</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' regional-digital-services')</t>
+  </si>
+  <si>
+    <t>products?group=schools-digital</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' schools-digital')</t>
+  </si>
+  <si>
+    <t>Remove this filter schools-digital</t>
+  </si>
+  <si>
+    <t>#group-schools-digital</t>
+  </si>
+  <si>
+    <t>products?group=sector-facing-services</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' sector-facing-services')</t>
+  </si>
+  <si>
+    <t>Remove this filter sector-facing-services</t>
+  </si>
+  <si>
+    <t>#group-sector-facing-services</t>
+  </si>
+  <si>
+    <t>#group-regional-digital-services</t>
   </si>
 </sst>
 </file>
@@ -1407,7 +1419,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1435,6 +1447,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1514,7 +1532,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1525,6 +1543,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4164,13 +4183,13 @@
     </row>
     <row r="4" spans="1:1149" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>442</v>
+        <v>430</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>443</v>
+        <v>431</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>444</v>
+        <v>432</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
@@ -4179,7 +4198,7 @@
         <v>1</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>445</v>
+        <v>433</v>
       </c>
       <c r="G4"/>
       <c r="H4"/>
@@ -11157,64 +11176,64 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
     </row>
   </sheetData>
@@ -11234,78 +11253,78 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
     </row>
   </sheetData>
@@ -11326,78 +11345,78 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>192</v>
+        <v>180</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
     </row>
   </sheetData>
@@ -11417,99 +11436,99 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>203</v>
+        <v>191</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
     </row>
   </sheetData>
@@ -11529,85 +11548,85 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
     </row>
   </sheetData>
@@ -11627,99 +11646,99 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
     </row>
   </sheetData>
@@ -11762,36 +11781,36 @@
         <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -12017,106 +12036,106 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>226</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
     </row>
   </sheetData>
@@ -12160,36 +12179,36 @@
         <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -12415,80 +12434,80 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
     </row>
   </sheetData>
@@ -12531,36 +12550,36 @@
         <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>270</v>
+        <v>258</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -12786,132 +12805,132 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>273</v>
+        <v>261</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>278</v>
+        <v>266</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>282</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>285</v>
+        <v>273</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
     </row>
     <row r="7" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
     </row>
   </sheetData>
@@ -12955,36 +12974,36 @@
         <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>293</v>
+        <v>281</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -13210,106 +13229,106 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>299</v>
+        <v>287</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>300</v>
+        <v>288</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>301</v>
+        <v>289</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>304</v>
+        <v>292</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>305</v>
+        <v>293</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>307</v>
+        <v>295</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>308</v>
+        <v>296</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>309</v>
+        <v>297</v>
       </c>
     </row>
   </sheetData>
@@ -13375,7 +13394,7 @@
         <v>41</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>42</v>
@@ -13415,10 +13434,10 @@
         <v>48</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
@@ -13570,36 +13589,36 @@
         <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>310</v>
+        <v>298</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>311</v>
+        <v>299</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>312</v>
+        <v>300</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -13825,80 +13844,80 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>313</v>
+        <v>301</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>314</v>
+        <v>302</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>315</v>
+        <v>303</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>316</v>
+        <v>304</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>317</v>
+        <v>305</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>318</v>
+        <v>306</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>319</v>
+        <v>307</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>320</v>
+        <v>308</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>321</v>
+        <v>309</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>322</v>
+        <v>310</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>323</v>
+        <v>311</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>324</v>
+        <v>312</v>
       </c>
     </row>
   </sheetData>
@@ -13941,36 +13960,36 @@
         <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>325</v>
+        <v>313</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>326</v>
+        <v>314</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>327</v>
+        <v>315</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -14196,132 +14215,132 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>329</v>
+        <v>317</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>331</v>
+        <v>319</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>332</v>
+        <v>320</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>334</v>
+        <v>322</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>335</v>
+        <v>323</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
-        <v>336</v>
+        <v>324</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>338</v>
+        <v>326</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>340</v>
+        <v>328</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>342</v>
+        <v>330</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>341</v>
+        <v>329</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>343</v>
+        <v>331</v>
       </c>
     </row>
     <row r="7" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>344</v>
+        <v>332</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>346</v>
+        <v>334</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>347</v>
+        <v>335</v>
       </c>
     </row>
   </sheetData>
@@ -14364,36 +14383,36 @@
         <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>348</v>
+        <v>336</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>349</v>
+        <v>337</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>350</v>
+        <v>338</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -14619,132 +14638,132 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>351</v>
+        <v>339</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>352</v>
+        <v>340</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>353</v>
+        <v>341</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>354</v>
+        <v>342</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>355</v>
+        <v>343</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>356</v>
+        <v>344</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>358</v>
+        <v>346</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
-        <v>359</v>
+        <v>347</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>360</v>
+        <v>348</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>361</v>
+        <v>349</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>362</v>
+        <v>350</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>363</v>
+        <v>351</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>365</v>
+        <v>353</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>364</v>
+        <v>352</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>366</v>
+        <v>354</v>
       </c>
     </row>
     <row r="7" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>367</v>
+        <v>355</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>368</v>
+        <v>356</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>369</v>
+        <v>357</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>370</v>
+        <v>358</v>
       </c>
     </row>
   </sheetData>
@@ -14787,36 +14806,36 @@
         <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>380</v>
+        <v>368</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>381</v>
+        <v>369</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -15042,210 +15061,210 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>383</v>
+        <v>371</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>384</v>
+        <v>372</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>385</v>
+        <v>373</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>386</v>
+        <v>374</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>387</v>
+        <v>375</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>388</v>
+        <v>376</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>389</v>
+        <v>377</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>390</v>
+        <v>378</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
-        <v>391</v>
+        <v>379</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>392</v>
+        <v>380</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>393</v>
+        <v>381</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>394</v>
+        <v>382</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>395</v>
+        <v>383</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>396</v>
+        <v>384</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>397</v>
+        <v>385</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>398</v>
+        <v>386</v>
       </c>
     </row>
     <row r="7" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>399</v>
+        <v>387</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>400</v>
+        <v>388</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>401</v>
+        <v>389</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>402</v>
+        <v>390</v>
       </c>
     </row>
     <row r="8" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>403</v>
+        <v>391</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>404</v>
+        <v>392</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>405</v>
+        <v>393</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>406</v>
+        <v>394</v>
       </c>
     </row>
     <row r="9" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>407</v>
+        <v>395</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>408</v>
+        <v>396</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>409</v>
+        <v>397</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>410</v>
+        <v>398</v>
       </c>
     </row>
     <row r="10" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>411</v>
+        <v>399</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>412</v>
+        <v>400</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>413</v>
+        <v>401</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>414</v>
+        <v>402</v>
       </c>
     </row>
   </sheetData>
@@ -15289,36 +15308,36 @@
         <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>415</v>
+        <v>403</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>416</v>
+        <v>404</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>417</v>
+        <v>405</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -15544,158 +15563,158 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>418</v>
+        <v>406</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>419</v>
+        <v>407</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>420</v>
+        <v>408</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>421</v>
+        <v>409</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>422</v>
+        <v>410</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>423</v>
+        <v>411</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>424</v>
+        <v>412</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>425</v>
+        <v>413</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
-        <v>426</v>
+        <v>414</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>427</v>
+        <v>415</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>428</v>
+        <v>416</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>429</v>
+        <v>417</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>431</v>
+        <v>419</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>432</v>
+        <v>420</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>433</v>
+        <v>421</v>
       </c>
     </row>
     <row r="7" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>434</v>
+        <v>422</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>435</v>
+        <v>423</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>436</v>
+        <v>424</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>437</v>
+        <v>425</v>
       </c>
     </row>
     <row r="8" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A8" s="9" t="s">
-        <v>438</v>
+        <v>426</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>439</v>
+        <v>427</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>440</v>
+        <v>428</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>441</v>
+        <v>429</v>
       </c>
     </row>
   </sheetData>
@@ -15706,7 +15725,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9169CA5-09CB-4ADC-8EEE-AB383FD3DBB7}">
-  <dimension ref="A1:AMO11"/>
+  <dimension ref="A1:AMO12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="40.54296875" bestFit="1" customWidth="1"/>
@@ -15739,82 +15758,82 @@
     </row>
     <row r="2" spans="1:1029" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>372</v>
+        <v>360</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>373</v>
+        <v>361</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>374</v>
+        <v>362</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>371</v>
+        <v>359</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>375</v>
+        <v>363</v>
       </c>
     </row>
     <row r="3" spans="1:1029" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>92</v>
+      <c r="A3" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>80</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>93</v>
+        <v>359</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:1029" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>371</v>
+        <v>359</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
     </row>
     <row r="5" spans="1:1029" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>70</v>
+        <v>434</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>71</v>
+        <v>435</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>72</v>
+        <v>436</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>371</v>
+        <v>359</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>73</v>
+        <v>437</v>
       </c>
       <c r="G5"/>
       <c r="H5"/>
@@ -16841,63 +16860,63 @@
       <c r="AMO5"/>
     </row>
     <row r="6" spans="1:1029" x14ac:dyDescent="0.35">
-      <c r="A6" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>96</v>
+      <c r="A6" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>84</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>97</v>
+        <v>359</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:1029" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>371</v>
+        <v>359</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" spans="1:1029" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>81</v>
+        <v>438</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>74</v>
+        <v>440</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>75</v>
+        <v>439</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>371</v>
+        <v>359</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>76</v>
+        <v>449</v>
       </c>
       <c r="G8"/>
       <c r="H8"/>
@@ -17925,62 +17944,82 @@
     </row>
     <row r="9" spans="1:1029" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>80</v>
+        <v>441</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>77</v>
+        <v>442</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>78</v>
+        <v>443</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>371</v>
+        <v>359</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>79</v>
+        <v>444</v>
       </c>
     </row>
     <row r="10" spans="1:1029" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>82</v>
+        <v>445</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>83</v>
+        <v>446</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>84</v>
+        <v>447</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>371</v>
+        <v>359</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>85</v>
+        <v>448</v>
       </c>
     </row>
     <row r="11" spans="1:1029" x14ac:dyDescent="0.35">
-      <c r="A11" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>119</v>
+      <c r="A11" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>72</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>120</v>
+        <v>359</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1029" x14ac:dyDescent="0.35">
+      <c r="A12" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -18023,22 +18062,22 @@
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="G2"/>
       <c r="H2"/>
@@ -18266,22 +18305,22 @@
     </row>
     <row r="3" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="G3"/>
       <c r="H3"/>
@@ -18509,22 +18548,22 @@
     </row>
     <row r="4" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>377</v>
+        <v>365</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>378</v>
+        <v>366</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>379</v>
+        <v>367</v>
       </c>
       <c r="G4"/>
       <c r="H4"/>
@@ -18752,42 +18791,42 @@
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -18807,71 +18846,71 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -18890,64 +18929,64 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -18966,78 +19005,78 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -19057,71 +19096,71 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
     </row>
   </sheetData>
@@ -19141,92 +19180,92 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
     </row>
   </sheetData>

--- a/testdata.xlsx
+++ b/testdata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sshiwani\workspace\find-information-products-services-tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7442755-0F79-49B6-9FA8-E67CA91AD833}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24635E98-D493-4C20-BE24-573CC1FCB0CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" firstSheet="14" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="category_phase" sheetId="1" r:id="rId1"/>
@@ -689,9 +689,6 @@
     <t>Social worker</t>
   </si>
   <si>
-    <t>Remove this filter Adult learner</t>
-  </si>
-  <si>
     <t>//h3[normalize-space()='User groups']</t>
   </si>
   <si>
@@ -1398,6 +1395,9 @@
   </si>
   <si>
     <t>#group-regional-digital-services</t>
+  </si>
+  <si>
+    <t>Remove this filter Adult learner (18+)</t>
   </si>
 </sst>
 </file>
@@ -4183,13 +4183,13 @@
     </row>
     <row r="4" spans="1:1149" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>430</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>431</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>432</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
@@ -4198,7 +4198,7 @@
         <v>1</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="G4"/>
       <c r="H4"/>
@@ -11781,33 +11781,33 @@
         <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>222</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>213</v>
+        <v>449</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="F2" s="3" t="s">
-        <v>215</v>
-      </c>
       <c r="G2" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>120</v>
@@ -12036,106 +12036,106 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>220</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>221</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>215</v>
-      </c>
       <c r="G3" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>225</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>227</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>228</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="F4" s="3" t="s">
-        <v>215</v>
-      </c>
       <c r="G4" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="H4" s="3" t="s">
         <v>229</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="3" t="s">
         <v>232</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>233</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>215</v>
-      </c>
       <c r="G5" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="H5" s="3" t="s">
         <v>234</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="C6" s="3" t="s">
         <v>237</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>238</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="F6" s="3" t="s">
-        <v>215</v>
-      </c>
       <c r="G6" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="H6" s="3" t="s">
         <v>239</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>240</v>
       </c>
     </row>
   </sheetData>
@@ -12179,33 +12179,33 @@
         <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>222</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="3" t="s">
         <v>242</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>243</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="F2" s="3" t="s">
-        <v>215</v>
-      </c>
       <c r="G2" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>131</v>
@@ -12434,80 +12434,80 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>245</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>246</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>215</v>
-      </c>
       <c r="G3" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>249</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>250</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="F4" s="3" t="s">
-        <v>215</v>
-      </c>
       <c r="G4" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="3" t="s">
         <v>253</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>254</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>215</v>
-      </c>
       <c r="G5" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
   </sheetData>
@@ -12550,33 +12550,33 @@
         <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>222</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="3" t="s">
         <v>257</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>258</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="F2" s="3" t="s">
-        <v>215</v>
-      </c>
       <c r="G2" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>140</v>
@@ -12805,132 +12805,132 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>260</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>261</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>215</v>
-      </c>
       <c r="G3" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>263</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>264</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="F4" s="3" t="s">
-        <v>215</v>
-      </c>
       <c r="G4" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="B5" s="8" t="s">
         <v>267</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="C5" s="8" t="s">
         <v>268</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>269</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>215</v>
-      </c>
       <c r="G5" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="C6" s="3" t="s">
         <v>272</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>273</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="F6" s="3" t="s">
-        <v>215</v>
-      </c>
       <c r="G6" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="7" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>275</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>276</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="F7" s="3" t="s">
-        <v>215</v>
-      </c>
       <c r="G7" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
   </sheetData>
@@ -12974,33 +12974,33 @@
         <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>222</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="3" t="s">
         <v>280</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>281</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="F2" s="3" t="s">
-        <v>215</v>
-      </c>
       <c r="G2" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>145</v>
@@ -13229,106 +13229,106 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>283</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>284</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>215</v>
-      </c>
       <c r="G3" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>287</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>288</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="F4" s="3" t="s">
-        <v>215</v>
-      </c>
       <c r="G4" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
+        <v>289</v>
+      </c>
+      <c r="B5" s="8" t="s">
         <v>290</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="C5" s="8" t="s">
         <v>291</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>292</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>215</v>
-      </c>
       <c r="G5" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="C6" s="3" t="s">
         <v>295</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>296</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="F6" s="3" t="s">
-        <v>215</v>
-      </c>
       <c r="G6" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
   </sheetData>
@@ -13589,33 +13589,33 @@
         <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>222</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="3" t="s">
         <v>299</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>300</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="F2" s="3" t="s">
-        <v>215</v>
-      </c>
       <c r="G2" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>162</v>
@@ -13844,80 +13844,80 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>302</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>303</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>215</v>
-      </c>
       <c r="G3" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>306</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>307</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="F4" s="3" t="s">
-        <v>215</v>
-      </c>
       <c r="G4" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="3" t="s">
         <v>310</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>311</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>215</v>
-      </c>
       <c r="G5" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
   </sheetData>
@@ -13960,33 +13960,33 @@
         <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>222</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="3" t="s">
         <v>314</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>315</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="F2" s="3" t="s">
-        <v>215</v>
-      </c>
       <c r="G2" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>168</v>
@@ -14215,132 +14215,132 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>317</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>318</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>215</v>
-      </c>
       <c r="G3" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>321</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>322</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="F4" s="3" t="s">
-        <v>215</v>
-      </c>
       <c r="G4" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="B5" s="8" t="s">
         <v>324</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="C5" s="8" t="s">
         <v>325</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>326</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>215</v>
-      </c>
       <c r="G5" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>328</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>329</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="F6" s="3" t="s">
-        <v>215</v>
-      </c>
       <c r="G6" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="7" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="C7" s="3" t="s">
         <v>333</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>334</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="F7" s="3" t="s">
-        <v>215</v>
-      </c>
       <c r="G7" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
   </sheetData>
@@ -14383,33 +14383,33 @@
         <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>222</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="3" t="s">
         <v>337</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>338</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="F2" s="3" t="s">
-        <v>215</v>
-      </c>
       <c r="G2" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>176</v>
@@ -14638,132 +14638,132 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>340</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>341</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>215</v>
-      </c>
       <c r="G3" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>343</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>344</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="F4" s="3" t="s">
-        <v>215</v>
-      </c>
       <c r="G4" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
+        <v>346</v>
+      </c>
+      <c r="B5" s="8" t="s">
         <v>347</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="C5" s="8" t="s">
         <v>348</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>349</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>215</v>
-      </c>
       <c r="G5" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>351</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>352</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="F6" s="3" t="s">
-        <v>215</v>
-      </c>
       <c r="G6" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="7" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="C7" s="3" t="s">
         <v>356</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>357</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="F7" s="3" t="s">
-        <v>215</v>
-      </c>
       <c r="G7" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
   </sheetData>
@@ -14806,33 +14806,33 @@
         <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>222</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>368</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="3" t="s">
         <v>369</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>370</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="F2" s="3" t="s">
-        <v>215</v>
-      </c>
       <c r="G2" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>184</v>
@@ -15061,210 +15061,210 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>372</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>373</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>215</v>
-      </c>
       <c r="G3" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>376</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>377</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="F4" s="3" t="s">
-        <v>215</v>
-      </c>
       <c r="G4" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="B5" s="8" t="s">
         <v>379</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="C5" s="8" t="s">
         <v>380</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>381</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>215</v>
-      </c>
       <c r="G5" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>383</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="C6" s="3" t="s">
         <v>384</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>385</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="F6" s="3" t="s">
-        <v>215</v>
-      </c>
       <c r="G6" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="7" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="C7" s="3" t="s">
         <v>388</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>389</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="F7" s="3" t="s">
-        <v>215</v>
-      </c>
       <c r="G7" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="8" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>391</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="C8" s="3" t="s">
         <v>392</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>393</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E8" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>215</v>
-      </c>
       <c r="G8" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="9" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>395</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="C9" s="3" t="s">
         <v>396</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>397</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E9" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>215</v>
-      </c>
       <c r="G9" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="10" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>399</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="C10" s="3" t="s">
         <v>400</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>401</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E10" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="F10" s="3" t="s">
-        <v>215</v>
-      </c>
       <c r="G10" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
   </sheetData>
@@ -15308,33 +15308,33 @@
         <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>222</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>403</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="3" t="s">
         <v>404</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>405</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="F2" s="3" t="s">
-        <v>215</v>
-      </c>
       <c r="G2" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>195</v>
@@ -15563,158 +15563,158 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>406</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>407</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>408</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>215</v>
-      </c>
       <c r="G3" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>410</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>411</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>412</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="F4" s="3" t="s">
-        <v>215</v>
-      </c>
       <c r="G4" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
+        <v>413</v>
+      </c>
+      <c r="B5" s="8" t="s">
         <v>414</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="C5" s="8" t="s">
         <v>415</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>416</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>215</v>
-      </c>
       <c r="G5" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>418</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="C6" s="3" t="s">
         <v>419</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>420</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="F6" s="3" t="s">
-        <v>215</v>
-      </c>
       <c r="G6" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="7" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>422</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="C7" s="3" t="s">
         <v>423</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>424</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="F7" s="3" t="s">
-        <v>215</v>
-      </c>
       <c r="G7" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="8" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A8" s="9" t="s">
+        <v>425</v>
+      </c>
+      <c r="B8" s="9" t="s">
         <v>426</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="C8" s="9" t="s">
         <v>427</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>428</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E8" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>215</v>
-      </c>
       <c r="G8" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
   </sheetData>
@@ -15758,22 +15758,22 @@
     </row>
     <row r="2" spans="1:1029" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="3" t="s">
         <v>361</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>362</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="3" spans="1:1029" x14ac:dyDescent="0.35">
@@ -15790,7 +15790,7 @@
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F3" s="10" t="s">
         <v>81</v>
@@ -15810,7 +15810,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>112</v>
@@ -15818,22 +15818,22 @@
     </row>
     <row r="5" spans="1:1029" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>434</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="3" t="s">
         <v>435</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>436</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="G5"/>
       <c r="H5"/>
@@ -16873,7 +16873,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F6" s="10" t="s">
         <v>85</v>
@@ -16893,7 +16893,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>77</v>
@@ -16901,22 +16901,22 @@
     </row>
     <row r="8" spans="1:1029" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>438</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>440</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>439</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="G8"/>
       <c r="H8"/>
@@ -17944,42 +17944,42 @@
     </row>
     <row r="9" spans="1:1029" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>441</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="C9" s="3" t="s">
         <v>442</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>443</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="10" spans="1:1029" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>445</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="C10" s="3" t="s">
         <v>446</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>447</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="11" spans="1:1029" x14ac:dyDescent="0.35">
@@ -17996,7 +17996,7 @@
         <v>0</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F11" s="10" t="s">
         <v>73</v>
@@ -18016,7 +18016,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>108</v>
@@ -18548,13 +18548,13 @@
     </row>
     <row r="4" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>365</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>366</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
@@ -18563,7 +18563,7 @@
         <v>89</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="G4"/>
       <c r="H4"/>

--- a/testdata.xlsx
+++ b/testdata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sshiwani\workspace\find-information-products-services-tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24635E98-D493-4C20-BE24-573CC1FCB0CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{297BEE1D-61DC-4366-971F-AE90EFF1E76A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" firstSheet="14" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" firstSheet="13" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="category_phase" sheetId="1" r:id="rId1"/>
@@ -28,15 +28,17 @@
     <sheet name="usergroup_ParentorCarer_list" sheetId="13" r:id="rId13"/>
     <sheet name="usergroup_ProfExtUserofDfE_list" sheetId="14" r:id="rId14"/>
     <sheet name="usergroup_SocialCWorkforce_list" sheetId="15" r:id="rId15"/>
-    <sheet name="UGSubcategory_AdultLearner" sheetId="16" r:id="rId16"/>
-    <sheet name="UGSubcategory_CareersAdviser" sheetId="17" r:id="rId17"/>
-    <sheet name="UGSubcategory_ChildOrYoungPers" sheetId="18" r:id="rId18"/>
-    <sheet name="UGSubcategory_DfEWorkforce" sheetId="19" r:id="rId19"/>
-    <sheet name="UGSubcategory_Employer" sheetId="20" r:id="rId20"/>
-    <sheet name="UGSubcategory_LAWorkforce" sheetId="21" r:id="rId21"/>
-    <sheet name="UGSubcategory_NEETOrCareerSeek" sheetId="22" r:id="rId22"/>
-    <sheet name="UGSubcategory_ParentOrCarer" sheetId="23" r:id="rId23"/>
-    <sheet name="UGSubcateg_ProfExtUserofDfEData" sheetId="24" r:id="rId24"/>
+    <sheet name="Sheet2" sheetId="26" r:id="rId16"/>
+    <sheet name="UGSubcategory_AdultLearner" sheetId="16" r:id="rId17"/>
+    <sheet name="UGSubcategory_CareersAdviser" sheetId="17" r:id="rId18"/>
+    <sheet name="UGSubcategory_ChildOrYoungPers" sheetId="18" r:id="rId19"/>
+    <sheet name="UGSubcategory_DfEWorkforce" sheetId="19" r:id="rId20"/>
+    <sheet name="UGSubcategory_Employer" sheetId="20" r:id="rId21"/>
+    <sheet name="UGSubcategory_LAWorkforce" sheetId="21" r:id="rId22"/>
+    <sheet name="UGSubcategory_NEETOrCareerSeek" sheetId="22" r:id="rId23"/>
+    <sheet name="UGSubcategory_ParentOrCarer" sheetId="23" r:id="rId24"/>
+    <sheet name="UGSubcateg_ProfExtUserofDfEData" sheetId="24" r:id="rId25"/>
+    <sheet name="Sheet1" sheetId="25" r:id="rId26"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -48,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="889" uniqueCount="450">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="897" uniqueCount="450">
   <si>
     <t>Search and filter products and services</t>
   </si>
@@ -260,18 +262,6 @@
     <t>#channel-web</t>
   </si>
   <si>
-    <t>products?group=skills</t>
-  </si>
-  <si>
-    <t>ul.moj-filter-tags li a:has-text('skills')</t>
-  </si>
-  <si>
-    <t>Remove this filter skills</t>
-  </si>
-  <si>
-    <t>#group-skills</t>
-  </si>
-  <si>
     <t>products?group=operations-and-infrastructure</t>
   </si>
   <si>
@@ -284,30 +274,6 @@
     <t>#group-operations-and-infrastructure</t>
   </si>
   <si>
-    <t>products?group=cxd</t>
-  </si>
-  <si>
-    <t>ul.moj-filter-tags li a:has-text('cxd')</t>
-  </si>
-  <si>
-    <t>Remove this filter cxd</t>
-  </si>
-  <si>
-    <t>#group-cxd</t>
-  </si>
-  <si>
-    <t>products?group=funding</t>
-  </si>
-  <si>
-    <t>ul.moj-filter-tags li a:has-text('funding')</t>
-  </si>
-  <si>
-    <t>Remove this filter funding</t>
-  </si>
-  <si>
-    <t>#group-funding</t>
-  </si>
-  <si>
     <t>products?type=api</t>
   </si>
   <si>
@@ -1398,6 +1364,42 @@
   </si>
   <si>
     <t>Remove this filter Adult learner (18+)</t>
+  </si>
+  <si>
+    <t>products?group=customer-experience-and-design</t>
+  </si>
+  <si>
+    <t>Remove this filter customer-experience-and-design</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text('customer-experience-and-design')</t>
+  </si>
+  <si>
+    <t>#group-customer-experience-and-design</t>
+  </si>
+  <si>
+    <t>Remove this filter funding-and-financial-oversight</t>
+  </si>
+  <si>
+    <t>products?group=funding-and-financial-oversight</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text('funding-and-financial-oversight')</t>
+  </si>
+  <si>
+    <t>#group-funding-and-financial-oversight</t>
+  </si>
+  <si>
+    <t>products?group=skills-and-growth</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text('skills-and-growth')</t>
+  </si>
+  <si>
+    <t>Remove this filter skills-and-growth</t>
+  </si>
+  <si>
+    <t>#group-skills-and-growth</t>
   </si>
 </sst>
 </file>
@@ -1419,7 +1421,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1447,12 +1449,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1532,7 +1528,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1543,7 +1539,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4183,13 +4178,13 @@
     </row>
     <row r="4" spans="1:1149" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>429</v>
+        <v>417</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>431</v>
+        <v>419</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
@@ -4198,7 +4193,7 @@
         <v>1</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>432</v>
+        <v>420</v>
       </c>
       <c r="G4"/>
       <c r="H4"/>
@@ -11176,64 +11171,64 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
   </sheetData>
@@ -11253,78 +11248,78 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
     </row>
   </sheetData>
@@ -11345,78 +11340,78 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
     </row>
   </sheetData>
@@ -11436,99 +11431,99 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>192</v>
+        <v>180</v>
       </c>
     </row>
   </sheetData>
@@ -11548,85 +11543,85 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
     </row>
   </sheetData>
@@ -11646,99 +11641,99 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>203</v>
+        <v>191</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
     </row>
   </sheetData>
@@ -11747,6 +11742,91 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B03D9F5-4C72-4FCD-8443-70945EFA9D2B}">
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="54.1796875" customWidth="1"/>
+    <col min="2" max="2" width="47.453125" customWidth="1"/>
+    <col min="3" max="3" width="43.90625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B2" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B3" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="3"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" s="3"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" s="3"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB5527F7-85DB-4F8E-B4B3-EC8453E599E1}">
   <dimension ref="A1:HU6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -11781,36 +11861,36 @@
         <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>449</v>
+        <v>437</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -12036,106 +12116,106 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>213</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>238</v>
+        <v>226</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>239</v>
+        <v>227</v>
       </c>
     </row>
   </sheetData>
@@ -12144,7 +12224,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A99CF6C3-F305-48A2-AB80-2C2D7CE6460C}">
   <dimension ref="A1:HU5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -12179,36 +12259,36 @@
         <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -12434,80 +12514,80 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
     </row>
   </sheetData>
@@ -12515,7 +12595,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EFF0597-7FD1-4E6A-AA71-DB9F9FAB97A9}">
   <dimension ref="A1:HU7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -12550,36 +12630,36 @@
         <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -12805,132 +12885,132 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>269</v>
+        <v>257</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>270</v>
+        <v>258</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>273</v>
+        <v>261</v>
       </c>
     </row>
     <row r="7" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>277</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -12939,7 +13019,225 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2DC696B-E1A8-430C-BC9E-87DD1A6FBE9F}">
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="33.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="33.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.90625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F4A57AC-4620-4875-88AE-9F5C739A9042}">
   <dimension ref="A1:HU6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -12974,36 +13272,36 @@
         <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -13229,106 +13527,106 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>285</v>
+        <v>273</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>292</v>
+        <v>280</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>293</v>
+        <v>281</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
   </sheetData>
@@ -13336,225 +13634,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2DC696B-E1A8-430C-BC9E-87DD1A6FBE9F}">
-  <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="33.08984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="43.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="33.36328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.90625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="25.36328125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C1C130F-0899-4810-82F6-950C9CB07234}">
   <dimension ref="A1:HU5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -13589,36 +13669,36 @@
         <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>299</v>
+        <v>287</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -13844,80 +13924,80 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>300</v>
+        <v>288</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>301</v>
+        <v>289</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>304</v>
+        <v>292</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>305</v>
+        <v>293</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>307</v>
+        <v>295</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>308</v>
+        <v>296</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>309</v>
+        <v>297</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>310</v>
+        <v>298</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>311</v>
+        <v>299</v>
       </c>
     </row>
   </sheetData>
@@ -13925,7 +14005,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AB9395B-D522-49AD-B790-5334356249F6}">
   <dimension ref="A1:HU7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -13960,36 +14040,36 @@
         <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>312</v>
+        <v>300</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>313</v>
+        <v>301</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>314</v>
+        <v>302</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -14215,132 +14295,132 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>315</v>
+        <v>303</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>316</v>
+        <v>304</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>317</v>
+        <v>305</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>318</v>
+        <v>306</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>319</v>
+        <v>307</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>320</v>
+        <v>308</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>321</v>
+        <v>309</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>322</v>
+        <v>310</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
-        <v>323</v>
+        <v>311</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>324</v>
+        <v>312</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>325</v>
+        <v>313</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>326</v>
+        <v>314</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>327</v>
+        <v>315</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>329</v>
+        <v>317</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>330</v>
+        <v>318</v>
       </c>
     </row>
     <row r="7" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>331</v>
+        <v>319</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>332</v>
+        <v>320</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>334</v>
+        <v>322</v>
       </c>
     </row>
   </sheetData>
@@ -14348,7 +14428,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEE91763-AD0C-4544-A433-3B50C88AEB79}">
   <dimension ref="A1:HU7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -14383,36 +14463,36 @@
         <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>335</v>
+        <v>323</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>336</v>
+        <v>324</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -14638,132 +14718,132 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>338</v>
+        <v>326</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>340</v>
+        <v>328</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>341</v>
+        <v>329</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>342</v>
+        <v>330</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>344</v>
+        <v>332</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>343</v>
+        <v>331</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
-        <v>346</v>
+        <v>334</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>347</v>
+        <v>335</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>348</v>
+        <v>336</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>349</v>
+        <v>337</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>350</v>
+        <v>338</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>352</v>
+        <v>340</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>351</v>
+        <v>339</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>353</v>
+        <v>341</v>
       </c>
     </row>
     <row r="7" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>354</v>
+        <v>342</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>355</v>
+        <v>343</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>356</v>
+        <v>344</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
     </row>
   </sheetData>
@@ -14771,7 +14851,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20DD36AA-F163-4AAB-BD30-4AE6290CCAE7}">
   <dimension ref="A1:HU10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -14806,36 +14886,36 @@
         <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>367</v>
+        <v>355</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>368</v>
+        <v>356</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>369</v>
+        <v>357</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -15061,210 +15141,210 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>370</v>
+        <v>358</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>371</v>
+        <v>359</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>372</v>
+        <v>360</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>373</v>
+        <v>361</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>374</v>
+        <v>362</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>375</v>
+        <v>363</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>377</v>
+        <v>365</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
-        <v>378</v>
+        <v>366</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>379</v>
+        <v>367</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>380</v>
+        <v>368</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>381</v>
+        <v>369</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>383</v>
+        <v>371</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>384</v>
+        <v>372</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>385</v>
+        <v>373</v>
       </c>
     </row>
     <row r="7" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>386</v>
+        <v>374</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>387</v>
+        <v>375</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>388</v>
+        <v>376</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>389</v>
+        <v>377</v>
       </c>
     </row>
     <row r="8" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>390</v>
+        <v>378</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>391</v>
+        <v>379</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>392</v>
+        <v>380</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>393</v>
+        <v>381</v>
       </c>
     </row>
     <row r="9" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>394</v>
+        <v>382</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>395</v>
+        <v>383</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>396</v>
+        <v>384</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>397</v>
+        <v>385</v>
       </c>
     </row>
     <row r="10" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>398</v>
+        <v>386</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>399</v>
+        <v>387</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>400</v>
+        <v>388</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>401</v>
+        <v>389</v>
       </c>
     </row>
   </sheetData>
@@ -15273,7 +15353,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6EE6111-FDB3-4B43-8820-BBF68AAFCD6D}">
   <dimension ref="A1:HU8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -15308,36 +15388,36 @@
         <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>402</v>
+        <v>390</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>403</v>
+        <v>391</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>404</v>
+        <v>392</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -15563,162 +15643,171 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>405</v>
+        <v>393</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>406</v>
+        <v>394</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>407</v>
+        <v>395</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>408</v>
+        <v>396</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>409</v>
+        <v>397</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>410</v>
+        <v>398</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>411</v>
+        <v>399</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>412</v>
+        <v>400</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
-        <v>413</v>
+        <v>401</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>414</v>
+        <v>402</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>415</v>
+        <v>403</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>416</v>
+        <v>404</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>417</v>
+        <v>405</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>418</v>
+        <v>406</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>419</v>
+        <v>407</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>420</v>
+        <v>408</v>
       </c>
     </row>
     <row r="7" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>421</v>
+        <v>409</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>422</v>
+        <v>410</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>423</v>
+        <v>411</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>424</v>
+        <v>412</v>
       </c>
     </row>
     <row r="8" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A8" s="9" t="s">
-        <v>425</v>
+        <v>413</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>426</v>
+        <v>414</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>427</v>
+        <v>415</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>428</v>
+        <v>416</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6428663-7558-48F1-8CD3-947F03FFD4CC}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -15728,12 +15817,12 @@
   <dimension ref="A1:AMO12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="40.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="52.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.36328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="43.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="55.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="43.90625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="33.36328125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="34.54296875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="32.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="35.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1029" x14ac:dyDescent="0.35">
@@ -15758,82 +15847,82 @@
     </row>
     <row r="2" spans="1:1029" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>359</v>
+        <v>347</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>360</v>
+        <v>348</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>361</v>
+        <v>349</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>358</v>
+        <v>346</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>362</v>
+        <v>350</v>
       </c>
     </row>
     <row r="3" spans="1:1029" x14ac:dyDescent="0.35">
-      <c r="A3" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>80</v>
+      <c r="A3" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>439</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>81</v>
+        <v>346</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="4" spans="1:1029" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>358</v>
+        <v>346</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:1029" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>433</v>
+        <v>421</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>434</v>
+        <v>422</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>435</v>
+        <v>423</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>358</v>
+        <v>346</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>436</v>
+        <v>424</v>
       </c>
       <c r="G5"/>
       <c r="H5"/>
@@ -16860,63 +16949,63 @@
       <c r="AMO5"/>
     </row>
     <row r="6" spans="1:1029" x14ac:dyDescent="0.35">
-      <c r="A6" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>84</v>
+      <c r="A6" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>442</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>85</v>
+        <v>346</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>445</v>
       </c>
     </row>
     <row r="7" spans="1:1029" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>358</v>
+        <v>346</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8" spans="1:1029" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>437</v>
+        <v>425</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>439</v>
+        <v>427</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>438</v>
+        <v>426</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>358</v>
+        <v>346</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>448</v>
+        <v>436</v>
       </c>
       <c r="G8"/>
       <c r="H8"/>
@@ -17944,82 +18033,82 @@
     </row>
     <row r="9" spans="1:1029" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>440</v>
+        <v>428</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>441</v>
+        <v>429</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>442</v>
+        <v>430</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>358</v>
+        <v>346</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>443</v>
+        <v>431</v>
       </c>
     </row>
     <row r="10" spans="1:1029" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>444</v>
+        <v>432</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>445</v>
+        <v>433</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>446</v>
+        <v>434</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>358</v>
+        <v>346</v>
       </c>
       <c r="F10" s="3" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1029" x14ac:dyDescent="0.35">
+      <c r="A11" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>447</v>
       </c>
-    </row>
-    <row r="11" spans="1:1029" x14ac:dyDescent="0.35">
-      <c r="A11" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>72</v>
+      <c r="C11" s="3" t="s">
+        <v>448</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="F11" s="10" t="s">
-        <v>73</v>
+        <v>346</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>449</v>
       </c>
     </row>
     <row r="12" spans="1:1029" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>358</v>
+        <v>346</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -18062,22 +18151,22 @@
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G2"/>
       <c r="H2"/>
@@ -18305,22 +18394,22 @@
     </row>
     <row r="3" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G3"/>
       <c r="H3"/>
@@ -18548,22 +18637,22 @@
     </row>
     <row r="4" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>363</v>
+        <v>351</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>364</v>
+        <v>352</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>365</v>
+        <v>353</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>366</v>
+        <v>354</v>
       </c>
       <c r="G4"/>
       <c r="H4"/>
@@ -18791,42 +18880,42 @@
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -18846,71 +18935,71 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>
@@ -18929,64 +19018,64 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -19005,78 +19094,78 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -19096,71 +19185,71 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>
@@ -19180,92 +19269,92 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
     </row>
   </sheetData>

--- a/testdata.xlsx
+++ b/testdata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sshiwani\workspace\find-information-products-services-tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{297BEE1D-61DC-4366-971F-AE90EFF1E76A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5106E12-4C7B-4221-B5AE-6E364F41D686}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" firstSheet="13" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" firstSheet="14" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="category_phase" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
     <sheet name="usergroup_ParentorCarer_list" sheetId="13" r:id="rId13"/>
     <sheet name="usergroup_ProfExtUserofDfE_list" sheetId="14" r:id="rId14"/>
     <sheet name="usergroup_SocialCWorkforce_list" sheetId="15" r:id="rId15"/>
-    <sheet name="Sheet2" sheetId="26" r:id="rId16"/>
+    <sheet name="usergroup_SocialWorker_list" sheetId="26" r:id="rId16"/>
     <sheet name="UGSubcategory_AdultLearner" sheetId="16" r:id="rId17"/>
     <sheet name="UGSubcategory_CareersAdviser" sheetId="17" r:id="rId18"/>
     <sheet name="UGSubcategory_ChildOrYoungPers" sheetId="18" r:id="rId19"/>
@@ -38,7 +38,7 @@
     <sheet name="UGSubcategory_NEETOrCareerSeek" sheetId="22" r:id="rId23"/>
     <sheet name="UGSubcategory_ParentOrCarer" sheetId="23" r:id="rId24"/>
     <sheet name="UGSubcateg_ProfExtUserofDfEData" sheetId="24" r:id="rId25"/>
-    <sheet name="Sheet1" sheetId="25" r:id="rId26"/>
+    <sheet name="UGSubcategory_SCWorkforce" sheetId="25" r:id="rId26"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="897" uniqueCount="450">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="977" uniqueCount="488">
   <si>
     <t>Search and filter products and services</t>
   </si>
@@ -1400,6 +1400,120 @@
   </si>
   <si>
     <t>#group-skills-and-growth</t>
+  </si>
+  <si>
+    <t>categories/user-group/social-care-workforce/social-worker</t>
+  </si>
+  <si>
+    <t>Browse products in Social worker</t>
+  </si>
+  <si>
+    <t>Chief Social Worker for Children and Families</t>
+  </si>
+  <si>
+    <t>Child Protection Lead Practitioner</t>
+  </si>
+  <si>
+    <t>Practice leader (social worker)</t>
+  </si>
+  <si>
+    <t>Practice supervisor (social worker)</t>
+  </si>
+  <si>
+    <t>Principal Child and Family Social Worker</t>
+  </si>
+  <si>
+    <t>products?userGroup=social-care-workforce</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text('Social care workforce')</t>
+  </si>
+  <si>
+    <t>Remove this filter Social care workforce</t>
+  </si>
+  <si>
+    <t>products?userGroup=childrens-care-home-workforce</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(" Children's care home workforce  (Social care workforce)")</t>
+  </si>
+  <si>
+    <t>Remove this filter Children's care home workforce  (Social care workforce)</t>
+  </si>
+  <si>
+    <t>Children's care home workforce  (Social care workforce)</t>
+  </si>
+  <si>
+    <t>products?userGroup=childrens-centre-staff-member</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remove this filter Children's centre staff member </t>
+  </si>
+  <si>
+    <t>Children's centre staff member  (Social care workforce)</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(" Children's centre staff member ")</t>
+  </si>
+  <si>
+    <t>products?userGroup=early-intervention-practitioner</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text('Early intervention practitioner  (Social care workforce)')</t>
+  </si>
+  <si>
+    <t>Remove this filter Early intervention practitioner  (Social care workforce)</t>
+  </si>
+  <si>
+    <t>Early intervention practitioner  (Social care workforce)</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Early intervention support worker  (Social care workforce)')</t>
+  </si>
+  <si>
+    <t>products?userGroup=category-value-3</t>
+  </si>
+  <si>
+    <t>Remove this filter Early intervention support worker  (Social care workforce)</t>
+  </si>
+  <si>
+    <t>Early intervention support worker  (Social care workforce)</t>
+  </si>
+  <si>
+    <t>products?userGroup=family-hub-practitioner</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Family hub practitioner  (Social care workforce)')</t>
+  </si>
+  <si>
+    <t>Remove this filter Family hub practitioner  (Social care workforce)</t>
+  </si>
+  <si>
+    <t>Family hub practitioner  (Social care workforce)</t>
+  </si>
+  <si>
+    <t>products?userGroup=family-support-worker</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Family support worker  (Social care workforce)')</t>
+  </si>
+  <si>
+    <t>Remove this filter Family support worker  (Social care workforce)</t>
+  </si>
+  <si>
+    <t>Family support worker  (Social care workforce)</t>
+  </si>
+  <si>
+    <t>products?userGroup=personal-adviser-social-care-workforce</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Personal adviser (social care workforce)  (Social care workforce)')</t>
+  </si>
+  <si>
+    <t>Remove this filter Personal adviser (social care workforce)  (Social care workforce)</t>
+  </si>
+  <si>
+    <t>Personal adviser (social care workforce)  (Social care workforce)</t>
   </si>
 </sst>
 </file>
@@ -11743,7 +11857,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B03D9F5-4C72-4FCD-8443-70945EFA9D2B}">
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="54.1796875" customWidth="1"/>
@@ -11752,74 +11866,84 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="B1" s="3" t="s">
+      <c r="A1" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B2" s="3" t="s">
-        <v>115</v>
-      </c>
       <c r="C2" s="3" t="s">
-        <v>116</v>
+        <v>451</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B4" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-    </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" s="3"/>
+      <c r="A5" s="3" t="s">
+        <v>200</v>
+      </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" s="3"/>
+      <c r="A6" s="3" t="s">
+        <v>452</v>
+      </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" s="3"/>
+      <c r="A7" s="3" t="s">
+        <v>453</v>
+      </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" s="3"/>
+      <c r="A8" s="3" t="s">
+        <v>454</v>
+      </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" s="3"/>
+      <c r="A9" s="3" t="s">
+        <v>455</v>
+      </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10" s="3"/>
+      <c r="A10" s="3" t="s">
+        <v>456</v>
+      </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11" s="3"/>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A12" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -15805,9 +15929,476 @@
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6428663-7558-48F1-8CD3-947F03FFD4CC}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:HU9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="50.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="52.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.453125" customWidth="1"/>
+    <col min="4" max="4" width="33.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="33.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.08984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="40.81640625" customWidth="1"/>
+    <col min="8" max="8" width="57.08984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="I2"/>
+      <c r="J2"/>
+      <c r="K2"/>
+      <c r="L2"/>
+      <c r="M2"/>
+      <c r="N2"/>
+      <c r="O2"/>
+      <c r="P2"/>
+      <c r="Q2"/>
+      <c r="R2"/>
+      <c r="S2"/>
+      <c r="T2"/>
+      <c r="U2"/>
+      <c r="V2"/>
+      <c r="W2"/>
+      <c r="X2"/>
+      <c r="Y2"/>
+      <c r="Z2"/>
+      <c r="AA2"/>
+      <c r="AB2"/>
+      <c r="AC2"/>
+      <c r="AD2"/>
+      <c r="AE2"/>
+      <c r="AF2"/>
+      <c r="AG2"/>
+      <c r="AH2"/>
+      <c r="AI2"/>
+      <c r="AJ2"/>
+      <c r="AK2"/>
+      <c r="AL2"/>
+      <c r="AM2"/>
+      <c r="AN2"/>
+      <c r="AO2"/>
+      <c r="AP2"/>
+      <c r="AQ2"/>
+      <c r="AR2"/>
+      <c r="AS2"/>
+      <c r="AT2"/>
+      <c r="AU2"/>
+      <c r="AV2"/>
+      <c r="AW2"/>
+      <c r="AX2"/>
+      <c r="AY2"/>
+      <c r="AZ2"/>
+      <c r="BA2"/>
+      <c r="BB2"/>
+      <c r="BC2"/>
+      <c r="BD2"/>
+      <c r="BE2"/>
+      <c r="BF2"/>
+      <c r="BG2"/>
+      <c r="BH2"/>
+      <c r="BI2"/>
+      <c r="BJ2"/>
+      <c r="BK2"/>
+      <c r="BL2"/>
+      <c r="BM2"/>
+      <c r="BN2"/>
+      <c r="BO2"/>
+      <c r="BP2"/>
+      <c r="BQ2"/>
+      <c r="BR2"/>
+      <c r="BS2"/>
+      <c r="BT2"/>
+      <c r="BU2"/>
+      <c r="BV2"/>
+      <c r="BW2"/>
+      <c r="BX2"/>
+      <c r="BY2"/>
+      <c r="BZ2"/>
+      <c r="CA2"/>
+      <c r="CB2"/>
+      <c r="CC2"/>
+      <c r="CD2"/>
+      <c r="CE2"/>
+      <c r="CF2"/>
+      <c r="CG2"/>
+      <c r="CH2"/>
+      <c r="CI2"/>
+      <c r="CJ2"/>
+      <c r="CK2"/>
+      <c r="CL2"/>
+      <c r="CM2"/>
+      <c r="CN2"/>
+      <c r="CO2"/>
+      <c r="CP2"/>
+      <c r="CQ2"/>
+      <c r="CR2"/>
+      <c r="CS2"/>
+      <c r="CT2"/>
+      <c r="CU2"/>
+      <c r="CV2"/>
+      <c r="CW2"/>
+      <c r="CX2"/>
+      <c r="CY2"/>
+      <c r="CZ2"/>
+      <c r="DA2"/>
+      <c r="DB2"/>
+      <c r="DC2"/>
+      <c r="DD2"/>
+      <c r="DE2"/>
+      <c r="DF2"/>
+      <c r="DG2"/>
+      <c r="DH2"/>
+      <c r="DI2"/>
+      <c r="DJ2"/>
+      <c r="DK2"/>
+      <c r="DL2"/>
+      <c r="DM2"/>
+      <c r="DN2"/>
+      <c r="DO2"/>
+      <c r="DP2"/>
+      <c r="DQ2"/>
+      <c r="DR2"/>
+      <c r="DS2"/>
+      <c r="DT2"/>
+      <c r="DU2"/>
+      <c r="DV2"/>
+      <c r="DW2"/>
+      <c r="DX2"/>
+      <c r="DY2"/>
+      <c r="DZ2"/>
+      <c r="EA2"/>
+      <c r="EB2"/>
+      <c r="EC2"/>
+      <c r="ED2"/>
+      <c r="EE2"/>
+      <c r="EF2"/>
+      <c r="EG2"/>
+      <c r="EH2"/>
+      <c r="EI2"/>
+      <c r="EJ2"/>
+      <c r="EK2"/>
+      <c r="EL2"/>
+      <c r="EM2"/>
+      <c r="EN2"/>
+      <c r="EO2"/>
+      <c r="EP2"/>
+      <c r="EQ2"/>
+      <c r="ER2"/>
+      <c r="ES2"/>
+      <c r="ET2"/>
+      <c r="EU2"/>
+      <c r="EV2"/>
+      <c r="EW2"/>
+      <c r="EX2"/>
+      <c r="EY2"/>
+      <c r="EZ2"/>
+      <c r="FA2"/>
+      <c r="FB2"/>
+      <c r="FC2"/>
+      <c r="FD2"/>
+      <c r="FE2"/>
+      <c r="FF2"/>
+      <c r="FG2"/>
+      <c r="FH2"/>
+      <c r="FI2"/>
+      <c r="FJ2"/>
+      <c r="FK2"/>
+      <c r="FL2"/>
+      <c r="FM2"/>
+      <c r="FN2"/>
+      <c r="FO2"/>
+      <c r="FP2"/>
+      <c r="FQ2"/>
+      <c r="FR2"/>
+      <c r="FS2"/>
+      <c r="FT2"/>
+      <c r="FU2"/>
+      <c r="FV2"/>
+      <c r="FW2"/>
+      <c r="FX2"/>
+      <c r="FY2"/>
+      <c r="FZ2"/>
+      <c r="GA2"/>
+      <c r="GB2"/>
+      <c r="GC2"/>
+      <c r="GD2"/>
+      <c r="GE2"/>
+      <c r="GF2"/>
+      <c r="GG2"/>
+      <c r="GH2"/>
+      <c r="GI2"/>
+      <c r="GJ2"/>
+      <c r="GK2"/>
+      <c r="GL2"/>
+      <c r="GM2"/>
+      <c r="GN2"/>
+      <c r="GO2"/>
+      <c r="GP2"/>
+      <c r="GQ2"/>
+      <c r="GR2"/>
+      <c r="GS2"/>
+      <c r="GT2"/>
+      <c r="GU2"/>
+      <c r="GV2"/>
+      <c r="GW2"/>
+      <c r="GX2"/>
+      <c r="GY2"/>
+      <c r="GZ2"/>
+      <c r="HA2"/>
+      <c r="HB2"/>
+      <c r="HC2"/>
+      <c r="HD2"/>
+      <c r="HE2"/>
+      <c r="HF2"/>
+      <c r="HG2"/>
+      <c r="HH2"/>
+      <c r="HI2"/>
+      <c r="HJ2"/>
+      <c r="HK2"/>
+      <c r="HL2"/>
+      <c r="HM2"/>
+      <c r="HN2"/>
+      <c r="HO2"/>
+      <c r="HP2"/>
+      <c r="HQ2"/>
+      <c r="HR2"/>
+      <c r="HS2"/>
+      <c r="HT2"/>
+      <c r="HU2"/>
+    </row>
+    <row r="3" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="4" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="5" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A5" s="8" t="s">
+        <v>468</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>469</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>470</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="6" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="7" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="8" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="9" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>487</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/testdata.xlsx
+++ b/testdata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sshiwani\workspace\find-information-products-services-tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5106E12-4C7B-4221-B5AE-6E364F41D686}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B074F4D3-2814-4AA5-8B40-1FC99FED345C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" firstSheet="14" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" firstSheet="10" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="category_phase" sheetId="1" r:id="rId1"/>
@@ -39,6 +39,7 @@
     <sheet name="UGSubcategory_ParentOrCarer" sheetId="23" r:id="rId24"/>
     <sheet name="UGSubcateg_ProfExtUserofDfEData" sheetId="24" r:id="rId25"/>
     <sheet name="UGSubcategory_SCWorkforce" sheetId="25" r:id="rId26"/>
+    <sheet name="UGSubcategory_SocialWorker" sheetId="27" r:id="rId27"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -50,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="977" uniqueCount="488">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1033" uniqueCount="512">
   <si>
     <t>Search and filter products and services</t>
   </si>
@@ -1514,6 +1515,78 @@
   </si>
   <si>
     <t>Personal adviser (social care workforce)  (Social care workforce)</t>
+  </si>
+  <si>
+    <t>products?userGroup=social-worker</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Social worker  (Social care workforce)')</t>
+  </si>
+  <si>
+    <t>Remove this filter Social worker  (Social care workforce)</t>
+  </si>
+  <si>
+    <t>Social worker  (Social care workforce)</t>
+  </si>
+  <si>
+    <t>products?userGroup=chief-social-worker-for-children-and-families</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Chief Social Worker for Children and Families ')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remove this filter Chief Social Worker for Children and Families </t>
+  </si>
+  <si>
+    <t>Chief Social Worker for Children and Families  (Social worker)</t>
+  </si>
+  <si>
+    <t>products?userGroup=child-protection-lead-practitioner</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Child Protection Lead Practitioner ')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remove this filter Child Protection Lead Practitioner </t>
+  </si>
+  <si>
+    <t>Child Protection Lead Practitioner  (Social worker)</t>
+  </si>
+  <si>
+    <t>products?userGroup=practice-leader-social-worker</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Practice leader (social worker) ')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remove this filter Practice leader (social worker) </t>
+  </si>
+  <si>
+    <t>Practice leader (social worker)  (Social worker)</t>
+  </si>
+  <si>
+    <t>products?userGroup=practice-supervisor-social-worker</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Practice supervisor (social worker) ')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remove this filter Practice supervisor (social worker) </t>
+  </si>
+  <si>
+    <t>Practice supervisor (social worker)  (Social worker)</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Principal Child and Family Social Worker ')</t>
+  </si>
+  <si>
+    <t>products?userGroup=principal-child-and-family-social-worker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remove this filter Principal Child and Family Social Worker </t>
+  </si>
+  <si>
+    <t>Principal Child and Family Social Worker  (Social worker)</t>
   </si>
 </sst>
 </file>
@@ -16403,6 +16476,429 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A4E3580-B709-4E66-9F6E-B7F9948D7FD3}">
+  <dimension ref="A1:HU7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="50.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="52.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.453125" customWidth="1"/>
+    <col min="4" max="4" width="33.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="33.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.08984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="40.81640625" customWidth="1"/>
+    <col min="8" max="8" width="57.08984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="I2"/>
+      <c r="J2"/>
+      <c r="K2"/>
+      <c r="L2"/>
+      <c r="M2"/>
+      <c r="N2"/>
+      <c r="O2"/>
+      <c r="P2"/>
+      <c r="Q2"/>
+      <c r="R2"/>
+      <c r="S2"/>
+      <c r="T2"/>
+      <c r="U2"/>
+      <c r="V2"/>
+      <c r="W2"/>
+      <c r="X2"/>
+      <c r="Y2"/>
+      <c r="Z2"/>
+      <c r="AA2"/>
+      <c r="AB2"/>
+      <c r="AC2"/>
+      <c r="AD2"/>
+      <c r="AE2"/>
+      <c r="AF2"/>
+      <c r="AG2"/>
+      <c r="AH2"/>
+      <c r="AI2"/>
+      <c r="AJ2"/>
+      <c r="AK2"/>
+      <c r="AL2"/>
+      <c r="AM2"/>
+      <c r="AN2"/>
+      <c r="AO2"/>
+      <c r="AP2"/>
+      <c r="AQ2"/>
+      <c r="AR2"/>
+      <c r="AS2"/>
+      <c r="AT2"/>
+      <c r="AU2"/>
+      <c r="AV2"/>
+      <c r="AW2"/>
+      <c r="AX2"/>
+      <c r="AY2"/>
+      <c r="AZ2"/>
+      <c r="BA2"/>
+      <c r="BB2"/>
+      <c r="BC2"/>
+      <c r="BD2"/>
+      <c r="BE2"/>
+      <c r="BF2"/>
+      <c r="BG2"/>
+      <c r="BH2"/>
+      <c r="BI2"/>
+      <c r="BJ2"/>
+      <c r="BK2"/>
+      <c r="BL2"/>
+      <c r="BM2"/>
+      <c r="BN2"/>
+      <c r="BO2"/>
+      <c r="BP2"/>
+      <c r="BQ2"/>
+      <c r="BR2"/>
+      <c r="BS2"/>
+      <c r="BT2"/>
+      <c r="BU2"/>
+      <c r="BV2"/>
+      <c r="BW2"/>
+      <c r="BX2"/>
+      <c r="BY2"/>
+      <c r="BZ2"/>
+      <c r="CA2"/>
+      <c r="CB2"/>
+      <c r="CC2"/>
+      <c r="CD2"/>
+      <c r="CE2"/>
+      <c r="CF2"/>
+      <c r="CG2"/>
+      <c r="CH2"/>
+      <c r="CI2"/>
+      <c r="CJ2"/>
+      <c r="CK2"/>
+      <c r="CL2"/>
+      <c r="CM2"/>
+      <c r="CN2"/>
+      <c r="CO2"/>
+      <c r="CP2"/>
+      <c r="CQ2"/>
+      <c r="CR2"/>
+      <c r="CS2"/>
+      <c r="CT2"/>
+      <c r="CU2"/>
+      <c r="CV2"/>
+      <c r="CW2"/>
+      <c r="CX2"/>
+      <c r="CY2"/>
+      <c r="CZ2"/>
+      <c r="DA2"/>
+      <c r="DB2"/>
+      <c r="DC2"/>
+      <c r="DD2"/>
+      <c r="DE2"/>
+      <c r="DF2"/>
+      <c r="DG2"/>
+      <c r="DH2"/>
+      <c r="DI2"/>
+      <c r="DJ2"/>
+      <c r="DK2"/>
+      <c r="DL2"/>
+      <c r="DM2"/>
+      <c r="DN2"/>
+      <c r="DO2"/>
+      <c r="DP2"/>
+      <c r="DQ2"/>
+      <c r="DR2"/>
+      <c r="DS2"/>
+      <c r="DT2"/>
+      <c r="DU2"/>
+      <c r="DV2"/>
+      <c r="DW2"/>
+      <c r="DX2"/>
+      <c r="DY2"/>
+      <c r="DZ2"/>
+      <c r="EA2"/>
+      <c r="EB2"/>
+      <c r="EC2"/>
+      <c r="ED2"/>
+      <c r="EE2"/>
+      <c r="EF2"/>
+      <c r="EG2"/>
+      <c r="EH2"/>
+      <c r="EI2"/>
+      <c r="EJ2"/>
+      <c r="EK2"/>
+      <c r="EL2"/>
+      <c r="EM2"/>
+      <c r="EN2"/>
+      <c r="EO2"/>
+      <c r="EP2"/>
+      <c r="EQ2"/>
+      <c r="ER2"/>
+      <c r="ES2"/>
+      <c r="ET2"/>
+      <c r="EU2"/>
+      <c r="EV2"/>
+      <c r="EW2"/>
+      <c r="EX2"/>
+      <c r="EY2"/>
+      <c r="EZ2"/>
+      <c r="FA2"/>
+      <c r="FB2"/>
+      <c r="FC2"/>
+      <c r="FD2"/>
+      <c r="FE2"/>
+      <c r="FF2"/>
+      <c r="FG2"/>
+      <c r="FH2"/>
+      <c r="FI2"/>
+      <c r="FJ2"/>
+      <c r="FK2"/>
+      <c r="FL2"/>
+      <c r="FM2"/>
+      <c r="FN2"/>
+      <c r="FO2"/>
+      <c r="FP2"/>
+      <c r="FQ2"/>
+      <c r="FR2"/>
+      <c r="FS2"/>
+      <c r="FT2"/>
+      <c r="FU2"/>
+      <c r="FV2"/>
+      <c r="FW2"/>
+      <c r="FX2"/>
+      <c r="FY2"/>
+      <c r="FZ2"/>
+      <c r="GA2"/>
+      <c r="GB2"/>
+      <c r="GC2"/>
+      <c r="GD2"/>
+      <c r="GE2"/>
+      <c r="GF2"/>
+      <c r="GG2"/>
+      <c r="GH2"/>
+      <c r="GI2"/>
+      <c r="GJ2"/>
+      <c r="GK2"/>
+      <c r="GL2"/>
+      <c r="GM2"/>
+      <c r="GN2"/>
+      <c r="GO2"/>
+      <c r="GP2"/>
+      <c r="GQ2"/>
+      <c r="GR2"/>
+      <c r="GS2"/>
+      <c r="GT2"/>
+      <c r="GU2"/>
+      <c r="GV2"/>
+      <c r="GW2"/>
+      <c r="GX2"/>
+      <c r="GY2"/>
+      <c r="GZ2"/>
+      <c r="HA2"/>
+      <c r="HB2"/>
+      <c r="HC2"/>
+      <c r="HD2"/>
+      <c r="HE2"/>
+      <c r="HF2"/>
+      <c r="HG2"/>
+      <c r="HH2"/>
+      <c r="HI2"/>
+      <c r="HJ2"/>
+      <c r="HK2"/>
+      <c r="HL2"/>
+      <c r="HM2"/>
+      <c r="HN2"/>
+      <c r="HO2"/>
+      <c r="HP2"/>
+      <c r="HQ2"/>
+      <c r="HR2"/>
+      <c r="HS2"/>
+      <c r="HT2"/>
+      <c r="HU2"/>
+    </row>
+    <row r="3" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>493</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="4" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="5" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A5" s="8" t="s">
+        <v>500</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>501</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>502</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="6" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="7" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>511</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9169CA5-09CB-4ADC-8EEE-AB383FD3DBB7}">
   <dimension ref="A1:AMO12"/>

--- a/testdata.xlsx
+++ b/testdata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sshiwani\workspace\find-information-products-services-tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B074F4D3-2814-4AA5-8B40-1FC99FED345C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AA9572B-ED4F-4DF7-BF30-28BE31D05844}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" firstSheet="10" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" firstSheet="28" activeTab="29" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="category_phase" sheetId="1" r:id="rId1"/>
@@ -29,17 +29,20 @@
     <sheet name="usergroup_ProfExtUserofDfE_list" sheetId="14" r:id="rId14"/>
     <sheet name="usergroup_SocialCWorkforce_list" sheetId="15" r:id="rId15"/>
     <sheet name="usergroup_SocialWorker_list" sheetId="26" r:id="rId16"/>
-    <sheet name="UGSubcategory_AdultLearner" sheetId="16" r:id="rId17"/>
-    <sheet name="UGSubcategory_CareersAdviser" sheetId="17" r:id="rId18"/>
-    <sheet name="UGSubcategory_ChildOrYoungPers" sheetId="18" r:id="rId19"/>
-    <sheet name="UGSubcategory_DfEWorkforce" sheetId="19" r:id="rId20"/>
-    <sheet name="UGSubcategory_Employer" sheetId="20" r:id="rId21"/>
-    <sheet name="UGSubcategory_LAWorkforce" sheetId="21" r:id="rId22"/>
-    <sheet name="UGSubcategory_NEETOrCareerSeek" sheetId="22" r:id="rId23"/>
-    <sheet name="UGSubcategory_ParentOrCarer" sheetId="23" r:id="rId24"/>
-    <sheet name="UGSubcateg_ProfExtUserofDfEData" sheetId="24" r:id="rId25"/>
-    <sheet name="UGSubcategory_SCWorkforce" sheetId="25" r:id="rId26"/>
-    <sheet name="UGSubcategory_SocialWorker" sheetId="27" r:id="rId27"/>
+    <sheet name="UG_EPEYAcademyTruWorkforce_list" sheetId="30" r:id="rId17"/>
+    <sheet name="UGSubcategory_AdultLearner" sheetId="16" r:id="rId18"/>
+    <sheet name="UGSubcategory_CareersAdviser" sheetId="17" r:id="rId19"/>
+    <sheet name="UGSubcategory_ChildOrYoungPers" sheetId="18" r:id="rId20"/>
+    <sheet name="UGSubcategory_DfEWorkforce" sheetId="19" r:id="rId21"/>
+    <sheet name="UGSubcategory_Employer" sheetId="20" r:id="rId22"/>
+    <sheet name="UGSubcategory_LAWorkforce" sheetId="21" r:id="rId23"/>
+    <sheet name="UGSubcategory_NEETOrCareerSeek" sheetId="22" r:id="rId24"/>
+    <sheet name="UGSubcategory_ParentOrCarer" sheetId="23" r:id="rId25"/>
+    <sheet name="UGSubcateg_ProfExtUserofDfEData" sheetId="24" r:id="rId26"/>
+    <sheet name="UGSubcategory_SCWorkforce" sheetId="25" r:id="rId27"/>
+    <sheet name="UGSubcategory_SocialWorker" sheetId="27" r:id="rId28"/>
+    <sheet name="UGSubcategory_EPandEYWorkforce" sheetId="29" r:id="rId29"/>
+    <sheet name="EPEYSubcateg_AcademyTWorkforce" sheetId="31" r:id="rId30"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -51,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1033" uniqueCount="512">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1166" uniqueCount="571">
   <si>
     <t>Search and filter products and services</t>
   </si>
@@ -1587,6 +1590,183 @@
   </si>
   <si>
     <t>Principal Child and Family Social Worker  (Social worker)</t>
+  </si>
+  <si>
+    <t>products?userGroup=education-provider-and-early-years-workforce</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Education provider and early years workforce')</t>
+  </si>
+  <si>
+    <t>Remove this filter Education provider and early years workforce</t>
+  </si>
+  <si>
+    <t>categories/user-group/education-provider-and-early-years-workforce/academy-and-trust-workforce</t>
+  </si>
+  <si>
+    <t>Browse products in Academy and trust workforce</t>
+  </si>
+  <si>
+    <t>Academy governor</t>
+  </si>
+  <si>
+    <t>Academy headteacher (primary)</t>
+  </si>
+  <si>
+    <t>Academy headteacher (secondary)</t>
+  </si>
+  <si>
+    <t>Academy higher level teaching assistant</t>
+  </si>
+  <si>
+    <t>Academy school business professional</t>
+  </si>
+  <si>
+    <t>Academy support staff</t>
+  </si>
+  <si>
+    <t>Academy teacher (primary)</t>
+  </si>
+  <si>
+    <t>Academy teacher (secondary)</t>
+  </si>
+  <si>
+    <t>Academy teaching assistant</t>
+  </si>
+  <si>
+    <t>Academy trustee</t>
+  </si>
+  <si>
+    <t>products?userGroup=academy-and-trust-workforce</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Academy and trust workforce  (Education provider and early years workforce)')</t>
+  </si>
+  <si>
+    <t>Remove this filter Academy and trust workforce  (Education provider and early years workforce)</t>
+  </si>
+  <si>
+    <t>Academy and trust workforce  (Education provider and early years workforce)</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Academy governor  (Academy and trust workforce)')</t>
+  </si>
+  <si>
+    <t>products?userGroup=academy-governor</t>
+  </si>
+  <si>
+    <t>Remove this filter Academy governor  (Academy and trust workforce)</t>
+  </si>
+  <si>
+    <t>Academy governor  (Academy and trust workforce)</t>
+  </si>
+  <si>
+    <t>products?userGroup=academy-headteacher-primary</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Academy headteacher (primary)  (Academy and trust workforce)')</t>
+  </si>
+  <si>
+    <t>Remove this filter Academy headteacher (primary)  (Academy and trust workforce)</t>
+  </si>
+  <si>
+    <t>Academy headteacher (primary)  (Academy and trust workforce)</t>
+  </si>
+  <si>
+    <t>products?userGroup=academy-headteacher-secondary</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Academy headteacher (secondary)  (Academy and trust workforce)')</t>
+  </si>
+  <si>
+    <t>Remove this filter Academy headteacher (secondary)  (Academy and trust workforce)</t>
+  </si>
+  <si>
+    <t>Academy headteacher (secondary)  (Academy and trust workforce)</t>
+  </si>
+  <si>
+    <t>products?userGroup=academy-higher-level-teaching-assistant</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Academy higher level teaching assistant ')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remove this filter Academy higher level teaching assistant </t>
+  </si>
+  <si>
+    <t>Academy higher level teaching assistant  (Academy and trust workforce)</t>
+  </si>
+  <si>
+    <t>products?userGroup=academy-school-business-professional</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Academy school business professional  (Academy and trust workforce)')</t>
+  </si>
+  <si>
+    <t>Remove this filter Academy school business professional  (Academy and trust workforce)</t>
+  </si>
+  <si>
+    <t>Academy school business professional  (Academy and trust workforce)</t>
+  </si>
+  <si>
+    <t>products?userGroup=academy-support-staff</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Academy support staff  (Academy and trust workforce)')</t>
+  </si>
+  <si>
+    <t>Remove this filter Academy support staff  (Academy and trust workforce)</t>
+  </si>
+  <si>
+    <t>Academy support staff  (Academy and trust workforce)</t>
+  </si>
+  <si>
+    <t>products?userGroup=academy-teacher-primary</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Academy teacher (primary)  (Academy and trust workforce)')</t>
+  </si>
+  <si>
+    <t>Academy teacher (primary)  (Academy and trust workforce)</t>
+  </si>
+  <si>
+    <t>Remove this filter Academy teacher (primary)  (Academy and trust workforce)</t>
+  </si>
+  <si>
+    <t>products?userGroup=academy-teacher-secondary</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Academy teacher (secondary)  (Academy and trust workforce)')</t>
+  </si>
+  <si>
+    <t>Remove this filter Academy teacher (secondary)  (Academy and trust workforce)</t>
+  </si>
+  <si>
+    <t>Academy teacher (secondary)  (Academy and trust workforce)</t>
+  </si>
+  <si>
+    <t>products?userGroup=academy-teaching-assistant</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Academy teaching assistant ')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remove this filter Academy teaching assistant </t>
+  </si>
+  <si>
+    <t>Academy teaching assistant  (Academy and trust workforce)</t>
+  </si>
+  <si>
+    <t>products?userGroup=academy-trustee</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Academy trustee ')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remove this filter Academy trustee </t>
+  </si>
+  <si>
+    <t>Academy trustee  (Academy and trust workforce)</t>
   </si>
 </sst>
 </file>
@@ -1640,7 +1820,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -1711,11 +1891,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1726,6 +1919,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -12024,6 +12218,136 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E55FD73-18AE-49C9-9000-5AF4367B4AE3}">
+  <dimension ref="A1:C15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="54.1796875" customWidth="1"/>
+    <col min="2" max="2" width="47.453125" customWidth="1"/>
+    <col min="3" max="3" width="43.90625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B3" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B4" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>518</v>
+      </c>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>519</v>
+      </c>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>521</v>
+      </c>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" s="3" t="s">
+        <v>522</v>
+      </c>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" s="3" t="s">
+        <v>523</v>
+      </c>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" s="3" t="s">
+        <v>526</v>
+      </c>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB5527F7-85DB-4F8E-B4B3-EC8453E599E1}">
   <dimension ref="A1:HU6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -12421,7 +12745,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A99CF6C3-F305-48A2-AB80-2C2D7CE6460C}">
   <dimension ref="A1:HU5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -12792,7 +13116,225 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2DC696B-E1A8-430C-BC9E-87DD1A6FBE9F}">
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="33.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="33.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.90625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EFF0597-7FD1-4E6A-AA71-DB9F9FAB97A9}">
   <dimension ref="A1:HU7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -13216,225 +13758,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2DC696B-E1A8-430C-BC9E-87DD1A6FBE9F}">
-  <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="33.08984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="43.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="33.36328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.90625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="25.36328125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F4A57AC-4620-4875-88AE-9F5C739A9042}">
   <dimension ref="A1:HU6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -13831,7 +14155,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C1C130F-0899-4810-82F6-950C9CB07234}">
   <dimension ref="A1:HU5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -14202,7 +14526,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AB9395B-D522-49AD-B790-5334356249F6}">
   <dimension ref="A1:HU7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -14625,7 +14949,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEE91763-AD0C-4544-A433-3B50C88AEB79}">
   <dimension ref="A1:HU7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -15048,7 +15372,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20DD36AA-F163-4AAB-BD30-4AE6290CCAE7}">
   <dimension ref="A1:HU10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -15550,7 +15874,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6EE6111-FDB3-4B43-8820-BBF68AAFCD6D}">
   <dimension ref="A1:HU8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -16000,7 +16324,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6428663-7558-48F1-8CD3-947F03FFD4CC}">
   <dimension ref="A1:HU9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -16476,7 +16800,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A4E3580-B709-4E66-9F6E-B7F9948D7FD3}">
   <dimension ref="A1:HU7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -16893,6 +17217,299 @@
       <c r="H7" s="3" t="s">
         <v>511</v>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95706458-CD50-4C74-87C4-ABAE617927AD}">
+  <dimension ref="A1:HU2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="50.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="52.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.453125" customWidth="1"/>
+    <col min="4" max="4" width="33.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="33.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.08984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="40.81640625" customWidth="1"/>
+    <col min="8" max="8" width="57.08984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="I2"/>
+      <c r="J2"/>
+      <c r="K2"/>
+      <c r="L2"/>
+      <c r="M2"/>
+      <c r="N2"/>
+      <c r="O2"/>
+      <c r="P2"/>
+      <c r="Q2"/>
+      <c r="R2"/>
+      <c r="S2"/>
+      <c r="T2"/>
+      <c r="U2"/>
+      <c r="V2"/>
+      <c r="W2"/>
+      <c r="X2"/>
+      <c r="Y2"/>
+      <c r="Z2"/>
+      <c r="AA2"/>
+      <c r="AB2"/>
+      <c r="AC2"/>
+      <c r="AD2"/>
+      <c r="AE2"/>
+      <c r="AF2"/>
+      <c r="AG2"/>
+      <c r="AH2"/>
+      <c r="AI2"/>
+      <c r="AJ2"/>
+      <c r="AK2"/>
+      <c r="AL2"/>
+      <c r="AM2"/>
+      <c r="AN2"/>
+      <c r="AO2"/>
+      <c r="AP2"/>
+      <c r="AQ2"/>
+      <c r="AR2"/>
+      <c r="AS2"/>
+      <c r="AT2"/>
+      <c r="AU2"/>
+      <c r="AV2"/>
+      <c r="AW2"/>
+      <c r="AX2"/>
+      <c r="AY2"/>
+      <c r="AZ2"/>
+      <c r="BA2"/>
+      <c r="BB2"/>
+      <c r="BC2"/>
+      <c r="BD2"/>
+      <c r="BE2"/>
+      <c r="BF2"/>
+      <c r="BG2"/>
+      <c r="BH2"/>
+      <c r="BI2"/>
+      <c r="BJ2"/>
+      <c r="BK2"/>
+      <c r="BL2"/>
+      <c r="BM2"/>
+      <c r="BN2"/>
+      <c r="BO2"/>
+      <c r="BP2"/>
+      <c r="BQ2"/>
+      <c r="BR2"/>
+      <c r="BS2"/>
+      <c r="BT2"/>
+      <c r="BU2"/>
+      <c r="BV2"/>
+      <c r="BW2"/>
+      <c r="BX2"/>
+      <c r="BY2"/>
+      <c r="BZ2"/>
+      <c r="CA2"/>
+      <c r="CB2"/>
+      <c r="CC2"/>
+      <c r="CD2"/>
+      <c r="CE2"/>
+      <c r="CF2"/>
+      <c r="CG2"/>
+      <c r="CH2"/>
+      <c r="CI2"/>
+      <c r="CJ2"/>
+      <c r="CK2"/>
+      <c r="CL2"/>
+      <c r="CM2"/>
+      <c r="CN2"/>
+      <c r="CO2"/>
+      <c r="CP2"/>
+      <c r="CQ2"/>
+      <c r="CR2"/>
+      <c r="CS2"/>
+      <c r="CT2"/>
+      <c r="CU2"/>
+      <c r="CV2"/>
+      <c r="CW2"/>
+      <c r="CX2"/>
+      <c r="CY2"/>
+      <c r="CZ2"/>
+      <c r="DA2"/>
+      <c r="DB2"/>
+      <c r="DC2"/>
+      <c r="DD2"/>
+      <c r="DE2"/>
+      <c r="DF2"/>
+      <c r="DG2"/>
+      <c r="DH2"/>
+      <c r="DI2"/>
+      <c r="DJ2"/>
+      <c r="DK2"/>
+      <c r="DL2"/>
+      <c r="DM2"/>
+      <c r="DN2"/>
+      <c r="DO2"/>
+      <c r="DP2"/>
+      <c r="DQ2"/>
+      <c r="DR2"/>
+      <c r="DS2"/>
+      <c r="DT2"/>
+      <c r="DU2"/>
+      <c r="DV2"/>
+      <c r="DW2"/>
+      <c r="DX2"/>
+      <c r="DY2"/>
+      <c r="DZ2"/>
+      <c r="EA2"/>
+      <c r="EB2"/>
+      <c r="EC2"/>
+      <c r="ED2"/>
+      <c r="EE2"/>
+      <c r="EF2"/>
+      <c r="EG2"/>
+      <c r="EH2"/>
+      <c r="EI2"/>
+      <c r="EJ2"/>
+      <c r="EK2"/>
+      <c r="EL2"/>
+      <c r="EM2"/>
+      <c r="EN2"/>
+      <c r="EO2"/>
+      <c r="EP2"/>
+      <c r="EQ2"/>
+      <c r="ER2"/>
+      <c r="ES2"/>
+      <c r="ET2"/>
+      <c r="EU2"/>
+      <c r="EV2"/>
+      <c r="EW2"/>
+      <c r="EX2"/>
+      <c r="EY2"/>
+      <c r="EZ2"/>
+      <c r="FA2"/>
+      <c r="FB2"/>
+      <c r="FC2"/>
+      <c r="FD2"/>
+      <c r="FE2"/>
+      <c r="FF2"/>
+      <c r="FG2"/>
+      <c r="FH2"/>
+      <c r="FI2"/>
+      <c r="FJ2"/>
+      <c r="FK2"/>
+      <c r="FL2"/>
+      <c r="FM2"/>
+      <c r="FN2"/>
+      <c r="FO2"/>
+      <c r="FP2"/>
+      <c r="FQ2"/>
+      <c r="FR2"/>
+      <c r="FS2"/>
+      <c r="FT2"/>
+      <c r="FU2"/>
+      <c r="FV2"/>
+      <c r="FW2"/>
+      <c r="FX2"/>
+      <c r="FY2"/>
+      <c r="FZ2"/>
+      <c r="GA2"/>
+      <c r="GB2"/>
+      <c r="GC2"/>
+      <c r="GD2"/>
+      <c r="GE2"/>
+      <c r="GF2"/>
+      <c r="GG2"/>
+      <c r="GH2"/>
+      <c r="GI2"/>
+      <c r="GJ2"/>
+      <c r="GK2"/>
+      <c r="GL2"/>
+      <c r="GM2"/>
+      <c r="GN2"/>
+      <c r="GO2"/>
+      <c r="GP2"/>
+      <c r="GQ2"/>
+      <c r="GR2"/>
+      <c r="GS2"/>
+      <c r="GT2"/>
+      <c r="GU2"/>
+      <c r="GV2"/>
+      <c r="GW2"/>
+      <c r="GX2"/>
+      <c r="GY2"/>
+      <c r="GZ2"/>
+      <c r="HA2"/>
+      <c r="HB2"/>
+      <c r="HC2"/>
+      <c r="HD2"/>
+      <c r="HE2"/>
+      <c r="HF2"/>
+      <c r="HG2"/>
+      <c r="HH2"/>
+      <c r="HI2"/>
+      <c r="HJ2"/>
+      <c r="HK2"/>
+      <c r="HL2"/>
+      <c r="HM2"/>
+      <c r="HN2"/>
+      <c r="HO2"/>
+      <c r="HP2"/>
+      <c r="HQ2"/>
+      <c r="HR2"/>
+      <c r="HS2"/>
+      <c r="HT2"/>
+      <c r="HU2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -19203,6 +19820,560 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AD86191-7CFE-4ED9-9129-FF78170AB51E}">
+  <dimension ref="A1:HU12"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="50.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="52.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.453125" customWidth="1"/>
+    <col min="4" max="4" width="33.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="33.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.08984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="40.81640625" customWidth="1"/>
+    <col min="8" max="8" width="65.54296875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>528</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>530</v>
+      </c>
+      <c r="I2"/>
+      <c r="J2"/>
+      <c r="K2"/>
+      <c r="L2"/>
+      <c r="M2"/>
+      <c r="N2"/>
+      <c r="O2"/>
+      <c r="P2"/>
+      <c r="Q2"/>
+      <c r="R2"/>
+      <c r="S2"/>
+      <c r="T2"/>
+      <c r="U2"/>
+      <c r="V2"/>
+      <c r="W2"/>
+      <c r="X2"/>
+      <c r="Y2"/>
+      <c r="Z2"/>
+      <c r="AA2"/>
+      <c r="AB2"/>
+      <c r="AC2"/>
+      <c r="AD2"/>
+      <c r="AE2"/>
+      <c r="AF2"/>
+      <c r="AG2"/>
+      <c r="AH2"/>
+      <c r="AI2"/>
+      <c r="AJ2"/>
+      <c r="AK2"/>
+      <c r="AL2"/>
+      <c r="AM2"/>
+      <c r="AN2"/>
+      <c r="AO2"/>
+      <c r="AP2"/>
+      <c r="AQ2"/>
+      <c r="AR2"/>
+      <c r="AS2"/>
+      <c r="AT2"/>
+      <c r="AU2"/>
+      <c r="AV2"/>
+      <c r="AW2"/>
+      <c r="AX2"/>
+      <c r="AY2"/>
+      <c r="AZ2"/>
+      <c r="BA2"/>
+      <c r="BB2"/>
+      <c r="BC2"/>
+      <c r="BD2"/>
+      <c r="BE2"/>
+      <c r="BF2"/>
+      <c r="BG2"/>
+      <c r="BH2"/>
+      <c r="BI2"/>
+      <c r="BJ2"/>
+      <c r="BK2"/>
+      <c r="BL2"/>
+      <c r="BM2"/>
+      <c r="BN2"/>
+      <c r="BO2"/>
+      <c r="BP2"/>
+      <c r="BQ2"/>
+      <c r="BR2"/>
+      <c r="BS2"/>
+      <c r="BT2"/>
+      <c r="BU2"/>
+      <c r="BV2"/>
+      <c r="BW2"/>
+      <c r="BX2"/>
+      <c r="BY2"/>
+      <c r="BZ2"/>
+      <c r="CA2"/>
+      <c r="CB2"/>
+      <c r="CC2"/>
+      <c r="CD2"/>
+      <c r="CE2"/>
+      <c r="CF2"/>
+      <c r="CG2"/>
+      <c r="CH2"/>
+      <c r="CI2"/>
+      <c r="CJ2"/>
+      <c r="CK2"/>
+      <c r="CL2"/>
+      <c r="CM2"/>
+      <c r="CN2"/>
+      <c r="CO2"/>
+      <c r="CP2"/>
+      <c r="CQ2"/>
+      <c r="CR2"/>
+      <c r="CS2"/>
+      <c r="CT2"/>
+      <c r="CU2"/>
+      <c r="CV2"/>
+      <c r="CW2"/>
+      <c r="CX2"/>
+      <c r="CY2"/>
+      <c r="CZ2"/>
+      <c r="DA2"/>
+      <c r="DB2"/>
+      <c r="DC2"/>
+      <c r="DD2"/>
+      <c r="DE2"/>
+      <c r="DF2"/>
+      <c r="DG2"/>
+      <c r="DH2"/>
+      <c r="DI2"/>
+      <c r="DJ2"/>
+      <c r="DK2"/>
+      <c r="DL2"/>
+      <c r="DM2"/>
+      <c r="DN2"/>
+      <c r="DO2"/>
+      <c r="DP2"/>
+      <c r="DQ2"/>
+      <c r="DR2"/>
+      <c r="DS2"/>
+      <c r="DT2"/>
+      <c r="DU2"/>
+      <c r="DV2"/>
+      <c r="DW2"/>
+      <c r="DX2"/>
+      <c r="DY2"/>
+      <c r="DZ2"/>
+      <c r="EA2"/>
+      <c r="EB2"/>
+      <c r="EC2"/>
+      <c r="ED2"/>
+      <c r="EE2"/>
+      <c r="EF2"/>
+      <c r="EG2"/>
+      <c r="EH2"/>
+      <c r="EI2"/>
+      <c r="EJ2"/>
+      <c r="EK2"/>
+      <c r="EL2"/>
+      <c r="EM2"/>
+      <c r="EN2"/>
+      <c r="EO2"/>
+      <c r="EP2"/>
+      <c r="EQ2"/>
+      <c r="ER2"/>
+      <c r="ES2"/>
+      <c r="ET2"/>
+      <c r="EU2"/>
+      <c r="EV2"/>
+      <c r="EW2"/>
+      <c r="EX2"/>
+      <c r="EY2"/>
+      <c r="EZ2"/>
+      <c r="FA2"/>
+      <c r="FB2"/>
+      <c r="FC2"/>
+      <c r="FD2"/>
+      <c r="FE2"/>
+      <c r="FF2"/>
+      <c r="FG2"/>
+      <c r="FH2"/>
+      <c r="FI2"/>
+      <c r="FJ2"/>
+      <c r="FK2"/>
+      <c r="FL2"/>
+      <c r="FM2"/>
+      <c r="FN2"/>
+      <c r="FO2"/>
+      <c r="FP2"/>
+      <c r="FQ2"/>
+      <c r="FR2"/>
+      <c r="FS2"/>
+      <c r="FT2"/>
+      <c r="FU2"/>
+      <c r="FV2"/>
+      <c r="FW2"/>
+      <c r="FX2"/>
+      <c r="FY2"/>
+      <c r="FZ2"/>
+      <c r="GA2"/>
+      <c r="GB2"/>
+      <c r="GC2"/>
+      <c r="GD2"/>
+      <c r="GE2"/>
+      <c r="GF2"/>
+      <c r="GG2"/>
+      <c r="GH2"/>
+      <c r="GI2"/>
+      <c r="GJ2"/>
+      <c r="GK2"/>
+      <c r="GL2"/>
+      <c r="GM2"/>
+      <c r="GN2"/>
+      <c r="GO2"/>
+      <c r="GP2"/>
+      <c r="GQ2"/>
+      <c r="GR2"/>
+      <c r="GS2"/>
+      <c r="GT2"/>
+      <c r="GU2"/>
+      <c r="GV2"/>
+      <c r="GW2"/>
+      <c r="GX2"/>
+      <c r="GY2"/>
+      <c r="GZ2"/>
+      <c r="HA2"/>
+      <c r="HB2"/>
+      <c r="HC2"/>
+      <c r="HD2"/>
+      <c r="HE2"/>
+      <c r="HF2"/>
+      <c r="HG2"/>
+      <c r="HH2"/>
+      <c r="HI2"/>
+      <c r="HJ2"/>
+      <c r="HK2"/>
+      <c r="HL2"/>
+      <c r="HM2"/>
+      <c r="HN2"/>
+      <c r="HO2"/>
+      <c r="HP2"/>
+      <c r="HQ2"/>
+      <c r="HR2"/>
+      <c r="HS2"/>
+      <c r="HT2"/>
+      <c r="HU2"/>
+    </row>
+    <row r="3" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>533</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="4" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>537</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="5" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A5" s="8" t="s">
+        <v>539</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>540</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>541</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="6" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>543</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>544</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>545</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="7" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="8" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>552</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>553</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="9" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>558</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="10" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>561</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="11" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A11" s="3" t="s">
+        <v>563</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>564</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>565</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G11" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="12" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A12" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>569</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>570</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{005D001A-3768-4392-8BD8-510250183310}">
   <dimension ref="A1:HU6"/>

--- a/testdata.xlsx
+++ b/testdata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sshiwani\workspace\find-information-products-services-tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AA9572B-ED4F-4DF7-BF30-28BE31D05844}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03279657-AE4E-4469-BDE8-A24A591A0385}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" firstSheet="28" activeTab="29" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" firstSheet="32" activeTab="33" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="category_phase" sheetId="1" r:id="rId1"/>
@@ -30,19 +30,23 @@
     <sheet name="usergroup_SocialCWorkforce_list" sheetId="15" r:id="rId15"/>
     <sheet name="usergroup_SocialWorker_list" sheetId="26" r:id="rId16"/>
     <sheet name="UG_EPEYAcademyTruWorkforce_list" sheetId="30" r:id="rId17"/>
-    <sheet name="UGSubcategory_AdultLearner" sheetId="16" r:id="rId18"/>
-    <sheet name="UGSubcategory_CareersAdviser" sheetId="17" r:id="rId19"/>
-    <sheet name="UGSubcategory_ChildOrYoungPers" sheetId="18" r:id="rId20"/>
-    <sheet name="UGSubcategory_DfEWorkforce" sheetId="19" r:id="rId21"/>
-    <sheet name="UGSubcategory_Employer" sheetId="20" r:id="rId22"/>
-    <sheet name="UGSubcategory_LAWorkforce" sheetId="21" r:id="rId23"/>
-    <sheet name="UGSubcategory_NEETOrCareerSeek" sheetId="22" r:id="rId24"/>
-    <sheet name="UGSubcategory_ParentOrCarer" sheetId="23" r:id="rId25"/>
-    <sheet name="UGSubcateg_ProfExtUserofDfEData" sheetId="24" r:id="rId26"/>
-    <sheet name="UGSubcategory_SCWorkforce" sheetId="25" r:id="rId27"/>
-    <sheet name="UGSubcategory_SocialWorker" sheetId="27" r:id="rId28"/>
-    <sheet name="UGSubcategory_EPandEYWorkforce" sheetId="29" r:id="rId29"/>
-    <sheet name="EPEYSubcateg_AcademyTWorkforce" sheetId="31" r:id="rId30"/>
+    <sheet name="UG_EPEYAltProvSetWorkforce_list" sheetId="32" r:id="rId18"/>
+    <sheet name="UG_EPEYEarlyYearsWorkforce_list" sheetId="35" r:id="rId19"/>
+    <sheet name="UGSubcategory_AdultLearner" sheetId="16" r:id="rId20"/>
+    <sheet name="UGSubcategory_CareersAdviser" sheetId="17" r:id="rId21"/>
+    <sheet name="UGSubcategory_ChildOrYoungPers" sheetId="18" r:id="rId22"/>
+    <sheet name="UGSubcategory_DfEWorkforce" sheetId="19" r:id="rId23"/>
+    <sheet name="UGSubcategory_Employer" sheetId="20" r:id="rId24"/>
+    <sheet name="UGSubcategory_LAWorkforce" sheetId="21" r:id="rId25"/>
+    <sheet name="UGSubcategory_NEETOrCareerSeek" sheetId="22" r:id="rId26"/>
+    <sheet name="UGSubcategory_ParentOrCarer" sheetId="23" r:id="rId27"/>
+    <sheet name="UGSubcateg_ProfExtUserofDfEData" sheetId="24" r:id="rId28"/>
+    <sheet name="UGSubcategory_SCWorkforce" sheetId="25" r:id="rId29"/>
+    <sheet name="UGSubcategory_SocialWorker" sheetId="27" r:id="rId30"/>
+    <sheet name="UGSubcategory_EPandEYWorkforce" sheetId="29" r:id="rId31"/>
+    <sheet name="EPEYSubcateg_AcademyTWorkforce" sheetId="31" r:id="rId32"/>
+    <sheet name="EPEYSubcateg_AltProSetWorkforce" sheetId="33" r:id="rId33"/>
+    <sheet name="EPEYSubcateg_EarlyYearsWorkforc" sheetId="34" r:id="rId34"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -54,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1166" uniqueCount="571">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1255" uniqueCount="602">
   <si>
     <t>Search and filter products and services</t>
   </si>
@@ -1767,6 +1771,99 @@
   </si>
   <si>
     <t>Academy trustee  (Academy and trust workforce)</t>
+  </si>
+  <si>
+    <t>categories/user-group/education-provider-and-early-years-workforce/alternative-provision-setting-workforce</t>
+  </si>
+  <si>
+    <t>Browse products in Alternative provision setting workforce</t>
+  </si>
+  <si>
+    <t>Alternative provision setting mentor</t>
+  </si>
+  <si>
+    <t>Alternative provision setting support assistant</t>
+  </si>
+  <si>
+    <t>Alternative provision setting teacher</t>
+  </si>
+  <si>
+    <t>products?userGroup=alternative-provision-setting-workforce</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Alternative provision setting workforce ')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remove this filter Alternative provision setting workforce </t>
+  </si>
+  <si>
+    <t>Alternative provision setting workforce  (Education provider and early years workforce)</t>
+  </si>
+  <si>
+    <t>products?userGroup=alternative-provision-setting-mentor</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Alternative provision setting mentor ')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remove this filter Alternative provision setting mentor </t>
+  </si>
+  <si>
+    <t>Alternative provision setting mentor  (Alternative provision setting workforce)</t>
+  </si>
+  <si>
+    <t>products?userGroup=alternative-provision-setting-support-assistant</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' alternative-provision-setting-support-assistant')</t>
+  </si>
+  <si>
+    <t>Remove this filter alternative-provision-setting-support-assistant</t>
+  </si>
+  <si>
+    <t>products?userGroup=alternative-provision-setting-teacher</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Alternative provision setting teacher  (Alternative provision setting workforce)')</t>
+  </si>
+  <si>
+    <t>Remove this filter Alternative provision setting teacher  (Alternative provision setting workforce)</t>
+  </si>
+  <si>
+    <t>Alternative provision setting teacher  (Alternative provision setting workforce)</t>
+  </si>
+  <si>
+    <t>categories/user-group/education-provider-and-early-years-workforce/early-years-workforce</t>
+  </si>
+  <si>
+    <t>Browse products in Early years workforce</t>
+  </si>
+  <si>
+    <t>Early years teacher</t>
+  </si>
+  <si>
+    <t>products?userGroup=early-years-workforce</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Early years workforce  (Education provider and early years workforce)')</t>
+  </si>
+  <si>
+    <t>Remove this filter Early years workforce  (Education provider and early years workforce)</t>
+  </si>
+  <si>
+    <t>Early years workforce  (Education provider and early years workforce)</t>
+  </si>
+  <si>
+    <t>products?userGroup=early-years-teacher</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Early years teacher  (Early years workforce)')</t>
+  </si>
+  <si>
+    <t>Remove this filter Early years teacher  (Early years workforce)</t>
+  </si>
+  <si>
+    <t>Early years teacher  (Early years workforce)</t>
   </si>
 </sst>
 </file>
@@ -1788,7 +1885,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1816,6 +1913,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1908,7 +2011,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1920,6 +2023,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -12348,6 +12452,372 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3235E800-0517-4419-BDEC-02DDE8FA7B7F}">
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="54.1796875" customWidth="1"/>
+    <col min="2" max="2" width="47.453125" customWidth="1"/>
+    <col min="3" max="3" width="50.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B3" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B4" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>573</v>
+      </c>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>574</v>
+      </c>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF697B66-4B1C-421E-AABA-D2FBFBB56C35}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="54.1796875" customWidth="1"/>
+    <col min="2" max="2" width="47.453125" customWidth="1"/>
+    <col min="3" max="3" width="50.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>591</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B3" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B4" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>593</v>
+      </c>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2DC696B-E1A8-430C-BC9E-87DD1A6FBE9F}">
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="33.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="33.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.90625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB5527F7-85DB-4F8E-B4B3-EC8453E599E1}">
   <dimension ref="A1:HU6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -12745,7 +13215,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A99CF6C3-F305-48A2-AB80-2C2D7CE6460C}">
   <dimension ref="A1:HU5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -13116,225 +13586,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2DC696B-E1A8-430C-BC9E-87DD1A6FBE9F}">
-  <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="33.08984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="43.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="33.36328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.90625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="25.36328125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EFF0597-7FD1-4E6A-AA71-DB9F9FAB97A9}">
   <dimension ref="A1:HU7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -13758,7 +14010,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F4A57AC-4620-4875-88AE-9F5C739A9042}">
   <dimension ref="A1:HU6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -14155,7 +14407,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C1C130F-0899-4810-82F6-950C9CB07234}">
   <dimension ref="A1:HU5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -14526,7 +14778,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AB9395B-D522-49AD-B790-5334356249F6}">
   <dimension ref="A1:HU7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -14949,7 +15201,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEE91763-AD0C-4544-A433-3B50C88AEB79}">
   <dimension ref="A1:HU7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -15372,7 +15624,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20DD36AA-F163-4AAB-BD30-4AE6290CCAE7}">
   <dimension ref="A1:HU10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -15874,7 +16126,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6EE6111-FDB3-4B43-8820-BBF68AAFCD6D}">
   <dimension ref="A1:HU8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -16324,7 +16576,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6428663-7558-48F1-8CD3-947F03FFD4CC}">
   <dimension ref="A1:HU9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -16796,722 +17048,6 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A4E3580-B709-4E66-9F6E-B7F9948D7FD3}">
-  <dimension ref="A1:HU7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="50.90625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="52.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.453125" customWidth="1"/>
-    <col min="4" max="4" width="33.36328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="33.08984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.08984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="40.81640625" customWidth="1"/>
-    <col min="8" max="8" width="57.08984375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
-        <v>488</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>489</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>490</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>491</v>
-      </c>
-      <c r="I2"/>
-      <c r="J2"/>
-      <c r="K2"/>
-      <c r="L2"/>
-      <c r="M2"/>
-      <c r="N2"/>
-      <c r="O2"/>
-      <c r="P2"/>
-      <c r="Q2"/>
-      <c r="R2"/>
-      <c r="S2"/>
-      <c r="T2"/>
-      <c r="U2"/>
-      <c r="V2"/>
-      <c r="W2"/>
-      <c r="X2"/>
-      <c r="Y2"/>
-      <c r="Z2"/>
-      <c r="AA2"/>
-      <c r="AB2"/>
-      <c r="AC2"/>
-      <c r="AD2"/>
-      <c r="AE2"/>
-      <c r="AF2"/>
-      <c r="AG2"/>
-      <c r="AH2"/>
-      <c r="AI2"/>
-      <c r="AJ2"/>
-      <c r="AK2"/>
-      <c r="AL2"/>
-      <c r="AM2"/>
-      <c r="AN2"/>
-      <c r="AO2"/>
-      <c r="AP2"/>
-      <c r="AQ2"/>
-      <c r="AR2"/>
-      <c r="AS2"/>
-      <c r="AT2"/>
-      <c r="AU2"/>
-      <c r="AV2"/>
-      <c r="AW2"/>
-      <c r="AX2"/>
-      <c r="AY2"/>
-      <c r="AZ2"/>
-      <c r="BA2"/>
-      <c r="BB2"/>
-      <c r="BC2"/>
-      <c r="BD2"/>
-      <c r="BE2"/>
-      <c r="BF2"/>
-      <c r="BG2"/>
-      <c r="BH2"/>
-      <c r="BI2"/>
-      <c r="BJ2"/>
-      <c r="BK2"/>
-      <c r="BL2"/>
-      <c r="BM2"/>
-      <c r="BN2"/>
-      <c r="BO2"/>
-      <c r="BP2"/>
-      <c r="BQ2"/>
-      <c r="BR2"/>
-      <c r="BS2"/>
-      <c r="BT2"/>
-      <c r="BU2"/>
-      <c r="BV2"/>
-      <c r="BW2"/>
-      <c r="BX2"/>
-      <c r="BY2"/>
-      <c r="BZ2"/>
-      <c r="CA2"/>
-      <c r="CB2"/>
-      <c r="CC2"/>
-      <c r="CD2"/>
-      <c r="CE2"/>
-      <c r="CF2"/>
-      <c r="CG2"/>
-      <c r="CH2"/>
-      <c r="CI2"/>
-      <c r="CJ2"/>
-      <c r="CK2"/>
-      <c r="CL2"/>
-      <c r="CM2"/>
-      <c r="CN2"/>
-      <c r="CO2"/>
-      <c r="CP2"/>
-      <c r="CQ2"/>
-      <c r="CR2"/>
-      <c r="CS2"/>
-      <c r="CT2"/>
-      <c r="CU2"/>
-      <c r="CV2"/>
-      <c r="CW2"/>
-      <c r="CX2"/>
-      <c r="CY2"/>
-      <c r="CZ2"/>
-      <c r="DA2"/>
-      <c r="DB2"/>
-      <c r="DC2"/>
-      <c r="DD2"/>
-      <c r="DE2"/>
-      <c r="DF2"/>
-      <c r="DG2"/>
-      <c r="DH2"/>
-      <c r="DI2"/>
-      <c r="DJ2"/>
-      <c r="DK2"/>
-      <c r="DL2"/>
-      <c r="DM2"/>
-      <c r="DN2"/>
-      <c r="DO2"/>
-      <c r="DP2"/>
-      <c r="DQ2"/>
-      <c r="DR2"/>
-      <c r="DS2"/>
-      <c r="DT2"/>
-      <c r="DU2"/>
-      <c r="DV2"/>
-      <c r="DW2"/>
-      <c r="DX2"/>
-      <c r="DY2"/>
-      <c r="DZ2"/>
-      <c r="EA2"/>
-      <c r="EB2"/>
-      <c r="EC2"/>
-      <c r="ED2"/>
-      <c r="EE2"/>
-      <c r="EF2"/>
-      <c r="EG2"/>
-      <c r="EH2"/>
-      <c r="EI2"/>
-      <c r="EJ2"/>
-      <c r="EK2"/>
-      <c r="EL2"/>
-      <c r="EM2"/>
-      <c r="EN2"/>
-      <c r="EO2"/>
-      <c r="EP2"/>
-      <c r="EQ2"/>
-      <c r="ER2"/>
-      <c r="ES2"/>
-      <c r="ET2"/>
-      <c r="EU2"/>
-      <c r="EV2"/>
-      <c r="EW2"/>
-      <c r="EX2"/>
-      <c r="EY2"/>
-      <c r="EZ2"/>
-      <c r="FA2"/>
-      <c r="FB2"/>
-      <c r="FC2"/>
-      <c r="FD2"/>
-      <c r="FE2"/>
-      <c r="FF2"/>
-      <c r="FG2"/>
-      <c r="FH2"/>
-      <c r="FI2"/>
-      <c r="FJ2"/>
-      <c r="FK2"/>
-      <c r="FL2"/>
-      <c r="FM2"/>
-      <c r="FN2"/>
-      <c r="FO2"/>
-      <c r="FP2"/>
-      <c r="FQ2"/>
-      <c r="FR2"/>
-      <c r="FS2"/>
-      <c r="FT2"/>
-      <c r="FU2"/>
-      <c r="FV2"/>
-      <c r="FW2"/>
-      <c r="FX2"/>
-      <c r="FY2"/>
-      <c r="FZ2"/>
-      <c r="GA2"/>
-      <c r="GB2"/>
-      <c r="GC2"/>
-      <c r="GD2"/>
-      <c r="GE2"/>
-      <c r="GF2"/>
-      <c r="GG2"/>
-      <c r="GH2"/>
-      <c r="GI2"/>
-      <c r="GJ2"/>
-      <c r="GK2"/>
-      <c r="GL2"/>
-      <c r="GM2"/>
-      <c r="GN2"/>
-      <c r="GO2"/>
-      <c r="GP2"/>
-      <c r="GQ2"/>
-      <c r="GR2"/>
-      <c r="GS2"/>
-      <c r="GT2"/>
-      <c r="GU2"/>
-      <c r="GV2"/>
-      <c r="GW2"/>
-      <c r="GX2"/>
-      <c r="GY2"/>
-      <c r="GZ2"/>
-      <c r="HA2"/>
-      <c r="HB2"/>
-      <c r="HC2"/>
-      <c r="HD2"/>
-      <c r="HE2"/>
-      <c r="HF2"/>
-      <c r="HG2"/>
-      <c r="HH2"/>
-      <c r="HI2"/>
-      <c r="HJ2"/>
-      <c r="HK2"/>
-      <c r="HL2"/>
-      <c r="HM2"/>
-      <c r="HN2"/>
-      <c r="HO2"/>
-      <c r="HP2"/>
-      <c r="HQ2"/>
-      <c r="HR2"/>
-      <c r="HS2"/>
-      <c r="HT2"/>
-      <c r="HU2"/>
-    </row>
-    <row r="3" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
-        <v>492</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>493</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>494</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="4" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
-        <v>496</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>497</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>498</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="5" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A5" s="8" t="s">
-        <v>500</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>501</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>502</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="6" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A6" s="3" t="s">
-        <v>504</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>505</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>506</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="7" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A7" s="3" t="s">
-        <v>509</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>508</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>510</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>511</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95706458-CD50-4C74-87C4-ABAE617927AD}">
-  <dimension ref="A1:HU2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="50.90625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="52.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.453125" customWidth="1"/>
-    <col min="4" max="4" width="33.36328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="33.08984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.08984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="40.81640625" customWidth="1"/>
-    <col min="8" max="8" width="57.08984375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
-        <v>512</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>513</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>514</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="I2"/>
-      <c r="J2"/>
-      <c r="K2"/>
-      <c r="L2"/>
-      <c r="M2"/>
-      <c r="N2"/>
-      <c r="O2"/>
-      <c r="P2"/>
-      <c r="Q2"/>
-      <c r="R2"/>
-      <c r="S2"/>
-      <c r="T2"/>
-      <c r="U2"/>
-      <c r="V2"/>
-      <c r="W2"/>
-      <c r="X2"/>
-      <c r="Y2"/>
-      <c r="Z2"/>
-      <c r="AA2"/>
-      <c r="AB2"/>
-      <c r="AC2"/>
-      <c r="AD2"/>
-      <c r="AE2"/>
-      <c r="AF2"/>
-      <c r="AG2"/>
-      <c r="AH2"/>
-      <c r="AI2"/>
-      <c r="AJ2"/>
-      <c r="AK2"/>
-      <c r="AL2"/>
-      <c r="AM2"/>
-      <c r="AN2"/>
-      <c r="AO2"/>
-      <c r="AP2"/>
-      <c r="AQ2"/>
-      <c r="AR2"/>
-      <c r="AS2"/>
-      <c r="AT2"/>
-      <c r="AU2"/>
-      <c r="AV2"/>
-      <c r="AW2"/>
-      <c r="AX2"/>
-      <c r="AY2"/>
-      <c r="AZ2"/>
-      <c r="BA2"/>
-      <c r="BB2"/>
-      <c r="BC2"/>
-      <c r="BD2"/>
-      <c r="BE2"/>
-      <c r="BF2"/>
-      <c r="BG2"/>
-      <c r="BH2"/>
-      <c r="BI2"/>
-      <c r="BJ2"/>
-      <c r="BK2"/>
-      <c r="BL2"/>
-      <c r="BM2"/>
-      <c r="BN2"/>
-      <c r="BO2"/>
-      <c r="BP2"/>
-      <c r="BQ2"/>
-      <c r="BR2"/>
-      <c r="BS2"/>
-      <c r="BT2"/>
-      <c r="BU2"/>
-      <c r="BV2"/>
-      <c r="BW2"/>
-      <c r="BX2"/>
-      <c r="BY2"/>
-      <c r="BZ2"/>
-      <c r="CA2"/>
-      <c r="CB2"/>
-      <c r="CC2"/>
-      <c r="CD2"/>
-      <c r="CE2"/>
-      <c r="CF2"/>
-      <c r="CG2"/>
-      <c r="CH2"/>
-      <c r="CI2"/>
-      <c r="CJ2"/>
-      <c r="CK2"/>
-      <c r="CL2"/>
-      <c r="CM2"/>
-      <c r="CN2"/>
-      <c r="CO2"/>
-      <c r="CP2"/>
-      <c r="CQ2"/>
-      <c r="CR2"/>
-      <c r="CS2"/>
-      <c r="CT2"/>
-      <c r="CU2"/>
-      <c r="CV2"/>
-      <c r="CW2"/>
-      <c r="CX2"/>
-      <c r="CY2"/>
-      <c r="CZ2"/>
-      <c r="DA2"/>
-      <c r="DB2"/>
-      <c r="DC2"/>
-      <c r="DD2"/>
-      <c r="DE2"/>
-      <c r="DF2"/>
-      <c r="DG2"/>
-      <c r="DH2"/>
-      <c r="DI2"/>
-      <c r="DJ2"/>
-      <c r="DK2"/>
-      <c r="DL2"/>
-      <c r="DM2"/>
-      <c r="DN2"/>
-      <c r="DO2"/>
-      <c r="DP2"/>
-      <c r="DQ2"/>
-      <c r="DR2"/>
-      <c r="DS2"/>
-      <c r="DT2"/>
-      <c r="DU2"/>
-      <c r="DV2"/>
-      <c r="DW2"/>
-      <c r="DX2"/>
-      <c r="DY2"/>
-      <c r="DZ2"/>
-      <c r="EA2"/>
-      <c r="EB2"/>
-      <c r="EC2"/>
-      <c r="ED2"/>
-      <c r="EE2"/>
-      <c r="EF2"/>
-      <c r="EG2"/>
-      <c r="EH2"/>
-      <c r="EI2"/>
-      <c r="EJ2"/>
-      <c r="EK2"/>
-      <c r="EL2"/>
-      <c r="EM2"/>
-      <c r="EN2"/>
-      <c r="EO2"/>
-      <c r="EP2"/>
-      <c r="EQ2"/>
-      <c r="ER2"/>
-      <c r="ES2"/>
-      <c r="ET2"/>
-      <c r="EU2"/>
-      <c r="EV2"/>
-      <c r="EW2"/>
-      <c r="EX2"/>
-      <c r="EY2"/>
-      <c r="EZ2"/>
-      <c r="FA2"/>
-      <c r="FB2"/>
-      <c r="FC2"/>
-      <c r="FD2"/>
-      <c r="FE2"/>
-      <c r="FF2"/>
-      <c r="FG2"/>
-      <c r="FH2"/>
-      <c r="FI2"/>
-      <c r="FJ2"/>
-      <c r="FK2"/>
-      <c r="FL2"/>
-      <c r="FM2"/>
-      <c r="FN2"/>
-      <c r="FO2"/>
-      <c r="FP2"/>
-      <c r="FQ2"/>
-      <c r="FR2"/>
-      <c r="FS2"/>
-      <c r="FT2"/>
-      <c r="FU2"/>
-      <c r="FV2"/>
-      <c r="FW2"/>
-      <c r="FX2"/>
-      <c r="FY2"/>
-      <c r="FZ2"/>
-      <c r="GA2"/>
-      <c r="GB2"/>
-      <c r="GC2"/>
-      <c r="GD2"/>
-      <c r="GE2"/>
-      <c r="GF2"/>
-      <c r="GG2"/>
-      <c r="GH2"/>
-      <c r="GI2"/>
-      <c r="GJ2"/>
-      <c r="GK2"/>
-      <c r="GL2"/>
-      <c r="GM2"/>
-      <c r="GN2"/>
-      <c r="GO2"/>
-      <c r="GP2"/>
-      <c r="GQ2"/>
-      <c r="GR2"/>
-      <c r="GS2"/>
-      <c r="GT2"/>
-      <c r="GU2"/>
-      <c r="GV2"/>
-      <c r="GW2"/>
-      <c r="GX2"/>
-      <c r="GY2"/>
-      <c r="GZ2"/>
-      <c r="HA2"/>
-      <c r="HB2"/>
-      <c r="HC2"/>
-      <c r="HD2"/>
-      <c r="HE2"/>
-      <c r="HF2"/>
-      <c r="HG2"/>
-      <c r="HH2"/>
-      <c r="HI2"/>
-      <c r="HJ2"/>
-      <c r="HK2"/>
-      <c r="HL2"/>
-      <c r="HM2"/>
-      <c r="HN2"/>
-      <c r="HO2"/>
-      <c r="HP2"/>
-      <c r="HQ2"/>
-      <c r="HR2"/>
-      <c r="HS2"/>
-      <c r="HT2"/>
-      <c r="HU2"/>
-    </row>
-  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -19821,8 +19357,8 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AD86191-7CFE-4ED9-9129-FF78170AB51E}">
-  <dimension ref="A1:HU12"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A4E3580-B709-4E66-9F6E-B7F9948D7FD3}">
+  <dimension ref="A1:HU7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="50.90625" bestFit="1" customWidth="1"/>
@@ -19832,7 +19368,7 @@
     <col min="5" max="5" width="33.08984375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17.08984375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="40.81640625" customWidth="1"/>
-    <col min="8" max="8" width="65.54296875" customWidth="1"/>
+    <col min="8" max="8" width="57.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:229" x14ac:dyDescent="0.35">
@@ -19863,13 +19399,13 @@
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>527</v>
+        <v>488</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>528</v>
+        <v>489</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>529</v>
+        <v>490</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
@@ -19884,7 +19420,7 @@
         <v>211</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>530</v>
+        <v>491</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -20110,6 +19646,722 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>493</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="4" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="5" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A5" s="8" t="s">
+        <v>500</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>501</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>502</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="6" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="7" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>511</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95706458-CD50-4C74-87C4-ABAE617927AD}">
+  <dimension ref="A1:HU2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="50.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="52.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.453125" customWidth="1"/>
+    <col min="4" max="4" width="33.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="33.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.08984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="40.81640625" customWidth="1"/>
+    <col min="8" max="8" width="57.08984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="I2"/>
+      <c r="J2"/>
+      <c r="K2"/>
+      <c r="L2"/>
+      <c r="M2"/>
+      <c r="N2"/>
+      <c r="O2"/>
+      <c r="P2"/>
+      <c r="Q2"/>
+      <c r="R2"/>
+      <c r="S2"/>
+      <c r="T2"/>
+      <c r="U2"/>
+      <c r="V2"/>
+      <c r="W2"/>
+      <c r="X2"/>
+      <c r="Y2"/>
+      <c r="Z2"/>
+      <c r="AA2"/>
+      <c r="AB2"/>
+      <c r="AC2"/>
+      <c r="AD2"/>
+      <c r="AE2"/>
+      <c r="AF2"/>
+      <c r="AG2"/>
+      <c r="AH2"/>
+      <c r="AI2"/>
+      <c r="AJ2"/>
+      <c r="AK2"/>
+      <c r="AL2"/>
+      <c r="AM2"/>
+      <c r="AN2"/>
+      <c r="AO2"/>
+      <c r="AP2"/>
+      <c r="AQ2"/>
+      <c r="AR2"/>
+      <c r="AS2"/>
+      <c r="AT2"/>
+      <c r="AU2"/>
+      <c r="AV2"/>
+      <c r="AW2"/>
+      <c r="AX2"/>
+      <c r="AY2"/>
+      <c r="AZ2"/>
+      <c r="BA2"/>
+      <c r="BB2"/>
+      <c r="BC2"/>
+      <c r="BD2"/>
+      <c r="BE2"/>
+      <c r="BF2"/>
+      <c r="BG2"/>
+      <c r="BH2"/>
+      <c r="BI2"/>
+      <c r="BJ2"/>
+      <c r="BK2"/>
+      <c r="BL2"/>
+      <c r="BM2"/>
+      <c r="BN2"/>
+      <c r="BO2"/>
+      <c r="BP2"/>
+      <c r="BQ2"/>
+      <c r="BR2"/>
+      <c r="BS2"/>
+      <c r="BT2"/>
+      <c r="BU2"/>
+      <c r="BV2"/>
+      <c r="BW2"/>
+      <c r="BX2"/>
+      <c r="BY2"/>
+      <c r="BZ2"/>
+      <c r="CA2"/>
+      <c r="CB2"/>
+      <c r="CC2"/>
+      <c r="CD2"/>
+      <c r="CE2"/>
+      <c r="CF2"/>
+      <c r="CG2"/>
+      <c r="CH2"/>
+      <c r="CI2"/>
+      <c r="CJ2"/>
+      <c r="CK2"/>
+      <c r="CL2"/>
+      <c r="CM2"/>
+      <c r="CN2"/>
+      <c r="CO2"/>
+      <c r="CP2"/>
+      <c r="CQ2"/>
+      <c r="CR2"/>
+      <c r="CS2"/>
+      <c r="CT2"/>
+      <c r="CU2"/>
+      <c r="CV2"/>
+      <c r="CW2"/>
+      <c r="CX2"/>
+      <c r="CY2"/>
+      <c r="CZ2"/>
+      <c r="DA2"/>
+      <c r="DB2"/>
+      <c r="DC2"/>
+      <c r="DD2"/>
+      <c r="DE2"/>
+      <c r="DF2"/>
+      <c r="DG2"/>
+      <c r="DH2"/>
+      <c r="DI2"/>
+      <c r="DJ2"/>
+      <c r="DK2"/>
+      <c r="DL2"/>
+      <c r="DM2"/>
+      <c r="DN2"/>
+      <c r="DO2"/>
+      <c r="DP2"/>
+      <c r="DQ2"/>
+      <c r="DR2"/>
+      <c r="DS2"/>
+      <c r="DT2"/>
+      <c r="DU2"/>
+      <c r="DV2"/>
+      <c r="DW2"/>
+      <c r="DX2"/>
+      <c r="DY2"/>
+      <c r="DZ2"/>
+      <c r="EA2"/>
+      <c r="EB2"/>
+      <c r="EC2"/>
+      <c r="ED2"/>
+      <c r="EE2"/>
+      <c r="EF2"/>
+      <c r="EG2"/>
+      <c r="EH2"/>
+      <c r="EI2"/>
+      <c r="EJ2"/>
+      <c r="EK2"/>
+      <c r="EL2"/>
+      <c r="EM2"/>
+      <c r="EN2"/>
+      <c r="EO2"/>
+      <c r="EP2"/>
+      <c r="EQ2"/>
+      <c r="ER2"/>
+      <c r="ES2"/>
+      <c r="ET2"/>
+      <c r="EU2"/>
+      <c r="EV2"/>
+      <c r="EW2"/>
+      <c r="EX2"/>
+      <c r="EY2"/>
+      <c r="EZ2"/>
+      <c r="FA2"/>
+      <c r="FB2"/>
+      <c r="FC2"/>
+      <c r="FD2"/>
+      <c r="FE2"/>
+      <c r="FF2"/>
+      <c r="FG2"/>
+      <c r="FH2"/>
+      <c r="FI2"/>
+      <c r="FJ2"/>
+      <c r="FK2"/>
+      <c r="FL2"/>
+      <c r="FM2"/>
+      <c r="FN2"/>
+      <c r="FO2"/>
+      <c r="FP2"/>
+      <c r="FQ2"/>
+      <c r="FR2"/>
+      <c r="FS2"/>
+      <c r="FT2"/>
+      <c r="FU2"/>
+      <c r="FV2"/>
+      <c r="FW2"/>
+      <c r="FX2"/>
+      <c r="FY2"/>
+      <c r="FZ2"/>
+      <c r="GA2"/>
+      <c r="GB2"/>
+      <c r="GC2"/>
+      <c r="GD2"/>
+      <c r="GE2"/>
+      <c r="GF2"/>
+      <c r="GG2"/>
+      <c r="GH2"/>
+      <c r="GI2"/>
+      <c r="GJ2"/>
+      <c r="GK2"/>
+      <c r="GL2"/>
+      <c r="GM2"/>
+      <c r="GN2"/>
+      <c r="GO2"/>
+      <c r="GP2"/>
+      <c r="GQ2"/>
+      <c r="GR2"/>
+      <c r="GS2"/>
+      <c r="GT2"/>
+      <c r="GU2"/>
+      <c r="GV2"/>
+      <c r="GW2"/>
+      <c r="GX2"/>
+      <c r="GY2"/>
+      <c r="GZ2"/>
+      <c r="HA2"/>
+      <c r="HB2"/>
+      <c r="HC2"/>
+      <c r="HD2"/>
+      <c r="HE2"/>
+      <c r="HF2"/>
+      <c r="HG2"/>
+      <c r="HH2"/>
+      <c r="HI2"/>
+      <c r="HJ2"/>
+      <c r="HK2"/>
+      <c r="HL2"/>
+      <c r="HM2"/>
+      <c r="HN2"/>
+      <c r="HO2"/>
+      <c r="HP2"/>
+      <c r="HQ2"/>
+      <c r="HR2"/>
+      <c r="HS2"/>
+      <c r="HT2"/>
+      <c r="HU2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AD86191-7CFE-4ED9-9129-FF78170AB51E}">
+  <dimension ref="A1:HU12"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="50.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="52.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.453125" customWidth="1"/>
+    <col min="4" max="4" width="33.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="33.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.08984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="40.81640625" customWidth="1"/>
+    <col min="8" max="8" width="65.54296875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>528</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>530</v>
+      </c>
+      <c r="I2"/>
+      <c r="J2"/>
+      <c r="K2"/>
+      <c r="L2"/>
+      <c r="M2"/>
+      <c r="N2"/>
+      <c r="O2"/>
+      <c r="P2"/>
+      <c r="Q2"/>
+      <c r="R2"/>
+      <c r="S2"/>
+      <c r="T2"/>
+      <c r="U2"/>
+      <c r="V2"/>
+      <c r="W2"/>
+      <c r="X2"/>
+      <c r="Y2"/>
+      <c r="Z2"/>
+      <c r="AA2"/>
+      <c r="AB2"/>
+      <c r="AC2"/>
+      <c r="AD2"/>
+      <c r="AE2"/>
+      <c r="AF2"/>
+      <c r="AG2"/>
+      <c r="AH2"/>
+      <c r="AI2"/>
+      <c r="AJ2"/>
+      <c r="AK2"/>
+      <c r="AL2"/>
+      <c r="AM2"/>
+      <c r="AN2"/>
+      <c r="AO2"/>
+      <c r="AP2"/>
+      <c r="AQ2"/>
+      <c r="AR2"/>
+      <c r="AS2"/>
+      <c r="AT2"/>
+      <c r="AU2"/>
+      <c r="AV2"/>
+      <c r="AW2"/>
+      <c r="AX2"/>
+      <c r="AY2"/>
+      <c r="AZ2"/>
+      <c r="BA2"/>
+      <c r="BB2"/>
+      <c r="BC2"/>
+      <c r="BD2"/>
+      <c r="BE2"/>
+      <c r="BF2"/>
+      <c r="BG2"/>
+      <c r="BH2"/>
+      <c r="BI2"/>
+      <c r="BJ2"/>
+      <c r="BK2"/>
+      <c r="BL2"/>
+      <c r="BM2"/>
+      <c r="BN2"/>
+      <c r="BO2"/>
+      <c r="BP2"/>
+      <c r="BQ2"/>
+      <c r="BR2"/>
+      <c r="BS2"/>
+      <c r="BT2"/>
+      <c r="BU2"/>
+      <c r="BV2"/>
+      <c r="BW2"/>
+      <c r="BX2"/>
+      <c r="BY2"/>
+      <c r="BZ2"/>
+      <c r="CA2"/>
+      <c r="CB2"/>
+      <c r="CC2"/>
+      <c r="CD2"/>
+      <c r="CE2"/>
+      <c r="CF2"/>
+      <c r="CG2"/>
+      <c r="CH2"/>
+      <c r="CI2"/>
+      <c r="CJ2"/>
+      <c r="CK2"/>
+      <c r="CL2"/>
+      <c r="CM2"/>
+      <c r="CN2"/>
+      <c r="CO2"/>
+      <c r="CP2"/>
+      <c r="CQ2"/>
+      <c r="CR2"/>
+      <c r="CS2"/>
+      <c r="CT2"/>
+      <c r="CU2"/>
+      <c r="CV2"/>
+      <c r="CW2"/>
+      <c r="CX2"/>
+      <c r="CY2"/>
+      <c r="CZ2"/>
+      <c r="DA2"/>
+      <c r="DB2"/>
+      <c r="DC2"/>
+      <c r="DD2"/>
+      <c r="DE2"/>
+      <c r="DF2"/>
+      <c r="DG2"/>
+      <c r="DH2"/>
+      <c r="DI2"/>
+      <c r="DJ2"/>
+      <c r="DK2"/>
+      <c r="DL2"/>
+      <c r="DM2"/>
+      <c r="DN2"/>
+      <c r="DO2"/>
+      <c r="DP2"/>
+      <c r="DQ2"/>
+      <c r="DR2"/>
+      <c r="DS2"/>
+      <c r="DT2"/>
+      <c r="DU2"/>
+      <c r="DV2"/>
+      <c r="DW2"/>
+      <c r="DX2"/>
+      <c r="DY2"/>
+      <c r="DZ2"/>
+      <c r="EA2"/>
+      <c r="EB2"/>
+      <c r="EC2"/>
+      <c r="ED2"/>
+      <c r="EE2"/>
+      <c r="EF2"/>
+      <c r="EG2"/>
+      <c r="EH2"/>
+      <c r="EI2"/>
+      <c r="EJ2"/>
+      <c r="EK2"/>
+      <c r="EL2"/>
+      <c r="EM2"/>
+      <c r="EN2"/>
+      <c r="EO2"/>
+      <c r="EP2"/>
+      <c r="EQ2"/>
+      <c r="ER2"/>
+      <c r="ES2"/>
+      <c r="ET2"/>
+      <c r="EU2"/>
+      <c r="EV2"/>
+      <c r="EW2"/>
+      <c r="EX2"/>
+      <c r="EY2"/>
+      <c r="EZ2"/>
+      <c r="FA2"/>
+      <c r="FB2"/>
+      <c r="FC2"/>
+      <c r="FD2"/>
+      <c r="FE2"/>
+      <c r="FF2"/>
+      <c r="FG2"/>
+      <c r="FH2"/>
+      <c r="FI2"/>
+      <c r="FJ2"/>
+      <c r="FK2"/>
+      <c r="FL2"/>
+      <c r="FM2"/>
+      <c r="FN2"/>
+      <c r="FO2"/>
+      <c r="FP2"/>
+      <c r="FQ2"/>
+      <c r="FR2"/>
+      <c r="FS2"/>
+      <c r="FT2"/>
+      <c r="FU2"/>
+      <c r="FV2"/>
+      <c r="FW2"/>
+      <c r="FX2"/>
+      <c r="FY2"/>
+      <c r="FZ2"/>
+      <c r="GA2"/>
+      <c r="GB2"/>
+      <c r="GC2"/>
+      <c r="GD2"/>
+      <c r="GE2"/>
+      <c r="GF2"/>
+      <c r="GG2"/>
+      <c r="GH2"/>
+      <c r="GI2"/>
+      <c r="GJ2"/>
+      <c r="GK2"/>
+      <c r="GL2"/>
+      <c r="GM2"/>
+      <c r="GN2"/>
+      <c r="GO2"/>
+      <c r="GP2"/>
+      <c r="GQ2"/>
+      <c r="GR2"/>
+      <c r="GS2"/>
+      <c r="GT2"/>
+      <c r="GU2"/>
+      <c r="GV2"/>
+      <c r="GW2"/>
+      <c r="GX2"/>
+      <c r="GY2"/>
+      <c r="GZ2"/>
+      <c r="HA2"/>
+      <c r="HB2"/>
+      <c r="HC2"/>
+      <c r="HD2"/>
+      <c r="HE2"/>
+      <c r="HF2"/>
+      <c r="HG2"/>
+      <c r="HH2"/>
+      <c r="HI2"/>
+      <c r="HJ2"/>
+      <c r="HK2"/>
+      <c r="HL2"/>
+      <c r="HM2"/>
+      <c r="HN2"/>
+      <c r="HO2"/>
+      <c r="HP2"/>
+      <c r="HQ2"/>
+      <c r="HR2"/>
+      <c r="HS2"/>
+      <c r="HT2"/>
+      <c r="HU2"/>
+    </row>
+    <row r="3" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
         <v>532</v>
       </c>
       <c r="B3" s="3" t="s">
@@ -20370,6 +20622,694 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24EB34D0-BCF8-4F57-88CC-AC842687528F}">
+  <dimension ref="A1:HU5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="52.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="52.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.453125" customWidth="1"/>
+    <col min="4" max="4" width="33.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="33.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.08984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="40.81640625" customWidth="1"/>
+    <col min="8" max="8" width="65.54296875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>577</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>579</v>
+      </c>
+      <c r="I2"/>
+      <c r="J2"/>
+      <c r="K2"/>
+      <c r="L2"/>
+      <c r="M2"/>
+      <c r="N2"/>
+      <c r="O2"/>
+      <c r="P2"/>
+      <c r="Q2"/>
+      <c r="R2"/>
+      <c r="S2"/>
+      <c r="T2"/>
+      <c r="U2"/>
+      <c r="V2"/>
+      <c r="W2"/>
+      <c r="X2"/>
+      <c r="Y2"/>
+      <c r="Z2"/>
+      <c r="AA2"/>
+      <c r="AB2"/>
+      <c r="AC2"/>
+      <c r="AD2"/>
+      <c r="AE2"/>
+      <c r="AF2"/>
+      <c r="AG2"/>
+      <c r="AH2"/>
+      <c r="AI2"/>
+      <c r="AJ2"/>
+      <c r="AK2"/>
+      <c r="AL2"/>
+      <c r="AM2"/>
+      <c r="AN2"/>
+      <c r="AO2"/>
+      <c r="AP2"/>
+      <c r="AQ2"/>
+      <c r="AR2"/>
+      <c r="AS2"/>
+      <c r="AT2"/>
+      <c r="AU2"/>
+      <c r="AV2"/>
+      <c r="AW2"/>
+      <c r="AX2"/>
+      <c r="AY2"/>
+      <c r="AZ2"/>
+      <c r="BA2"/>
+      <c r="BB2"/>
+      <c r="BC2"/>
+      <c r="BD2"/>
+      <c r="BE2"/>
+      <c r="BF2"/>
+      <c r="BG2"/>
+      <c r="BH2"/>
+      <c r="BI2"/>
+      <c r="BJ2"/>
+      <c r="BK2"/>
+      <c r="BL2"/>
+      <c r="BM2"/>
+      <c r="BN2"/>
+      <c r="BO2"/>
+      <c r="BP2"/>
+      <c r="BQ2"/>
+      <c r="BR2"/>
+      <c r="BS2"/>
+      <c r="BT2"/>
+      <c r="BU2"/>
+      <c r="BV2"/>
+      <c r="BW2"/>
+      <c r="BX2"/>
+      <c r="BY2"/>
+      <c r="BZ2"/>
+      <c r="CA2"/>
+      <c r="CB2"/>
+      <c r="CC2"/>
+      <c r="CD2"/>
+      <c r="CE2"/>
+      <c r="CF2"/>
+      <c r="CG2"/>
+      <c r="CH2"/>
+      <c r="CI2"/>
+      <c r="CJ2"/>
+      <c r="CK2"/>
+      <c r="CL2"/>
+      <c r="CM2"/>
+      <c r="CN2"/>
+      <c r="CO2"/>
+      <c r="CP2"/>
+      <c r="CQ2"/>
+      <c r="CR2"/>
+      <c r="CS2"/>
+      <c r="CT2"/>
+      <c r="CU2"/>
+      <c r="CV2"/>
+      <c r="CW2"/>
+      <c r="CX2"/>
+      <c r="CY2"/>
+      <c r="CZ2"/>
+      <c r="DA2"/>
+      <c r="DB2"/>
+      <c r="DC2"/>
+      <c r="DD2"/>
+      <c r="DE2"/>
+      <c r="DF2"/>
+      <c r="DG2"/>
+      <c r="DH2"/>
+      <c r="DI2"/>
+      <c r="DJ2"/>
+      <c r="DK2"/>
+      <c r="DL2"/>
+      <c r="DM2"/>
+      <c r="DN2"/>
+      <c r="DO2"/>
+      <c r="DP2"/>
+      <c r="DQ2"/>
+      <c r="DR2"/>
+      <c r="DS2"/>
+      <c r="DT2"/>
+      <c r="DU2"/>
+      <c r="DV2"/>
+      <c r="DW2"/>
+      <c r="DX2"/>
+      <c r="DY2"/>
+      <c r="DZ2"/>
+      <c r="EA2"/>
+      <c r="EB2"/>
+      <c r="EC2"/>
+      <c r="ED2"/>
+      <c r="EE2"/>
+      <c r="EF2"/>
+      <c r="EG2"/>
+      <c r="EH2"/>
+      <c r="EI2"/>
+      <c r="EJ2"/>
+      <c r="EK2"/>
+      <c r="EL2"/>
+      <c r="EM2"/>
+      <c r="EN2"/>
+      <c r="EO2"/>
+      <c r="EP2"/>
+      <c r="EQ2"/>
+      <c r="ER2"/>
+      <c r="ES2"/>
+      <c r="ET2"/>
+      <c r="EU2"/>
+      <c r="EV2"/>
+      <c r="EW2"/>
+      <c r="EX2"/>
+      <c r="EY2"/>
+      <c r="EZ2"/>
+      <c r="FA2"/>
+      <c r="FB2"/>
+      <c r="FC2"/>
+      <c r="FD2"/>
+      <c r="FE2"/>
+      <c r="FF2"/>
+      <c r="FG2"/>
+      <c r="FH2"/>
+      <c r="FI2"/>
+      <c r="FJ2"/>
+      <c r="FK2"/>
+      <c r="FL2"/>
+      <c r="FM2"/>
+      <c r="FN2"/>
+      <c r="FO2"/>
+      <c r="FP2"/>
+      <c r="FQ2"/>
+      <c r="FR2"/>
+      <c r="FS2"/>
+      <c r="FT2"/>
+      <c r="FU2"/>
+      <c r="FV2"/>
+      <c r="FW2"/>
+      <c r="FX2"/>
+      <c r="FY2"/>
+      <c r="FZ2"/>
+      <c r="GA2"/>
+      <c r="GB2"/>
+      <c r="GC2"/>
+      <c r="GD2"/>
+      <c r="GE2"/>
+      <c r="GF2"/>
+      <c r="GG2"/>
+      <c r="GH2"/>
+      <c r="GI2"/>
+      <c r="GJ2"/>
+      <c r="GK2"/>
+      <c r="GL2"/>
+      <c r="GM2"/>
+      <c r="GN2"/>
+      <c r="GO2"/>
+      <c r="GP2"/>
+      <c r="GQ2"/>
+      <c r="GR2"/>
+      <c r="GS2"/>
+      <c r="GT2"/>
+      <c r="GU2"/>
+      <c r="GV2"/>
+      <c r="GW2"/>
+      <c r="GX2"/>
+      <c r="GY2"/>
+      <c r="GZ2"/>
+      <c r="HA2"/>
+      <c r="HB2"/>
+      <c r="HC2"/>
+      <c r="HD2"/>
+      <c r="HE2"/>
+      <c r="HF2"/>
+      <c r="HG2"/>
+      <c r="HH2"/>
+      <c r="HI2"/>
+      <c r="HJ2"/>
+      <c r="HK2"/>
+      <c r="HL2"/>
+      <c r="HM2"/>
+      <c r="HN2"/>
+      <c r="HO2"/>
+      <c r="HP2"/>
+      <c r="HQ2"/>
+      <c r="HR2"/>
+      <c r="HS2"/>
+      <c r="HT2"/>
+      <c r="HU2"/>
+    </row>
+    <row r="3" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>580</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>582</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="4" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A4" s="11" t="s">
+        <v>584</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>585</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>586</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="H4" s="11"/>
+    </row>
+    <row r="5" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>587</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>588</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>589</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>590</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7271F742-0542-4B33-AEE2-20AE8A69F475}">
+  <dimension ref="A1:HU3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="52.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="52.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.453125" customWidth="1"/>
+    <col min="4" max="4" width="33.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="33.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.08984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="40.81640625" customWidth="1"/>
+    <col min="8" max="8" width="65.54296875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>594</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>595</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>596</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="I2"/>
+      <c r="J2"/>
+      <c r="K2"/>
+      <c r="L2"/>
+      <c r="M2"/>
+      <c r="N2"/>
+      <c r="O2"/>
+      <c r="P2"/>
+      <c r="Q2"/>
+      <c r="R2"/>
+      <c r="S2"/>
+      <c r="T2"/>
+      <c r="U2"/>
+      <c r="V2"/>
+      <c r="W2"/>
+      <c r="X2"/>
+      <c r="Y2"/>
+      <c r="Z2"/>
+      <c r="AA2"/>
+      <c r="AB2"/>
+      <c r="AC2"/>
+      <c r="AD2"/>
+      <c r="AE2"/>
+      <c r="AF2"/>
+      <c r="AG2"/>
+      <c r="AH2"/>
+      <c r="AI2"/>
+      <c r="AJ2"/>
+      <c r="AK2"/>
+      <c r="AL2"/>
+      <c r="AM2"/>
+      <c r="AN2"/>
+      <c r="AO2"/>
+      <c r="AP2"/>
+      <c r="AQ2"/>
+      <c r="AR2"/>
+      <c r="AS2"/>
+      <c r="AT2"/>
+      <c r="AU2"/>
+      <c r="AV2"/>
+      <c r="AW2"/>
+      <c r="AX2"/>
+      <c r="AY2"/>
+      <c r="AZ2"/>
+      <c r="BA2"/>
+      <c r="BB2"/>
+      <c r="BC2"/>
+      <c r="BD2"/>
+      <c r="BE2"/>
+      <c r="BF2"/>
+      <c r="BG2"/>
+      <c r="BH2"/>
+      <c r="BI2"/>
+      <c r="BJ2"/>
+      <c r="BK2"/>
+      <c r="BL2"/>
+      <c r="BM2"/>
+      <c r="BN2"/>
+      <c r="BO2"/>
+      <c r="BP2"/>
+      <c r="BQ2"/>
+      <c r="BR2"/>
+      <c r="BS2"/>
+      <c r="BT2"/>
+      <c r="BU2"/>
+      <c r="BV2"/>
+      <c r="BW2"/>
+      <c r="BX2"/>
+      <c r="BY2"/>
+      <c r="BZ2"/>
+      <c r="CA2"/>
+      <c r="CB2"/>
+      <c r="CC2"/>
+      <c r="CD2"/>
+      <c r="CE2"/>
+      <c r="CF2"/>
+      <c r="CG2"/>
+      <c r="CH2"/>
+      <c r="CI2"/>
+      <c r="CJ2"/>
+      <c r="CK2"/>
+      <c r="CL2"/>
+      <c r="CM2"/>
+      <c r="CN2"/>
+      <c r="CO2"/>
+      <c r="CP2"/>
+      <c r="CQ2"/>
+      <c r="CR2"/>
+      <c r="CS2"/>
+      <c r="CT2"/>
+      <c r="CU2"/>
+      <c r="CV2"/>
+      <c r="CW2"/>
+      <c r="CX2"/>
+      <c r="CY2"/>
+      <c r="CZ2"/>
+      <c r="DA2"/>
+      <c r="DB2"/>
+      <c r="DC2"/>
+      <c r="DD2"/>
+      <c r="DE2"/>
+      <c r="DF2"/>
+      <c r="DG2"/>
+      <c r="DH2"/>
+      <c r="DI2"/>
+      <c r="DJ2"/>
+      <c r="DK2"/>
+      <c r="DL2"/>
+      <c r="DM2"/>
+      <c r="DN2"/>
+      <c r="DO2"/>
+      <c r="DP2"/>
+      <c r="DQ2"/>
+      <c r="DR2"/>
+      <c r="DS2"/>
+      <c r="DT2"/>
+      <c r="DU2"/>
+      <c r="DV2"/>
+      <c r="DW2"/>
+      <c r="DX2"/>
+      <c r="DY2"/>
+      <c r="DZ2"/>
+      <c r="EA2"/>
+      <c r="EB2"/>
+      <c r="EC2"/>
+      <c r="ED2"/>
+      <c r="EE2"/>
+      <c r="EF2"/>
+      <c r="EG2"/>
+      <c r="EH2"/>
+      <c r="EI2"/>
+      <c r="EJ2"/>
+      <c r="EK2"/>
+      <c r="EL2"/>
+      <c r="EM2"/>
+      <c r="EN2"/>
+      <c r="EO2"/>
+      <c r="EP2"/>
+      <c r="EQ2"/>
+      <c r="ER2"/>
+      <c r="ES2"/>
+      <c r="ET2"/>
+      <c r="EU2"/>
+      <c r="EV2"/>
+      <c r="EW2"/>
+      <c r="EX2"/>
+      <c r="EY2"/>
+      <c r="EZ2"/>
+      <c r="FA2"/>
+      <c r="FB2"/>
+      <c r="FC2"/>
+      <c r="FD2"/>
+      <c r="FE2"/>
+      <c r="FF2"/>
+      <c r="FG2"/>
+      <c r="FH2"/>
+      <c r="FI2"/>
+      <c r="FJ2"/>
+      <c r="FK2"/>
+      <c r="FL2"/>
+      <c r="FM2"/>
+      <c r="FN2"/>
+      <c r="FO2"/>
+      <c r="FP2"/>
+      <c r="FQ2"/>
+      <c r="FR2"/>
+      <c r="FS2"/>
+      <c r="FT2"/>
+      <c r="FU2"/>
+      <c r="FV2"/>
+      <c r="FW2"/>
+      <c r="FX2"/>
+      <c r="FY2"/>
+      <c r="FZ2"/>
+      <c r="GA2"/>
+      <c r="GB2"/>
+      <c r="GC2"/>
+      <c r="GD2"/>
+      <c r="GE2"/>
+      <c r="GF2"/>
+      <c r="GG2"/>
+      <c r="GH2"/>
+      <c r="GI2"/>
+      <c r="GJ2"/>
+      <c r="GK2"/>
+      <c r="GL2"/>
+      <c r="GM2"/>
+      <c r="GN2"/>
+      <c r="GO2"/>
+      <c r="GP2"/>
+      <c r="GQ2"/>
+      <c r="GR2"/>
+      <c r="GS2"/>
+      <c r="GT2"/>
+      <c r="GU2"/>
+      <c r="GV2"/>
+      <c r="GW2"/>
+      <c r="GX2"/>
+      <c r="GY2"/>
+      <c r="GZ2"/>
+      <c r="HA2"/>
+      <c r="HB2"/>
+      <c r="HC2"/>
+      <c r="HD2"/>
+      <c r="HE2"/>
+      <c r="HF2"/>
+      <c r="HG2"/>
+      <c r="HH2"/>
+      <c r="HI2"/>
+      <c r="HJ2"/>
+      <c r="HK2"/>
+      <c r="HL2"/>
+      <c r="HM2"/>
+      <c r="HN2"/>
+      <c r="HO2"/>
+      <c r="HP2"/>
+      <c r="HQ2"/>
+      <c r="HR2"/>
+      <c r="HS2"/>
+      <c r="HT2"/>
+      <c r="HU2"/>
+    </row>
+    <row r="3" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>599</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>600</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>601</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/testdata.xlsx
+++ b/testdata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sshiwani\workspace\find-information-products-services-tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03279657-AE4E-4469-BDE8-A24A591A0385}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DC67814-7EC6-4595-B980-9CA1061BB621}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" firstSheet="32" activeTab="33" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" firstSheet="18" activeTab="19" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="category_phase" sheetId="1" r:id="rId1"/>
@@ -32,21 +32,23 @@
     <sheet name="UG_EPEYAcademyTruWorkforce_list" sheetId="30" r:id="rId17"/>
     <sheet name="UG_EPEYAltProvSetWorkforce_list" sheetId="32" r:id="rId18"/>
     <sheet name="UG_EPEYEarlyYearsWorkforce_list" sheetId="35" r:id="rId19"/>
-    <sheet name="UGSubcategory_AdultLearner" sheetId="16" r:id="rId20"/>
-    <sheet name="UGSubcategory_CareersAdviser" sheetId="17" r:id="rId21"/>
-    <sheet name="UGSubcategory_ChildOrYoungPers" sheetId="18" r:id="rId22"/>
-    <sheet name="UGSubcategory_DfEWorkforce" sheetId="19" r:id="rId23"/>
-    <sheet name="UGSubcategory_Employer" sheetId="20" r:id="rId24"/>
-    <sheet name="UGSubcategory_LAWorkforce" sheetId="21" r:id="rId25"/>
-    <sheet name="UGSubcategory_NEETOrCareerSeek" sheetId="22" r:id="rId26"/>
-    <sheet name="UGSubcategory_ParentOrCarer" sheetId="23" r:id="rId27"/>
-    <sheet name="UGSubcateg_ProfExtUserofDfEData" sheetId="24" r:id="rId28"/>
-    <sheet name="UGSubcategory_SCWorkforce" sheetId="25" r:id="rId29"/>
-    <sheet name="UGSubcategory_SocialWorker" sheetId="27" r:id="rId30"/>
-    <sheet name="UGSubcategory_EPandEYWorkforce" sheetId="29" r:id="rId31"/>
-    <sheet name="EPEYSubcateg_AcademyTWorkforce" sheetId="31" r:id="rId32"/>
-    <sheet name="EPEYSubcateg_AltProSetWorkforce" sheetId="33" r:id="rId33"/>
-    <sheet name="EPEYSubcateg_EarlyYearsWorkforc" sheetId="34" r:id="rId34"/>
+    <sheet name="UG_EPEYFurtherEduWorkforce_list" sheetId="37" r:id="rId20"/>
+    <sheet name="UGSubcategory_AdultLearner" sheetId="16" r:id="rId21"/>
+    <sheet name="UGSubcategory_CareersAdviser" sheetId="17" r:id="rId22"/>
+    <sheet name="UGSubcategory_ChildOrYoungPers" sheetId="18" r:id="rId23"/>
+    <sheet name="UGSubcategory_DfEWorkforce" sheetId="19" r:id="rId24"/>
+    <sheet name="UGSubcategory_Employer" sheetId="20" r:id="rId25"/>
+    <sheet name="UGSubcategory_LAWorkforce" sheetId="21" r:id="rId26"/>
+    <sheet name="UGSubcategory_NEETOrCareerSeek" sheetId="22" r:id="rId27"/>
+    <sheet name="UGSubcategory_ParentOrCarer" sheetId="23" r:id="rId28"/>
+    <sheet name="UGSubcateg_ProfExtUserofDfEData" sheetId="24" r:id="rId29"/>
+    <sheet name="UGSubcategory_SCWorkforce" sheetId="25" r:id="rId30"/>
+    <sheet name="UGSubcategory_SocialWorker" sheetId="27" r:id="rId31"/>
+    <sheet name="UGSubcategory_EPandEYWorkforce" sheetId="29" r:id="rId32"/>
+    <sheet name="EPEYSubcateg_AcademyTWorkforce" sheetId="31" r:id="rId33"/>
+    <sheet name="EPEYSubcateg_AltProSetWorkforce" sheetId="33" r:id="rId34"/>
+    <sheet name="EPEYSubcatg_EarlyYearsWorkforce" sheetId="34" r:id="rId35"/>
+    <sheet name="EPEYSubcatg_FurtherEduWorkforce" sheetId="36" r:id="rId36"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -58,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1255" uniqueCount="602">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1308" uniqueCount="622">
   <si>
     <t>Search and filter products and services</t>
   </si>
@@ -1864,6 +1866,66 @@
   </si>
   <si>
     <t>Early years teacher  (Early years workforce)</t>
+  </si>
+  <si>
+    <t>categories/user-group/education-provider-and-early-years-workforce/further-education-workforce</t>
+  </si>
+  <si>
+    <t>Browse products in Further education workforce</t>
+  </si>
+  <si>
+    <t>College leader</t>
+  </si>
+  <si>
+    <t>College support staff</t>
+  </si>
+  <si>
+    <t>Lecturer (further education)</t>
+  </si>
+  <si>
+    <t>products?userGroup=further-education-workforce</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' further-education-workforce')</t>
+  </si>
+  <si>
+    <t>Remove this filter further-education-workforce</t>
+  </si>
+  <si>
+    <t>products?userGroup=college-leader</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' College leader  (Further education workforce)')</t>
+  </si>
+  <si>
+    <t>Remove this filter College leader  (Further education workforce)</t>
+  </si>
+  <si>
+    <t>College leader  (Further education workforce)</t>
+  </si>
+  <si>
+    <t>products?userGroup=college-support-staff</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' College support staff  (Further education workforce)')</t>
+  </si>
+  <si>
+    <t>Remove this filter College support staff  (Further education workforce)</t>
+  </si>
+  <si>
+    <t>College support staff  (Further education workforce)</t>
+  </si>
+  <si>
+    <t>products?userGroup=lecturer-further-education</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Lecturer (further education) ')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remove this filter Lecturer (further education) </t>
+  </si>
+  <si>
+    <t>Lecturer (further education)  (Further education workforce)</t>
   </si>
 </sst>
 </file>
@@ -12818,6 +12880,87 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85EB819D-F775-4E64-97E5-4F6BB5F27AC7}">
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="54.1796875" customWidth="1"/>
+    <col min="2" max="2" width="47.453125" customWidth="1"/>
+    <col min="3" max="3" width="50.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>602</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B3" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B4" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>604</v>
+      </c>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>606</v>
+      </c>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB5527F7-85DB-4F8E-B4B3-EC8453E599E1}">
   <dimension ref="A1:HU6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -13215,7 +13358,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A99CF6C3-F305-48A2-AB80-2C2D7CE6460C}">
   <dimension ref="A1:HU5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -13586,7 +13729,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EFF0597-7FD1-4E6A-AA71-DB9F9FAB97A9}">
   <dimension ref="A1:HU7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -14010,7 +14153,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F4A57AC-4620-4875-88AE-9F5C739A9042}">
   <dimension ref="A1:HU6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -14407,7 +14550,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C1C130F-0899-4810-82F6-950C9CB07234}">
   <dimension ref="A1:HU5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -14778,7 +14921,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AB9395B-D522-49AD-B790-5334356249F6}">
   <dimension ref="A1:HU7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -15201,7 +15344,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEE91763-AD0C-4544-A433-3B50C88AEB79}">
   <dimension ref="A1:HU7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -15624,7 +15767,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20DD36AA-F163-4AAB-BD30-4AE6290CCAE7}">
   <dimension ref="A1:HU10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -16126,7 +16269,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6EE6111-FDB3-4B43-8820-BBF68AAFCD6D}">
   <dimension ref="A1:HU8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -16568,482 +16711,6 @@
       </c>
       <c r="H8" s="9" t="s">
         <v>416</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6428663-7558-48F1-8CD3-947F03FFD4CC}">
-  <dimension ref="A1:HU9"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="50.90625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="52.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.453125" customWidth="1"/>
-    <col min="4" max="4" width="33.36328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="33.08984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.08984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="40.81640625" customWidth="1"/>
-    <col min="8" max="8" width="57.08984375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
-        <v>457</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>458</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>459</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="I2"/>
-      <c r="J2"/>
-      <c r="K2"/>
-      <c r="L2"/>
-      <c r="M2"/>
-      <c r="N2"/>
-      <c r="O2"/>
-      <c r="P2"/>
-      <c r="Q2"/>
-      <c r="R2"/>
-      <c r="S2"/>
-      <c r="T2"/>
-      <c r="U2"/>
-      <c r="V2"/>
-      <c r="W2"/>
-      <c r="X2"/>
-      <c r="Y2"/>
-      <c r="Z2"/>
-      <c r="AA2"/>
-      <c r="AB2"/>
-      <c r="AC2"/>
-      <c r="AD2"/>
-      <c r="AE2"/>
-      <c r="AF2"/>
-      <c r="AG2"/>
-      <c r="AH2"/>
-      <c r="AI2"/>
-      <c r="AJ2"/>
-      <c r="AK2"/>
-      <c r="AL2"/>
-      <c r="AM2"/>
-      <c r="AN2"/>
-      <c r="AO2"/>
-      <c r="AP2"/>
-      <c r="AQ2"/>
-      <c r="AR2"/>
-      <c r="AS2"/>
-      <c r="AT2"/>
-      <c r="AU2"/>
-      <c r="AV2"/>
-      <c r="AW2"/>
-      <c r="AX2"/>
-      <c r="AY2"/>
-      <c r="AZ2"/>
-      <c r="BA2"/>
-      <c r="BB2"/>
-      <c r="BC2"/>
-      <c r="BD2"/>
-      <c r="BE2"/>
-      <c r="BF2"/>
-      <c r="BG2"/>
-      <c r="BH2"/>
-      <c r="BI2"/>
-      <c r="BJ2"/>
-      <c r="BK2"/>
-      <c r="BL2"/>
-      <c r="BM2"/>
-      <c r="BN2"/>
-      <c r="BO2"/>
-      <c r="BP2"/>
-      <c r="BQ2"/>
-      <c r="BR2"/>
-      <c r="BS2"/>
-      <c r="BT2"/>
-      <c r="BU2"/>
-      <c r="BV2"/>
-      <c r="BW2"/>
-      <c r="BX2"/>
-      <c r="BY2"/>
-      <c r="BZ2"/>
-      <c r="CA2"/>
-      <c r="CB2"/>
-      <c r="CC2"/>
-      <c r="CD2"/>
-      <c r="CE2"/>
-      <c r="CF2"/>
-      <c r="CG2"/>
-      <c r="CH2"/>
-      <c r="CI2"/>
-      <c r="CJ2"/>
-      <c r="CK2"/>
-      <c r="CL2"/>
-      <c r="CM2"/>
-      <c r="CN2"/>
-      <c r="CO2"/>
-      <c r="CP2"/>
-      <c r="CQ2"/>
-      <c r="CR2"/>
-      <c r="CS2"/>
-      <c r="CT2"/>
-      <c r="CU2"/>
-      <c r="CV2"/>
-      <c r="CW2"/>
-      <c r="CX2"/>
-      <c r="CY2"/>
-      <c r="CZ2"/>
-      <c r="DA2"/>
-      <c r="DB2"/>
-      <c r="DC2"/>
-      <c r="DD2"/>
-      <c r="DE2"/>
-      <c r="DF2"/>
-      <c r="DG2"/>
-      <c r="DH2"/>
-      <c r="DI2"/>
-      <c r="DJ2"/>
-      <c r="DK2"/>
-      <c r="DL2"/>
-      <c r="DM2"/>
-      <c r="DN2"/>
-      <c r="DO2"/>
-      <c r="DP2"/>
-      <c r="DQ2"/>
-      <c r="DR2"/>
-      <c r="DS2"/>
-      <c r="DT2"/>
-      <c r="DU2"/>
-      <c r="DV2"/>
-      <c r="DW2"/>
-      <c r="DX2"/>
-      <c r="DY2"/>
-      <c r="DZ2"/>
-      <c r="EA2"/>
-      <c r="EB2"/>
-      <c r="EC2"/>
-      <c r="ED2"/>
-      <c r="EE2"/>
-      <c r="EF2"/>
-      <c r="EG2"/>
-      <c r="EH2"/>
-      <c r="EI2"/>
-      <c r="EJ2"/>
-      <c r="EK2"/>
-      <c r="EL2"/>
-      <c r="EM2"/>
-      <c r="EN2"/>
-      <c r="EO2"/>
-      <c r="EP2"/>
-      <c r="EQ2"/>
-      <c r="ER2"/>
-      <c r="ES2"/>
-      <c r="ET2"/>
-      <c r="EU2"/>
-      <c r="EV2"/>
-      <c r="EW2"/>
-      <c r="EX2"/>
-      <c r="EY2"/>
-      <c r="EZ2"/>
-      <c r="FA2"/>
-      <c r="FB2"/>
-      <c r="FC2"/>
-      <c r="FD2"/>
-      <c r="FE2"/>
-      <c r="FF2"/>
-      <c r="FG2"/>
-      <c r="FH2"/>
-      <c r="FI2"/>
-      <c r="FJ2"/>
-      <c r="FK2"/>
-      <c r="FL2"/>
-      <c r="FM2"/>
-      <c r="FN2"/>
-      <c r="FO2"/>
-      <c r="FP2"/>
-      <c r="FQ2"/>
-      <c r="FR2"/>
-      <c r="FS2"/>
-      <c r="FT2"/>
-      <c r="FU2"/>
-      <c r="FV2"/>
-      <c r="FW2"/>
-      <c r="FX2"/>
-      <c r="FY2"/>
-      <c r="FZ2"/>
-      <c r="GA2"/>
-      <c r="GB2"/>
-      <c r="GC2"/>
-      <c r="GD2"/>
-      <c r="GE2"/>
-      <c r="GF2"/>
-      <c r="GG2"/>
-      <c r="GH2"/>
-      <c r="GI2"/>
-      <c r="GJ2"/>
-      <c r="GK2"/>
-      <c r="GL2"/>
-      <c r="GM2"/>
-      <c r="GN2"/>
-      <c r="GO2"/>
-      <c r="GP2"/>
-      <c r="GQ2"/>
-      <c r="GR2"/>
-      <c r="GS2"/>
-      <c r="GT2"/>
-      <c r="GU2"/>
-      <c r="GV2"/>
-      <c r="GW2"/>
-      <c r="GX2"/>
-      <c r="GY2"/>
-      <c r="GZ2"/>
-      <c r="HA2"/>
-      <c r="HB2"/>
-      <c r="HC2"/>
-      <c r="HD2"/>
-      <c r="HE2"/>
-      <c r="HF2"/>
-      <c r="HG2"/>
-      <c r="HH2"/>
-      <c r="HI2"/>
-      <c r="HJ2"/>
-      <c r="HK2"/>
-      <c r="HL2"/>
-      <c r="HM2"/>
-      <c r="HN2"/>
-      <c r="HO2"/>
-      <c r="HP2"/>
-      <c r="HQ2"/>
-      <c r="HR2"/>
-      <c r="HS2"/>
-      <c r="HT2"/>
-      <c r="HU2"/>
-    </row>
-    <row r="3" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
-        <v>460</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>461</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>462</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="4" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
-        <v>464</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>467</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>465</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="5" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A5" s="8" t="s">
-        <v>468</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>469</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>470</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="6" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A6" s="3" t="s">
-        <v>473</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>472</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>474</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="7" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A7" s="3" t="s">
-        <v>476</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>477</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>478</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="8" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A8" s="3" t="s">
-        <v>480</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>481</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>482</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="9" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A9" s="3" t="s">
-        <v>484</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>485</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>487</v>
       </c>
     </row>
   </sheetData>
@@ -19357,8 +19024,8 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A4E3580-B709-4E66-9F6E-B7F9948D7FD3}">
-  <dimension ref="A1:HU7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6428663-7558-48F1-8CD3-947F03FFD4CC}">
+  <dimension ref="A1:HU9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="50.90625" bestFit="1" customWidth="1"/>
@@ -19399,13 +19066,13 @@
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>488</v>
+        <v>457</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>489</v>
+        <v>458</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>490</v>
+        <v>459</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
@@ -19420,7 +19087,7 @@
         <v>211</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>491</v>
+        <v>192</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -19646,13 +19313,13 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>492</v>
+        <v>460</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>493</v>
+        <v>461</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>494</v>
+        <v>462</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
@@ -19667,18 +19334,18 @@
         <v>211</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>495</v>
+        <v>463</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>496</v>
+        <v>464</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>497</v>
+        <v>467</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>498</v>
+        <v>465</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
@@ -19693,18 +19360,18 @@
         <v>211</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>499</v>
+        <v>466</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
-        <v>500</v>
+        <v>468</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>501</v>
+        <v>469</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>502</v>
+        <v>470</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
@@ -19719,18 +19386,18 @@
         <v>211</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>503</v>
+        <v>471</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>504</v>
+        <v>473</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>505</v>
+        <v>472</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>506</v>
+        <v>474</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>0</v>
@@ -19745,18 +19412,18 @@
         <v>211</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>507</v>
+        <v>475</v>
       </c>
     </row>
     <row r="7" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>509</v>
+        <v>476</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>508</v>
+        <v>477</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>510</v>
+        <v>478</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>0</v>
@@ -19771,17 +19438,70 @@
         <v>211</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>511</v>
+        <v>479</v>
+      </c>
+    </row>
+    <row r="8" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="9" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>487</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95706458-CD50-4C74-87C4-ABAE617927AD}">
-  <dimension ref="A1:HU2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A4E3580-B709-4E66-9F6E-B7F9948D7FD3}">
+  <dimension ref="A1:HU7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="50.90625" bestFit="1" customWidth="1"/>
@@ -19822,13 +19542,13 @@
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>512</v>
+        <v>488</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>513</v>
+        <v>489</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>514</v>
+        <v>490</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
@@ -19843,7 +19563,7 @@
         <v>211</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>140</v>
+        <v>491</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -20067,14 +19787,144 @@
       <c r="HT2"/>
       <c r="HU2"/>
     </row>
+    <row r="3" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>493</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="4" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="5" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A5" s="8" t="s">
+        <v>500</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>501</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>502</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="6" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="7" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>511</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AD86191-7CFE-4ED9-9129-FF78170AB51E}">
-  <dimension ref="A1:HU12"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95706458-CD50-4C74-87C4-ABAE617927AD}">
+  <dimension ref="A1:HU2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="50.90625" bestFit="1" customWidth="1"/>
@@ -20084,7 +19934,7 @@
     <col min="5" max="5" width="33.08984375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17.08984375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="40.81640625" customWidth="1"/>
-    <col min="8" max="8" width="65.54296875" customWidth="1"/>
+    <col min="8" max="8" width="57.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:229" x14ac:dyDescent="0.35">
@@ -20115,13 +19965,13 @@
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>527</v>
+        <v>512</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>528</v>
+        <v>513</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>529</v>
+        <v>514</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
@@ -20136,7 +19986,7 @@
         <v>211</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>530</v>
+        <v>140</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -20360,278 +20210,17 @@
       <c r="HT2"/>
       <c r="HU2"/>
     </row>
-    <row r="3" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
-        <v>532</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>531</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>533</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="4" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
-        <v>535</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>536</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>537</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="5" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A5" s="8" t="s">
-        <v>539</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>540</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>541</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="6" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A6" s="3" t="s">
-        <v>543</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>544</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>545</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="7" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A7" s="3" t="s">
-        <v>547</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>548</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>549</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="8" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A8" s="3" t="s">
-        <v>551</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>552</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>553</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G8" s="10" t="s">
-        <v>211</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="9" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A9" s="3" t="s">
-        <v>555</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>556</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>558</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G9" s="10" t="s">
-        <v>211</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="10" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A10" s="3" t="s">
-        <v>559</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>560</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>561</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G10" s="10" t="s">
-        <v>211</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="11" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A11" s="3" t="s">
-        <v>563</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>564</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>565</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G11" s="10" t="s">
-        <v>211</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="12" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A12" s="3" t="s">
-        <v>567</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>568</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>569</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G12" s="10" t="s">
-        <v>211</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>570</v>
-      </c>
-    </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24EB34D0-BCF8-4F57-88CC-AC842687528F}">
-  <dimension ref="A1:HU5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AD86191-7CFE-4ED9-9129-FF78170AB51E}">
+  <dimension ref="A1:HU12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="52.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="50.90625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="52.26953125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="42.453125" customWidth="1"/>
     <col min="4" max="4" width="33.36328125" bestFit="1" customWidth="1"/>
@@ -20669,13 +20258,13 @@
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>576</v>
+        <v>527</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>577</v>
+        <v>528</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>578</v>
+        <v>529</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
@@ -20690,7 +20279,7 @@
         <v>211</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>579</v>
+        <v>530</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -20916,13 +20505,13 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>580</v>
+        <v>532</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>581</v>
+        <v>531</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>582</v>
+        <v>533</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
@@ -20937,42 +20526,44 @@
         <v>211</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>583</v>
+        <v>534</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A4" s="11" t="s">
-        <v>584</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>585</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>586</v>
-      </c>
-      <c r="D4" s="11" t="s">
+      <c r="A4" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>537</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="H4" s="11"/>
+      <c r="H4" s="3" t="s">
+        <v>538</v>
+      </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A5" s="3" t="s">
-        <v>587</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>588</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>589</v>
+      <c r="A5" s="8" t="s">
+        <v>539</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>540</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>541</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
@@ -20987,17 +20578,200 @@
         <v>211</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>590</v>
+        <v>542</v>
+      </c>
+    </row>
+    <row r="6" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>543</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>544</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>545</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="7" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="8" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>552</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>553</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="9" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>558</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="10" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>561</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="11" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A11" s="3" t="s">
+        <v>563</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>564</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>565</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G11" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="12" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A12" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>569</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>570</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7271F742-0542-4B33-AEE2-20AE8A69F475}">
-  <dimension ref="A1:HU3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24EB34D0-BCF8-4F57-88CC-AC842687528F}">
+  <dimension ref="A1:HU5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="52.453125" bestFit="1" customWidth="1"/>
@@ -21038,13 +20812,13 @@
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>594</v>
+        <v>576</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>595</v>
+        <v>577</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>596</v>
+        <v>578</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
@@ -21059,7 +20833,7 @@
         <v>211</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>597</v>
+        <v>579</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -21285,6 +21059,375 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
+        <v>580</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>582</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="4" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A4" s="11" t="s">
+        <v>584</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>585</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>586</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="H4" s="11"/>
+    </row>
+    <row r="5" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>587</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>588</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>589</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>590</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7271F742-0542-4B33-AEE2-20AE8A69F475}">
+  <dimension ref="A1:HU3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="52.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="52.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.453125" customWidth="1"/>
+    <col min="4" max="4" width="33.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="33.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.08984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="40.81640625" customWidth="1"/>
+    <col min="8" max="8" width="65.54296875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>594</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>595</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>596</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="I2"/>
+      <c r="J2"/>
+      <c r="K2"/>
+      <c r="L2"/>
+      <c r="M2"/>
+      <c r="N2"/>
+      <c r="O2"/>
+      <c r="P2"/>
+      <c r="Q2"/>
+      <c r="R2"/>
+      <c r="S2"/>
+      <c r="T2"/>
+      <c r="U2"/>
+      <c r="V2"/>
+      <c r="W2"/>
+      <c r="X2"/>
+      <c r="Y2"/>
+      <c r="Z2"/>
+      <c r="AA2"/>
+      <c r="AB2"/>
+      <c r="AC2"/>
+      <c r="AD2"/>
+      <c r="AE2"/>
+      <c r="AF2"/>
+      <c r="AG2"/>
+      <c r="AH2"/>
+      <c r="AI2"/>
+      <c r="AJ2"/>
+      <c r="AK2"/>
+      <c r="AL2"/>
+      <c r="AM2"/>
+      <c r="AN2"/>
+      <c r="AO2"/>
+      <c r="AP2"/>
+      <c r="AQ2"/>
+      <c r="AR2"/>
+      <c r="AS2"/>
+      <c r="AT2"/>
+      <c r="AU2"/>
+      <c r="AV2"/>
+      <c r="AW2"/>
+      <c r="AX2"/>
+      <c r="AY2"/>
+      <c r="AZ2"/>
+      <c r="BA2"/>
+      <c r="BB2"/>
+      <c r="BC2"/>
+      <c r="BD2"/>
+      <c r="BE2"/>
+      <c r="BF2"/>
+      <c r="BG2"/>
+      <c r="BH2"/>
+      <c r="BI2"/>
+      <c r="BJ2"/>
+      <c r="BK2"/>
+      <c r="BL2"/>
+      <c r="BM2"/>
+      <c r="BN2"/>
+      <c r="BO2"/>
+      <c r="BP2"/>
+      <c r="BQ2"/>
+      <c r="BR2"/>
+      <c r="BS2"/>
+      <c r="BT2"/>
+      <c r="BU2"/>
+      <c r="BV2"/>
+      <c r="BW2"/>
+      <c r="BX2"/>
+      <c r="BY2"/>
+      <c r="BZ2"/>
+      <c r="CA2"/>
+      <c r="CB2"/>
+      <c r="CC2"/>
+      <c r="CD2"/>
+      <c r="CE2"/>
+      <c r="CF2"/>
+      <c r="CG2"/>
+      <c r="CH2"/>
+      <c r="CI2"/>
+      <c r="CJ2"/>
+      <c r="CK2"/>
+      <c r="CL2"/>
+      <c r="CM2"/>
+      <c r="CN2"/>
+      <c r="CO2"/>
+      <c r="CP2"/>
+      <c r="CQ2"/>
+      <c r="CR2"/>
+      <c r="CS2"/>
+      <c r="CT2"/>
+      <c r="CU2"/>
+      <c r="CV2"/>
+      <c r="CW2"/>
+      <c r="CX2"/>
+      <c r="CY2"/>
+      <c r="CZ2"/>
+      <c r="DA2"/>
+      <c r="DB2"/>
+      <c r="DC2"/>
+      <c r="DD2"/>
+      <c r="DE2"/>
+      <c r="DF2"/>
+      <c r="DG2"/>
+      <c r="DH2"/>
+      <c r="DI2"/>
+      <c r="DJ2"/>
+      <c r="DK2"/>
+      <c r="DL2"/>
+      <c r="DM2"/>
+      <c r="DN2"/>
+      <c r="DO2"/>
+      <c r="DP2"/>
+      <c r="DQ2"/>
+      <c r="DR2"/>
+      <c r="DS2"/>
+      <c r="DT2"/>
+      <c r="DU2"/>
+      <c r="DV2"/>
+      <c r="DW2"/>
+      <c r="DX2"/>
+      <c r="DY2"/>
+      <c r="DZ2"/>
+      <c r="EA2"/>
+      <c r="EB2"/>
+      <c r="EC2"/>
+      <c r="ED2"/>
+      <c r="EE2"/>
+      <c r="EF2"/>
+      <c r="EG2"/>
+      <c r="EH2"/>
+      <c r="EI2"/>
+      <c r="EJ2"/>
+      <c r="EK2"/>
+      <c r="EL2"/>
+      <c r="EM2"/>
+      <c r="EN2"/>
+      <c r="EO2"/>
+      <c r="EP2"/>
+      <c r="EQ2"/>
+      <c r="ER2"/>
+      <c r="ES2"/>
+      <c r="ET2"/>
+      <c r="EU2"/>
+      <c r="EV2"/>
+      <c r="EW2"/>
+      <c r="EX2"/>
+      <c r="EY2"/>
+      <c r="EZ2"/>
+      <c r="FA2"/>
+      <c r="FB2"/>
+      <c r="FC2"/>
+      <c r="FD2"/>
+      <c r="FE2"/>
+      <c r="FF2"/>
+      <c r="FG2"/>
+      <c r="FH2"/>
+      <c r="FI2"/>
+      <c r="FJ2"/>
+      <c r="FK2"/>
+      <c r="FL2"/>
+      <c r="FM2"/>
+      <c r="FN2"/>
+      <c r="FO2"/>
+      <c r="FP2"/>
+      <c r="FQ2"/>
+      <c r="FR2"/>
+      <c r="FS2"/>
+      <c r="FT2"/>
+      <c r="FU2"/>
+      <c r="FV2"/>
+      <c r="FW2"/>
+      <c r="FX2"/>
+      <c r="FY2"/>
+      <c r="FZ2"/>
+      <c r="GA2"/>
+      <c r="GB2"/>
+      <c r="GC2"/>
+      <c r="GD2"/>
+      <c r="GE2"/>
+      <c r="GF2"/>
+      <c r="GG2"/>
+      <c r="GH2"/>
+      <c r="GI2"/>
+      <c r="GJ2"/>
+      <c r="GK2"/>
+      <c r="GL2"/>
+      <c r="GM2"/>
+      <c r="GN2"/>
+      <c r="GO2"/>
+      <c r="GP2"/>
+      <c r="GQ2"/>
+      <c r="GR2"/>
+      <c r="GS2"/>
+      <c r="GT2"/>
+      <c r="GU2"/>
+      <c r="GV2"/>
+      <c r="GW2"/>
+      <c r="GX2"/>
+      <c r="GY2"/>
+      <c r="GZ2"/>
+      <c r="HA2"/>
+      <c r="HB2"/>
+      <c r="HC2"/>
+      <c r="HD2"/>
+      <c r="HE2"/>
+      <c r="HF2"/>
+      <c r="HG2"/>
+      <c r="HH2"/>
+      <c r="HI2"/>
+      <c r="HJ2"/>
+      <c r="HK2"/>
+      <c r="HL2"/>
+      <c r="HM2"/>
+      <c r="HN2"/>
+      <c r="HO2"/>
+      <c r="HP2"/>
+      <c r="HQ2"/>
+      <c r="HR2"/>
+      <c r="HS2"/>
+      <c r="HT2"/>
+      <c r="HU2"/>
+    </row>
+    <row r="3" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
         <v>598</v>
       </c>
       <c r="B3" s="3" t="s">
@@ -21310,6 +21453,376 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{738B4CF9-CA20-4A87-AA62-B89EDC02284E}">
+  <dimension ref="A1:HU5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="52.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="52.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.453125" customWidth="1"/>
+    <col min="4" max="4" width="33.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="33.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.08984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="40.81640625" customWidth="1"/>
+    <col min="8" max="8" width="65.54296875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>608</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>609</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H2" s="11"/>
+      <c r="I2"/>
+      <c r="J2"/>
+      <c r="K2"/>
+      <c r="L2"/>
+      <c r="M2"/>
+      <c r="N2"/>
+      <c r="O2"/>
+      <c r="P2"/>
+      <c r="Q2"/>
+      <c r="R2"/>
+      <c r="S2"/>
+      <c r="T2"/>
+      <c r="U2"/>
+      <c r="V2"/>
+      <c r="W2"/>
+      <c r="X2"/>
+      <c r="Y2"/>
+      <c r="Z2"/>
+      <c r="AA2"/>
+      <c r="AB2"/>
+      <c r="AC2"/>
+      <c r="AD2"/>
+      <c r="AE2"/>
+      <c r="AF2"/>
+      <c r="AG2"/>
+      <c r="AH2"/>
+      <c r="AI2"/>
+      <c r="AJ2"/>
+      <c r="AK2"/>
+      <c r="AL2"/>
+      <c r="AM2"/>
+      <c r="AN2"/>
+      <c r="AO2"/>
+      <c r="AP2"/>
+      <c r="AQ2"/>
+      <c r="AR2"/>
+      <c r="AS2"/>
+      <c r="AT2"/>
+      <c r="AU2"/>
+      <c r="AV2"/>
+      <c r="AW2"/>
+      <c r="AX2"/>
+      <c r="AY2"/>
+      <c r="AZ2"/>
+      <c r="BA2"/>
+      <c r="BB2"/>
+      <c r="BC2"/>
+      <c r="BD2"/>
+      <c r="BE2"/>
+      <c r="BF2"/>
+      <c r="BG2"/>
+      <c r="BH2"/>
+      <c r="BI2"/>
+      <c r="BJ2"/>
+      <c r="BK2"/>
+      <c r="BL2"/>
+      <c r="BM2"/>
+      <c r="BN2"/>
+      <c r="BO2"/>
+      <c r="BP2"/>
+      <c r="BQ2"/>
+      <c r="BR2"/>
+      <c r="BS2"/>
+      <c r="BT2"/>
+      <c r="BU2"/>
+      <c r="BV2"/>
+      <c r="BW2"/>
+      <c r="BX2"/>
+      <c r="BY2"/>
+      <c r="BZ2"/>
+      <c r="CA2"/>
+      <c r="CB2"/>
+      <c r="CC2"/>
+      <c r="CD2"/>
+      <c r="CE2"/>
+      <c r="CF2"/>
+      <c r="CG2"/>
+      <c r="CH2"/>
+      <c r="CI2"/>
+      <c r="CJ2"/>
+      <c r="CK2"/>
+      <c r="CL2"/>
+      <c r="CM2"/>
+      <c r="CN2"/>
+      <c r="CO2"/>
+      <c r="CP2"/>
+      <c r="CQ2"/>
+      <c r="CR2"/>
+      <c r="CS2"/>
+      <c r="CT2"/>
+      <c r="CU2"/>
+      <c r="CV2"/>
+      <c r="CW2"/>
+      <c r="CX2"/>
+      <c r="CY2"/>
+      <c r="CZ2"/>
+      <c r="DA2"/>
+      <c r="DB2"/>
+      <c r="DC2"/>
+      <c r="DD2"/>
+      <c r="DE2"/>
+      <c r="DF2"/>
+      <c r="DG2"/>
+      <c r="DH2"/>
+      <c r="DI2"/>
+      <c r="DJ2"/>
+      <c r="DK2"/>
+      <c r="DL2"/>
+      <c r="DM2"/>
+      <c r="DN2"/>
+      <c r="DO2"/>
+      <c r="DP2"/>
+      <c r="DQ2"/>
+      <c r="DR2"/>
+      <c r="DS2"/>
+      <c r="DT2"/>
+      <c r="DU2"/>
+      <c r="DV2"/>
+      <c r="DW2"/>
+      <c r="DX2"/>
+      <c r="DY2"/>
+      <c r="DZ2"/>
+      <c r="EA2"/>
+      <c r="EB2"/>
+      <c r="EC2"/>
+      <c r="ED2"/>
+      <c r="EE2"/>
+      <c r="EF2"/>
+      <c r="EG2"/>
+      <c r="EH2"/>
+      <c r="EI2"/>
+      <c r="EJ2"/>
+      <c r="EK2"/>
+      <c r="EL2"/>
+      <c r="EM2"/>
+      <c r="EN2"/>
+      <c r="EO2"/>
+      <c r="EP2"/>
+      <c r="EQ2"/>
+      <c r="ER2"/>
+      <c r="ES2"/>
+      <c r="ET2"/>
+      <c r="EU2"/>
+      <c r="EV2"/>
+      <c r="EW2"/>
+      <c r="EX2"/>
+      <c r="EY2"/>
+      <c r="EZ2"/>
+      <c r="FA2"/>
+      <c r="FB2"/>
+      <c r="FC2"/>
+      <c r="FD2"/>
+      <c r="FE2"/>
+      <c r="FF2"/>
+      <c r="FG2"/>
+      <c r="FH2"/>
+      <c r="FI2"/>
+      <c r="FJ2"/>
+      <c r="FK2"/>
+      <c r="FL2"/>
+      <c r="FM2"/>
+      <c r="FN2"/>
+      <c r="FO2"/>
+      <c r="FP2"/>
+      <c r="FQ2"/>
+      <c r="FR2"/>
+      <c r="FS2"/>
+      <c r="FT2"/>
+      <c r="FU2"/>
+      <c r="FV2"/>
+      <c r="FW2"/>
+      <c r="FX2"/>
+      <c r="FY2"/>
+      <c r="FZ2"/>
+      <c r="GA2"/>
+      <c r="GB2"/>
+      <c r="GC2"/>
+      <c r="GD2"/>
+      <c r="GE2"/>
+      <c r="GF2"/>
+      <c r="GG2"/>
+      <c r="GH2"/>
+      <c r="GI2"/>
+      <c r="GJ2"/>
+      <c r="GK2"/>
+      <c r="GL2"/>
+      <c r="GM2"/>
+      <c r="GN2"/>
+      <c r="GO2"/>
+      <c r="GP2"/>
+      <c r="GQ2"/>
+      <c r="GR2"/>
+      <c r="GS2"/>
+      <c r="GT2"/>
+      <c r="GU2"/>
+      <c r="GV2"/>
+      <c r="GW2"/>
+      <c r="GX2"/>
+      <c r="GY2"/>
+      <c r="GZ2"/>
+      <c r="HA2"/>
+      <c r="HB2"/>
+      <c r="HC2"/>
+      <c r="HD2"/>
+      <c r="HE2"/>
+      <c r="HF2"/>
+      <c r="HG2"/>
+      <c r="HH2"/>
+      <c r="HI2"/>
+      <c r="HJ2"/>
+      <c r="HK2"/>
+      <c r="HL2"/>
+      <c r="HM2"/>
+      <c r="HN2"/>
+      <c r="HO2"/>
+      <c r="HP2"/>
+      <c r="HQ2"/>
+      <c r="HR2"/>
+      <c r="HS2"/>
+      <c r="HT2"/>
+      <c r="HU2"/>
+    </row>
+    <row r="3" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>610</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>611</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>612</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="4" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>614</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>615</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>616</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="5" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>618</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>619</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>620</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>621</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/testdata.xlsx
+++ b/testdata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sshiwani\workspace\find-information-products-services-tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DC67814-7EC6-4595-B980-9CA1061BB621}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3998CDD-2D0D-4FE1-90F0-EC349A662F70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" firstSheet="18" activeTab="19" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" firstSheet="19" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="category_phase" sheetId="1" r:id="rId1"/>
@@ -33,22 +33,24 @@
     <sheet name="UG_EPEYAltProvSetWorkforce_list" sheetId="32" r:id="rId18"/>
     <sheet name="UG_EPEYEarlyYearsWorkforce_list" sheetId="35" r:id="rId19"/>
     <sheet name="UG_EPEYFurtherEduWorkforce_list" sheetId="37" r:id="rId20"/>
-    <sheet name="UGSubcategory_AdultLearner" sheetId="16" r:id="rId21"/>
-    <sheet name="UGSubcategory_CareersAdviser" sheetId="17" r:id="rId22"/>
-    <sheet name="UGSubcategory_ChildOrYoungPers" sheetId="18" r:id="rId23"/>
-    <sheet name="UGSubcategory_DfEWorkforce" sheetId="19" r:id="rId24"/>
-    <sheet name="UGSubcategory_Employer" sheetId="20" r:id="rId25"/>
-    <sheet name="UGSubcategory_LAWorkforce" sheetId="21" r:id="rId26"/>
-    <sheet name="UGSubcategory_NEETOrCareerSeek" sheetId="22" r:id="rId27"/>
-    <sheet name="UGSubcategory_ParentOrCarer" sheetId="23" r:id="rId28"/>
-    <sheet name="UGSubcateg_ProfExtUserofDfEData" sheetId="24" r:id="rId29"/>
-    <sheet name="UGSubcategory_SCWorkforce" sheetId="25" r:id="rId30"/>
-    <sheet name="UGSubcategory_SocialWorker" sheetId="27" r:id="rId31"/>
-    <sheet name="UGSubcategory_EPandEYWorkforce" sheetId="29" r:id="rId32"/>
-    <sheet name="EPEYSubcateg_AcademyTWorkforce" sheetId="31" r:id="rId33"/>
-    <sheet name="EPEYSubcateg_AltProSetWorkforce" sheetId="33" r:id="rId34"/>
-    <sheet name="EPEYSubcatg_EarlyYearsWorkforce" sheetId="34" r:id="rId35"/>
-    <sheet name="EPEYSubcatg_FurtherEduWorkforce" sheetId="36" r:id="rId36"/>
+    <sheet name="UG_EPEYHigherEduWorkforce_list" sheetId="38" r:id="rId21"/>
+    <sheet name="UGSubcategory_AdultLearner" sheetId="16" r:id="rId22"/>
+    <sheet name="UGSubcategory_CareersAdviser" sheetId="17" r:id="rId23"/>
+    <sheet name="UGSubcategory_ChildOrYoungPers" sheetId="18" r:id="rId24"/>
+    <sheet name="UGSubcategory_DfEWorkforce" sheetId="19" r:id="rId25"/>
+    <sheet name="UGSubcategory_Employer" sheetId="20" r:id="rId26"/>
+    <sheet name="UGSubcategory_LAWorkforce" sheetId="21" r:id="rId27"/>
+    <sheet name="UGSubcategory_NEETOrCareerSeek" sheetId="22" r:id="rId28"/>
+    <sheet name="UGSubcategory_ParentOrCarer" sheetId="23" r:id="rId29"/>
+    <sheet name="UGSubcateg_ProfExtUserofDfEData" sheetId="24" r:id="rId30"/>
+    <sheet name="UGSubcategory_SCWorkforce" sheetId="25" r:id="rId31"/>
+    <sheet name="UGSubcategory_SocialWorker" sheetId="27" r:id="rId32"/>
+    <sheet name="UGSubcategory_EPandEYWorkforce" sheetId="29" r:id="rId33"/>
+    <sheet name="EPEYSubcateg_AcademyTWorkforce" sheetId="31" r:id="rId34"/>
+    <sheet name="EPEYSubcateg_AltProSetWorkforce" sheetId="33" r:id="rId35"/>
+    <sheet name="EPEYSubcatg_EarlyYearsWorkforce" sheetId="34" r:id="rId36"/>
+    <sheet name="EPEYSubcatg_FurtherEduWorkforce" sheetId="36" r:id="rId37"/>
+    <sheet name="EPEYSubcatg_HigherEduWorkforce" sheetId="39" r:id="rId38"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -60,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1308" uniqueCount="622">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1362" uniqueCount="643">
   <si>
     <t>Search and filter products and services</t>
   </si>
@@ -1926,6 +1928,69 @@
   </si>
   <si>
     <t>Lecturer (further education)  (Further education workforce)</t>
+  </si>
+  <si>
+    <t>categories/user-group/education-provider-and-early-years-workforce/higher-education-workforce</t>
+  </si>
+  <si>
+    <t>Browse products in Higher education workforce</t>
+  </si>
+  <si>
+    <t>Lecturer (higher education)</t>
+  </si>
+  <si>
+    <t>University leader</t>
+  </si>
+  <si>
+    <t>University support staff</t>
+  </si>
+  <si>
+    <t>products?userGroup=higher-education-workforce</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Higher education workforce  (Education provider and early years workforce)')</t>
+  </si>
+  <si>
+    <t>Remove this filter Higher education workforce  (Education provider and early years workforce)</t>
+  </si>
+  <si>
+    <t>Higher education workforce  (Education provider and early years workforce)</t>
+  </si>
+  <si>
+    <t>products?userGroup=lecturer-higher-education</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Lecturer (higher education) ')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remove this filter Lecturer (higher education) </t>
+  </si>
+  <si>
+    <t>Lecturer (higher education)  (Higher education workforce)</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' University leader ')</t>
+  </si>
+  <si>
+    <t>products?userGroup=university-leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remove this filter University leader </t>
+  </si>
+  <si>
+    <t>University leader  (Higher education workforce)</t>
+  </si>
+  <si>
+    <t>products?userGroup=university-support-staff</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' University support staff  (Higher education workforce)')</t>
+  </si>
+  <si>
+    <t>Remove this filter University support staff  (Higher education workforce)</t>
+  </si>
+  <si>
+    <t>University support staff  (Higher education workforce)</t>
   </si>
 </sst>
 </file>
@@ -12961,6 +13026,87 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8566466-31D4-4316-960A-E75B8AD62D44}">
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="54.1796875" customWidth="1"/>
+    <col min="2" max="2" width="47.453125" customWidth="1"/>
+    <col min="3" max="3" width="50.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>622</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B3" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B4" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>624</v>
+      </c>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>625</v>
+      </c>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>626</v>
+      </c>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB5527F7-85DB-4F8E-B4B3-EC8453E599E1}">
   <dimension ref="A1:HU6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -13358,7 +13504,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A99CF6C3-F305-48A2-AB80-2C2D7CE6460C}">
   <dimension ref="A1:HU5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -13729,7 +13875,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EFF0597-7FD1-4E6A-AA71-DB9F9FAB97A9}">
   <dimension ref="A1:HU7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -14153,7 +14299,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F4A57AC-4620-4875-88AE-9F5C739A9042}">
   <dimension ref="A1:HU6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -14550,7 +14696,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C1C130F-0899-4810-82F6-950C9CB07234}">
   <dimension ref="A1:HU5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -14921,7 +15067,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AB9395B-D522-49AD-B790-5334356249F6}">
   <dimension ref="A1:HU7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -15344,7 +15490,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEE91763-AD0C-4544-A433-3B50C88AEB79}">
   <dimension ref="A1:HU7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -15767,7 +15913,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20DD36AA-F163-4AAB-BD30-4AE6290CCAE7}">
   <dimension ref="A1:HU10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -16261,456 +16407,6 @@
       </c>
       <c r="H10" s="3" t="s">
         <v>389</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6EE6111-FDB3-4B43-8820-BBF68AAFCD6D}">
-  <dimension ref="A1:HU8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="50.90625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="52.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.453125" customWidth="1"/>
-    <col min="4" max="4" width="33.36328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="33.08984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.08984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="40.81640625" customWidth="1"/>
-    <col min="8" max="8" width="62.54296875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
-        <v>390</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>391</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>392</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="I2"/>
-      <c r="J2"/>
-      <c r="K2"/>
-      <c r="L2"/>
-      <c r="M2"/>
-      <c r="N2"/>
-      <c r="O2"/>
-      <c r="P2"/>
-      <c r="Q2"/>
-      <c r="R2"/>
-      <c r="S2"/>
-      <c r="T2"/>
-      <c r="U2"/>
-      <c r="V2"/>
-      <c r="W2"/>
-      <c r="X2"/>
-      <c r="Y2"/>
-      <c r="Z2"/>
-      <c r="AA2"/>
-      <c r="AB2"/>
-      <c r="AC2"/>
-      <c r="AD2"/>
-      <c r="AE2"/>
-      <c r="AF2"/>
-      <c r="AG2"/>
-      <c r="AH2"/>
-      <c r="AI2"/>
-      <c r="AJ2"/>
-      <c r="AK2"/>
-      <c r="AL2"/>
-      <c r="AM2"/>
-      <c r="AN2"/>
-      <c r="AO2"/>
-      <c r="AP2"/>
-      <c r="AQ2"/>
-      <c r="AR2"/>
-      <c r="AS2"/>
-      <c r="AT2"/>
-      <c r="AU2"/>
-      <c r="AV2"/>
-      <c r="AW2"/>
-      <c r="AX2"/>
-      <c r="AY2"/>
-      <c r="AZ2"/>
-      <c r="BA2"/>
-      <c r="BB2"/>
-      <c r="BC2"/>
-      <c r="BD2"/>
-      <c r="BE2"/>
-      <c r="BF2"/>
-      <c r="BG2"/>
-      <c r="BH2"/>
-      <c r="BI2"/>
-      <c r="BJ2"/>
-      <c r="BK2"/>
-      <c r="BL2"/>
-      <c r="BM2"/>
-      <c r="BN2"/>
-      <c r="BO2"/>
-      <c r="BP2"/>
-      <c r="BQ2"/>
-      <c r="BR2"/>
-      <c r="BS2"/>
-      <c r="BT2"/>
-      <c r="BU2"/>
-      <c r="BV2"/>
-      <c r="BW2"/>
-      <c r="BX2"/>
-      <c r="BY2"/>
-      <c r="BZ2"/>
-      <c r="CA2"/>
-      <c r="CB2"/>
-      <c r="CC2"/>
-      <c r="CD2"/>
-      <c r="CE2"/>
-      <c r="CF2"/>
-      <c r="CG2"/>
-      <c r="CH2"/>
-      <c r="CI2"/>
-      <c r="CJ2"/>
-      <c r="CK2"/>
-      <c r="CL2"/>
-      <c r="CM2"/>
-      <c r="CN2"/>
-      <c r="CO2"/>
-      <c r="CP2"/>
-      <c r="CQ2"/>
-      <c r="CR2"/>
-      <c r="CS2"/>
-      <c r="CT2"/>
-      <c r="CU2"/>
-      <c r="CV2"/>
-      <c r="CW2"/>
-      <c r="CX2"/>
-      <c r="CY2"/>
-      <c r="CZ2"/>
-      <c r="DA2"/>
-      <c r="DB2"/>
-      <c r="DC2"/>
-      <c r="DD2"/>
-      <c r="DE2"/>
-      <c r="DF2"/>
-      <c r="DG2"/>
-      <c r="DH2"/>
-      <c r="DI2"/>
-      <c r="DJ2"/>
-      <c r="DK2"/>
-      <c r="DL2"/>
-      <c r="DM2"/>
-      <c r="DN2"/>
-      <c r="DO2"/>
-      <c r="DP2"/>
-      <c r="DQ2"/>
-      <c r="DR2"/>
-      <c r="DS2"/>
-      <c r="DT2"/>
-      <c r="DU2"/>
-      <c r="DV2"/>
-      <c r="DW2"/>
-      <c r="DX2"/>
-      <c r="DY2"/>
-      <c r="DZ2"/>
-      <c r="EA2"/>
-      <c r="EB2"/>
-      <c r="EC2"/>
-      <c r="ED2"/>
-      <c r="EE2"/>
-      <c r="EF2"/>
-      <c r="EG2"/>
-      <c r="EH2"/>
-      <c r="EI2"/>
-      <c r="EJ2"/>
-      <c r="EK2"/>
-      <c r="EL2"/>
-      <c r="EM2"/>
-      <c r="EN2"/>
-      <c r="EO2"/>
-      <c r="EP2"/>
-      <c r="EQ2"/>
-      <c r="ER2"/>
-      <c r="ES2"/>
-      <c r="ET2"/>
-      <c r="EU2"/>
-      <c r="EV2"/>
-      <c r="EW2"/>
-      <c r="EX2"/>
-      <c r="EY2"/>
-      <c r="EZ2"/>
-      <c r="FA2"/>
-      <c r="FB2"/>
-      <c r="FC2"/>
-      <c r="FD2"/>
-      <c r="FE2"/>
-      <c r="FF2"/>
-      <c r="FG2"/>
-      <c r="FH2"/>
-      <c r="FI2"/>
-      <c r="FJ2"/>
-      <c r="FK2"/>
-      <c r="FL2"/>
-      <c r="FM2"/>
-      <c r="FN2"/>
-      <c r="FO2"/>
-      <c r="FP2"/>
-      <c r="FQ2"/>
-      <c r="FR2"/>
-      <c r="FS2"/>
-      <c r="FT2"/>
-      <c r="FU2"/>
-      <c r="FV2"/>
-      <c r="FW2"/>
-      <c r="FX2"/>
-      <c r="FY2"/>
-      <c r="FZ2"/>
-      <c r="GA2"/>
-      <c r="GB2"/>
-      <c r="GC2"/>
-      <c r="GD2"/>
-      <c r="GE2"/>
-      <c r="GF2"/>
-      <c r="GG2"/>
-      <c r="GH2"/>
-      <c r="GI2"/>
-      <c r="GJ2"/>
-      <c r="GK2"/>
-      <c r="GL2"/>
-      <c r="GM2"/>
-      <c r="GN2"/>
-      <c r="GO2"/>
-      <c r="GP2"/>
-      <c r="GQ2"/>
-      <c r="GR2"/>
-      <c r="GS2"/>
-      <c r="GT2"/>
-      <c r="GU2"/>
-      <c r="GV2"/>
-      <c r="GW2"/>
-      <c r="GX2"/>
-      <c r="GY2"/>
-      <c r="GZ2"/>
-      <c r="HA2"/>
-      <c r="HB2"/>
-      <c r="HC2"/>
-      <c r="HD2"/>
-      <c r="HE2"/>
-      <c r="HF2"/>
-      <c r="HG2"/>
-      <c r="HH2"/>
-      <c r="HI2"/>
-      <c r="HJ2"/>
-      <c r="HK2"/>
-      <c r="HL2"/>
-      <c r="HM2"/>
-      <c r="HN2"/>
-      <c r="HO2"/>
-      <c r="HP2"/>
-      <c r="HQ2"/>
-      <c r="HR2"/>
-      <c r="HS2"/>
-      <c r="HT2"/>
-      <c r="HU2"/>
-    </row>
-    <row r="3" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>394</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>395</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="4" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
-        <v>397</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>398</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>399</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="5" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A5" s="8" t="s">
-        <v>401</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>402</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>403</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="6" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A6" s="3" t="s">
-        <v>405</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>406</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>407</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="7" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A7" s="3" t="s">
-        <v>409</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>411</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="8" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A8" s="9" t="s">
-        <v>413</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>414</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>415</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="H8" s="9" t="s">
-        <v>416</v>
       </c>
     </row>
   </sheetData>
@@ -19024,8 +18720,8 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6428663-7558-48F1-8CD3-947F03FFD4CC}">
-  <dimension ref="A1:HU9"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6EE6111-FDB3-4B43-8820-BBF68AAFCD6D}">
+  <dimension ref="A1:HU8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="50.90625" bestFit="1" customWidth="1"/>
@@ -19035,7 +18731,7 @@
     <col min="5" max="5" width="33.08984375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17.08984375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="40.81640625" customWidth="1"/>
-    <col min="8" max="8" width="57.08984375" customWidth="1"/>
+    <col min="8" max="8" width="62.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:229" x14ac:dyDescent="0.35">
@@ -19066,13 +18762,13 @@
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>457</v>
+        <v>390</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>458</v>
+        <v>391</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>459</v>
+        <v>392</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
@@ -19087,7 +18783,7 @@
         <v>211</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -19313,13 +19009,13 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>460</v>
+        <v>393</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>461</v>
+        <v>394</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>462</v>
+        <v>395</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
@@ -19334,18 +19030,18 @@
         <v>211</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>463</v>
+        <v>396</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>464</v>
+        <v>397</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>467</v>
+        <v>398</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>465</v>
+        <v>399</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
@@ -19360,18 +19056,18 @@
         <v>211</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>466</v>
+        <v>400</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
-        <v>468</v>
+        <v>401</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>469</v>
+        <v>402</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>470</v>
+        <v>403</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
@@ -19386,18 +19082,18 @@
         <v>211</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>471</v>
+        <v>404</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>473</v>
+        <v>405</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>472</v>
+        <v>406</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>474</v>
+        <v>407</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>0</v>
@@ -19412,18 +19108,18 @@
         <v>211</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>475</v>
+        <v>408</v>
       </c>
     </row>
     <row r="7" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>476</v>
+        <v>409</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>477</v>
+        <v>410</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>478</v>
+        <v>411</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>0</v>
@@ -19438,18 +19134,18 @@
         <v>211</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>479</v>
+        <v>412</v>
       </c>
     </row>
     <row r="8" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A8" s="3" t="s">
-        <v>480</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>481</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>482</v>
+      <c r="A8" s="9" t="s">
+        <v>413</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>414</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>415</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>0</v>
@@ -19463,34 +19159,8 @@
       <c r="G8" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="9" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A9" s="3" t="s">
-        <v>484</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>485</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>487</v>
+      <c r="H8" s="9" t="s">
+        <v>416</v>
       </c>
     </row>
   </sheetData>
@@ -19500,8 +19170,8 @@
 </file>
 
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A4E3580-B709-4E66-9F6E-B7F9948D7FD3}">
-  <dimension ref="A1:HU7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6428663-7558-48F1-8CD3-947F03FFD4CC}">
+  <dimension ref="A1:HU9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="50.90625" bestFit="1" customWidth="1"/>
@@ -19542,13 +19212,13 @@
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>488</v>
+        <v>457</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>489</v>
+        <v>458</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>490</v>
+        <v>459</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
@@ -19563,7 +19233,7 @@
         <v>211</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>491</v>
+        <v>192</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -19789,13 +19459,13 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>492</v>
+        <v>460</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>493</v>
+        <v>461</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>494</v>
+        <v>462</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
@@ -19810,18 +19480,18 @@
         <v>211</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>495</v>
+        <v>463</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>496</v>
+        <v>464</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>497</v>
+        <v>467</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>498</v>
+        <v>465</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
@@ -19836,18 +19506,18 @@
         <v>211</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>499</v>
+        <v>466</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
-        <v>500</v>
+        <v>468</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>501</v>
+        <v>469</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>502</v>
+        <v>470</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
@@ -19862,18 +19532,18 @@
         <v>211</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>503</v>
+        <v>471</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>504</v>
+        <v>473</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>505</v>
+        <v>472</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>506</v>
+        <v>474</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>0</v>
@@ -19888,18 +19558,18 @@
         <v>211</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>507</v>
+        <v>475</v>
       </c>
     </row>
     <row r="7" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>509</v>
+        <v>476</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>508</v>
+        <v>477</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>510</v>
+        <v>478</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>0</v>
@@ -19914,17 +19584,70 @@
         <v>211</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>511</v>
+        <v>479</v>
+      </c>
+    </row>
+    <row r="8" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="9" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>487</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95706458-CD50-4C74-87C4-ABAE617927AD}">
-  <dimension ref="A1:HU2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A4E3580-B709-4E66-9F6E-B7F9948D7FD3}">
+  <dimension ref="A1:HU7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="50.90625" bestFit="1" customWidth="1"/>
@@ -19965,13 +19688,13 @@
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>512</v>
+        <v>488</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>513</v>
+        <v>489</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>514</v>
+        <v>490</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
@@ -19986,7 +19709,7 @@
         <v>211</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>140</v>
+        <v>491</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -20210,14 +19933,144 @@
       <c r="HT2"/>
       <c r="HU2"/>
     </row>
+    <row r="3" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>493</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="4" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="5" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A5" s="8" t="s">
+        <v>500</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>501</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>502</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="6" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="7" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>511</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AD86191-7CFE-4ED9-9129-FF78170AB51E}">
-  <dimension ref="A1:HU12"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95706458-CD50-4C74-87C4-ABAE617927AD}">
+  <dimension ref="A1:HU2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="50.90625" bestFit="1" customWidth="1"/>
@@ -20227,7 +20080,7 @@
     <col min="5" max="5" width="33.08984375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17.08984375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="40.81640625" customWidth="1"/>
-    <col min="8" max="8" width="65.54296875" customWidth="1"/>
+    <col min="8" max="8" width="57.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:229" x14ac:dyDescent="0.35">
@@ -20258,13 +20111,13 @@
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>527</v>
+        <v>512</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>528</v>
+        <v>513</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>529</v>
+        <v>514</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
@@ -20279,7 +20132,7 @@
         <v>211</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>530</v>
+        <v>140</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -20503,278 +20356,17 @@
       <c r="HT2"/>
       <c r="HU2"/>
     </row>
-    <row r="3" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
-        <v>532</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>531</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>533</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="4" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
-        <v>535</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>536</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>537</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="5" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A5" s="8" t="s">
-        <v>539</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>540</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>541</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="6" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A6" s="3" t="s">
-        <v>543</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>544</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>545</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="7" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A7" s="3" t="s">
-        <v>547</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>548</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>549</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="8" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A8" s="3" t="s">
-        <v>551</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>552</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>553</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G8" s="10" t="s">
-        <v>211</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="9" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A9" s="3" t="s">
-        <v>555</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>556</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>558</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G9" s="10" t="s">
-        <v>211</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="10" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A10" s="3" t="s">
-        <v>559</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>560</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>561</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G10" s="10" t="s">
-        <v>211</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="11" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A11" s="3" t="s">
-        <v>563</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>564</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>565</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G11" s="10" t="s">
-        <v>211</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="12" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A12" s="3" t="s">
-        <v>567</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>568</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>569</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G12" s="10" t="s">
-        <v>211</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>570</v>
-      </c>
-    </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24EB34D0-BCF8-4F57-88CC-AC842687528F}">
-  <dimension ref="A1:HU5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AD86191-7CFE-4ED9-9129-FF78170AB51E}">
+  <dimension ref="A1:HU12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="52.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="50.90625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="52.26953125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="42.453125" customWidth="1"/>
     <col min="4" max="4" width="33.36328125" bestFit="1" customWidth="1"/>
@@ -20812,13 +20404,13 @@
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>576</v>
+        <v>527</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>577</v>
+        <v>528</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>578</v>
+        <v>529</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
@@ -20833,7 +20425,7 @@
         <v>211</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>579</v>
+        <v>530</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -21059,13 +20651,13 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>580</v>
+        <v>532</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>581</v>
+        <v>531</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>582</v>
+        <v>533</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
@@ -21080,42 +20672,44 @@
         <v>211</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>583</v>
+        <v>534</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A4" s="11" t="s">
-        <v>584</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>585</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>586</v>
-      </c>
-      <c r="D4" s="11" t="s">
+      <c r="A4" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>537</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="H4" s="11"/>
+      <c r="H4" s="3" t="s">
+        <v>538</v>
+      </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A5" s="3" t="s">
-        <v>587</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>588</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>589</v>
+      <c r="A5" s="8" t="s">
+        <v>539</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>540</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>541</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
@@ -21130,17 +20724,200 @@
         <v>211</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>590</v>
+        <v>542</v>
+      </c>
+    </row>
+    <row r="6" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>543</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>544</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>545</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="7" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="8" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>552</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>553</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="9" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>558</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="10" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>561</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="11" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A11" s="3" t="s">
+        <v>563</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>564</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>565</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G11" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="12" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A12" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>569</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>570</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7271F742-0542-4B33-AEE2-20AE8A69F475}">
-  <dimension ref="A1:HU3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24EB34D0-BCF8-4F57-88CC-AC842687528F}">
+  <dimension ref="A1:HU5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="52.453125" bestFit="1" customWidth="1"/>
@@ -21181,13 +20958,13 @@
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>594</v>
+        <v>576</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>595</v>
+        <v>577</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>596</v>
+        <v>578</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
@@ -21202,7 +20979,7 @@
         <v>211</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>597</v>
+        <v>579</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -21428,13 +21205,13 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>598</v>
+        <v>580</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>599</v>
+        <v>581</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>600</v>
+        <v>582</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
@@ -21449,7 +21226,57 @@
         <v>211</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>601</v>
+        <v>583</v>
+      </c>
+    </row>
+    <row r="4" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A4" s="11" t="s">
+        <v>584</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>585</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>586</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="H4" s="11"/>
+    </row>
+    <row r="5" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>587</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>588</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>589</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>590</v>
       </c>
     </row>
   </sheetData>
@@ -21458,6 +21285,325 @@
 </file>
 
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7271F742-0542-4B33-AEE2-20AE8A69F475}">
+  <dimension ref="A1:HU3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="52.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="52.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.453125" customWidth="1"/>
+    <col min="4" max="4" width="33.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="33.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.08984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="40.81640625" customWidth="1"/>
+    <col min="8" max="8" width="65.54296875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>594</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>595</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>596</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="I2"/>
+      <c r="J2"/>
+      <c r="K2"/>
+      <c r="L2"/>
+      <c r="M2"/>
+      <c r="N2"/>
+      <c r="O2"/>
+      <c r="P2"/>
+      <c r="Q2"/>
+      <c r="R2"/>
+      <c r="S2"/>
+      <c r="T2"/>
+      <c r="U2"/>
+      <c r="V2"/>
+      <c r="W2"/>
+      <c r="X2"/>
+      <c r="Y2"/>
+      <c r="Z2"/>
+      <c r="AA2"/>
+      <c r="AB2"/>
+      <c r="AC2"/>
+      <c r="AD2"/>
+      <c r="AE2"/>
+      <c r="AF2"/>
+      <c r="AG2"/>
+      <c r="AH2"/>
+      <c r="AI2"/>
+      <c r="AJ2"/>
+      <c r="AK2"/>
+      <c r="AL2"/>
+      <c r="AM2"/>
+      <c r="AN2"/>
+      <c r="AO2"/>
+      <c r="AP2"/>
+      <c r="AQ2"/>
+      <c r="AR2"/>
+      <c r="AS2"/>
+      <c r="AT2"/>
+      <c r="AU2"/>
+      <c r="AV2"/>
+      <c r="AW2"/>
+      <c r="AX2"/>
+      <c r="AY2"/>
+      <c r="AZ2"/>
+      <c r="BA2"/>
+      <c r="BB2"/>
+      <c r="BC2"/>
+      <c r="BD2"/>
+      <c r="BE2"/>
+      <c r="BF2"/>
+      <c r="BG2"/>
+      <c r="BH2"/>
+      <c r="BI2"/>
+      <c r="BJ2"/>
+      <c r="BK2"/>
+      <c r="BL2"/>
+      <c r="BM2"/>
+      <c r="BN2"/>
+      <c r="BO2"/>
+      <c r="BP2"/>
+      <c r="BQ2"/>
+      <c r="BR2"/>
+      <c r="BS2"/>
+      <c r="BT2"/>
+      <c r="BU2"/>
+      <c r="BV2"/>
+      <c r="BW2"/>
+      <c r="BX2"/>
+      <c r="BY2"/>
+      <c r="BZ2"/>
+      <c r="CA2"/>
+      <c r="CB2"/>
+      <c r="CC2"/>
+      <c r="CD2"/>
+      <c r="CE2"/>
+      <c r="CF2"/>
+      <c r="CG2"/>
+      <c r="CH2"/>
+      <c r="CI2"/>
+      <c r="CJ2"/>
+      <c r="CK2"/>
+      <c r="CL2"/>
+      <c r="CM2"/>
+      <c r="CN2"/>
+      <c r="CO2"/>
+      <c r="CP2"/>
+      <c r="CQ2"/>
+      <c r="CR2"/>
+      <c r="CS2"/>
+      <c r="CT2"/>
+      <c r="CU2"/>
+      <c r="CV2"/>
+      <c r="CW2"/>
+      <c r="CX2"/>
+      <c r="CY2"/>
+      <c r="CZ2"/>
+      <c r="DA2"/>
+      <c r="DB2"/>
+      <c r="DC2"/>
+      <c r="DD2"/>
+      <c r="DE2"/>
+      <c r="DF2"/>
+      <c r="DG2"/>
+      <c r="DH2"/>
+      <c r="DI2"/>
+      <c r="DJ2"/>
+      <c r="DK2"/>
+      <c r="DL2"/>
+      <c r="DM2"/>
+      <c r="DN2"/>
+      <c r="DO2"/>
+      <c r="DP2"/>
+      <c r="DQ2"/>
+      <c r="DR2"/>
+      <c r="DS2"/>
+      <c r="DT2"/>
+      <c r="DU2"/>
+      <c r="DV2"/>
+      <c r="DW2"/>
+      <c r="DX2"/>
+      <c r="DY2"/>
+      <c r="DZ2"/>
+      <c r="EA2"/>
+      <c r="EB2"/>
+      <c r="EC2"/>
+      <c r="ED2"/>
+      <c r="EE2"/>
+      <c r="EF2"/>
+      <c r="EG2"/>
+      <c r="EH2"/>
+      <c r="EI2"/>
+      <c r="EJ2"/>
+      <c r="EK2"/>
+      <c r="EL2"/>
+      <c r="EM2"/>
+      <c r="EN2"/>
+      <c r="EO2"/>
+      <c r="EP2"/>
+      <c r="EQ2"/>
+      <c r="ER2"/>
+      <c r="ES2"/>
+      <c r="ET2"/>
+      <c r="EU2"/>
+      <c r="EV2"/>
+      <c r="EW2"/>
+      <c r="EX2"/>
+      <c r="EY2"/>
+      <c r="EZ2"/>
+      <c r="FA2"/>
+      <c r="FB2"/>
+      <c r="FC2"/>
+      <c r="FD2"/>
+      <c r="FE2"/>
+      <c r="FF2"/>
+      <c r="FG2"/>
+      <c r="FH2"/>
+      <c r="FI2"/>
+      <c r="FJ2"/>
+      <c r="FK2"/>
+      <c r="FL2"/>
+      <c r="FM2"/>
+      <c r="FN2"/>
+      <c r="FO2"/>
+      <c r="FP2"/>
+      <c r="FQ2"/>
+      <c r="FR2"/>
+      <c r="FS2"/>
+      <c r="FT2"/>
+      <c r="FU2"/>
+      <c r="FV2"/>
+      <c r="FW2"/>
+      <c r="FX2"/>
+      <c r="FY2"/>
+      <c r="FZ2"/>
+      <c r="GA2"/>
+      <c r="GB2"/>
+      <c r="GC2"/>
+      <c r="GD2"/>
+      <c r="GE2"/>
+      <c r="GF2"/>
+      <c r="GG2"/>
+      <c r="GH2"/>
+      <c r="GI2"/>
+      <c r="GJ2"/>
+      <c r="GK2"/>
+      <c r="GL2"/>
+      <c r="GM2"/>
+      <c r="GN2"/>
+      <c r="GO2"/>
+      <c r="GP2"/>
+      <c r="GQ2"/>
+      <c r="GR2"/>
+      <c r="GS2"/>
+      <c r="GT2"/>
+      <c r="GU2"/>
+      <c r="GV2"/>
+      <c r="GW2"/>
+      <c r="GX2"/>
+      <c r="GY2"/>
+      <c r="GZ2"/>
+      <c r="HA2"/>
+      <c r="HB2"/>
+      <c r="HC2"/>
+      <c r="HD2"/>
+      <c r="HE2"/>
+      <c r="HF2"/>
+      <c r="HG2"/>
+      <c r="HH2"/>
+      <c r="HI2"/>
+      <c r="HJ2"/>
+      <c r="HK2"/>
+      <c r="HL2"/>
+      <c r="HM2"/>
+      <c r="HN2"/>
+      <c r="HO2"/>
+      <c r="HP2"/>
+      <c r="HQ2"/>
+      <c r="HR2"/>
+      <c r="HS2"/>
+      <c r="HT2"/>
+      <c r="HU2"/>
+    </row>
+    <row r="3" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>599</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>600</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>601</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{738B4CF9-CA20-4A87-AA62-B89EDC02284E}">
   <dimension ref="A1:HU5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -21499,25 +21645,25 @@
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="11" t="s">
         <v>607</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="11" t="s">
         <v>608</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="11" t="s">
         <v>609</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="11" t="s">
         <v>201</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="11" t="s">
         <v>202</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="11" t="s">
         <v>211</v>
       </c>
       <c r="H2" s="11"/>
@@ -21823,6 +21969,377 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09B1B3C7-FD6F-4E3B-8CD4-D9B4FAD90EEE}">
+  <dimension ref="A1:HU5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="50.54296875" customWidth="1"/>
+    <col min="2" max="2" width="52.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.453125" customWidth="1"/>
+    <col min="4" max="4" width="33.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="33.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.08984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="40.81640625" customWidth="1"/>
+    <col min="8" max="8" width="65.54296875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>628</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>629</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>630</v>
+      </c>
+      <c r="I2"/>
+      <c r="J2"/>
+      <c r="K2"/>
+      <c r="L2"/>
+      <c r="M2"/>
+      <c r="N2"/>
+      <c r="O2"/>
+      <c r="P2"/>
+      <c r="Q2"/>
+      <c r="R2"/>
+      <c r="S2"/>
+      <c r="T2"/>
+      <c r="U2"/>
+      <c r="V2"/>
+      <c r="W2"/>
+      <c r="X2"/>
+      <c r="Y2"/>
+      <c r="Z2"/>
+      <c r="AA2"/>
+      <c r="AB2"/>
+      <c r="AC2"/>
+      <c r="AD2"/>
+      <c r="AE2"/>
+      <c r="AF2"/>
+      <c r="AG2"/>
+      <c r="AH2"/>
+      <c r="AI2"/>
+      <c r="AJ2"/>
+      <c r="AK2"/>
+      <c r="AL2"/>
+      <c r="AM2"/>
+      <c r="AN2"/>
+      <c r="AO2"/>
+      <c r="AP2"/>
+      <c r="AQ2"/>
+      <c r="AR2"/>
+      <c r="AS2"/>
+      <c r="AT2"/>
+      <c r="AU2"/>
+      <c r="AV2"/>
+      <c r="AW2"/>
+      <c r="AX2"/>
+      <c r="AY2"/>
+      <c r="AZ2"/>
+      <c r="BA2"/>
+      <c r="BB2"/>
+      <c r="BC2"/>
+      <c r="BD2"/>
+      <c r="BE2"/>
+      <c r="BF2"/>
+      <c r="BG2"/>
+      <c r="BH2"/>
+      <c r="BI2"/>
+      <c r="BJ2"/>
+      <c r="BK2"/>
+      <c r="BL2"/>
+      <c r="BM2"/>
+      <c r="BN2"/>
+      <c r="BO2"/>
+      <c r="BP2"/>
+      <c r="BQ2"/>
+      <c r="BR2"/>
+      <c r="BS2"/>
+      <c r="BT2"/>
+      <c r="BU2"/>
+      <c r="BV2"/>
+      <c r="BW2"/>
+      <c r="BX2"/>
+      <c r="BY2"/>
+      <c r="BZ2"/>
+      <c r="CA2"/>
+      <c r="CB2"/>
+      <c r="CC2"/>
+      <c r="CD2"/>
+      <c r="CE2"/>
+      <c r="CF2"/>
+      <c r="CG2"/>
+      <c r="CH2"/>
+      <c r="CI2"/>
+      <c r="CJ2"/>
+      <c r="CK2"/>
+      <c r="CL2"/>
+      <c r="CM2"/>
+      <c r="CN2"/>
+      <c r="CO2"/>
+      <c r="CP2"/>
+      <c r="CQ2"/>
+      <c r="CR2"/>
+      <c r="CS2"/>
+      <c r="CT2"/>
+      <c r="CU2"/>
+      <c r="CV2"/>
+      <c r="CW2"/>
+      <c r="CX2"/>
+      <c r="CY2"/>
+      <c r="CZ2"/>
+      <c r="DA2"/>
+      <c r="DB2"/>
+      <c r="DC2"/>
+      <c r="DD2"/>
+      <c r="DE2"/>
+      <c r="DF2"/>
+      <c r="DG2"/>
+      <c r="DH2"/>
+      <c r="DI2"/>
+      <c r="DJ2"/>
+      <c r="DK2"/>
+      <c r="DL2"/>
+      <c r="DM2"/>
+      <c r="DN2"/>
+      <c r="DO2"/>
+      <c r="DP2"/>
+      <c r="DQ2"/>
+      <c r="DR2"/>
+      <c r="DS2"/>
+      <c r="DT2"/>
+      <c r="DU2"/>
+      <c r="DV2"/>
+      <c r="DW2"/>
+      <c r="DX2"/>
+      <c r="DY2"/>
+      <c r="DZ2"/>
+      <c r="EA2"/>
+      <c r="EB2"/>
+      <c r="EC2"/>
+      <c r="ED2"/>
+      <c r="EE2"/>
+      <c r="EF2"/>
+      <c r="EG2"/>
+      <c r="EH2"/>
+      <c r="EI2"/>
+      <c r="EJ2"/>
+      <c r="EK2"/>
+      <c r="EL2"/>
+      <c r="EM2"/>
+      <c r="EN2"/>
+      <c r="EO2"/>
+      <c r="EP2"/>
+      <c r="EQ2"/>
+      <c r="ER2"/>
+      <c r="ES2"/>
+      <c r="ET2"/>
+      <c r="EU2"/>
+      <c r="EV2"/>
+      <c r="EW2"/>
+      <c r="EX2"/>
+      <c r="EY2"/>
+      <c r="EZ2"/>
+      <c r="FA2"/>
+      <c r="FB2"/>
+      <c r="FC2"/>
+      <c r="FD2"/>
+      <c r="FE2"/>
+      <c r="FF2"/>
+      <c r="FG2"/>
+      <c r="FH2"/>
+      <c r="FI2"/>
+      <c r="FJ2"/>
+      <c r="FK2"/>
+      <c r="FL2"/>
+      <c r="FM2"/>
+      <c r="FN2"/>
+      <c r="FO2"/>
+      <c r="FP2"/>
+      <c r="FQ2"/>
+      <c r="FR2"/>
+      <c r="FS2"/>
+      <c r="FT2"/>
+      <c r="FU2"/>
+      <c r="FV2"/>
+      <c r="FW2"/>
+      <c r="FX2"/>
+      <c r="FY2"/>
+      <c r="FZ2"/>
+      <c r="GA2"/>
+      <c r="GB2"/>
+      <c r="GC2"/>
+      <c r="GD2"/>
+      <c r="GE2"/>
+      <c r="GF2"/>
+      <c r="GG2"/>
+      <c r="GH2"/>
+      <c r="GI2"/>
+      <c r="GJ2"/>
+      <c r="GK2"/>
+      <c r="GL2"/>
+      <c r="GM2"/>
+      <c r="GN2"/>
+      <c r="GO2"/>
+      <c r="GP2"/>
+      <c r="GQ2"/>
+      <c r="GR2"/>
+      <c r="GS2"/>
+      <c r="GT2"/>
+      <c r="GU2"/>
+      <c r="GV2"/>
+      <c r="GW2"/>
+      <c r="GX2"/>
+      <c r="GY2"/>
+      <c r="GZ2"/>
+      <c r="HA2"/>
+      <c r="HB2"/>
+      <c r="HC2"/>
+      <c r="HD2"/>
+      <c r="HE2"/>
+      <c r="HF2"/>
+      <c r="HG2"/>
+      <c r="HH2"/>
+      <c r="HI2"/>
+      <c r="HJ2"/>
+      <c r="HK2"/>
+      <c r="HL2"/>
+      <c r="HM2"/>
+      <c r="HN2"/>
+      <c r="HO2"/>
+      <c r="HP2"/>
+      <c r="HQ2"/>
+      <c r="HR2"/>
+      <c r="HS2"/>
+      <c r="HT2"/>
+      <c r="HU2"/>
+    </row>
+    <row r="3" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>631</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>632</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>633</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="4" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>636</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>635</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>637</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="5" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>639</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>640</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>641</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>642</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/testdata.xlsx
+++ b/testdata.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sshiwani\workspace\find-information-products-services-tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3998CDD-2D0D-4FE1-90F0-EC349A662F70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6E5EAFA-BB35-47A2-8B35-96DF87C73B5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" firstSheet="19" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" firstSheet="38" activeTab="39" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="category_phase" sheetId="1" r:id="rId1"/>
@@ -34,23 +34,25 @@
     <sheet name="UG_EPEYEarlyYearsWorkforce_list" sheetId="35" r:id="rId19"/>
     <sheet name="UG_EPEYFurtherEduWorkforce_list" sheetId="37" r:id="rId20"/>
     <sheet name="UG_EPEYHigherEduWorkforce_list" sheetId="38" r:id="rId21"/>
-    <sheet name="UGSubcategory_AdultLearner" sheetId="16" r:id="rId22"/>
-    <sheet name="UGSubcategory_CareersAdviser" sheetId="17" r:id="rId23"/>
-    <sheet name="UGSubcategory_ChildOrYoungPers" sheetId="18" r:id="rId24"/>
-    <sheet name="UGSubcategory_DfEWorkforce" sheetId="19" r:id="rId25"/>
-    <sheet name="UGSubcategory_Employer" sheetId="20" r:id="rId26"/>
-    <sheet name="UGSubcategory_LAWorkforce" sheetId="21" r:id="rId27"/>
-    <sheet name="UGSubcategory_NEETOrCareerSeek" sheetId="22" r:id="rId28"/>
-    <sheet name="UGSubcategory_ParentOrCarer" sheetId="23" r:id="rId29"/>
-    <sheet name="UGSubcateg_ProfExtUserofDfEData" sheetId="24" r:id="rId30"/>
-    <sheet name="UGSubcategory_SCWorkforce" sheetId="25" r:id="rId31"/>
-    <sheet name="UGSubcategory_SocialWorker" sheetId="27" r:id="rId32"/>
-    <sheet name="UGSubcategory_EPandEYWorkforce" sheetId="29" r:id="rId33"/>
-    <sheet name="EPEYSubcateg_AcademyTWorkforce" sheetId="31" r:id="rId34"/>
-    <sheet name="EPEYSubcateg_AltProSetWorkforce" sheetId="33" r:id="rId35"/>
-    <sheet name="EPEYSubcatg_EarlyYearsWorkforce" sheetId="34" r:id="rId36"/>
-    <sheet name="EPEYSubcatg_FurtherEduWorkforce" sheetId="36" r:id="rId37"/>
-    <sheet name="EPEYSubcatg_HigherEduWorkforce" sheetId="39" r:id="rId38"/>
+    <sheet name="UG_EPEY_SENDProfessional_list" sheetId="40" r:id="rId22"/>
+    <sheet name="UGSubcategory_AdultLearner" sheetId="16" r:id="rId23"/>
+    <sheet name="UGSubcategory_CareersAdviser" sheetId="17" r:id="rId24"/>
+    <sheet name="UGSubcategory_ChildOrYoungPers" sheetId="18" r:id="rId25"/>
+    <sheet name="UGSubcategory_DfEWorkforce" sheetId="19" r:id="rId26"/>
+    <sheet name="UGSubcategory_Employer" sheetId="20" r:id="rId27"/>
+    <sheet name="UGSubcategory_LAWorkforce" sheetId="21" r:id="rId28"/>
+    <sheet name="UGSubcategory_NEETOrCareerSeek" sheetId="22" r:id="rId29"/>
+    <sheet name="UGSubcategory_ParentOrCarer" sheetId="23" r:id="rId30"/>
+    <sheet name="UGSubcateg_ProfExtUserofDfEData" sheetId="24" r:id="rId31"/>
+    <sheet name="UGSubcategory_SCWorkforce" sheetId="25" r:id="rId32"/>
+    <sheet name="UGSubcategory_SocialWorker" sheetId="27" r:id="rId33"/>
+    <sheet name="UGSubcategory_EPandEYWorkforce" sheetId="29" r:id="rId34"/>
+    <sheet name="EPEYSubcateg_AcademyTWorkforce" sheetId="31" r:id="rId35"/>
+    <sheet name="EPEYSubcateg_AltProSetWorkforce" sheetId="33" r:id="rId36"/>
+    <sheet name="EPEYSubcatg_EarlyYearsWorkforce" sheetId="34" r:id="rId37"/>
+    <sheet name="EPEYSubcatg_FurtherEduWorkforce" sheetId="36" r:id="rId38"/>
+    <sheet name="EPEYSubcatg_HigherEduWorkforce" sheetId="39" r:id="rId39"/>
+    <sheet name="EPEYSubcateg_SENDProfessional" sheetId="41" r:id="rId40"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -62,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1362" uniqueCount="643">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1434" uniqueCount="674">
   <si>
     <t>Search and filter products and services</t>
   </si>
@@ -1991,6 +1993,99 @@
   </si>
   <si>
     <t>University support staff  (Higher education workforce)</t>
+  </si>
+  <si>
+    <t>categories/user-group/education-provider-and-early-years-workforce/send-professional</t>
+  </si>
+  <si>
+    <t>Browse products in SEND professional</t>
+  </si>
+  <si>
+    <t>ECHP coordinator</t>
+  </si>
+  <si>
+    <t>SEN coordinator</t>
+  </si>
+  <si>
+    <t>SEND speech and language therapist</t>
+  </si>
+  <si>
+    <t>SEND teacher</t>
+  </si>
+  <si>
+    <t>SEND teaching assistant</t>
+  </si>
+  <si>
+    <t>products?userGroup=send-professional</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' SEND professional ')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remove this filter SEND professional </t>
+  </si>
+  <si>
+    <t>SEND professional  (Education provider and early years workforce)</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' ECHP coordinator ')</t>
+  </si>
+  <si>
+    <t>products?userGroup=echp-coordinator</t>
+  </si>
+  <si>
+    <t>Remove this filter ECHP coordinator</t>
+  </si>
+  <si>
+    <t>ECHP coordinator  (SEND professional)</t>
+  </si>
+  <si>
+    <t>products?userGroup=sen-coordinator</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' SEN coordinator ')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remove this filter SEN coordinator </t>
+  </si>
+  <si>
+    <t>SEN coordinator  (SEND professional)</t>
+  </si>
+  <si>
+    <t>products?userGroup=send-speech-and-language-therapist</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text('  SEND speech and language therapist ')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remove this filter SEND speech and language therapist </t>
+  </si>
+  <si>
+    <t>SEND speech and language therapist  (SEND professional)</t>
+  </si>
+  <si>
+    <t>products?userGroup=send-teacher</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' SEND teacher  (SEND professional)')</t>
+  </si>
+  <si>
+    <t>Remove this filter SEND teacher  (SEND professional)</t>
+  </si>
+  <si>
+    <t>SEND teacher  (SEND professional)</t>
+  </si>
+  <si>
+    <t>products?userGroup=send-teaching-assistant</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' SEND teaching assistant ')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remove this filter SEND teaching assistant </t>
+  </si>
+  <si>
+    <t>SEND teaching assistant  (SEND professional)</t>
   </si>
 </sst>
 </file>
@@ -13107,6 +13202,101 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85AB9B63-18E3-4595-A79C-C8492E7240D1}">
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="54.1796875" customWidth="1"/>
+    <col min="2" max="2" width="47.453125" customWidth="1"/>
+    <col min="3" max="3" width="50.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>643</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B3" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B4" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>645</v>
+      </c>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>646</v>
+      </c>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>647</v>
+      </c>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>648</v>
+      </c>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB5527F7-85DB-4F8E-B4B3-EC8453E599E1}">
   <dimension ref="A1:HU6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -13504,7 +13694,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A99CF6C3-F305-48A2-AB80-2C2D7CE6460C}">
   <dimension ref="A1:HU5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -13875,7 +14065,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EFF0597-7FD1-4E6A-AA71-DB9F9FAB97A9}">
   <dimension ref="A1:HU7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -14299,7 +14489,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F4A57AC-4620-4875-88AE-9F5C739A9042}">
   <dimension ref="A1:HU6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -14696,7 +14886,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C1C130F-0899-4810-82F6-950C9CB07234}">
   <dimension ref="A1:HU5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -15067,7 +15257,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AB9395B-D522-49AD-B790-5334356249F6}">
   <dimension ref="A1:HU7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -15490,7 +15680,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEE91763-AD0C-4544-A433-3B50C88AEB79}">
   <dimension ref="A1:HU7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -15909,508 +16099,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20DD36AA-F163-4AAB-BD30-4AE6290CCAE7}">
-  <dimension ref="A1:HU10"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="50.90625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="52.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.453125" customWidth="1"/>
-    <col min="4" max="4" width="33.36328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="33.08984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.08984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="40.81640625" customWidth="1"/>
-    <col min="8" max="8" width="62.54296875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="I2"/>
-      <c r="J2"/>
-      <c r="K2"/>
-      <c r="L2"/>
-      <c r="M2"/>
-      <c r="N2"/>
-      <c r="O2"/>
-      <c r="P2"/>
-      <c r="Q2"/>
-      <c r="R2"/>
-      <c r="S2"/>
-      <c r="T2"/>
-      <c r="U2"/>
-      <c r="V2"/>
-      <c r="W2"/>
-      <c r="X2"/>
-      <c r="Y2"/>
-      <c r="Z2"/>
-      <c r="AA2"/>
-      <c r="AB2"/>
-      <c r="AC2"/>
-      <c r="AD2"/>
-      <c r="AE2"/>
-      <c r="AF2"/>
-      <c r="AG2"/>
-      <c r="AH2"/>
-      <c r="AI2"/>
-      <c r="AJ2"/>
-      <c r="AK2"/>
-      <c r="AL2"/>
-      <c r="AM2"/>
-      <c r="AN2"/>
-      <c r="AO2"/>
-      <c r="AP2"/>
-      <c r="AQ2"/>
-      <c r="AR2"/>
-      <c r="AS2"/>
-      <c r="AT2"/>
-      <c r="AU2"/>
-      <c r="AV2"/>
-      <c r="AW2"/>
-      <c r="AX2"/>
-      <c r="AY2"/>
-      <c r="AZ2"/>
-      <c r="BA2"/>
-      <c r="BB2"/>
-      <c r="BC2"/>
-      <c r="BD2"/>
-      <c r="BE2"/>
-      <c r="BF2"/>
-      <c r="BG2"/>
-      <c r="BH2"/>
-      <c r="BI2"/>
-      <c r="BJ2"/>
-      <c r="BK2"/>
-      <c r="BL2"/>
-      <c r="BM2"/>
-      <c r="BN2"/>
-      <c r="BO2"/>
-      <c r="BP2"/>
-      <c r="BQ2"/>
-      <c r="BR2"/>
-      <c r="BS2"/>
-      <c r="BT2"/>
-      <c r="BU2"/>
-      <c r="BV2"/>
-      <c r="BW2"/>
-      <c r="BX2"/>
-      <c r="BY2"/>
-      <c r="BZ2"/>
-      <c r="CA2"/>
-      <c r="CB2"/>
-      <c r="CC2"/>
-      <c r="CD2"/>
-      <c r="CE2"/>
-      <c r="CF2"/>
-      <c r="CG2"/>
-      <c r="CH2"/>
-      <c r="CI2"/>
-      <c r="CJ2"/>
-      <c r="CK2"/>
-      <c r="CL2"/>
-      <c r="CM2"/>
-      <c r="CN2"/>
-      <c r="CO2"/>
-      <c r="CP2"/>
-      <c r="CQ2"/>
-      <c r="CR2"/>
-      <c r="CS2"/>
-      <c r="CT2"/>
-      <c r="CU2"/>
-      <c r="CV2"/>
-      <c r="CW2"/>
-      <c r="CX2"/>
-      <c r="CY2"/>
-      <c r="CZ2"/>
-      <c r="DA2"/>
-      <c r="DB2"/>
-      <c r="DC2"/>
-      <c r="DD2"/>
-      <c r="DE2"/>
-      <c r="DF2"/>
-      <c r="DG2"/>
-      <c r="DH2"/>
-      <c r="DI2"/>
-      <c r="DJ2"/>
-      <c r="DK2"/>
-      <c r="DL2"/>
-      <c r="DM2"/>
-      <c r="DN2"/>
-      <c r="DO2"/>
-      <c r="DP2"/>
-      <c r="DQ2"/>
-      <c r="DR2"/>
-      <c r="DS2"/>
-      <c r="DT2"/>
-      <c r="DU2"/>
-      <c r="DV2"/>
-      <c r="DW2"/>
-      <c r="DX2"/>
-      <c r="DY2"/>
-      <c r="DZ2"/>
-      <c r="EA2"/>
-      <c r="EB2"/>
-      <c r="EC2"/>
-      <c r="ED2"/>
-      <c r="EE2"/>
-      <c r="EF2"/>
-      <c r="EG2"/>
-      <c r="EH2"/>
-      <c r="EI2"/>
-      <c r="EJ2"/>
-      <c r="EK2"/>
-      <c r="EL2"/>
-      <c r="EM2"/>
-      <c r="EN2"/>
-      <c r="EO2"/>
-      <c r="EP2"/>
-      <c r="EQ2"/>
-      <c r="ER2"/>
-      <c r="ES2"/>
-      <c r="ET2"/>
-      <c r="EU2"/>
-      <c r="EV2"/>
-      <c r="EW2"/>
-      <c r="EX2"/>
-      <c r="EY2"/>
-      <c r="EZ2"/>
-      <c r="FA2"/>
-      <c r="FB2"/>
-      <c r="FC2"/>
-      <c r="FD2"/>
-      <c r="FE2"/>
-      <c r="FF2"/>
-      <c r="FG2"/>
-      <c r="FH2"/>
-      <c r="FI2"/>
-      <c r="FJ2"/>
-      <c r="FK2"/>
-      <c r="FL2"/>
-      <c r="FM2"/>
-      <c r="FN2"/>
-      <c r="FO2"/>
-      <c r="FP2"/>
-      <c r="FQ2"/>
-      <c r="FR2"/>
-      <c r="FS2"/>
-      <c r="FT2"/>
-      <c r="FU2"/>
-      <c r="FV2"/>
-      <c r="FW2"/>
-      <c r="FX2"/>
-      <c r="FY2"/>
-      <c r="FZ2"/>
-      <c r="GA2"/>
-      <c r="GB2"/>
-      <c r="GC2"/>
-      <c r="GD2"/>
-      <c r="GE2"/>
-      <c r="GF2"/>
-      <c r="GG2"/>
-      <c r="GH2"/>
-      <c r="GI2"/>
-      <c r="GJ2"/>
-      <c r="GK2"/>
-      <c r="GL2"/>
-      <c r="GM2"/>
-      <c r="GN2"/>
-      <c r="GO2"/>
-      <c r="GP2"/>
-      <c r="GQ2"/>
-      <c r="GR2"/>
-      <c r="GS2"/>
-      <c r="GT2"/>
-      <c r="GU2"/>
-      <c r="GV2"/>
-      <c r="GW2"/>
-      <c r="GX2"/>
-      <c r="GY2"/>
-      <c r="GZ2"/>
-      <c r="HA2"/>
-      <c r="HB2"/>
-      <c r="HC2"/>
-      <c r="HD2"/>
-      <c r="HE2"/>
-      <c r="HF2"/>
-      <c r="HG2"/>
-      <c r="HH2"/>
-      <c r="HI2"/>
-      <c r="HJ2"/>
-      <c r="HK2"/>
-      <c r="HL2"/>
-      <c r="HM2"/>
-      <c r="HN2"/>
-      <c r="HO2"/>
-      <c r="HP2"/>
-      <c r="HQ2"/>
-      <c r="HR2"/>
-      <c r="HS2"/>
-      <c r="HT2"/>
-      <c r="HU2"/>
-    </row>
-    <row r="3" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="4" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="5" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A5" s="8" t="s">
-        <v>366</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>367</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>368</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="6" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A6" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="7" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A7" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>375</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="8" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A8" s="3" t="s">
-        <v>378</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>379</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="9" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A9" s="3" t="s">
-        <v>382</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>383</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>384</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="10" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A10" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>387</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>389</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -18720,8 +18408,8 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6EE6111-FDB3-4B43-8820-BBF68AAFCD6D}">
-  <dimension ref="A1:HU8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20DD36AA-F163-4AAB-BD30-4AE6290CCAE7}">
+  <dimension ref="A1:HU10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="50.90625" bestFit="1" customWidth="1"/>
@@ -18762,13 +18450,13 @@
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>390</v>
+        <v>355</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>391</v>
+        <v>356</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>392</v>
+        <v>357</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
@@ -18783,7 +18471,7 @@
         <v>211</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -19009,13 +18697,13 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>393</v>
+        <v>358</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>394</v>
+        <v>359</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>395</v>
+        <v>360</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
@@ -19030,18 +18718,18 @@
         <v>211</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>396</v>
+        <v>361</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>397</v>
+        <v>362</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>398</v>
+        <v>363</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>399</v>
+        <v>364</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
@@ -19056,18 +18744,18 @@
         <v>211</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>400</v>
+        <v>365</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
-        <v>401</v>
+        <v>366</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>402</v>
+        <v>367</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>403</v>
+        <v>368</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
@@ -19082,18 +18770,18 @@
         <v>211</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>404</v>
+        <v>369</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>405</v>
+        <v>370</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>406</v>
+        <v>371</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>407</v>
+        <v>372</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>0</v>
@@ -19108,18 +18796,18 @@
         <v>211</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>408</v>
+        <v>373</v>
       </c>
     </row>
     <row r="7" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>409</v>
+        <v>374</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>410</v>
+        <v>375</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>411</v>
+        <v>376</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>0</v>
@@ -19134,18 +18822,18 @@
         <v>211</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>412</v>
+        <v>377</v>
       </c>
     </row>
     <row r="8" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A8" s="9" t="s">
-        <v>413</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>414</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>415</v>
+      <c r="A8" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>380</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>0</v>
@@ -19159,8 +18847,60 @@
       <c r="G8" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="H8" s="9" t="s">
-        <v>416</v>
+      <c r="H8" s="3" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="9" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="10" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>389</v>
       </c>
     </row>
   </sheetData>
@@ -19170,8 +18910,8 @@
 </file>
 
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6428663-7558-48F1-8CD3-947F03FFD4CC}">
-  <dimension ref="A1:HU9"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6EE6111-FDB3-4B43-8820-BBF68AAFCD6D}">
+  <dimension ref="A1:HU8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="50.90625" bestFit="1" customWidth="1"/>
@@ -19181,7 +18921,7 @@
     <col min="5" max="5" width="33.08984375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17.08984375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="40.81640625" customWidth="1"/>
-    <col min="8" max="8" width="57.08984375" customWidth="1"/>
+    <col min="8" max="8" width="62.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:229" x14ac:dyDescent="0.35">
@@ -19212,13 +18952,13 @@
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>457</v>
+        <v>390</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>458</v>
+        <v>391</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>459</v>
+        <v>392</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
@@ -19233,7 +18973,7 @@
         <v>211</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -19459,13 +19199,13 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>460</v>
+        <v>393</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>461</v>
+        <v>394</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>462</v>
+        <v>395</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
@@ -19480,18 +19220,18 @@
         <v>211</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>463</v>
+        <v>396</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>464</v>
+        <v>397</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>467</v>
+        <v>398</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>465</v>
+        <v>399</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
@@ -19506,18 +19246,18 @@
         <v>211</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>466</v>
+        <v>400</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
-        <v>468</v>
+        <v>401</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>469</v>
+        <v>402</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>470</v>
+        <v>403</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
@@ -19532,18 +19272,18 @@
         <v>211</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>471</v>
+        <v>404</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>473</v>
+        <v>405</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>472</v>
+        <v>406</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>474</v>
+        <v>407</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>0</v>
@@ -19558,18 +19298,18 @@
         <v>211</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>475</v>
+        <v>408</v>
       </c>
     </row>
     <row r="7" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>476</v>
+        <v>409</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>477</v>
+        <v>410</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>478</v>
+        <v>411</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>0</v>
@@ -19584,18 +19324,18 @@
         <v>211</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>479</v>
+        <v>412</v>
       </c>
     </row>
     <row r="8" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A8" s="3" t="s">
-        <v>480</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>481</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>482</v>
+      <c r="A8" s="9" t="s">
+        <v>413</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>414</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>415</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>0</v>
@@ -19609,34 +19349,8 @@
       <c r="G8" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="9" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A9" s="3" t="s">
-        <v>484</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>485</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>487</v>
+      <c r="H8" s="9" t="s">
+        <v>416</v>
       </c>
     </row>
   </sheetData>
@@ -19646,8 +19360,8 @@
 </file>
 
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A4E3580-B709-4E66-9F6E-B7F9948D7FD3}">
-  <dimension ref="A1:HU7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6428663-7558-48F1-8CD3-947F03FFD4CC}">
+  <dimension ref="A1:HU9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="50.90625" bestFit="1" customWidth="1"/>
@@ -19688,13 +19402,13 @@
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>488</v>
+        <v>457</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>489</v>
+        <v>458</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>490</v>
+        <v>459</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
@@ -19709,7 +19423,7 @@
         <v>211</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>491</v>
+        <v>192</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -19935,13 +19649,13 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>492</v>
+        <v>460</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>493</v>
+        <v>461</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>494</v>
+        <v>462</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
@@ -19956,18 +19670,18 @@
         <v>211</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>495</v>
+        <v>463</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>496</v>
+        <v>464</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>497</v>
+        <v>467</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>498</v>
+        <v>465</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
@@ -19982,18 +19696,18 @@
         <v>211</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>499</v>
+        <v>466</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
-        <v>500</v>
+        <v>468</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>501</v>
+        <v>469</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>502</v>
+        <v>470</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
@@ -20008,18 +19722,18 @@
         <v>211</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>503</v>
+        <v>471</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>504</v>
+        <v>473</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>505</v>
+        <v>472</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>506</v>
+        <v>474</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>0</v>
@@ -20034,18 +19748,18 @@
         <v>211</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>507</v>
+        <v>475</v>
       </c>
     </row>
     <row r="7" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>509</v>
+        <v>476</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>508</v>
+        <v>477</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>510</v>
+        <v>478</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>0</v>
@@ -20060,17 +19774,70 @@
         <v>211</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>511</v>
+        <v>479</v>
+      </c>
+    </row>
+    <row r="8" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="9" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>487</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95706458-CD50-4C74-87C4-ABAE617927AD}">
-  <dimension ref="A1:HU2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A4E3580-B709-4E66-9F6E-B7F9948D7FD3}">
+  <dimension ref="A1:HU7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="50.90625" bestFit="1" customWidth="1"/>
@@ -20111,13 +19878,13 @@
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>512</v>
+        <v>488</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>513</v>
+        <v>489</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>514</v>
+        <v>490</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
@@ -20132,7 +19899,7 @@
         <v>211</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>140</v>
+        <v>491</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -20356,14 +20123,144 @@
       <c r="HT2"/>
       <c r="HU2"/>
     </row>
+    <row r="3" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>493</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="4" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="5" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A5" s="8" t="s">
+        <v>500</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>501</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>502</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="6" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="7" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>511</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AD86191-7CFE-4ED9-9129-FF78170AB51E}">
-  <dimension ref="A1:HU12"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95706458-CD50-4C74-87C4-ABAE617927AD}">
+  <dimension ref="A1:HU2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="50.90625" bestFit="1" customWidth="1"/>
@@ -20373,7 +20270,7 @@
     <col min="5" max="5" width="33.08984375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17.08984375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="40.81640625" customWidth="1"/>
-    <col min="8" max="8" width="65.54296875" customWidth="1"/>
+    <col min="8" max="8" width="57.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:229" x14ac:dyDescent="0.35">
@@ -20404,13 +20301,13 @@
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>527</v>
+        <v>512</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>528</v>
+        <v>513</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>529</v>
+        <v>514</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
@@ -20425,7 +20322,7 @@
         <v>211</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>530</v>
+        <v>140</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -20649,278 +20546,17 @@
       <c r="HT2"/>
       <c r="HU2"/>
     </row>
-    <row r="3" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
-        <v>532</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>531</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>533</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="4" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
-        <v>535</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>536</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>537</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="5" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A5" s="8" t="s">
-        <v>539</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>540</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>541</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="6" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A6" s="3" t="s">
-        <v>543</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>544</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>545</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="7" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A7" s="3" t="s">
-        <v>547</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>548</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>549</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="8" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A8" s="3" t="s">
-        <v>551</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>552</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>553</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G8" s="10" t="s">
-        <v>211</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="9" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A9" s="3" t="s">
-        <v>555</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>556</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>558</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G9" s="10" t="s">
-        <v>211</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="10" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A10" s="3" t="s">
-        <v>559</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>560</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>561</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G10" s="10" t="s">
-        <v>211</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="11" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A11" s="3" t="s">
-        <v>563</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>564</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>565</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G11" s="10" t="s">
-        <v>211</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="12" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A12" s="3" t="s">
-        <v>567</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>568</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>569</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G12" s="10" t="s">
-        <v>211</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>570</v>
-      </c>
-    </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24EB34D0-BCF8-4F57-88CC-AC842687528F}">
-  <dimension ref="A1:HU5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AD86191-7CFE-4ED9-9129-FF78170AB51E}">
+  <dimension ref="A1:HU12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="52.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="50.90625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="52.26953125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="42.453125" customWidth="1"/>
     <col min="4" max="4" width="33.36328125" bestFit="1" customWidth="1"/>
@@ -20958,13 +20594,13 @@
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>576</v>
+        <v>527</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>577</v>
+        <v>528</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>578</v>
+        <v>529</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
@@ -20979,7 +20615,7 @@
         <v>211</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>579</v>
+        <v>530</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -21205,13 +20841,13 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>580</v>
+        <v>532</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>581</v>
+        <v>531</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>582</v>
+        <v>533</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
@@ -21226,42 +20862,44 @@
         <v>211</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>583</v>
+        <v>534</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A4" s="11" t="s">
-        <v>584</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>585</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>586</v>
-      </c>
-      <c r="D4" s="11" t="s">
+      <c r="A4" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>537</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="H4" s="11"/>
+      <c r="H4" s="3" t="s">
+        <v>538</v>
+      </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A5" s="3" t="s">
-        <v>587</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>588</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>589</v>
+      <c r="A5" s="8" t="s">
+        <v>539</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>540</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>541</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
@@ -21276,17 +20914,200 @@
         <v>211</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>590</v>
+        <v>542</v>
+      </c>
+    </row>
+    <row r="6" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>543</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>544</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>545</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="7" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="8" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>552</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>553</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="9" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>558</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="10" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>561</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="11" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A11" s="3" t="s">
+        <v>563</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>564</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>565</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G11" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="12" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A12" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>569</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>570</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7271F742-0542-4B33-AEE2-20AE8A69F475}">
-  <dimension ref="A1:HU3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24EB34D0-BCF8-4F57-88CC-AC842687528F}">
+  <dimension ref="A1:HU5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="52.453125" bestFit="1" customWidth="1"/>
@@ -21327,13 +21148,13 @@
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>594</v>
+        <v>576</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>595</v>
+        <v>577</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>596</v>
+        <v>578</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
@@ -21348,7 +21169,7 @@
         <v>211</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>597</v>
+        <v>579</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -21574,13 +21395,13 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>598</v>
+        <v>580</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>599</v>
+        <v>581</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>600</v>
+        <v>582</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
@@ -21595,7 +21416,57 @@
         <v>211</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>601</v>
+        <v>583</v>
+      </c>
+    </row>
+    <row r="4" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A4" s="11" t="s">
+        <v>584</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>585</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>586</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="H4" s="11"/>
+    </row>
+    <row r="5" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>587</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>588</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>589</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>590</v>
       </c>
     </row>
   </sheetData>
@@ -21604,6 +21475,325 @@
 </file>
 
 <file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7271F742-0542-4B33-AEE2-20AE8A69F475}">
+  <dimension ref="A1:HU3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="52.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="52.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.453125" customWidth="1"/>
+    <col min="4" max="4" width="33.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="33.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.08984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="40.81640625" customWidth="1"/>
+    <col min="8" max="8" width="65.54296875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>594</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>595</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>596</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="I2"/>
+      <c r="J2"/>
+      <c r="K2"/>
+      <c r="L2"/>
+      <c r="M2"/>
+      <c r="N2"/>
+      <c r="O2"/>
+      <c r="P2"/>
+      <c r="Q2"/>
+      <c r="R2"/>
+      <c r="S2"/>
+      <c r="T2"/>
+      <c r="U2"/>
+      <c r="V2"/>
+      <c r="W2"/>
+      <c r="X2"/>
+      <c r="Y2"/>
+      <c r="Z2"/>
+      <c r="AA2"/>
+      <c r="AB2"/>
+      <c r="AC2"/>
+      <c r="AD2"/>
+      <c r="AE2"/>
+      <c r="AF2"/>
+      <c r="AG2"/>
+      <c r="AH2"/>
+      <c r="AI2"/>
+      <c r="AJ2"/>
+      <c r="AK2"/>
+      <c r="AL2"/>
+      <c r="AM2"/>
+      <c r="AN2"/>
+      <c r="AO2"/>
+      <c r="AP2"/>
+      <c r="AQ2"/>
+      <c r="AR2"/>
+      <c r="AS2"/>
+      <c r="AT2"/>
+      <c r="AU2"/>
+      <c r="AV2"/>
+      <c r="AW2"/>
+      <c r="AX2"/>
+      <c r="AY2"/>
+      <c r="AZ2"/>
+      <c r="BA2"/>
+      <c r="BB2"/>
+      <c r="BC2"/>
+      <c r="BD2"/>
+      <c r="BE2"/>
+      <c r="BF2"/>
+      <c r="BG2"/>
+      <c r="BH2"/>
+      <c r="BI2"/>
+      <c r="BJ2"/>
+      <c r="BK2"/>
+      <c r="BL2"/>
+      <c r="BM2"/>
+      <c r="BN2"/>
+      <c r="BO2"/>
+      <c r="BP2"/>
+      <c r="BQ2"/>
+      <c r="BR2"/>
+      <c r="BS2"/>
+      <c r="BT2"/>
+      <c r="BU2"/>
+      <c r="BV2"/>
+      <c r="BW2"/>
+      <c r="BX2"/>
+      <c r="BY2"/>
+      <c r="BZ2"/>
+      <c r="CA2"/>
+      <c r="CB2"/>
+      <c r="CC2"/>
+      <c r="CD2"/>
+      <c r="CE2"/>
+      <c r="CF2"/>
+      <c r="CG2"/>
+      <c r="CH2"/>
+      <c r="CI2"/>
+      <c r="CJ2"/>
+      <c r="CK2"/>
+      <c r="CL2"/>
+      <c r="CM2"/>
+      <c r="CN2"/>
+      <c r="CO2"/>
+      <c r="CP2"/>
+      <c r="CQ2"/>
+      <c r="CR2"/>
+      <c r="CS2"/>
+      <c r="CT2"/>
+      <c r="CU2"/>
+      <c r="CV2"/>
+      <c r="CW2"/>
+      <c r="CX2"/>
+      <c r="CY2"/>
+      <c r="CZ2"/>
+      <c r="DA2"/>
+      <c r="DB2"/>
+      <c r="DC2"/>
+      <c r="DD2"/>
+      <c r="DE2"/>
+      <c r="DF2"/>
+      <c r="DG2"/>
+      <c r="DH2"/>
+      <c r="DI2"/>
+      <c r="DJ2"/>
+      <c r="DK2"/>
+      <c r="DL2"/>
+      <c r="DM2"/>
+      <c r="DN2"/>
+      <c r="DO2"/>
+      <c r="DP2"/>
+      <c r="DQ2"/>
+      <c r="DR2"/>
+      <c r="DS2"/>
+      <c r="DT2"/>
+      <c r="DU2"/>
+      <c r="DV2"/>
+      <c r="DW2"/>
+      <c r="DX2"/>
+      <c r="DY2"/>
+      <c r="DZ2"/>
+      <c r="EA2"/>
+      <c r="EB2"/>
+      <c r="EC2"/>
+      <c r="ED2"/>
+      <c r="EE2"/>
+      <c r="EF2"/>
+      <c r="EG2"/>
+      <c r="EH2"/>
+      <c r="EI2"/>
+      <c r="EJ2"/>
+      <c r="EK2"/>
+      <c r="EL2"/>
+      <c r="EM2"/>
+      <c r="EN2"/>
+      <c r="EO2"/>
+      <c r="EP2"/>
+      <c r="EQ2"/>
+      <c r="ER2"/>
+      <c r="ES2"/>
+      <c r="ET2"/>
+      <c r="EU2"/>
+      <c r="EV2"/>
+      <c r="EW2"/>
+      <c r="EX2"/>
+      <c r="EY2"/>
+      <c r="EZ2"/>
+      <c r="FA2"/>
+      <c r="FB2"/>
+      <c r="FC2"/>
+      <c r="FD2"/>
+      <c r="FE2"/>
+      <c r="FF2"/>
+      <c r="FG2"/>
+      <c r="FH2"/>
+      <c r="FI2"/>
+      <c r="FJ2"/>
+      <c r="FK2"/>
+      <c r="FL2"/>
+      <c r="FM2"/>
+      <c r="FN2"/>
+      <c r="FO2"/>
+      <c r="FP2"/>
+      <c r="FQ2"/>
+      <c r="FR2"/>
+      <c r="FS2"/>
+      <c r="FT2"/>
+      <c r="FU2"/>
+      <c r="FV2"/>
+      <c r="FW2"/>
+      <c r="FX2"/>
+      <c r="FY2"/>
+      <c r="FZ2"/>
+      <c r="GA2"/>
+      <c r="GB2"/>
+      <c r="GC2"/>
+      <c r="GD2"/>
+      <c r="GE2"/>
+      <c r="GF2"/>
+      <c r="GG2"/>
+      <c r="GH2"/>
+      <c r="GI2"/>
+      <c r="GJ2"/>
+      <c r="GK2"/>
+      <c r="GL2"/>
+      <c r="GM2"/>
+      <c r="GN2"/>
+      <c r="GO2"/>
+      <c r="GP2"/>
+      <c r="GQ2"/>
+      <c r="GR2"/>
+      <c r="GS2"/>
+      <c r="GT2"/>
+      <c r="GU2"/>
+      <c r="GV2"/>
+      <c r="GW2"/>
+      <c r="GX2"/>
+      <c r="GY2"/>
+      <c r="GZ2"/>
+      <c r="HA2"/>
+      <c r="HB2"/>
+      <c r="HC2"/>
+      <c r="HD2"/>
+      <c r="HE2"/>
+      <c r="HF2"/>
+      <c r="HG2"/>
+      <c r="HH2"/>
+      <c r="HI2"/>
+      <c r="HJ2"/>
+      <c r="HK2"/>
+      <c r="HL2"/>
+      <c r="HM2"/>
+      <c r="HN2"/>
+      <c r="HO2"/>
+      <c r="HP2"/>
+      <c r="HQ2"/>
+      <c r="HR2"/>
+      <c r="HS2"/>
+      <c r="HT2"/>
+      <c r="HU2"/>
+    </row>
+    <row r="3" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>599</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>600</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>601</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{738B4CF9-CA20-4A87-AA62-B89EDC02284E}">
   <dimension ref="A1:HU5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -21973,7 +22163,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09B1B3C7-FD6F-4E3B-8CD4-D9B4FAD90EEE}">
   <dimension ref="A1:HU5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -23151,6 +23341,430 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23CC273B-FFDA-44C0-9F09-DBCCADFC6C49}">
+  <dimension ref="A1:HU7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="50.54296875" customWidth="1"/>
+    <col min="2" max="2" width="52.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.453125" customWidth="1"/>
+    <col min="4" max="4" width="33.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="33.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.08984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="40.81640625" customWidth="1"/>
+    <col min="8" max="8" width="65.54296875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>650</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>651</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>652</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>653</v>
+      </c>
+      <c r="I2"/>
+      <c r="J2"/>
+      <c r="K2"/>
+      <c r="L2"/>
+      <c r="M2"/>
+      <c r="N2"/>
+      <c r="O2"/>
+      <c r="P2"/>
+      <c r="Q2"/>
+      <c r="R2"/>
+      <c r="S2"/>
+      <c r="T2"/>
+      <c r="U2"/>
+      <c r="V2"/>
+      <c r="W2"/>
+      <c r="X2"/>
+      <c r="Y2"/>
+      <c r="Z2"/>
+      <c r="AA2"/>
+      <c r="AB2"/>
+      <c r="AC2"/>
+      <c r="AD2"/>
+      <c r="AE2"/>
+      <c r="AF2"/>
+      <c r="AG2"/>
+      <c r="AH2"/>
+      <c r="AI2"/>
+      <c r="AJ2"/>
+      <c r="AK2"/>
+      <c r="AL2"/>
+      <c r="AM2"/>
+      <c r="AN2"/>
+      <c r="AO2"/>
+      <c r="AP2"/>
+      <c r="AQ2"/>
+      <c r="AR2"/>
+      <c r="AS2"/>
+      <c r="AT2"/>
+      <c r="AU2"/>
+      <c r="AV2"/>
+      <c r="AW2"/>
+      <c r="AX2"/>
+      <c r="AY2"/>
+      <c r="AZ2"/>
+      <c r="BA2"/>
+      <c r="BB2"/>
+      <c r="BC2"/>
+      <c r="BD2"/>
+      <c r="BE2"/>
+      <c r="BF2"/>
+      <c r="BG2"/>
+      <c r="BH2"/>
+      <c r="BI2"/>
+      <c r="BJ2"/>
+      <c r="BK2"/>
+      <c r="BL2"/>
+      <c r="BM2"/>
+      <c r="BN2"/>
+      <c r="BO2"/>
+      <c r="BP2"/>
+      <c r="BQ2"/>
+      <c r="BR2"/>
+      <c r="BS2"/>
+      <c r="BT2"/>
+      <c r="BU2"/>
+      <c r="BV2"/>
+      <c r="BW2"/>
+      <c r="BX2"/>
+      <c r="BY2"/>
+      <c r="BZ2"/>
+      <c r="CA2"/>
+      <c r="CB2"/>
+      <c r="CC2"/>
+      <c r="CD2"/>
+      <c r="CE2"/>
+      <c r="CF2"/>
+      <c r="CG2"/>
+      <c r="CH2"/>
+      <c r="CI2"/>
+      <c r="CJ2"/>
+      <c r="CK2"/>
+      <c r="CL2"/>
+      <c r="CM2"/>
+      <c r="CN2"/>
+      <c r="CO2"/>
+      <c r="CP2"/>
+      <c r="CQ2"/>
+      <c r="CR2"/>
+      <c r="CS2"/>
+      <c r="CT2"/>
+      <c r="CU2"/>
+      <c r="CV2"/>
+      <c r="CW2"/>
+      <c r="CX2"/>
+      <c r="CY2"/>
+      <c r="CZ2"/>
+      <c r="DA2"/>
+      <c r="DB2"/>
+      <c r="DC2"/>
+      <c r="DD2"/>
+      <c r="DE2"/>
+      <c r="DF2"/>
+      <c r="DG2"/>
+      <c r="DH2"/>
+      <c r="DI2"/>
+      <c r="DJ2"/>
+      <c r="DK2"/>
+      <c r="DL2"/>
+      <c r="DM2"/>
+      <c r="DN2"/>
+      <c r="DO2"/>
+      <c r="DP2"/>
+      <c r="DQ2"/>
+      <c r="DR2"/>
+      <c r="DS2"/>
+      <c r="DT2"/>
+      <c r="DU2"/>
+      <c r="DV2"/>
+      <c r="DW2"/>
+      <c r="DX2"/>
+      <c r="DY2"/>
+      <c r="DZ2"/>
+      <c r="EA2"/>
+      <c r="EB2"/>
+      <c r="EC2"/>
+      <c r="ED2"/>
+      <c r="EE2"/>
+      <c r="EF2"/>
+      <c r="EG2"/>
+      <c r="EH2"/>
+      <c r="EI2"/>
+      <c r="EJ2"/>
+      <c r="EK2"/>
+      <c r="EL2"/>
+      <c r="EM2"/>
+      <c r="EN2"/>
+      <c r="EO2"/>
+      <c r="EP2"/>
+      <c r="EQ2"/>
+      <c r="ER2"/>
+      <c r="ES2"/>
+      <c r="ET2"/>
+      <c r="EU2"/>
+      <c r="EV2"/>
+      <c r="EW2"/>
+      <c r="EX2"/>
+      <c r="EY2"/>
+      <c r="EZ2"/>
+      <c r="FA2"/>
+      <c r="FB2"/>
+      <c r="FC2"/>
+      <c r="FD2"/>
+      <c r="FE2"/>
+      <c r="FF2"/>
+      <c r="FG2"/>
+      <c r="FH2"/>
+      <c r="FI2"/>
+      <c r="FJ2"/>
+      <c r="FK2"/>
+      <c r="FL2"/>
+      <c r="FM2"/>
+      <c r="FN2"/>
+      <c r="FO2"/>
+      <c r="FP2"/>
+      <c r="FQ2"/>
+      <c r="FR2"/>
+      <c r="FS2"/>
+      <c r="FT2"/>
+      <c r="FU2"/>
+      <c r="FV2"/>
+      <c r="FW2"/>
+      <c r="FX2"/>
+      <c r="FY2"/>
+      <c r="FZ2"/>
+      <c r="GA2"/>
+      <c r="GB2"/>
+      <c r="GC2"/>
+      <c r="GD2"/>
+      <c r="GE2"/>
+      <c r="GF2"/>
+      <c r="GG2"/>
+      <c r="GH2"/>
+      <c r="GI2"/>
+      <c r="GJ2"/>
+      <c r="GK2"/>
+      <c r="GL2"/>
+      <c r="GM2"/>
+      <c r="GN2"/>
+      <c r="GO2"/>
+      <c r="GP2"/>
+      <c r="GQ2"/>
+      <c r="GR2"/>
+      <c r="GS2"/>
+      <c r="GT2"/>
+      <c r="GU2"/>
+      <c r="GV2"/>
+      <c r="GW2"/>
+      <c r="GX2"/>
+      <c r="GY2"/>
+      <c r="GZ2"/>
+      <c r="HA2"/>
+      <c r="HB2"/>
+      <c r="HC2"/>
+      <c r="HD2"/>
+      <c r="HE2"/>
+      <c r="HF2"/>
+      <c r="HG2"/>
+      <c r="HH2"/>
+      <c r="HI2"/>
+      <c r="HJ2"/>
+      <c r="HK2"/>
+      <c r="HL2"/>
+      <c r="HM2"/>
+      <c r="HN2"/>
+      <c r="HO2"/>
+      <c r="HP2"/>
+      <c r="HQ2"/>
+      <c r="HR2"/>
+      <c r="HS2"/>
+      <c r="HT2"/>
+      <c r="HU2"/>
+    </row>
+    <row r="3" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>655</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>654</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="4" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>658</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>659</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>660</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="5" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>662</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>663</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>664</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="6" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>666</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>667</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="7" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>670</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>671</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>672</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>673</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0334D8A-9DDC-4B51-9686-8ED497406295}">
   <dimension ref="A1:C9"/>

--- a/testdata.xlsx
+++ b/testdata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sshiwani\workspace\find-information-products-services-tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6E5EAFA-BB35-47A2-8B35-96DF87C73B5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4DA9259-E008-4B65-9E20-CCBE67F2BD55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" firstSheet="38" activeTab="39" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" firstSheet="39" activeTab="41" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="category_phase" sheetId="1" r:id="rId1"/>
@@ -35,24 +35,26 @@
     <sheet name="UG_EPEYFurtherEduWorkforce_list" sheetId="37" r:id="rId20"/>
     <sheet name="UG_EPEYHigherEduWorkforce_list" sheetId="38" r:id="rId21"/>
     <sheet name="UG_EPEY_SENDProfessional_list" sheetId="40" r:id="rId22"/>
-    <sheet name="UGSubcategory_AdultLearner" sheetId="16" r:id="rId23"/>
-    <sheet name="UGSubcategory_CareersAdviser" sheetId="17" r:id="rId24"/>
-    <sheet name="UGSubcategory_ChildOrYoungPers" sheetId="18" r:id="rId25"/>
-    <sheet name="UGSubcategory_DfEWorkforce" sheetId="19" r:id="rId26"/>
-    <sheet name="UGSubcategory_Employer" sheetId="20" r:id="rId27"/>
-    <sheet name="UGSubcategory_LAWorkforce" sheetId="21" r:id="rId28"/>
-    <sheet name="UGSubcategory_NEETOrCareerSeek" sheetId="22" r:id="rId29"/>
-    <sheet name="UGSubcategory_ParentOrCarer" sheetId="23" r:id="rId30"/>
-    <sheet name="UGSubcateg_ProfExtUserofDfEData" sheetId="24" r:id="rId31"/>
-    <sheet name="UGSubcategory_SCWorkforce" sheetId="25" r:id="rId32"/>
-    <sheet name="UGSubcategory_SocialWorker" sheetId="27" r:id="rId33"/>
-    <sheet name="UGSubcategory_EPandEYWorkforce" sheetId="29" r:id="rId34"/>
-    <sheet name="EPEYSubcateg_AcademyTWorkforce" sheetId="31" r:id="rId35"/>
-    <sheet name="EPEYSubcateg_AltProSetWorkforce" sheetId="33" r:id="rId36"/>
-    <sheet name="EPEYSubcatg_EarlyYearsWorkforce" sheetId="34" r:id="rId37"/>
-    <sheet name="EPEYSubcatg_FurtherEduWorkforce" sheetId="36" r:id="rId38"/>
-    <sheet name="EPEYSubcatg_HigherEduWorkforce" sheetId="39" r:id="rId39"/>
-    <sheet name="EPEYSubcateg_SENDProfessional" sheetId="41" r:id="rId40"/>
+    <sheet name="UG_EPEY_SchoolWorkforce_list" sheetId="42" r:id="rId23"/>
+    <sheet name="UGSubcategory_AdultLearner" sheetId="16" r:id="rId24"/>
+    <sheet name="UGSubcategory_CareersAdviser" sheetId="17" r:id="rId25"/>
+    <sheet name="UGSubcategory_ChildOrYoungPers" sheetId="18" r:id="rId26"/>
+    <sheet name="UGSubcategory_DfEWorkforce" sheetId="19" r:id="rId27"/>
+    <sheet name="UGSubcategory_Employer" sheetId="20" r:id="rId28"/>
+    <sheet name="UGSubcategory_LAWorkforce" sheetId="21" r:id="rId29"/>
+    <sheet name="UGSubcategory_NEETOrCareerSeek" sheetId="22" r:id="rId30"/>
+    <sheet name="UGSubcategory_ParentOrCarer" sheetId="23" r:id="rId31"/>
+    <sheet name="UGSubcateg_ProfExtUserofDfEData" sheetId="24" r:id="rId32"/>
+    <sheet name="UGSubcategory_SCWorkforce" sheetId="25" r:id="rId33"/>
+    <sheet name="UGSubcategory_SocialWorker" sheetId="27" r:id="rId34"/>
+    <sheet name="UGSubcategory_EPandEYWorkforce" sheetId="29" r:id="rId35"/>
+    <sheet name="EPEYSubcateg_AcademyTWorkforce" sheetId="31" r:id="rId36"/>
+    <sheet name="EPEYSubcateg_AltProSetWorkforce" sheetId="33" r:id="rId37"/>
+    <sheet name="EPEYSubcatg_EarlyYearsWorkforce" sheetId="34" r:id="rId38"/>
+    <sheet name="EPEYSubcatg_FurtherEduWorkforce" sheetId="36" r:id="rId39"/>
+    <sheet name="EPEYSubcatg_HigherEduWorkforce" sheetId="39" r:id="rId40"/>
+    <sheet name="EPEYSubcateg_SENDProfessional" sheetId="41" r:id="rId41"/>
+    <sheet name="EPEYSubcateg_SchoolWorkforce" sheetId="43" r:id="rId42"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -64,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1434" uniqueCount="674">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1541" uniqueCount="724">
   <si>
     <t>Search and filter products and services</t>
   </si>
@@ -2086,6 +2088,156 @@
   </si>
   <si>
     <t>SEND teaching assistant  (SEND professional)</t>
+  </si>
+  <si>
+    <t>categories/user-group/education-provider-and-early-years-workforce/school-workforce</t>
+  </si>
+  <si>
+    <t>Browse products in School workforce</t>
+  </si>
+  <si>
+    <t>Headteacher (primary school)</t>
+  </si>
+  <si>
+    <t>Headteacher (secondary school)</t>
+  </si>
+  <si>
+    <t>Higher level teaching assistant</t>
+  </si>
+  <si>
+    <t>School business professional</t>
+  </si>
+  <si>
+    <t>School governor</t>
+  </si>
+  <si>
+    <t>School support staff</t>
+  </si>
+  <si>
+    <t>Teacher (primary school)</t>
+  </si>
+  <si>
+    <t>Teacher (secondary school)</t>
+  </si>
+  <si>
+    <t>Teaching assistant</t>
+  </si>
+  <si>
+    <t>products?userGroup=school-workforce</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' school-workforce')</t>
+  </si>
+  <si>
+    <t>Remove this filter school-workforce</t>
+  </si>
+  <si>
+    <t>products?userGroup=headteacher-primary-school</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Headteacher (primary school)  (School workforce)')</t>
+  </si>
+  <si>
+    <t>Remove this filter Headteacher (primary school)  (School workforce)</t>
+  </si>
+  <si>
+    <t>Headteacher (primary school)  (School workforce)</t>
+  </si>
+  <si>
+    <t>products?userGroup=headteacher-secondary-school</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Headteacher (secondary school)  (School workforce)')</t>
+  </si>
+  <si>
+    <t>Remove this filter Headteacher (secondary school)  (School workforce)</t>
+  </si>
+  <si>
+    <t>Headteacher (secondary school)  (School workforce)</t>
+  </si>
+  <si>
+    <t>products?userGroup=higher-level-teaching-assistant</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Higher level teaching assistant ')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remove this filter Higher level teaching assistant </t>
+  </si>
+  <si>
+    <t>Higher level teaching assistant  (School workforce)</t>
+  </si>
+  <si>
+    <t>products?userGroup=school-business-professional</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' School business professional  (School workforce)')</t>
+  </si>
+  <si>
+    <t>Remove this filter School business professional  (School workforce)</t>
+  </si>
+  <si>
+    <t>School business professional  (School workforce)</t>
+  </si>
+  <si>
+    <t>products?userGroup=school-governor</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' School governor  (School workforce)')</t>
+  </si>
+  <si>
+    <t>Remove this filter School governor  (School workforce)</t>
+  </si>
+  <si>
+    <t>School governor  (School workforce)</t>
+  </si>
+  <si>
+    <t>products?userGroup=school-support-staff</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' School support staff  (School workforce)')</t>
+  </si>
+  <si>
+    <t>Remove this filter School support staff  (School workforce)</t>
+  </si>
+  <si>
+    <t>School support staff  (School workforce)</t>
+  </si>
+  <si>
+    <t>products?userGroup=teacher-primary-school</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Teacher (primary school)  (School workforce)')</t>
+  </si>
+  <si>
+    <t>Remove this filter Teacher (primary school)  (School workforce)</t>
+  </si>
+  <si>
+    <t>Teacher (primary school)  (School workforce)</t>
+  </si>
+  <si>
+    <t>products?userGroup=teacher-secondary-school</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Teacher (secondary school)  (School workforce)')</t>
+  </si>
+  <si>
+    <t>Remove this filter Teacher (secondary school)  (School workforce)</t>
+  </si>
+  <si>
+    <t>Teacher (secondary school)  (School workforce)</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Teaching assistant ')</t>
+  </si>
+  <si>
+    <t>products?userGroup=teaching-assistant</t>
+  </si>
+  <si>
+    <t>Remove this filter Teaching assistant</t>
+  </si>
+  <si>
+    <t>Teaching assistant  (School workforce)</t>
   </si>
 </sst>
 </file>
@@ -13297,6 +13449,129 @@
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64EE4916-3635-401E-B0F2-CEC0B70B2EED}">
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="54.1796875" customWidth="1"/>
+    <col min="2" max="2" width="47.453125" customWidth="1"/>
+    <col min="3" max="3" width="50.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>674</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B3" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B4" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>676</v>
+      </c>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>677</v>
+      </c>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>678</v>
+      </c>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>679</v>
+      </c>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>680</v>
+      </c>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" s="3" t="s">
+        <v>681</v>
+      </c>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" s="3" t="s">
+        <v>682</v>
+      </c>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" s="3" t="s">
+        <v>683</v>
+      </c>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" s="3" t="s">
+        <v>684</v>
+      </c>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB5527F7-85DB-4F8E-B4B3-EC8453E599E1}">
   <dimension ref="A1:HU6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -13694,7 +13969,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A99CF6C3-F305-48A2-AB80-2C2D7CE6460C}">
   <dimension ref="A1:HU5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -14065,7 +14340,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EFF0597-7FD1-4E6A-AA71-DB9F9FAB97A9}">
   <dimension ref="A1:HU7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -14489,7 +14764,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F4A57AC-4620-4875-88AE-9F5C739A9042}">
   <dimension ref="A1:HU6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -14886,7 +15161,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C1C130F-0899-4810-82F6-950C9CB07234}">
   <dimension ref="A1:HU5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -15257,7 +15532,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AB9395B-D522-49AD-B790-5334356249F6}">
   <dimension ref="A1:HU7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -15673,429 +15948,6 @@
       </c>
       <c r="H7" s="3" t="s">
         <v>322</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEE91763-AD0C-4544-A433-3B50C88AEB79}">
-  <dimension ref="A1:HU7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="50.90625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="52.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.453125" customWidth="1"/>
-    <col min="4" max="4" width="33.36328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="33.08984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.08984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="40.81640625" customWidth="1"/>
-    <col min="8" max="8" width="62.54296875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="I2"/>
-      <c r="J2"/>
-      <c r="K2"/>
-      <c r="L2"/>
-      <c r="M2"/>
-      <c r="N2"/>
-      <c r="O2"/>
-      <c r="P2"/>
-      <c r="Q2"/>
-      <c r="R2"/>
-      <c r="S2"/>
-      <c r="T2"/>
-      <c r="U2"/>
-      <c r="V2"/>
-      <c r="W2"/>
-      <c r="X2"/>
-      <c r="Y2"/>
-      <c r="Z2"/>
-      <c r="AA2"/>
-      <c r="AB2"/>
-      <c r="AC2"/>
-      <c r="AD2"/>
-      <c r="AE2"/>
-      <c r="AF2"/>
-      <c r="AG2"/>
-      <c r="AH2"/>
-      <c r="AI2"/>
-      <c r="AJ2"/>
-      <c r="AK2"/>
-      <c r="AL2"/>
-      <c r="AM2"/>
-      <c r="AN2"/>
-      <c r="AO2"/>
-      <c r="AP2"/>
-      <c r="AQ2"/>
-      <c r="AR2"/>
-      <c r="AS2"/>
-      <c r="AT2"/>
-      <c r="AU2"/>
-      <c r="AV2"/>
-      <c r="AW2"/>
-      <c r="AX2"/>
-      <c r="AY2"/>
-      <c r="AZ2"/>
-      <c r="BA2"/>
-      <c r="BB2"/>
-      <c r="BC2"/>
-      <c r="BD2"/>
-      <c r="BE2"/>
-      <c r="BF2"/>
-      <c r="BG2"/>
-      <c r="BH2"/>
-      <c r="BI2"/>
-      <c r="BJ2"/>
-      <c r="BK2"/>
-      <c r="BL2"/>
-      <c r="BM2"/>
-      <c r="BN2"/>
-      <c r="BO2"/>
-      <c r="BP2"/>
-      <c r="BQ2"/>
-      <c r="BR2"/>
-      <c r="BS2"/>
-      <c r="BT2"/>
-      <c r="BU2"/>
-      <c r="BV2"/>
-      <c r="BW2"/>
-      <c r="BX2"/>
-      <c r="BY2"/>
-      <c r="BZ2"/>
-      <c r="CA2"/>
-      <c r="CB2"/>
-      <c r="CC2"/>
-      <c r="CD2"/>
-      <c r="CE2"/>
-      <c r="CF2"/>
-      <c r="CG2"/>
-      <c r="CH2"/>
-      <c r="CI2"/>
-      <c r="CJ2"/>
-      <c r="CK2"/>
-      <c r="CL2"/>
-      <c r="CM2"/>
-      <c r="CN2"/>
-      <c r="CO2"/>
-      <c r="CP2"/>
-      <c r="CQ2"/>
-      <c r="CR2"/>
-      <c r="CS2"/>
-      <c r="CT2"/>
-      <c r="CU2"/>
-      <c r="CV2"/>
-      <c r="CW2"/>
-      <c r="CX2"/>
-      <c r="CY2"/>
-      <c r="CZ2"/>
-      <c r="DA2"/>
-      <c r="DB2"/>
-      <c r="DC2"/>
-      <c r="DD2"/>
-      <c r="DE2"/>
-      <c r="DF2"/>
-      <c r="DG2"/>
-      <c r="DH2"/>
-      <c r="DI2"/>
-      <c r="DJ2"/>
-      <c r="DK2"/>
-      <c r="DL2"/>
-      <c r="DM2"/>
-      <c r="DN2"/>
-      <c r="DO2"/>
-      <c r="DP2"/>
-      <c r="DQ2"/>
-      <c r="DR2"/>
-      <c r="DS2"/>
-      <c r="DT2"/>
-      <c r="DU2"/>
-      <c r="DV2"/>
-      <c r="DW2"/>
-      <c r="DX2"/>
-      <c r="DY2"/>
-      <c r="DZ2"/>
-      <c r="EA2"/>
-      <c r="EB2"/>
-      <c r="EC2"/>
-      <c r="ED2"/>
-      <c r="EE2"/>
-      <c r="EF2"/>
-      <c r="EG2"/>
-      <c r="EH2"/>
-      <c r="EI2"/>
-      <c r="EJ2"/>
-      <c r="EK2"/>
-      <c r="EL2"/>
-      <c r="EM2"/>
-      <c r="EN2"/>
-      <c r="EO2"/>
-      <c r="EP2"/>
-      <c r="EQ2"/>
-      <c r="ER2"/>
-      <c r="ES2"/>
-      <c r="ET2"/>
-      <c r="EU2"/>
-      <c r="EV2"/>
-      <c r="EW2"/>
-      <c r="EX2"/>
-      <c r="EY2"/>
-      <c r="EZ2"/>
-      <c r="FA2"/>
-      <c r="FB2"/>
-      <c r="FC2"/>
-      <c r="FD2"/>
-      <c r="FE2"/>
-      <c r="FF2"/>
-      <c r="FG2"/>
-      <c r="FH2"/>
-      <c r="FI2"/>
-      <c r="FJ2"/>
-      <c r="FK2"/>
-      <c r="FL2"/>
-      <c r="FM2"/>
-      <c r="FN2"/>
-      <c r="FO2"/>
-      <c r="FP2"/>
-      <c r="FQ2"/>
-      <c r="FR2"/>
-      <c r="FS2"/>
-      <c r="FT2"/>
-      <c r="FU2"/>
-      <c r="FV2"/>
-      <c r="FW2"/>
-      <c r="FX2"/>
-      <c r="FY2"/>
-      <c r="FZ2"/>
-      <c r="GA2"/>
-      <c r="GB2"/>
-      <c r="GC2"/>
-      <c r="GD2"/>
-      <c r="GE2"/>
-      <c r="GF2"/>
-      <c r="GG2"/>
-      <c r="GH2"/>
-      <c r="GI2"/>
-      <c r="GJ2"/>
-      <c r="GK2"/>
-      <c r="GL2"/>
-      <c r="GM2"/>
-      <c r="GN2"/>
-      <c r="GO2"/>
-      <c r="GP2"/>
-      <c r="GQ2"/>
-      <c r="GR2"/>
-      <c r="GS2"/>
-      <c r="GT2"/>
-      <c r="GU2"/>
-      <c r="GV2"/>
-      <c r="GW2"/>
-      <c r="GX2"/>
-      <c r="GY2"/>
-      <c r="GZ2"/>
-      <c r="HA2"/>
-      <c r="HB2"/>
-      <c r="HC2"/>
-      <c r="HD2"/>
-      <c r="HE2"/>
-      <c r="HF2"/>
-      <c r="HG2"/>
-      <c r="HH2"/>
-      <c r="HI2"/>
-      <c r="HJ2"/>
-      <c r="HK2"/>
-      <c r="HL2"/>
-      <c r="HM2"/>
-      <c r="HN2"/>
-      <c r="HO2"/>
-      <c r="HP2"/>
-      <c r="HQ2"/>
-      <c r="HR2"/>
-      <c r="HS2"/>
-      <c r="HT2"/>
-      <c r="HU2"/>
-    </row>
-    <row r="3" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="4" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="5" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A5" s="8" t="s">
-        <v>334</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>335</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="6" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A6" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="7" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A7" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>345</v>
       </c>
     </row>
   </sheetData>
@@ -18408,8 +18260,8 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20DD36AA-F163-4AAB-BD30-4AE6290CCAE7}">
-  <dimension ref="A1:HU10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEE91763-AD0C-4544-A433-3B50C88AEB79}">
+  <dimension ref="A1:HU7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="50.90625" bestFit="1" customWidth="1"/>
@@ -18450,13 +18302,13 @@
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>355</v>
+        <v>323</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>356</v>
+        <v>324</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>357</v>
+        <v>325</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
@@ -18471,7 +18323,7 @@
         <v>211</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -18697,13 +18549,13 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>358</v>
+        <v>326</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>359</v>
+        <v>327</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>360</v>
+        <v>328</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
@@ -18718,18 +18570,18 @@
         <v>211</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>361</v>
+        <v>329</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>362</v>
+        <v>330</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>363</v>
+        <v>332</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>364</v>
+        <v>331</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
@@ -18744,18 +18596,18 @@
         <v>211</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>365</v>
+        <v>333</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
-        <v>366</v>
+        <v>334</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>367</v>
+        <v>335</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>368</v>
+        <v>336</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
@@ -18770,18 +18622,18 @@
         <v>211</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>369</v>
+        <v>337</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>370</v>
+        <v>338</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>371</v>
+        <v>340</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>372</v>
+        <v>339</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>0</v>
@@ -18796,18 +18648,18 @@
         <v>211</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>373</v>
+        <v>341</v>
       </c>
     </row>
     <row r="7" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>374</v>
+        <v>342</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>375</v>
+        <v>343</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>376</v>
+        <v>344</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>0</v>
@@ -18822,96 +18674,17 @@
         <v>211</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="8" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A8" s="3" t="s">
-        <v>378</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>379</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="9" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A9" s="3" t="s">
-        <v>382</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>383</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>384</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="10" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A10" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>387</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>389</v>
+        <v>345</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6EE6111-FDB3-4B43-8820-BBF68AAFCD6D}">
-  <dimension ref="A1:HU8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20DD36AA-F163-4AAB-BD30-4AE6290CCAE7}">
+  <dimension ref="A1:HU10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="50.90625" bestFit="1" customWidth="1"/>
@@ -18952,13 +18725,13 @@
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>390</v>
+        <v>355</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>391</v>
+        <v>356</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>392</v>
+        <v>357</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
@@ -18973,7 +18746,7 @@
         <v>211</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -19199,13 +18972,13 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>393</v>
+        <v>358</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>394</v>
+        <v>359</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>395</v>
+        <v>360</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
@@ -19220,18 +18993,18 @@
         <v>211</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>396</v>
+        <v>361</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>397</v>
+        <v>362</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>398</v>
+        <v>363</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>399</v>
+        <v>364</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
@@ -19246,18 +19019,18 @@
         <v>211</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>400</v>
+        <v>365</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
-        <v>401</v>
+        <v>366</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>402</v>
+        <v>367</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>403</v>
+        <v>368</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
@@ -19272,18 +19045,18 @@
         <v>211</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>404</v>
+        <v>369</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>405</v>
+        <v>370</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>406</v>
+        <v>371</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>407</v>
+        <v>372</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>0</v>
@@ -19298,18 +19071,18 @@
         <v>211</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>408</v>
+        <v>373</v>
       </c>
     </row>
     <row r="7" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>409</v>
+        <v>374</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>410</v>
+        <v>375</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>411</v>
+        <v>376</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>0</v>
@@ -19324,18 +19097,18 @@
         <v>211</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>412</v>
+        <v>377</v>
       </c>
     </row>
     <row r="8" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A8" s="9" t="s">
-        <v>413</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>414</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>415</v>
+      <c r="A8" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>380</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>0</v>
@@ -19349,8 +19122,60 @@
       <c r="G8" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="H8" s="9" t="s">
-        <v>416</v>
+      <c r="H8" s="3" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="9" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="10" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>389</v>
       </c>
     </row>
   </sheetData>
@@ -19360,8 +19185,8 @@
 </file>
 
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6428663-7558-48F1-8CD3-947F03FFD4CC}">
-  <dimension ref="A1:HU9"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6EE6111-FDB3-4B43-8820-BBF68AAFCD6D}">
+  <dimension ref="A1:HU8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="50.90625" bestFit="1" customWidth="1"/>
@@ -19371,7 +19196,7 @@
     <col min="5" max="5" width="33.08984375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17.08984375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="40.81640625" customWidth="1"/>
-    <col min="8" max="8" width="57.08984375" customWidth="1"/>
+    <col min="8" max="8" width="62.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:229" x14ac:dyDescent="0.35">
@@ -19402,13 +19227,13 @@
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>457</v>
+        <v>390</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>458</v>
+        <v>391</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>459</v>
+        <v>392</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
@@ -19423,7 +19248,7 @@
         <v>211</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -19649,13 +19474,13 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>460</v>
+        <v>393</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>461</v>
+        <v>394</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>462</v>
+        <v>395</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
@@ -19670,18 +19495,18 @@
         <v>211</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>463</v>
+        <v>396</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>464</v>
+        <v>397</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>467</v>
+        <v>398</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>465</v>
+        <v>399</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
@@ -19696,18 +19521,18 @@
         <v>211</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>466</v>
+        <v>400</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
-        <v>468</v>
+        <v>401</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>469</v>
+        <v>402</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>470</v>
+        <v>403</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
@@ -19722,18 +19547,18 @@
         <v>211</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>471</v>
+        <v>404</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>473</v>
+        <v>405</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>472</v>
+        <v>406</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>474</v>
+        <v>407</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>0</v>
@@ -19748,18 +19573,18 @@
         <v>211</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>475</v>
+        <v>408</v>
       </c>
     </row>
     <row r="7" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>476</v>
+        <v>409</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>477</v>
+        <v>410</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>478</v>
+        <v>411</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>0</v>
@@ -19774,18 +19599,18 @@
         <v>211</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>479</v>
+        <v>412</v>
       </c>
     </row>
     <row r="8" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A8" s="3" t="s">
-        <v>480</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>481</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>482</v>
+      <c r="A8" s="9" t="s">
+        <v>413</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>414</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>415</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>0</v>
@@ -19799,34 +19624,8 @@
       <c r="G8" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="9" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A9" s="3" t="s">
-        <v>484</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>485</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>487</v>
+      <c r="H8" s="9" t="s">
+        <v>416</v>
       </c>
     </row>
   </sheetData>
@@ -19836,8 +19635,8 @@
 </file>
 
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A4E3580-B709-4E66-9F6E-B7F9948D7FD3}">
-  <dimension ref="A1:HU7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6428663-7558-48F1-8CD3-947F03FFD4CC}">
+  <dimension ref="A1:HU9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="50.90625" bestFit="1" customWidth="1"/>
@@ -19878,13 +19677,13 @@
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>488</v>
+        <v>457</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>489</v>
+        <v>458</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>490</v>
+        <v>459</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
@@ -19899,7 +19698,7 @@
         <v>211</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>491</v>
+        <v>192</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -20125,13 +19924,13 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>492</v>
+        <v>460</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>493</v>
+        <v>461</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>494</v>
+        <v>462</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
@@ -20146,18 +19945,18 @@
         <v>211</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>495</v>
+        <v>463</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>496</v>
+        <v>464</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>497</v>
+        <v>467</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>498</v>
+        <v>465</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
@@ -20172,18 +19971,18 @@
         <v>211</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>499</v>
+        <v>466</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
-        <v>500</v>
+        <v>468</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>501</v>
+        <v>469</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>502</v>
+        <v>470</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
@@ -20198,18 +19997,18 @@
         <v>211</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>503</v>
+        <v>471</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>504</v>
+        <v>473</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>505</v>
+        <v>472</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>506</v>
+        <v>474</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>0</v>
@@ -20224,18 +20023,18 @@
         <v>211</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>507</v>
+        <v>475</v>
       </c>
     </row>
     <row r="7" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>509</v>
+        <v>476</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>508</v>
+        <v>477</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>510</v>
+        <v>478</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>0</v>
@@ -20250,17 +20049,70 @@
         <v>211</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>511</v>
+        <v>479</v>
+      </c>
+    </row>
+    <row r="8" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="9" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>487</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95706458-CD50-4C74-87C4-ABAE617927AD}">
-  <dimension ref="A1:HU2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A4E3580-B709-4E66-9F6E-B7F9948D7FD3}">
+  <dimension ref="A1:HU7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="50.90625" bestFit="1" customWidth="1"/>
@@ -20301,13 +20153,13 @@
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>512</v>
+        <v>488</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>513</v>
+        <v>489</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>514</v>
+        <v>490</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
@@ -20322,7 +20174,7 @@
         <v>211</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>140</v>
+        <v>491</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -20546,14 +20398,144 @@
       <c r="HT2"/>
       <c r="HU2"/>
     </row>
+    <row r="3" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>493</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="4" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="5" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A5" s="8" t="s">
+        <v>500</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>501</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>502</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="6" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="7" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>511</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AD86191-7CFE-4ED9-9129-FF78170AB51E}">
-  <dimension ref="A1:HU12"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95706458-CD50-4C74-87C4-ABAE617927AD}">
+  <dimension ref="A1:HU2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="50.90625" bestFit="1" customWidth="1"/>
@@ -20563,7 +20545,7 @@
     <col min="5" max="5" width="33.08984375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17.08984375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="40.81640625" customWidth="1"/>
-    <col min="8" max="8" width="65.54296875" customWidth="1"/>
+    <col min="8" max="8" width="57.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:229" x14ac:dyDescent="0.35">
@@ -20594,13 +20576,13 @@
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>527</v>
+        <v>512</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>528</v>
+        <v>513</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>529</v>
+        <v>514</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
@@ -20615,7 +20597,7 @@
         <v>211</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>530</v>
+        <v>140</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -20839,278 +20821,17 @@
       <c r="HT2"/>
       <c r="HU2"/>
     </row>
-    <row r="3" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
-        <v>532</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>531</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>533</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="4" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
-        <v>535</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>536</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>537</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="5" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A5" s="8" t="s">
-        <v>539</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>540</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>541</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="6" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A6" s="3" t="s">
-        <v>543</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>544</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>545</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="7" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A7" s="3" t="s">
-        <v>547</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>548</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>549</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="8" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A8" s="3" t="s">
-        <v>551</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>552</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>553</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G8" s="10" t="s">
-        <v>211</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="9" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A9" s="3" t="s">
-        <v>555</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>556</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>558</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G9" s="10" t="s">
-        <v>211</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="10" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A10" s="3" t="s">
-        <v>559</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>560</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>561</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G10" s="10" t="s">
-        <v>211</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="11" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A11" s="3" t="s">
-        <v>563</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>564</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>565</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G11" s="10" t="s">
-        <v>211</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="12" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A12" s="3" t="s">
-        <v>567</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>568</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>569</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G12" s="10" t="s">
-        <v>211</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>570</v>
-      </c>
-    </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24EB34D0-BCF8-4F57-88CC-AC842687528F}">
-  <dimension ref="A1:HU5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AD86191-7CFE-4ED9-9129-FF78170AB51E}">
+  <dimension ref="A1:HU12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="52.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="50.90625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="52.26953125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="42.453125" customWidth="1"/>
     <col min="4" max="4" width="33.36328125" bestFit="1" customWidth="1"/>
@@ -21148,13 +20869,13 @@
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>576</v>
+        <v>527</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>577</v>
+        <v>528</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>578</v>
+        <v>529</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
@@ -21169,7 +20890,7 @@
         <v>211</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>579</v>
+        <v>530</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -21395,13 +21116,13 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>580</v>
+        <v>532</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>581</v>
+        <v>531</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>582</v>
+        <v>533</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
@@ -21416,42 +21137,44 @@
         <v>211</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>583</v>
+        <v>534</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A4" s="11" t="s">
-        <v>584</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>585</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>586</v>
-      </c>
-      <c r="D4" s="11" t="s">
+      <c r="A4" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>537</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="H4" s="11"/>
+      <c r="H4" s="3" t="s">
+        <v>538</v>
+      </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A5" s="3" t="s">
-        <v>587</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>588</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>589</v>
+      <c r="A5" s="8" t="s">
+        <v>539</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>540</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>541</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
@@ -21466,17 +21189,200 @@
         <v>211</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>590</v>
+        <v>542</v>
+      </c>
+    </row>
+    <row r="6" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>543</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>544</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>545</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="7" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="8" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>552</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>553</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="9" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>558</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="10" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>561</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="11" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A11" s="3" t="s">
+        <v>563</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>564</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>565</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G11" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="12" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A12" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>569</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>570</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7271F742-0542-4B33-AEE2-20AE8A69F475}">
-  <dimension ref="A1:HU3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24EB34D0-BCF8-4F57-88CC-AC842687528F}">
+  <dimension ref="A1:HU5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="52.453125" bestFit="1" customWidth="1"/>
@@ -21517,13 +21423,13 @@
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>594</v>
+        <v>576</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>595</v>
+        <v>577</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>596</v>
+        <v>578</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
@@ -21538,7 +21444,7 @@
         <v>211</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>597</v>
+        <v>579</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -21764,13 +21670,13 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>598</v>
+        <v>580</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>599</v>
+        <v>581</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>600</v>
+        <v>582</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
@@ -21785,7 +21691,57 @@
         <v>211</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>601</v>
+        <v>583</v>
+      </c>
+    </row>
+    <row r="4" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A4" s="11" t="s">
+        <v>584</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>585</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>586</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="H4" s="11"/>
+    </row>
+    <row r="5" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>587</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>588</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>589</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>590</v>
       </c>
     </row>
   </sheetData>
@@ -21794,6 +21750,325 @@
 </file>
 
 <file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7271F742-0542-4B33-AEE2-20AE8A69F475}">
+  <dimension ref="A1:HU3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="52.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="52.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.453125" customWidth="1"/>
+    <col min="4" max="4" width="33.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="33.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.08984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="40.81640625" customWidth="1"/>
+    <col min="8" max="8" width="65.54296875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>594</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>595</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>596</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="I2"/>
+      <c r="J2"/>
+      <c r="K2"/>
+      <c r="L2"/>
+      <c r="M2"/>
+      <c r="N2"/>
+      <c r="O2"/>
+      <c r="P2"/>
+      <c r="Q2"/>
+      <c r="R2"/>
+      <c r="S2"/>
+      <c r="T2"/>
+      <c r="U2"/>
+      <c r="V2"/>
+      <c r="W2"/>
+      <c r="X2"/>
+      <c r="Y2"/>
+      <c r="Z2"/>
+      <c r="AA2"/>
+      <c r="AB2"/>
+      <c r="AC2"/>
+      <c r="AD2"/>
+      <c r="AE2"/>
+      <c r="AF2"/>
+      <c r="AG2"/>
+      <c r="AH2"/>
+      <c r="AI2"/>
+      <c r="AJ2"/>
+      <c r="AK2"/>
+      <c r="AL2"/>
+      <c r="AM2"/>
+      <c r="AN2"/>
+      <c r="AO2"/>
+      <c r="AP2"/>
+      <c r="AQ2"/>
+      <c r="AR2"/>
+      <c r="AS2"/>
+      <c r="AT2"/>
+      <c r="AU2"/>
+      <c r="AV2"/>
+      <c r="AW2"/>
+      <c r="AX2"/>
+      <c r="AY2"/>
+      <c r="AZ2"/>
+      <c r="BA2"/>
+      <c r="BB2"/>
+      <c r="BC2"/>
+      <c r="BD2"/>
+      <c r="BE2"/>
+      <c r="BF2"/>
+      <c r="BG2"/>
+      <c r="BH2"/>
+      <c r="BI2"/>
+      <c r="BJ2"/>
+      <c r="BK2"/>
+      <c r="BL2"/>
+      <c r="BM2"/>
+      <c r="BN2"/>
+      <c r="BO2"/>
+      <c r="BP2"/>
+      <c r="BQ2"/>
+      <c r="BR2"/>
+      <c r="BS2"/>
+      <c r="BT2"/>
+      <c r="BU2"/>
+      <c r="BV2"/>
+      <c r="BW2"/>
+      <c r="BX2"/>
+      <c r="BY2"/>
+      <c r="BZ2"/>
+      <c r="CA2"/>
+      <c r="CB2"/>
+      <c r="CC2"/>
+      <c r="CD2"/>
+      <c r="CE2"/>
+      <c r="CF2"/>
+      <c r="CG2"/>
+      <c r="CH2"/>
+      <c r="CI2"/>
+      <c r="CJ2"/>
+      <c r="CK2"/>
+      <c r="CL2"/>
+      <c r="CM2"/>
+      <c r="CN2"/>
+      <c r="CO2"/>
+      <c r="CP2"/>
+      <c r="CQ2"/>
+      <c r="CR2"/>
+      <c r="CS2"/>
+      <c r="CT2"/>
+      <c r="CU2"/>
+      <c r="CV2"/>
+      <c r="CW2"/>
+      <c r="CX2"/>
+      <c r="CY2"/>
+      <c r="CZ2"/>
+      <c r="DA2"/>
+      <c r="DB2"/>
+      <c r="DC2"/>
+      <c r="DD2"/>
+      <c r="DE2"/>
+      <c r="DF2"/>
+      <c r="DG2"/>
+      <c r="DH2"/>
+      <c r="DI2"/>
+      <c r="DJ2"/>
+      <c r="DK2"/>
+      <c r="DL2"/>
+      <c r="DM2"/>
+      <c r="DN2"/>
+      <c r="DO2"/>
+      <c r="DP2"/>
+      <c r="DQ2"/>
+      <c r="DR2"/>
+      <c r="DS2"/>
+      <c r="DT2"/>
+      <c r="DU2"/>
+      <c r="DV2"/>
+      <c r="DW2"/>
+      <c r="DX2"/>
+      <c r="DY2"/>
+      <c r="DZ2"/>
+      <c r="EA2"/>
+      <c r="EB2"/>
+      <c r="EC2"/>
+      <c r="ED2"/>
+      <c r="EE2"/>
+      <c r="EF2"/>
+      <c r="EG2"/>
+      <c r="EH2"/>
+      <c r="EI2"/>
+      <c r="EJ2"/>
+      <c r="EK2"/>
+      <c r="EL2"/>
+      <c r="EM2"/>
+      <c r="EN2"/>
+      <c r="EO2"/>
+      <c r="EP2"/>
+      <c r="EQ2"/>
+      <c r="ER2"/>
+      <c r="ES2"/>
+      <c r="ET2"/>
+      <c r="EU2"/>
+      <c r="EV2"/>
+      <c r="EW2"/>
+      <c r="EX2"/>
+      <c r="EY2"/>
+      <c r="EZ2"/>
+      <c r="FA2"/>
+      <c r="FB2"/>
+      <c r="FC2"/>
+      <c r="FD2"/>
+      <c r="FE2"/>
+      <c r="FF2"/>
+      <c r="FG2"/>
+      <c r="FH2"/>
+      <c r="FI2"/>
+      <c r="FJ2"/>
+      <c r="FK2"/>
+      <c r="FL2"/>
+      <c r="FM2"/>
+      <c r="FN2"/>
+      <c r="FO2"/>
+      <c r="FP2"/>
+      <c r="FQ2"/>
+      <c r="FR2"/>
+      <c r="FS2"/>
+      <c r="FT2"/>
+      <c r="FU2"/>
+      <c r="FV2"/>
+      <c r="FW2"/>
+      <c r="FX2"/>
+      <c r="FY2"/>
+      <c r="FZ2"/>
+      <c r="GA2"/>
+      <c r="GB2"/>
+      <c r="GC2"/>
+      <c r="GD2"/>
+      <c r="GE2"/>
+      <c r="GF2"/>
+      <c r="GG2"/>
+      <c r="GH2"/>
+      <c r="GI2"/>
+      <c r="GJ2"/>
+      <c r="GK2"/>
+      <c r="GL2"/>
+      <c r="GM2"/>
+      <c r="GN2"/>
+      <c r="GO2"/>
+      <c r="GP2"/>
+      <c r="GQ2"/>
+      <c r="GR2"/>
+      <c r="GS2"/>
+      <c r="GT2"/>
+      <c r="GU2"/>
+      <c r="GV2"/>
+      <c r="GW2"/>
+      <c r="GX2"/>
+      <c r="GY2"/>
+      <c r="GZ2"/>
+      <c r="HA2"/>
+      <c r="HB2"/>
+      <c r="HC2"/>
+      <c r="HD2"/>
+      <c r="HE2"/>
+      <c r="HF2"/>
+      <c r="HG2"/>
+      <c r="HH2"/>
+      <c r="HI2"/>
+      <c r="HJ2"/>
+      <c r="HK2"/>
+      <c r="HL2"/>
+      <c r="HM2"/>
+      <c r="HN2"/>
+      <c r="HO2"/>
+      <c r="HP2"/>
+      <c r="HQ2"/>
+      <c r="HR2"/>
+      <c r="HS2"/>
+      <c r="HT2"/>
+      <c r="HU2"/>
+    </row>
+    <row r="3" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>599</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>600</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>601</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{738B4CF9-CA20-4A87-AA62-B89EDC02284E}">
   <dimension ref="A1:HU5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -22159,377 +22434,6 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09B1B3C7-FD6F-4E3B-8CD4-D9B4FAD90EEE}">
-  <dimension ref="A1:HU5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="50.54296875" customWidth="1"/>
-    <col min="2" max="2" width="52.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.453125" customWidth="1"/>
-    <col min="4" max="4" width="33.36328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="33.08984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.08984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="40.81640625" customWidth="1"/>
-    <col min="8" max="8" width="65.54296875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
-        <v>627</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>628</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>629</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>630</v>
-      </c>
-      <c r="I2"/>
-      <c r="J2"/>
-      <c r="K2"/>
-      <c r="L2"/>
-      <c r="M2"/>
-      <c r="N2"/>
-      <c r="O2"/>
-      <c r="P2"/>
-      <c r="Q2"/>
-      <c r="R2"/>
-      <c r="S2"/>
-      <c r="T2"/>
-      <c r="U2"/>
-      <c r="V2"/>
-      <c r="W2"/>
-      <c r="X2"/>
-      <c r="Y2"/>
-      <c r="Z2"/>
-      <c r="AA2"/>
-      <c r="AB2"/>
-      <c r="AC2"/>
-      <c r="AD2"/>
-      <c r="AE2"/>
-      <c r="AF2"/>
-      <c r="AG2"/>
-      <c r="AH2"/>
-      <c r="AI2"/>
-      <c r="AJ2"/>
-      <c r="AK2"/>
-      <c r="AL2"/>
-      <c r="AM2"/>
-      <c r="AN2"/>
-      <c r="AO2"/>
-      <c r="AP2"/>
-      <c r="AQ2"/>
-      <c r="AR2"/>
-      <c r="AS2"/>
-      <c r="AT2"/>
-      <c r="AU2"/>
-      <c r="AV2"/>
-      <c r="AW2"/>
-      <c r="AX2"/>
-      <c r="AY2"/>
-      <c r="AZ2"/>
-      <c r="BA2"/>
-      <c r="BB2"/>
-      <c r="BC2"/>
-      <c r="BD2"/>
-      <c r="BE2"/>
-      <c r="BF2"/>
-      <c r="BG2"/>
-      <c r="BH2"/>
-      <c r="BI2"/>
-      <c r="BJ2"/>
-      <c r="BK2"/>
-      <c r="BL2"/>
-      <c r="BM2"/>
-      <c r="BN2"/>
-      <c r="BO2"/>
-      <c r="BP2"/>
-      <c r="BQ2"/>
-      <c r="BR2"/>
-      <c r="BS2"/>
-      <c r="BT2"/>
-      <c r="BU2"/>
-      <c r="BV2"/>
-      <c r="BW2"/>
-      <c r="BX2"/>
-      <c r="BY2"/>
-      <c r="BZ2"/>
-      <c r="CA2"/>
-      <c r="CB2"/>
-      <c r="CC2"/>
-      <c r="CD2"/>
-      <c r="CE2"/>
-      <c r="CF2"/>
-      <c r="CG2"/>
-      <c r="CH2"/>
-      <c r="CI2"/>
-      <c r="CJ2"/>
-      <c r="CK2"/>
-      <c r="CL2"/>
-      <c r="CM2"/>
-      <c r="CN2"/>
-      <c r="CO2"/>
-      <c r="CP2"/>
-      <c r="CQ2"/>
-      <c r="CR2"/>
-      <c r="CS2"/>
-      <c r="CT2"/>
-      <c r="CU2"/>
-      <c r="CV2"/>
-      <c r="CW2"/>
-      <c r="CX2"/>
-      <c r="CY2"/>
-      <c r="CZ2"/>
-      <c r="DA2"/>
-      <c r="DB2"/>
-      <c r="DC2"/>
-      <c r="DD2"/>
-      <c r="DE2"/>
-      <c r="DF2"/>
-      <c r="DG2"/>
-      <c r="DH2"/>
-      <c r="DI2"/>
-      <c r="DJ2"/>
-      <c r="DK2"/>
-      <c r="DL2"/>
-      <c r="DM2"/>
-      <c r="DN2"/>
-      <c r="DO2"/>
-      <c r="DP2"/>
-      <c r="DQ2"/>
-      <c r="DR2"/>
-      <c r="DS2"/>
-      <c r="DT2"/>
-      <c r="DU2"/>
-      <c r="DV2"/>
-      <c r="DW2"/>
-      <c r="DX2"/>
-      <c r="DY2"/>
-      <c r="DZ2"/>
-      <c r="EA2"/>
-      <c r="EB2"/>
-      <c r="EC2"/>
-      <c r="ED2"/>
-      <c r="EE2"/>
-      <c r="EF2"/>
-      <c r="EG2"/>
-      <c r="EH2"/>
-      <c r="EI2"/>
-      <c r="EJ2"/>
-      <c r="EK2"/>
-      <c r="EL2"/>
-      <c r="EM2"/>
-      <c r="EN2"/>
-      <c r="EO2"/>
-      <c r="EP2"/>
-      <c r="EQ2"/>
-      <c r="ER2"/>
-      <c r="ES2"/>
-      <c r="ET2"/>
-      <c r="EU2"/>
-      <c r="EV2"/>
-      <c r="EW2"/>
-      <c r="EX2"/>
-      <c r="EY2"/>
-      <c r="EZ2"/>
-      <c r="FA2"/>
-      <c r="FB2"/>
-      <c r="FC2"/>
-      <c r="FD2"/>
-      <c r="FE2"/>
-      <c r="FF2"/>
-      <c r="FG2"/>
-      <c r="FH2"/>
-      <c r="FI2"/>
-      <c r="FJ2"/>
-      <c r="FK2"/>
-      <c r="FL2"/>
-      <c r="FM2"/>
-      <c r="FN2"/>
-      <c r="FO2"/>
-      <c r="FP2"/>
-      <c r="FQ2"/>
-      <c r="FR2"/>
-      <c r="FS2"/>
-      <c r="FT2"/>
-      <c r="FU2"/>
-      <c r="FV2"/>
-      <c r="FW2"/>
-      <c r="FX2"/>
-      <c r="FY2"/>
-      <c r="FZ2"/>
-      <c r="GA2"/>
-      <c r="GB2"/>
-      <c r="GC2"/>
-      <c r="GD2"/>
-      <c r="GE2"/>
-      <c r="GF2"/>
-      <c r="GG2"/>
-      <c r="GH2"/>
-      <c r="GI2"/>
-      <c r="GJ2"/>
-      <c r="GK2"/>
-      <c r="GL2"/>
-      <c r="GM2"/>
-      <c r="GN2"/>
-      <c r="GO2"/>
-      <c r="GP2"/>
-      <c r="GQ2"/>
-      <c r="GR2"/>
-      <c r="GS2"/>
-      <c r="GT2"/>
-      <c r="GU2"/>
-      <c r="GV2"/>
-      <c r="GW2"/>
-      <c r="GX2"/>
-      <c r="GY2"/>
-      <c r="GZ2"/>
-      <c r="HA2"/>
-      <c r="HB2"/>
-      <c r="HC2"/>
-      <c r="HD2"/>
-      <c r="HE2"/>
-      <c r="HF2"/>
-      <c r="HG2"/>
-      <c r="HH2"/>
-      <c r="HI2"/>
-      <c r="HJ2"/>
-      <c r="HK2"/>
-      <c r="HL2"/>
-      <c r="HM2"/>
-      <c r="HN2"/>
-      <c r="HO2"/>
-      <c r="HP2"/>
-      <c r="HQ2"/>
-      <c r="HR2"/>
-      <c r="HS2"/>
-      <c r="HT2"/>
-      <c r="HU2"/>
-    </row>
-    <row r="3" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
-        <v>631</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>632</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>633</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="4" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
-        <v>636</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>635</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>637</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="5" spans="1:229" x14ac:dyDescent="0.35">
-      <c r="A5" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>640</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>641</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>642</v>
-      </c>
-    </row>
-  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -23342,8 +23246,8 @@
 </file>
 
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23CC273B-FFDA-44C0-9F09-DBCCADFC6C49}">
-  <dimension ref="A1:HU7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09B1B3C7-FD6F-4E3B-8CD4-D9B4FAD90EEE}">
+  <dimension ref="A1:HU5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="50.54296875" customWidth="1"/>
@@ -23384,13 +23288,13 @@
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>650</v>
+        <v>627</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>651</v>
+        <v>628</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>652</v>
+        <v>629</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
@@ -23405,7 +23309,7 @@
         <v>211</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>653</v>
+        <v>630</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -23631,6 +23535,377 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
+        <v>631</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>632</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>633</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="4" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>636</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>635</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>637</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="5" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>639</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>640</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>641</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>642</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23CC273B-FFDA-44C0-9F09-DBCCADFC6C49}">
+  <dimension ref="A1:HU7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="50.54296875" customWidth="1"/>
+    <col min="2" max="2" width="52.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.453125" customWidth="1"/>
+    <col min="4" max="4" width="33.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="33.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.08984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="40.81640625" customWidth="1"/>
+    <col min="8" max="8" width="65.54296875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>650</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>651</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>652</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>653</v>
+      </c>
+      <c r="I2"/>
+      <c r="J2"/>
+      <c r="K2"/>
+      <c r="L2"/>
+      <c r="M2"/>
+      <c r="N2"/>
+      <c r="O2"/>
+      <c r="P2"/>
+      <c r="Q2"/>
+      <c r="R2"/>
+      <c r="S2"/>
+      <c r="T2"/>
+      <c r="U2"/>
+      <c r="V2"/>
+      <c r="W2"/>
+      <c r="X2"/>
+      <c r="Y2"/>
+      <c r="Z2"/>
+      <c r="AA2"/>
+      <c r="AB2"/>
+      <c r="AC2"/>
+      <c r="AD2"/>
+      <c r="AE2"/>
+      <c r="AF2"/>
+      <c r="AG2"/>
+      <c r="AH2"/>
+      <c r="AI2"/>
+      <c r="AJ2"/>
+      <c r="AK2"/>
+      <c r="AL2"/>
+      <c r="AM2"/>
+      <c r="AN2"/>
+      <c r="AO2"/>
+      <c r="AP2"/>
+      <c r="AQ2"/>
+      <c r="AR2"/>
+      <c r="AS2"/>
+      <c r="AT2"/>
+      <c r="AU2"/>
+      <c r="AV2"/>
+      <c r="AW2"/>
+      <c r="AX2"/>
+      <c r="AY2"/>
+      <c r="AZ2"/>
+      <c r="BA2"/>
+      <c r="BB2"/>
+      <c r="BC2"/>
+      <c r="BD2"/>
+      <c r="BE2"/>
+      <c r="BF2"/>
+      <c r="BG2"/>
+      <c r="BH2"/>
+      <c r="BI2"/>
+      <c r="BJ2"/>
+      <c r="BK2"/>
+      <c r="BL2"/>
+      <c r="BM2"/>
+      <c r="BN2"/>
+      <c r="BO2"/>
+      <c r="BP2"/>
+      <c r="BQ2"/>
+      <c r="BR2"/>
+      <c r="BS2"/>
+      <c r="BT2"/>
+      <c r="BU2"/>
+      <c r="BV2"/>
+      <c r="BW2"/>
+      <c r="BX2"/>
+      <c r="BY2"/>
+      <c r="BZ2"/>
+      <c r="CA2"/>
+      <c r="CB2"/>
+      <c r="CC2"/>
+      <c r="CD2"/>
+      <c r="CE2"/>
+      <c r="CF2"/>
+      <c r="CG2"/>
+      <c r="CH2"/>
+      <c r="CI2"/>
+      <c r="CJ2"/>
+      <c r="CK2"/>
+      <c r="CL2"/>
+      <c r="CM2"/>
+      <c r="CN2"/>
+      <c r="CO2"/>
+      <c r="CP2"/>
+      <c r="CQ2"/>
+      <c r="CR2"/>
+      <c r="CS2"/>
+      <c r="CT2"/>
+      <c r="CU2"/>
+      <c r="CV2"/>
+      <c r="CW2"/>
+      <c r="CX2"/>
+      <c r="CY2"/>
+      <c r="CZ2"/>
+      <c r="DA2"/>
+      <c r="DB2"/>
+      <c r="DC2"/>
+      <c r="DD2"/>
+      <c r="DE2"/>
+      <c r="DF2"/>
+      <c r="DG2"/>
+      <c r="DH2"/>
+      <c r="DI2"/>
+      <c r="DJ2"/>
+      <c r="DK2"/>
+      <c r="DL2"/>
+      <c r="DM2"/>
+      <c r="DN2"/>
+      <c r="DO2"/>
+      <c r="DP2"/>
+      <c r="DQ2"/>
+      <c r="DR2"/>
+      <c r="DS2"/>
+      <c r="DT2"/>
+      <c r="DU2"/>
+      <c r="DV2"/>
+      <c r="DW2"/>
+      <c r="DX2"/>
+      <c r="DY2"/>
+      <c r="DZ2"/>
+      <c r="EA2"/>
+      <c r="EB2"/>
+      <c r="EC2"/>
+      <c r="ED2"/>
+      <c r="EE2"/>
+      <c r="EF2"/>
+      <c r="EG2"/>
+      <c r="EH2"/>
+      <c r="EI2"/>
+      <c r="EJ2"/>
+      <c r="EK2"/>
+      <c r="EL2"/>
+      <c r="EM2"/>
+      <c r="EN2"/>
+      <c r="EO2"/>
+      <c r="EP2"/>
+      <c r="EQ2"/>
+      <c r="ER2"/>
+      <c r="ES2"/>
+      <c r="ET2"/>
+      <c r="EU2"/>
+      <c r="EV2"/>
+      <c r="EW2"/>
+      <c r="EX2"/>
+      <c r="EY2"/>
+      <c r="EZ2"/>
+      <c r="FA2"/>
+      <c r="FB2"/>
+      <c r="FC2"/>
+      <c r="FD2"/>
+      <c r="FE2"/>
+      <c r="FF2"/>
+      <c r="FG2"/>
+      <c r="FH2"/>
+      <c r="FI2"/>
+      <c r="FJ2"/>
+      <c r="FK2"/>
+      <c r="FL2"/>
+      <c r="FM2"/>
+      <c r="FN2"/>
+      <c r="FO2"/>
+      <c r="FP2"/>
+      <c r="FQ2"/>
+      <c r="FR2"/>
+      <c r="FS2"/>
+      <c r="FT2"/>
+      <c r="FU2"/>
+      <c r="FV2"/>
+      <c r="FW2"/>
+      <c r="FX2"/>
+      <c r="FY2"/>
+      <c r="FZ2"/>
+      <c r="GA2"/>
+      <c r="GB2"/>
+      <c r="GC2"/>
+      <c r="GD2"/>
+      <c r="GE2"/>
+      <c r="GF2"/>
+      <c r="GG2"/>
+      <c r="GH2"/>
+      <c r="GI2"/>
+      <c r="GJ2"/>
+      <c r="GK2"/>
+      <c r="GL2"/>
+      <c r="GM2"/>
+      <c r="GN2"/>
+      <c r="GO2"/>
+      <c r="GP2"/>
+      <c r="GQ2"/>
+      <c r="GR2"/>
+      <c r="GS2"/>
+      <c r="GT2"/>
+      <c r="GU2"/>
+      <c r="GV2"/>
+      <c r="GW2"/>
+      <c r="GX2"/>
+      <c r="GY2"/>
+      <c r="GZ2"/>
+      <c r="HA2"/>
+      <c r="HB2"/>
+      <c r="HC2"/>
+      <c r="HD2"/>
+      <c r="HE2"/>
+      <c r="HF2"/>
+      <c r="HG2"/>
+      <c r="HH2"/>
+      <c r="HI2"/>
+      <c r="HJ2"/>
+      <c r="HK2"/>
+      <c r="HL2"/>
+      <c r="HM2"/>
+      <c r="HN2"/>
+      <c r="HO2"/>
+      <c r="HP2"/>
+      <c r="HQ2"/>
+      <c r="HR2"/>
+      <c r="HS2"/>
+      <c r="HT2"/>
+      <c r="HU2"/>
+    </row>
+    <row r="3" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
         <v>655</v>
       </c>
       <c r="B3" s="3" t="s">
@@ -23761,6 +24036,531 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F4A5E3B-1F6E-404D-9F27-5E0D8E1F2B54}">
+  <dimension ref="A1:HU11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="50.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="50.26953125" customWidth="1"/>
+    <col min="3" max="3" width="42.453125" customWidth="1"/>
+    <col min="4" max="4" width="33.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="33.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.08984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="40.81640625" customWidth="1"/>
+    <col min="8" max="8" width="65.54296875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="2" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>688</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>689</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>690</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="3" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>692</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>693</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>694</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="4" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A4" s="8" t="s">
+        <v>696</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>697</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>698</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="5" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>700</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>701</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>702</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="6" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>704</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>705</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>706</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="7" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>710</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="8" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>712</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>714</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="9" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>716</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>717</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>718</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="10" spans="1:229" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>721</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>720</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>722</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="11" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="3" t="s">
+        <v>685</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>686</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>687</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="H11" s="11"/>
+      <c r="I11"/>
+      <c r="J11"/>
+      <c r="K11"/>
+      <c r="L11"/>
+      <c r="M11"/>
+      <c r="N11"/>
+      <c r="O11"/>
+      <c r="P11"/>
+      <c r="Q11"/>
+      <c r="R11"/>
+      <c r="S11"/>
+      <c r="T11"/>
+      <c r="U11"/>
+      <c r="V11"/>
+      <c r="W11"/>
+      <c r="X11"/>
+      <c r="Y11"/>
+      <c r="Z11"/>
+      <c r="AA11"/>
+      <c r="AB11"/>
+      <c r="AC11"/>
+      <c r="AD11"/>
+      <c r="AE11"/>
+      <c r="AF11"/>
+      <c r="AG11"/>
+      <c r="AH11"/>
+      <c r="AI11"/>
+      <c r="AJ11"/>
+      <c r="AK11"/>
+      <c r="AL11"/>
+      <c r="AM11"/>
+      <c r="AN11"/>
+      <c r="AO11"/>
+      <c r="AP11"/>
+      <c r="AQ11"/>
+      <c r="AR11"/>
+      <c r="AS11"/>
+      <c r="AT11"/>
+      <c r="AU11"/>
+      <c r="AV11"/>
+      <c r="AW11"/>
+      <c r="AX11"/>
+      <c r="AY11"/>
+      <c r="AZ11"/>
+      <c r="BA11"/>
+      <c r="BB11"/>
+      <c r="BC11"/>
+      <c r="BD11"/>
+      <c r="BE11"/>
+      <c r="BF11"/>
+      <c r="BG11"/>
+      <c r="BH11"/>
+      <c r="BI11"/>
+      <c r="BJ11"/>
+      <c r="BK11"/>
+      <c r="BL11"/>
+      <c r="BM11"/>
+      <c r="BN11"/>
+      <c r="BO11"/>
+      <c r="BP11"/>
+      <c r="BQ11"/>
+      <c r="BR11"/>
+      <c r="BS11"/>
+      <c r="BT11"/>
+      <c r="BU11"/>
+      <c r="BV11"/>
+      <c r="BW11"/>
+      <c r="BX11"/>
+      <c r="BY11"/>
+      <c r="BZ11"/>
+      <c r="CA11"/>
+      <c r="CB11"/>
+      <c r="CC11"/>
+      <c r="CD11"/>
+      <c r="CE11"/>
+      <c r="CF11"/>
+      <c r="CG11"/>
+      <c r="CH11"/>
+      <c r="CI11"/>
+      <c r="CJ11"/>
+      <c r="CK11"/>
+      <c r="CL11"/>
+      <c r="CM11"/>
+      <c r="CN11"/>
+      <c r="CO11"/>
+      <c r="CP11"/>
+      <c r="CQ11"/>
+      <c r="CR11"/>
+      <c r="CS11"/>
+      <c r="CT11"/>
+      <c r="CU11"/>
+      <c r="CV11"/>
+      <c r="CW11"/>
+      <c r="CX11"/>
+      <c r="CY11"/>
+      <c r="CZ11"/>
+      <c r="DA11"/>
+      <c r="DB11"/>
+      <c r="DC11"/>
+      <c r="DD11"/>
+      <c r="DE11"/>
+      <c r="DF11"/>
+      <c r="DG11"/>
+      <c r="DH11"/>
+      <c r="DI11"/>
+      <c r="DJ11"/>
+      <c r="DK11"/>
+      <c r="DL11"/>
+      <c r="DM11"/>
+      <c r="DN11"/>
+      <c r="DO11"/>
+      <c r="DP11"/>
+      <c r="DQ11"/>
+      <c r="DR11"/>
+      <c r="DS11"/>
+      <c r="DT11"/>
+      <c r="DU11"/>
+      <c r="DV11"/>
+      <c r="DW11"/>
+      <c r="DX11"/>
+      <c r="DY11"/>
+      <c r="DZ11"/>
+      <c r="EA11"/>
+      <c r="EB11"/>
+      <c r="EC11"/>
+      <c r="ED11"/>
+      <c r="EE11"/>
+      <c r="EF11"/>
+      <c r="EG11"/>
+      <c r="EH11"/>
+      <c r="EI11"/>
+      <c r="EJ11"/>
+      <c r="EK11"/>
+      <c r="EL11"/>
+      <c r="EM11"/>
+      <c r="EN11"/>
+      <c r="EO11"/>
+      <c r="EP11"/>
+      <c r="EQ11"/>
+      <c r="ER11"/>
+      <c r="ES11"/>
+      <c r="ET11"/>
+      <c r="EU11"/>
+      <c r="EV11"/>
+      <c r="EW11"/>
+      <c r="EX11"/>
+      <c r="EY11"/>
+      <c r="EZ11"/>
+      <c r="FA11"/>
+      <c r="FB11"/>
+      <c r="FC11"/>
+      <c r="FD11"/>
+      <c r="FE11"/>
+      <c r="FF11"/>
+      <c r="FG11"/>
+      <c r="FH11"/>
+      <c r="FI11"/>
+      <c r="FJ11"/>
+      <c r="FK11"/>
+      <c r="FL11"/>
+      <c r="FM11"/>
+      <c r="FN11"/>
+      <c r="FO11"/>
+      <c r="FP11"/>
+      <c r="FQ11"/>
+      <c r="FR11"/>
+      <c r="FS11"/>
+      <c r="FT11"/>
+      <c r="FU11"/>
+      <c r="FV11"/>
+      <c r="FW11"/>
+      <c r="FX11"/>
+      <c r="FY11"/>
+      <c r="FZ11"/>
+      <c r="GA11"/>
+      <c r="GB11"/>
+      <c r="GC11"/>
+      <c r="GD11"/>
+      <c r="GE11"/>
+      <c r="GF11"/>
+      <c r="GG11"/>
+      <c r="GH11"/>
+      <c r="GI11"/>
+      <c r="GJ11"/>
+      <c r="GK11"/>
+      <c r="GL11"/>
+      <c r="GM11"/>
+      <c r="GN11"/>
+      <c r="GO11"/>
+      <c r="GP11"/>
+      <c r="GQ11"/>
+      <c r="GR11"/>
+      <c r="GS11"/>
+      <c r="GT11"/>
+      <c r="GU11"/>
+      <c r="GV11"/>
+      <c r="GW11"/>
+      <c r="GX11"/>
+      <c r="GY11"/>
+      <c r="GZ11"/>
+      <c r="HA11"/>
+      <c r="HB11"/>
+      <c r="HC11"/>
+      <c r="HD11"/>
+      <c r="HE11"/>
+      <c r="HF11"/>
+      <c r="HG11"/>
+      <c r="HH11"/>
+      <c r="HI11"/>
+      <c r="HJ11"/>
+      <c r="HK11"/>
+      <c r="HL11"/>
+      <c r="HM11"/>
+      <c r="HN11"/>
+      <c r="HO11"/>
+      <c r="HP11"/>
+      <c r="HQ11"/>
+      <c r="HR11"/>
+      <c r="HS11"/>
+      <c r="HT11"/>
+      <c r="HU11"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/testdata.xlsx
+++ b/testdata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sshiwani\workspace\find-information-products-services-tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4DA9259-E008-4B65-9E20-CCBE67F2BD55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4702A7A5-1E11-4D93-830F-BBF1EC54434C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" firstSheet="39" activeTab="41" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="category_phase" sheetId="1" r:id="rId1"/>
@@ -281,12 +281,6 @@
     <t>products?group=operations-and-infrastructure</t>
   </si>
   <si>
-    <t>ul.moj-filter-tags li a:has-text('operations-and-infrastructure')</t>
-  </si>
-  <si>
-    <t>Remove this filter operations-and-infrastructure</t>
-  </si>
-  <si>
     <t>#group-operations-and-infrastructure</t>
   </si>
   <si>
@@ -350,24 +344,12 @@
     <t>products?group=strategy</t>
   </si>
   <si>
-    <t>ul.moj-filter-tags li a:has-text(' strategy')</t>
-  </si>
-  <si>
-    <t>Remove this filter strategy</t>
-  </si>
-  <si>
     <t>#group-strategy</t>
   </si>
   <si>
     <t>products?group=enterprise-data</t>
   </si>
   <si>
-    <t>ul.moj-filter-tags li a:has-text(' enterprise-data')</t>
-  </si>
-  <si>
-    <t>Remove this filter enterprise-data</t>
-  </si>
-  <si>
     <t>#group-enterprise-data</t>
   </si>
   <si>
@@ -1112,12 +1094,6 @@
     <t>products?group=commercial</t>
   </si>
   <si>
-    <t>ul.moj-filter-tags li a:has-text(' commercial')</t>
-  </si>
-  <si>
-    <t>Remove this filter commercial</t>
-  </si>
-  <si>
     <t>#group-commercial</t>
   </si>
   <si>
@@ -1334,45 +1310,21 @@
     <t>products?group=children-and-families</t>
   </si>
   <si>
-    <t>ul.moj-filter-tags li a:has-text(' children-and-families')</t>
-  </si>
-  <si>
-    <t>Remove this filter children-and-families</t>
-  </si>
-  <si>
     <t>#group-children-and-families</t>
   </si>
   <si>
     <t>products?group=regional-digital-services</t>
   </si>
   <si>
-    <t>Remove this filter regional-digital-services</t>
-  </si>
-  <si>
-    <t>ul.moj-filter-tags li a:has-text(' regional-digital-services')</t>
-  </si>
-  <si>
     <t>products?group=schools-digital</t>
   </si>
   <si>
-    <t>ul.moj-filter-tags li a:has-text(' schools-digital')</t>
-  </si>
-  <si>
-    <t>Remove this filter schools-digital</t>
-  </si>
-  <si>
     <t>#group-schools-digital</t>
   </si>
   <si>
     <t>products?group=sector-facing-services</t>
   </si>
   <si>
-    <t>ul.moj-filter-tags li a:has-text(' sector-facing-services')</t>
-  </si>
-  <si>
-    <t>Remove this filter sector-facing-services</t>
-  </si>
-  <si>
     <t>#group-sector-facing-services</t>
   </si>
   <si>
@@ -1385,36 +1337,18 @@
     <t>products?group=customer-experience-and-design</t>
   </si>
   <si>
-    <t>Remove this filter customer-experience-and-design</t>
-  </si>
-  <si>
-    <t>ul.moj-filter-tags li a:has-text('customer-experience-and-design')</t>
-  </si>
-  <si>
     <t>#group-customer-experience-and-design</t>
   </si>
   <si>
-    <t>Remove this filter funding-and-financial-oversight</t>
-  </si>
-  <si>
     <t>products?group=funding-and-financial-oversight</t>
   </si>
   <si>
-    <t>ul.moj-filter-tags li a:has-text('funding-and-financial-oversight')</t>
-  </si>
-  <si>
     <t>#group-funding-and-financial-oversight</t>
   </si>
   <si>
     <t>products?group=skills-and-growth</t>
   </si>
   <si>
-    <t>ul.moj-filter-tags li a:has-text('skills-and-growth')</t>
-  </si>
-  <si>
-    <t>Remove this filter skills-and-growth</t>
-  </si>
-  <si>
     <t>#group-skills-and-growth</t>
   </si>
   <si>
@@ -2238,6 +2172,72 @@
   </si>
   <si>
     <t>Teaching assistant  (School workforce)</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text('  Commercial')</t>
+  </si>
+  <si>
+    <t>Remove this filter Commercial</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Customer Experience and Design')</t>
+  </si>
+  <si>
+    <t>Remove this filter Customer Experience and Design</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Enterprise Data')</t>
+  </si>
+  <si>
+    <t>Remove this filter Enterprise Data</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Children and Families')</t>
+  </si>
+  <si>
+    <t>Remove this filter Children and Families</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Funding and Financial Oversight')</t>
+  </si>
+  <si>
+    <t>Remove this filter Funding and Financial Oversight</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Operations and Infrastructure')</t>
+  </si>
+  <si>
+    <t>Remove this filter Operations and Infrastructure</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Regional Digital Services')</t>
+  </si>
+  <si>
+    <t>Remove this filter Regional Digital Services</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Schools Digital')</t>
+  </si>
+  <si>
+    <t>Remove this filter Schools Digital</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Sector Facing Services')</t>
+  </si>
+  <si>
+    <t>Remove this filter Sector Facing Services</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Skills and Growth')</t>
+  </si>
+  <si>
+    <t>Remove this filter Skills and Growth</t>
+  </si>
+  <si>
+    <t>ul.moj-filter-tags li a:has-text(' Strategy')</t>
+  </si>
+  <si>
+    <t>Remove this filter Strategy</t>
   </si>
 </sst>
 </file>
@@ -5037,13 +5037,13 @@
     </row>
     <row r="4" spans="1:1149" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
@@ -5052,7 +5052,7 @@
         <v>1</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>420</v>
+        <v>412</v>
       </c>
       <c r="G4"/>
       <c r="H4"/>
@@ -12030,64 +12030,64 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
     </row>
   </sheetData>
@@ -12107,78 +12107,78 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>
@@ -12199,78 +12199,78 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
     </row>
   </sheetData>
@@ -12290,99 +12290,99 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
     </row>
   </sheetData>
@@ -12402,85 +12402,85 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
     </row>
   </sheetData>
@@ -12500,99 +12500,99 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
     </row>
   </sheetData>
@@ -12612,80 +12612,80 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>450</v>
+        <v>428</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>451</v>
+        <v>429</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>452</v>
+        <v>430</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>453</v>
+        <v>431</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>454</v>
+        <v>432</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>455</v>
+        <v>433</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>456</v>
+        <v>434</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -12707,115 +12707,115 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>515</v>
+        <v>493</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>516</v>
+        <v>494</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>517</v>
+        <v>495</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>518</v>
+        <v>496</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>519</v>
+        <v>497</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>520</v>
+        <v>498</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>521</v>
+        <v>499</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>522</v>
+        <v>500</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>523</v>
+        <v>501</v>
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>524</v>
+        <v>502</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>525</v>
+        <v>503</v>
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
-        <v>526</v>
+        <v>504</v>
       </c>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -12837,66 +12837,66 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>571</v>
+        <v>549</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>572</v>
+        <v>550</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>573</v>
+        <v>551</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>574</v>
+        <v>552</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>575</v>
+        <v>553</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -12918,52 +12918,52 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>591</v>
+        <v>569</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>592</v>
+        <v>570</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>593</v>
+        <v>571</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -13031,7 +13031,7 @@
         <v>41</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>42</v>
@@ -13071,10 +13071,10 @@
         <v>48</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
@@ -13203,66 +13203,66 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>602</v>
+        <v>580</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>603</v>
+        <v>581</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>604</v>
+        <v>582</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>605</v>
+        <v>583</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>606</v>
+        <v>584</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -13284,66 +13284,66 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>622</v>
+        <v>600</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>623</v>
+        <v>601</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>624</v>
+        <v>602</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>625</v>
+        <v>603</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>626</v>
+        <v>604</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -13365,80 +13365,80 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>643</v>
+        <v>621</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>644</v>
+        <v>622</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>645</v>
+        <v>623</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>646</v>
+        <v>624</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>647</v>
+        <v>625</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>648</v>
+        <v>626</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>649</v>
+        <v>627</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -13460,108 +13460,108 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>674</v>
+        <v>652</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>675</v>
+        <v>653</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>676</v>
+        <v>654</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>677</v>
+        <v>655</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>678</v>
+        <v>656</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>679</v>
+        <v>657</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>680</v>
+        <v>658</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>681</v>
+        <v>659</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>682</v>
+        <v>660</v>
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>683</v>
+        <v>661</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>684</v>
+        <v>662</v>
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -13606,36 +13606,36 @@
         <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>437</v>
+        <v>421</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -13861,106 +13861,106 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
     </row>
   </sheetData>
@@ -14004,36 +14004,36 @@
         <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -14259,80 +14259,80 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
     </row>
   </sheetData>
@@ -14375,36 +14375,36 @@
         <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -14630,132 +14630,132 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
     </row>
     <row r="7" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
     </row>
   </sheetData>
@@ -14799,36 +14799,36 @@
         <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -15054,106 +15054,106 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
     </row>
   </sheetData>
@@ -15196,36 +15196,36 @@
         <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -15451,80 +15451,80 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
     </row>
   </sheetData>
@@ -15567,36 +15567,36 @@
         <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -15822,132 +15822,132 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="7" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
     </row>
   </sheetData>
@@ -15990,82 +15990,82 @@
     </row>
     <row r="2" spans="1:1029" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>348</v>
+        <v>702</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>349</v>
+        <v>703</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>350</v>
+        <v>342</v>
       </c>
     </row>
     <row r="3" spans="1:1029" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>438</v>
+        <v>422</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>440</v>
+        <v>704</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>439</v>
+        <v>705</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>441</v>
+        <v>423</v>
       </c>
     </row>
     <row r="4" spans="1:1029" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>98</v>
+        <v>706</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>99</v>
+        <v>707</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" spans="1:1029" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>422</v>
+        <v>708</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>423</v>
+        <v>709</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>424</v>
+        <v>414</v>
       </c>
       <c r="G5"/>
       <c r="H5"/>
@@ -17093,22 +17093,22 @@
     </row>
     <row r="6" spans="1:1029" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>443</v>
+        <v>424</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>444</v>
+        <v>710</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>442</v>
+        <v>711</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>445</v>
+        <v>425</v>
       </c>
     </row>
     <row r="7" spans="1:1029" x14ac:dyDescent="0.35">
@@ -17116,39 +17116,39 @@
         <v>70</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>71</v>
+        <v>712</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>72</v>
+        <v>713</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="8" spans="1:1029" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>425</v>
+        <v>415</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>427</v>
+        <v>714</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>426</v>
+        <v>715</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>436</v>
+        <v>420</v>
       </c>
       <c r="G8"/>
       <c r="H8"/>
@@ -18176,82 +18176,82 @@
     </row>
     <row r="9" spans="1:1029" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>428</v>
+        <v>416</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>429</v>
+        <v>716</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>430</v>
+        <v>717</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>431</v>
+        <v>417</v>
       </c>
     </row>
     <row r="10" spans="1:1029" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>432</v>
+        <v>418</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>433</v>
+        <v>718</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>434</v>
+        <v>719</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>435</v>
+        <v>419</v>
       </c>
     </row>
     <row r="11" spans="1:1029" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>446</v>
+        <v>426</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>447</v>
+        <v>720</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>448</v>
+        <v>721</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>449</v>
+        <v>427</v>
       </c>
     </row>
     <row r="12" spans="1:1029" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>94</v>
+        <v>722</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>95</v>
+        <v>723</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -18294,36 +18294,36 @@
         <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -18549,132 +18549,132 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
     </row>
     <row r="7" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
   </sheetData>
@@ -18717,36 +18717,36 @@
         <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -18972,210 +18972,210 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>369</v>
+        <v>361</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>370</v>
+        <v>362</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
     </row>
     <row r="7" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>377</v>
+        <v>369</v>
       </c>
     </row>
     <row r="8" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
     </row>
     <row r="9" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
     </row>
     <row r="10" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>388</v>
+        <v>380</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
     </row>
   </sheetData>
@@ -19219,36 +19219,36 @@
         <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>391</v>
+        <v>383</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -19474,158 +19474,158 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>393</v>
+        <v>385</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
     </row>
     <row r="7" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
     </row>
     <row r="8" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A8" s="9" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
     </row>
   </sheetData>
@@ -19669,36 +19669,36 @@
         <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>457</v>
+        <v>435</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>458</v>
+        <v>436</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>459</v>
+        <v>437</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -19924,184 +19924,184 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>460</v>
+        <v>438</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>461</v>
+        <v>439</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>462</v>
+        <v>440</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>463</v>
+        <v>441</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>464</v>
+        <v>442</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>467</v>
+        <v>445</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>465</v>
+        <v>443</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>466</v>
+        <v>444</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
-        <v>468</v>
+        <v>446</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>469</v>
+        <v>447</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>470</v>
+        <v>448</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>471</v>
+        <v>449</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>473</v>
+        <v>451</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>472</v>
+        <v>450</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>474</v>
+        <v>452</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>475</v>
+        <v>453</v>
       </c>
     </row>
     <row r="7" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>476</v>
+        <v>454</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>477</v>
+        <v>455</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>478</v>
+        <v>456</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>479</v>
+        <v>457</v>
       </c>
     </row>
     <row r="8" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>480</v>
+        <v>458</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>481</v>
+        <v>459</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>482</v>
+        <v>460</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>483</v>
+        <v>461</v>
       </c>
     </row>
     <row r="9" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>484</v>
+        <v>462</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>485</v>
+        <v>463</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>486</v>
+        <v>464</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>487</v>
+        <v>465</v>
       </c>
     </row>
   </sheetData>
@@ -20145,36 +20145,36 @@
         <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>488</v>
+        <v>466</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>489</v>
+        <v>467</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>490</v>
+        <v>468</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>491</v>
+        <v>469</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -20400,132 +20400,132 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>492</v>
+        <v>470</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>493</v>
+        <v>471</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>494</v>
+        <v>472</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>495</v>
+        <v>473</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>496</v>
+        <v>474</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>497</v>
+        <v>475</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>498</v>
+        <v>476</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>499</v>
+        <v>477</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
-        <v>500</v>
+        <v>478</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>501</v>
+        <v>479</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>502</v>
+        <v>480</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>503</v>
+        <v>481</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>504</v>
+        <v>482</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>505</v>
+        <v>483</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>506</v>
+        <v>484</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>507</v>
+        <v>485</v>
       </c>
     </row>
     <row r="7" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>509</v>
+        <v>487</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>508</v>
+        <v>486</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>510</v>
+        <v>488</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>511</v>
+        <v>489</v>
       </c>
     </row>
   </sheetData>
@@ -20568,36 +20568,36 @@
         <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>512</v>
+        <v>490</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>513</v>
+        <v>491</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>514</v>
+        <v>492</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -20861,36 +20861,36 @@
         <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>527</v>
+        <v>505</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>528</v>
+        <v>506</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>529</v>
+        <v>507</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>530</v>
+        <v>508</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -21116,262 +21116,262 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>532</v>
+        <v>510</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>531</v>
+        <v>509</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>533</v>
+        <v>511</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>534</v>
+        <v>512</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>535</v>
+        <v>513</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>536</v>
+        <v>514</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>537</v>
+        <v>515</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>538</v>
+        <v>516</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
-        <v>539</v>
+        <v>517</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>540</v>
+        <v>518</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>541</v>
+        <v>519</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>542</v>
+        <v>520</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>543</v>
+        <v>521</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>544</v>
+        <v>522</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>545</v>
+        <v>523</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>546</v>
+        <v>524</v>
       </c>
     </row>
     <row r="7" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>547</v>
+        <v>525</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>548</v>
+        <v>526</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>549</v>
+        <v>527</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>550</v>
+        <v>528</v>
       </c>
     </row>
     <row r="8" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>551</v>
+        <v>529</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>552</v>
+        <v>530</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>553</v>
+        <v>531</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>554</v>
+        <v>532</v>
       </c>
     </row>
     <row r="9" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>555</v>
+        <v>533</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>556</v>
+        <v>534</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>558</v>
+        <v>536</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>557</v>
+        <v>535</v>
       </c>
     </row>
     <row r="10" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>559</v>
+        <v>537</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>560</v>
+        <v>538</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>561</v>
+        <v>539</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>562</v>
+        <v>540</v>
       </c>
     </row>
     <row r="11" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>563</v>
+        <v>541</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>564</v>
+        <v>542</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>565</v>
+        <v>543</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>566</v>
+        <v>544</v>
       </c>
     </row>
     <row r="12" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>567</v>
+        <v>545</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>568</v>
+        <v>546</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>569</v>
+        <v>547</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>570</v>
+        <v>548</v>
       </c>
     </row>
   </sheetData>
@@ -21415,36 +21415,36 @@
         <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>576</v>
+        <v>554</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>577</v>
+        <v>555</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>578</v>
+        <v>556</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>579</v>
+        <v>557</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -21670,78 +21670,78 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>580</v>
+        <v>558</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>581</v>
+        <v>559</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>582</v>
+        <v>560</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>583</v>
+        <v>561</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="11" t="s">
-        <v>584</v>
+        <v>562</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>585</v>
+        <v>563</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>586</v>
+        <v>564</v>
       </c>
       <c r="D4" s="11" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H4" s="11"/>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>587</v>
+        <v>565</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>588</v>
+        <v>566</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>589</v>
+        <v>567</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>590</v>
+        <v>568</v>
       </c>
     </row>
   </sheetData>
@@ -21784,36 +21784,36 @@
         <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>594</v>
+        <v>572</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>595</v>
+        <v>573</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>596</v>
+        <v>574</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>597</v>
+        <v>575</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -22039,28 +22039,28 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>598</v>
+        <v>576</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>599</v>
+        <v>577</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>600</v>
+        <v>578</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>601</v>
+        <v>579</v>
       </c>
     </row>
   </sheetData>
@@ -22103,33 +22103,33 @@
         <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="11" t="s">
-        <v>607</v>
+        <v>585</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>608</v>
+        <v>586</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>609</v>
+        <v>587</v>
       </c>
       <c r="D2" s="11" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H2" s="11"/>
       <c r="I2"/>
@@ -22356,80 +22356,80 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>610</v>
+        <v>588</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>611</v>
+        <v>589</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>612</v>
+        <v>590</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>613</v>
+        <v>591</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>614</v>
+        <v>592</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>615</v>
+        <v>593</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>616</v>
+        <v>594</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>617</v>
+        <v>595</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>618</v>
+        <v>596</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>619</v>
+        <v>597</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>620</v>
+        <v>598</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>621</v>
+        <v>599</v>
       </c>
     </row>
   </sheetData>
@@ -22473,22 +22473,22 @@
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>74</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>76</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G2"/>
       <c r="H2"/>
@@ -22716,22 +22716,22 @@
     </row>
     <row r="3" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>79</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>81</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G3"/>
       <c r="H3"/>
@@ -22959,22 +22959,22 @@
     </row>
     <row r="4" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="G4"/>
       <c r="H4"/>
@@ -23202,42 +23202,42 @@
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>83</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>85</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>87</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -23280,36 +23280,36 @@
         <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>627</v>
+        <v>605</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>628</v>
+        <v>606</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>629</v>
+        <v>607</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>630</v>
+        <v>608</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -23535,80 +23535,80 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>631</v>
+        <v>609</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>632</v>
+        <v>610</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>633</v>
+        <v>611</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>634</v>
+        <v>612</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>636</v>
+        <v>614</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>635</v>
+        <v>613</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>637</v>
+        <v>615</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>638</v>
+        <v>616</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>639</v>
+        <v>617</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>640</v>
+        <v>618</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>641</v>
+        <v>619</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>642</v>
+        <v>620</v>
       </c>
     </row>
   </sheetData>
@@ -23651,36 +23651,36 @@
         <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>650</v>
+        <v>628</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>651</v>
+        <v>629</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>652</v>
+        <v>630</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>653</v>
+        <v>631</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -23906,132 +23906,132 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>655</v>
+        <v>633</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>654</v>
+        <v>632</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>656</v>
+        <v>634</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>657</v>
+        <v>635</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>658</v>
+        <v>636</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>659</v>
+        <v>637</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>660</v>
+        <v>638</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>661</v>
+        <v>639</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>662</v>
+        <v>640</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>663</v>
+        <v>641</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>664</v>
+        <v>642</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>665</v>
+        <v>643</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>666</v>
+        <v>644</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>667</v>
+        <v>645</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>668</v>
+        <v>646</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>669</v>
+        <v>647</v>
       </c>
     </row>
     <row r="7" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>670</v>
+        <v>648</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>671</v>
+        <v>649</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>672</v>
+        <v>650</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>673</v>
+        <v>651</v>
       </c>
     </row>
   </sheetData>
@@ -24075,267 +24075,267 @@
         <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
     </row>
     <row r="2" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>688</v>
+        <v>666</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>689</v>
+        <v>667</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>690</v>
+        <v>668</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>691</v>
+        <v>669</v>
       </c>
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>692</v>
+        <v>670</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>693</v>
+        <v>671</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>694</v>
+        <v>672</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>695</v>
+        <v>673</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="8" t="s">
-        <v>696</v>
+        <v>674</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>697</v>
+        <v>675</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>698</v>
+        <v>676</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>699</v>
+        <v>677</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>700</v>
+        <v>678</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>701</v>
+        <v>679</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>702</v>
+        <v>680</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>703</v>
+        <v>681</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>704</v>
+        <v>682</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>705</v>
+        <v>683</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>706</v>
+        <v>684</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>707</v>
+        <v>685</v>
       </c>
     </row>
     <row r="7" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>708</v>
+        <v>686</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>709</v>
+        <v>687</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>710</v>
+        <v>688</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>711</v>
+        <v>689</v>
       </c>
     </row>
     <row r="8" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>712</v>
+        <v>690</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>713</v>
+        <v>691</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>714</v>
+        <v>692</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>715</v>
+        <v>693</v>
       </c>
     </row>
     <row r="9" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>716</v>
+        <v>694</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>717</v>
+        <v>695</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>718</v>
+        <v>696</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>719</v>
+        <v>697</v>
       </c>
     </row>
     <row r="10" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>721</v>
+        <v>699</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>720</v>
+        <v>698</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>722</v>
+        <v>700</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>723</v>
+        <v>701</v>
       </c>
     </row>
     <row r="11" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>685</v>
+        <v>663</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>686</v>
+        <v>664</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>687</v>
+        <v>665</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H11" s="11"/>
       <c r="I11"/>
@@ -24577,71 +24577,71 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -24660,64 +24660,64 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -24736,78 +24736,78 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -24827,71 +24827,71 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -24911,92 +24911,92 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>

--- a/testdata.xlsx
+++ b/testdata.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sshiwani\workspace\find-information-products-services-tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4702A7A5-1E11-4D93-830F-BBF1EC54434C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FD55A19-F542-4D27-85D3-F48791966A1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="category_phase" sheetId="1" r:id="rId1"/>
@@ -176,12 +176,6 @@
     <t>Checkbox_Locator</t>
   </si>
   <si>
-    <t>ul.moj-filter-tags li a:has-text('Chat')</t>
-  </si>
-  <si>
-    <t>Remove this filter Chat</t>
-  </si>
-  <si>
     <t>products?channel=chat</t>
   </si>
   <si>
@@ -194,21 +188,12 @@
     <t>products?channel=email</t>
   </si>
   <si>
-    <t>Remove this filter Email</t>
-  </si>
-  <si>
     <t>#channel-email</t>
   </si>
   <si>
-    <t>ul.moj-filter-tags li a:has-text('Face-to-face')</t>
-  </si>
-  <si>
     <t>products?channel=face-to-face</t>
   </si>
   <si>
-    <t>Remove this filter Face-to-face</t>
-  </si>
-  <si>
     <t>#channel-face-to-face</t>
   </si>
   <si>
@@ -221,60 +206,30 @@
     <t>products?channel=other-digital-media</t>
   </si>
   <si>
-    <t>ul.moj-filter-tags li a:has-text('Other digital media')</t>
-  </si>
-  <si>
-    <t>Remove this filter Other digital media</t>
-  </si>
-  <si>
     <t>#channel-other-digital-media</t>
   </si>
   <si>
     <t>products?channel=phone</t>
   </si>
   <si>
-    <t>ul.moj-filter-tags li a:has-text('Phone')</t>
-  </si>
-  <si>
-    <t>Remove this filter Phone</t>
-  </si>
-  <si>
     <t>#channel-phone</t>
   </si>
   <si>
     <t>products?channel=print-media</t>
   </si>
   <si>
-    <t>ul.moj-filter-tags li a:has-text('Print media')</t>
-  </si>
-  <si>
-    <t>Remove this filter Print media</t>
-  </si>
-  <si>
     <t>#channel-print-media</t>
   </si>
   <si>
     <t>products?channel=sms</t>
   </si>
   <si>
-    <t>ul.moj-filter-tags li a:has-text('SMS')</t>
-  </si>
-  <si>
-    <t>Remove this filter SMS</t>
-  </si>
-  <si>
     <t>#channel-sms</t>
   </si>
   <si>
     <t>products?channel=web</t>
   </si>
   <si>
-    <t>ul.moj-filter-tags li a:has-text('Web')</t>
-  </si>
-  <si>
-    <t>Remove this filter Web</t>
-  </si>
-  <si>
     <t>#channel-web</t>
   </si>
   <si>
@@ -335,12 +290,6 @@
     <t>#type-transactional</t>
   </si>
   <si>
-    <t>ul.moj-filter-tags li a:has-text(' Native app')</t>
-  </si>
-  <si>
-    <t>Remove this filter Native app</t>
-  </si>
-  <si>
     <t>products?group=strategy</t>
   </si>
   <si>
@@ -353,9 +302,6 @@
     <t>#group-enterprise-data</t>
   </si>
   <si>
-    <t>ul.moj-filter-tags li a:has-text(' Email')</t>
-  </si>
-  <si>
     <t>Col1</t>
   </si>
   <si>
@@ -2238,6 +2184,60 @@
   </si>
   <si>
     <t>Remove this filter Strategy</t>
+  </si>
+  <si>
+    <t>a.filter-badge:has(span:text-is('Chat'))</t>
+  </si>
+  <si>
+    <t>a.filter-badge:has(span:text-is('Email'))</t>
+  </si>
+  <si>
+    <t>a.filter-badge:has(span:text-is('Face-to-face'))</t>
+  </si>
+  <si>
+    <t>a.filter-badge:has(span:text-is('Native app'))</t>
+  </si>
+  <si>
+    <t>a.filter-badge:has(span:text-is('Other digital media'))</t>
+  </si>
+  <si>
+    <t>a.filter-badge:has(span:text-is('Phone'))</t>
+  </si>
+  <si>
+    <t>a.filter-badge:has(span:text-is('Print media'))</t>
+  </si>
+  <si>
+    <t>a.filter-badge:has(span:text-is('SMS'))</t>
+  </si>
+  <si>
+    <t>a.filter-badge:has(span:text-is('Web'))</t>
+  </si>
+  <si>
+    <t>Chat × Remove Chat filter</t>
+  </si>
+  <si>
+    <t>Email × Remove Email filter</t>
+  </si>
+  <si>
+    <t>Face-to-face × Remove Face-to-face filter</t>
+  </si>
+  <si>
+    <t>Native app × Remove Native app filter</t>
+  </si>
+  <si>
+    <t>Other digital media × Remove Other digital media filter</t>
+  </si>
+  <si>
+    <t>Phone × Remove Phone filter</t>
+  </si>
+  <si>
+    <t>Print media × Remove Print media filter</t>
+  </si>
+  <si>
+    <t>SMS × Remove SMS filter</t>
+  </si>
+  <si>
+    <t>Web × Remove Web filter</t>
   </si>
 </sst>
 </file>
@@ -5037,13 +5037,13 @@
     </row>
     <row r="4" spans="1:1149" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>409</v>
+        <v>391</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>410</v>
+        <v>392</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>411</v>
+        <v>393</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
@@ -5052,7 +5052,7 @@
         <v>1</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>412</v>
+        <v>394</v>
       </c>
       <c r="G4"/>
       <c r="H4"/>
@@ -12030,64 +12030,64 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>143</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>146</v>
+        <v>128</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>147</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -12107,78 +12107,78 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>151</v>
+        <v>133</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>152</v>
+        <v>134</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>
@@ -12199,78 +12199,78 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>159</v>
+        <v>141</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>160</v>
+        <v>142</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>162</v>
+        <v>144</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>163</v>
+        <v>145</v>
       </c>
     </row>
   </sheetData>
@@ -12290,99 +12290,99 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>164</v>
+        <v>146</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>165</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>166</v>
+        <v>148</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>167</v>
+        <v>149</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>168</v>
+        <v>150</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>169</v>
+        <v>151</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>172</v>
+        <v>154</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>174</v>
+        <v>156</v>
       </c>
     </row>
   </sheetData>
@@ -12402,85 +12402,85 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>176</v>
+        <v>158</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>177</v>
+        <v>159</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>178</v>
+        <v>160</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>179</v>
+        <v>161</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>180</v>
+        <v>162</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>181</v>
+        <v>163</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>183</v>
+        <v>165</v>
       </c>
     </row>
   </sheetData>
@@ -12500,99 +12500,99 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>189</v>
+        <v>171</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>191</v>
+        <v>173</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>192</v>
+        <v>174</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>193</v>
+        <v>175</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>194</v>
+        <v>176</v>
       </c>
     </row>
   </sheetData>
@@ -12612,80 +12612,80 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>428</v>
+        <v>410</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>429</v>
+        <v>411</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>194</v>
+        <v>176</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>430</v>
+        <v>412</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>431</v>
+        <v>413</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>432</v>
+        <v>414</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>433</v>
+        <v>415</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>434</v>
+        <v>416</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -12707,115 +12707,115 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>493</v>
+        <v>475</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>494</v>
+        <v>476</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>495</v>
+        <v>477</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>496</v>
+        <v>478</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>497</v>
+        <v>479</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>498</v>
+        <v>480</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>499</v>
+        <v>481</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>500</v>
+        <v>482</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>501</v>
+        <v>483</v>
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>502</v>
+        <v>484</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>503</v>
+        <v>485</v>
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
-        <v>504</v>
+        <v>486</v>
       </c>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -12837,66 +12837,66 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>549</v>
+        <v>531</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>550</v>
+        <v>532</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>551</v>
+        <v>533</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>552</v>
+        <v>534</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>553</v>
+        <v>535</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -12918,52 +12918,52 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>569</v>
+        <v>551</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>570</v>
+        <v>552</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>571</v>
+        <v>553</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -12975,7 +12975,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2DC696B-E1A8-430C-BC9E-87DD1A6FBE9F}">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:BD10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="33.08984375" bestFit="1" customWidth="1"/>
@@ -12986,7 +12986,7 @@
     <col min="6" max="6" width="25.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:56" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>30</v>
       </c>
@@ -13006,185 +13006,635 @@
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:56" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>36</v>
+        <v>706</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>37</v>
+        <v>715</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G2"/>
+      <c r="H2"/>
+      <c r="I2"/>
+      <c r="J2"/>
+      <c r="K2"/>
+      <c r="L2"/>
+      <c r="M2"/>
+      <c r="N2"/>
+      <c r="O2"/>
+      <c r="P2"/>
+      <c r="Q2"/>
+      <c r="R2"/>
+      <c r="S2"/>
+      <c r="T2"/>
+      <c r="U2"/>
+      <c r="V2"/>
+      <c r="W2"/>
+      <c r="X2"/>
+      <c r="Y2"/>
+      <c r="Z2"/>
+      <c r="AA2"/>
+      <c r="AB2"/>
+      <c r="AC2"/>
+      <c r="AD2"/>
+      <c r="AE2"/>
+      <c r="AF2"/>
+      <c r="AG2"/>
+      <c r="AH2"/>
+      <c r="AI2"/>
+      <c r="AJ2"/>
+      <c r="AK2"/>
+      <c r="AL2"/>
+      <c r="AM2"/>
+      <c r="AN2"/>
+      <c r="AO2"/>
+      <c r="AP2"/>
+      <c r="AQ2"/>
+      <c r="AR2"/>
+      <c r="AS2"/>
+      <c r="AT2"/>
+      <c r="AU2"/>
+      <c r="AV2"/>
+      <c r="AW2"/>
+      <c r="AX2"/>
+      <c r="AY2"/>
+      <c r="AZ2"/>
+      <c r="BA2"/>
+      <c r="BB2"/>
+      <c r="BC2"/>
+      <c r="BD2"/>
+    </row>
+    <row r="3" spans="1:56" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="F2" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="B3" s="3" t="s">
-        <v>95</v>
+        <v>707</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>42</v>
+        <v>716</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
+        <v>40</v>
+      </c>
+      <c r="G3"/>
+      <c r="H3"/>
+      <c r="I3"/>
+      <c r="J3"/>
+      <c r="K3"/>
+      <c r="L3"/>
+      <c r="M3"/>
+      <c r="N3"/>
+      <c r="O3"/>
+      <c r="P3"/>
+      <c r="Q3"/>
+      <c r="R3"/>
+      <c r="S3"/>
+      <c r="T3"/>
+      <c r="U3"/>
+      <c r="V3"/>
+      <c r="W3"/>
+      <c r="X3"/>
+      <c r="Y3"/>
+      <c r="Z3"/>
+      <c r="AA3"/>
+      <c r="AB3"/>
+      <c r="AC3"/>
+      <c r="AD3"/>
+      <c r="AE3"/>
+      <c r="AF3"/>
+      <c r="AG3"/>
+      <c r="AH3"/>
+      <c r="AI3"/>
+      <c r="AJ3"/>
+      <c r="AK3"/>
+      <c r="AL3"/>
+      <c r="AM3"/>
+      <c r="AN3"/>
+      <c r="AO3"/>
+      <c r="AP3"/>
+      <c r="AQ3"/>
+      <c r="AR3"/>
+      <c r="AS3"/>
+      <c r="AT3"/>
+      <c r="AU3"/>
+      <c r="AV3"/>
+      <c r="AW3"/>
+      <c r="AX3"/>
+      <c r="AY3"/>
+      <c r="AZ3"/>
+      <c r="BA3"/>
+      <c r="BB3"/>
+      <c r="BC3"/>
+      <c r="BD3"/>
+    </row>
+    <row r="4" spans="1:56" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>44</v>
+        <v>708</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>46</v>
+        <v>717</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
+        <v>42</v>
+      </c>
+      <c r="G4"/>
+      <c r="H4"/>
+      <c r="I4"/>
+      <c r="J4"/>
+      <c r="K4"/>
+      <c r="L4"/>
+      <c r="M4"/>
+      <c r="N4"/>
+      <c r="O4"/>
+      <c r="P4"/>
+      <c r="Q4"/>
+      <c r="R4"/>
+      <c r="S4"/>
+      <c r="T4"/>
+      <c r="U4"/>
+      <c r="V4"/>
+      <c r="W4"/>
+      <c r="X4"/>
+      <c r="Y4"/>
+      <c r="Z4"/>
+      <c r="AA4"/>
+      <c r="AB4"/>
+      <c r="AC4"/>
+      <c r="AD4"/>
+      <c r="AE4"/>
+      <c r="AF4"/>
+      <c r="AG4"/>
+      <c r="AH4"/>
+      <c r="AI4"/>
+      <c r="AJ4"/>
+      <c r="AK4"/>
+      <c r="AL4"/>
+      <c r="AM4"/>
+      <c r="AN4"/>
+      <c r="AO4"/>
+      <c r="AP4"/>
+      <c r="AQ4"/>
+      <c r="AR4"/>
+      <c r="AS4"/>
+      <c r="AT4"/>
+      <c r="AU4"/>
+      <c r="AV4"/>
+      <c r="AW4"/>
+      <c r="AX4"/>
+      <c r="AY4"/>
+      <c r="AZ4"/>
+      <c r="BA4"/>
+      <c r="BB4"/>
+      <c r="BC4"/>
+      <c r="BD4"/>
+    </row>
+    <row r="5" spans="1:56" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>89</v>
+        <v>709</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>90</v>
+        <v>718</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
+        <v>44</v>
+      </c>
+      <c r="G5"/>
+      <c r="H5"/>
+      <c r="I5"/>
+      <c r="J5"/>
+      <c r="K5"/>
+      <c r="L5"/>
+      <c r="M5"/>
+      <c r="N5"/>
+      <c r="O5"/>
+      <c r="P5"/>
+      <c r="Q5"/>
+      <c r="R5"/>
+      <c r="S5"/>
+      <c r="T5"/>
+      <c r="U5"/>
+      <c r="V5"/>
+      <c r="W5"/>
+      <c r="X5"/>
+      <c r="Y5"/>
+      <c r="Z5"/>
+      <c r="AA5"/>
+      <c r="AB5"/>
+      <c r="AC5"/>
+      <c r="AD5"/>
+      <c r="AE5"/>
+      <c r="AF5"/>
+      <c r="AG5"/>
+      <c r="AH5"/>
+      <c r="AI5"/>
+      <c r="AJ5"/>
+      <c r="AK5"/>
+      <c r="AL5"/>
+      <c r="AM5"/>
+      <c r="AN5"/>
+      <c r="AO5"/>
+      <c r="AP5"/>
+      <c r="AQ5"/>
+      <c r="AR5"/>
+      <c r="AS5"/>
+      <c r="AT5"/>
+      <c r="AU5"/>
+      <c r="AV5"/>
+      <c r="AW5"/>
+      <c r="AX5"/>
+      <c r="AY5"/>
+      <c r="AZ5"/>
+      <c r="BA5"/>
+      <c r="BB5"/>
+      <c r="BC5"/>
+      <c r="BD5"/>
+    </row>
+    <row r="6" spans="1:56" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>51</v>
+        <v>710</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>52</v>
+        <v>719</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
+        <v>46</v>
+      </c>
+      <c r="G6"/>
+      <c r="H6"/>
+      <c r="I6"/>
+      <c r="J6"/>
+      <c r="K6"/>
+      <c r="L6"/>
+      <c r="M6"/>
+      <c r="N6"/>
+      <c r="O6"/>
+      <c r="P6"/>
+      <c r="Q6"/>
+      <c r="R6"/>
+      <c r="S6"/>
+      <c r="T6"/>
+      <c r="U6"/>
+      <c r="V6"/>
+      <c r="W6"/>
+      <c r="X6"/>
+      <c r="Y6"/>
+      <c r="Z6"/>
+      <c r="AA6"/>
+      <c r="AB6"/>
+      <c r="AC6"/>
+      <c r="AD6"/>
+      <c r="AE6"/>
+      <c r="AF6"/>
+      <c r="AG6"/>
+      <c r="AH6"/>
+      <c r="AI6"/>
+      <c r="AJ6"/>
+      <c r="AK6"/>
+      <c r="AL6"/>
+      <c r="AM6"/>
+      <c r="AN6"/>
+      <c r="AO6"/>
+      <c r="AP6"/>
+      <c r="AQ6"/>
+      <c r="AR6"/>
+      <c r="AS6"/>
+      <c r="AT6"/>
+      <c r="AU6"/>
+      <c r="AV6"/>
+      <c r="AW6"/>
+      <c r="AX6"/>
+      <c r="AY6"/>
+      <c r="AZ6"/>
+      <c r="BA6"/>
+      <c r="BB6"/>
+      <c r="BC6"/>
+      <c r="BD6"/>
+    </row>
+    <row r="7" spans="1:56" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>55</v>
+        <v>711</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>56</v>
+        <v>720</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
+        <v>48</v>
+      </c>
+      <c r="G7"/>
+      <c r="H7"/>
+      <c r="I7"/>
+      <c r="J7"/>
+      <c r="K7"/>
+      <c r="L7"/>
+      <c r="M7"/>
+      <c r="N7"/>
+      <c r="O7"/>
+      <c r="P7"/>
+      <c r="Q7"/>
+      <c r="R7"/>
+      <c r="S7"/>
+      <c r="T7"/>
+      <c r="U7"/>
+      <c r="V7"/>
+      <c r="W7"/>
+      <c r="X7"/>
+      <c r="Y7"/>
+      <c r="Z7"/>
+      <c r="AA7"/>
+      <c r="AB7"/>
+      <c r="AC7"/>
+      <c r="AD7"/>
+      <c r="AE7"/>
+      <c r="AF7"/>
+      <c r="AG7"/>
+      <c r="AH7"/>
+      <c r="AI7"/>
+      <c r="AJ7"/>
+      <c r="AK7"/>
+      <c r="AL7"/>
+      <c r="AM7"/>
+      <c r="AN7"/>
+      <c r="AO7"/>
+      <c r="AP7"/>
+      <c r="AQ7"/>
+      <c r="AR7"/>
+      <c r="AS7"/>
+      <c r="AT7"/>
+      <c r="AU7"/>
+      <c r="AV7"/>
+      <c r="AW7"/>
+      <c r="AX7"/>
+      <c r="AY7"/>
+      <c r="AZ7"/>
+      <c r="BA7"/>
+      <c r="BB7"/>
+      <c r="BC7"/>
+      <c r="BD7"/>
+    </row>
+    <row r="8" spans="1:56" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>59</v>
+        <v>712</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>60</v>
+        <v>721</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
+        <v>50</v>
+      </c>
+      <c r="G8"/>
+      <c r="H8"/>
+      <c r="I8"/>
+      <c r="J8"/>
+      <c r="K8"/>
+      <c r="L8"/>
+      <c r="M8"/>
+      <c r="N8"/>
+      <c r="O8"/>
+      <c r="P8"/>
+      <c r="Q8"/>
+      <c r="R8"/>
+      <c r="S8"/>
+      <c r="T8"/>
+      <c r="U8"/>
+      <c r="V8"/>
+      <c r="W8"/>
+      <c r="X8"/>
+      <c r="Y8"/>
+      <c r="Z8"/>
+      <c r="AA8"/>
+      <c r="AB8"/>
+      <c r="AC8"/>
+      <c r="AD8"/>
+      <c r="AE8"/>
+      <c r="AF8"/>
+      <c r="AG8"/>
+      <c r="AH8"/>
+      <c r="AI8"/>
+      <c r="AJ8"/>
+      <c r="AK8"/>
+      <c r="AL8"/>
+      <c r="AM8"/>
+      <c r="AN8"/>
+      <c r="AO8"/>
+      <c r="AP8"/>
+      <c r="AQ8"/>
+      <c r="AR8"/>
+      <c r="AS8"/>
+      <c r="AT8"/>
+      <c r="AU8"/>
+      <c r="AV8"/>
+      <c r="AW8"/>
+      <c r="AX8"/>
+      <c r="AY8"/>
+      <c r="AZ8"/>
+      <c r="BA8"/>
+      <c r="BB8"/>
+      <c r="BC8"/>
+      <c r="BD8"/>
+    </row>
+    <row r="9" spans="1:56" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>63</v>
+        <v>713</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>64</v>
+        <v>722</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
+        <v>52</v>
+      </c>
+      <c r="G9"/>
+      <c r="H9"/>
+      <c r="I9"/>
+      <c r="J9"/>
+      <c r="K9"/>
+      <c r="L9"/>
+      <c r="M9"/>
+      <c r="N9"/>
+      <c r="O9"/>
+      <c r="P9"/>
+      <c r="Q9"/>
+      <c r="R9"/>
+      <c r="S9"/>
+      <c r="T9"/>
+      <c r="U9"/>
+      <c r="V9"/>
+      <c r="W9"/>
+      <c r="X9"/>
+      <c r="Y9"/>
+      <c r="Z9"/>
+      <c r="AA9"/>
+      <c r="AB9"/>
+      <c r="AC9"/>
+      <c r="AD9"/>
+      <c r="AE9"/>
+      <c r="AF9"/>
+      <c r="AG9"/>
+      <c r="AH9"/>
+      <c r="AI9"/>
+      <c r="AJ9"/>
+      <c r="AK9"/>
+      <c r="AL9"/>
+      <c r="AM9"/>
+      <c r="AN9"/>
+      <c r="AO9"/>
+      <c r="AP9"/>
+      <c r="AQ9"/>
+      <c r="AR9"/>
+      <c r="AS9"/>
+      <c r="AT9"/>
+      <c r="AU9"/>
+      <c r="AV9"/>
+      <c r="AW9"/>
+      <c r="AX9"/>
+      <c r="AY9"/>
+      <c r="AZ9"/>
+      <c r="BA9"/>
+      <c r="BB9"/>
+      <c r="BC9"/>
+      <c r="BD9"/>
+    </row>
+    <row r="10" spans="1:56" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>67</v>
+        <v>714</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>68</v>
+        <v>723</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>69</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="G10"/>
+      <c r="H10"/>
+      <c r="I10"/>
+      <c r="J10"/>
+      <c r="K10"/>
+      <c r="L10"/>
+      <c r="M10"/>
+      <c r="N10"/>
+      <c r="O10"/>
+      <c r="P10"/>
+      <c r="Q10"/>
+      <c r="R10"/>
+      <c r="S10"/>
+      <c r="T10"/>
+      <c r="U10"/>
+      <c r="V10"/>
+      <c r="W10"/>
+      <c r="X10"/>
+      <c r="Y10"/>
+      <c r="Z10"/>
+      <c r="AA10"/>
+      <c r="AB10"/>
+      <c r="AC10"/>
+      <c r="AD10"/>
+      <c r="AE10"/>
+      <c r="AF10"/>
+      <c r="AG10"/>
+      <c r="AH10"/>
+      <c r="AI10"/>
+      <c r="AJ10"/>
+      <c r="AK10"/>
+      <c r="AL10"/>
+      <c r="AM10"/>
+      <c r="AN10"/>
+      <c r="AO10"/>
+      <c r="AP10"/>
+      <c r="AQ10"/>
+      <c r="AR10"/>
+      <c r="AS10"/>
+      <c r="AT10"/>
+      <c r="AU10"/>
+      <c r="AV10"/>
+      <c r="AW10"/>
+      <c r="AX10"/>
+      <c r="AY10"/>
+      <c r="AZ10"/>
+      <c r="BA10"/>
+      <c r="BB10"/>
+      <c r="BC10"/>
+      <c r="BD10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13203,66 +13653,66 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>580</v>
+        <v>562</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>581</v>
+        <v>563</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>582</v>
+        <v>564</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>583</v>
+        <v>565</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>584</v>
+        <v>566</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -13284,66 +13734,66 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>600</v>
+        <v>582</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>601</v>
+        <v>583</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>139</v>
+        <v>121</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>602</v>
+        <v>584</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>603</v>
+        <v>585</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>604</v>
+        <v>586</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -13365,80 +13815,80 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>621</v>
+        <v>603</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>622</v>
+        <v>604</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>623</v>
+        <v>605</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>624</v>
+        <v>606</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>625</v>
+        <v>607</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>626</v>
+        <v>608</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>627</v>
+        <v>609</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -13460,108 +13910,108 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>652</v>
+        <v>634</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>653</v>
+        <v>635</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>654</v>
+        <v>636</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>655</v>
+        <v>637</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>656</v>
+        <v>638</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>657</v>
+        <v>639</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>658</v>
+        <v>640</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>659</v>
+        <v>641</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>660</v>
+        <v>642</v>
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>661</v>
+        <v>643</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>662</v>
+        <v>644</v>
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -13606,36 +14056,36 @@
         <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>198</v>
+        <v>180</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>197</v>
+        <v>179</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>421</v>
+        <v>403</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -13861,106 +14311,106 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>199</v>
+        <v>181</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>201</v>
+        <v>183</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>202</v>
+        <v>184</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>206</v>
+        <v>188</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>200</v>
+        <v>182</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>210</v>
+        <v>192</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>211</v>
+        <v>193</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>212</v>
+        <v>194</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>213</v>
+        <v>195</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>214</v>
+        <v>196</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>215</v>
+        <v>197</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>216</v>
+        <v>198</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>217</v>
+        <v>199</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>218</v>
+        <v>200</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>220</v>
+        <v>202</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>221</v>
+        <v>203</v>
       </c>
     </row>
   </sheetData>
@@ -14004,36 +14454,36 @@
         <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>222</v>
+        <v>204</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>223</v>
+        <v>205</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -14259,80 +14709,80 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>225</v>
+        <v>207</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>226</v>
+        <v>208</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>227</v>
+        <v>209</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>228</v>
+        <v>210</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>229</v>
+        <v>211</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>230</v>
+        <v>212</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>231</v>
+        <v>213</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>232</v>
+        <v>214</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>233</v>
+        <v>215</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>234</v>
+        <v>216</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>235</v>
+        <v>217</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>236</v>
+        <v>218</v>
       </c>
     </row>
   </sheetData>
@@ -14375,36 +14825,36 @@
         <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>237</v>
+        <v>219</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>238</v>
+        <v>220</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>239</v>
+        <v>221</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -14630,132 +15080,132 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>240</v>
+        <v>222</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>241</v>
+        <v>223</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>242</v>
+        <v>224</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>243</v>
+        <v>225</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>244</v>
+        <v>226</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>246</v>
+        <v>228</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>245</v>
+        <v>227</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>247</v>
+        <v>229</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
-        <v>248</v>
+        <v>230</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>249</v>
+        <v>231</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>250</v>
+        <v>232</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>251</v>
+        <v>233</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>252</v>
+        <v>234</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>253</v>
+        <v>235</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>255</v>
+        <v>237</v>
       </c>
     </row>
     <row r="7" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>256</v>
+        <v>238</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>258</v>
+        <v>240</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>259</v>
+        <v>241</v>
       </c>
     </row>
   </sheetData>
@@ -14799,36 +15249,36 @@
         <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>260</v>
+        <v>242</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>261</v>
+        <v>243</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>262</v>
+        <v>244</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -15054,106 +15504,106 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>263</v>
+        <v>245</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>264</v>
+        <v>246</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>265</v>
+        <v>247</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>266</v>
+        <v>248</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>267</v>
+        <v>249</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>268</v>
+        <v>250</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>269</v>
+        <v>251</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>270</v>
+        <v>252</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
-        <v>271</v>
+        <v>253</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>272</v>
+        <v>254</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>273</v>
+        <v>255</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>274</v>
+        <v>256</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>275</v>
+        <v>257</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>276</v>
+        <v>258</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>277</v>
+        <v>259</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>278</v>
+        <v>260</v>
       </c>
     </row>
   </sheetData>
@@ -15196,36 +15646,36 @@
         <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>279</v>
+        <v>261</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>280</v>
+        <v>262</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>281</v>
+        <v>263</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -15451,80 +15901,80 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>282</v>
+        <v>264</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>283</v>
+        <v>265</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>284</v>
+        <v>266</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>285</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>286</v>
+        <v>268</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>288</v>
+        <v>270</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>290</v>
+        <v>272</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>291</v>
+        <v>273</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>292</v>
+        <v>274</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>293</v>
+        <v>275</v>
       </c>
     </row>
   </sheetData>
@@ -15567,36 +16017,36 @@
         <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>294</v>
+        <v>276</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>295</v>
+        <v>277</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>296</v>
+        <v>278</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -15822,132 +16272,132 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>297</v>
+        <v>279</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>298</v>
+        <v>280</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>299</v>
+        <v>281</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>300</v>
+        <v>282</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>301</v>
+        <v>283</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>302</v>
+        <v>284</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>303</v>
+        <v>285</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>304</v>
+        <v>286</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
-        <v>305</v>
+        <v>287</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>306</v>
+        <v>288</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>307</v>
+        <v>289</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>308</v>
+        <v>290</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>309</v>
+        <v>291</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>311</v>
+        <v>293</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>310</v>
+        <v>292</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>312</v>
+        <v>294</v>
       </c>
     </row>
     <row r="7" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>313</v>
+        <v>295</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>314</v>
+        <v>296</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>315</v>
+        <v>297</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>316</v>
+        <v>298</v>
       </c>
     </row>
   </sheetData>
@@ -15990,82 +16440,82 @@
     </row>
     <row r="2" spans="1:1029" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>341</v>
+        <v>323</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>702</v>
+        <v>684</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>703</v>
+        <v>685</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>340</v>
+        <v>322</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>342</v>
+        <v>324</v>
       </c>
     </row>
     <row r="3" spans="1:1029" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>422</v>
+        <v>404</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>704</v>
+        <v>686</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>705</v>
+        <v>687</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>340</v>
+        <v>322</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>423</v>
+        <v>405</v>
       </c>
     </row>
     <row r="4" spans="1:1029" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>706</v>
+        <v>688</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>707</v>
+        <v>689</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>340</v>
+        <v>322</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:1029" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>413</v>
+        <v>395</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>708</v>
+        <v>690</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>709</v>
+        <v>691</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>340</v>
+        <v>322</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>414</v>
+        <v>396</v>
       </c>
       <c r="G5"/>
       <c r="H5"/>
@@ -17093,62 +17543,62 @@
     </row>
     <row r="6" spans="1:1029" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>424</v>
+        <v>406</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>710</v>
+        <v>692</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>711</v>
+        <v>693</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>340</v>
+        <v>322</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>425</v>
+        <v>407</v>
       </c>
     </row>
     <row r="7" spans="1:1029" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>712</v>
+        <v>694</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>713</v>
+        <v>695</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>340</v>
+        <v>322</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:1029" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>415</v>
+        <v>397</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>714</v>
+        <v>696</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>715</v>
+        <v>697</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>340</v>
+        <v>322</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>420</v>
+        <v>402</v>
       </c>
       <c r="G8"/>
       <c r="H8"/>
@@ -18176,82 +18626,82 @@
     </row>
     <row r="9" spans="1:1029" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>416</v>
+        <v>398</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>716</v>
+        <v>698</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>717</v>
+        <v>699</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>340</v>
+        <v>322</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>417</v>
+        <v>399</v>
       </c>
     </row>
     <row r="10" spans="1:1029" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>418</v>
+        <v>400</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>718</v>
+        <v>700</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>719</v>
+        <v>701</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>340</v>
+        <v>322</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>419</v>
+        <v>401</v>
       </c>
     </row>
     <row r="11" spans="1:1029" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>426</v>
+        <v>408</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>720</v>
+        <v>702</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>721</v>
+        <v>703</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>340</v>
+        <v>322</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>427</v>
+        <v>409</v>
       </c>
     </row>
     <row r="12" spans="1:1029" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>722</v>
+        <v>704</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>723</v>
+        <v>705</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>340</v>
+        <v>322</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -18294,36 +18744,36 @@
         <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>317</v>
+        <v>299</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>318</v>
+        <v>300</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>319</v>
+        <v>301</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -18549,132 +18999,132 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>320</v>
+        <v>302</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>321</v>
+        <v>303</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>322</v>
+        <v>304</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>323</v>
+        <v>305</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>324</v>
+        <v>306</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>326</v>
+        <v>308</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>325</v>
+        <v>307</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
-        <v>328</v>
+        <v>310</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>329</v>
+        <v>311</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>330</v>
+        <v>312</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>331</v>
+        <v>313</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>332</v>
+        <v>314</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>334</v>
+        <v>316</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>333</v>
+        <v>315</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>335</v>
+        <v>317</v>
       </c>
     </row>
     <row r="7" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>336</v>
+        <v>318</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>337</v>
+        <v>319</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>338</v>
+        <v>320</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>339</v>
+        <v>321</v>
       </c>
     </row>
   </sheetData>
@@ -18717,36 +19167,36 @@
         <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>347</v>
+        <v>329</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>348</v>
+        <v>330</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>349</v>
+        <v>331</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>166</v>
+        <v>148</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -18972,210 +19422,210 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>350</v>
+        <v>332</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>351</v>
+        <v>333</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>352</v>
+        <v>334</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>353</v>
+        <v>335</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>354</v>
+        <v>336</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>355</v>
+        <v>337</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>356</v>
+        <v>338</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>357</v>
+        <v>339</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
-        <v>358</v>
+        <v>340</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>359</v>
+        <v>341</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>360</v>
+        <v>342</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>361</v>
+        <v>343</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>363</v>
+        <v>345</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>364</v>
+        <v>346</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>365</v>
+        <v>347</v>
       </c>
     </row>
     <row r="7" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>366</v>
+        <v>348</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>367</v>
+        <v>349</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>368</v>
+        <v>350</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>369</v>
+        <v>351</v>
       </c>
     </row>
     <row r="8" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>370</v>
+        <v>352</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>371</v>
+        <v>353</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>372</v>
+        <v>354</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>373</v>
+        <v>355</v>
       </c>
     </row>
     <row r="9" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>374</v>
+        <v>356</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>375</v>
+        <v>357</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>376</v>
+        <v>358</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>377</v>
+        <v>359</v>
       </c>
     </row>
     <row r="10" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>378</v>
+        <v>360</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>379</v>
+        <v>361</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>380</v>
+        <v>362</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>381</v>
+        <v>363</v>
       </c>
     </row>
   </sheetData>
@@ -19219,36 +19669,36 @@
         <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>382</v>
+        <v>364</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>384</v>
+        <v>366</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>177</v>
+        <v>159</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -19474,158 +19924,158 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>385</v>
+        <v>367</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>386</v>
+        <v>368</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>387</v>
+        <v>369</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>388</v>
+        <v>370</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>389</v>
+        <v>371</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>390</v>
+        <v>372</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>391</v>
+        <v>373</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>392</v>
+        <v>374</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
-        <v>393</v>
+        <v>375</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>394</v>
+        <v>376</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>395</v>
+        <v>377</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>396</v>
+        <v>378</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>397</v>
+        <v>379</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>398</v>
+        <v>380</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>399</v>
+        <v>381</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>400</v>
+        <v>382</v>
       </c>
     </row>
     <row r="7" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>401</v>
+        <v>383</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>402</v>
+        <v>384</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>403</v>
+        <v>385</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>404</v>
+        <v>386</v>
       </c>
     </row>
     <row r="8" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A8" s="9" t="s">
-        <v>405</v>
+        <v>387</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>406</v>
+        <v>388</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>407</v>
+        <v>389</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>408</v>
+        <v>390</v>
       </c>
     </row>
   </sheetData>
@@ -19669,36 +20119,36 @@
         <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>435</v>
+        <v>417</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>436</v>
+        <v>418</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>437</v>
+        <v>419</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -19924,184 +20374,184 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>438</v>
+        <v>420</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>439</v>
+        <v>421</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>440</v>
+        <v>422</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>441</v>
+        <v>423</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>442</v>
+        <v>424</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>445</v>
+        <v>427</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>443</v>
+        <v>425</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>444</v>
+        <v>426</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
-        <v>446</v>
+        <v>428</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>447</v>
+        <v>429</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>448</v>
+        <v>430</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>449</v>
+        <v>431</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>451</v>
+        <v>433</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>450</v>
+        <v>432</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>452</v>
+        <v>434</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>453</v>
+        <v>435</v>
       </c>
     </row>
     <row r="7" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>454</v>
+        <v>436</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>455</v>
+        <v>437</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>456</v>
+        <v>438</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>457</v>
+        <v>439</v>
       </c>
     </row>
     <row r="8" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>458</v>
+        <v>440</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>459</v>
+        <v>441</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>460</v>
+        <v>442</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>461</v>
+        <v>443</v>
       </c>
     </row>
     <row r="9" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>462</v>
+        <v>444</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>463</v>
+        <v>445</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>464</v>
+        <v>446</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>465</v>
+        <v>447</v>
       </c>
     </row>
   </sheetData>
@@ -20145,36 +20595,36 @@
         <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>466</v>
+        <v>448</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>467</v>
+        <v>449</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>468</v>
+        <v>450</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>469</v>
+        <v>451</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -20400,132 +20850,132 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>470</v>
+        <v>452</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>471</v>
+        <v>453</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>472</v>
+        <v>454</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>473</v>
+        <v>455</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>474</v>
+        <v>456</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>475</v>
+        <v>457</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>476</v>
+        <v>458</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>477</v>
+        <v>459</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
-        <v>478</v>
+        <v>460</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>479</v>
+        <v>461</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>480</v>
+        <v>462</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>481</v>
+        <v>463</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>482</v>
+        <v>464</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>483</v>
+        <v>465</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>484</v>
+        <v>466</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>485</v>
+        <v>467</v>
       </c>
     </row>
     <row r="7" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>487</v>
+        <v>469</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>486</v>
+        <v>468</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>488</v>
+        <v>470</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>489</v>
+        <v>471</v>
       </c>
     </row>
   </sheetData>
@@ -20568,36 +21018,36 @@
         <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>490</v>
+        <v>472</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>491</v>
+        <v>473</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>492</v>
+        <v>474</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>134</v>
+        <v>116</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -20861,36 +21311,36 @@
         <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>505</v>
+        <v>487</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>506</v>
+        <v>488</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>507</v>
+        <v>489</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>508</v>
+        <v>490</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -21116,262 +21566,262 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>510</v>
+        <v>492</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>509</v>
+        <v>491</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>511</v>
+        <v>493</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>512</v>
+        <v>494</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>513</v>
+        <v>495</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>514</v>
+        <v>496</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>515</v>
+        <v>497</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>516</v>
+        <v>498</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
-        <v>517</v>
+        <v>499</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>518</v>
+        <v>500</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>519</v>
+        <v>501</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>520</v>
+        <v>502</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>521</v>
+        <v>503</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>522</v>
+        <v>504</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>523</v>
+        <v>505</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>524</v>
+        <v>506</v>
       </c>
     </row>
     <row r="7" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>525</v>
+        <v>507</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>526</v>
+        <v>508</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>527</v>
+        <v>509</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>528</v>
+        <v>510</v>
       </c>
     </row>
     <row r="8" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>529</v>
+        <v>511</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>530</v>
+        <v>512</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>531</v>
+        <v>513</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>532</v>
+        <v>514</v>
       </c>
     </row>
     <row r="9" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>533</v>
+        <v>515</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>534</v>
+        <v>516</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>536</v>
+        <v>518</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>535</v>
+        <v>517</v>
       </c>
     </row>
     <row r="10" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>537</v>
+        <v>519</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>538</v>
+        <v>520</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>539</v>
+        <v>521</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>540</v>
+        <v>522</v>
       </c>
     </row>
     <row r="11" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>541</v>
+        <v>523</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>542</v>
+        <v>524</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>543</v>
+        <v>525</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>544</v>
+        <v>526</v>
       </c>
     </row>
     <row r="12" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>545</v>
+        <v>527</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>547</v>
+        <v>529</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>548</v>
+        <v>530</v>
       </c>
     </row>
   </sheetData>
@@ -21415,36 +21865,36 @@
         <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>554</v>
+        <v>536</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>555</v>
+        <v>537</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>556</v>
+        <v>538</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>557</v>
+        <v>539</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -21670,78 +22120,78 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>558</v>
+        <v>540</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>559</v>
+        <v>541</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>560</v>
+        <v>542</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>561</v>
+        <v>543</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="11" t="s">
-        <v>562</v>
+        <v>544</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>563</v>
+        <v>545</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>564</v>
+        <v>546</v>
       </c>
       <c r="D4" s="11" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H4" s="11"/>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>565</v>
+        <v>547</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>566</v>
+        <v>548</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>567</v>
+        <v>549</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>568</v>
+        <v>550</v>
       </c>
     </row>
   </sheetData>
@@ -21784,36 +22234,36 @@
         <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>572</v>
+        <v>554</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>573</v>
+        <v>555</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>574</v>
+        <v>556</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>575</v>
+        <v>557</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -22039,28 +22489,28 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>576</v>
+        <v>558</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>577</v>
+        <v>559</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>578</v>
+        <v>560</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>579</v>
+        <v>561</v>
       </c>
     </row>
   </sheetData>
@@ -22103,33 +22553,33 @@
         <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="11" t="s">
-        <v>585</v>
+        <v>567</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>586</v>
+        <v>568</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>587</v>
+        <v>569</v>
       </c>
       <c r="D2" s="11" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H2" s="11"/>
       <c r="I2"/>
@@ -22356,80 +22806,80 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>588</v>
+        <v>570</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>589</v>
+        <v>571</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>590</v>
+        <v>572</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>591</v>
+        <v>573</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>592</v>
+        <v>574</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>593</v>
+        <v>575</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>594</v>
+        <v>576</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>595</v>
+        <v>577</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>596</v>
+        <v>578</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>597</v>
+        <v>579</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>598</v>
+        <v>580</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>599</v>
+        <v>581</v>
       </c>
     </row>
   </sheetData>
@@ -22473,22 +22923,22 @@
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="G2"/>
       <c r="H2"/>
@@ -22716,22 +23166,22 @@
     </row>
     <row r="3" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="G3"/>
       <c r="H3"/>
@@ -22959,22 +23409,22 @@
     </row>
     <row r="4" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>343</v>
+        <v>325</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>344</v>
+        <v>326</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>345</v>
+        <v>327</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>346</v>
+        <v>328</v>
       </c>
       <c r="G4"/>
       <c r="H4"/>
@@ -23202,42 +23652,42 @@
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -23280,36 +23730,36 @@
         <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>605</v>
+        <v>587</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>606</v>
+        <v>588</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>607</v>
+        <v>589</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>608</v>
+        <v>590</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -23535,80 +23985,80 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>609</v>
+        <v>591</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>610</v>
+        <v>592</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>611</v>
+        <v>593</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>612</v>
+        <v>594</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>614</v>
+        <v>596</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>613</v>
+        <v>595</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>615</v>
+        <v>597</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>616</v>
+        <v>598</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>617</v>
+        <v>599</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>618</v>
+        <v>600</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>619</v>
+        <v>601</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>620</v>
+        <v>602</v>
       </c>
     </row>
   </sheetData>
@@ -23651,36 +24101,36 @@
         <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>628</v>
+        <v>610</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>629</v>
+        <v>611</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>630</v>
+        <v>612</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>631</v>
+        <v>613</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -23906,132 +24356,132 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>633</v>
+        <v>615</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>632</v>
+        <v>614</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>634</v>
+        <v>616</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>635</v>
+        <v>617</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>636</v>
+        <v>618</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>637</v>
+        <v>619</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>638</v>
+        <v>620</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>639</v>
+        <v>621</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>640</v>
+        <v>622</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>641</v>
+        <v>623</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>642</v>
+        <v>624</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>643</v>
+        <v>625</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>644</v>
+        <v>626</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>645</v>
+        <v>627</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>646</v>
+        <v>628</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>647</v>
+        <v>629</v>
       </c>
     </row>
     <row r="7" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>648</v>
+        <v>630</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>649</v>
+        <v>631</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>650</v>
+        <v>632</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>651</v>
+        <v>633</v>
       </c>
     </row>
   </sheetData>
@@ -24075,267 +24525,267 @@
         <v>35</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
     </row>
     <row r="2" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>666</v>
+        <v>648</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>667</v>
+        <v>649</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>668</v>
+        <v>650</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>669</v>
+        <v>651</v>
       </c>
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>670</v>
+        <v>652</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>671</v>
+        <v>653</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>672</v>
+        <v>654</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>673</v>
+        <v>655</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="8" t="s">
-        <v>674</v>
+        <v>656</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>675</v>
+        <v>657</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>676</v>
+        <v>658</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>677</v>
+        <v>659</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>678</v>
+        <v>660</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>679</v>
+        <v>661</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>680</v>
+        <v>662</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>681</v>
+        <v>663</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>682</v>
+        <v>664</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>683</v>
+        <v>665</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>684</v>
+        <v>666</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>685</v>
+        <v>667</v>
       </c>
     </row>
     <row r="7" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>686</v>
+        <v>668</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>687</v>
+        <v>669</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>688</v>
+        <v>670</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>689</v>
+        <v>671</v>
       </c>
     </row>
     <row r="8" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>690</v>
+        <v>672</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>691</v>
+        <v>673</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>692</v>
+        <v>674</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>693</v>
+        <v>675</v>
       </c>
     </row>
     <row r="9" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>694</v>
+        <v>676</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>695</v>
+        <v>677</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>696</v>
+        <v>678</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>697</v>
+        <v>679</v>
       </c>
     </row>
     <row r="10" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>699</v>
+        <v>681</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>698</v>
+        <v>680</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>700</v>
+        <v>682</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>701</v>
+        <v>683</v>
       </c>
     </row>
     <row r="11" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>663</v>
+        <v>645</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>664</v>
+        <v>646</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>665</v>
+        <v>647</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="H11" s="11"/>
       <c r="I11"/>
@@ -24577,71 +25027,71 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -24660,64 +25110,64 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -24736,78 +25186,78 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -24827,71 +25277,71 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -24911,92 +25361,92 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>132</v>
+        <v>114</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>134</v>
+        <v>116</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>139</v>
+        <v>121</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>

--- a/testdata.xlsx
+++ b/testdata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sshiwani\workspace\find-information-products-services-tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FD55A19-F542-4D27-85D3-F48791966A1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3F0D659-6032-43B9-81B8-4909DFB63D94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="category_phase" sheetId="1" r:id="rId1"/>
@@ -77,84 +77,42 @@
     <t>products?phase=discovery</t>
   </si>
   <si>
-    <t>ul.moj-filter-tags li a:has-text('Discovery')</t>
-  </si>
-  <si>
-    <t>Remove this filter Discovery</t>
-  </si>
-  <si>
     <t>#phase-discovery</t>
   </si>
   <si>
     <t>products?phase=alpha</t>
   </si>
   <si>
-    <t>ul.moj-filter-tags li a:has-text('Alpha')</t>
-  </si>
-  <si>
-    <t>Remove this filter Alpha</t>
-  </si>
-  <si>
     <t>#phase-alpha</t>
   </si>
   <si>
     <t>products?phase=private-beta</t>
   </si>
   <si>
-    <t>ul.moj-filter-tags li a:has-text('Private beta')</t>
-  </si>
-  <si>
-    <t>Remove this filter Private beta</t>
-  </si>
-  <si>
     <t>#phase-private-beta</t>
   </si>
   <si>
     <t>products?phase=public-beta</t>
   </si>
   <si>
-    <t>ul.moj-filter-tags li a:has-text('Public beta')</t>
-  </si>
-  <si>
-    <t>Remove this filter Public beta</t>
-  </si>
-  <si>
     <t>#phase-public-beta</t>
   </si>
   <si>
     <t>products?phase=live</t>
   </si>
   <si>
-    <t>ul.moj-filter-tags li a:has-text('Live')</t>
-  </si>
-  <si>
-    <t>Remove this filter Live</t>
-  </si>
-  <si>
     <t>#phase-live</t>
   </si>
   <si>
     <t>products?phase=decommissioning</t>
   </si>
   <si>
-    <t>ul.moj-filter-tags li a:has-text('Decommissioning')</t>
-  </si>
-  <si>
-    <t>Remove this filter Decommissioning</t>
-  </si>
-  <si>
     <t>#phase-decommissioning</t>
   </si>
   <si>
     <t>products?phase=decommissioned</t>
   </si>
   <si>
-    <t>ul.moj-filter-tags li a:has-text('Decommissioned')</t>
-  </si>
-  <si>
-    <t>Remove this filter Decommissioned</t>
-  </si>
-  <si>
     <t>#phase-decommissioned</t>
   </si>
   <si>
@@ -1244,12 +1202,6 @@
     <t>products?phase=did-not-progress</t>
   </si>
   <si>
-    <t>ul.moj-filter-tags li a:has-text(' Did not progress')</t>
-  </si>
-  <si>
-    <t>Remove this filter Did not progress</t>
-  </si>
-  <si>
     <t>#phase-did-not-progress</t>
   </si>
   <si>
@@ -2120,72 +2072,6 @@
     <t>Teaching assistant  (School workforce)</t>
   </si>
   <si>
-    <t>ul.moj-filter-tags li a:has-text('  Commercial')</t>
-  </si>
-  <si>
-    <t>Remove this filter Commercial</t>
-  </si>
-  <si>
-    <t>ul.moj-filter-tags li a:has-text(' Customer Experience and Design')</t>
-  </si>
-  <si>
-    <t>Remove this filter Customer Experience and Design</t>
-  </si>
-  <si>
-    <t>ul.moj-filter-tags li a:has-text(' Enterprise Data')</t>
-  </si>
-  <si>
-    <t>Remove this filter Enterprise Data</t>
-  </si>
-  <si>
-    <t>ul.moj-filter-tags li a:has-text(' Children and Families')</t>
-  </si>
-  <si>
-    <t>Remove this filter Children and Families</t>
-  </si>
-  <si>
-    <t>ul.moj-filter-tags li a:has-text(' Funding and Financial Oversight')</t>
-  </si>
-  <si>
-    <t>Remove this filter Funding and Financial Oversight</t>
-  </si>
-  <si>
-    <t>ul.moj-filter-tags li a:has-text(' Operations and Infrastructure')</t>
-  </si>
-  <si>
-    <t>Remove this filter Operations and Infrastructure</t>
-  </si>
-  <si>
-    <t>ul.moj-filter-tags li a:has-text(' Regional Digital Services')</t>
-  </si>
-  <si>
-    <t>Remove this filter Regional Digital Services</t>
-  </si>
-  <si>
-    <t>ul.moj-filter-tags li a:has-text(' Schools Digital')</t>
-  </si>
-  <si>
-    <t>Remove this filter Schools Digital</t>
-  </si>
-  <si>
-    <t>ul.moj-filter-tags li a:has-text(' Sector Facing Services')</t>
-  </si>
-  <si>
-    <t>Remove this filter Sector Facing Services</t>
-  </si>
-  <si>
-    <t>ul.moj-filter-tags li a:has-text(' Skills and Growth')</t>
-  </si>
-  <si>
-    <t>Remove this filter Skills and Growth</t>
-  </si>
-  <si>
-    <t>ul.moj-filter-tags li a:has-text(' Strategy')</t>
-  </si>
-  <si>
-    <t>Remove this filter Strategy</t>
-  </si>
-  <si>
     <t>a.filter-badge:has(span:text-is('Chat'))</t>
   </si>
   <si>
@@ -2238,6 +2124,120 @@
   </si>
   <si>
     <t>Web × Remove Web filter</t>
+  </si>
+  <si>
+    <t>a.filter-badge:has(span:text-is('Commercial'))</t>
+  </si>
+  <si>
+    <t>a.filter-badge:has(span:text-is('Customer Experience and Design'))</t>
+  </si>
+  <si>
+    <t>a.filter-badge:has(span:text-is('Enterprise Data'))</t>
+  </si>
+  <si>
+    <t>a.filter-badge:has(span:text-is('Children and Families'))</t>
+  </si>
+  <si>
+    <t>a.filter-badge:has(span:text-is('Funding and Financial Oversight'))</t>
+  </si>
+  <si>
+    <t>a.filter-badge:has(span:text-is('Operations and Infrastructure'))</t>
+  </si>
+  <si>
+    <t>a.filter-badge:has(span:text-is('Regional Digital Services'))</t>
+  </si>
+  <si>
+    <t>a.filter-badge:has(span:text-is('Schools Digital'))</t>
+  </si>
+  <si>
+    <t>a.filter-badge:has(span:text-is('Sector Facing Services'))</t>
+  </si>
+  <si>
+    <t>a.filter-badge:has(span:text-is('Skills and Growth'))</t>
+  </si>
+  <si>
+    <t>a.filter-badge:has(span:text-is('Strategy'))</t>
+  </si>
+  <si>
+    <t>Commercial × Remove Commercial filter</t>
+  </si>
+  <si>
+    <t>Customer Experience and Design × Remove Customer Experience and Design filter</t>
+  </si>
+  <si>
+    <t>Children and Families × Remove Children and Families filter</t>
+  </si>
+  <si>
+    <t>Enterprise Data × Remove Enterprise Data filter</t>
+  </si>
+  <si>
+    <t>Funding and Financial Oversight × Remove Funding and Financial Oversight filter</t>
+  </si>
+  <si>
+    <t>Operations and Infrastructure × Remove Operations and Infrastructure filter</t>
+  </si>
+  <si>
+    <t>Regional Digital Services × Remove Regional Digital Services filter</t>
+  </si>
+  <si>
+    <t>Schools Digital × Remove Schools Digital filter</t>
+  </si>
+  <si>
+    <t>Sector Facing Services × Remove Sector Facing Services filter</t>
+  </si>
+  <si>
+    <t>Skills and Growth × Remove Skills and Growth filter</t>
+  </si>
+  <si>
+    <t>Strategy × Remove Strategy filter</t>
+  </si>
+  <si>
+    <t>a.filter-badge:has(span:text-is('Discovery'))</t>
+  </si>
+  <si>
+    <t>a.filter-badge:has(span:text-is('Alpha'))</t>
+  </si>
+  <si>
+    <t>a.filter-badge:has(span:text-is('Did not progress'))</t>
+  </si>
+  <si>
+    <t>a.filter-badge:has(span:text-is('Private beta'))</t>
+  </si>
+  <si>
+    <t>a.filter-badge:has(span:text-is('Public beta'))</t>
+  </si>
+  <si>
+    <t>a.filter-badge:has(span:text-is('Live'))</t>
+  </si>
+  <si>
+    <t>a.filter-badge:has(span:text-is('Decommissioning'))</t>
+  </si>
+  <si>
+    <t>a.filter-badge:has(span:text-is('Decommissioned'))</t>
+  </si>
+  <si>
+    <t>Discovery × Remove Discovery filter</t>
+  </si>
+  <si>
+    <t>Alpha × Remove Alpha filter</t>
+  </si>
+  <si>
+    <t>Did not progress × Remove Did not progress filter</t>
+  </si>
+  <si>
+    <t>Private beta × Remove Private beta filter</t>
+  </si>
+  <si>
+    <t>Public beta × Remove Public beta filter</t>
+  </si>
+  <si>
+    <t>Live × Remove Live filter</t>
+  </si>
+  <si>
+    <t>Decommissioning × Remove Decommissioning filter</t>
+  </si>
+  <si>
+    <t>Decommissioned × Remove Decommissioned filter</t>
   </si>
 </sst>
 </file>
@@ -2691,22 +2691,22 @@
   <sheetData>
     <row r="1" spans="1:1149" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:1149" s="5" customFormat="1" x14ac:dyDescent="0.35">
@@ -2714,10 +2714,10 @@
         <v>2</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>3</v>
+        <v>708</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>4</v>
+        <v>716</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
@@ -2726,7 +2726,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G2"/>
       <c r="H2"/>
@@ -3874,13 +3874,13 @@
     </row>
     <row r="3" spans="1:1149" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>7</v>
+        <v>709</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>8</v>
+        <v>717</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
@@ -3889,7 +3889,7 @@
         <v>1</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G3"/>
       <c r="H3"/>
@@ -5037,13 +5037,13 @@
     </row>
     <row r="4" spans="1:1149" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>391</v>
+        <v>377</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>392</v>
+        <v>710</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>393</v>
+        <v>718</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
@@ -5052,7 +5052,7 @@
         <v>1</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>394</v>
+        <v>378</v>
       </c>
       <c r="G4"/>
       <c r="H4"/>
@@ -6200,13 +6200,13 @@
     </row>
     <row r="5" spans="1:1149" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>11</v>
+        <v>711</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>12</v>
+        <v>719</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
@@ -6215,7 +6215,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="G5"/>
       <c r="H5"/>
@@ -7363,13 +7363,13 @@
     </row>
     <row r="6" spans="1:1149" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>15</v>
+        <v>712</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>16</v>
+        <v>720</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>0</v>
@@ -7378,7 +7378,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="G6"/>
       <c r="H6"/>
@@ -8526,13 +8526,13 @@
     </row>
     <row r="7" spans="1:1149" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>19</v>
+        <v>713</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>20</v>
+        <v>721</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>0</v>
@@ -8541,7 +8541,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="G7"/>
       <c r="H7"/>
@@ -9689,13 +9689,13 @@
     </row>
     <row r="8" spans="1:1149" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>23</v>
+        <v>714</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>24</v>
+        <v>722</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>0</v>
@@ -9704,7 +9704,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="G8"/>
       <c r="H8"/>
@@ -10852,13 +10852,13 @@
     </row>
     <row r="9" spans="1:1149" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>27</v>
+        <v>715</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>28</v>
+        <v>723</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>0</v>
@@ -10867,7 +10867,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="G9"/>
       <c r="H9"/>
@@ -12030,64 +12030,64 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>
@@ -12107,78 +12107,78 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -12199,78 +12199,78 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -12290,99 +12290,99 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>152</v>
+        <v>138</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>154</v>
+        <v>140</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>155</v>
+        <v>141</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -12402,85 +12402,85 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>164</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -12500,99 +12500,99 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>169</v>
+        <v>155</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>170</v>
+        <v>156</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>171</v>
+        <v>157</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>175</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>176</v>
+        <v>162</v>
       </c>
     </row>
   </sheetData>
@@ -12612,80 +12612,80 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>410</v>
+        <v>394</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>411</v>
+        <v>395</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>412</v>
+        <v>396</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>413</v>
+        <v>397</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>414</v>
+        <v>398</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>415</v>
+        <v>399</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>416</v>
+        <v>400</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -12707,115 +12707,115 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>475</v>
+        <v>459</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>476</v>
+        <v>460</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>477</v>
+        <v>461</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>478</v>
+        <v>462</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>479</v>
+        <v>463</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>480</v>
+        <v>464</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>481</v>
+        <v>465</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>482</v>
+        <v>466</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>483</v>
+        <v>467</v>
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>484</v>
+        <v>468</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>485</v>
+        <v>469</v>
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
-        <v>486</v>
+        <v>470</v>
       </c>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -12837,66 +12837,66 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>531</v>
+        <v>515</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>532</v>
+        <v>516</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>533</v>
+        <v>517</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>534</v>
+        <v>518</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>535</v>
+        <v>519</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -12918,52 +12918,52 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>551</v>
+        <v>535</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>552</v>
+        <v>536</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>553</v>
+        <v>537</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -12988,42 +12988,42 @@
   <sheetData>
     <row r="1" spans="1:56" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:56" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>706</v>
+        <v>668</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>715</v>
+        <v>677</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="G2"/>
       <c r="H2"/>
@@ -13078,22 +13078,22 @@
     </row>
     <row r="3" spans="1:56" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>707</v>
+        <v>669</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>716</v>
+        <v>678</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="G3"/>
       <c r="H3"/>
@@ -13148,22 +13148,22 @@
     </row>
     <row r="4" spans="1:56" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>708</v>
+        <v>670</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>717</v>
+        <v>679</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="G4"/>
       <c r="H4"/>
@@ -13218,22 +13218,22 @@
     </row>
     <row r="5" spans="1:56" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>709</v>
+        <v>671</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>718</v>
+        <v>680</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="G5"/>
       <c r="H5"/>
@@ -13288,22 +13288,22 @@
     </row>
     <row r="6" spans="1:56" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>710</v>
+        <v>672</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>719</v>
+        <v>681</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="G6"/>
       <c r="H6"/>
@@ -13358,22 +13358,22 @@
     </row>
     <row r="7" spans="1:56" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>711</v>
+        <v>673</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>720</v>
+        <v>682</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="G7"/>
       <c r="H7"/>
@@ -13428,22 +13428,22 @@
     </row>
     <row r="8" spans="1:56" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>712</v>
+        <v>674</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>721</v>
+        <v>683</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="G8"/>
       <c r="H8"/>
@@ -13498,22 +13498,22 @@
     </row>
     <row r="9" spans="1:56" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>713</v>
+        <v>675</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>722</v>
+        <v>684</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="G9"/>
       <c r="H9"/>
@@ -13568,22 +13568,22 @@
     </row>
     <row r="10" spans="1:56" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>714</v>
+        <v>676</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>723</v>
+        <v>685</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="G10"/>
       <c r="H10"/>
@@ -13653,66 +13653,66 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>562</v>
+        <v>546</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>563</v>
+        <v>547</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>564</v>
+        <v>548</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>565</v>
+        <v>549</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>566</v>
+        <v>550</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -13734,66 +13734,66 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>582</v>
+        <v>566</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>583</v>
+        <v>567</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>584</v>
+        <v>568</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>585</v>
+        <v>569</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>586</v>
+        <v>570</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -13815,80 +13815,80 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>603</v>
+        <v>587</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>604</v>
+        <v>588</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>605</v>
+        <v>589</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>606</v>
+        <v>590</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>607</v>
+        <v>591</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>608</v>
+        <v>592</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>609</v>
+        <v>593</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -13910,108 +13910,108 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>634</v>
+        <v>618</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>635</v>
+        <v>619</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>636</v>
+        <v>620</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>637</v>
+        <v>621</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>638</v>
+        <v>622</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>639</v>
+        <v>623</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>640</v>
+        <v>624</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>641</v>
+        <v>625</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>642</v>
+        <v>626</v>
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>643</v>
+        <v>627</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>644</v>
+        <v>628</v>
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -14038,54 +14038,54 @@
   <sheetData>
     <row r="1" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>180</v>
+        <v>166</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>179</v>
+        <v>165</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>403</v>
+        <v>387</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -14311,106 +14311,106 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F4" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>192</v>
-      </c>
       <c r="H4" s="3" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>194</v>
+        <v>180</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>197</v>
+        <v>183</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>200</v>
+        <v>186</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>201</v>
+        <v>187</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>202</v>
+        <v>188</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>203</v>
+        <v>189</v>
       </c>
     </row>
   </sheetData>
@@ -14436,54 +14436,54 @@
   <sheetData>
     <row r="1" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>205</v>
+        <v>191</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -14709,80 +14709,80 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>207</v>
+        <v>193</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>208</v>
+        <v>194</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>209</v>
+        <v>195</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>210</v>
+        <v>196</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>217</v>
+        <v>203</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
     </row>
   </sheetData>
@@ -14807,54 +14807,54 @@
   <sheetData>
     <row r="1" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -15080,132 +15080,132 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>223</v>
+        <v>209</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>226</v>
+        <v>212</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>227</v>
+        <v>213</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>229</v>
+        <v>215</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>231</v>
+        <v>217</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>232</v>
+        <v>218</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>233</v>
+        <v>219</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>234</v>
+        <v>220</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>235</v>
+        <v>221</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>236</v>
+        <v>222</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>237</v>
+        <v>223</v>
       </c>
     </row>
     <row r="7" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>239</v>
+        <v>225</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>241</v>
+        <v>227</v>
       </c>
     </row>
   </sheetData>
@@ -15231,54 +15231,54 @@
   <sheetData>
     <row r="1" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>244</v>
+        <v>230</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -15504,106 +15504,106 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>250</v>
+        <v>236</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>254</v>
+        <v>240</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>256</v>
+        <v>242</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>257</v>
+        <v>243</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>258</v>
+        <v>244</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>259</v>
+        <v>245</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>260</v>
+        <v>246</v>
       </c>
     </row>
   </sheetData>
@@ -15628,54 +15628,54 @@
   <sheetData>
     <row r="1" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>261</v>
+        <v>247</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>262</v>
+        <v>248</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>263</v>
+        <v>249</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -15901,80 +15901,80 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>264</v>
+        <v>250</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>266</v>
+        <v>252</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>267</v>
+        <v>253</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>268</v>
+        <v>254</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>269</v>
+        <v>255</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>270</v>
+        <v>256</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>271</v>
+        <v>257</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>272</v>
+        <v>258</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>273</v>
+        <v>259</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>274</v>
+        <v>260</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>275</v>
+        <v>261</v>
       </c>
     </row>
   </sheetData>
@@ -15999,54 +15999,54 @@
   <sheetData>
     <row r="1" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>276</v>
+        <v>262</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>277</v>
+        <v>263</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>278</v>
+        <v>264</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -16272,132 +16272,132 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>279</v>
+        <v>265</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>280</v>
+        <v>266</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>281</v>
+        <v>267</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>282</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>283</v>
+        <v>269</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>284</v>
+        <v>270</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>285</v>
+        <v>271</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>286</v>
+        <v>272</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
-        <v>287</v>
+        <v>273</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>288</v>
+        <v>274</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>289</v>
+        <v>275</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>290</v>
+        <v>276</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>293</v>
+        <v>279</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>292</v>
+        <v>278</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>294</v>
+        <v>280</v>
       </c>
     </row>
     <row r="7" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>295</v>
+        <v>281</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>296</v>
+        <v>282</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>297</v>
+        <v>283</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>298</v>
+        <v>284</v>
       </c>
     </row>
   </sheetData>
@@ -16420,102 +16420,102 @@
   <sheetData>
     <row r="1" spans="1:1029" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:1029" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>323</v>
+        <v>309</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>685</v>
+        <v>697</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>322</v>
+        <v>308</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>324</v>
+        <v>310</v>
       </c>
     </row>
     <row r="3" spans="1:1029" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>404</v>
+        <v>388</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>687</v>
+        <v>698</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>322</v>
+        <v>308</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>405</v>
+        <v>389</v>
       </c>
     </row>
     <row r="4" spans="1:1029" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>688</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>689</v>
+        <v>700</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>322</v>
+        <v>308</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:1029" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>395</v>
+        <v>379</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>691</v>
+        <v>699</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>322</v>
+        <v>308</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>396</v>
+        <v>380</v>
       </c>
       <c r="G5"/>
       <c r="H5"/>
@@ -17543,62 +17543,62 @@
     </row>
     <row r="6" spans="1:1029" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>406</v>
+        <v>390</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>693</v>
+        <v>701</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>322</v>
+        <v>308</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>407</v>
+        <v>391</v>
       </c>
     </row>
     <row r="7" spans="1:1029" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>695</v>
+        <v>702</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>322</v>
+        <v>308</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:1029" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>397</v>
+        <v>381</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>696</v>
+        <v>692</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>697</v>
+        <v>703</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>322</v>
+        <v>308</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>402</v>
+        <v>386</v>
       </c>
       <c r="G8"/>
       <c r="H8"/>
@@ -18626,82 +18626,82 @@
     </row>
     <row r="9" spans="1:1029" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>398</v>
+        <v>382</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>698</v>
+        <v>693</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>699</v>
+        <v>704</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>322</v>
+        <v>308</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>399</v>
+        <v>383</v>
       </c>
     </row>
     <row r="10" spans="1:1029" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>400</v>
+        <v>384</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>700</v>
+        <v>694</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>322</v>
+        <v>308</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>401</v>
+        <v>385</v>
       </c>
     </row>
     <row r="11" spans="1:1029" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>408</v>
+        <v>392</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>702</v>
+        <v>695</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>322</v>
+        <v>308</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>409</v>
+        <v>393</v>
       </c>
     </row>
     <row r="12" spans="1:1029" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>704</v>
+        <v>696</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>322</v>
+        <v>308</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -18726,54 +18726,54 @@
   <sheetData>
     <row r="1" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>299</v>
+        <v>285</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>300</v>
+        <v>286</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>301</v>
+        <v>287</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -18999,132 +18999,132 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>302</v>
+        <v>288</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>303</v>
+        <v>289</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>304</v>
+        <v>290</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>305</v>
+        <v>291</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>306</v>
+        <v>292</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>308</v>
+        <v>294</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>307</v>
+        <v>293</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>309</v>
+        <v>295</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
-        <v>310</v>
+        <v>296</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>311</v>
+        <v>297</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>312</v>
+        <v>298</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>313</v>
+        <v>299</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>314</v>
+        <v>300</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>316</v>
+        <v>302</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>315</v>
+        <v>301</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>317</v>
+        <v>303</v>
       </c>
     </row>
     <row r="7" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>318</v>
+        <v>304</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>319</v>
+        <v>305</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>320</v>
+        <v>306</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>321</v>
+        <v>307</v>
       </c>
     </row>
   </sheetData>
@@ -19149,54 +19149,54 @@
   <sheetData>
     <row r="1" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>329</v>
+        <v>315</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>330</v>
+        <v>316</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>331</v>
+        <v>317</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -19422,210 +19422,210 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>332</v>
+        <v>318</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>333</v>
+        <v>319</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>334</v>
+        <v>320</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>335</v>
+        <v>321</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>336</v>
+        <v>322</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>337</v>
+        <v>323</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>338</v>
+        <v>324</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>339</v>
+        <v>325</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
-        <v>340</v>
+        <v>326</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>341</v>
+        <v>327</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>342</v>
+        <v>328</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>343</v>
+        <v>329</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>344</v>
+        <v>330</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>345</v>
+        <v>331</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>346</v>
+        <v>332</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>347</v>
+        <v>333</v>
       </c>
     </row>
     <row r="7" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>348</v>
+        <v>334</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>349</v>
+        <v>335</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>350</v>
+        <v>336</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>351</v>
+        <v>337</v>
       </c>
     </row>
     <row r="8" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>352</v>
+        <v>338</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>353</v>
+        <v>339</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>354</v>
+        <v>340</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>355</v>
+        <v>341</v>
       </c>
     </row>
     <row r="9" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>356</v>
+        <v>342</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>357</v>
+        <v>343</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>358</v>
+        <v>344</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>359</v>
+        <v>345</v>
       </c>
     </row>
     <row r="10" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>360</v>
+        <v>346</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>361</v>
+        <v>347</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>362</v>
+        <v>348</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>363</v>
+        <v>349</v>
       </c>
     </row>
   </sheetData>
@@ -19651,54 +19651,54 @@
   <sheetData>
     <row r="1" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>364</v>
+        <v>350</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>365</v>
+        <v>351</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>366</v>
+        <v>352</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -19924,158 +19924,158 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>367</v>
+        <v>353</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>368</v>
+        <v>354</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>369</v>
+        <v>355</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>370</v>
+        <v>356</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>371</v>
+        <v>357</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>372</v>
+        <v>358</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>373</v>
+        <v>359</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>374</v>
+        <v>360</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
-        <v>375</v>
+        <v>361</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>376</v>
+        <v>362</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>377</v>
+        <v>363</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>378</v>
+        <v>364</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>379</v>
+        <v>365</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>380</v>
+        <v>366</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>381</v>
+        <v>367</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>382</v>
+        <v>368</v>
       </c>
     </row>
     <row r="7" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>383</v>
+        <v>369</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>384</v>
+        <v>370</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>385</v>
+        <v>371</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>386</v>
+        <v>372</v>
       </c>
     </row>
     <row r="8" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A8" s="9" t="s">
-        <v>387</v>
+        <v>373</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>388</v>
+        <v>374</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>389</v>
+        <v>375</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>390</v>
+        <v>376</v>
       </c>
     </row>
   </sheetData>
@@ -20101,54 +20101,54 @@
   <sheetData>
     <row r="1" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>417</v>
+        <v>401</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>418</v>
+        <v>402</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>419</v>
+        <v>403</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -20374,184 +20374,184 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>420</v>
+        <v>404</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>421</v>
+        <v>405</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>422</v>
+        <v>406</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>423</v>
+        <v>407</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>424</v>
+        <v>408</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>427</v>
+        <v>411</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>425</v>
+        <v>409</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>426</v>
+        <v>410</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
-        <v>428</v>
+        <v>412</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>429</v>
+        <v>413</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>430</v>
+        <v>414</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>431</v>
+        <v>415</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>433</v>
+        <v>417</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>432</v>
+        <v>416</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>434</v>
+        <v>418</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>435</v>
+        <v>419</v>
       </c>
     </row>
     <row r="7" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>436</v>
+        <v>420</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>437</v>
+        <v>421</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>438</v>
+        <v>422</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>439</v>
+        <v>423</v>
       </c>
     </row>
     <row r="8" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>440</v>
+        <v>424</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>441</v>
+        <v>425</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>442</v>
+        <v>426</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>443</v>
+        <v>427</v>
       </c>
     </row>
     <row r="9" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>444</v>
+        <v>428</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>445</v>
+        <v>429</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>446</v>
+        <v>430</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>447</v>
+        <v>431</v>
       </c>
     </row>
   </sheetData>
@@ -20577,54 +20577,54 @@
   <sheetData>
     <row r="1" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>448</v>
+        <v>432</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>449</v>
+        <v>433</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>450</v>
+        <v>434</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>451</v>
+        <v>435</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -20850,132 +20850,132 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>452</v>
+        <v>436</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>453</v>
+        <v>437</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>454</v>
+        <v>438</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>455</v>
+        <v>439</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>456</v>
+        <v>440</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>457</v>
+        <v>441</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>458</v>
+        <v>442</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>459</v>
+        <v>443</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
-        <v>460</v>
+        <v>444</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>461</v>
+        <v>445</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>462</v>
+        <v>446</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>463</v>
+        <v>447</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>464</v>
+        <v>448</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>465</v>
+        <v>449</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>466</v>
+        <v>450</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>467</v>
+        <v>451</v>
       </c>
     </row>
     <row r="7" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>469</v>
+        <v>453</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>468</v>
+        <v>452</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>470</v>
+        <v>454</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>471</v>
+        <v>455</v>
       </c>
     </row>
   </sheetData>
@@ -21000,54 +21000,54 @@
   <sheetData>
     <row r="1" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>472</v>
+        <v>456</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>473</v>
+        <v>457</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>474</v>
+        <v>458</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -21293,54 +21293,54 @@
   <sheetData>
     <row r="1" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>487</v>
+        <v>471</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>488</v>
+        <v>472</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>489</v>
+        <v>473</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>490</v>
+        <v>474</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -21566,262 +21566,262 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>492</v>
+        <v>476</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>491</v>
+        <v>475</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>493</v>
+        <v>477</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>494</v>
+        <v>478</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>495</v>
+        <v>479</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>496</v>
+        <v>480</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>497</v>
+        <v>481</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>498</v>
+        <v>482</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
-        <v>499</v>
+        <v>483</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>500</v>
+        <v>484</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>501</v>
+        <v>485</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>502</v>
+        <v>486</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>503</v>
+        <v>487</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>504</v>
+        <v>488</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>505</v>
+        <v>489</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>506</v>
+        <v>490</v>
       </c>
     </row>
     <row r="7" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>507</v>
+        <v>491</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>508</v>
+        <v>492</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>509</v>
+        <v>493</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>510</v>
+        <v>494</v>
       </c>
     </row>
     <row r="8" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>511</v>
+        <v>495</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>512</v>
+        <v>496</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>513</v>
+        <v>497</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>514</v>
+        <v>498</v>
       </c>
     </row>
     <row r="9" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>515</v>
+        <v>499</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>516</v>
+        <v>500</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>518</v>
+        <v>502</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>517</v>
+        <v>501</v>
       </c>
     </row>
     <row r="10" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>519</v>
+        <v>503</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>520</v>
+        <v>504</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>521</v>
+        <v>505</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>522</v>
+        <v>506</v>
       </c>
     </row>
     <row r="11" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>524</v>
+        <v>508</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>525</v>
+        <v>509</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>526</v>
+        <v>510</v>
       </c>
     </row>
     <row r="12" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>527</v>
+        <v>511</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>528</v>
+        <v>512</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>529</v>
+        <v>513</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>530</v>
+        <v>514</v>
       </c>
     </row>
   </sheetData>
@@ -21847,54 +21847,54 @@
   <sheetData>
     <row r="1" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>536</v>
+        <v>520</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>537</v>
+        <v>521</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>538</v>
+        <v>522</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>539</v>
+        <v>523</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -22120,78 +22120,78 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>540</v>
+        <v>524</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>541</v>
+        <v>525</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>542</v>
+        <v>526</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>543</v>
+        <v>527</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="11" t="s">
-        <v>544</v>
+        <v>528</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>545</v>
+        <v>529</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>546</v>
+        <v>530</v>
       </c>
       <c r="D4" s="11" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H4" s="11"/>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>547</v>
+        <v>531</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>548</v>
+        <v>532</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>549</v>
+        <v>533</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>550</v>
+        <v>534</v>
       </c>
     </row>
   </sheetData>
@@ -22216,54 +22216,54 @@
   <sheetData>
     <row r="1" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>554</v>
+        <v>538</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>555</v>
+        <v>539</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>556</v>
+        <v>540</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>557</v>
+        <v>541</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -22489,28 +22489,28 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>558</v>
+        <v>542</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>559</v>
+        <v>543</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>560</v>
+        <v>544</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>561</v>
+        <v>545</v>
       </c>
     </row>
   </sheetData>
@@ -22535,51 +22535,51 @@
   <sheetData>
     <row r="1" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="11" t="s">
-        <v>567</v>
+        <v>551</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>568</v>
+        <v>552</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>569</v>
+        <v>553</v>
       </c>
       <c r="D2" s="11" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H2" s="11"/>
       <c r="I2"/>
@@ -22806,80 +22806,80 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>570</v>
+        <v>554</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>571</v>
+        <v>555</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>572</v>
+        <v>556</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>573</v>
+        <v>557</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>574</v>
+        <v>558</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>575</v>
+        <v>559</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>576</v>
+        <v>560</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>577</v>
+        <v>561</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>578</v>
+        <v>562</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>579</v>
+        <v>563</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>580</v>
+        <v>564</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>581</v>
+        <v>565</v>
       </c>
     </row>
   </sheetData>
@@ -22903,42 +22903,42 @@
   <sheetData>
     <row r="1" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="G2"/>
       <c r="H2"/>
@@ -23166,22 +23166,22 @@
     </row>
     <row r="3" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="G3"/>
       <c r="H3"/>
@@ -23409,22 +23409,22 @@
     </row>
     <row r="4" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>325</v>
+        <v>311</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>327</v>
+        <v>313</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>328</v>
+        <v>314</v>
       </c>
       <c r="G4"/>
       <c r="H4"/>
@@ -23652,42 +23652,42 @@
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -23712,54 +23712,54 @@
   <sheetData>
     <row r="1" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>587</v>
+        <v>571</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>588</v>
+        <v>572</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>589</v>
+        <v>573</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>590</v>
+        <v>574</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -23985,80 +23985,80 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>591</v>
+        <v>575</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>592</v>
+        <v>576</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>593</v>
+        <v>577</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>594</v>
+        <v>578</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>596</v>
+        <v>580</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>595</v>
+        <v>579</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>597</v>
+        <v>581</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>598</v>
+        <v>582</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>599</v>
+        <v>583</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>600</v>
+        <v>584</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>601</v>
+        <v>585</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>602</v>
+        <v>586</v>
       </c>
     </row>
   </sheetData>
@@ -24083,54 +24083,54 @@
   <sheetData>
     <row r="1" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>610</v>
+        <v>594</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>611</v>
+        <v>595</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>612</v>
+        <v>596</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>613</v>
+        <v>597</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -24356,132 +24356,132 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>615</v>
+        <v>599</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>614</v>
+        <v>598</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>616</v>
+        <v>600</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>617</v>
+        <v>601</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>618</v>
+        <v>602</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>619</v>
+        <v>603</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>620</v>
+        <v>604</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>621</v>
+        <v>605</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>622</v>
+        <v>606</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>623</v>
+        <v>607</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>624</v>
+        <v>608</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>625</v>
+        <v>609</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>626</v>
+        <v>610</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>627</v>
+        <v>611</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>628</v>
+        <v>612</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>629</v>
+        <v>613</v>
       </c>
     </row>
     <row r="7" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>630</v>
+        <v>614</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>631</v>
+        <v>615</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>632</v>
+        <v>616</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>633</v>
+        <v>617</v>
       </c>
     </row>
   </sheetData>
@@ -24507,285 +24507,285 @@
   <sheetData>
     <row r="1" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
     </row>
     <row r="2" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>648</v>
+        <v>632</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>649</v>
+        <v>633</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>650</v>
+        <v>634</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>651</v>
+        <v>635</v>
       </c>
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>652</v>
+        <v>636</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>653</v>
+        <v>637</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>654</v>
+        <v>638</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>655</v>
+        <v>639</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="8" t="s">
-        <v>656</v>
+        <v>640</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>657</v>
+        <v>641</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>658</v>
+        <v>642</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>659</v>
+        <v>643</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>660</v>
+        <v>644</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>661</v>
+        <v>645</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>662</v>
+        <v>646</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>663</v>
+        <v>647</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>664</v>
+        <v>648</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>665</v>
+        <v>649</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>666</v>
+        <v>650</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>667</v>
+        <v>651</v>
       </c>
     </row>
     <row r="7" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>668</v>
+        <v>652</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>669</v>
+        <v>653</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>670</v>
+        <v>654</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>671</v>
+        <v>655</v>
       </c>
     </row>
     <row r="8" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>672</v>
+        <v>656</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>673</v>
+        <v>657</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>674</v>
+        <v>658</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>675</v>
+        <v>659</v>
       </c>
     </row>
     <row r="9" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>676</v>
+        <v>660</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>677</v>
+        <v>661</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>678</v>
+        <v>662</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>679</v>
+        <v>663</v>
       </c>
     </row>
     <row r="10" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>681</v>
+        <v>665</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>680</v>
+        <v>664</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>682</v>
+        <v>666</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>683</v>
+        <v>667</v>
       </c>
     </row>
     <row r="11" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>645</v>
+        <v>629</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>646</v>
+        <v>630</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>647</v>
+        <v>631</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="H11" s="11"/>
       <c r="I11"/>
@@ -25027,71 +25027,71 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -25110,64 +25110,64 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -25186,78 +25186,78 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -25277,71 +25277,71 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>112</v>
+        <v>98</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -25361,92 +25361,92 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>

--- a/testdata.xlsx
+++ b/testdata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sshiwani\workspace\find-information-products-services-tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3F0D659-6032-43B9-81B8-4909DFB63D94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F0CE05E-F74F-4ABB-A383-B2976520B645}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="22780" windowHeight="14540" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="category_phase" sheetId="1" r:id="rId1"/>
@@ -200,9 +200,6 @@
     <t>products?type=api</t>
   </si>
   <si>
-    <t>ul.moj-filter-tags li a:has-text('API')</t>
-  </si>
-  <si>
     <t>Remove this filter API</t>
   </si>
   <si>
@@ -215,9 +212,6 @@
     <t>products?type=campaign</t>
   </si>
   <si>
-    <t>ul.moj-filter-tags li a:has-text('Campaign')</t>
-  </si>
-  <si>
     <t>Remove this filter Campaign</t>
   </si>
   <si>
@@ -227,9 +221,6 @@
     <t>products?type=information</t>
   </si>
   <si>
-    <t>ul.moj-filter-tags li a:has-text(' Information')</t>
-  </si>
-  <si>
     <t>Remove this filter Information</t>
   </si>
   <si>
@@ -239,9 +230,6 @@
     <t>products?type=transactional</t>
   </si>
   <si>
-    <t>ul.moj-filter-tags li a:has-text(' Transactional')</t>
-  </si>
-  <si>
     <t>Remove this filter Transactional</t>
   </si>
   <si>
@@ -1001,12 +989,6 @@
     <t>#group-commercial</t>
   </si>
   <si>
-    <t>products?type=data-collection-and-reporting</t>
-  </si>
-  <si>
-    <t>ul.moj-filter-tags li a:has-text(' Data collection and reporting')</t>
-  </si>
-  <si>
     <t>Remove this filter Data collection and reporting</t>
   </si>
   <si>
@@ -2238,6 +2220,24 @@
   </si>
   <si>
     <t>Decommissioned × Remove Decommissioned filter</t>
+  </si>
+  <si>
+    <t>a.filter-badge:has(span:text-is('API'))</t>
+  </si>
+  <si>
+    <t>a.filter-badge:has(span:text-is('Campaign'))</t>
+  </si>
+  <si>
+    <t>products?type=data</t>
+  </si>
+  <si>
+    <t>a.filter-badge:has(span:text-is('Data'))</t>
+  </si>
+  <si>
+    <t>a.filter-badge:has(span:text-is('Information'))</t>
+  </si>
+  <si>
+    <t>a.filter-badge:has(span:text-is('Transactional'))</t>
   </si>
 </sst>
 </file>
@@ -2714,10 +2714,10 @@
         <v>2</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>708</v>
+        <v>702</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>716</v>
+        <v>710</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
@@ -3877,10 +3877,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>709</v>
+        <v>703</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>717</v>
+        <v>711</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
@@ -5037,13 +5037,13 @@
     </row>
     <row r="4" spans="1:1149" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>710</v>
+        <v>704</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
@@ -5052,7 +5052,7 @@
         <v>1</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="G4"/>
       <c r="H4"/>
@@ -6203,10 +6203,10 @@
         <v>6</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>711</v>
+        <v>705</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>719</v>
+        <v>713</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
@@ -7366,10 +7366,10 @@
         <v>8</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>720</v>
+        <v>714</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>10</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>721</v>
+        <v>715</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>0</v>
@@ -9692,10 +9692,10 @@
         <v>12</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>714</v>
+        <v>708</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>0</v>
@@ -10855,10 +10855,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>715</v>
+        <v>709</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>723</v>
+        <v>717</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>0</v>
@@ -12030,64 +12030,64 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -12107,78 +12107,78 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -12199,78 +12199,78 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -12290,99 +12290,99 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -12402,85 +12402,85 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
     </row>
   </sheetData>
@@ -12500,99 +12500,99 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
     </row>
   </sheetData>
@@ -12612,80 +12612,80 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -12707,115 +12707,115 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -12837,66 +12837,66 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>518</v>
+        <v>512</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>519</v>
+        <v>513</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -12918,52 +12918,52 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>536</v>
+        <v>530</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -13011,10 +13011,10 @@
         <v>22</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>668</v>
+        <v>662</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>677</v>
+        <v>671</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
@@ -13081,10 +13081,10 @@
         <v>25</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>669</v>
+        <v>663</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
@@ -13151,10 +13151,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>670</v>
+        <v>664</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>679</v>
+        <v>673</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
@@ -13221,10 +13221,10 @@
         <v>29</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>671</v>
+        <v>665</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>680</v>
+        <v>674</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
@@ -13291,10 +13291,10 @@
         <v>31</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>672</v>
+        <v>666</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>681</v>
+        <v>675</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>0</v>
@@ -13361,10 +13361,10 @@
         <v>33</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>673</v>
+        <v>667</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>682</v>
+        <v>676</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>0</v>
@@ -13431,10 +13431,10 @@
         <v>35</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>683</v>
+        <v>677</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>0</v>
@@ -13501,10 +13501,10 @@
         <v>37</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>675</v>
+        <v>669</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>684</v>
+        <v>678</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>0</v>
@@ -13571,10 +13571,10 @@
         <v>39</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>676</v>
+        <v>670</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>0</v>
@@ -13653,66 +13653,66 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -13734,66 +13734,66 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>566</v>
+        <v>560</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>567</v>
+        <v>561</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>569</v>
+        <v>563</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>570</v>
+        <v>564</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -13815,80 +13815,80 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>587</v>
+        <v>581</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>588</v>
+        <v>582</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>589</v>
+        <v>583</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>591</v>
+        <v>585</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>593</v>
+        <v>587</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -13910,108 +13910,108 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>618</v>
+        <v>612</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>619</v>
+        <v>613</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>620</v>
+        <v>614</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>621</v>
+        <v>615</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>622</v>
+        <v>616</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>623</v>
+        <v>617</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>624</v>
+        <v>618</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>627</v>
+        <v>621</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>628</v>
+        <v>622</v>
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -14056,36 +14056,36 @@
         <v>21</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -14311,106 +14311,106 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
     </row>
   </sheetData>
@@ -14454,36 +14454,36 @@
         <v>21</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -14709,80 +14709,80 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
     </row>
   </sheetData>
@@ -14825,36 +14825,36 @@
         <v>21</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -15080,132 +15080,132 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
     </row>
     <row r="7" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
     </row>
   </sheetData>
@@ -15249,36 +15249,36 @@
         <v>21</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -15504,106 +15504,106 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
     </row>
   </sheetData>
@@ -15646,36 +15646,36 @@
         <v>21</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -15901,80 +15901,80 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
     </row>
   </sheetData>
@@ -16017,36 +16017,36 @@
         <v>21</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -16272,132 +16272,132 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
     </row>
     <row r="7" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
     </row>
   </sheetData>
@@ -16440,82 +16440,82 @@
     </row>
     <row r="2" spans="1:1029" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>686</v>
+        <v>680</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>697</v>
+        <v>691</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
     </row>
     <row r="3" spans="1:1029" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>698</v>
+        <v>692</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
     </row>
     <row r="4" spans="1:1029" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>700</v>
+        <v>694</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:1029" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>689</v>
+        <v>683</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>699</v>
+        <v>693</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="G5"/>
       <c r="H5"/>
@@ -17543,22 +17543,22 @@
     </row>
     <row r="6" spans="1:1029" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>690</v>
+        <v>684</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>701</v>
+        <v>695</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
     </row>
     <row r="7" spans="1:1029" x14ac:dyDescent="0.35">
@@ -17566,16 +17566,16 @@
         <v>41</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>691</v>
+        <v>685</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>42</v>
@@ -17583,22 +17583,22 @@
     </row>
     <row r="8" spans="1:1029" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>692</v>
+        <v>686</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>703</v>
+        <v>697</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="G8"/>
       <c r="H8"/>
@@ -18626,82 +18626,82 @@
     </row>
     <row r="9" spans="1:1029" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>704</v>
+        <v>698</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
     </row>
     <row r="10" spans="1:1029" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>694</v>
+        <v>688</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>705</v>
+        <v>699</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
     </row>
     <row r="11" spans="1:1029" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>695</v>
+        <v>689</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>706</v>
+        <v>700</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
     </row>
     <row r="12" spans="1:1029" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>696</v>
+        <v>690</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>707</v>
+        <v>701</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -18744,36 +18744,36 @@
         <v>21</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -18999,132 +18999,132 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
     </row>
     <row r="7" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
     </row>
   </sheetData>
@@ -19167,36 +19167,36 @@
         <v>21</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -19422,210 +19422,210 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
     </row>
     <row r="7" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
     </row>
     <row r="8" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
     </row>
     <row r="9" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="10" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
     </row>
   </sheetData>
@@ -19669,36 +19669,36 @@
         <v>21</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -19924,158 +19924,158 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
     </row>
     <row r="7" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
     </row>
     <row r="8" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A8" s="9" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
     </row>
   </sheetData>
@@ -20119,36 +20119,36 @@
         <v>21</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -20374,184 +20374,184 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
     </row>
     <row r="7" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
     </row>
     <row r="8" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
     </row>
     <row r="9" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
     </row>
   </sheetData>
@@ -20595,36 +20595,36 @@
         <v>21</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -20850,132 +20850,132 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
     </row>
     <row r="7" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
     </row>
   </sheetData>
@@ -21018,36 +21018,36 @@
         <v>21</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -21311,36 +21311,36 @@
         <v>21</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -21566,262 +21566,262 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
     </row>
     <row r="7" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
     </row>
     <row r="8" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
     </row>
     <row r="9" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>501</v>
+        <v>495</v>
       </c>
     </row>
     <row r="10" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
     </row>
     <row r="11" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
     </row>
     <row r="12" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>512</v>
+        <v>506</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>513</v>
+        <v>507</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
     </row>
   </sheetData>
@@ -21865,36 +21865,36 @@
         <v>21</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>520</v>
+        <v>514</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>521</v>
+        <v>515</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -22120,78 +22120,78 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>527</v>
+        <v>521</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="11" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="D4" s="11" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H4" s="11"/>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
     </row>
   </sheetData>
@@ -22234,36 +22234,36 @@
         <v>21</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -22489,28 +22489,28 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
     </row>
   </sheetData>
@@ -22553,33 +22553,33 @@
         <v>21</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="11" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>553</v>
+        <v>547</v>
       </c>
       <c r="D2" s="11" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H2" s="11"/>
       <c r="I2"/>
@@ -22806,80 +22806,80 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>557</v>
+        <v>551</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>558</v>
+        <v>552</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>559</v>
+        <v>553</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>561</v>
+        <v>555</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>562</v>
+        <v>556</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>563</v>
+        <v>557</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>564</v>
+        <v>558</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>565</v>
+        <v>559</v>
       </c>
     </row>
   </sheetData>
@@ -22926,19 +22926,19 @@
         <v>43</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>718</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>44</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>45</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>46</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="G2"/>
       <c r="H2"/>
@@ -23166,22 +23166,22 @@
     </row>
     <row r="3" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G3"/>
       <c r="H3"/>
@@ -23409,22 +23409,22 @@
     </row>
     <row r="4" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>311</v>
+        <v>720</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>312</v>
+        <v>721</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="G4"/>
       <c r="H4"/>
@@ -23652,42 +23652,42 @@
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>53</v>
+        <v>722</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>57</v>
+        <v>723</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -23730,36 +23730,36 @@
         <v>21</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>572</v>
+        <v>566</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>573</v>
+        <v>567</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>574</v>
+        <v>568</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -23985,80 +23985,80 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>575</v>
+        <v>569</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>576</v>
+        <v>570</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>577</v>
+        <v>571</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>578</v>
+        <v>572</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>580</v>
+        <v>574</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>579</v>
+        <v>573</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>581</v>
+        <v>575</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>582</v>
+        <v>576</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>583</v>
+        <v>577</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>584</v>
+        <v>578</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>585</v>
+        <v>579</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>586</v>
+        <v>580</v>
       </c>
     </row>
   </sheetData>
@@ -24101,36 +24101,36 @@
         <v>21</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
     </row>
     <row r="2" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>596</v>
+        <v>590</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>597</v>
+        <v>591</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -24356,132 +24356,132 @@
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>599</v>
+        <v>593</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>598</v>
+        <v>592</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>600</v>
+        <v>594</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>601</v>
+        <v>595</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>602</v>
+        <v>596</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>603</v>
+        <v>597</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>605</v>
+        <v>599</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>607</v>
+        <v>601</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>608</v>
+        <v>602</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>609</v>
+        <v>603</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>610</v>
+        <v>604</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>612</v>
+        <v>606</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>613</v>
+        <v>607</v>
       </c>
     </row>
     <row r="7" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>614</v>
+        <v>608</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>615</v>
+        <v>609</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>616</v>
+        <v>610</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>617</v>
+        <v>611</v>
       </c>
     </row>
   </sheetData>
@@ -24525,267 +24525,267 @@
         <v>21</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
     </row>
     <row r="2" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>632</v>
+        <v>626</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>633</v>
+        <v>627</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>635</v>
+        <v>629</v>
       </c>
     </row>
     <row r="3" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>636</v>
+        <v>630</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>637</v>
+        <v>631</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>638</v>
+        <v>632</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
     </row>
     <row r="4" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A4" s="8" t="s">
-        <v>640</v>
+        <v>634</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>641</v>
+        <v>635</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>642</v>
+        <v>636</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>643</v>
+        <v>637</v>
       </c>
     </row>
     <row r="5" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>644</v>
+        <v>638</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>645</v>
+        <v>639</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>646</v>
+        <v>640</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>647</v>
+        <v>641</v>
       </c>
     </row>
     <row r="6" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>648</v>
+        <v>642</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>649</v>
+        <v>643</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>650</v>
+        <v>644</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>651</v>
+        <v>645</v>
       </c>
     </row>
     <row r="7" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>653</v>
+        <v>647</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>654</v>
+        <v>648</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>655</v>
+        <v>649</v>
       </c>
     </row>
     <row r="8" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>656</v>
+        <v>650</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>657</v>
+        <v>651</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>658</v>
+        <v>652</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>659</v>
+        <v>653</v>
       </c>
     </row>
     <row r="9" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>660</v>
+        <v>654</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>661</v>
+        <v>655</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>662</v>
+        <v>656</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>0</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>663</v>
+        <v>657</v>
       </c>
     </row>
     <row r="10" spans="1:229" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>665</v>
+        <v>659</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>664</v>
+        <v>658</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>666</v>
+        <v>660</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>667</v>
+        <v>661</v>
       </c>
     </row>
     <row r="11" spans="1:229" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>629</v>
+        <v>623</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>630</v>
+        <v>624</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>631</v>
+        <v>625</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>0</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H11" s="11"/>
       <c r="I11"/>
@@ -25027,71 +25027,71 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -25110,64 +25110,64 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -25186,78 +25186,78 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -25277,71 +25277,71 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -25361,92 +25361,92 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>

--- a/testdata.xlsx
+++ b/testdata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sshiwani\workspace\find-information-products-services-tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F0CE05E-F74F-4ABB-A383-B2976520B645}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{133063DD-EEAB-4A47-98C6-66EBCA11B111}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="22780" windowHeight="14540" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="category_phase" sheetId="1" r:id="rId1"/>
@@ -200,9 +200,6 @@
     <t>products?type=api</t>
   </si>
   <si>
-    <t>Remove this filter API</t>
-  </si>
-  <si>
     <t>//h3[normalize-space()='Type']</t>
   </si>
   <si>
@@ -212,27 +209,18 @@
     <t>products?type=campaign</t>
   </si>
   <si>
-    <t>Remove this filter Campaign</t>
-  </si>
-  <si>
     <t>#type-campaign</t>
   </si>
   <si>
     <t>products?type=information</t>
   </si>
   <si>
-    <t>Remove this filter Information</t>
-  </si>
-  <si>
     <t>#type-information</t>
   </si>
   <si>
     <t>products?type=transactional</t>
   </si>
   <si>
-    <t>Remove this filter Transactional</t>
-  </si>
-  <si>
     <t>#type-transactional</t>
   </si>
   <si>
@@ -989,12 +977,6 @@
     <t>#group-commercial</t>
   </si>
   <si>
-    <t>Remove this filter Data collection and reporting</t>
-  </si>
-  <si>
-    <t>#type-data-collection-and-reporting</t>
-  </si>
-  <si>
     <t>products?userGroup=parent-or-carer</t>
   </si>
   <si>
@@ -2238,6 +2220,24 @@
   </si>
   <si>
     <t>a.filter-badge:has(span:text-is('Transactional'))</t>
+  </si>
+  <si>
+    <t>API × Remove API filter</t>
+  </si>
+  <si>
+    <t>Campaign × Remove Campaign filter</t>
+  </si>
+  <si>
+    <t>Data    × Remove Data    filter</t>
+  </si>
+  <si>
+    <t>Information × Remove Information filter</t>
+  </si>
+  <si>
+    <t>Transactional × Remove Transactional filter</t>
+  </si>
+  <si>
+    <t>#type-data</t>
   </si>
 </sst>
 </file>
@@ -2714,10 +2714,10 @@
         <v>2</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>710</v>
+        <v>704</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>0</v>
@@ -3877,10 +3877,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>703</v>
+        <v>697</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>711</v>
+        <v>705</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>0</v>
@@ -5037,13 +5037,13 @@
     </row>
     <row r="4" spans="1:1149" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>704</v>
+        <v>698</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>0</v>
@@ -5052,7 +5052,7 @@
         <v>1</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="G4"/>
       <c r="H4"/>
@@ -6203,10 +6203,10 @@
         <v>6</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>705</v>
+        <v>699</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>0</v>
@@ -7366,10 +7366,10 @@
         <v>8</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>706</v>
+        <v>700</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>714</v>
+        <v>708</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>10</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>707</v>
+        <v>701</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>715</v>
+        <v>709</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>0</v>
@@ -9692,10 +9692,10 @@
         <v>12</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>708</v>
+        <v>702</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>716</v>
+        <v>710</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>0</v>
@@ -10855,10 +10855,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>709</v>
+        <v>703</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>717</v>
+        <v>711</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>0</v>
@@ -12030,64 +12030,64 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B5" s="3"/>
       <c r="